--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1824,11 +1824,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1580326454"/>
-        <c:axId val="594287334"/>
+        <c:axId val="964096663"/>
+        <c:axId val="1518513051"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1580326454"/>
+        <c:axId val="964096663"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1880,10 +1880,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="594287334"/>
+        <c:crossAx val="1518513051"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="594287334"/>
+        <c:axId val="1518513051"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1947,7 +1947,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1580326454"/>
+        <c:crossAx val="964096663"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2151,12 +2151,13 @@
         <n v="2842.53"/>
         <n v="98.98"/>
         <n v="120.75"/>
-        <n v="113.31"/>
+        <n v="113.8"/>
         <n v="530.0"/>
         <n v="1500.0"/>
         <n v="195.0"/>
         <n v="95.05"/>
         <n v="7200.0"/>
+        <n v="113.31"/>
         <n v="580.0"/>
         <n v="930.0"/>
         <n v="6800.0"/>
@@ -2316,6 +2317,7 @@
         <item x="91"/>
         <item x="92"/>
         <item x="93"/>
+        <item x="94"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4007,8 +4009,8 @@
       <c r="B69" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C69" s="9">
-        <v>113.31</v>
+      <c r="C69" s="19">
+        <v>113.8</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>7</v>
@@ -10734,7 +10736,7 @@
       </c>
       <c r="K3" s="51">
         <f>SUM(B4:B123)</f>
-        <v>210357.36</v>
+        <v>210357.85</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>114</v>
@@ -10813,7 +10815,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>15343.61</v>
+        <v>15343.12</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -10823,7 +10825,7 @@
       </c>
       <c r="B6" s="53">
         <f>IF($A6="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
-        <v>20003.24</v>
+        <v>20003.73</v>
       </c>
       <c r="C6" s="53">
         <f>IF($A6="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A6,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -10831,7 +10833,7 @@
       </c>
       <c r="D6" s="53">
         <f t="shared" si="1"/>
-        <v>-2170.86</v>
+        <v>-2171.35</v>
       </c>
       <c r="E6" s="54">
         <f>IF($A6="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -10843,14 +10845,14 @@
       </c>
       <c r="G6" s="53">
         <f t="shared" si="2"/>
-        <v>15343.61</v>
+        <v>15343.12</v>
       </c>
       <c r="J6" s="50" t="s">
         <v>117</v>
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>1442.05</v>
+        <v>1441.56</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -10880,14 +10882,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>17389.5</v>
+        <v>17389.01</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>118</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>-2170.86</v>
+        <v>-2171.35</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -10917,14 +10919,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>18025.32</v>
+        <v>18024.83</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>119</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>103.0035714</v>
+        <v>102.9685714</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -10954,14 +10956,14 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>17441.14</v>
+        <v>17440.65</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>120</v>
       </c>
       <c r="K9" s="51">
         <f>MAX(B4:B123)</f>
-        <v>20003.24</v>
+        <v>20003.73</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -10991,7 +10993,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>16296.96</v>
+        <v>16296.47</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>121</v>
@@ -11028,7 +11030,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14502.78</v>
+        <v>14502.29</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>122</v>
@@ -11065,7 +11067,7 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>13108.8</v>
+        <v>13108.31</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>123</v>
@@ -11102,7 +11104,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>12214.62</v>
+        <v>12214.13</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11132,7 +11134,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7800.44</v>
+        <v>7799.95</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11163,7 +11165,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7891.59</v>
+        <v>7891.1</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11193,7 +11195,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4835.64</v>
+        <v>4835.15</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11223,7 +11225,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>1442.05</v>
+        <v>1441.56</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1824,11 +1824,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="964096663"/>
-        <c:axId val="1518513051"/>
+        <c:axId val="923462904"/>
+        <c:axId val="584998742"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="964096663"/>
+        <c:axId val="923462904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1880,10 +1880,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1518513051"/>
+        <c:crossAx val="584998742"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1518513051"/>
+        <c:axId val="584998742"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1947,7 +1947,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="964096663"/>
+        <c:crossAx val="923462904"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -19,14 +19,14 @@
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="Iv/9GyEIl/Fo9N+ijCjXHohDzNVAWsoraoYr+HOnk+k="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="eeNxZXef6w87iQJZpyoGEb5PkCaLzxxlQV/POc07mbg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="418">
   <si>
     <t>Data</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>Lote 5680 mar.</t>
-  </si>
-  <si>
-    <t>Resumo mensal automático</t>
   </si>
   <si>
     <t>Último mês com dados</t>
@@ -1830,11 +1827,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="134430318"/>
-        <c:axId val="968189263"/>
+        <c:axId val="1498902442"/>
+        <c:axId val="427643584"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="134430318"/>
+        <c:axId val="1498902442"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1886,10 +1883,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="968189263"/>
+        <c:crossAx val="427643584"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="968189263"/>
+        <c:axId val="427643584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,7 +1950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="134430318"/>
+        <c:crossAx val="1498902442"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -10730,9 +10727,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="43" t="s">
-        <v>105</v>
-      </c>
+      <c r="A1" s="43"/>
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
       <c r="D1" s="44"/>
@@ -10744,12 +10739,12 @@
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
       <c r="M1" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="J2" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K2" s="47"/>
       <c r="M2" s="48">
@@ -10759,35 +10754,35 @@
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="C3" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="F3" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="G3" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="J3" s="50" t="s">
         <v>114</v>
-      </c>
-      <c r="J3" s="50" t="s">
-        <v>115</v>
       </c>
       <c r="K3" s="51">
         <f>SUM(B4:B123)</f>
         <v>210817.85</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
@@ -10819,7 +10814,7 @@
         <v>18328.09</v>
       </c>
       <c r="J4" s="50" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K4" s="51">
         <f>SUM(C4:C123)</f>
@@ -10859,7 +10854,7 @@
         <v>17514.47</v>
       </c>
       <c r="J5" s="50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
@@ -10896,7 +10891,7 @@
         <v>14883.12</v>
       </c>
       <c r="J6" s="50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K6" s="51">
         <f>G17</f>
@@ -10933,7 +10928,7 @@
         <v>16929.01</v>
       </c>
       <c r="J7" s="50" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
@@ -10970,7 +10965,7 @@
         <v>17564.83</v>
       </c>
       <c r="J8" s="50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
@@ -11007,7 +11002,7 @@
         <v>16980.65</v>
       </c>
       <c r="J9" s="50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K9" s="51">
         <f>MAX(B4:B123)</f>
@@ -11044,7 +11039,7 @@
         <v>15836.47</v>
       </c>
       <c r="J10" s="50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K10" s="51">
         <f>MAX(C4:C123)</f>
@@ -11081,7 +11076,7 @@
         <v>14042.29</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K11" s="58" t="str">
         <f>TEXT(A4,"mmm/yy")&amp;" a "&amp;TEXT($M$2,"mmm/yy")</f>
@@ -11118,7 +11113,7 @@
         <v>12648.31</v>
       </c>
       <c r="J12" s="50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K12" s="58" t="str">
         <f>TEXT(TODAY(),"mmm/yy")</f>
@@ -15377,156 +15372,156 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="C1" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="D1" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="E1" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="F1" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="G1" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="H1" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="I1" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="I1" s="60" t="s">
+      <c r="J1" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="K1" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="K1" s="60" t="s">
+      <c r="L1" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="L1" s="60" t="s">
+      <c r="M1" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="M1" s="60" t="s">
+      <c r="N1" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="N1" s="60" t="s">
+      <c r="O1" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="O1" s="60" t="s">
+      <c r="P1" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="P1" s="60" t="s">
+      <c r="Q1" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="60" t="s">
+      <c r="R1" s="60" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="60" t="s">
+      <c r="S1" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="S1" s="60" t="s">
+      <c r="T1" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="T1" s="60" t="s">
+      <c r="U1" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="U1" s="60" t="s">
+      <c r="V1" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="V1" s="60" t="s">
+      <c r="W1" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="W1" s="60" t="s">
+      <c r="X1" s="60" t="s">
         <v>148</v>
       </c>
-      <c r="X1" s="60" t="s">
+      <c r="Y1" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="Y1" s="60" t="s">
+      <c r="Z1" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="Z1" s="60" t="s">
+      <c r="AA1" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="AA1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AC1" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="AC1" s="61" t="s">
+      <c r="AD1" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="AD1" s="61" t="s">
+      <c r="AE1" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="AE1" s="61" t="s">
+      <c r="AF1" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="AF1" s="61" t="s">
+      <c r="AG1" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="AG1" s="61" t="s">
+      <c r="AH1" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="AH1" s="61" t="s">
+      <c r="AI1" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="AI1" s="61" t="s">
+      <c r="AJ1" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="AJ1" s="61" t="s">
+      <c r="AK1" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="AK1" s="61" t="s">
+      <c r="AL1" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="AL1" s="62" t="s">
+      <c r="AM1" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="AM1" s="62" t="s">
+      <c r="AN1" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="AN1" s="62" t="s">
+      <c r="AO1" s="62" t="s">
         <v>165</v>
       </c>
-      <c r="AO1" s="62" t="s">
+      <c r="AP1" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="AP1" s="62" t="s">
+      <c r="AQ1" s="62" t="s">
         <v>167</v>
       </c>
-      <c r="AQ1" s="62" t="s">
+      <c r="AR1" s="62" t="s">
         <v>168</v>
       </c>
-      <c r="AR1" s="62" t="s">
+      <c r="AS1" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="AS1" s="62" t="s">
+      <c r="AT1" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="AT1" s="62" t="s">
+      <c r="AU1" s="62" t="s">
         <v>171</v>
       </c>
-      <c r="AU1" s="62" t="s">
+      <c r="AV1" s="62" t="s">
         <v>172</v>
       </c>
-      <c r="AV1" s="62" t="s">
+      <c r="AW1" s="62" t="s">
         <v>173</v>
-      </c>
-      <c r="AW1" s="62" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2" s="63">
         <v>266.87</v>
@@ -15544,56 +15539,56 @@
         <v>17.0</v>
       </c>
       <c r="G2" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H2" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I2" s="64"/>
       <c r="J2" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K2" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L2" s="65"/>
       <c r="M2" s="65"/>
       <c r="N2" s="65"/>
       <c r="O2" s="65"/>
       <c r="P2" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q2" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="R2" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="S2" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="R2" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="S2" s="42" t="s">
+      <c r="T2" s="42" t="s">
         <v>181</v>
-      </c>
-      <c r="T2" s="42" t="s">
-        <v>182</v>
       </c>
       <c r="U2" s="64"/>
       <c r="V2" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W2" s="64"/>
       <c r="X2" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y2" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y2" s="67" t="s">
+      <c r="Z2" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z2" s="66" t="s">
+      <c r="AA2" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB2" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA2" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB2" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC2" s="69">
         <v>25.0</v>
@@ -15635,10 +15630,10 @@
         <v>181.0</v>
       </c>
       <c r="AP2" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ2" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="AQ2" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="AR2" s="70">
         <v>0.0</v>
@@ -15661,7 +15656,7 @@
     </row>
     <row r="3">
       <c r="A3" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="63">
         <v>100.0</v>
@@ -15679,56 +15674,56 @@
         <v>90.0</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I3" s="64"/>
       <c r="J3" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L3" s="64"/>
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
       <c r="P3" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q3" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="R3" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S3" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="R3" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S3" s="42" t="s">
+      <c r="T3" s="72" t="s">
         <v>194</v>
-      </c>
-      <c r="T3" s="72" t="s">
-        <v>195</v>
       </c>
       <c r="U3" s="64"/>
       <c r="V3" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W3" s="64"/>
       <c r="X3" s="66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y3" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z3" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA3" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB3" s="68" t="s">
         <v>196</v>
-      </c>
-      <c r="Z3" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA3" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB3" s="68" t="s">
-        <v>197</v>
       </c>
       <c r="AC3" s="69">
         <v>45.0</v>
@@ -15766,10 +15761,10 @@
         <v>90.0</v>
       </c>
       <c r="AP3" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ3" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ3" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR3" s="75"/>
       <c r="AS3" s="74"/>
@@ -15780,7 +15775,7 @@
     </row>
     <row r="4">
       <c r="A4" s="42" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" s="63">
         <v>100.0</v>
@@ -15798,56 +15793,56 @@
         <v>180.0</v>
       </c>
       <c r="G4" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H4" s="63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I4" s="64"/>
       <c r="J4" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K4" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L4" s="64"/>
       <c r="M4" s="64"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
       <c r="P4" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q4" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="R4" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S4" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="R4" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S4" s="42" t="s">
+      <c r="T4" s="72" t="s">
         <v>194</v>
-      </c>
-      <c r="T4" s="72" t="s">
-        <v>195</v>
       </c>
       <c r="U4" s="64"/>
       <c r="V4" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W4" s="64"/>
       <c r="X4" s="66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y4" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z4" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA4" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB4" s="68" t="s">
         <v>196</v>
-      </c>
-      <c r="Z4" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA4" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB4" s="68" t="s">
-        <v>197</v>
       </c>
       <c r="AC4" s="69">
         <v>45.0</v>
@@ -15885,10 +15880,10 @@
         <v>180.0</v>
       </c>
       <c r="AP4" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ4" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ4" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR4" s="75"/>
       <c r="AS4" s="74"/>
@@ -15899,7 +15894,7 @@
     </row>
     <row r="5">
       <c r="A5" s="42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B5" s="63">
         <v>109.0</v>
@@ -15917,56 +15912,56 @@
         <v>365.0</v>
       </c>
       <c r="G5" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H5" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I5" s="64"/>
       <c r="J5" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K5" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L5" s="65"/>
       <c r="M5" s="65"/>
       <c r="N5" s="65"/>
       <c r="O5" s="65"/>
       <c r="P5" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q5" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R5" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S5" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="T5" s="42" t="s">
         <v>202</v>
-      </c>
-      <c r="T5" s="42" t="s">
-        <v>203</v>
       </c>
       <c r="U5" s="64"/>
       <c r="V5" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W5" s="64"/>
       <c r="X5" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y5" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y5" s="67" t="s">
+      <c r="Z5" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z5" s="66" t="s">
+      <c r="AA5" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB5" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA5" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB5" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC5" s="69">
         <v>25.0</v>
@@ -16008,10 +16003,10 @@
         <v>365.0</v>
       </c>
       <c r="AP5" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ5" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ5" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR5" s="70">
         <v>2.0</v>
@@ -16034,7 +16029,7 @@
     </row>
     <row r="6">
       <c r="A6" s="42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B6" s="63">
         <v>110.0</v>
@@ -16052,56 +16047,56 @@
         <v>2190.0</v>
       </c>
       <c r="G6" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H6" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H6" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I6" s="64"/>
       <c r="J6" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K6" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L6" s="65"/>
       <c r="M6" s="65"/>
       <c r="N6" s="65"/>
       <c r="O6" s="65"/>
       <c r="P6" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q6" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R6" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S6" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T6" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U6" s="64"/>
       <c r="V6" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W6" s="64"/>
       <c r="X6" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y6" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y6" s="67" t="s">
+      <c r="Z6" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z6" s="66" t="s">
+      <c r="AA6" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB6" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA6" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB6" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC6" s="69">
         <v>10.0</v>
@@ -16143,10 +16138,10 @@
         <v>2190.0</v>
       </c>
       <c r="AP6" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ6" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ6" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR6" s="70">
         <v>5.0</v>
@@ -16169,7 +16164,7 @@
     </row>
     <row r="7">
       <c r="A7" s="42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B7" s="63">
         <v>111.0</v>
@@ -16187,56 +16182,56 @@
         <v>730.0</v>
       </c>
       <c r="G7" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H7" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I7" s="64"/>
       <c r="J7" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K7" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L7" s="65"/>
       <c r="M7" s="65"/>
       <c r="N7" s="65"/>
       <c r="O7" s="65"/>
       <c r="P7" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q7" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R7" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S7" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T7" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U7" s="64"/>
       <c r="V7" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W7" s="64"/>
       <c r="X7" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y7" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y7" s="67" t="s">
+      <c r="Z7" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z7" s="66" t="s">
+      <c r="AA7" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB7" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA7" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB7" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC7" s="69">
         <v>10.0</v>
@@ -16278,10 +16273,10 @@
         <v>730.0</v>
       </c>
       <c r="AP7" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ7" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ7" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR7" s="70">
         <v>3.0</v>
@@ -16304,7 +16299,7 @@
     </row>
     <row r="8">
       <c r="A8" s="42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B8" s="63">
         <v>112.0</v>
@@ -16322,56 +16317,56 @@
         <v>1095.0</v>
       </c>
       <c r="G8" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H8" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I8" s="64"/>
       <c r="J8" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L8" s="65"/>
       <c r="M8" s="65"/>
       <c r="N8" s="65"/>
       <c r="O8" s="65"/>
       <c r="P8" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q8" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R8" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S8" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T8" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U8" s="64"/>
       <c r="V8" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W8" s="64"/>
       <c r="X8" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y8" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y8" s="67" t="s">
+      <c r="Z8" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z8" s="66" t="s">
+      <c r="AA8" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB8" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA8" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB8" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC8" s="69">
         <v>10.0</v>
@@ -16413,10 +16408,10 @@
         <v>1095.0</v>
       </c>
       <c r="AP8" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ8" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ8" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR8" s="70">
         <v>3.0</v>
@@ -16439,7 +16434,7 @@
     </row>
     <row r="9">
       <c r="A9" s="42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B9" s="63">
         <v>113.0</v>
@@ -16457,56 +16452,56 @@
         <v>1460.0</v>
       </c>
       <c r="G9" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H9" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I9" s="64"/>
       <c r="J9" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K9" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L9" s="65"/>
       <c r="M9" s="65"/>
       <c r="N9" s="65"/>
       <c r="O9" s="65"/>
       <c r="P9" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q9" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R9" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S9" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T9" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U9" s="64"/>
       <c r="V9" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W9" s="64"/>
       <c r="X9" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y9" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y9" s="67" t="s">
+      <c r="Z9" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z9" s="66" t="s">
+      <c r="AA9" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB9" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA9" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB9" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC9" s="69">
         <v>10.0</v>
@@ -16548,10 +16543,10 @@
         <v>1460.0</v>
       </c>
       <c r="AP9" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ9" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ9" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR9" s="70">
         <v>3.0</v>
@@ -16574,7 +16569,7 @@
     </row>
     <row r="10">
       <c r="A10" s="42" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B10" s="63">
         <v>114.0</v>
@@ -16592,56 +16587,56 @@
         <v>1825.0</v>
       </c>
       <c r="G10" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H10" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H10" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I10" s="64"/>
       <c r="J10" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L10" s="65"/>
       <c r="M10" s="65"/>
       <c r="N10" s="65"/>
       <c r="O10" s="65"/>
       <c r="P10" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q10" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R10" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S10" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T10" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U10" s="64"/>
       <c r="V10" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W10" s="64"/>
       <c r="X10" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y10" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y10" s="67" t="s">
+      <c r="Z10" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z10" s="66" t="s">
+      <c r="AA10" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB10" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA10" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB10" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC10" s="69">
         <v>10.0</v>
@@ -16683,10 +16678,10 @@
         <v>1825.0</v>
       </c>
       <c r="AP10" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ10" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ10" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR10" s="70">
         <v>2.0</v>
@@ -16709,7 +16704,7 @@
     </row>
     <row r="11">
       <c r="A11" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B11" s="63">
         <v>108.0</v>
@@ -16727,56 +16722,56 @@
         <v>1095.0</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H11" s="72" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I11" s="64"/>
       <c r="J11" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L11" s="65"/>
       <c r="M11" s="65"/>
       <c r="N11" s="65"/>
       <c r="O11" s="65"/>
       <c r="P11" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q11" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R11" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S11" s="42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T11" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U11" s="64"/>
       <c r="V11" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W11" s="64"/>
       <c r="X11" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y11" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y11" s="67" t="s">
+      <c r="Z11" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z11" s="66" t="s">
+      <c r="AA11" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB11" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA11" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB11" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC11" s="69">
         <v>10.0</v>
@@ -16818,10 +16813,10 @@
         <v>1095.0</v>
       </c>
       <c r="AP11" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ11" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ11" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR11" s="70">
         <v>5.0</v>
@@ -16844,7 +16839,7 @@
     </row>
     <row r="12">
       <c r="A12" s="42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B12" s="63">
         <v>100.0</v>
@@ -16862,56 +16857,56 @@
         <v>730.0</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H12" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I12" s="64"/>
       <c r="J12" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L12" s="65"/>
       <c r="M12" s="65"/>
       <c r="N12" s="65"/>
       <c r="O12" s="65"/>
       <c r="P12" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q12" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="R12" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S12" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="R12" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S12" s="42" t="s">
-        <v>219</v>
-      </c>
       <c r="T12" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U12" s="64"/>
       <c r="V12" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W12" s="64"/>
       <c r="X12" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y12" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y12" s="67" t="s">
+      <c r="Z12" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z12" s="66" t="s">
+      <c r="AA12" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB12" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA12" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB12" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC12" s="69">
         <v>10.0</v>
@@ -16953,10 +16948,10 @@
         <v>730.0</v>
       </c>
       <c r="AP12" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ12" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ12" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR12" s="70">
         <v>11.0</v>
@@ -16979,7 +16974,7 @@
     </row>
     <row r="13">
       <c r="A13" s="42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B13" s="63">
         <v>100.0</v>
@@ -16997,56 +16992,56 @@
         <v>1095.0</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H13" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I13" s="64"/>
       <c r="J13" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K13" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L13" s="65"/>
       <c r="M13" s="65"/>
       <c r="N13" s="65"/>
       <c r="O13" s="65"/>
       <c r="P13" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q13" s="42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R13" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S13" s="42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="T13" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U13" s="64"/>
       <c r="V13" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W13" s="64"/>
       <c r="X13" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y13" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y13" s="67" t="s">
+      <c r="Z13" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z13" s="66" t="s">
+      <c r="AA13" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB13" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA13" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB13" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC13" s="69">
         <v>10.0</v>
@@ -17088,10 +17083,10 @@
         <v>1095.0</v>
       </c>
       <c r="AP13" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ13" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ13" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR13" s="70">
         <v>11.0</v>
@@ -17114,7 +17109,7 @@
     </row>
     <row r="14">
       <c r="A14" s="42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B14" s="63">
         <v>105.0</v>
@@ -17132,56 +17127,56 @@
         <v>0.0</v>
       </c>
       <c r="G14" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H14" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I14" s="64"/>
       <c r="J14" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L14" s="65"/>
       <c r="M14" s="65"/>
       <c r="N14" s="65"/>
       <c r="O14" s="65"/>
       <c r="P14" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q14" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="R14" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S14" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="R14" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S14" s="42" t="s">
-        <v>225</v>
-      </c>
       <c r="T14" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U14" s="64"/>
       <c r="V14" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W14" s="64"/>
       <c r="X14" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y14" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z14" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y14" s="67" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z14" s="76" t="s">
+      <c r="AA14" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB14" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA14" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB14" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC14" s="69">
         <v>100.0</v>
@@ -17223,10 +17218,10 @@
         <v>0.0</v>
       </c>
       <c r="AP14" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ14" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ14" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR14" s="70">
         <v>0.0</v>
@@ -17249,7 +17244,7 @@
     </row>
     <row r="15">
       <c r="A15" s="42" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B15" s="63">
         <v>8.65</v>
@@ -17267,56 +17262,56 @@
         <v>1825.0</v>
       </c>
       <c r="G15" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I15" s="64"/>
       <c r="J15" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K15" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L15" s="65"/>
       <c r="M15" s="65"/>
       <c r="N15" s="65"/>
       <c r="O15" s="65"/>
       <c r="P15" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q15" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R15" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S15" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T15" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U15" s="64"/>
       <c r="V15" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W15" s="64"/>
       <c r="X15" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y15" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y15" s="67" t="s">
+      <c r="Z15" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z15" s="66" t="s">
+      <c r="AA15" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB15" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA15" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB15" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC15" s="69">
         <v>10.0</v>
@@ -17358,10 +17353,10 @@
         <v>1825.0</v>
       </c>
       <c r="AP15" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ15" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ15" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR15" s="70">
         <v>15.0</v>
@@ -17384,7 +17379,7 @@
     </row>
     <row r="16">
       <c r="A16" s="42" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="63">
         <v>8.68</v>
@@ -17402,56 +17397,56 @@
         <v>1095.0</v>
       </c>
       <c r="G16" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H16" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I16" s="64"/>
       <c r="J16" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L16" s="65"/>
       <c r="M16" s="65"/>
       <c r="N16" s="65"/>
       <c r="O16" s="65"/>
       <c r="P16" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q16" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R16" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S16" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T16" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U16" s="64"/>
       <c r="V16" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W16" s="64"/>
       <c r="X16" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y16" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y16" s="67" t="s">
+      <c r="Z16" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z16" s="66" t="s">
+      <c r="AA16" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB16" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA16" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB16" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC16" s="69">
         <v>10.0</v>
@@ -17493,10 +17488,10 @@
         <v>1095.0</v>
       </c>
       <c r="AP16" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ16" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ16" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR16" s="70">
         <v>10.0</v>
@@ -17519,7 +17514,7 @@
     </row>
     <row r="17">
       <c r="A17" s="42" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="63">
         <v>8.69</v>
@@ -17537,56 +17532,56 @@
         <v>1460.0</v>
       </c>
       <c r="G17" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I17" s="64"/>
       <c r="J17" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K17" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L17" s="65"/>
       <c r="M17" s="65"/>
       <c r="N17" s="65"/>
       <c r="O17" s="65"/>
       <c r="P17" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q17" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R17" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S17" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T17" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U17" s="64"/>
       <c r="V17" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W17" s="64"/>
       <c r="X17" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y17" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y17" s="67" t="s">
+      <c r="Z17" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z17" s="66" t="s">
+      <c r="AA17" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB17" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA17" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB17" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC17" s="69">
         <v>10.0</v>
@@ -17628,10 +17623,10 @@
         <v>1460.0</v>
       </c>
       <c r="AP17" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ17" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ17" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR17" s="70">
         <v>15.0</v>
@@ -17654,7 +17649,7 @@
     </row>
     <row r="18">
       <c r="A18" s="42" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B18" s="63">
         <v>9.01</v>
@@ -17672,56 +17667,56 @@
         <v>730.0</v>
       </c>
       <c r="G18" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H18" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I18" s="64"/>
       <c r="J18" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K18" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L18" s="65"/>
       <c r="M18" s="65"/>
       <c r="N18" s="65"/>
       <c r="O18" s="65"/>
       <c r="P18" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q18" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R18" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S18" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T18" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U18" s="64"/>
       <c r="V18" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W18" s="64"/>
       <c r="X18" s="76" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y18" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z18" s="76" t="s">
         <v>185</v>
       </c>
-      <c r="Z18" s="76" t="s">
+      <c r="AA18" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB18" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA18" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB18" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC18" s="69">
         <v>10.0</v>
@@ -17763,10 +17758,10 @@
         <v>730.0</v>
       </c>
       <c r="AP18" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ18" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ18" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR18" s="70">
         <v>9.0</v>
@@ -17789,7 +17784,7 @@
     </row>
     <row r="19">
       <c r="A19" s="42" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B19" s="63">
         <v>14.84</v>
@@ -17807,56 +17802,56 @@
         <v>1095.0</v>
       </c>
       <c r="G19" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I19" s="64"/>
       <c r="J19" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K19" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L19" s="65"/>
       <c r="M19" s="65"/>
       <c r="N19" s="65"/>
       <c r="O19" s="65"/>
       <c r="P19" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q19" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R19" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S19" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T19" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U19" s="64"/>
       <c r="V19" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W19" s="64"/>
       <c r="X19" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y19" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y19" s="67" t="s">
+      <c r="Z19" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z19" s="66" t="s">
+      <c r="AA19" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB19" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA19" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB19" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC19" s="69">
         <v>10.0</v>
@@ -17898,10 +17893,10 @@
         <v>1095.0</v>
       </c>
       <c r="AP19" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ19" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ19" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR19" s="70">
         <v>6.0</v>
@@ -17924,7 +17919,7 @@
     </row>
     <row r="20">
       <c r="A20" s="42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B20" s="63">
         <v>14.88</v>
@@ -17942,56 +17937,56 @@
         <v>730.0</v>
       </c>
       <c r="G20" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I20" s="64"/>
       <c r="J20" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K20" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L20" s="65"/>
       <c r="M20" s="65"/>
       <c r="N20" s="65"/>
       <c r="O20" s="65"/>
       <c r="P20" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q20" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R20" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S20" s="42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T20" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U20" s="64"/>
       <c r="V20" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W20" s="64"/>
       <c r="X20" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y20" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y20" s="67" t="s">
+      <c r="Z20" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z20" s="66" t="s">
+      <c r="AA20" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB20" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA20" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB20" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC20" s="69">
         <v>10.0</v>
@@ -18033,10 +18028,10 @@
         <v>730.0</v>
       </c>
       <c r="AP20" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ20" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ20" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR20" s="70">
         <v>6.0</v>
@@ -18059,7 +18054,7 @@
     </row>
     <row r="21">
       <c r="A21" s="42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B21" s="63">
         <v>14.9</v>
@@ -18077,56 +18072,56 @@
         <v>1460.0</v>
       </c>
       <c r="G21" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H21" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I21" s="64"/>
       <c r="J21" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K21" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L21" s="65"/>
       <c r="M21" s="65"/>
       <c r="N21" s="65"/>
       <c r="O21" s="65"/>
       <c r="P21" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q21" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R21" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S21" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T21" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U21" s="64"/>
       <c r="V21" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W21" s="64"/>
       <c r="X21" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y21" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y21" s="67" t="s">
+      <c r="Z21" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z21" s="66" t="s">
+      <c r="AA21" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB21" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA21" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB21" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC21" s="69">
         <v>10.0</v>
@@ -18168,10 +18163,10 @@
         <v>1460.0</v>
       </c>
       <c r="AP21" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ21" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ21" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR21" s="70">
         <v>9.0</v>
@@ -18194,7 +18189,7 @@
     </row>
     <row r="22">
       <c r="A22" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" s="63">
         <v>14.96</v>
@@ -18212,56 +18207,56 @@
         <v>1825.0</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H22" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I22" s="64"/>
       <c r="J22" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K22" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L22" s="65"/>
       <c r="M22" s="65"/>
       <c r="N22" s="65"/>
       <c r="O22" s="65"/>
       <c r="P22" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q22" s="42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R22" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S22" s="42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T22" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U22" s="64"/>
       <c r="V22" s="42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W22" s="64"/>
       <c r="X22" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y22" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y22" s="67" t="s">
+      <c r="Z22" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z22" s="66" t="s">
+      <c r="AA22" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB22" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA22" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB22" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC22" s="69">
         <v>10.0</v>
@@ -18303,10 +18298,10 @@
         <v>1825.0</v>
       </c>
       <c r="AP22" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ22" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ22" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR22" s="70">
         <v>8.0</v>
@@ -18329,7 +18324,7 @@
     </row>
     <row r="23">
       <c r="A23" s="42" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B23" s="63">
         <v>107.0</v>
@@ -18347,58 +18342,58 @@
         <v>0.0</v>
       </c>
       <c r="G23" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H23" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I23" s="63">
         <v>5.0E8</v>
       </c>
       <c r="J23" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K23" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L23" s="65"/>
       <c r="M23" s="65"/>
       <c r="N23" s="65"/>
       <c r="O23" s="65"/>
       <c r="P23" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q23" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="R23" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S23" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="R23" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S23" s="42" t="s">
-        <v>241</v>
-      </c>
       <c r="T23" s="42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U23" s="64"/>
       <c r="V23" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W23" s="64"/>
       <c r="X23" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y23" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z23" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y23" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z23" s="76" t="s">
+      <c r="AA23" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB23" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA23" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB23" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC23" s="69">
         <v>100.0</v>
@@ -18440,10 +18435,10 @@
         <v>0.0</v>
       </c>
       <c r="AP23" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ23" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ23" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR23" s="70">
         <v>2.0</v>
@@ -18466,7 +18461,7 @@
     </row>
     <row r="24">
       <c r="A24" s="42" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" s="63">
         <v>15.0</v>
@@ -18484,56 +18479,56 @@
         <v>90.0</v>
       </c>
       <c r="G24" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H24" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I24" s="64"/>
       <c r="J24" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K24" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L24" s="65"/>
       <c r="M24" s="65"/>
       <c r="N24" s="65"/>
       <c r="O24" s="65"/>
       <c r="P24" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q24" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="R24" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S24" s="42" t="s">
         <v>244</v>
       </c>
-      <c r="R24" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S24" s="42" t="s">
+      <c r="T24" s="42" t="s">
         <v>245</v>
-      </c>
-      <c r="T24" s="42" t="s">
-        <v>246</v>
       </c>
       <c r="U24" s="64"/>
       <c r="V24" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W24" s="64"/>
       <c r="X24" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y24" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y24" s="67" t="s">
+      <c r="Z24" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z24" s="66" t="s">
-        <v>186</v>
-      </c>
       <c r="AA24" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB24" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC24" s="69">
         <v>45.0</v>
@@ -18575,10 +18570,10 @@
         <v>90.0</v>
       </c>
       <c r="AP24" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ24" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ24" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR24" s="70">
         <v>2.0</v>
@@ -18601,7 +18596,7 @@
     </row>
     <row r="25">
       <c r="A25" s="42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B25" s="63">
         <v>140.0</v>
@@ -18619,56 +18614,56 @@
         <v>360.0</v>
       </c>
       <c r="G25" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H25" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I25" s="64"/>
       <c r="J25" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K25" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L25" s="65"/>
       <c r="M25" s="65"/>
       <c r="N25" s="65"/>
       <c r="O25" s="65"/>
       <c r="P25" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q25" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R25" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S25" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="T25" s="42" t="s">
         <v>248</v>
-      </c>
-      <c r="T25" s="42" t="s">
-        <v>249</v>
       </c>
       <c r="U25" s="64"/>
       <c r="V25" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W25" s="64"/>
       <c r="X25" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y25" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y25" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z25" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA25" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB25" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC25" s="69">
         <v>25.0</v>
@@ -18710,10 +18705,10 @@
         <v>360.0</v>
       </c>
       <c r="AP25" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ25" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ25" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR25" s="70">
         <v>0.0</v>
@@ -18736,7 +18731,7 @@
     </row>
     <row r="26">
       <c r="A26" s="42" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" s="63">
         <v>106.0</v>
@@ -18754,56 +18749,56 @@
         <v>31.0</v>
       </c>
       <c r="G26" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H26" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I26" s="64"/>
       <c r="J26" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K26" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L26" s="65"/>
       <c r="M26" s="65"/>
       <c r="N26" s="65"/>
       <c r="O26" s="65"/>
       <c r="P26" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q26" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R26" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S26" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="T26" s="42" t="s">
         <v>252</v>
-      </c>
-      <c r="T26" s="42" t="s">
-        <v>253</v>
       </c>
       <c r="U26" s="64"/>
       <c r="V26" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W26" s="64"/>
       <c r="X26" s="78" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y26" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z26" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA26" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB26" s="68" t="s">
         <v>254</v>
-      </c>
-      <c r="Y26" s="67" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z26" s="78" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA26" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB26" s="68" t="s">
-        <v>255</v>
       </c>
       <c r="AC26" s="69">
         <v>65.0</v>
@@ -18845,10 +18840,10 @@
         <v>31.0</v>
       </c>
       <c r="AP26" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ26" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ26" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR26" s="70">
         <v>0.0</v>
@@ -18871,7 +18866,7 @@
     </row>
     <row r="27">
       <c r="A27" s="42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" s="63">
         <v>100.0</v>
@@ -18889,56 +18884,56 @@
         <v>0.0</v>
       </c>
       <c r="G27" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H27" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I27" s="64"/>
       <c r="J27" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K27" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L27" s="65"/>
       <c r="M27" s="65"/>
       <c r="N27" s="65"/>
       <c r="O27" s="65"/>
       <c r="P27" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q27" s="42" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R27" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S27" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="T27" s="42" t="s">
         <v>257</v>
-      </c>
-      <c r="T27" s="42" t="s">
-        <v>258</v>
       </c>
       <c r="U27" s="64"/>
       <c r="V27" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W27" s="64"/>
       <c r="X27" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y27" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y27" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z27" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA27" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB27" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA27" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB27" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC27" s="69">
         <v>100.0</v>
@@ -18980,10 +18975,10 @@
         <v>0.0</v>
       </c>
       <c r="AP27" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ27" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ27" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR27" s="70">
         <v>2.0</v>
@@ -19006,7 +19001,7 @@
     </row>
     <row r="28">
       <c r="A28" s="42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B28" s="63">
         <v>112.0</v>
@@ -19024,58 +19019,58 @@
         <v>90.0</v>
       </c>
       <c r="G28" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H28" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I28" s="63">
         <v>500000.0</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K28" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L28" s="65"/>
       <c r="M28" s="65"/>
       <c r="N28" s="65"/>
       <c r="O28" s="65"/>
       <c r="P28" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q28" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R28" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S28" s="42" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T28" s="42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U28" s="64"/>
       <c r="V28" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W28" s="64"/>
       <c r="X28" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y28" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z28" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y28" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z28" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA28" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB28" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC28" s="69">
         <v>45.0</v>
@@ -19117,10 +19112,10 @@
         <v>90.0</v>
       </c>
       <c r="AP28" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ28" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ28" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR28" s="70">
         <v>1.0</v>
@@ -19143,7 +19138,7 @@
     </row>
     <row r="29">
       <c r="A29" s="42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B29" s="63">
         <v>116.0</v>
@@ -19161,58 +19156,58 @@
         <v>181.0</v>
       </c>
       <c r="G29" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H29" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I29" s="63">
         <v>500000.0</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K29" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L29" s="65"/>
       <c r="M29" s="65"/>
       <c r="N29" s="65"/>
       <c r="O29" s="65"/>
       <c r="P29" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q29" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R29" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S29" s="42" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T29" s="42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U29" s="64"/>
       <c r="V29" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W29" s="64"/>
       <c r="X29" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y29" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z29" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y29" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z29" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA29" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB29" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC29" s="69">
         <v>25.0</v>
@@ -19254,10 +19249,10 @@
         <v>181.0</v>
       </c>
       <c r="AP29" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ29" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ29" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR29" s="70">
         <v>1.0</v>
@@ -19280,7 +19275,7 @@
     </row>
     <row r="30">
       <c r="A30" s="42" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B30" s="63">
         <v>119.0</v>
@@ -19298,58 +19293,58 @@
         <v>361.0</v>
       </c>
       <c r="G30" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H30" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H30" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I30" s="63">
         <v>500000.0</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K30" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L30" s="65"/>
       <c r="M30" s="65"/>
       <c r="N30" s="65"/>
       <c r="O30" s="65"/>
       <c r="P30" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q30" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R30" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S30" s="42" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T30" s="42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U30" s="64"/>
       <c r="V30" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W30" s="64"/>
       <c r="X30" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y30" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z30" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y30" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z30" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA30" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB30" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC30" s="69">
         <v>25.0</v>
@@ -19391,10 +19386,10 @@
         <v>361.0</v>
       </c>
       <c r="AP30" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ30" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ30" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR30" s="70">
         <v>0.0</v>
@@ -19417,7 +19412,7 @@
     </row>
     <row r="31">
       <c r="A31" s="42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B31" s="63">
         <v>120.0</v>
@@ -19435,58 +19430,58 @@
         <v>721.0</v>
       </c>
       <c r="G31" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H31" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I31" s="63">
         <v>500000.0</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K31" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L31" s="65"/>
       <c r="M31" s="65"/>
       <c r="N31" s="65"/>
       <c r="O31" s="65"/>
       <c r="P31" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q31" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R31" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S31" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T31" s="42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U31" s="64"/>
       <c r="V31" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W31" s="64"/>
       <c r="X31" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y31" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z31" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y31" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z31" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA31" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB31" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC31" s="69">
         <v>10.0</v>
@@ -19528,10 +19523,10 @@
         <v>721.0</v>
       </c>
       <c r="AP31" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ31" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ31" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR31" s="70">
         <v>0.0</v>
@@ -19572,58 +19567,58 @@
         <v>60.0</v>
       </c>
       <c r="G32" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H32" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I32" s="63">
         <v>20000.0</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K32" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L32" s="65"/>
       <c r="M32" s="65"/>
       <c r="N32" s="65"/>
       <c r="O32" s="65"/>
       <c r="P32" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q32" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R32" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S32" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T32" s="42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U32" s="64"/>
       <c r="V32" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W32" s="64"/>
       <c r="X32" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y32" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z32" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y32" s="77" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z32" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA32" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB32" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC32" s="69">
         <v>65.0</v>
@@ -19665,10 +19660,10 @@
         <v>60.0</v>
       </c>
       <c r="AP32" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ32" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ32" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR32" s="70">
         <v>0.0</v>
@@ -19691,7 +19686,7 @@
     </row>
     <row r="33">
       <c r="A33" s="42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B33" s="63">
         <v>104.0</v>
@@ -19709,58 +19704,58 @@
         <v>90.0</v>
       </c>
       <c r="G33" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H33" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I33" s="63">
         <v>1.0E7</v>
       </c>
       <c r="J33" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K33" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L33" s="65"/>
       <c r="M33" s="65"/>
       <c r="N33" s="65"/>
       <c r="O33" s="65"/>
       <c r="P33" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q33" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R33" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S33" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="T33" s="72" t="s">
         <v>269</v>
-      </c>
-      <c r="T33" s="72" t="s">
-        <v>270</v>
       </c>
       <c r="U33" s="64"/>
       <c r="V33" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W33" s="64"/>
       <c r="X33" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y33" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y33" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z33" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA33" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB33" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC33" s="69">
         <v>45.0</v>
@@ -19802,10 +19797,10 @@
         <v>90.0</v>
       </c>
       <c r="AP33" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ33" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ33" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR33" s="70">
         <v>0.0</v>
@@ -19828,7 +19823,7 @@
     </row>
     <row r="34">
       <c r="A34" s="42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B34" s="63">
         <v>105.0</v>
@@ -19846,58 +19841,58 @@
         <v>180.0</v>
       </c>
       <c r="G34" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H34" s="63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I34" s="63">
         <v>1.0E7</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K34" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L34" s="65"/>
       <c r="M34" s="65"/>
       <c r="N34" s="65"/>
       <c r="O34" s="65"/>
       <c r="P34" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q34" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R34" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S34" s="42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T34" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U34" s="64"/>
       <c r="V34" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W34" s="64"/>
       <c r="X34" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y34" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y34" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z34" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA34" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB34" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC34" s="69">
         <v>45.0</v>
@@ -19939,10 +19934,10 @@
         <v>180.0</v>
       </c>
       <c r="AP34" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ34" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ34" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR34" s="70">
         <v>1.0</v>
@@ -19965,7 +19960,7 @@
     </row>
     <row r="35">
       <c r="A35" s="42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B35" s="63">
         <v>14.9</v>
@@ -19983,56 +19978,56 @@
         <v>365.0</v>
       </c>
       <c r="G35" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H35" s="63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I35" s="63">
         <v>1.0E7</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K35" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L35" s="65"/>
       <c r="M35" s="65"/>
       <c r="N35" s="65"/>
       <c r="O35" s="65"/>
       <c r="P35" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q35" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R35" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S35" s="42" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T35" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U35" s="64"/>
       <c r="V35" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W35" s="64"/>
       <c r="X35" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y35" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z35" s="79"/>
       <c r="AA35" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB35" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC35" s="69">
         <v>25.0</v>
@@ -20074,10 +20069,10 @@
         <v>365.0</v>
       </c>
       <c r="AP35" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ35" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ35" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR35" s="70">
         <v>0.0</v>
@@ -20100,7 +20095,7 @@
     </row>
     <row r="36">
       <c r="A36" s="42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B36" s="63">
         <v>15.0</v>
@@ -20118,58 +20113,58 @@
         <v>180.0</v>
       </c>
       <c r="G36" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H36" s="63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I36" s="63">
         <v>1.0E7</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K36" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L36" s="65"/>
       <c r="M36" s="65"/>
       <c r="N36" s="65"/>
       <c r="O36" s="65"/>
       <c r="P36" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q36" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R36" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S36" s="42" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T36" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U36" s="64"/>
       <c r="V36" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W36" s="64"/>
       <c r="X36" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y36" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y36" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z36" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA36" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB36" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC36" s="69">
         <v>45.0</v>
@@ -20211,10 +20206,10 @@
         <v>180.0</v>
       </c>
       <c r="AP36" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ36" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ36" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR36" s="70">
         <v>0.0</v>
@@ -20237,7 +20232,7 @@
     </row>
     <row r="37">
       <c r="A37" s="42" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B37" s="63">
         <v>120.0</v>
@@ -20255,56 +20250,56 @@
         <v>90.0</v>
       </c>
       <c r="G37" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H37" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I37" s="64"/>
       <c r="J37" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K37" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L37" s="64"/>
       <c r="M37" s="64"/>
       <c r="N37" s="64"/>
       <c r="O37" s="64"/>
       <c r="P37" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q37" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R37" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S37" s="42" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T37" s="42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U37" s="64"/>
       <c r="V37" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W37" s="64"/>
       <c r="X37" s="66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y37" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z37" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA37" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB37" s="68" t="s">
         <v>196</v>
-      </c>
-      <c r="Z37" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA37" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB37" s="68" t="s">
-        <v>197</v>
       </c>
       <c r="AC37" s="69">
         <v>45.0</v>
@@ -20342,10 +20337,10 @@
         <v>90.0</v>
       </c>
       <c r="AP37" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ37" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ37" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR37" s="75"/>
       <c r="AS37" s="74"/>
@@ -20356,7 +20351,7 @@
     </row>
     <row r="38">
       <c r="A38" s="42" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B38" s="63">
         <v>120.0</v>
@@ -20374,56 +20369,56 @@
         <v>180.0</v>
       </c>
       <c r="G38" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H38" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I38" s="64"/>
       <c r="J38" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K38" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L38" s="64"/>
       <c r="M38" s="64"/>
       <c r="N38" s="64"/>
       <c r="O38" s="64"/>
       <c r="P38" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q38" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R38" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S38" s="42" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T38" s="42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U38" s="64"/>
       <c r="V38" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W38" s="64"/>
       <c r="X38" s="66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y38" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z38" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA38" s="68" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB38" s="68" t="s">
         <v>196</v>
-      </c>
-      <c r="Z38" s="66" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA38" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB38" s="68" t="s">
-        <v>197</v>
       </c>
       <c r="AC38" s="69">
         <v>45.0</v>
@@ -20461,10 +20456,10 @@
         <v>180.0</v>
       </c>
       <c r="AP38" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ38" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ38" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR38" s="75"/>
       <c r="AS38" s="74"/>
@@ -20475,7 +20470,7 @@
     </row>
     <row r="39">
       <c r="A39" s="42" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B39" s="63">
         <v>107.25</v>
@@ -20493,56 +20488,56 @@
         <v>540.0</v>
       </c>
       <c r="G39" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H39" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I39" s="64"/>
       <c r="J39" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K39" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L39" s="65"/>
       <c r="M39" s="65"/>
       <c r="N39" s="65"/>
       <c r="O39" s="65"/>
       <c r="P39" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q39" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R39" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S39" s="42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T39" s="42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U39" s="64"/>
       <c r="V39" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W39" s="64"/>
       <c r="X39" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y39" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y39" s="67" t="s">
+      <c r="Z39" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z39" s="66" t="s">
+      <c r="AA39" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB39" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA39" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB39" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC39" s="69">
         <v>10.0</v>
@@ -20584,10 +20579,10 @@
         <v>540.0</v>
       </c>
       <c r="AP39" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ39" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ39" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR39" s="70">
         <v>5.0</v>
@@ -20628,56 +20623,56 @@
         <v>0.0</v>
       </c>
       <c r="G40" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H40" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I40" s="64"/>
       <c r="J40" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K40" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L40" s="65"/>
       <c r="M40" s="65"/>
       <c r="N40" s="65"/>
       <c r="O40" s="65"/>
       <c r="P40" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q40" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R40" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S40" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="T40" s="42" t="s">
         <v>285</v>
-      </c>
-      <c r="T40" s="42" t="s">
-        <v>286</v>
       </c>
       <c r="U40" s="64"/>
       <c r="V40" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W40" s="64"/>
       <c r="X40" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y40" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z40" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y40" s="67" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z40" s="76" t="s">
+      <c r="AA40" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB40" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA40" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB40" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC40" s="69">
         <v>100.0</v>
@@ -20719,10 +20714,10 @@
         <v>0.0</v>
       </c>
       <c r="AP40" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ40" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ40" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR40" s="70">
         <v>0.0</v>
@@ -20763,56 +20758,56 @@
         <v>0.0</v>
       </c>
       <c r="G41" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I41" s="64"/>
       <c r="J41" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K41" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L41" s="65"/>
       <c r="M41" s="65"/>
       <c r="N41" s="65"/>
       <c r="O41" s="65"/>
       <c r="P41" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q41" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R41" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S41" s="42" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T41" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U41" s="64"/>
       <c r="V41" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W41" s="64"/>
       <c r="X41" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y41" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="Y41" s="73" t="s">
+      <c r="Z41" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z41" s="66" t="s">
-        <v>186</v>
-      </c>
       <c r="AA41" s="68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AB41" s="68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AC41" s="69">
         <v>100.0</v>
@@ -20850,10 +20845,10 @@
         <v>0.0</v>
       </c>
       <c r="AP41" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ41" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ41" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR41" s="75"/>
       <c r="AS41" s="74"/>
@@ -20864,7 +20859,7 @@
     </row>
     <row r="42">
       <c r="A42" s="42" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B42" s="63">
         <v>150.0</v>
@@ -20882,58 +20877,58 @@
         <v>0.0</v>
       </c>
       <c r="G42" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H42" s="63" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I42" s="63">
         <v>60000.0</v>
       </c>
       <c r="J42" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K42" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L42" s="65"/>
       <c r="M42" s="65"/>
       <c r="N42" s="65"/>
       <c r="O42" s="65"/>
       <c r="P42" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q42" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R42" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S42" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="T42" s="42" t="s">
         <v>290</v>
-      </c>
-      <c r="T42" s="42" t="s">
-        <v>291</v>
       </c>
       <c r="U42" s="64"/>
       <c r="V42" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W42" s="64"/>
       <c r="X42" s="66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y42" s="77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z42" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA42" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB42" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA42" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB42" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC42" s="69">
         <v>100.0</v>
@@ -20975,10 +20970,10 @@
         <v>0.0</v>
       </c>
       <c r="AP42" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ42" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ42" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR42" s="70">
         <v>0.0</v>
@@ -21019,58 +21014,58 @@
         <v>0.0</v>
       </c>
       <c r="G43" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H43" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H43" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I43" s="63">
         <v>3000.0</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K43" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L43" s="65"/>
       <c r="M43" s="65"/>
       <c r="N43" s="65"/>
       <c r="O43" s="65"/>
       <c r="P43" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q43" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R43" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S43" s="42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T43" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U43" s="64"/>
       <c r="V43" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W43" s="64"/>
       <c r="X43" s="66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Y43" s="73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Z43" s="66" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA43" s="68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AB43" s="68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AC43" s="69">
         <v>100.0</v>
@@ -21108,10 +21103,10 @@
         <v>0.0</v>
       </c>
       <c r="AP43" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ43" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ43" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR43" s="75"/>
       <c r="AS43" s="74"/>
@@ -21122,7 +21117,7 @@
     </row>
     <row r="44">
       <c r="A44" s="42" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B44" s="63">
         <v>100.0</v>
@@ -21140,23 +21135,23 @@
         <v>0.0</v>
       </c>
       <c r="G44" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H44" s="63" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I44" s="64"/>
       <c r="J44" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K44" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="L44" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="L44" s="42" t="s">
+      <c r="M44" s="42" t="s">
         <v>297</v>
-      </c>
-      <c r="M44" s="42" t="s">
-        <v>298</v>
       </c>
       <c r="N44" s="63">
         <v>2.0</v>
@@ -21165,39 +21160,39 @@
         <v>1.0</v>
       </c>
       <c r="P44" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q44" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R44" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S44" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="T44" s="42" t="s">
         <v>299</v>
-      </c>
-      <c r="T44" s="42" t="s">
-        <v>300</v>
       </c>
       <c r="U44" s="64"/>
       <c r="V44" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W44" s="64"/>
       <c r="X44" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y44" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z44" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA44" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB44" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA44" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB44" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC44" s="69">
         <v>100.0</v>
@@ -21239,10 +21234,10 @@
         <v>0.0</v>
       </c>
       <c r="AP44" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ44" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ44" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR44" s="70">
         <v>2.0</v>
@@ -21265,7 +21260,7 @@
     </row>
     <row r="45">
       <c r="A45" s="42" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B45" s="63">
         <v>100.0</v>
@@ -21283,23 +21278,23 @@
         <v>0.0</v>
       </c>
       <c r="G45" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H45" s="72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I45" s="64"/>
       <c r="J45" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K45" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="L45" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="L45" s="42" t="s">
-        <v>297</v>
-      </c>
       <c r="M45" s="42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N45" s="72">
         <v>2.0</v>
@@ -21308,39 +21303,39 @@
         <v>1.0</v>
       </c>
       <c r="P45" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q45" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R45" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S45" s="42" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T45" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U45" s="64"/>
       <c r="V45" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W45" s="64"/>
       <c r="X45" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y45" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z45" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA45" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB45" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA45" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB45" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC45" s="69">
         <v>100.0</v>
@@ -21382,10 +21377,10 @@
         <v>0.0</v>
       </c>
       <c r="AP45" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ45" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ45" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR45" s="70">
         <v>0.0</v>
@@ -21408,7 +21403,7 @@
     </row>
     <row r="46">
       <c r="A46" s="42" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B46" s="63">
         <v>100.0</v>
@@ -21426,23 +21421,23 @@
         <v>0.0</v>
       </c>
       <c r="G46" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H46" s="72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I46" s="64"/>
       <c r="J46" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K46" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="L46" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="L46" s="42" t="s">
-        <v>297</v>
-      </c>
       <c r="M46" s="42" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N46" s="72">
         <v>2.0</v>
@@ -21451,39 +21446,39 @@
         <v>1.0</v>
       </c>
       <c r="P46" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q46" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R46" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S46" s="42" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="T46" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U46" s="64"/>
       <c r="V46" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W46" s="64"/>
       <c r="X46" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y46" s="73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z46" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA46" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB46" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA46" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB46" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC46" s="69">
         <v>100.0</v>
@@ -21525,10 +21520,10 @@
         <v>0.0</v>
       </c>
       <c r="AP46" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ46" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ46" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR46" s="70">
         <v>0.0</v>
@@ -21551,7 +21546,7 @@
     </row>
     <row r="47">
       <c r="A47" s="42" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B47" s="63">
         <v>80.0</v>
@@ -21569,56 +21564,56 @@
         <v>2.0</v>
       </c>
       <c r="G47" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H47" s="63" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I47" s="64"/>
       <c r="J47" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K47" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L47" s="65"/>
       <c r="M47" s="65"/>
       <c r="N47" s="65"/>
       <c r="O47" s="65"/>
       <c r="P47" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R47" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S47" s="42" t="s">
+        <v>310</v>
+      </c>
+      <c r="T47" s="42" t="s">
         <v>311</v>
-      </c>
-      <c r="T47" s="42" t="s">
-        <v>312</v>
       </c>
       <c r="U47" s="64"/>
       <c r="V47" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W47" s="64"/>
       <c r="X47" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y47" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y47" s="67" t="s">
+      <c r="Z47" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z47" s="66" t="s">
-        <v>186</v>
-      </c>
       <c r="AA47" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB47" s="68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AC47" s="69">
         <v>100.0</v>
@@ -21660,10 +21655,10 @@
         <v>2.0</v>
       </c>
       <c r="AP47" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ47" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ47" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR47" s="70">
         <v>4.0</v>
@@ -21686,7 +21681,7 @@
     </row>
     <row r="48">
       <c r="A48" s="42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B48" s="63">
         <v>100.0</v>
@@ -21704,56 +21699,56 @@
         <v>0.0</v>
       </c>
       <c r="G48" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H48" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I48" s="64"/>
       <c r="J48" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K48" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L48" s="65"/>
       <c r="M48" s="65"/>
       <c r="N48" s="65"/>
       <c r="O48" s="65"/>
       <c r="P48" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R48" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S48" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="T48" s="42" t="s">
         <v>315</v>
-      </c>
-      <c r="T48" s="42" t="s">
-        <v>316</v>
       </c>
       <c r="U48" s="64"/>
       <c r="V48" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W48" s="64"/>
       <c r="X48" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y48" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y48" s="67" t="s">
+      <c r="Z48" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z48" s="66" t="s">
+      <c r="AA48" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB48" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA48" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB48" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC48" s="69">
         <v>25.0</v>
@@ -21795,10 +21790,10 @@
         <v>181.0</v>
       </c>
       <c r="AP48" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ48" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="AQ48" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="AR48" s="70">
         <v>1.0</v>
@@ -21821,7 +21816,7 @@
     </row>
     <row r="49">
       <c r="A49" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B49" s="63">
         <v>115.75</v>
@@ -21839,56 +21834,56 @@
         <v>365.0</v>
       </c>
       <c r="G49" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H49" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I49" s="64"/>
       <c r="J49" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K49" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L49" s="65"/>
       <c r="M49" s="65"/>
       <c r="N49" s="65"/>
       <c r="O49" s="65"/>
       <c r="P49" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q49" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R49" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S49" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="T49" s="42" t="s">
         <v>319</v>
-      </c>
-      <c r="T49" s="42" t="s">
-        <v>320</v>
       </c>
       <c r="U49" s="64"/>
       <c r="V49" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W49" s="64"/>
       <c r="X49" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y49" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y49" s="67" t="s">
+      <c r="Z49" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z49" s="66" t="s">
+      <c r="AA49" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB49" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA49" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB49" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC49" s="69">
         <v>25.0</v>
@@ -21930,10 +21925,10 @@
         <v>365.0</v>
       </c>
       <c r="AP49" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ49" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ49" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR49" s="70">
         <v>1.0</v>
@@ -21956,7 +21951,7 @@
     </row>
     <row r="50">
       <c r="A50" s="42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B50" s="63">
         <v>119.16</v>
@@ -21974,54 +21969,54 @@
         <v>730.0</v>
       </c>
       <c r="G50" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H50" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I50" s="64"/>
       <c r="J50" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K50" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L50" s="65"/>
       <c r="M50" s="65"/>
       <c r="N50" s="65"/>
       <c r="O50" s="65"/>
       <c r="P50" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R50" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S50" s="42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T50" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U50" s="64"/>
       <c r="V50" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W50" s="64"/>
       <c r="X50" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y50" s="67" t="s">
         <v>184</v>
-      </c>
-      <c r="Y50" s="67" t="s">
-        <v>185</v>
       </c>
       <c r="Z50" s="81"/>
       <c r="AA50" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB50" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC50" s="69">
         <v>10.0</v>
@@ -22063,10 +22058,10 @@
         <v>730.0</v>
       </c>
       <c r="AP50" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ50" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ50" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR50" s="70">
         <v>0.0</v>
@@ -22089,7 +22084,7 @@
     </row>
     <row r="51">
       <c r="A51" s="42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B51" s="63">
         <v>104.41</v>
@@ -22107,56 +22102,56 @@
         <v>90.0</v>
       </c>
       <c r="G51" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H51" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H51" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I51" s="64"/>
       <c r="J51" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K51" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L51" s="65"/>
       <c r="M51" s="65"/>
       <c r="N51" s="65"/>
       <c r="O51" s="65"/>
       <c r="P51" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R51" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S51" s="42" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T51" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U51" s="64"/>
       <c r="V51" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W51" s="64"/>
       <c r="X51" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y51" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y51" s="67" t="s">
+      <c r="Z51" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z51" s="66" t="s">
-        <v>186</v>
-      </c>
       <c r="AA51" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB51" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC51" s="69">
         <v>45.0</v>
@@ -22198,10 +22193,10 @@
         <v>90.0</v>
       </c>
       <c r="AP51" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ51" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ51" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR51" s="70">
         <v>3.0</v>
@@ -22224,7 +22219,7 @@
     </row>
     <row r="52">
       <c r="A52" s="42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B52" s="63">
         <v>108.76</v>
@@ -22242,56 +22237,56 @@
         <v>180.0</v>
       </c>
       <c r="G52" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H52" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H52" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I52" s="64"/>
       <c r="J52" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K52" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L52" s="65"/>
       <c r="M52" s="65"/>
       <c r="N52" s="65"/>
       <c r="O52" s="65"/>
       <c r="P52" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q52" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R52" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S52" s="42" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T52" s="42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U52" s="64"/>
       <c r="V52" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W52" s="64"/>
       <c r="X52" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y52" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y52" s="67" t="s">
+      <c r="Z52" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z52" s="66" t="s">
-        <v>186</v>
-      </c>
       <c r="AA52" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB52" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC52" s="69">
         <v>45.0</v>
@@ -22333,10 +22328,10 @@
         <v>180.0</v>
       </c>
       <c r="AP52" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ52" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ52" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR52" s="70">
         <v>2.0</v>
@@ -22359,7 +22354,7 @@
     </row>
     <row r="53">
       <c r="A53" s="42" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B53" s="63">
         <v>100.0</v>
@@ -22377,56 +22372,56 @@
         <v>31.0</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H53" s="63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I53" s="64"/>
       <c r="J53" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K53" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K53" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L53" s="65"/>
       <c r="M53" s="65"/>
       <c r="N53" s="65"/>
       <c r="O53" s="65"/>
       <c r="P53" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q53" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R53" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S53" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="T53" s="42" t="s">
         <v>328</v>
-      </c>
-      <c r="T53" s="42" t="s">
-        <v>329</v>
       </c>
       <c r="U53" s="64"/>
       <c r="V53" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W53" s="64"/>
       <c r="X53" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y53" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y53" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z53" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA53" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB53" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AC53" s="69">
         <v>65.0</v>
@@ -22468,10 +22463,10 @@
         <v>31.0</v>
       </c>
       <c r="AP53" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ53" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ53" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR53" s="70">
         <v>1.0</v>
@@ -22494,7 +22489,7 @@
     </row>
     <row r="54">
       <c r="A54" s="42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B54" s="63">
         <v>10.84</v>
@@ -22512,56 +22507,56 @@
         <v>1825.0</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H54" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I54" s="64"/>
       <c r="J54" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K54" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L54" s="65"/>
       <c r="M54" s="65"/>
       <c r="N54" s="65"/>
       <c r="O54" s="65"/>
       <c r="P54" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q54" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R54" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S54" s="42" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="T54" s="42" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="U54" s="64"/>
       <c r="V54" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W54" s="64"/>
       <c r="X54" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y54" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y54" s="67" t="s">
+      <c r="Z54" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z54" s="66" t="s">
+      <c r="AA54" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB54" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA54" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB54" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC54" s="69">
         <v>10.0</v>
@@ -22603,10 +22598,10 @@
         <v>1825.0</v>
       </c>
       <c r="AP54" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ54" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ54" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR54" s="70">
         <v>4.0</v>
@@ -22629,7 +22624,7 @@
     </row>
     <row r="55">
       <c r="A55" s="42" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B55" s="63">
         <v>88.0</v>
@@ -22647,56 +22642,56 @@
         <v>90.0</v>
       </c>
       <c r="G55" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H55" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I55" s="64"/>
       <c r="J55" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K55" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L55" s="65"/>
       <c r="M55" s="65"/>
       <c r="N55" s="65"/>
       <c r="O55" s="65"/>
       <c r="P55" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R55" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S55" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="T55" s="42" t="s">
         <v>334</v>
-      </c>
-      <c r="T55" s="42" t="s">
-        <v>335</v>
       </c>
       <c r="U55" s="64"/>
       <c r="V55" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W55" s="64"/>
       <c r="X55" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y55" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y55" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z55" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA55" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB55" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC55" s="69">
         <v>45.0</v>
@@ -22738,10 +22733,10 @@
         <v>90.0</v>
       </c>
       <c r="AP55" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ55" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ55" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR55" s="70">
         <v>0.0</v>
@@ -22764,7 +22759,7 @@
     </row>
     <row r="56">
       <c r="A56" s="42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B56" s="63">
         <v>5.5</v>
@@ -22782,56 +22777,56 @@
         <v>1080.0</v>
       </c>
       <c r="G56" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H56" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I56" s="64"/>
       <c r="J56" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K56" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L56" s="65"/>
       <c r="M56" s="65"/>
       <c r="N56" s="65"/>
       <c r="O56" s="65"/>
       <c r="P56" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q56" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="R56" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="S56" s="42" t="s">
         <v>337</v>
       </c>
-      <c r="R56" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="S56" s="42" t="s">
-        <v>338</v>
-      </c>
       <c r="T56" s="72" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="U56" s="64"/>
       <c r="V56" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W56" s="64"/>
       <c r="X56" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y56" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="Y56" s="73" t="s">
+      <c r="Z56" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z56" s="66" t="s">
+      <c r="AA56" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB56" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA56" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB56" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC56" s="69">
         <v>10.0</v>
@@ -22873,10 +22868,10 @@
         <v>1080.0</v>
       </c>
       <c r="AP56" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ56" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ56" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR56" s="70">
         <v>7.0</v>
@@ -22899,7 +22894,7 @@
     </row>
     <row r="57">
       <c r="A57" s="42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B57" s="63">
         <v>93.5</v>
@@ -22917,56 +22912,56 @@
         <v>730.0</v>
       </c>
       <c r="G57" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H57" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I57" s="64"/>
       <c r="J57" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K57" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L57" s="65"/>
       <c r="M57" s="65"/>
       <c r="N57" s="65"/>
       <c r="O57" s="65"/>
       <c r="P57" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q57" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R57" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S57" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="T57" s="42" t="s">
         <v>340</v>
-      </c>
-      <c r="T57" s="42" t="s">
-        <v>341</v>
       </c>
       <c r="U57" s="64"/>
       <c r="V57" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W57" s="64"/>
       <c r="X57" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y57" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z57" s="78" t="s">
         <v>185</v>
       </c>
-      <c r="Z57" s="78" t="s">
+      <c r="AA57" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB57" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA57" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB57" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC57" s="69">
         <v>10.0</v>
@@ -23008,10 +23003,10 @@
         <v>730.0</v>
       </c>
       <c r="AP57" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ57" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ57" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR57" s="70">
         <v>0.0</v>
@@ -23034,7 +23029,7 @@
     </row>
     <row r="58">
       <c r="A58" s="42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B58" s="63">
         <v>12.05</v>
@@ -23052,54 +23047,54 @@
         <v>365.0</v>
       </c>
       <c r="G58" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H58" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I58" s="64"/>
       <c r="J58" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K58" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L58" s="65"/>
       <c r="M58" s="65"/>
       <c r="N58" s="65"/>
       <c r="O58" s="65"/>
       <c r="P58" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q58" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R58" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S58" s="42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T58" s="42" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U58" s="64"/>
       <c r="V58" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W58" s="64"/>
       <c r="X58" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y58" s="67" t="s">
         <v>184</v>
-      </c>
-      <c r="Y58" s="67" t="s">
-        <v>185</v>
       </c>
       <c r="Z58" s="81"/>
       <c r="AA58" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB58" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC58" s="69">
         <v>25.0</v>
@@ -23141,10 +23136,10 @@
         <v>365.0</v>
       </c>
       <c r="AP58" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ58" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ58" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR58" s="70">
         <v>0.0</v>
@@ -23167,7 +23162,7 @@
     </row>
     <row r="59">
       <c r="A59" s="42" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B59" s="63">
         <v>11.86</v>
@@ -23185,56 +23180,56 @@
         <v>730.0</v>
       </c>
       <c r="G59" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H59" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I59" s="64"/>
       <c r="J59" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K59" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L59" s="65"/>
       <c r="M59" s="65"/>
       <c r="N59" s="65"/>
       <c r="O59" s="65"/>
       <c r="P59" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R59" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S59" s="42" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T59" s="42" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U59" s="64"/>
       <c r="V59" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W59" s="64"/>
       <c r="X59" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y59" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y59" s="67" t="s">
+      <c r="Z59" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z59" s="66" t="s">
+      <c r="AA59" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB59" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA59" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB59" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC59" s="69">
         <v>10.0</v>
@@ -23276,10 +23271,10 @@
         <v>730.0</v>
       </c>
       <c r="AP59" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ59" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ59" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR59" s="70">
         <v>1.0</v>
@@ -23302,7 +23297,7 @@
     </row>
     <row r="60">
       <c r="A60" s="42" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B60" s="63">
         <v>11.8</v>
@@ -23320,56 +23315,56 @@
         <v>1095.0</v>
       </c>
       <c r="G60" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H60" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I60" s="64"/>
       <c r="J60" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K60" s="42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L60" s="65"/>
       <c r="M60" s="65"/>
       <c r="N60" s="65"/>
       <c r="O60" s="65"/>
       <c r="P60" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q60" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R60" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S60" s="42" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="T60" s="42" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U60" s="64"/>
       <c r="V60" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W60" s="64"/>
       <c r="X60" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y60" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y60" s="67" t="s">
+      <c r="Z60" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z60" s="66" t="s">
+      <c r="AA60" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB60" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA60" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB60" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC60" s="69">
         <v>10.0</v>
@@ -23411,10 +23406,10 @@
         <v>1095.0</v>
       </c>
       <c r="AP60" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ60" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ60" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR60" s="70">
         <v>1.0</v>
@@ -23437,7 +23432,7 @@
     </row>
     <row r="61">
       <c r="A61" s="42" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B61" s="63">
         <v>92.0</v>
@@ -23455,56 +23450,56 @@
         <v>180.0</v>
       </c>
       <c r="G61" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H61" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I61" s="64"/>
       <c r="J61" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K61" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L61" s="65"/>
       <c r="M61" s="65"/>
       <c r="N61" s="65"/>
       <c r="O61" s="65"/>
       <c r="P61" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R61" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S61" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="T61" s="42" t="s">
         <v>350</v>
-      </c>
-      <c r="T61" s="42" t="s">
-        <v>351</v>
       </c>
       <c r="U61" s="64"/>
       <c r="V61" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W61" s="64"/>
       <c r="X61" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y61" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z61" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y61" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z61" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA61" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB61" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AC61" s="69">
         <v>45.0</v>
@@ -23546,10 +23541,10 @@
         <v>180.0</v>
       </c>
       <c r="AP61" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ61" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ61" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR61" s="70">
         <v>0.0</v>
@@ -23572,7 +23567,7 @@
     </row>
     <row r="62">
       <c r="A62" s="42" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B62" s="63">
         <v>100.0</v>
@@ -23590,56 +23585,56 @@
         <v>360.0</v>
       </c>
       <c r="G62" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H62" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I62" s="64"/>
       <c r="J62" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K62" s="42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L62" s="65"/>
       <c r="M62" s="65"/>
       <c r="N62" s="65"/>
       <c r="O62" s="65"/>
       <c r="P62" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q62" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R62" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S62" s="42" t="s">
+        <v>352</v>
+      </c>
+      <c r="T62" s="72" t="s">
         <v>353</v>
-      </c>
-      <c r="T62" s="72" t="s">
-        <v>354</v>
       </c>
       <c r="U62" s="64"/>
       <c r="V62" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W62" s="64"/>
       <c r="X62" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y62" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z62" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="Y62" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z62" s="76" t="s">
-        <v>227</v>
-      </c>
       <c r="AA62" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB62" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC62" s="69">
         <v>25.0</v>
@@ -23681,10 +23676,10 @@
         <v>360.0</v>
       </c>
       <c r="AP62" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ62" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ62" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR62" s="70">
         <v>0.0</v>
@@ -23707,7 +23702,7 @@
     </row>
     <row r="63">
       <c r="A63" s="42" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B63" s="63">
         <v>104.21</v>
@@ -23725,56 +23720,56 @@
         <v>0.0</v>
       </c>
       <c r="G63" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H63" s="63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I63" s="64"/>
       <c r="J63" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K63" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K63" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L63" s="65"/>
       <c r="M63" s="65"/>
       <c r="N63" s="65"/>
       <c r="O63" s="65"/>
       <c r="P63" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q63" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R63" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S63" s="42" t="s">
+        <v>355</v>
+      </c>
+      <c r="T63" s="42" t="s">
         <v>356</v>
-      </c>
-      <c r="T63" s="42" t="s">
-        <v>357</v>
       </c>
       <c r="U63" s="64"/>
       <c r="V63" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W63" s="64"/>
       <c r="X63" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Y63" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z63" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA63" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB63" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA63" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB63" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC63" s="69">
         <v>100.0</v>
@@ -23816,10 +23811,10 @@
         <v>0.0</v>
       </c>
       <c r="AP63" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ63" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ63" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR63" s="70">
         <v>5.0</v>
@@ -23842,7 +23837,7 @@
     </row>
     <row r="64">
       <c r="A64" s="42" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B64" s="63">
         <v>115.0</v>
@@ -23860,58 +23855,58 @@
         <v>0.0</v>
       </c>
       <c r="G64" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H64" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I64" s="72">
         <v>5000.0</v>
       </c>
       <c r="J64" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K64" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L64" s="65"/>
       <c r="M64" s="65"/>
       <c r="N64" s="65"/>
       <c r="O64" s="65"/>
       <c r="P64" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q64" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R64" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S64" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="T64" s="42" t="s">
         <v>359</v>
-      </c>
-      <c r="T64" s="42" t="s">
-        <v>360</v>
       </c>
       <c r="U64" s="64"/>
       <c r="V64" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W64" s="64"/>
       <c r="X64" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y64" s="67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z64" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA64" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB64" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA64" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB64" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC64" s="69">
         <v>100.0</v>
@@ -23953,10 +23948,10 @@
         <v>0.0</v>
       </c>
       <c r="AP64" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ64" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ64" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR64" s="70">
         <v>1.0</v>
@@ -23979,7 +23974,7 @@
     </row>
     <row r="65">
       <c r="A65" s="42" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B65" s="63">
         <v>120.0</v>
@@ -23997,58 +23992,58 @@
         <v>0.0</v>
       </c>
       <c r="G65" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H65" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I65" s="72">
         <v>10000.0</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K65" s="42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L65" s="65"/>
       <c r="M65" s="65"/>
       <c r="N65" s="65"/>
       <c r="O65" s="65"/>
       <c r="P65" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q65" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R65" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S65" s="42" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="T65" s="42" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U65" s="64"/>
       <c r="V65" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W65" s="64"/>
       <c r="X65" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y65" s="67" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z65" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA65" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB65" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA65" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB65" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC65" s="69">
         <v>100.0</v>
@@ -24090,10 +24085,10 @@
         <v>0.0</v>
       </c>
       <c r="AP65" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ65" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ65" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR65" s="70">
         <v>0.0</v>
@@ -24116,7 +24111,7 @@
     </row>
     <row r="66">
       <c r="A66" s="42" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B66" s="63">
         <v>110.37</v>
@@ -24134,56 +24129,56 @@
         <v>0.0</v>
       </c>
       <c r="G66" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H66" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H66" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I66" s="64"/>
       <c r="J66" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K66" s="42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L66" s="65"/>
       <c r="M66" s="65"/>
       <c r="N66" s="65"/>
       <c r="O66" s="65"/>
       <c r="P66" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q66" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R66" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S66" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="T66" s="42" t="s">
         <v>364</v>
-      </c>
-      <c r="T66" s="42" t="s">
-        <v>365</v>
       </c>
       <c r="U66" s="64"/>
       <c r="V66" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W66" s="64"/>
       <c r="X66" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y66" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z66" s="80" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA66" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB66" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC66" s="69">
         <v>25.0</v>
@@ -24225,10 +24220,10 @@
         <v>181.0</v>
       </c>
       <c r="AP66" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ66" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="AQ66" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="AR66" s="70">
         <v>0.0</v>
@@ -24251,7 +24246,7 @@
     </row>
     <row r="67">
       <c r="A67" s="42" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B67" s="63">
         <v>7.67</v>
@@ -24269,56 +24264,56 @@
         <v>0.0</v>
       </c>
       <c r="G67" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H67" s="63" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I67" s="64"/>
       <c r="J67" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K67" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L67" s="65"/>
       <c r="M67" s="65"/>
       <c r="N67" s="65"/>
       <c r="O67" s="65"/>
       <c r="P67" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q67" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R67" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S67" s="42" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="T67" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U67" s="64"/>
       <c r="V67" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W67" s="64"/>
       <c r="X67" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y67" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y67" s="67" t="s">
+      <c r="Z67" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z67" s="66" t="s">
+      <c r="AA67" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB67" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA67" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB67" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC67" s="69">
         <v>25.0</v>
@@ -24360,10 +24355,10 @@
         <v>365.0</v>
       </c>
       <c r="AP67" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ67" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR67" s="70">
         <v>1.0</v>
@@ -24386,7 +24381,7 @@
     </row>
     <row r="68">
       <c r="A68" s="42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B68" s="63">
         <v>7.63</v>
@@ -24404,56 +24399,56 @@
         <v>0.0</v>
       </c>
       <c r="G68" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H68" s="63" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I68" s="64"/>
       <c r="J68" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K68" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L68" s="65"/>
       <c r="M68" s="65"/>
       <c r="N68" s="65"/>
       <c r="O68" s="65"/>
       <c r="P68" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q68" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R68" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S68" s="42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="T68" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U68" s="64"/>
       <c r="V68" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W68" s="64"/>
       <c r="X68" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y68" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y68" s="67" t="s">
+      <c r="Z68" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z68" s="66" t="s">
+      <c r="AA68" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB68" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA68" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB68" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC68" s="69">
         <v>25.0</v>
@@ -24495,10 +24490,10 @@
         <v>365.0</v>
       </c>
       <c r="AP68" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ68" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR68" s="70">
         <v>1.0</v>
@@ -24521,7 +24516,7 @@
     </row>
     <row r="69">
       <c r="A69" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B69" s="63">
         <v>7.6</v>
@@ -24539,56 +24534,56 @@
         <v>0.0</v>
       </c>
       <c r="G69" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H69" s="63" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I69" s="64"/>
       <c r="J69" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K69" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L69" s="65"/>
       <c r="M69" s="65"/>
       <c r="N69" s="65"/>
       <c r="O69" s="65"/>
       <c r="P69" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q69" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R69" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S69" s="42" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="T69" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U69" s="64"/>
       <c r="V69" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W69" s="64"/>
       <c r="X69" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y69" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y69" s="67" t="s">
+      <c r="Z69" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z69" s="66" t="s">
+      <c r="AA69" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB69" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA69" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB69" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC69" s="69">
         <v>25.0</v>
@@ -24630,10 +24625,10 @@
         <v>365.0</v>
       </c>
       <c r="AP69" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ69" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR69" s="70">
         <v>1.0</v>
@@ -24656,7 +24651,7 @@
     </row>
     <row r="70">
       <c r="A70" s="42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B70" s="63">
         <v>7.56</v>
@@ -24674,56 +24669,56 @@
         <v>0.0</v>
       </c>
       <c r="G70" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H70" s="63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I70" s="64"/>
       <c r="J70" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K70" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L70" s="65"/>
       <c r="M70" s="65"/>
       <c r="N70" s="65"/>
       <c r="O70" s="65"/>
       <c r="P70" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q70" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R70" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S70" s="42" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="T70" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U70" s="64"/>
       <c r="V70" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W70" s="64"/>
       <c r="X70" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y70" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y70" s="67" t="s">
+      <c r="Z70" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z70" s="66" t="s">
+      <c r="AA70" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB70" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA70" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB70" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC70" s="69">
         <v>25.0</v>
@@ -24765,10 +24760,10 @@
         <v>365.0</v>
       </c>
       <c r="AP70" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ70" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR70" s="70">
         <v>1.0</v>
@@ -24791,7 +24786,7 @@
     </row>
     <row r="71">
       <c r="A71" s="42" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B71" s="63">
         <v>7.5</v>
@@ -24809,56 +24804,56 @@
         <v>0.0</v>
       </c>
       <c r="G71" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H71" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I71" s="64"/>
       <c r="J71" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K71" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L71" s="65"/>
       <c r="M71" s="65"/>
       <c r="N71" s="65"/>
       <c r="O71" s="65"/>
       <c r="P71" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q71" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R71" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S71" s="42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T71" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U71" s="64"/>
       <c r="V71" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W71" s="64"/>
       <c r="X71" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y71" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y71" s="67" t="s">
+      <c r="Z71" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z71" s="66" t="s">
+      <c r="AA71" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB71" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA71" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB71" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC71" s="69">
         <v>25.0</v>
@@ -24900,10 +24895,10 @@
         <v>365.0</v>
       </c>
       <c r="AP71" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ71" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR71" s="70">
         <v>1.0</v>
@@ -24926,7 +24921,7 @@
     </row>
     <row r="72">
       <c r="A72" s="42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B72" s="63">
         <v>7.44</v>
@@ -24944,56 +24939,56 @@
         <v>0.0</v>
       </c>
       <c r="G72" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H72" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I72" s="64"/>
       <c r="J72" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K72" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L72" s="65"/>
       <c r="M72" s="65"/>
       <c r="N72" s="65"/>
       <c r="O72" s="65"/>
       <c r="P72" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q72" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R72" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S72" s="42" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T72" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U72" s="64"/>
       <c r="V72" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W72" s="64"/>
       <c r="X72" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y72" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y72" s="67" t="s">
+      <c r="Z72" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z72" s="66" t="s">
+      <c r="AA72" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB72" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA72" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB72" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC72" s="69">
         <v>25.0</v>
@@ -25035,10 +25030,10 @@
         <v>365.0</v>
       </c>
       <c r="AP72" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ72" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR72" s="70">
         <v>1.0</v>
@@ -25061,7 +25056,7 @@
     </row>
     <row r="73">
       <c r="A73" s="42" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B73" s="63">
         <v>7.38</v>
@@ -25079,56 +25074,56 @@
         <v>0.0</v>
       </c>
       <c r="G73" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H73" s="63" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I73" s="64"/>
       <c r="J73" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K73" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L73" s="65"/>
       <c r="M73" s="65"/>
       <c r="N73" s="65"/>
       <c r="O73" s="65"/>
       <c r="P73" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q73" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R73" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S73" s="42" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="T73" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U73" s="64"/>
       <c r="V73" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W73" s="64"/>
       <c r="X73" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y73" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y73" s="67" t="s">
+      <c r="Z73" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z73" s="66" t="s">
+      <c r="AA73" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB73" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA73" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB73" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC73" s="69">
         <v>25.0</v>
@@ -25170,10 +25165,10 @@
         <v>365.0</v>
       </c>
       <c r="AP73" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ73" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR73" s="70">
         <v>1.0</v>
@@ -25196,7 +25191,7 @@
     </row>
     <row r="74">
       <c r="A74" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B74" s="63">
         <v>7.31</v>
@@ -25214,56 +25209,56 @@
         <v>0.0</v>
       </c>
       <c r="G74" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H74" s="63" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I74" s="64"/>
       <c r="J74" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K74" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L74" s="65"/>
       <c r="M74" s="65"/>
       <c r="N74" s="65"/>
       <c r="O74" s="65"/>
       <c r="P74" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q74" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R74" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S74" s="42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="T74" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U74" s="64"/>
       <c r="V74" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W74" s="64"/>
       <c r="X74" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y74" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y74" s="67" t="s">
+      <c r="Z74" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z74" s="66" t="s">
+      <c r="AA74" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB74" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA74" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB74" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC74" s="69">
         <v>25.0</v>
@@ -25305,10 +25300,10 @@
         <v>365.0</v>
       </c>
       <c r="AP74" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ74" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR74" s="70">
         <v>3.0</v>
@@ -25331,7 +25326,7 @@
     </row>
     <row r="75">
       <c r="A75" s="42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B75" s="63">
         <v>7.57</v>
@@ -25349,56 +25344,56 @@
         <v>0.0</v>
       </c>
       <c r="G75" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H75" s="63" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I75" s="64"/>
       <c r="J75" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K75" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L75" s="65"/>
       <c r="M75" s="65"/>
       <c r="N75" s="65"/>
       <c r="O75" s="65"/>
       <c r="P75" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q75" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R75" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S75" s="42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="T75" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U75" s="64"/>
       <c r="V75" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W75" s="64"/>
       <c r="X75" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y75" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y75" s="67" t="s">
+      <c r="Z75" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z75" s="66" t="s">
+      <c r="AA75" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB75" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA75" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB75" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC75" s="69">
         <v>25.0</v>
@@ -25440,10 +25435,10 @@
         <v>365.0</v>
       </c>
       <c r="AP75" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ75" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR75" s="70">
         <v>1.0</v>
@@ -25466,7 +25461,7 @@
     </row>
     <row r="76">
       <c r="A76" s="42" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B76" s="63">
         <v>5.8</v>
@@ -25484,56 +25479,56 @@
         <v>0.0</v>
       </c>
       <c r="G76" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H76" s="63" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I76" s="64"/>
       <c r="J76" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K76" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L76" s="65"/>
       <c r="M76" s="65"/>
       <c r="N76" s="65"/>
       <c r="O76" s="65"/>
       <c r="P76" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q76" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R76" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S76" s="42" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T76" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U76" s="64"/>
       <c r="V76" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W76" s="64"/>
       <c r="X76" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y76" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y76" s="67" t="s">
+      <c r="Z76" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z76" s="66" t="s">
+      <c r="AA76" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB76" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA76" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB76" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC76" s="69">
         <v>25.0</v>
@@ -25575,10 +25570,10 @@
         <v>365.0</v>
       </c>
       <c r="AP76" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ76" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR76" s="70">
         <v>11.0</v>
@@ -25601,7 +25596,7 @@
     </row>
     <row r="77">
       <c r="A77" s="42" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B77" s="63">
         <v>7.34</v>
@@ -25619,56 +25614,56 @@
         <v>0.0</v>
       </c>
       <c r="G77" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H77" s="63" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I77" s="64"/>
       <c r="J77" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K77" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L77" s="65"/>
       <c r="M77" s="65"/>
       <c r="N77" s="65"/>
       <c r="O77" s="65"/>
       <c r="P77" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q77" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R77" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S77" s="42" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="T77" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U77" s="64"/>
       <c r="V77" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W77" s="64"/>
       <c r="X77" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y77" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y77" s="67" t="s">
+      <c r="Z77" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="Z77" s="66" t="s">
+      <c r="AA77" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB77" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA77" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB77" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC77" s="69">
         <v>25.0</v>
@@ -25710,10 +25705,10 @@
         <v>365.0</v>
       </c>
       <c r="AP77" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ77" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR77" s="70">
         <v>2.0</v>
@@ -25736,7 +25731,7 @@
     </row>
     <row r="78">
       <c r="A78" s="42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B78" s="63">
         <v>13.39</v>
@@ -25754,56 +25749,56 @@
         <v>0.0</v>
       </c>
       <c r="G78" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H78" s="63" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I78" s="64"/>
       <c r="J78" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K78" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L78" s="65"/>
       <c r="M78" s="65"/>
       <c r="N78" s="65"/>
       <c r="O78" s="65"/>
       <c r="P78" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q78" s="42" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R78" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S78" s="42" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="T78" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U78" s="64"/>
       <c r="V78" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W78" s="64"/>
       <c r="X78" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y78" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y78" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z78" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA78" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB78" s="68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AC78" s="69">
         <v>25.0</v>
@@ -25845,10 +25840,10 @@
         <v>199.0</v>
       </c>
       <c r="AP78" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ78" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR78" s="70">
         <v>0.0</v>
@@ -25871,7 +25866,7 @@
     </row>
     <row r="79">
       <c r="A79" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B79" s="63">
         <v>1.0</v>
@@ -25889,56 +25884,56 @@
         <v>0.0</v>
       </c>
       <c r="G79" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H79" s="63" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I79" s="64"/>
       <c r="J79" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K79" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L79" s="65"/>
       <c r="M79" s="65"/>
       <c r="N79" s="65"/>
       <c r="O79" s="65"/>
       <c r="P79" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q79" s="42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R79" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S79" s="42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="T79" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U79" s="64"/>
       <c r="V79" s="42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="W79" s="64"/>
       <c r="X79" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y79" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y79" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z79" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA79" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB79" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AC79" s="69">
         <v>85.0</v>
@@ -25980,10 +25975,10 @@
         <v>27.0</v>
       </c>
       <c r="AP79" s="68" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AQ79" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR79" s="70">
         <v>0.0</v>
@@ -26006,7 +26001,7 @@
     </row>
     <row r="80">
       <c r="A80" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B80" s="63">
         <v>0.09</v>
@@ -26024,56 +26019,56 @@
         <v>0.0</v>
       </c>
       <c r="G80" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H80" s="63" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I80" s="64"/>
       <c r="J80" s="42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K80" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L80" s="65"/>
       <c r="M80" s="65"/>
       <c r="N80" s="65"/>
       <c r="O80" s="65"/>
       <c r="P80" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q80" s="42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R80" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S80" s="42" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="T80" s="42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U80" s="64"/>
       <c r="V80" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W80" s="64"/>
       <c r="X80" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y80" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y80" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z80" s="66" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA80" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB80" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AC80" s="69">
         <v>65.0</v>
@@ -26115,10 +26110,10 @@
         <v>35.0</v>
       </c>
       <c r="AP80" s="68" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AQ80" s="68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR80" s="70">
         <v>1.0</v>
@@ -26141,7 +26136,7 @@
     </row>
     <row r="81">
       <c r="A81" s="42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B81" s="63">
         <v>267.89</v>
@@ -26159,56 +26154,56 @@
         <v>6.0</v>
       </c>
       <c r="G81" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H81" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H81" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I81" s="64"/>
       <c r="J81" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K81" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K81" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L81" s="65"/>
       <c r="M81" s="65"/>
       <c r="N81" s="65"/>
       <c r="O81" s="65"/>
       <c r="P81" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q81" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R81" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S81" s="42" t="s">
+        <v>410</v>
+      </c>
+      <c r="T81" s="42" t="s">
         <v>411</v>
-      </c>
-      <c r="T81" s="42" t="s">
-        <v>412</v>
       </c>
       <c r="U81" s="64"/>
       <c r="V81" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W81" s="64"/>
       <c r="X81" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y81" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z81" s="80" t="s">
         <v>185</v>
       </c>
-      <c r="Z81" s="80" t="s">
+      <c r="AA81" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB81" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA81" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB81" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC81" s="69">
         <v>25.0</v>
@@ -26250,10 +26245,10 @@
         <v>181.0</v>
       </c>
       <c r="AP81" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ81" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="AQ81" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="AR81" s="70">
         <v>0.0</v>
@@ -26276,7 +26271,7 @@
     </row>
     <row r="82">
       <c r="A82" s="42" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B82" s="63">
         <v>338.42</v>
@@ -26294,56 +26289,56 @@
         <v>6.0</v>
       </c>
       <c r="G82" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H82" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H82" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I82" s="64"/>
       <c r="J82" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K82" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K82" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L82" s="65"/>
       <c r="M82" s="65"/>
       <c r="N82" s="65"/>
       <c r="O82" s="65"/>
       <c r="P82" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q82" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R82" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S82" s="42" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="T82" s="42" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="U82" s="64"/>
       <c r="V82" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W82" s="64"/>
       <c r="X82" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y82" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z82" s="80" t="s">
         <v>185</v>
       </c>
-      <c r="Z82" s="80" t="s">
+      <c r="AA82" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB82" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA82" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB82" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC82" s="69">
         <v>25.0</v>
@@ -26385,10 +26380,10 @@
         <v>181.0</v>
       </c>
       <c r="AP82" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ82" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="AQ82" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="AR82" s="70">
         <v>0.0</v>
@@ -26411,7 +26406,7 @@
     </row>
     <row r="83">
       <c r="A83" s="42" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B83" s="63">
         <v>100.47</v>
@@ -26429,56 +26424,56 @@
         <v>0.0</v>
       </c>
       <c r="G83" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H83" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H83" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I83" s="64"/>
       <c r="J83" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K83" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K83" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L83" s="65"/>
       <c r="M83" s="65"/>
       <c r="N83" s="65"/>
       <c r="O83" s="65"/>
       <c r="P83" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q83" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R83" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S83" s="42" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T83" s="42" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="U83" s="64"/>
       <c r="V83" s="42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W83" s="64"/>
       <c r="X83" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y83" s="67" t="s">
         <v>184</v>
       </c>
-      <c r="Y83" s="67" t="s">
-        <v>185</v>
-      </c>
       <c r="Z83" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA83" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB83" s="68" t="s">
         <v>227</v>
-      </c>
-      <c r="AA83" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB83" s="68" t="s">
-        <v>228</v>
       </c>
       <c r="AC83" s="69">
         <v>100.0</v>
@@ -26520,10 +26515,10 @@
         <v>0.0</v>
       </c>
       <c r="AP83" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ83" s="68" t="s">
         <v>198</v>
-      </c>
-      <c r="AQ83" s="68" t="s">
-        <v>199</v>
       </c>
       <c r="AR83" s="70">
         <v>4.0</v>
@@ -26546,7 +26541,7 @@
     </row>
     <row r="84">
       <c r="A84" s="42" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B84" s="63">
         <v>441.89</v>
@@ -26564,56 +26559,56 @@
         <v>6.0</v>
       </c>
       <c r="G84" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="H84" s="63" t="s">
         <v>176</v>
-      </c>
-      <c r="H84" s="63" t="s">
-        <v>177</v>
       </c>
       <c r="I84" s="64"/>
       <c r="J84" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="K84" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="K84" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="L84" s="65"/>
       <c r="M84" s="65"/>
       <c r="N84" s="65"/>
       <c r="O84" s="65"/>
       <c r="P84" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q84" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R84" s="42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S84" s="42" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T84" s="42" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="U84" s="64"/>
       <c r="V84" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W84" s="64"/>
       <c r="X84" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Y84" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z84" s="80" t="s">
         <v>185</v>
       </c>
-      <c r="Z84" s="80" t="s">
+      <c r="AA84" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB84" s="68" t="s">
         <v>186</v>
-      </c>
-      <c r="AA84" s="68" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB84" s="68" t="s">
-        <v>187</v>
       </c>
       <c r="AC84" s="69">
         <v>25.0</v>
@@ -26655,10 +26650,10 @@
         <v>181.0</v>
       </c>
       <c r="AP84" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ84" s="68" t="s">
         <v>188</v>
-      </c>
-      <c r="AQ84" s="68" t="s">
-        <v>189</v>
       </c>
       <c r="AR84" s="70">
         <v>0.0</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -271,7 +271,7 @@
     <t>CDB Neon Planejado 150% CDI - 60 dias</t>
   </si>
   <si>
-    <t>Lote 7000 mai.</t>
+    <t>Lote 7600 mai.</t>
   </si>
   <si>
     <t>Lote 3600 mai.</t>
@@ -1827,11 +1827,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1498902442"/>
-        <c:axId val="427643584"/>
+        <c:axId val="2007175572"/>
+        <c:axId val="987094786"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1498902442"/>
+        <c:axId val="2007175572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1883,10 +1883,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427643584"/>
+        <c:crossAx val="987094786"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="427643584"/>
+        <c:axId val="987094786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1950,7 +1950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1498902442"/>
+        <c:crossAx val="2007175572"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -8224,13 +8224,15 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="27" t="s">
         <v>81</v>
       </c>
       <c r="B18" s="23">
         <v>46145.0</v>
       </c>
-      <c r="C18" s="9"/>
+      <c r="C18" s="19">
+        <v>7600.0</v>
+      </c>
       <c r="D18" s="9">
         <v>7000.0</v>
       </c>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1827,11 +1827,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="2007175572"/>
-        <c:axId val="987094786"/>
+        <c:axId val="1003032112"/>
+        <c:axId val="792849031"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2007175572"/>
+        <c:axId val="1003032112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1883,10 +1883,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="987094786"/>
+        <c:crossAx val="792849031"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="987094786"/>
+        <c:axId val="792849031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1950,7 +1950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2007175572"/>
+        <c:crossAx val="1003032112"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -8230,11 +8230,11 @@
       <c r="B18" s="23">
         <v>46145.0</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="23">
+        <v>46145.0</v>
+      </c>
+      <c r="D18" s="19">
         <v>7600.0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>7000.0</v>
       </c>
       <c r="E18" s="38"/>
     </row>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="K4" s="51">
         <f>SUM(C4:C123)</f>
-        <v>211799.41</v>
+        <v>212399.41</v>
       </c>
       <c r="M4" s="52">
         <v>46054.0</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>14883.12</v>
+        <v>17529.01</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>981.56</v>
+        <v>1581.56</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -10911,11 +10911,11 @@
       </c>
       <c r="C7" s="56">
         <f>IF($A7="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>16280</v>
+        <v>16880</v>
       </c>
       <c r="D7" s="56">
         <f t="shared" si="1"/>
-        <v>2045.89</v>
+        <v>2645.89</v>
       </c>
       <c r="E7" s="57">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -10927,14 +10927,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>16929.01</v>
+        <v>17529.01</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>119</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>-2631.35</v>
+        <v>2645.89</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -10964,14 +10964,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>17564.83</v>
+        <v>18164.83</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>120</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>70.11142857</v>
+        <v>112.9685714</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>16980.65</v>
+        <v>17580.65</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>121</v>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>15836.47</v>
+        <v>16436.47</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>122</v>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14042.29</v>
+        <v>14642.29</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>123</v>
@@ -11112,14 +11112,14 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>12648.31</v>
+        <v>13248.31</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>124</v>
       </c>
       <c r="K12" s="58" t="str">
         <f>TEXT(TODAY(),"mmm/yy")</f>
-        <v>abr./26</v>
+        <v>mai./26</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>11754.13</v>
+        <v>12354.13</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7339.95</v>
+        <v>7939.95</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7431.1</v>
+        <v>8031.1</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4375.15</v>
+        <v>4975.15</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>981.56</v>
+        <v>1581.56</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1827,11 +1827,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1003032112"/>
-        <c:axId val="792849031"/>
+        <c:axId val="2091344126"/>
+        <c:axId val="630947835"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1003032112"/>
+        <c:axId val="2091344126"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1883,10 +1883,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="792849031"/>
+        <c:crossAx val="630947835"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="792849031"/>
+        <c:axId val="630947835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1950,7 +1950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1003032112"/>
+        <c:crossAx val="2091344126"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -8227,11 +8227,11 @@
       <c r="A18" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="23">
-        <v>46145.0</v>
-      </c>
-      <c r="C18" s="23">
-        <v>46145.0</v>
+      <c r="B18" s="25">
+        <v>46146.0</v>
+      </c>
+      <c r="C18" s="25">
+        <v>46146.0</v>
       </c>
       <c r="D18" s="19">
         <v>7600.0</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1833,11 +1833,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1246675312"/>
-        <c:axId val="539199386"/>
+        <c:axId val="1949847858"/>
+        <c:axId val="1695210420"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1246675312"/>
+        <c:axId val="1949847858"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1889,10 +1889,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539199386"/>
+        <c:crossAx val="1695210420"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="539199386"/>
+        <c:axId val="1695210420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1956,7 +1956,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1246675312"/>
+        <c:crossAx val="1949847858"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1833,11 +1833,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1949847858"/>
-        <c:axId val="1695210420"/>
+        <c:axId val="1273439569"/>
+        <c:axId val="1631041630"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1949847858"/>
+        <c:axId val="1273439569"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1889,10 +1889,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1695210420"/>
+        <c:crossAx val="1631041630"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1695210420"/>
+        <c:axId val="1631041630"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1956,7 +1956,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1949847858"/>
+        <c:crossAx val="1273439569"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1885,11 +1885,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1668028830"/>
-        <c:axId val="918903352"/>
+        <c:axId val="1171015455"/>
+        <c:axId val="207886665"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1668028830"/>
+        <c:axId val="1171015455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1941,10 +1941,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="918903352"/>
+        <c:crossAx val="207886665"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="918903352"/>
+        <c:axId val="207886665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2008,7 +2008,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1668028830"/>
+        <c:crossAx val="1171015455"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2219,11 +2219,12 @@
         <n v="250.0"/>
         <n v="59.8"/>
         <n v="3122.53"/>
-        <n v="195.0"/>
+        <n v="417.56"/>
         <n v="95.05"/>
         <n v="5372.0"/>
         <n v="113.31"/>
         <n v="580.0"/>
+        <n v="195.0"/>
         <n v="7200.0"/>
         <n v="930.0"/>
         <n v="6800.0"/>
@@ -2393,6 +2394,7 @@
         <item x="98"/>
         <item x="99"/>
         <item x="100"/>
+        <item x="101"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4234,8 +4236,8 @@
       <c r="B77" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C77" s="9">
-        <v>195.0</v>
+      <c r="C77" s="19">
+        <v>417.56</v>
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="28"/>
@@ -10935,7 +10937,7 @@
       </c>
       <c r="K3" s="51">
         <f>SUM(B4:B123)</f>
-        <v>214374.68</v>
+        <v>214597.24</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>120</v>
@@ -11014,7 +11016,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>17331.43</v>
+        <v>17108.87</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -11051,7 +11053,7 @@
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>1383.98</v>
+        <v>1161.42</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -11061,7 +11063,7 @@
       </c>
       <c r="B7" s="56">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>17790.94</v>
+        <v>18013.5</v>
       </c>
       <c r="C7" s="56">
         <f>IF($A7="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11069,7 +11071,7 @@
       </c>
       <c r="D7" s="56">
         <f t="shared" si="1"/>
-        <v>2448.31</v>
+        <v>2225.75</v>
       </c>
       <c r="E7" s="57">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11081,14 +11083,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>17331.43</v>
+        <v>17108.87</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>124</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>2448.31</v>
+        <v>2225.75</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -11118,14 +11120,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>17967.25</v>
+        <v>17744.69</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>125</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>98.85571429</v>
+        <v>82.95857143</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -11155,7 +11157,7 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>17383.07</v>
+        <v>17160.51</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>126</v>
@@ -11192,7 +11194,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>16238.89</v>
+        <v>16016.33</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>127</v>
@@ -11229,7 +11231,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14444.71</v>
+        <v>14222.15</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>128</v>
@@ -11266,7 +11268,7 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>13050.73</v>
+        <v>12828.17</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>129</v>
@@ -11303,7 +11305,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>12156.55</v>
+        <v>11933.99</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11333,7 +11335,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7742.37</v>
+        <v>7519.81</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11364,7 +11366,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7833.52</v>
+        <v>7610.96</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11394,7 +11396,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4777.57</v>
+        <v>4555.01</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11424,7 +11426,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>1383.98</v>
+        <v>1161.42</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1885,11 +1885,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1171015455"/>
-        <c:axId val="207886665"/>
+        <c:axId val="431609867"/>
+        <c:axId val="694196671"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1171015455"/>
+        <c:axId val="431609867"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1941,10 +1941,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="207886665"/>
+        <c:crossAx val="694196671"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="207886665"/>
+        <c:axId val="694196671"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2008,7 +2008,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1171015455"/>
+        <c:crossAx val="431609867"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2220,7 +2220,9 @@
         <n v="59.8"/>
         <n v="3122.53"/>
         <n v="417.56"/>
+        <n v="110.0"/>
         <n v="95.05"/>
+        <n v="980.86"/>
         <n v="5372.0"/>
         <n v="113.31"/>
         <n v="580.0"/>
@@ -2395,6 +2397,8 @@
         <item x="99"/>
         <item x="100"/>
         <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4262,8 +4266,8 @@
       <c r="B79" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C79" s="9">
-        <v>120.0</v>
+      <c r="C79" s="19">
+        <v>110.0</v>
       </c>
       <c r="G79" s="9"/>
       <c r="H79" s="28"/>
@@ -4301,8 +4305,8 @@
       <c r="B82" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="9">
-        <v>981.95</v>
+      <c r="C82" s="19">
+        <v>980.86</v>
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="28"/>
@@ -10937,7 +10941,7 @@
       </c>
       <c r="K3" s="51">
         <f>SUM(B4:B123)</f>
-        <v>214597.24</v>
+        <v>214586.15</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>120</v>
@@ -11016,7 +11020,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>17108.87</v>
+        <v>17119.96</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -11053,7 +11057,7 @@
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>1161.42</v>
+        <v>1172.51</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -11063,7 +11067,7 @@
       </c>
       <c r="B7" s="56">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>18013.5</v>
+        <v>18002.41</v>
       </c>
       <c r="C7" s="56">
         <f>IF($A7="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11071,7 +11075,7 @@
       </c>
       <c r="D7" s="56">
         <f t="shared" si="1"/>
-        <v>2225.75</v>
+        <v>2236.84</v>
       </c>
       <c r="E7" s="57">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11083,14 +11087,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>17108.87</v>
+        <v>17119.96</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>124</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>2225.75</v>
+        <v>2236.84</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -11120,14 +11124,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>17744.69</v>
+        <v>17755.78</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>125</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>82.95857143</v>
+        <v>83.75071429</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -11157,7 +11161,7 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>17160.51</v>
+        <v>17171.6</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>126</v>
@@ -11194,7 +11198,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>16016.33</v>
+        <v>16027.42</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>127</v>
@@ -11231,7 +11235,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14222.15</v>
+        <v>14233.24</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>128</v>
@@ -11268,7 +11272,7 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>12828.17</v>
+        <v>12839.26</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>129</v>
@@ -11305,7 +11309,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>11933.99</v>
+        <v>11945.08</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11335,7 +11339,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7519.81</v>
+        <v>7530.9</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11366,7 +11370,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7610.96</v>
+        <v>7622.05</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11396,7 +11400,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4555.01</v>
+        <v>4566.1</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11426,7 +11430,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>1161.42</v>
+        <v>1172.51</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1891,11 +1891,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="149332456"/>
-        <c:axId val="1495169957"/>
+        <c:axId val="810789996"/>
+        <c:axId val="666644846"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="149332456"/>
+        <c:axId val="810789996"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1947,10 +1947,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1495169957"/>
+        <c:crossAx val="666644846"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1495169957"/>
+        <c:axId val="666644846"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2014,7 +2014,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="149332456"/>
+        <c:crossAx val="810789996"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -8450,7 +8450,7 @@
         <v>46147.0</v>
       </c>
       <c r="D20" s="19">
-        <v>3119.43</v>
+        <v>3119.0</v>
       </c>
       <c r="E20" s="42" t="s">
         <v>85</v>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K4" s="51">
         <f>SUM(C4:C123)</f>
-        <v>218878.09</v>
+        <v>218877.66</v>
       </c>
       <c r="M4" s="52">
         <v>46054.0</v>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>17120.42</v>
+        <v>17119.99</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>1172.97</v>
+        <v>1172.54</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -11129,11 +11129,11 @@
       </c>
       <c r="C7" s="56">
         <f>IF($A7="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>23358.68</v>
+        <v>23358.25</v>
       </c>
       <c r="D7" s="56">
         <f t="shared" si="1"/>
-        <v>2237.3</v>
+        <v>2236.87</v>
       </c>
       <c r="E7" s="57">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11145,14 +11145,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>17120.42</v>
+        <v>17119.99</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>126</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>2237.3</v>
+        <v>2236.87</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -11182,14 +11182,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>17756.24</v>
+        <v>17755.81</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>127</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>83.78357143</v>
+        <v>83.75285714</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>17172.06</v>
+        <v>17171.63</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>128</v>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>16027.88</v>
+        <v>16027.45</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>129</v>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14233.7</v>
+        <v>14233.27</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>130</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>12839.72</v>
+        <v>12839.29</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>131</v>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>11945.54</v>
+        <v>11945.11</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7531.36</v>
+        <v>7530.93</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7622.51</v>
+        <v>7622.08</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4566.56</v>
+        <v>4566.13</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>1172.97</v>
+        <v>1172.54</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1891,11 +1891,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="810789996"/>
-        <c:axId val="666644846"/>
+        <c:axId val="830855195"/>
+        <c:axId val="1007824981"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="810789996"/>
+        <c:axId val="830855195"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1947,10 +1947,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="666644846"/>
+        <c:crossAx val="1007824981"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="666644846"/>
+        <c:axId val="1007824981"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2014,7 +2014,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="810789996"/>
+        <c:crossAx val="830855195"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2228,7 +2228,7 @@
         <n v="3119.43"/>
         <n v="417.1"/>
         <n v="110.0"/>
-        <n v="95.05"/>
+        <n v="98.88"/>
         <n v="980.86"/>
         <n v="5372.0"/>
         <n v="113.31"/>
@@ -4314,8 +4314,8 @@
       <c r="H80" s="28"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="1">
-        <v>46152.0</v>
+      <c r="A81" s="23">
+        <v>46150.0</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>38</v>
@@ -4333,8 +4333,8 @@
       <c r="B82" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C82" s="9">
-        <v>95.05</v>
+      <c r="C82" s="19">
+        <v>98.88</v>
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="28"/>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="K3" s="51">
         <f>SUM(B4:B123)</f>
-        <v>217705.12</v>
+        <v>217708.95</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>122</v>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>17119.99</v>
+        <v>17116.16</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>1172.54</v>
+        <v>1168.71</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="B7" s="56">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>21121.38</v>
+        <v>21125.21</v>
       </c>
       <c r="C7" s="56">
         <f>IF($A7="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="D7" s="56">
         <f t="shared" si="1"/>
-        <v>2236.87</v>
+        <v>2233.04</v>
       </c>
       <c r="E7" s="57">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11145,14 +11145,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>17119.99</v>
+        <v>17116.16</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>126</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>2236.87</v>
+        <v>2233.04</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -11182,14 +11182,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>17755.81</v>
+        <v>17751.98</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>127</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>83.75285714</v>
+        <v>83.47928571</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -11219,14 +11219,14 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>17171.63</v>
+        <v>17167.8</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>128</v>
       </c>
       <c r="K9" s="51">
         <f>MAX(B4:B123)</f>
-        <v>21121.38</v>
+        <v>21125.21</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>16027.45</v>
+        <v>16023.62</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>129</v>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14233.27</v>
+        <v>14229.44</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>130</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>12839.29</v>
+        <v>12835.46</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>131</v>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>11945.11</v>
+        <v>11941.28</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7530.93</v>
+        <v>7527.1</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7622.08</v>
+        <v>7618.25</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4566.13</v>
+        <v>4562.3</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>1172.54</v>
+        <v>1168.71</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -12,7 +12,7 @@
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$224</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Inventário de Lotes'!$A$1:$E$43</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Resumo Mensal'!$A$3:$G$123</definedName>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$84</definedName>
+    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$85</definedName>
   </definedNames>
   <calcPr/>
   <pivotCaches>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="439">
   <si>
     <t>Data</t>
   </si>
@@ -1341,6 +1341,9 @@
   </si>
   <si>
     <t>Rentab, bruta 12M 65,09%; Comparativo 441,89% do CDI; Aplicação D+0; Resgate D+4 corridos + liquidação D+2 úteis; Mov, mínima e saldo mínimo R$ 100; Horário 15h; Risco médio 14</t>
+  </si>
+  <si>
+    <t>Genial 2020 %</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1578,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1763,9 +1766,12 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1891,11 +1897,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="830855195"/>
-        <c:axId val="1007824981"/>
+        <c:axId val="1939784455"/>
+        <c:axId val="1428979078"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="830855195"/>
+        <c:axId val="1939784455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1947,10 +1953,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1007824981"/>
+        <c:crossAx val="1428979078"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1007824981"/>
+        <c:axId val="1428979078"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2014,7 +2020,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="830855195"/>
+        <c:crossAx val="1939784455"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -15575,20 +15581,49 @@
     <col customWidth="1" min="6" max="6" width="16.14"/>
     <col customWidth="1" min="7" max="7" width="12.14"/>
     <col customWidth="1" min="8" max="8" width="20.14"/>
-    <col customWidth="1" min="9" max="10" width="23.0"/>
-    <col customWidth="1" min="11" max="11" width="8.57"/>
-    <col customWidth="1" min="12" max="12" width="14.86"/>
-    <col customWidth="1" min="13" max="16" width="23.0"/>
-    <col customWidth="1" min="17" max="17" width="19.0"/>
-    <col customWidth="1" min="18" max="18" width="14.14"/>
-    <col customWidth="1" min="19" max="19" width="7.43"/>
-    <col customWidth="1" min="20" max="20" width="256.86"/>
-    <col customWidth="1" min="21" max="22" width="23.0"/>
-    <col customWidth="1" min="23" max="23" width="13.29"/>
-    <col customWidth="1" min="24" max="24" width="23.0"/>
-    <col customWidth="1" min="25" max="25" width="23.86"/>
-    <col customWidth="1" min="26" max="26" width="22.86"/>
-    <col customWidth="1" min="27" max="51" width="101.71"/>
+    <col customWidth="1" min="9" max="9" width="20.43"/>
+    <col customWidth="1" min="10" max="10" width="8.57"/>
+    <col customWidth="1" min="11" max="11" width="14.86"/>
+    <col customWidth="1" min="12" max="12" width="16.14"/>
+    <col customWidth="1" min="13" max="13" width="19.0"/>
+    <col customWidth="1" min="14" max="14" width="13.71"/>
+    <col customWidth="1" min="15" max="15" width="15.0"/>
+    <col customWidth="1" min="16" max="16" width="19.0"/>
+    <col customWidth="1" min="17" max="17" width="14.14"/>
+    <col customWidth="1" min="18" max="18" width="7.43"/>
+    <col customWidth="1" min="19" max="19" width="255.29"/>
+    <col customWidth="1" min="20" max="20" width="17.14"/>
+    <col customWidth="1" min="21" max="21" width="15.14"/>
+    <col customWidth="1" min="22" max="22" width="13.29"/>
+    <col customWidth="1" min="23" max="23" width="13.0"/>
+    <col customWidth="1" min="24" max="24" width="23.86"/>
+    <col customWidth="1" min="25" max="25" width="22.86"/>
+    <col customWidth="1" min="26" max="26" width="38.86"/>
+    <col customWidth="1" min="27" max="27" width="16.29"/>
+    <col customWidth="1" min="28" max="28" width="29.43"/>
+    <col customWidth="1" min="29" max="29" width="14.43"/>
+    <col customWidth="1" min="30" max="30" width="12.43"/>
+    <col customWidth="1" min="31" max="31" width="21.29"/>
+    <col customWidth="1" min="32" max="32" width="19.14"/>
+    <col customWidth="1" min="33" max="33" width="17.29"/>
+    <col customWidth="1" min="34" max="34" width="20.0"/>
+    <col customWidth="1" min="35" max="35" width="22.71"/>
+    <col customWidth="1" min="36" max="36" width="17.86"/>
+    <col customWidth="1" min="37" max="37" width="23.43"/>
+    <col customWidth="1" min="38" max="38" width="8.57"/>
+    <col customWidth="1" min="39" max="39" width="23.14"/>
+    <col customWidth="1" min="40" max="40" width="28.43"/>
+    <col customWidth="1" min="41" max="41" width="26.0"/>
+    <col customWidth="1" min="42" max="42" width="28.29"/>
+    <col customWidth="1" min="43" max="43" width="23.0"/>
+    <col customWidth="1" min="44" max="44" width="25.71"/>
+    <col customWidth="1" min="45" max="45" width="25.86"/>
+    <col customWidth="1" min="46" max="46" width="27.14"/>
+    <col customWidth="1" min="47" max="47" width="13.71"/>
+    <col customWidth="1" min="48" max="48" width="28.71"/>
+    <col customWidth="1" min="49" max="49" width="31.71"/>
+    <col customWidth="1" min="50" max="50" width="13.86"/>
+    <col customWidth="1" min="51" max="51" width="24.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27400,4551 +27435,4591 @@
       </c>
     </row>
     <row r="85">
-      <c r="G85" s="65"/>
-      <c r="I85" s="80"/>
+      <c r="A85" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="B85" s="24">
+        <v>220.0</v>
+      </c>
+      <c r="C85" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="D85" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="E85" s="24">
+        <v>60.0</v>
+      </c>
+      <c r="F85" s="24">
+        <v>60.0</v>
+      </c>
+      <c r="G85" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="H85" s="24">
+        <v>100.0</v>
+      </c>
+      <c r="I85" s="80">
+        <v>3000.0</v>
+      </c>
+      <c r="J85" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="K85" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="P85" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q85" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="R85" s="24" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="81"/>
       <c r="G86" s="65"/>
-      <c r="I86" s="80"/>
+      <c r="I86" s="82"/>
     </row>
     <row r="87">
       <c r="B87" s="81"/>
       <c r="G87" s="65"/>
-      <c r="I87" s="80"/>
+      <c r="I87" s="82"/>
     </row>
     <row r="88">
       <c r="B88" s="81"/>
       <c r="G88" s="65"/>
-      <c r="I88" s="80"/>
+      <c r="I88" s="82"/>
     </row>
     <row r="89">
       <c r="B89" s="81"/>
       <c r="G89" s="65"/>
-      <c r="I89" s="80"/>
+      <c r="I89" s="82"/>
     </row>
     <row r="90">
       <c r="B90" s="81"/>
       <c r="G90" s="65"/>
-      <c r="I90" s="80"/>
+      <c r="I90" s="82"/>
     </row>
     <row r="91">
       <c r="B91" s="81"/>
       <c r="G91" s="65"/>
-      <c r="I91" s="80"/>
+      <c r="I91" s="82"/>
     </row>
     <row r="92">
       <c r="B92" s="81"/>
       <c r="G92" s="65"/>
-      <c r="I92" s="80"/>
+      <c r="I92" s="82"/>
     </row>
     <row r="93">
       <c r="B93" s="81"/>
       <c r="G93" s="65"/>
-      <c r="I93" s="80"/>
+      <c r="I93" s="82"/>
     </row>
     <row r="94">
       <c r="B94" s="81"/>
       <c r="G94" s="65"/>
-      <c r="I94" s="80"/>
+      <c r="I94" s="82"/>
     </row>
     <row r="95">
       <c r="B95" s="81"/>
       <c r="G95" s="65"/>
-      <c r="I95" s="80"/>
+      <c r="I95" s="82"/>
     </row>
     <row r="96">
       <c r="B96" s="81"/>
       <c r="G96" s="65"/>
-      <c r="I96" s="80"/>
+      <c r="I96" s="82"/>
     </row>
     <row r="97">
       <c r="B97" s="81"/>
       <c r="G97" s="65"/>
-      <c r="I97" s="80"/>
+      <c r="I97" s="82"/>
     </row>
     <row r="98">
       <c r="B98" s="81"/>
       <c r="G98" s="65"/>
-      <c r="I98" s="80"/>
+      <c r="I98" s="82"/>
     </row>
     <row r="99">
       <c r="B99" s="81"/>
       <c r="G99" s="65"/>
-      <c r="I99" s="80"/>
+      <c r="I99" s="82"/>
     </row>
     <row r="100">
       <c r="B100" s="81"/>
       <c r="G100" s="65"/>
-      <c r="I100" s="80"/>
+      <c r="I100" s="82"/>
     </row>
     <row r="101">
       <c r="B101" s="81"/>
       <c r="G101" s="65"/>
-      <c r="I101" s="80"/>
+      <c r="I101" s="82"/>
     </row>
     <row r="102">
       <c r="B102" s="81"/>
       <c r="G102" s="65"/>
-      <c r="I102" s="80"/>
+      <c r="I102" s="82"/>
     </row>
     <row r="103">
       <c r="B103" s="81"/>
       <c r="G103" s="65"/>
-      <c r="I103" s="80"/>
+      <c r="I103" s="82"/>
     </row>
     <row r="104">
       <c r="B104" s="81"/>
       <c r="G104" s="65"/>
-      <c r="I104" s="80"/>
+      <c r="I104" s="82"/>
     </row>
     <row r="105">
       <c r="B105" s="81"/>
       <c r="G105" s="65"/>
-      <c r="I105" s="80"/>
+      <c r="I105" s="82"/>
     </row>
     <row r="106">
       <c r="B106" s="81"/>
       <c r="G106" s="65"/>
-      <c r="I106" s="80"/>
+      <c r="I106" s="82"/>
     </row>
     <row r="107">
       <c r="B107" s="81"/>
       <c r="G107" s="65"/>
-      <c r="I107" s="80"/>
+      <c r="I107" s="82"/>
     </row>
     <row r="108">
       <c r="B108" s="81"/>
       <c r="G108" s="65"/>
-      <c r="I108" s="80"/>
+      <c r="I108" s="82"/>
     </row>
     <row r="109">
       <c r="B109" s="81"/>
       <c r="G109" s="65"/>
-      <c r="I109" s="80"/>
+      <c r="I109" s="82"/>
     </row>
     <row r="110">
       <c r="B110" s="81"/>
       <c r="G110" s="65"/>
-      <c r="I110" s="80"/>
+      <c r="I110" s="82"/>
     </row>
     <row r="111">
       <c r="B111" s="81"/>
       <c r="G111" s="65"/>
-      <c r="I111" s="80"/>
+      <c r="I111" s="82"/>
     </row>
     <row r="112">
       <c r="B112" s="81"/>
       <c r="G112" s="65"/>
-      <c r="I112" s="80"/>
+      <c r="I112" s="82"/>
     </row>
     <row r="113">
       <c r="B113" s="81"/>
       <c r="G113" s="65"/>
-      <c r="I113" s="80"/>
+      <c r="I113" s="82"/>
     </row>
     <row r="114">
       <c r="B114" s="81"/>
       <c r="G114" s="65"/>
-      <c r="I114" s="80"/>
+      <c r="I114" s="82"/>
     </row>
     <row r="115">
       <c r="B115" s="81"/>
       <c r="G115" s="65"/>
-      <c r="I115" s="80"/>
+      <c r="I115" s="82"/>
     </row>
     <row r="116">
       <c r="B116" s="81"/>
       <c r="G116" s="65"/>
-      <c r="I116" s="80"/>
+      <c r="I116" s="82"/>
     </row>
     <row r="117">
       <c r="B117" s="81"/>
       <c r="G117" s="65"/>
-      <c r="I117" s="80"/>
+      <c r="I117" s="82"/>
     </row>
     <row r="118">
       <c r="B118" s="81"/>
       <c r="G118" s="65"/>
-      <c r="I118" s="80"/>
+      <c r="I118" s="82"/>
     </row>
     <row r="119">
       <c r="B119" s="81"/>
       <c r="G119" s="65"/>
-      <c r="I119" s="80"/>
+      <c r="I119" s="82"/>
     </row>
     <row r="120">
       <c r="B120" s="81"/>
       <c r="G120" s="65"/>
-      <c r="I120" s="80"/>
+      <c r="I120" s="82"/>
     </row>
     <row r="121">
       <c r="B121" s="81"/>
       <c r="G121" s="65"/>
-      <c r="I121" s="80"/>
+      <c r="I121" s="82"/>
     </row>
     <row r="122">
       <c r="B122" s="81"/>
       <c r="G122" s="65"/>
-      <c r="I122" s="80"/>
+      <c r="I122" s="82"/>
     </row>
     <row r="123">
       <c r="B123" s="81"/>
       <c r="G123" s="65"/>
-      <c r="I123" s="80"/>
+      <c r="I123" s="82"/>
     </row>
     <row r="124">
       <c r="B124" s="81"/>
       <c r="G124" s="65"/>
-      <c r="I124" s="80"/>
+      <c r="I124" s="82"/>
     </row>
     <row r="125">
       <c r="B125" s="81"/>
       <c r="G125" s="65"/>
-      <c r="I125" s="80"/>
+      <c r="I125" s="82"/>
     </row>
     <row r="126">
       <c r="B126" s="81"/>
       <c r="G126" s="65"/>
-      <c r="I126" s="80"/>
+      <c r="I126" s="82"/>
     </row>
     <row r="127">
       <c r="B127" s="81"/>
       <c r="G127" s="65"/>
-      <c r="I127" s="80"/>
+      <c r="I127" s="82"/>
     </row>
     <row r="128">
       <c r="B128" s="81"/>
       <c r="G128" s="65"/>
-      <c r="I128" s="80"/>
+      <c r="I128" s="82"/>
     </row>
     <row r="129">
       <c r="B129" s="81"/>
       <c r="G129" s="65"/>
-      <c r="I129" s="80"/>
+      <c r="I129" s="82"/>
     </row>
     <row r="130">
       <c r="B130" s="81"/>
       <c r="G130" s="65"/>
-      <c r="I130" s="80"/>
+      <c r="I130" s="82"/>
     </row>
     <row r="131">
       <c r="B131" s="81"/>
       <c r="G131" s="65"/>
-      <c r="I131" s="80"/>
+      <c r="I131" s="82"/>
     </row>
     <row r="132">
       <c r="B132" s="81"/>
       <c r="G132" s="65"/>
-      <c r="I132" s="80"/>
+      <c r="I132" s="82"/>
     </row>
     <row r="133">
       <c r="B133" s="81"/>
       <c r="G133" s="65"/>
-      <c r="I133" s="80"/>
+      <c r="I133" s="82"/>
     </row>
     <row r="134">
       <c r="B134" s="81"/>
       <c r="G134" s="65"/>
-      <c r="I134" s="80"/>
+      <c r="I134" s="82"/>
     </row>
     <row r="135">
       <c r="B135" s="81"/>
       <c r="G135" s="65"/>
-      <c r="I135" s="80"/>
+      <c r="I135" s="82"/>
     </row>
     <row r="136">
       <c r="B136" s="81"/>
       <c r="G136" s="65"/>
-      <c r="I136" s="80"/>
+      <c r="I136" s="82"/>
     </row>
     <row r="137">
       <c r="B137" s="81"/>
       <c r="G137" s="65"/>
-      <c r="I137" s="80"/>
+      <c r="I137" s="82"/>
     </row>
     <row r="138">
       <c r="B138" s="81"/>
       <c r="G138" s="65"/>
-      <c r="I138" s="80"/>
+      <c r="I138" s="82"/>
     </row>
     <row r="139">
       <c r="B139" s="81"/>
       <c r="G139" s="65"/>
-      <c r="I139" s="80"/>
+      <c r="I139" s="82"/>
     </row>
     <row r="140">
       <c r="B140" s="81"/>
       <c r="G140" s="65"/>
-      <c r="I140" s="80"/>
+      <c r="I140" s="82"/>
     </row>
     <row r="141">
       <c r="B141" s="81"/>
       <c r="G141" s="65"/>
-      <c r="I141" s="80"/>
+      <c r="I141" s="82"/>
     </row>
     <row r="142">
       <c r="B142" s="81"/>
       <c r="G142" s="65"/>
-      <c r="I142" s="80"/>
+      <c r="I142" s="82"/>
     </row>
     <row r="143">
       <c r="B143" s="81"/>
       <c r="G143" s="65"/>
-      <c r="I143" s="80"/>
+      <c r="I143" s="82"/>
     </row>
     <row r="144">
       <c r="B144" s="81"/>
       <c r="G144" s="65"/>
-      <c r="I144" s="80"/>
+      <c r="I144" s="82"/>
     </row>
     <row r="145">
       <c r="B145" s="81"/>
       <c r="G145" s="65"/>
-      <c r="I145" s="80"/>
+      <c r="I145" s="82"/>
     </row>
     <row r="146">
       <c r="B146" s="81"/>
       <c r="G146" s="65"/>
-      <c r="I146" s="80"/>
+      <c r="I146" s="82"/>
     </row>
     <row r="147">
       <c r="B147" s="81"/>
       <c r="G147" s="65"/>
-      <c r="I147" s="80"/>
+      <c r="I147" s="82"/>
     </row>
     <row r="148">
       <c r="B148" s="81"/>
       <c r="G148" s="65"/>
-      <c r="I148" s="80"/>
+      <c r="I148" s="82"/>
     </row>
     <row r="149">
       <c r="B149" s="81"/>
       <c r="G149" s="65"/>
-      <c r="I149" s="80"/>
+      <c r="I149" s="82"/>
     </row>
     <row r="150">
       <c r="B150" s="81"/>
       <c r="G150" s="65"/>
-      <c r="I150" s="80"/>
+      <c r="I150" s="82"/>
     </row>
     <row r="151">
       <c r="B151" s="81"/>
       <c r="G151" s="65"/>
-      <c r="I151" s="80"/>
+      <c r="I151" s="82"/>
     </row>
     <row r="152">
       <c r="B152" s="81"/>
       <c r="G152" s="65"/>
-      <c r="I152" s="80"/>
+      <c r="I152" s="82"/>
     </row>
     <row r="153">
       <c r="B153" s="81"/>
       <c r="G153" s="65"/>
-      <c r="I153" s="80"/>
+      <c r="I153" s="82"/>
     </row>
     <row r="154">
       <c r="B154" s="81"/>
       <c r="G154" s="65"/>
-      <c r="I154" s="80"/>
+      <c r="I154" s="82"/>
     </row>
     <row r="155">
       <c r="B155" s="81"/>
       <c r="G155" s="65"/>
-      <c r="I155" s="80"/>
+      <c r="I155" s="82"/>
     </row>
     <row r="156">
       <c r="B156" s="81"/>
       <c r="G156" s="65"/>
-      <c r="I156" s="80"/>
+      <c r="I156" s="82"/>
     </row>
     <row r="157">
       <c r="B157" s="81"/>
       <c r="G157" s="65"/>
-      <c r="I157" s="80"/>
+      <c r="I157" s="82"/>
     </row>
     <row r="158">
       <c r="B158" s="81"/>
       <c r="G158" s="65"/>
-      <c r="I158" s="80"/>
+      <c r="I158" s="82"/>
     </row>
     <row r="159">
       <c r="B159" s="81"/>
       <c r="G159" s="65"/>
-      <c r="I159" s="80"/>
+      <c r="I159" s="82"/>
     </row>
     <row r="160">
       <c r="B160" s="81"/>
       <c r="G160" s="65"/>
-      <c r="I160" s="80"/>
+      <c r="I160" s="82"/>
     </row>
     <row r="161">
       <c r="B161" s="81"/>
       <c r="G161" s="65"/>
-      <c r="I161" s="80"/>
+      <c r="I161" s="82"/>
     </row>
     <row r="162">
       <c r="B162" s="81"/>
       <c r="G162" s="65"/>
-      <c r="I162" s="80"/>
+      <c r="I162" s="82"/>
     </row>
     <row r="163">
       <c r="B163" s="81"/>
       <c r="G163" s="65"/>
-      <c r="I163" s="80"/>
+      <c r="I163" s="82"/>
     </row>
     <row r="164">
       <c r="B164" s="81"/>
       <c r="G164" s="65"/>
-      <c r="I164" s="80"/>
+      <c r="I164" s="82"/>
     </row>
     <row r="165">
       <c r="B165" s="81"/>
       <c r="G165" s="65"/>
-      <c r="I165" s="80"/>
+      <c r="I165" s="82"/>
     </row>
     <row r="166">
       <c r="B166" s="81"/>
       <c r="G166" s="65"/>
-      <c r="I166" s="80"/>
+      <c r="I166" s="82"/>
     </row>
     <row r="167">
       <c r="B167" s="81"/>
       <c r="G167" s="65"/>
-      <c r="I167" s="80"/>
+      <c r="I167" s="82"/>
     </row>
     <row r="168">
       <c r="B168" s="81"/>
       <c r="G168" s="65"/>
-      <c r="I168" s="80"/>
+      <c r="I168" s="82"/>
     </row>
     <row r="169">
       <c r="B169" s="81"/>
       <c r="G169" s="65"/>
-      <c r="I169" s="80"/>
+      <c r="I169" s="82"/>
     </row>
     <row r="170">
       <c r="B170" s="81"/>
       <c r="G170" s="65"/>
-      <c r="I170" s="80"/>
+      <c r="I170" s="82"/>
     </row>
     <row r="171">
       <c r="B171" s="81"/>
       <c r="G171" s="65"/>
-      <c r="I171" s="80"/>
+      <c r="I171" s="82"/>
     </row>
     <row r="172">
       <c r="B172" s="81"/>
       <c r="G172" s="65"/>
-      <c r="I172" s="80"/>
+      <c r="I172" s="82"/>
     </row>
     <row r="173">
       <c r="B173" s="81"/>
       <c r="G173" s="65"/>
-      <c r="I173" s="80"/>
+      <c r="I173" s="82"/>
     </row>
     <row r="174">
       <c r="B174" s="81"/>
       <c r="G174" s="65"/>
-      <c r="I174" s="80"/>
+      <c r="I174" s="82"/>
     </row>
     <row r="175">
       <c r="B175" s="81"/>
       <c r="G175" s="65"/>
-      <c r="I175" s="80"/>
+      <c r="I175" s="82"/>
     </row>
     <row r="176">
       <c r="B176" s="81"/>
       <c r="G176" s="65"/>
-      <c r="I176" s="80"/>
+      <c r="I176" s="82"/>
     </row>
     <row r="177">
       <c r="B177" s="81"/>
       <c r="G177" s="65"/>
-      <c r="I177" s="80"/>
+      <c r="I177" s="82"/>
     </row>
     <row r="178">
       <c r="B178" s="81"/>
       <c r="G178" s="65"/>
-      <c r="I178" s="80"/>
+      <c r="I178" s="82"/>
     </row>
     <row r="179">
       <c r="B179" s="81"/>
       <c r="G179" s="65"/>
-      <c r="I179" s="80"/>
+      <c r="I179" s="82"/>
     </row>
     <row r="180">
       <c r="B180" s="81"/>
       <c r="G180" s="65"/>
-      <c r="I180" s="80"/>
+      <c r="I180" s="82"/>
     </row>
     <row r="181">
       <c r="B181" s="81"/>
       <c r="G181" s="65"/>
-      <c r="I181" s="80"/>
+      <c r="I181" s="82"/>
     </row>
     <row r="182">
       <c r="B182" s="81"/>
       <c r="G182" s="65"/>
-      <c r="I182" s="80"/>
+      <c r="I182" s="82"/>
     </row>
     <row r="183">
       <c r="B183" s="81"/>
       <c r="G183" s="65"/>
-      <c r="I183" s="80"/>
+      <c r="I183" s="82"/>
     </row>
     <row r="184">
       <c r="B184" s="81"/>
       <c r="G184" s="65"/>
-      <c r="I184" s="80"/>
+      <c r="I184" s="82"/>
     </row>
     <row r="185">
       <c r="B185" s="81"/>
       <c r="G185" s="65"/>
-      <c r="I185" s="80"/>
+      <c r="I185" s="82"/>
     </row>
     <row r="186">
       <c r="B186" s="81"/>
       <c r="G186" s="65"/>
-      <c r="I186" s="80"/>
+      <c r="I186" s="82"/>
     </row>
     <row r="187">
       <c r="B187" s="81"/>
       <c r="G187" s="65"/>
-      <c r="I187" s="80"/>
+      <c r="I187" s="82"/>
     </row>
     <row r="188">
       <c r="B188" s="81"/>
       <c r="G188" s="65"/>
-      <c r="I188" s="80"/>
+      <c r="I188" s="82"/>
     </row>
     <row r="189">
       <c r="B189" s="81"/>
       <c r="G189" s="65"/>
-      <c r="I189" s="80"/>
+      <c r="I189" s="82"/>
     </row>
     <row r="190">
       <c r="B190" s="81"/>
       <c r="G190" s="65"/>
-      <c r="I190" s="80"/>
+      <c r="I190" s="82"/>
     </row>
     <row r="191">
       <c r="B191" s="81"/>
       <c r="G191" s="65"/>
-      <c r="I191" s="80"/>
+      <c r="I191" s="82"/>
     </row>
     <row r="192">
       <c r="B192" s="81"/>
       <c r="G192" s="65"/>
-      <c r="I192" s="80"/>
+      <c r="I192" s="82"/>
     </row>
     <row r="193">
       <c r="B193" s="81"/>
       <c r="G193" s="65"/>
-      <c r="I193" s="80"/>
+      <c r="I193" s="82"/>
     </row>
     <row r="194">
       <c r="B194" s="81"/>
       <c r="G194" s="65"/>
-      <c r="I194" s="80"/>
+      <c r="I194" s="82"/>
     </row>
     <row r="195">
       <c r="B195" s="81"/>
       <c r="G195" s="65"/>
-      <c r="I195" s="80"/>
+      <c r="I195" s="82"/>
     </row>
     <row r="196">
       <c r="B196" s="81"/>
       <c r="G196" s="65"/>
-      <c r="I196" s="80"/>
+      <c r="I196" s="82"/>
     </row>
     <row r="197">
       <c r="B197" s="81"/>
       <c r="G197" s="65"/>
-      <c r="I197" s="80"/>
+      <c r="I197" s="82"/>
     </row>
     <row r="198">
       <c r="B198" s="81"/>
       <c r="G198" s="65"/>
-      <c r="I198" s="80"/>
+      <c r="I198" s="82"/>
     </row>
     <row r="199">
       <c r="B199" s="81"/>
       <c r="G199" s="65"/>
-      <c r="I199" s="80"/>
+      <c r="I199" s="82"/>
     </row>
     <row r="200">
       <c r="B200" s="81"/>
       <c r="G200" s="65"/>
-      <c r="I200" s="80"/>
+      <c r="I200" s="82"/>
     </row>
     <row r="201">
       <c r="B201" s="81"/>
       <c r="G201" s="65"/>
-      <c r="I201" s="80"/>
+      <c r="I201" s="82"/>
     </row>
     <row r="202">
       <c r="B202" s="81"/>
       <c r="G202" s="65"/>
-      <c r="I202" s="80"/>
+      <c r="I202" s="82"/>
     </row>
     <row r="203">
       <c r="B203" s="81"/>
       <c r="G203" s="65"/>
-      <c r="I203" s="80"/>
+      <c r="I203" s="82"/>
     </row>
     <row r="204">
       <c r="B204" s="81"/>
       <c r="G204" s="65"/>
-      <c r="I204" s="80"/>
+      <c r="I204" s="82"/>
     </row>
     <row r="205">
       <c r="B205" s="81"/>
       <c r="G205" s="65"/>
-      <c r="I205" s="80"/>
+      <c r="I205" s="82"/>
     </row>
     <row r="206">
       <c r="B206" s="81"/>
       <c r="G206" s="65"/>
-      <c r="I206" s="80"/>
+      <c r="I206" s="82"/>
     </row>
     <row r="207">
       <c r="B207" s="81"/>
       <c r="G207" s="65"/>
-      <c r="I207" s="80"/>
+      <c r="I207" s="82"/>
     </row>
     <row r="208">
       <c r="B208" s="81"/>
       <c r="G208" s="65"/>
-      <c r="I208" s="80"/>
+      <c r="I208" s="82"/>
     </row>
     <row r="209">
       <c r="B209" s="81"/>
       <c r="G209" s="65"/>
-      <c r="I209" s="80"/>
+      <c r="I209" s="82"/>
     </row>
     <row r="210">
       <c r="B210" s="81"/>
       <c r="G210" s="65"/>
-      <c r="I210" s="80"/>
+      <c r="I210" s="82"/>
     </row>
     <row r="211">
       <c r="B211" s="81"/>
       <c r="G211" s="65"/>
-      <c r="I211" s="80"/>
+      <c r="I211" s="82"/>
     </row>
     <row r="212">
       <c r="B212" s="81"/>
       <c r="G212" s="65"/>
-      <c r="I212" s="80"/>
+      <c r="I212" s="82"/>
     </row>
     <row r="213">
       <c r="B213" s="81"/>
       <c r="G213" s="65"/>
-      <c r="I213" s="80"/>
+      <c r="I213" s="82"/>
     </row>
     <row r="214">
       <c r="B214" s="81"/>
       <c r="G214" s="65"/>
-      <c r="I214" s="80"/>
+      <c r="I214" s="82"/>
     </row>
     <row r="215">
       <c r="B215" s="81"/>
       <c r="G215" s="65"/>
-      <c r="I215" s="80"/>
+      <c r="I215" s="82"/>
     </row>
     <row r="216">
       <c r="B216" s="81"/>
       <c r="G216" s="65"/>
-      <c r="I216" s="80"/>
+      <c r="I216" s="82"/>
     </row>
     <row r="217">
       <c r="B217" s="81"/>
       <c r="G217" s="65"/>
-      <c r="I217" s="80"/>
+      <c r="I217" s="82"/>
     </row>
     <row r="218">
       <c r="B218" s="81"/>
       <c r="G218" s="65"/>
-      <c r="I218" s="80"/>
+      <c r="I218" s="82"/>
     </row>
     <row r="219">
       <c r="B219" s="81"/>
       <c r="G219" s="65"/>
-      <c r="I219" s="80"/>
+      <c r="I219" s="82"/>
     </row>
     <row r="220">
       <c r="B220" s="81"/>
       <c r="G220" s="65"/>
-      <c r="I220" s="80"/>
+      <c r="I220" s="82"/>
     </row>
     <row r="221">
       <c r="B221" s="81"/>
       <c r="G221" s="65"/>
-      <c r="I221" s="80"/>
+      <c r="I221" s="82"/>
     </row>
     <row r="222">
       <c r="B222" s="81"/>
       <c r="G222" s="65"/>
-      <c r="I222" s="80"/>
+      <c r="I222" s="82"/>
     </row>
     <row r="223">
       <c r="B223" s="81"/>
       <c r="G223" s="65"/>
-      <c r="I223" s="80"/>
+      <c r="I223" s="82"/>
     </row>
     <row r="224">
       <c r="B224" s="81"/>
       <c r="G224" s="65"/>
-      <c r="I224" s="80"/>
+      <c r="I224" s="82"/>
     </row>
     <row r="225">
       <c r="B225" s="81"/>
       <c r="G225" s="65"/>
-      <c r="I225" s="80"/>
+      <c r="I225" s="82"/>
     </row>
     <row r="226">
       <c r="B226" s="81"/>
       <c r="G226" s="65"/>
-      <c r="I226" s="80"/>
+      <c r="I226" s="82"/>
     </row>
     <row r="227">
       <c r="B227" s="81"/>
       <c r="G227" s="65"/>
-      <c r="I227" s="80"/>
+      <c r="I227" s="82"/>
     </row>
     <row r="228">
       <c r="B228" s="81"/>
       <c r="G228" s="65"/>
-      <c r="I228" s="80"/>
+      <c r="I228" s="82"/>
     </row>
     <row r="229">
       <c r="B229" s="81"/>
       <c r="G229" s="65"/>
-      <c r="I229" s="80"/>
+      <c r="I229" s="82"/>
     </row>
     <row r="230">
       <c r="B230" s="81"/>
       <c r="G230" s="65"/>
-      <c r="I230" s="80"/>
+      <c r="I230" s="82"/>
     </row>
     <row r="231">
       <c r="B231" s="81"/>
       <c r="G231" s="65"/>
-      <c r="I231" s="80"/>
+      <c r="I231" s="82"/>
     </row>
     <row r="232">
       <c r="B232" s="81"/>
       <c r="G232" s="65"/>
-      <c r="I232" s="80"/>
+      <c r="I232" s="82"/>
     </row>
     <row r="233">
       <c r="B233" s="81"/>
       <c r="G233" s="65"/>
-      <c r="I233" s="80"/>
+      <c r="I233" s="82"/>
     </row>
     <row r="234">
       <c r="B234" s="81"/>
       <c r="G234" s="65"/>
-      <c r="I234" s="80"/>
+      <c r="I234" s="82"/>
     </row>
     <row r="235">
       <c r="B235" s="81"/>
       <c r="G235" s="65"/>
-      <c r="I235" s="80"/>
+      <c r="I235" s="82"/>
     </row>
     <row r="236">
       <c r="B236" s="81"/>
       <c r="G236" s="65"/>
-      <c r="I236" s="80"/>
+      <c r="I236" s="82"/>
     </row>
     <row r="237">
       <c r="B237" s="81"/>
       <c r="G237" s="65"/>
-      <c r="I237" s="80"/>
+      <c r="I237" s="82"/>
     </row>
     <row r="238">
       <c r="B238" s="81"/>
       <c r="G238" s="65"/>
-      <c r="I238" s="80"/>
+      <c r="I238" s="82"/>
     </row>
     <row r="239">
       <c r="B239" s="81"/>
       <c r="G239" s="65"/>
-      <c r="I239" s="80"/>
+      <c r="I239" s="82"/>
     </row>
     <row r="240">
       <c r="B240" s="81"/>
       <c r="G240" s="65"/>
-      <c r="I240" s="80"/>
+      <c r="I240" s="82"/>
     </row>
     <row r="241">
       <c r="B241" s="81"/>
       <c r="G241" s="65"/>
-      <c r="I241" s="80"/>
+      <c r="I241" s="82"/>
     </row>
     <row r="242">
       <c r="B242" s="81"/>
       <c r="G242" s="65"/>
-      <c r="I242" s="80"/>
+      <c r="I242" s="82"/>
     </row>
     <row r="243">
       <c r="B243" s="81"/>
       <c r="G243" s="65"/>
-      <c r="I243" s="80"/>
+      <c r="I243" s="82"/>
     </row>
     <row r="244">
       <c r="B244" s="81"/>
       <c r="G244" s="65"/>
-      <c r="I244" s="80"/>
+      <c r="I244" s="82"/>
     </row>
     <row r="245">
       <c r="B245" s="81"/>
       <c r="G245" s="65"/>
-      <c r="I245" s="80"/>
+      <c r="I245" s="82"/>
     </row>
     <row r="246">
       <c r="B246" s="81"/>
       <c r="G246" s="65"/>
-      <c r="I246" s="80"/>
+      <c r="I246" s="82"/>
     </row>
     <row r="247">
       <c r="B247" s="81"/>
       <c r="G247" s="65"/>
-      <c r="I247" s="80"/>
+      <c r="I247" s="82"/>
     </row>
     <row r="248">
       <c r="B248" s="81"/>
       <c r="G248" s="65"/>
-      <c r="I248" s="80"/>
+      <c r="I248" s="82"/>
     </row>
     <row r="249">
       <c r="B249" s="81"/>
       <c r="G249" s="65"/>
-      <c r="I249" s="80"/>
+      <c r="I249" s="82"/>
     </row>
     <row r="250">
       <c r="B250" s="81"/>
       <c r="G250" s="65"/>
-      <c r="I250" s="80"/>
+      <c r="I250" s="82"/>
     </row>
     <row r="251">
       <c r="B251" s="81"/>
       <c r="G251" s="65"/>
-      <c r="I251" s="80"/>
+      <c r="I251" s="82"/>
     </row>
     <row r="252">
       <c r="B252" s="81"/>
       <c r="G252" s="65"/>
-      <c r="I252" s="80"/>
+      <c r="I252" s="82"/>
     </row>
     <row r="253">
       <c r="B253" s="81"/>
       <c r="G253" s="65"/>
-      <c r="I253" s="80"/>
+      <c r="I253" s="82"/>
     </row>
     <row r="254">
       <c r="B254" s="81"/>
       <c r="G254" s="65"/>
-      <c r="I254" s="80"/>
+      <c r="I254" s="82"/>
     </row>
     <row r="255">
       <c r="B255" s="81"/>
       <c r="G255" s="65"/>
-      <c r="I255" s="80"/>
+      <c r="I255" s="82"/>
     </row>
     <row r="256">
       <c r="B256" s="81"/>
       <c r="G256" s="65"/>
-      <c r="I256" s="80"/>
+      <c r="I256" s="82"/>
     </row>
     <row r="257">
       <c r="B257" s="81"/>
       <c r="G257" s="65"/>
-      <c r="I257" s="80"/>
+      <c r="I257" s="82"/>
     </row>
     <row r="258">
       <c r="B258" s="81"/>
       <c r="G258" s="65"/>
-      <c r="I258" s="80"/>
+      <c r="I258" s="82"/>
     </row>
     <row r="259">
       <c r="B259" s="81"/>
       <c r="G259" s="65"/>
-      <c r="I259" s="80"/>
+      <c r="I259" s="82"/>
     </row>
     <row r="260">
       <c r="B260" s="81"/>
       <c r="G260" s="65"/>
-      <c r="I260" s="80"/>
+      <c r="I260" s="82"/>
     </row>
     <row r="261">
       <c r="B261" s="81"/>
       <c r="G261" s="65"/>
-      <c r="I261" s="80"/>
+      <c r="I261" s="82"/>
     </row>
     <row r="262">
       <c r="B262" s="81"/>
       <c r="G262" s="65"/>
-      <c r="I262" s="80"/>
+      <c r="I262" s="82"/>
     </row>
     <row r="263">
       <c r="B263" s="81"/>
       <c r="G263" s="65"/>
-      <c r="I263" s="80"/>
+      <c r="I263" s="82"/>
     </row>
     <row r="264">
       <c r="B264" s="81"/>
       <c r="G264" s="65"/>
-      <c r="I264" s="80"/>
+      <c r="I264" s="82"/>
     </row>
     <row r="265">
       <c r="B265" s="81"/>
       <c r="G265" s="65"/>
-      <c r="I265" s="80"/>
+      <c r="I265" s="82"/>
     </row>
     <row r="266">
       <c r="B266" s="81"/>
       <c r="G266" s="65"/>
-      <c r="I266" s="80"/>
+      <c r="I266" s="82"/>
     </row>
     <row r="267">
       <c r="B267" s="81"/>
       <c r="G267" s="65"/>
-      <c r="I267" s="80"/>
+      <c r="I267" s="82"/>
     </row>
     <row r="268">
       <c r="B268" s="81"/>
       <c r="G268" s="65"/>
-      <c r="I268" s="80"/>
+      <c r="I268" s="82"/>
     </row>
     <row r="269">
       <c r="B269" s="81"/>
       <c r="G269" s="65"/>
-      <c r="I269" s="80"/>
+      <c r="I269" s="82"/>
     </row>
     <row r="270">
       <c r="B270" s="81"/>
       <c r="G270" s="65"/>
-      <c r="I270" s="80"/>
+      <c r="I270" s="82"/>
     </row>
     <row r="271">
       <c r="B271" s="81"/>
       <c r="G271" s="65"/>
-      <c r="I271" s="80"/>
+      <c r="I271" s="82"/>
     </row>
     <row r="272">
       <c r="B272" s="81"/>
       <c r="G272" s="65"/>
-      <c r="I272" s="80"/>
+      <c r="I272" s="82"/>
     </row>
     <row r="273">
       <c r="B273" s="81"/>
       <c r="G273" s="65"/>
-      <c r="I273" s="80"/>
+      <c r="I273" s="82"/>
     </row>
     <row r="274">
       <c r="B274" s="81"/>
       <c r="G274" s="65"/>
-      <c r="I274" s="80"/>
+      <c r="I274" s="82"/>
     </row>
     <row r="275">
       <c r="B275" s="81"/>
       <c r="G275" s="65"/>
-      <c r="I275" s="80"/>
+      <c r="I275" s="82"/>
     </row>
     <row r="276">
       <c r="B276" s="81"/>
       <c r="G276" s="65"/>
-      <c r="I276" s="80"/>
+      <c r="I276" s="82"/>
     </row>
     <row r="277">
       <c r="B277" s="81"/>
       <c r="G277" s="65"/>
-      <c r="I277" s="80"/>
+      <c r="I277" s="82"/>
     </row>
     <row r="278">
       <c r="B278" s="81"/>
       <c r="G278" s="65"/>
-      <c r="I278" s="80"/>
+      <c r="I278" s="82"/>
     </row>
     <row r="279">
       <c r="B279" s="81"/>
       <c r="G279" s="65"/>
-      <c r="I279" s="80"/>
+      <c r="I279" s="82"/>
     </row>
     <row r="280">
       <c r="B280" s="81"/>
       <c r="G280" s="65"/>
-      <c r="I280" s="80"/>
+      <c r="I280" s="82"/>
     </row>
     <row r="281">
       <c r="B281" s="81"/>
       <c r="G281" s="65"/>
-      <c r="I281" s="80"/>
+      <c r="I281" s="82"/>
     </row>
     <row r="282">
       <c r="B282" s="81"/>
       <c r="G282" s="65"/>
-      <c r="I282" s="80"/>
+      <c r="I282" s="82"/>
     </row>
     <row r="283">
       <c r="B283" s="81"/>
       <c r="G283" s="65"/>
-      <c r="I283" s="80"/>
+      <c r="I283" s="82"/>
     </row>
     <row r="284">
       <c r="B284" s="81"/>
       <c r="G284" s="65"/>
-      <c r="I284" s="80"/>
+      <c r="I284" s="82"/>
     </row>
     <row r="285">
       <c r="B285" s="81"/>
       <c r="G285" s="65"/>
-      <c r="I285" s="80"/>
+      <c r="I285" s="82"/>
     </row>
     <row r="286">
       <c r="B286" s="81"/>
       <c r="G286" s="65"/>
-      <c r="I286" s="80"/>
+      <c r="I286" s="82"/>
     </row>
     <row r="287">
       <c r="B287" s="81"/>
       <c r="G287" s="65"/>
-      <c r="I287" s="80"/>
+      <c r="I287" s="82"/>
     </row>
     <row r="288">
       <c r="B288" s="81"/>
       <c r="G288" s="65"/>
-      <c r="I288" s="80"/>
+      <c r="I288" s="82"/>
     </row>
     <row r="289">
       <c r="B289" s="81"/>
       <c r="G289" s="65"/>
-      <c r="I289" s="80"/>
+      <c r="I289" s="82"/>
     </row>
     <row r="290">
       <c r="B290" s="81"/>
       <c r="G290" s="65"/>
-      <c r="I290" s="80"/>
+      <c r="I290" s="82"/>
     </row>
     <row r="291">
       <c r="B291" s="81"/>
       <c r="G291" s="65"/>
-      <c r="I291" s="80"/>
+      <c r="I291" s="82"/>
     </row>
     <row r="292">
       <c r="B292" s="81"/>
       <c r="G292" s="65"/>
-      <c r="I292" s="80"/>
+      <c r="I292" s="82"/>
     </row>
     <row r="293">
       <c r="B293" s="81"/>
       <c r="G293" s="65"/>
-      <c r="I293" s="80"/>
+      <c r="I293" s="82"/>
     </row>
     <row r="294">
       <c r="B294" s="81"/>
       <c r="G294" s="65"/>
-      <c r="I294" s="80"/>
+      <c r="I294" s="82"/>
     </row>
     <row r="295">
       <c r="B295" s="81"/>
       <c r="G295" s="65"/>
-      <c r="I295" s="80"/>
+      <c r="I295" s="82"/>
     </row>
     <row r="296">
       <c r="B296" s="81"/>
       <c r="G296" s="65"/>
-      <c r="I296" s="80"/>
+      <c r="I296" s="82"/>
     </row>
     <row r="297">
       <c r="B297" s="81"/>
       <c r="G297" s="65"/>
-      <c r="I297" s="80"/>
+      <c r="I297" s="82"/>
     </row>
     <row r="298">
       <c r="B298" s="81"/>
       <c r="G298" s="65"/>
-      <c r="I298" s="80"/>
+      <c r="I298" s="82"/>
     </row>
     <row r="299">
       <c r="B299" s="81"/>
       <c r="G299" s="65"/>
-      <c r="I299" s="80"/>
+      <c r="I299" s="82"/>
     </row>
     <row r="300">
       <c r="B300" s="81"/>
       <c r="G300" s="65"/>
-      <c r="I300" s="80"/>
+      <c r="I300" s="82"/>
     </row>
     <row r="301">
       <c r="B301" s="81"/>
       <c r="G301" s="65"/>
-      <c r="I301" s="80"/>
+      <c r="I301" s="82"/>
     </row>
     <row r="302">
       <c r="B302" s="81"/>
       <c r="G302" s="65"/>
-      <c r="I302" s="80"/>
+      <c r="I302" s="82"/>
     </row>
     <row r="303">
       <c r="B303" s="81"/>
       <c r="G303" s="65"/>
-      <c r="I303" s="80"/>
+      <c r="I303" s="82"/>
     </row>
     <row r="304">
       <c r="B304" s="81"/>
       <c r="G304" s="65"/>
-      <c r="I304" s="80"/>
+      <c r="I304" s="82"/>
     </row>
     <row r="305">
       <c r="B305" s="81"/>
       <c r="G305" s="65"/>
-      <c r="I305" s="80"/>
+      <c r="I305" s="82"/>
     </row>
     <row r="306">
       <c r="B306" s="81"/>
       <c r="G306" s="65"/>
-      <c r="I306" s="80"/>
+      <c r="I306" s="82"/>
     </row>
     <row r="307">
       <c r="B307" s="81"/>
       <c r="G307" s="65"/>
-      <c r="I307" s="80"/>
+      <c r="I307" s="82"/>
     </row>
     <row r="308">
       <c r="B308" s="81"/>
       <c r="G308" s="65"/>
-      <c r="I308" s="80"/>
+      <c r="I308" s="82"/>
     </row>
     <row r="309">
       <c r="B309" s="81"/>
       <c r="G309" s="65"/>
-      <c r="I309" s="80"/>
+      <c r="I309" s="82"/>
     </row>
     <row r="310">
       <c r="B310" s="81"/>
       <c r="G310" s="65"/>
-      <c r="I310" s="80"/>
+      <c r="I310" s="82"/>
     </row>
     <row r="311">
       <c r="B311" s="81"/>
       <c r="G311" s="65"/>
-      <c r="I311" s="80"/>
+      <c r="I311" s="82"/>
     </row>
     <row r="312">
       <c r="B312" s="81"/>
       <c r="G312" s="65"/>
-      <c r="I312" s="80"/>
+      <c r="I312" s="82"/>
     </row>
     <row r="313">
       <c r="B313" s="81"/>
       <c r="G313" s="65"/>
-      <c r="I313" s="80"/>
+      <c r="I313" s="82"/>
     </row>
     <row r="314">
       <c r="B314" s="81"/>
       <c r="G314" s="65"/>
-      <c r="I314" s="80"/>
+      <c r="I314" s="82"/>
     </row>
     <row r="315">
       <c r="B315" s="81"/>
       <c r="G315" s="65"/>
-      <c r="I315" s="80"/>
+      <c r="I315" s="82"/>
     </row>
     <row r="316">
       <c r="B316" s="81"/>
       <c r="G316" s="65"/>
-      <c r="I316" s="80"/>
+      <c r="I316" s="82"/>
     </row>
     <row r="317">
       <c r="B317" s="81"/>
       <c r="G317" s="65"/>
-      <c r="I317" s="80"/>
+      <c r="I317" s="82"/>
     </row>
     <row r="318">
       <c r="B318" s="81"/>
       <c r="G318" s="65"/>
-      <c r="I318" s="80"/>
+      <c r="I318" s="82"/>
     </row>
     <row r="319">
       <c r="B319" s="81"/>
       <c r="G319" s="65"/>
-      <c r="I319" s="80"/>
+      <c r="I319" s="82"/>
     </row>
     <row r="320">
       <c r="B320" s="81"/>
       <c r="G320" s="65"/>
-      <c r="I320" s="80"/>
+      <c r="I320" s="82"/>
     </row>
     <row r="321">
       <c r="B321" s="81"/>
       <c r="G321" s="65"/>
-      <c r="I321" s="80"/>
+      <c r="I321" s="82"/>
     </row>
     <row r="322">
       <c r="B322" s="81"/>
       <c r="G322" s="65"/>
-      <c r="I322" s="80"/>
+      <c r="I322" s="82"/>
     </row>
     <row r="323">
       <c r="B323" s="81"/>
       <c r="G323" s="65"/>
-      <c r="I323" s="80"/>
+      <c r="I323" s="82"/>
     </row>
     <row r="324">
       <c r="B324" s="81"/>
       <c r="G324" s="65"/>
-      <c r="I324" s="80"/>
+      <c r="I324" s="82"/>
     </row>
     <row r="325">
       <c r="B325" s="81"/>
       <c r="G325" s="65"/>
-      <c r="I325" s="80"/>
+      <c r="I325" s="82"/>
     </row>
     <row r="326">
       <c r="B326" s="81"/>
       <c r="G326" s="65"/>
-      <c r="I326" s="80"/>
+      <c r="I326" s="82"/>
     </row>
     <row r="327">
       <c r="B327" s="81"/>
       <c r="G327" s="65"/>
-      <c r="I327" s="80"/>
+      <c r="I327" s="82"/>
     </row>
     <row r="328">
       <c r="B328" s="81"/>
       <c r="G328" s="65"/>
-      <c r="I328" s="80"/>
+      <c r="I328" s="82"/>
     </row>
     <row r="329">
       <c r="B329" s="81"/>
       <c r="G329" s="65"/>
-      <c r="I329" s="80"/>
+      <c r="I329" s="82"/>
     </row>
     <row r="330">
       <c r="B330" s="81"/>
       <c r="G330" s="65"/>
-      <c r="I330" s="80"/>
+      <c r="I330" s="82"/>
     </row>
     <row r="331">
       <c r="B331" s="81"/>
       <c r="G331" s="65"/>
-      <c r="I331" s="80"/>
+      <c r="I331" s="82"/>
     </row>
     <row r="332">
       <c r="B332" s="81"/>
       <c r="G332" s="65"/>
-      <c r="I332" s="80"/>
+      <c r="I332" s="82"/>
     </row>
     <row r="333">
       <c r="B333" s="81"/>
       <c r="G333" s="65"/>
-      <c r="I333" s="80"/>
+      <c r="I333" s="82"/>
     </row>
     <row r="334">
       <c r="B334" s="81"/>
       <c r="G334" s="65"/>
-      <c r="I334" s="80"/>
+      <c r="I334" s="82"/>
     </row>
     <row r="335">
       <c r="B335" s="81"/>
       <c r="G335" s="65"/>
-      <c r="I335" s="80"/>
+      <c r="I335" s="82"/>
     </row>
     <row r="336">
       <c r="B336" s="81"/>
       <c r="G336" s="65"/>
-      <c r="I336" s="80"/>
+      <c r="I336" s="82"/>
     </row>
     <row r="337">
       <c r="B337" s="81"/>
       <c r="G337" s="65"/>
-      <c r="I337" s="80"/>
+      <c r="I337" s="82"/>
     </row>
     <row r="338">
       <c r="B338" s="81"/>
       <c r="G338" s="65"/>
-      <c r="I338" s="80"/>
+      <c r="I338" s="82"/>
     </row>
     <row r="339">
       <c r="B339" s="81"/>
       <c r="G339" s="65"/>
-      <c r="I339" s="80"/>
+      <c r="I339" s="82"/>
     </row>
     <row r="340">
       <c r="B340" s="81"/>
       <c r="G340" s="65"/>
-      <c r="I340" s="80"/>
+      <c r="I340" s="82"/>
     </row>
     <row r="341">
       <c r="B341" s="81"/>
       <c r="G341" s="65"/>
-      <c r="I341" s="80"/>
+      <c r="I341" s="82"/>
     </row>
     <row r="342">
       <c r="B342" s="81"/>
       <c r="G342" s="65"/>
-      <c r="I342" s="80"/>
+      <c r="I342" s="82"/>
     </row>
     <row r="343">
       <c r="B343" s="81"/>
       <c r="G343" s="65"/>
-      <c r="I343" s="80"/>
+      <c r="I343" s="82"/>
     </row>
     <row r="344">
       <c r="B344" s="81"/>
       <c r="G344" s="65"/>
-      <c r="I344" s="80"/>
+      <c r="I344" s="82"/>
     </row>
     <row r="345">
       <c r="B345" s="81"/>
       <c r="G345" s="65"/>
-      <c r="I345" s="80"/>
+      <c r="I345" s="82"/>
     </row>
     <row r="346">
       <c r="B346" s="81"/>
       <c r="G346" s="65"/>
-      <c r="I346" s="80"/>
+      <c r="I346" s="82"/>
     </row>
     <row r="347">
       <c r="B347" s="81"/>
       <c r="G347" s="65"/>
-      <c r="I347" s="80"/>
+      <c r="I347" s="82"/>
     </row>
     <row r="348">
       <c r="B348" s="81"/>
       <c r="G348" s="65"/>
-      <c r="I348" s="80"/>
+      <c r="I348" s="82"/>
     </row>
     <row r="349">
       <c r="B349" s="81"/>
       <c r="G349" s="65"/>
-      <c r="I349" s="80"/>
+      <c r="I349" s="82"/>
     </row>
     <row r="350">
       <c r="B350" s="81"/>
       <c r="G350" s="65"/>
-      <c r="I350" s="80"/>
+      <c r="I350" s="82"/>
     </row>
     <row r="351">
       <c r="B351" s="81"/>
       <c r="G351" s="65"/>
-      <c r="I351" s="80"/>
+      <c r="I351" s="82"/>
     </row>
     <row r="352">
       <c r="B352" s="81"/>
       <c r="G352" s="65"/>
-      <c r="I352" s="80"/>
+      <c r="I352" s="82"/>
     </row>
     <row r="353">
       <c r="B353" s="81"/>
       <c r="G353" s="65"/>
-      <c r="I353" s="80"/>
+      <c r="I353" s="82"/>
     </row>
     <row r="354">
       <c r="B354" s="81"/>
       <c r="G354" s="65"/>
-      <c r="I354" s="80"/>
+      <c r="I354" s="82"/>
     </row>
     <row r="355">
       <c r="B355" s="81"/>
       <c r="G355" s="65"/>
-      <c r="I355" s="80"/>
+      <c r="I355" s="82"/>
     </row>
     <row r="356">
       <c r="B356" s="81"/>
       <c r="G356" s="65"/>
-      <c r="I356" s="80"/>
+      <c r="I356" s="82"/>
     </row>
     <row r="357">
       <c r="B357" s="81"/>
       <c r="G357" s="65"/>
-      <c r="I357" s="80"/>
+      <c r="I357" s="82"/>
     </row>
     <row r="358">
       <c r="B358" s="81"/>
       <c r="G358" s="65"/>
-      <c r="I358" s="80"/>
+      <c r="I358" s="82"/>
     </row>
     <row r="359">
       <c r="B359" s="81"/>
       <c r="G359" s="65"/>
-      <c r="I359" s="80"/>
+      <c r="I359" s="82"/>
     </row>
     <row r="360">
       <c r="B360" s="81"/>
       <c r="G360" s="65"/>
-      <c r="I360" s="80"/>
+      <c r="I360" s="82"/>
     </row>
     <row r="361">
       <c r="B361" s="81"/>
       <c r="G361" s="65"/>
-      <c r="I361" s="80"/>
+      <c r="I361" s="82"/>
     </row>
     <row r="362">
       <c r="B362" s="81"/>
       <c r="G362" s="65"/>
-      <c r="I362" s="80"/>
+      <c r="I362" s="82"/>
     </row>
     <row r="363">
       <c r="B363" s="81"/>
       <c r="G363" s="65"/>
-      <c r="I363" s="80"/>
+      <c r="I363" s="82"/>
     </row>
     <row r="364">
       <c r="B364" s="81"/>
       <c r="G364" s="65"/>
-      <c r="I364" s="80"/>
+      <c r="I364" s="82"/>
     </row>
     <row r="365">
       <c r="B365" s="81"/>
       <c r="G365" s="65"/>
-      <c r="I365" s="80"/>
+      <c r="I365" s="82"/>
     </row>
     <row r="366">
       <c r="B366" s="81"/>
       <c r="G366" s="65"/>
-      <c r="I366" s="80"/>
+      <c r="I366" s="82"/>
     </row>
     <row r="367">
       <c r="B367" s="81"/>
       <c r="G367" s="65"/>
-      <c r="I367" s="80"/>
+      <c r="I367" s="82"/>
     </row>
     <row r="368">
       <c r="B368" s="81"/>
       <c r="G368" s="65"/>
-      <c r="I368" s="80"/>
+      <c r="I368" s="82"/>
     </row>
     <row r="369">
       <c r="B369" s="81"/>
       <c r="G369" s="65"/>
-      <c r="I369" s="80"/>
+      <c r="I369" s="82"/>
     </row>
     <row r="370">
       <c r="B370" s="81"/>
       <c r="G370" s="65"/>
-      <c r="I370" s="80"/>
+      <c r="I370" s="82"/>
     </row>
     <row r="371">
       <c r="B371" s="81"/>
       <c r="G371" s="65"/>
-      <c r="I371" s="80"/>
+      <c r="I371" s="82"/>
     </row>
     <row r="372">
       <c r="B372" s="81"/>
       <c r="G372" s="65"/>
-      <c r="I372" s="80"/>
+      <c r="I372" s="82"/>
     </row>
     <row r="373">
       <c r="B373" s="81"/>
       <c r="G373" s="65"/>
-      <c r="I373" s="80"/>
+      <c r="I373" s="82"/>
     </row>
     <row r="374">
       <c r="B374" s="81"/>
       <c r="G374" s="65"/>
-      <c r="I374" s="80"/>
+      <c r="I374" s="82"/>
     </row>
     <row r="375">
       <c r="B375" s="81"/>
       <c r="G375" s="65"/>
-      <c r="I375" s="80"/>
+      <c r="I375" s="82"/>
     </row>
     <row r="376">
       <c r="B376" s="81"/>
       <c r="G376" s="65"/>
-      <c r="I376" s="80"/>
+      <c r="I376" s="82"/>
     </row>
     <row r="377">
       <c r="B377" s="81"/>
       <c r="G377" s="65"/>
-      <c r="I377" s="80"/>
+      <c r="I377" s="82"/>
     </row>
     <row r="378">
       <c r="B378" s="81"/>
       <c r="G378" s="65"/>
-      <c r="I378" s="80"/>
+      <c r="I378" s="82"/>
     </row>
     <row r="379">
       <c r="B379" s="81"/>
       <c r="G379" s="65"/>
-      <c r="I379" s="80"/>
+      <c r="I379" s="82"/>
     </row>
     <row r="380">
       <c r="B380" s="81"/>
       <c r="G380" s="65"/>
-      <c r="I380" s="80"/>
+      <c r="I380" s="82"/>
     </row>
     <row r="381">
       <c r="B381" s="81"/>
       <c r="G381" s="65"/>
-      <c r="I381" s="80"/>
+      <c r="I381" s="82"/>
     </row>
     <row r="382">
       <c r="B382" s="81"/>
       <c r="G382" s="65"/>
-      <c r="I382" s="80"/>
+      <c r="I382" s="82"/>
     </row>
     <row r="383">
       <c r="B383" s="81"/>
       <c r="G383" s="65"/>
-      <c r="I383" s="80"/>
+      <c r="I383" s="82"/>
     </row>
     <row r="384">
       <c r="B384" s="81"/>
       <c r="G384" s="65"/>
-      <c r="I384" s="80"/>
+      <c r="I384" s="82"/>
     </row>
     <row r="385">
       <c r="B385" s="81"/>
       <c r="G385" s="65"/>
-      <c r="I385" s="80"/>
+      <c r="I385" s="82"/>
     </row>
     <row r="386">
       <c r="B386" s="81"/>
       <c r="G386" s="65"/>
-      <c r="I386" s="80"/>
+      <c r="I386" s="82"/>
     </row>
     <row r="387">
       <c r="B387" s="81"/>
       <c r="G387" s="65"/>
-      <c r="I387" s="80"/>
+      <c r="I387" s="82"/>
     </row>
     <row r="388">
       <c r="B388" s="81"/>
       <c r="G388" s="65"/>
-      <c r="I388" s="80"/>
+      <c r="I388" s="82"/>
     </row>
     <row r="389">
       <c r="B389" s="81"/>
       <c r="G389" s="65"/>
-      <c r="I389" s="80"/>
+      <c r="I389" s="82"/>
     </row>
     <row r="390">
       <c r="B390" s="81"/>
       <c r="G390" s="65"/>
-      <c r="I390" s="80"/>
+      <c r="I390" s="82"/>
     </row>
     <row r="391">
       <c r="B391" s="81"/>
       <c r="G391" s="65"/>
-      <c r="I391" s="80"/>
+      <c r="I391" s="82"/>
     </row>
     <row r="392">
       <c r="B392" s="81"/>
       <c r="G392" s="65"/>
-      <c r="I392" s="80"/>
+      <c r="I392" s="82"/>
     </row>
     <row r="393">
       <c r="B393" s="81"/>
       <c r="G393" s="65"/>
-      <c r="I393" s="80"/>
+      <c r="I393" s="82"/>
     </row>
     <row r="394">
       <c r="B394" s="81"/>
       <c r="G394" s="65"/>
-      <c r="I394" s="80"/>
+      <c r="I394" s="82"/>
     </row>
     <row r="395">
       <c r="B395" s="81"/>
       <c r="G395" s="65"/>
-      <c r="I395" s="80"/>
+      <c r="I395" s="82"/>
     </row>
     <row r="396">
       <c r="B396" s="81"/>
       <c r="G396" s="65"/>
-      <c r="I396" s="80"/>
+      <c r="I396" s="82"/>
     </row>
     <row r="397">
       <c r="B397" s="81"/>
       <c r="G397" s="65"/>
-      <c r="I397" s="80"/>
+      <c r="I397" s="82"/>
     </row>
     <row r="398">
       <c r="B398" s="81"/>
       <c r="G398" s="65"/>
-      <c r="I398" s="80"/>
+      <c r="I398" s="82"/>
     </row>
     <row r="399">
       <c r="B399" s="81"/>
       <c r="G399" s="65"/>
-      <c r="I399" s="80"/>
+      <c r="I399" s="82"/>
     </row>
     <row r="400">
       <c r="B400" s="81"/>
       <c r="G400" s="65"/>
-      <c r="I400" s="80"/>
+      <c r="I400" s="82"/>
     </row>
     <row r="401">
       <c r="B401" s="81"/>
       <c r="G401" s="65"/>
-      <c r="I401" s="80"/>
+      <c r="I401" s="82"/>
     </row>
     <row r="402">
       <c r="B402" s="81"/>
       <c r="G402" s="65"/>
-      <c r="I402" s="80"/>
+      <c r="I402" s="82"/>
     </row>
     <row r="403">
       <c r="B403" s="81"/>
       <c r="G403" s="65"/>
-      <c r="I403" s="80"/>
+      <c r="I403" s="82"/>
     </row>
     <row r="404">
       <c r="B404" s="81"/>
       <c r="G404" s="65"/>
-      <c r="I404" s="80"/>
+      <c r="I404" s="82"/>
     </row>
     <row r="405">
       <c r="B405" s="81"/>
       <c r="G405" s="65"/>
-      <c r="I405" s="80"/>
+      <c r="I405" s="82"/>
     </row>
     <row r="406">
       <c r="B406" s="81"/>
       <c r="G406" s="65"/>
-      <c r="I406" s="80"/>
+      <c r="I406" s="82"/>
     </row>
     <row r="407">
       <c r="B407" s="81"/>
       <c r="G407" s="65"/>
-      <c r="I407" s="80"/>
+      <c r="I407" s="82"/>
     </row>
     <row r="408">
       <c r="B408" s="81"/>
       <c r="G408" s="65"/>
-      <c r="I408" s="80"/>
+      <c r="I408" s="82"/>
     </row>
     <row r="409">
       <c r="B409" s="81"/>
       <c r="G409" s="65"/>
-      <c r="I409" s="80"/>
+      <c r="I409" s="82"/>
     </row>
     <row r="410">
       <c r="B410" s="81"/>
       <c r="G410" s="65"/>
-      <c r="I410" s="80"/>
+      <c r="I410" s="82"/>
     </row>
     <row r="411">
       <c r="B411" s="81"/>
       <c r="G411" s="65"/>
-      <c r="I411" s="80"/>
+      <c r="I411" s="82"/>
     </row>
     <row r="412">
       <c r="B412" s="81"/>
       <c r="G412" s="65"/>
-      <c r="I412" s="80"/>
+      <c r="I412" s="82"/>
     </row>
     <row r="413">
       <c r="B413" s="81"/>
       <c r="G413" s="65"/>
-      <c r="I413" s="80"/>
+      <c r="I413" s="82"/>
     </row>
     <row r="414">
       <c r="B414" s="81"/>
       <c r="G414" s="65"/>
-      <c r="I414" s="80"/>
+      <c r="I414" s="82"/>
     </row>
     <row r="415">
       <c r="B415" s="81"/>
       <c r="G415" s="65"/>
-      <c r="I415" s="80"/>
+      <c r="I415" s="82"/>
     </row>
     <row r="416">
       <c r="B416" s="81"/>
       <c r="G416" s="65"/>
-      <c r="I416" s="80"/>
+      <c r="I416" s="82"/>
     </row>
     <row r="417">
       <c r="B417" s="81"/>
       <c r="G417" s="65"/>
-      <c r="I417" s="80"/>
+      <c r="I417" s="82"/>
     </row>
     <row r="418">
       <c r="B418" s="81"/>
       <c r="G418" s="65"/>
-      <c r="I418" s="80"/>
+      <c r="I418" s="82"/>
     </row>
     <row r="419">
       <c r="B419" s="81"/>
       <c r="G419" s="65"/>
-      <c r="I419" s="80"/>
+      <c r="I419" s="82"/>
     </row>
     <row r="420">
       <c r="B420" s="81"/>
       <c r="G420" s="65"/>
-      <c r="I420" s="80"/>
+      <c r="I420" s="82"/>
     </row>
     <row r="421">
       <c r="B421" s="81"/>
       <c r="G421" s="65"/>
-      <c r="I421" s="80"/>
+      <c r="I421" s="82"/>
     </row>
     <row r="422">
       <c r="B422" s="81"/>
       <c r="G422" s="65"/>
-      <c r="I422" s="80"/>
+      <c r="I422" s="82"/>
     </row>
     <row r="423">
       <c r="B423" s="81"/>
       <c r="G423" s="65"/>
-      <c r="I423" s="80"/>
+      <c r="I423" s="82"/>
     </row>
     <row r="424">
       <c r="B424" s="81"/>
       <c r="G424" s="65"/>
-      <c r="I424" s="80"/>
+      <c r="I424" s="82"/>
     </row>
     <row r="425">
       <c r="B425" s="81"/>
       <c r="G425" s="65"/>
-      <c r="I425" s="80"/>
+      <c r="I425" s="82"/>
     </row>
     <row r="426">
       <c r="B426" s="81"/>
       <c r="G426" s="65"/>
-      <c r="I426" s="80"/>
+      <c r="I426" s="82"/>
     </row>
     <row r="427">
       <c r="B427" s="81"/>
       <c r="G427" s="65"/>
-      <c r="I427" s="80"/>
+      <c r="I427" s="82"/>
     </row>
     <row r="428">
       <c r="B428" s="81"/>
       <c r="G428" s="65"/>
-      <c r="I428" s="80"/>
+      <c r="I428" s="82"/>
     </row>
     <row r="429">
       <c r="B429" s="81"/>
       <c r="G429" s="65"/>
-      <c r="I429" s="80"/>
+      <c r="I429" s="82"/>
     </row>
     <row r="430">
       <c r="B430" s="81"/>
       <c r="G430" s="65"/>
-      <c r="I430" s="80"/>
+      <c r="I430" s="82"/>
     </row>
     <row r="431">
       <c r="B431" s="81"/>
       <c r="G431" s="65"/>
-      <c r="I431" s="80"/>
+      <c r="I431" s="82"/>
     </row>
     <row r="432">
       <c r="B432" s="81"/>
       <c r="G432" s="65"/>
-      <c r="I432" s="80"/>
+      <c r="I432" s="82"/>
     </row>
     <row r="433">
       <c r="B433" s="81"/>
       <c r="G433" s="65"/>
-      <c r="I433" s="80"/>
+      <c r="I433" s="82"/>
     </row>
     <row r="434">
       <c r="B434" s="81"/>
       <c r="G434" s="65"/>
-      <c r="I434" s="80"/>
+      <c r="I434" s="82"/>
     </row>
     <row r="435">
       <c r="B435" s="81"/>
       <c r="G435" s="65"/>
-      <c r="I435" s="80"/>
+      <c r="I435" s="82"/>
     </row>
     <row r="436">
       <c r="B436" s="81"/>
       <c r="G436" s="65"/>
-      <c r="I436" s="80"/>
+      <c r="I436" s="82"/>
     </row>
     <row r="437">
       <c r="B437" s="81"/>
       <c r="G437" s="65"/>
-      <c r="I437" s="80"/>
+      <c r="I437" s="82"/>
     </row>
     <row r="438">
       <c r="B438" s="81"/>
       <c r="G438" s="65"/>
-      <c r="I438" s="80"/>
+      <c r="I438" s="82"/>
     </row>
     <row r="439">
       <c r="B439" s="81"/>
       <c r="G439" s="65"/>
-      <c r="I439" s="80"/>
+      <c r="I439" s="82"/>
     </row>
     <row r="440">
       <c r="B440" s="81"/>
       <c r="G440" s="65"/>
-      <c r="I440" s="80"/>
+      <c r="I440" s="82"/>
     </row>
     <row r="441">
       <c r="B441" s="81"/>
       <c r="G441" s="65"/>
-      <c r="I441" s="80"/>
+      <c r="I441" s="82"/>
     </row>
     <row r="442">
       <c r="B442" s="81"/>
       <c r="G442" s="65"/>
-      <c r="I442" s="80"/>
+      <c r="I442" s="82"/>
     </row>
     <row r="443">
       <c r="B443" s="81"/>
       <c r="G443" s="65"/>
-      <c r="I443" s="80"/>
+      <c r="I443" s="82"/>
     </row>
     <row r="444">
       <c r="B444" s="81"/>
       <c r="G444" s="65"/>
-      <c r="I444" s="80"/>
+      <c r="I444" s="82"/>
     </row>
     <row r="445">
       <c r="B445" s="81"/>
       <c r="G445" s="65"/>
-      <c r="I445" s="80"/>
+      <c r="I445" s="82"/>
     </row>
     <row r="446">
       <c r="B446" s="81"/>
       <c r="G446" s="65"/>
-      <c r="I446" s="80"/>
+      <c r="I446" s="82"/>
     </row>
     <row r="447">
       <c r="B447" s="81"/>
       <c r="G447" s="65"/>
-      <c r="I447" s="80"/>
+      <c r="I447" s="82"/>
     </row>
     <row r="448">
       <c r="B448" s="81"/>
       <c r="G448" s="65"/>
-      <c r="I448" s="80"/>
+      <c r="I448" s="82"/>
     </row>
     <row r="449">
       <c r="B449" s="81"/>
       <c r="G449" s="65"/>
-      <c r="I449" s="80"/>
+      <c r="I449" s="82"/>
     </row>
     <row r="450">
       <c r="B450" s="81"/>
       <c r="G450" s="65"/>
-      <c r="I450" s="80"/>
+      <c r="I450" s="82"/>
     </row>
     <row r="451">
       <c r="B451" s="81"/>
       <c r="G451" s="65"/>
-      <c r="I451" s="80"/>
+      <c r="I451" s="82"/>
     </row>
     <row r="452">
       <c r="B452" s="81"/>
       <c r="G452" s="65"/>
-      <c r="I452" s="80"/>
+      <c r="I452" s="82"/>
     </row>
     <row r="453">
       <c r="B453" s="81"/>
       <c r="G453" s="65"/>
-      <c r="I453" s="80"/>
+      <c r="I453" s="82"/>
     </row>
     <row r="454">
       <c r="B454" s="81"/>
       <c r="G454" s="65"/>
-      <c r="I454" s="80"/>
+      <c r="I454" s="82"/>
     </row>
     <row r="455">
       <c r="B455" s="81"/>
       <c r="G455" s="65"/>
-      <c r="I455" s="80"/>
+      <c r="I455" s="82"/>
     </row>
     <row r="456">
       <c r="B456" s="81"/>
       <c r="G456" s="65"/>
-      <c r="I456" s="80"/>
+      <c r="I456" s="82"/>
     </row>
     <row r="457">
       <c r="B457" s="81"/>
       <c r="G457" s="65"/>
-      <c r="I457" s="80"/>
+      <c r="I457" s="82"/>
     </row>
     <row r="458">
       <c r="B458" s="81"/>
       <c r="G458" s="65"/>
-      <c r="I458" s="80"/>
+      <c r="I458" s="82"/>
     </row>
     <row r="459">
       <c r="B459" s="81"/>
       <c r="G459" s="65"/>
-      <c r="I459" s="80"/>
+      <c r="I459" s="82"/>
     </row>
     <row r="460">
       <c r="B460" s="81"/>
       <c r="G460" s="65"/>
-      <c r="I460" s="80"/>
+      <c r="I460" s="82"/>
     </row>
     <row r="461">
       <c r="B461" s="81"/>
       <c r="G461" s="65"/>
-      <c r="I461" s="80"/>
+      <c r="I461" s="82"/>
     </row>
     <row r="462">
       <c r="B462" s="81"/>
       <c r="G462" s="65"/>
-      <c r="I462" s="80"/>
+      <c r="I462" s="82"/>
     </row>
     <row r="463">
       <c r="B463" s="81"/>
       <c r="G463" s="65"/>
-      <c r="I463" s="80"/>
+      <c r="I463" s="82"/>
     </row>
     <row r="464">
       <c r="B464" s="81"/>
       <c r="G464" s="65"/>
-      <c r="I464" s="80"/>
+      <c r="I464" s="82"/>
     </row>
     <row r="465">
       <c r="B465" s="81"/>
       <c r="G465" s="65"/>
-      <c r="I465" s="80"/>
+      <c r="I465" s="82"/>
     </row>
     <row r="466">
       <c r="B466" s="81"/>
       <c r="G466" s="65"/>
-      <c r="I466" s="80"/>
+      <c r="I466" s="82"/>
     </row>
     <row r="467">
       <c r="B467" s="81"/>
       <c r="G467" s="65"/>
-      <c r="I467" s="80"/>
+      <c r="I467" s="82"/>
     </row>
     <row r="468">
       <c r="B468" s="81"/>
       <c r="G468" s="65"/>
-      <c r="I468" s="80"/>
+      <c r="I468" s="82"/>
     </row>
     <row r="469">
       <c r="B469" s="81"/>
       <c r="G469" s="65"/>
-      <c r="I469" s="80"/>
+      <c r="I469" s="82"/>
     </row>
     <row r="470">
       <c r="B470" s="81"/>
       <c r="G470" s="65"/>
-      <c r="I470" s="80"/>
+      <c r="I470" s="82"/>
     </row>
     <row r="471">
       <c r="B471" s="81"/>
       <c r="G471" s="65"/>
-      <c r="I471" s="80"/>
+      <c r="I471" s="82"/>
     </row>
     <row r="472">
       <c r="B472" s="81"/>
       <c r="G472" s="65"/>
-      <c r="I472" s="80"/>
+      <c r="I472" s="82"/>
     </row>
     <row r="473">
       <c r="B473" s="81"/>
       <c r="G473" s="65"/>
-      <c r="I473" s="80"/>
+      <c r="I473" s="82"/>
     </row>
     <row r="474">
       <c r="B474" s="81"/>
       <c r="G474" s="65"/>
-      <c r="I474" s="80"/>
+      <c r="I474" s="82"/>
     </row>
     <row r="475">
       <c r="B475" s="81"/>
       <c r="G475" s="65"/>
-      <c r="I475" s="80"/>
+      <c r="I475" s="82"/>
     </row>
     <row r="476">
       <c r="B476" s="81"/>
       <c r="G476" s="65"/>
-      <c r="I476" s="80"/>
+      <c r="I476" s="82"/>
     </row>
     <row r="477">
       <c r="B477" s="81"/>
       <c r="G477" s="65"/>
-      <c r="I477" s="80"/>
+      <c r="I477" s="82"/>
     </row>
     <row r="478">
       <c r="B478" s="81"/>
       <c r="G478" s="65"/>
-      <c r="I478" s="80"/>
+      <c r="I478" s="82"/>
     </row>
     <row r="479">
       <c r="B479" s="81"/>
       <c r="G479" s="65"/>
-      <c r="I479" s="80"/>
+      <c r="I479" s="82"/>
     </row>
     <row r="480">
       <c r="B480" s="81"/>
       <c r="G480" s="65"/>
-      <c r="I480" s="80"/>
+      <c r="I480" s="82"/>
     </row>
     <row r="481">
       <c r="B481" s="81"/>
       <c r="G481" s="65"/>
-      <c r="I481" s="80"/>
+      <c r="I481" s="82"/>
     </row>
     <row r="482">
       <c r="B482" s="81"/>
       <c r="G482" s="65"/>
-      <c r="I482" s="80"/>
+      <c r="I482" s="82"/>
     </row>
     <row r="483">
       <c r="B483" s="81"/>
       <c r="G483" s="65"/>
-      <c r="I483" s="80"/>
+      <c r="I483" s="82"/>
     </row>
     <row r="484">
       <c r="B484" s="81"/>
       <c r="G484" s="65"/>
-      <c r="I484" s="80"/>
+      <c r="I484" s="82"/>
     </row>
     <row r="485">
       <c r="B485" s="81"/>
       <c r="G485" s="65"/>
-      <c r="I485" s="80"/>
+      <c r="I485" s="82"/>
     </row>
     <row r="486">
       <c r="B486" s="81"/>
       <c r="G486" s="65"/>
-      <c r="I486" s="80"/>
+      <c r="I486" s="82"/>
     </row>
     <row r="487">
       <c r="B487" s="81"/>
       <c r="G487" s="65"/>
-      <c r="I487" s="80"/>
+      <c r="I487" s="82"/>
     </row>
     <row r="488">
       <c r="B488" s="81"/>
       <c r="G488" s="65"/>
-      <c r="I488" s="80"/>
+      <c r="I488" s="82"/>
     </row>
     <row r="489">
       <c r="B489" s="81"/>
       <c r="G489" s="65"/>
-      <c r="I489" s="80"/>
+      <c r="I489" s="82"/>
     </row>
     <row r="490">
       <c r="B490" s="81"/>
       <c r="G490" s="65"/>
-      <c r="I490" s="80"/>
+      <c r="I490" s="82"/>
     </row>
     <row r="491">
       <c r="B491" s="81"/>
       <c r="G491" s="65"/>
-      <c r="I491" s="80"/>
+      <c r="I491" s="82"/>
     </row>
     <row r="492">
       <c r="B492" s="81"/>
       <c r="G492" s="65"/>
-      <c r="I492" s="80"/>
+      <c r="I492" s="82"/>
     </row>
     <row r="493">
       <c r="B493" s="81"/>
       <c r="G493" s="65"/>
-      <c r="I493" s="80"/>
+      <c r="I493" s="82"/>
     </row>
     <row r="494">
       <c r="B494" s="81"/>
       <c r="G494" s="65"/>
-      <c r="I494" s="80"/>
+      <c r="I494" s="82"/>
     </row>
     <row r="495">
       <c r="B495" s="81"/>
       <c r="G495" s="65"/>
-      <c r="I495" s="80"/>
+      <c r="I495" s="82"/>
     </row>
     <row r="496">
       <c r="B496" s="81"/>
       <c r="G496" s="65"/>
-      <c r="I496" s="80"/>
+      <c r="I496" s="82"/>
     </row>
     <row r="497">
       <c r="B497" s="81"/>
       <c r="G497" s="65"/>
-      <c r="I497" s="80"/>
+      <c r="I497" s="82"/>
     </row>
     <row r="498">
       <c r="B498" s="81"/>
       <c r="G498" s="65"/>
-      <c r="I498" s="80"/>
+      <c r="I498" s="82"/>
     </row>
     <row r="499">
       <c r="B499" s="81"/>
       <c r="G499" s="65"/>
-      <c r="I499" s="80"/>
+      <c r="I499" s="82"/>
     </row>
     <row r="500">
       <c r="B500" s="81"/>
       <c r="G500" s="65"/>
-      <c r="I500" s="80"/>
+      <c r="I500" s="82"/>
     </row>
     <row r="501">
       <c r="B501" s="81"/>
       <c r="G501" s="65"/>
-      <c r="I501" s="80"/>
+      <c r="I501" s="82"/>
     </row>
     <row r="502">
       <c r="B502" s="81"/>
       <c r="G502" s="65"/>
-      <c r="I502" s="80"/>
+      <c r="I502" s="82"/>
     </row>
     <row r="503">
       <c r="B503" s="81"/>
       <c r="G503" s="65"/>
-      <c r="I503" s="80"/>
+      <c r="I503" s="82"/>
     </row>
     <row r="504">
       <c r="B504" s="81"/>
       <c r="G504" s="65"/>
-      <c r="I504" s="80"/>
+      <c r="I504" s="82"/>
     </row>
     <row r="505">
       <c r="B505" s="81"/>
       <c r="G505" s="65"/>
-      <c r="I505" s="80"/>
+      <c r="I505" s="82"/>
     </row>
     <row r="506">
       <c r="B506" s="81"/>
       <c r="G506" s="65"/>
-      <c r="I506" s="80"/>
+      <c r="I506" s="82"/>
     </row>
     <row r="507">
       <c r="B507" s="81"/>
       <c r="G507" s="65"/>
-      <c r="I507" s="80"/>
+      <c r="I507" s="82"/>
     </row>
     <row r="508">
       <c r="B508" s="81"/>
       <c r="G508" s="65"/>
-      <c r="I508" s="80"/>
+      <c r="I508" s="82"/>
     </row>
     <row r="509">
       <c r="B509" s="81"/>
       <c r="G509" s="65"/>
-      <c r="I509" s="80"/>
+      <c r="I509" s="82"/>
     </row>
     <row r="510">
       <c r="B510" s="81"/>
       <c r="G510" s="65"/>
-      <c r="I510" s="80"/>
+      <c r="I510" s="82"/>
     </row>
     <row r="511">
       <c r="B511" s="81"/>
       <c r="G511" s="65"/>
-      <c r="I511" s="80"/>
+      <c r="I511" s="82"/>
     </row>
     <row r="512">
       <c r="B512" s="81"/>
       <c r="G512" s="65"/>
-      <c r="I512" s="80"/>
+      <c r="I512" s="82"/>
     </row>
     <row r="513">
       <c r="B513" s="81"/>
       <c r="G513" s="65"/>
-      <c r="I513" s="80"/>
+      <c r="I513" s="82"/>
     </row>
     <row r="514">
       <c r="B514" s="81"/>
       <c r="G514" s="65"/>
-      <c r="I514" s="80"/>
+      <c r="I514" s="82"/>
     </row>
     <row r="515">
       <c r="B515" s="81"/>
       <c r="G515" s="65"/>
-      <c r="I515" s="80"/>
+      <c r="I515" s="82"/>
     </row>
     <row r="516">
       <c r="B516" s="81"/>
       <c r="G516" s="65"/>
-      <c r="I516" s="80"/>
+      <c r="I516" s="82"/>
     </row>
     <row r="517">
       <c r="B517" s="81"/>
       <c r="G517" s="65"/>
-      <c r="I517" s="80"/>
+      <c r="I517" s="82"/>
     </row>
     <row r="518">
       <c r="B518" s="81"/>
       <c r="G518" s="65"/>
-      <c r="I518" s="80"/>
+      <c r="I518" s="82"/>
     </row>
     <row r="519">
       <c r="B519" s="81"/>
       <c r="G519" s="65"/>
-      <c r="I519" s="80"/>
+      <c r="I519" s="82"/>
     </row>
     <row r="520">
       <c r="B520" s="81"/>
       <c r="G520" s="65"/>
-      <c r="I520" s="80"/>
+      <c r="I520" s="82"/>
     </row>
     <row r="521">
       <c r="B521" s="81"/>
       <c r="G521" s="65"/>
-      <c r="I521" s="80"/>
+      <c r="I521" s="82"/>
     </row>
     <row r="522">
       <c r="B522" s="81"/>
       <c r="G522" s="65"/>
-      <c r="I522" s="80"/>
+      <c r="I522" s="82"/>
     </row>
     <row r="523">
       <c r="B523" s="81"/>
       <c r="G523" s="65"/>
-      <c r="I523" s="80"/>
+      <c r="I523" s="82"/>
     </row>
     <row r="524">
       <c r="B524" s="81"/>
       <c r="G524" s="65"/>
-      <c r="I524" s="80"/>
+      <c r="I524" s="82"/>
     </row>
     <row r="525">
       <c r="B525" s="81"/>
       <c r="G525" s="65"/>
-      <c r="I525" s="80"/>
+      <c r="I525" s="82"/>
     </row>
     <row r="526">
       <c r="B526" s="81"/>
       <c r="G526" s="65"/>
-      <c r="I526" s="80"/>
+      <c r="I526" s="82"/>
     </row>
     <row r="527">
       <c r="B527" s="81"/>
       <c r="G527" s="65"/>
-      <c r="I527" s="80"/>
+      <c r="I527" s="82"/>
     </row>
     <row r="528">
       <c r="B528" s="81"/>
       <c r="G528" s="65"/>
-      <c r="I528" s="80"/>
+      <c r="I528" s="82"/>
     </row>
     <row r="529">
       <c r="B529" s="81"/>
       <c r="G529" s="65"/>
-      <c r="I529" s="80"/>
+      <c r="I529" s="82"/>
     </row>
     <row r="530">
       <c r="B530" s="81"/>
       <c r="G530" s="65"/>
-      <c r="I530" s="80"/>
+      <c r="I530" s="82"/>
     </row>
     <row r="531">
       <c r="B531" s="81"/>
       <c r="G531" s="65"/>
-      <c r="I531" s="80"/>
+      <c r="I531" s="82"/>
     </row>
     <row r="532">
       <c r="B532" s="81"/>
       <c r="G532" s="65"/>
-      <c r="I532" s="80"/>
+      <c r="I532" s="82"/>
     </row>
     <row r="533">
       <c r="B533" s="81"/>
       <c r="G533" s="65"/>
-      <c r="I533" s="80"/>
+      <c r="I533" s="82"/>
     </row>
     <row r="534">
       <c r="B534" s="81"/>
       <c r="G534" s="65"/>
-      <c r="I534" s="80"/>
+      <c r="I534" s="82"/>
     </row>
     <row r="535">
       <c r="B535" s="81"/>
       <c r="G535" s="65"/>
-      <c r="I535" s="80"/>
+      <c r="I535" s="82"/>
     </row>
     <row r="536">
       <c r="B536" s="81"/>
       <c r="G536" s="65"/>
-      <c r="I536" s="80"/>
+      <c r="I536" s="82"/>
     </row>
     <row r="537">
       <c r="B537" s="81"/>
       <c r="G537" s="65"/>
-      <c r="I537" s="80"/>
+      <c r="I537" s="82"/>
     </row>
     <row r="538">
       <c r="B538" s="81"/>
       <c r="G538" s="65"/>
-      <c r="I538" s="80"/>
+      <c r="I538" s="82"/>
     </row>
     <row r="539">
       <c r="B539" s="81"/>
       <c r="G539" s="65"/>
-      <c r="I539" s="80"/>
+      <c r="I539" s="82"/>
     </row>
     <row r="540">
       <c r="B540" s="81"/>
       <c r="G540" s="65"/>
-      <c r="I540" s="80"/>
+      <c r="I540" s="82"/>
     </row>
     <row r="541">
       <c r="B541" s="81"/>
       <c r="G541" s="65"/>
-      <c r="I541" s="80"/>
+      <c r="I541" s="82"/>
     </row>
     <row r="542">
       <c r="B542" s="81"/>
       <c r="G542" s="65"/>
-      <c r="I542" s="80"/>
+      <c r="I542" s="82"/>
     </row>
     <row r="543">
       <c r="B543" s="81"/>
       <c r="G543" s="65"/>
-      <c r="I543" s="80"/>
+      <c r="I543" s="82"/>
     </row>
     <row r="544">
       <c r="B544" s="81"/>
       <c r="G544" s="65"/>
-      <c r="I544" s="80"/>
+      <c r="I544" s="82"/>
     </row>
     <row r="545">
       <c r="B545" s="81"/>
       <c r="G545" s="65"/>
-      <c r="I545" s="80"/>
+      <c r="I545" s="82"/>
     </row>
     <row r="546">
       <c r="B546" s="81"/>
       <c r="G546" s="65"/>
-      <c r="I546" s="80"/>
+      <c r="I546" s="82"/>
     </row>
     <row r="547">
       <c r="B547" s="81"/>
       <c r="G547" s="65"/>
-      <c r="I547" s="80"/>
+      <c r="I547" s="82"/>
     </row>
     <row r="548">
       <c r="B548" s="81"/>
       <c r="G548" s="65"/>
-      <c r="I548" s="80"/>
+      <c r="I548" s="82"/>
     </row>
     <row r="549">
       <c r="B549" s="81"/>
       <c r="G549" s="65"/>
-      <c r="I549" s="80"/>
+      <c r="I549" s="82"/>
     </row>
     <row r="550">
       <c r="B550" s="81"/>
       <c r="G550" s="65"/>
-      <c r="I550" s="80"/>
+      <c r="I550" s="82"/>
     </row>
     <row r="551">
       <c r="B551" s="81"/>
       <c r="G551" s="65"/>
-      <c r="I551" s="80"/>
+      <c r="I551" s="82"/>
     </row>
     <row r="552">
       <c r="B552" s="81"/>
       <c r="G552" s="65"/>
-      <c r="I552" s="80"/>
+      <c r="I552" s="82"/>
     </row>
     <row r="553">
       <c r="B553" s="81"/>
       <c r="G553" s="65"/>
-      <c r="I553" s="80"/>
+      <c r="I553" s="82"/>
     </row>
     <row r="554">
       <c r="B554" s="81"/>
       <c r="G554" s="65"/>
-      <c r="I554" s="80"/>
+      <c r="I554" s="82"/>
     </row>
     <row r="555">
       <c r="B555" s="81"/>
       <c r="G555" s="65"/>
-      <c r="I555" s="80"/>
+      <c r="I555" s="82"/>
     </row>
     <row r="556">
       <c r="B556" s="81"/>
       <c r="G556" s="65"/>
-      <c r="I556" s="80"/>
+      <c r="I556" s="82"/>
     </row>
     <row r="557">
       <c r="B557" s="81"/>
       <c r="G557" s="65"/>
-      <c r="I557" s="80"/>
+      <c r="I557" s="82"/>
     </row>
     <row r="558">
       <c r="B558" s="81"/>
       <c r="G558" s="65"/>
-      <c r="I558" s="80"/>
+      <c r="I558" s="82"/>
     </row>
     <row r="559">
       <c r="B559" s="81"/>
       <c r="G559" s="65"/>
-      <c r="I559" s="80"/>
+      <c r="I559" s="82"/>
     </row>
     <row r="560">
       <c r="B560" s="81"/>
       <c r="G560" s="65"/>
-      <c r="I560" s="80"/>
+      <c r="I560" s="82"/>
     </row>
     <row r="561">
       <c r="B561" s="81"/>
       <c r="G561" s="65"/>
-      <c r="I561" s="80"/>
+      <c r="I561" s="82"/>
     </row>
     <row r="562">
       <c r="B562" s="81"/>
       <c r="G562" s="65"/>
-      <c r="I562" s="80"/>
+      <c r="I562" s="82"/>
     </row>
     <row r="563">
       <c r="B563" s="81"/>
       <c r="G563" s="65"/>
-      <c r="I563" s="80"/>
+      <c r="I563" s="82"/>
     </row>
     <row r="564">
       <c r="B564" s="81"/>
       <c r="G564" s="65"/>
-      <c r="I564" s="80"/>
+      <c r="I564" s="82"/>
     </row>
     <row r="565">
       <c r="B565" s="81"/>
       <c r="G565" s="65"/>
-      <c r="I565" s="80"/>
+      <c r="I565" s="82"/>
     </row>
     <row r="566">
       <c r="B566" s="81"/>
       <c r="G566" s="65"/>
-      <c r="I566" s="80"/>
+      <c r="I566" s="82"/>
     </row>
     <row r="567">
       <c r="B567" s="81"/>
       <c r="G567" s="65"/>
-      <c r="I567" s="80"/>
+      <c r="I567" s="82"/>
     </row>
     <row r="568">
       <c r="B568" s="81"/>
       <c r="G568" s="65"/>
-      <c r="I568" s="80"/>
+      <c r="I568" s="82"/>
     </row>
     <row r="569">
       <c r="B569" s="81"/>
       <c r="G569" s="65"/>
-      <c r="I569" s="80"/>
+      <c r="I569" s="82"/>
     </row>
     <row r="570">
       <c r="B570" s="81"/>
       <c r="G570" s="65"/>
-      <c r="I570" s="80"/>
+      <c r="I570" s="82"/>
     </row>
     <row r="571">
       <c r="B571" s="81"/>
       <c r="G571" s="65"/>
-      <c r="I571" s="80"/>
+      <c r="I571" s="82"/>
     </row>
     <row r="572">
       <c r="B572" s="81"/>
       <c r="G572" s="65"/>
-      <c r="I572" s="80"/>
+      <c r="I572" s="82"/>
     </row>
     <row r="573">
       <c r="B573" s="81"/>
       <c r="G573" s="65"/>
-      <c r="I573" s="80"/>
+      <c r="I573" s="82"/>
     </row>
     <row r="574">
       <c r="B574" s="81"/>
       <c r="G574" s="65"/>
-      <c r="I574" s="80"/>
+      <c r="I574" s="82"/>
     </row>
     <row r="575">
       <c r="B575" s="81"/>
       <c r="G575" s="65"/>
-      <c r="I575" s="80"/>
+      <c r="I575" s="82"/>
     </row>
     <row r="576">
       <c r="B576" s="81"/>
       <c r="G576" s="65"/>
-      <c r="I576" s="80"/>
+      <c r="I576" s="82"/>
     </row>
     <row r="577">
       <c r="B577" s="81"/>
       <c r="G577" s="65"/>
-      <c r="I577" s="80"/>
+      <c r="I577" s="82"/>
     </row>
     <row r="578">
       <c r="B578" s="81"/>
       <c r="G578" s="65"/>
-      <c r="I578" s="80"/>
+      <c r="I578" s="82"/>
     </row>
     <row r="579">
       <c r="B579" s="81"/>
       <c r="G579" s="65"/>
-      <c r="I579" s="80"/>
+      <c r="I579" s="82"/>
     </row>
     <row r="580">
       <c r="B580" s="81"/>
       <c r="G580" s="65"/>
-      <c r="I580" s="80"/>
+      <c r="I580" s="82"/>
     </row>
     <row r="581">
       <c r="B581" s="81"/>
       <c r="G581" s="65"/>
-      <c r="I581" s="80"/>
+      <c r="I581" s="82"/>
     </row>
     <row r="582">
       <c r="B582" s="81"/>
       <c r="G582" s="65"/>
-      <c r="I582" s="80"/>
+      <c r="I582" s="82"/>
     </row>
     <row r="583">
       <c r="B583" s="81"/>
       <c r="G583" s="65"/>
-      <c r="I583" s="80"/>
+      <c r="I583" s="82"/>
     </row>
     <row r="584">
       <c r="B584" s="81"/>
       <c r="G584" s="65"/>
-      <c r="I584" s="80"/>
+      <c r="I584" s="82"/>
     </row>
     <row r="585">
       <c r="B585" s="81"/>
       <c r="G585" s="65"/>
-      <c r="I585" s="80"/>
+      <c r="I585" s="82"/>
     </row>
     <row r="586">
       <c r="B586" s="81"/>
       <c r="G586" s="65"/>
-      <c r="I586" s="80"/>
+      <c r="I586" s="82"/>
     </row>
     <row r="587">
       <c r="B587" s="81"/>
       <c r="G587" s="65"/>
-      <c r="I587" s="80"/>
+      <c r="I587" s="82"/>
     </row>
     <row r="588">
       <c r="B588" s="81"/>
       <c r="G588" s="65"/>
-      <c r="I588" s="80"/>
+      <c r="I588" s="82"/>
     </row>
     <row r="589">
       <c r="B589" s="81"/>
       <c r="G589" s="65"/>
-      <c r="I589" s="80"/>
+      <c r="I589" s="82"/>
     </row>
     <row r="590">
       <c r="B590" s="81"/>
       <c r="G590" s="65"/>
-      <c r="I590" s="80"/>
+      <c r="I590" s="82"/>
     </row>
     <row r="591">
       <c r="B591" s="81"/>
       <c r="G591" s="65"/>
-      <c r="I591" s="80"/>
+      <c r="I591" s="82"/>
     </row>
     <row r="592">
       <c r="B592" s="81"/>
       <c r="G592" s="65"/>
-      <c r="I592" s="80"/>
+      <c r="I592" s="82"/>
     </row>
     <row r="593">
       <c r="B593" s="81"/>
       <c r="G593" s="65"/>
-      <c r="I593" s="80"/>
+      <c r="I593" s="82"/>
     </row>
     <row r="594">
       <c r="B594" s="81"/>
       <c r="G594" s="65"/>
-      <c r="I594" s="80"/>
+      <c r="I594" s="82"/>
     </row>
     <row r="595">
       <c r="B595" s="81"/>
       <c r="G595" s="65"/>
-      <c r="I595" s="80"/>
+      <c r="I595" s="82"/>
     </row>
     <row r="596">
       <c r="B596" s="81"/>
       <c r="G596" s="65"/>
-      <c r="I596" s="80"/>
+      <c r="I596" s="82"/>
     </row>
     <row r="597">
       <c r="B597" s="81"/>
       <c r="G597" s="65"/>
-      <c r="I597" s="80"/>
+      <c r="I597" s="82"/>
     </row>
     <row r="598">
       <c r="B598" s="81"/>
       <c r="G598" s="65"/>
-      <c r="I598" s="80"/>
+      <c r="I598" s="82"/>
     </row>
     <row r="599">
       <c r="B599" s="81"/>
       <c r="G599" s="65"/>
-      <c r="I599" s="80"/>
+      <c r="I599" s="82"/>
     </row>
     <row r="600">
       <c r="B600" s="81"/>
       <c r="G600" s="65"/>
-      <c r="I600" s="80"/>
+      <c r="I600" s="82"/>
     </row>
     <row r="601">
       <c r="B601" s="81"/>
       <c r="G601" s="65"/>
-      <c r="I601" s="80"/>
+      <c r="I601" s="82"/>
     </row>
     <row r="602">
       <c r="B602" s="81"/>
       <c r="G602" s="65"/>
-      <c r="I602" s="80"/>
+      <c r="I602" s="82"/>
     </row>
     <row r="603">
       <c r="B603" s="81"/>
       <c r="G603" s="65"/>
-      <c r="I603" s="80"/>
+      <c r="I603" s="82"/>
     </row>
     <row r="604">
       <c r="B604" s="81"/>
       <c r="G604" s="65"/>
-      <c r="I604" s="80"/>
+      <c r="I604" s="82"/>
     </row>
     <row r="605">
       <c r="B605" s="81"/>
       <c r="G605" s="65"/>
-      <c r="I605" s="80"/>
+      <c r="I605" s="82"/>
     </row>
     <row r="606">
       <c r="B606" s="81"/>
       <c r="G606" s="65"/>
-      <c r="I606" s="80"/>
+      <c r="I606" s="82"/>
     </row>
     <row r="607">
       <c r="B607" s="81"/>
       <c r="G607" s="65"/>
-      <c r="I607" s="80"/>
+      <c r="I607" s="82"/>
     </row>
     <row r="608">
       <c r="B608" s="81"/>
       <c r="G608" s="65"/>
-      <c r="I608" s="80"/>
+      <c r="I608" s="82"/>
     </row>
     <row r="609">
       <c r="B609" s="81"/>
       <c r="G609" s="65"/>
-      <c r="I609" s="80"/>
+      <c r="I609" s="82"/>
     </row>
     <row r="610">
       <c r="B610" s="81"/>
       <c r="G610" s="65"/>
-      <c r="I610" s="80"/>
+      <c r="I610" s="82"/>
     </row>
     <row r="611">
       <c r="B611" s="81"/>
       <c r="G611" s="65"/>
-      <c r="I611" s="80"/>
+      <c r="I611" s="82"/>
     </row>
     <row r="612">
       <c r="B612" s="81"/>
       <c r="G612" s="65"/>
-      <c r="I612" s="80"/>
+      <c r="I612" s="82"/>
     </row>
     <row r="613">
       <c r="B613" s="81"/>
       <c r="G613" s="65"/>
-      <c r="I613" s="80"/>
+      <c r="I613" s="82"/>
     </row>
     <row r="614">
       <c r="B614" s="81"/>
       <c r="G614" s="65"/>
-      <c r="I614" s="80"/>
+      <c r="I614" s="82"/>
     </row>
     <row r="615">
       <c r="B615" s="81"/>
       <c r="G615" s="65"/>
-      <c r="I615" s="80"/>
+      <c r="I615" s="82"/>
     </row>
     <row r="616">
       <c r="B616" s="81"/>
       <c r="G616" s="65"/>
-      <c r="I616" s="80"/>
+      <c r="I616" s="82"/>
     </row>
     <row r="617">
       <c r="B617" s="81"/>
       <c r="G617" s="65"/>
-      <c r="I617" s="80"/>
+      <c r="I617" s="82"/>
     </row>
     <row r="618">
       <c r="B618" s="81"/>
       <c r="G618" s="65"/>
-      <c r="I618" s="80"/>
+      <c r="I618" s="82"/>
     </row>
     <row r="619">
       <c r="B619" s="81"/>
       <c r="G619" s="65"/>
-      <c r="I619" s="80"/>
+      <c r="I619" s="82"/>
     </row>
     <row r="620">
       <c r="B620" s="81"/>
       <c r="G620" s="65"/>
-      <c r="I620" s="80"/>
+      <c r="I620" s="82"/>
     </row>
     <row r="621">
       <c r="B621" s="81"/>
       <c r="G621" s="65"/>
-      <c r="I621" s="80"/>
+      <c r="I621" s="82"/>
     </row>
     <row r="622">
       <c r="B622" s="81"/>
       <c r="G622" s="65"/>
-      <c r="I622" s="80"/>
+      <c r="I622" s="82"/>
     </row>
     <row r="623">
       <c r="B623" s="81"/>
       <c r="G623" s="65"/>
-      <c r="I623" s="80"/>
+      <c r="I623" s="82"/>
     </row>
     <row r="624">
       <c r="B624" s="81"/>
       <c r="G624" s="65"/>
-      <c r="I624" s="80"/>
+      <c r="I624" s="82"/>
     </row>
     <row r="625">
       <c r="B625" s="81"/>
       <c r="G625" s="65"/>
-      <c r="I625" s="80"/>
+      <c r="I625" s="82"/>
     </row>
     <row r="626">
       <c r="B626" s="81"/>
       <c r="G626" s="65"/>
-      <c r="I626" s="80"/>
+      <c r="I626" s="82"/>
     </row>
     <row r="627">
       <c r="B627" s="81"/>
       <c r="G627" s="65"/>
-      <c r="I627" s="80"/>
+      <c r="I627" s="82"/>
     </row>
     <row r="628">
       <c r="B628" s="81"/>
       <c r="G628" s="65"/>
-      <c r="I628" s="80"/>
+      <c r="I628" s="82"/>
     </row>
     <row r="629">
       <c r="B629" s="81"/>
       <c r="G629" s="65"/>
-      <c r="I629" s="80"/>
+      <c r="I629" s="82"/>
     </row>
     <row r="630">
       <c r="B630" s="81"/>
       <c r="G630" s="65"/>
-      <c r="I630" s="80"/>
+      <c r="I630" s="82"/>
     </row>
     <row r="631">
       <c r="B631" s="81"/>
       <c r="G631" s="65"/>
-      <c r="I631" s="80"/>
+      <c r="I631" s="82"/>
     </row>
     <row r="632">
       <c r="B632" s="81"/>
       <c r="G632" s="65"/>
-      <c r="I632" s="80"/>
+      <c r="I632" s="82"/>
     </row>
     <row r="633">
       <c r="B633" s="81"/>
       <c r="G633" s="65"/>
-      <c r="I633" s="80"/>
+      <c r="I633" s="82"/>
     </row>
     <row r="634">
       <c r="B634" s="81"/>
       <c r="G634" s="65"/>
-      <c r="I634" s="80"/>
+      <c r="I634" s="82"/>
     </row>
     <row r="635">
       <c r="B635" s="81"/>
       <c r="G635" s="65"/>
-      <c r="I635" s="80"/>
+      <c r="I635" s="82"/>
     </row>
     <row r="636">
       <c r="B636" s="81"/>
       <c r="G636" s="65"/>
-      <c r="I636" s="80"/>
+      <c r="I636" s="82"/>
     </row>
     <row r="637">
       <c r="B637" s="81"/>
       <c r="G637" s="65"/>
-      <c r="I637" s="80"/>
+      <c r="I637" s="82"/>
     </row>
     <row r="638">
       <c r="B638" s="81"/>
       <c r="G638" s="65"/>
-      <c r="I638" s="80"/>
+      <c r="I638" s="82"/>
     </row>
     <row r="639">
       <c r="B639" s="81"/>
       <c r="G639" s="65"/>
-      <c r="I639" s="80"/>
+      <c r="I639" s="82"/>
     </row>
     <row r="640">
       <c r="B640" s="81"/>
       <c r="G640" s="65"/>
-      <c r="I640" s="80"/>
+      <c r="I640" s="82"/>
     </row>
     <row r="641">
       <c r="B641" s="81"/>
       <c r="G641" s="65"/>
-      <c r="I641" s="80"/>
+      <c r="I641" s="82"/>
     </row>
     <row r="642">
       <c r="B642" s="81"/>
       <c r="G642" s="65"/>
-      <c r="I642" s="80"/>
+      <c r="I642" s="82"/>
     </row>
     <row r="643">
       <c r="B643" s="81"/>
       <c r="G643" s="65"/>
-      <c r="I643" s="80"/>
+      <c r="I643" s="82"/>
     </row>
     <row r="644">
       <c r="B644" s="81"/>
       <c r="G644" s="65"/>
-      <c r="I644" s="80"/>
+      <c r="I644" s="82"/>
     </row>
     <row r="645">
       <c r="B645" s="81"/>
       <c r="G645" s="65"/>
-      <c r="I645" s="80"/>
+      <c r="I645" s="82"/>
     </row>
     <row r="646">
       <c r="B646" s="81"/>
       <c r="G646" s="65"/>
-      <c r="I646" s="80"/>
+      <c r="I646" s="82"/>
     </row>
     <row r="647">
       <c r="B647" s="81"/>
       <c r="G647" s="65"/>
-      <c r="I647" s="80"/>
+      <c r="I647" s="82"/>
     </row>
     <row r="648">
       <c r="B648" s="81"/>
       <c r="G648" s="65"/>
-      <c r="I648" s="80"/>
+      <c r="I648" s="82"/>
     </row>
     <row r="649">
       <c r="B649" s="81"/>
       <c r="G649" s="65"/>
-      <c r="I649" s="80"/>
+      <c r="I649" s="82"/>
     </row>
     <row r="650">
       <c r="B650" s="81"/>
       <c r="G650" s="65"/>
-      <c r="I650" s="80"/>
+      <c r="I650" s="82"/>
     </row>
     <row r="651">
       <c r="B651" s="81"/>
       <c r="G651" s="65"/>
-      <c r="I651" s="80"/>
+      <c r="I651" s="82"/>
     </row>
     <row r="652">
       <c r="B652" s="81"/>
       <c r="G652" s="65"/>
-      <c r="I652" s="80"/>
+      <c r="I652" s="82"/>
     </row>
     <row r="653">
       <c r="B653" s="81"/>
       <c r="G653" s="65"/>
-      <c r="I653" s="80"/>
+      <c r="I653" s="82"/>
     </row>
     <row r="654">
       <c r="B654" s="81"/>
       <c r="G654" s="65"/>
-      <c r="I654" s="80"/>
+      <c r="I654" s="82"/>
     </row>
     <row r="655">
       <c r="B655" s="81"/>
       <c r="G655" s="65"/>
-      <c r="I655" s="80"/>
+      <c r="I655" s="82"/>
     </row>
     <row r="656">
       <c r="B656" s="81"/>
       <c r="G656" s="65"/>
-      <c r="I656" s="80"/>
+      <c r="I656" s="82"/>
     </row>
     <row r="657">
       <c r="B657" s="81"/>
       <c r="G657" s="65"/>
-      <c r="I657" s="80"/>
+      <c r="I657" s="82"/>
     </row>
     <row r="658">
       <c r="B658" s="81"/>
       <c r="G658" s="65"/>
-      <c r="I658" s="80"/>
+      <c r="I658" s="82"/>
     </row>
     <row r="659">
       <c r="B659" s="81"/>
       <c r="G659" s="65"/>
-      <c r="I659" s="80"/>
+      <c r="I659" s="82"/>
     </row>
     <row r="660">
       <c r="B660" s="81"/>
       <c r="G660" s="65"/>
-      <c r="I660" s="80"/>
+      <c r="I660" s="82"/>
     </row>
     <row r="661">
       <c r="B661" s="81"/>
       <c r="G661" s="65"/>
-      <c r="I661" s="80"/>
+      <c r="I661" s="82"/>
     </row>
     <row r="662">
       <c r="B662" s="81"/>
       <c r="G662" s="65"/>
-      <c r="I662" s="80"/>
+      <c r="I662" s="82"/>
     </row>
     <row r="663">
       <c r="B663" s="81"/>
       <c r="G663" s="65"/>
-      <c r="I663" s="80"/>
+      <c r="I663" s="82"/>
     </row>
     <row r="664">
       <c r="B664" s="81"/>
       <c r="G664" s="65"/>
-      <c r="I664" s="80"/>
+      <c r="I664" s="82"/>
     </row>
     <row r="665">
       <c r="B665" s="81"/>
       <c r="G665" s="65"/>
-      <c r="I665" s="80"/>
+      <c r="I665" s="82"/>
     </row>
     <row r="666">
       <c r="B666" s="81"/>
       <c r="G666" s="65"/>
-      <c r="I666" s="80"/>
+      <c r="I666" s="82"/>
     </row>
     <row r="667">
       <c r="B667" s="81"/>
       <c r="G667" s="65"/>
-      <c r="I667" s="80"/>
+      <c r="I667" s="82"/>
     </row>
     <row r="668">
       <c r="B668" s="81"/>
       <c r="G668" s="65"/>
-      <c r="I668" s="80"/>
+      <c r="I668" s="82"/>
     </row>
     <row r="669">
       <c r="B669" s="81"/>
       <c r="G669" s="65"/>
-      <c r="I669" s="80"/>
+      <c r="I669" s="82"/>
     </row>
     <row r="670">
       <c r="B670" s="81"/>
       <c r="G670" s="65"/>
-      <c r="I670" s="80"/>
+      <c r="I670" s="82"/>
     </row>
     <row r="671">
       <c r="B671" s="81"/>
       <c r="G671" s="65"/>
-      <c r="I671" s="80"/>
+      <c r="I671" s="82"/>
     </row>
     <row r="672">
       <c r="B672" s="81"/>
       <c r="G672" s="65"/>
-      <c r="I672" s="80"/>
+      <c r="I672" s="82"/>
     </row>
     <row r="673">
       <c r="B673" s="81"/>
       <c r="G673" s="65"/>
-      <c r="I673" s="80"/>
+      <c r="I673" s="82"/>
     </row>
     <row r="674">
       <c r="B674" s="81"/>
       <c r="G674" s="65"/>
-      <c r="I674" s="80"/>
+      <c r="I674" s="82"/>
     </row>
     <row r="675">
       <c r="B675" s="81"/>
       <c r="G675" s="65"/>
-      <c r="I675" s="80"/>
+      <c r="I675" s="82"/>
     </row>
     <row r="676">
       <c r="B676" s="81"/>
       <c r="G676" s="65"/>
-      <c r="I676" s="80"/>
+      <c r="I676" s="82"/>
     </row>
     <row r="677">
       <c r="B677" s="81"/>
       <c r="G677" s="65"/>
-      <c r="I677" s="80"/>
+      <c r="I677" s="82"/>
     </row>
     <row r="678">
       <c r="B678" s="81"/>
       <c r="G678" s="65"/>
-      <c r="I678" s="80"/>
+      <c r="I678" s="82"/>
     </row>
     <row r="679">
       <c r="B679" s="81"/>
       <c r="G679" s="65"/>
-      <c r="I679" s="80"/>
+      <c r="I679" s="82"/>
     </row>
     <row r="680">
       <c r="B680" s="81"/>
       <c r="G680" s="65"/>
-      <c r="I680" s="80"/>
+      <c r="I680" s="82"/>
     </row>
     <row r="681">
       <c r="B681" s="81"/>
       <c r="G681" s="65"/>
-      <c r="I681" s="80"/>
+      <c r="I681" s="82"/>
     </row>
     <row r="682">
       <c r="B682" s="81"/>
       <c r="G682" s="65"/>
-      <c r="I682" s="80"/>
+      <c r="I682" s="82"/>
     </row>
     <row r="683">
       <c r="B683" s="81"/>
       <c r="G683" s="65"/>
-      <c r="I683" s="80"/>
+      <c r="I683" s="82"/>
     </row>
     <row r="684">
       <c r="B684" s="81"/>
       <c r="G684" s="65"/>
-      <c r="I684" s="80"/>
+      <c r="I684" s="82"/>
     </row>
     <row r="685">
       <c r="B685" s="81"/>
       <c r="G685" s="65"/>
-      <c r="I685" s="80"/>
+      <c r="I685" s="82"/>
     </row>
     <row r="686">
       <c r="B686" s="81"/>
       <c r="G686" s="65"/>
-      <c r="I686" s="80"/>
+      <c r="I686" s="82"/>
     </row>
     <row r="687">
       <c r="B687" s="81"/>
       <c r="G687" s="65"/>
-      <c r="I687" s="80"/>
+      <c r="I687" s="82"/>
     </row>
     <row r="688">
       <c r="B688" s="81"/>
       <c r="G688" s="65"/>
-      <c r="I688" s="80"/>
+      <c r="I688" s="82"/>
     </row>
     <row r="689">
       <c r="B689" s="81"/>
       <c r="G689" s="65"/>
-      <c r="I689" s="80"/>
+      <c r="I689" s="82"/>
     </row>
     <row r="690">
       <c r="B690" s="81"/>
       <c r="G690" s="65"/>
-      <c r="I690" s="80"/>
+      <c r="I690" s="82"/>
     </row>
     <row r="691">
       <c r="B691" s="81"/>
       <c r="G691" s="65"/>
-      <c r="I691" s="80"/>
+      <c r="I691" s="82"/>
     </row>
     <row r="692">
       <c r="B692" s="81"/>
       <c r="G692" s="65"/>
-      <c r="I692" s="80"/>
+      <c r="I692" s="82"/>
     </row>
     <row r="693">
       <c r="B693" s="81"/>
       <c r="G693" s="65"/>
-      <c r="I693" s="80"/>
+      <c r="I693" s="82"/>
     </row>
     <row r="694">
       <c r="B694" s="81"/>
       <c r="G694" s="65"/>
-      <c r="I694" s="80"/>
+      <c r="I694" s="82"/>
     </row>
     <row r="695">
       <c r="B695" s="81"/>
       <c r="G695" s="65"/>
-      <c r="I695" s="80"/>
+      <c r="I695" s="82"/>
     </row>
     <row r="696">
       <c r="B696" s="81"/>
       <c r="G696" s="65"/>
-      <c r="I696" s="80"/>
+      <c r="I696" s="82"/>
     </row>
     <row r="697">
       <c r="B697" s="81"/>
       <c r="G697" s="65"/>
-      <c r="I697" s="80"/>
+      <c r="I697" s="82"/>
     </row>
     <row r="698">
       <c r="B698" s="81"/>
       <c r="G698" s="65"/>
-      <c r="I698" s="80"/>
+      <c r="I698" s="82"/>
     </row>
     <row r="699">
       <c r="B699" s="81"/>
       <c r="G699" s="65"/>
-      <c r="I699" s="80"/>
+      <c r="I699" s="82"/>
     </row>
     <row r="700">
       <c r="B700" s="81"/>
       <c r="G700" s="65"/>
-      <c r="I700" s="80"/>
+      <c r="I700" s="82"/>
     </row>
     <row r="701">
       <c r="B701" s="81"/>
       <c r="G701" s="65"/>
-      <c r="I701" s="80"/>
+      <c r="I701" s="82"/>
     </row>
     <row r="702">
       <c r="B702" s="81"/>
       <c r="G702" s="65"/>
-      <c r="I702" s="80"/>
+      <c r="I702" s="82"/>
     </row>
     <row r="703">
       <c r="B703" s="81"/>
       <c r="G703" s="65"/>
-      <c r="I703" s="80"/>
+      <c r="I703" s="82"/>
     </row>
     <row r="704">
       <c r="B704" s="81"/>
       <c r="G704" s="65"/>
-      <c r="I704" s="80"/>
+      <c r="I704" s="82"/>
     </row>
     <row r="705">
       <c r="B705" s="81"/>
       <c r="G705" s="65"/>
-      <c r="I705" s="80"/>
+      <c r="I705" s="82"/>
     </row>
     <row r="706">
       <c r="B706" s="81"/>
       <c r="G706" s="65"/>
-      <c r="I706" s="80"/>
+      <c r="I706" s="82"/>
     </row>
     <row r="707">
       <c r="B707" s="81"/>
       <c r="G707" s="65"/>
-      <c r="I707" s="80"/>
+      <c r="I707" s="82"/>
     </row>
     <row r="708">
       <c r="B708" s="81"/>
       <c r="G708" s="65"/>
-      <c r="I708" s="80"/>
+      <c r="I708" s="82"/>
     </row>
     <row r="709">
       <c r="B709" s="81"/>
       <c r="G709" s="65"/>
-      <c r="I709" s="80"/>
+      <c r="I709" s="82"/>
     </row>
     <row r="710">
       <c r="B710" s="81"/>
       <c r="G710" s="65"/>
-      <c r="I710" s="80"/>
+      <c r="I710" s="82"/>
     </row>
     <row r="711">
       <c r="B711" s="81"/>
       <c r="G711" s="65"/>
-      <c r="I711" s="80"/>
+      <c r="I711" s="82"/>
     </row>
     <row r="712">
       <c r="B712" s="81"/>
       <c r="G712" s="65"/>
-      <c r="I712" s="80"/>
+      <c r="I712" s="82"/>
     </row>
     <row r="713">
       <c r="B713" s="81"/>
       <c r="G713" s="65"/>
-      <c r="I713" s="80"/>
+      <c r="I713" s="82"/>
     </row>
     <row r="714">
       <c r="B714" s="81"/>
       <c r="G714" s="65"/>
-      <c r="I714" s="80"/>
+      <c r="I714" s="82"/>
     </row>
     <row r="715">
       <c r="B715" s="81"/>
       <c r="G715" s="65"/>
-      <c r="I715" s="80"/>
+      <c r="I715" s="82"/>
     </row>
     <row r="716">
       <c r="B716" s="81"/>
       <c r="G716" s="65"/>
-      <c r="I716" s="80"/>
+      <c r="I716" s="82"/>
     </row>
     <row r="717">
       <c r="B717" s="81"/>
       <c r="G717" s="65"/>
-      <c r="I717" s="80"/>
+      <c r="I717" s="82"/>
     </row>
     <row r="718">
       <c r="B718" s="81"/>
       <c r="G718" s="65"/>
-      <c r="I718" s="80"/>
+      <c r="I718" s="82"/>
     </row>
     <row r="719">
       <c r="B719" s="81"/>
       <c r="G719" s="65"/>
-      <c r="I719" s="80"/>
+      <c r="I719" s="82"/>
     </row>
     <row r="720">
       <c r="B720" s="81"/>
       <c r="G720" s="65"/>
-      <c r="I720" s="80"/>
+      <c r="I720" s="82"/>
     </row>
     <row r="721">
       <c r="B721" s="81"/>
       <c r="G721" s="65"/>
-      <c r="I721" s="80"/>
+      <c r="I721" s="82"/>
     </row>
     <row r="722">
       <c r="B722" s="81"/>
       <c r="G722" s="65"/>
-      <c r="I722" s="80"/>
+      <c r="I722" s="82"/>
     </row>
     <row r="723">
       <c r="B723" s="81"/>
       <c r="G723" s="65"/>
-      <c r="I723" s="80"/>
+      <c r="I723" s="82"/>
     </row>
     <row r="724">
       <c r="B724" s="81"/>
       <c r="G724" s="65"/>
-      <c r="I724" s="80"/>
+      <c r="I724" s="82"/>
     </row>
     <row r="725">
       <c r="B725" s="81"/>
       <c r="G725" s="65"/>
-      <c r="I725" s="80"/>
+      <c r="I725" s="82"/>
     </row>
     <row r="726">
       <c r="B726" s="81"/>
       <c r="G726" s="65"/>
-      <c r="I726" s="80"/>
+      <c r="I726" s="82"/>
     </row>
     <row r="727">
       <c r="B727" s="81"/>
       <c r="G727" s="65"/>
-      <c r="I727" s="80"/>
+      <c r="I727" s="82"/>
     </row>
     <row r="728">
       <c r="B728" s="81"/>
       <c r="G728" s="65"/>
-      <c r="I728" s="80"/>
+      <c r="I728" s="82"/>
     </row>
     <row r="729">
       <c r="B729" s="81"/>
       <c r="G729" s="65"/>
-      <c r="I729" s="80"/>
+      <c r="I729" s="82"/>
     </row>
     <row r="730">
       <c r="B730" s="81"/>
       <c r="G730" s="65"/>
-      <c r="I730" s="80"/>
+      <c r="I730" s="82"/>
     </row>
     <row r="731">
       <c r="B731" s="81"/>
       <c r="G731" s="65"/>
-      <c r="I731" s="80"/>
+      <c r="I731" s="82"/>
     </row>
     <row r="732">
       <c r="B732" s="81"/>
       <c r="G732" s="65"/>
-      <c r="I732" s="80"/>
+      <c r="I732" s="82"/>
     </row>
     <row r="733">
       <c r="B733" s="81"/>
       <c r="G733" s="65"/>
-      <c r="I733" s="80"/>
+      <c r="I733" s="82"/>
     </row>
     <row r="734">
       <c r="B734" s="81"/>
       <c r="G734" s="65"/>
-      <c r="I734" s="80"/>
+      <c r="I734" s="82"/>
     </row>
     <row r="735">
       <c r="B735" s="81"/>
       <c r="G735" s="65"/>
-      <c r="I735" s="80"/>
+      <c r="I735" s="82"/>
     </row>
     <row r="736">
       <c r="B736" s="81"/>
       <c r="G736" s="65"/>
-      <c r="I736" s="80"/>
+      <c r="I736" s="82"/>
     </row>
     <row r="737">
       <c r="B737" s="81"/>
       <c r="G737" s="65"/>
-      <c r="I737" s="80"/>
+      <c r="I737" s="82"/>
     </row>
     <row r="738">
       <c r="B738" s="81"/>
       <c r="G738" s="65"/>
-      <c r="I738" s="80"/>
+      <c r="I738" s="82"/>
     </row>
     <row r="739">
       <c r="B739" s="81"/>
       <c r="G739" s="65"/>
-      <c r="I739" s="80"/>
+      <c r="I739" s="82"/>
     </row>
     <row r="740">
       <c r="B740" s="81"/>
       <c r="G740" s="65"/>
-      <c r="I740" s="80"/>
+      <c r="I740" s="82"/>
     </row>
     <row r="741">
       <c r="B741" s="81"/>
       <c r="G741" s="65"/>
-      <c r="I741" s="80"/>
+      <c r="I741" s="82"/>
     </row>
     <row r="742">
       <c r="B742" s="81"/>
       <c r="G742" s="65"/>
-      <c r="I742" s="80"/>
+      <c r="I742" s="82"/>
     </row>
     <row r="743">
       <c r="B743" s="81"/>
       <c r="G743" s="65"/>
-      <c r="I743" s="80"/>
+      <c r="I743" s="82"/>
     </row>
     <row r="744">
       <c r="B744" s="81"/>
       <c r="G744" s="65"/>
-      <c r="I744" s="80"/>
+      <c r="I744" s="82"/>
     </row>
     <row r="745">
       <c r="B745" s="81"/>
       <c r="G745" s="65"/>
-      <c r="I745" s="80"/>
+      <c r="I745" s="82"/>
     </row>
     <row r="746">
       <c r="B746" s="81"/>
       <c r="G746" s="65"/>
-      <c r="I746" s="80"/>
+      <c r="I746" s="82"/>
     </row>
     <row r="747">
       <c r="B747" s="81"/>
       <c r="G747" s="65"/>
-      <c r="I747" s="80"/>
+      <c r="I747" s="82"/>
     </row>
     <row r="748">
       <c r="B748" s="81"/>
       <c r="G748" s="65"/>
-      <c r="I748" s="80"/>
+      <c r="I748" s="82"/>
     </row>
     <row r="749">
       <c r="B749" s="81"/>
       <c r="G749" s="65"/>
-      <c r="I749" s="80"/>
+      <c r="I749" s="82"/>
     </row>
     <row r="750">
       <c r="B750" s="81"/>
       <c r="G750" s="65"/>
-      <c r="I750" s="80"/>
+      <c r="I750" s="82"/>
     </row>
     <row r="751">
       <c r="B751" s="81"/>
       <c r="G751" s="65"/>
-      <c r="I751" s="80"/>
+      <c r="I751" s="82"/>
     </row>
     <row r="752">
       <c r="B752" s="81"/>
       <c r="G752" s="65"/>
-      <c r="I752" s="80"/>
+      <c r="I752" s="82"/>
     </row>
     <row r="753">
       <c r="B753" s="81"/>
       <c r="G753" s="65"/>
-      <c r="I753" s="80"/>
+      <c r="I753" s="82"/>
     </row>
     <row r="754">
       <c r="B754" s="81"/>
       <c r="G754" s="65"/>
-      <c r="I754" s="80"/>
+      <c r="I754" s="82"/>
     </row>
     <row r="755">
       <c r="B755" s="81"/>
       <c r="G755" s="65"/>
-      <c r="I755" s="80"/>
+      <c r="I755" s="82"/>
     </row>
     <row r="756">
       <c r="B756" s="81"/>
       <c r="G756" s="65"/>
-      <c r="I756" s="80"/>
+      <c r="I756" s="82"/>
     </row>
     <row r="757">
       <c r="B757" s="81"/>
       <c r="G757" s="65"/>
-      <c r="I757" s="80"/>
+      <c r="I757" s="82"/>
     </row>
     <row r="758">
       <c r="B758" s="81"/>
       <c r="G758" s="65"/>
-      <c r="I758" s="80"/>
+      <c r="I758" s="82"/>
     </row>
     <row r="759">
       <c r="B759" s="81"/>
       <c r="G759" s="65"/>
-      <c r="I759" s="80"/>
+      <c r="I759" s="82"/>
     </row>
     <row r="760">
       <c r="B760" s="81"/>
       <c r="G760" s="65"/>
-      <c r="I760" s="80"/>
+      <c r="I760" s="82"/>
     </row>
     <row r="761">
       <c r="B761" s="81"/>
       <c r="G761" s="65"/>
-      <c r="I761" s="80"/>
+      <c r="I761" s="82"/>
     </row>
     <row r="762">
       <c r="B762" s="81"/>
       <c r="G762" s="65"/>
-      <c r="I762" s="80"/>
+      <c r="I762" s="82"/>
     </row>
     <row r="763">
       <c r="B763" s="81"/>
       <c r="G763" s="65"/>
-      <c r="I763" s="80"/>
+      <c r="I763" s="82"/>
     </row>
     <row r="764">
       <c r="B764" s="81"/>
       <c r="G764" s="65"/>
-      <c r="I764" s="80"/>
+      <c r="I764" s="82"/>
     </row>
     <row r="765">
       <c r="B765" s="81"/>
       <c r="G765" s="65"/>
-      <c r="I765" s="80"/>
+      <c r="I765" s="82"/>
     </row>
     <row r="766">
       <c r="B766" s="81"/>
       <c r="G766" s="65"/>
-      <c r="I766" s="80"/>
+      <c r="I766" s="82"/>
     </row>
     <row r="767">
       <c r="B767" s="81"/>
       <c r="G767" s="65"/>
-      <c r="I767" s="80"/>
+      <c r="I767" s="82"/>
     </row>
     <row r="768">
       <c r="B768" s="81"/>
       <c r="G768" s="65"/>
-      <c r="I768" s="80"/>
+      <c r="I768" s="82"/>
     </row>
     <row r="769">
       <c r="B769" s="81"/>
       <c r="G769" s="65"/>
-      <c r="I769" s="80"/>
+      <c r="I769" s="82"/>
     </row>
     <row r="770">
       <c r="B770" s="81"/>
       <c r="G770" s="65"/>
-      <c r="I770" s="80"/>
+      <c r="I770" s="82"/>
     </row>
     <row r="771">
       <c r="B771" s="81"/>
       <c r="G771" s="65"/>
-      <c r="I771" s="80"/>
+      <c r="I771" s="82"/>
     </row>
     <row r="772">
       <c r="B772" s="81"/>
       <c r="G772" s="65"/>
-      <c r="I772" s="80"/>
+      <c r="I772" s="82"/>
     </row>
     <row r="773">
       <c r="B773" s="81"/>
       <c r="G773" s="65"/>
-      <c r="I773" s="80"/>
+      <c r="I773" s="82"/>
     </row>
     <row r="774">
       <c r="B774" s="81"/>
       <c r="G774" s="65"/>
-      <c r="I774" s="80"/>
+      <c r="I774" s="82"/>
     </row>
     <row r="775">
       <c r="B775" s="81"/>
       <c r="G775" s="65"/>
-      <c r="I775" s="80"/>
+      <c r="I775" s="82"/>
     </row>
     <row r="776">
       <c r="B776" s="81"/>
       <c r="G776" s="65"/>
-      <c r="I776" s="80"/>
+      <c r="I776" s="82"/>
     </row>
     <row r="777">
       <c r="B777" s="81"/>
       <c r="G777" s="65"/>
-      <c r="I777" s="80"/>
+      <c r="I777" s="82"/>
     </row>
     <row r="778">
       <c r="B778" s="81"/>
       <c r="G778" s="65"/>
-      <c r="I778" s="80"/>
+      <c r="I778" s="82"/>
     </row>
     <row r="779">
       <c r="B779" s="81"/>
       <c r="G779" s="65"/>
-      <c r="I779" s="80"/>
+      <c r="I779" s="82"/>
     </row>
     <row r="780">
       <c r="B780" s="81"/>
       <c r="G780" s="65"/>
-      <c r="I780" s="80"/>
+      <c r="I780" s="82"/>
     </row>
     <row r="781">
       <c r="B781" s="81"/>
       <c r="G781" s="65"/>
-      <c r="I781" s="80"/>
+      <c r="I781" s="82"/>
     </row>
     <row r="782">
       <c r="B782" s="81"/>
       <c r="G782" s="65"/>
-      <c r="I782" s="80"/>
+      <c r="I782" s="82"/>
     </row>
     <row r="783">
       <c r="B783" s="81"/>
       <c r="G783" s="65"/>
-      <c r="I783" s="80"/>
+      <c r="I783" s="82"/>
     </row>
     <row r="784">
       <c r="B784" s="81"/>
       <c r="G784" s="65"/>
-      <c r="I784" s="80"/>
+      <c r="I784" s="82"/>
     </row>
     <row r="785">
       <c r="B785" s="81"/>
       <c r="G785" s="65"/>
-      <c r="I785" s="80"/>
+      <c r="I785" s="82"/>
     </row>
     <row r="786">
       <c r="B786" s="81"/>
       <c r="G786" s="65"/>
-      <c r="I786" s="80"/>
+      <c r="I786" s="82"/>
     </row>
     <row r="787">
       <c r="B787" s="81"/>
       <c r="G787" s="65"/>
-      <c r="I787" s="80"/>
+      <c r="I787" s="82"/>
     </row>
     <row r="788">
       <c r="B788" s="81"/>
       <c r="G788" s="65"/>
-      <c r="I788" s="80"/>
+      <c r="I788" s="82"/>
     </row>
     <row r="789">
       <c r="B789" s="81"/>
       <c r="G789" s="65"/>
-      <c r="I789" s="80"/>
+      <c r="I789" s="82"/>
     </row>
     <row r="790">
       <c r="B790" s="81"/>
       <c r="G790" s="65"/>
-      <c r="I790" s="80"/>
+      <c r="I790" s="82"/>
     </row>
     <row r="791">
       <c r="B791" s="81"/>
       <c r="G791" s="65"/>
-      <c r="I791" s="80"/>
+      <c r="I791" s="82"/>
     </row>
     <row r="792">
       <c r="B792" s="81"/>
       <c r="G792" s="65"/>
-      <c r="I792" s="80"/>
+      <c r="I792" s="82"/>
     </row>
     <row r="793">
       <c r="B793" s="81"/>
       <c r="G793" s="65"/>
-      <c r="I793" s="80"/>
+      <c r="I793" s="82"/>
     </row>
     <row r="794">
       <c r="B794" s="81"/>
       <c r="G794" s="65"/>
-      <c r="I794" s="80"/>
+      <c r="I794" s="82"/>
     </row>
     <row r="795">
       <c r="B795" s="81"/>
       <c r="G795" s="65"/>
-      <c r="I795" s="80"/>
+      <c r="I795" s="82"/>
     </row>
     <row r="796">
       <c r="B796" s="81"/>
       <c r="G796" s="65"/>
-      <c r="I796" s="80"/>
+      <c r="I796" s="82"/>
     </row>
     <row r="797">
       <c r="B797" s="81"/>
       <c r="G797" s="65"/>
-      <c r="I797" s="80"/>
+      <c r="I797" s="82"/>
     </row>
     <row r="798">
       <c r="B798" s="81"/>
       <c r="G798" s="65"/>
-      <c r="I798" s="80"/>
+      <c r="I798" s="82"/>
     </row>
     <row r="799">
       <c r="B799" s="81"/>
       <c r="G799" s="65"/>
-      <c r="I799" s="80"/>
+      <c r="I799" s="82"/>
     </row>
     <row r="800">
       <c r="B800" s="81"/>
       <c r="G800" s="65"/>
-      <c r="I800" s="80"/>
+      <c r="I800" s="82"/>
     </row>
     <row r="801">
       <c r="B801" s="81"/>
       <c r="G801" s="65"/>
-      <c r="I801" s="80"/>
+      <c r="I801" s="82"/>
     </row>
     <row r="802">
       <c r="B802" s="81"/>
       <c r="G802" s="65"/>
-      <c r="I802" s="80"/>
+      <c r="I802" s="82"/>
     </row>
     <row r="803">
       <c r="B803" s="81"/>
       <c r="G803" s="65"/>
-      <c r="I803" s="80"/>
+      <c r="I803" s="82"/>
     </row>
     <row r="804">
       <c r="B804" s="81"/>
       <c r="G804" s="65"/>
-      <c r="I804" s="80"/>
+      <c r="I804" s="82"/>
     </row>
     <row r="805">
       <c r="B805" s="81"/>
       <c r="G805" s="65"/>
-      <c r="I805" s="80"/>
+      <c r="I805" s="82"/>
     </row>
     <row r="806">
       <c r="B806" s="81"/>
       <c r="G806" s="65"/>
-      <c r="I806" s="80"/>
+      <c r="I806" s="82"/>
     </row>
     <row r="807">
       <c r="B807" s="81"/>
       <c r="G807" s="65"/>
-      <c r="I807" s="80"/>
+      <c r="I807" s="82"/>
     </row>
     <row r="808">
       <c r="B808" s="81"/>
       <c r="G808" s="65"/>
-      <c r="I808" s="80"/>
+      <c r="I808" s="82"/>
     </row>
     <row r="809">
       <c r="B809" s="81"/>
       <c r="G809" s="65"/>
-      <c r="I809" s="80"/>
+      <c r="I809" s="82"/>
     </row>
     <row r="810">
       <c r="B810" s="81"/>
       <c r="G810" s="65"/>
-      <c r="I810" s="80"/>
+      <c r="I810" s="82"/>
     </row>
     <row r="811">
       <c r="B811" s="81"/>
       <c r="G811" s="65"/>
-      <c r="I811" s="80"/>
+      <c r="I811" s="82"/>
     </row>
     <row r="812">
       <c r="B812" s="81"/>
       <c r="G812" s="65"/>
-      <c r="I812" s="80"/>
+      <c r="I812" s="82"/>
     </row>
     <row r="813">
       <c r="B813" s="81"/>
       <c r="G813" s="65"/>
-      <c r="I813" s="80"/>
+      <c r="I813" s="82"/>
     </row>
     <row r="814">
       <c r="B814" s="81"/>
       <c r="G814" s="65"/>
-      <c r="I814" s="80"/>
+      <c r="I814" s="82"/>
     </row>
     <row r="815">
       <c r="B815" s="81"/>
       <c r="G815" s="65"/>
-      <c r="I815" s="80"/>
+      <c r="I815" s="82"/>
     </row>
     <row r="816">
       <c r="B816" s="81"/>
       <c r="G816" s="65"/>
-      <c r="I816" s="80"/>
+      <c r="I816" s="82"/>
     </row>
     <row r="817">
       <c r="B817" s="81"/>
       <c r="G817" s="65"/>
-      <c r="I817" s="80"/>
+      <c r="I817" s="82"/>
     </row>
     <row r="818">
       <c r="B818" s="81"/>
       <c r="G818" s="65"/>
-      <c r="I818" s="80"/>
+      <c r="I818" s="82"/>
     </row>
     <row r="819">
       <c r="B819" s="81"/>
       <c r="G819" s="65"/>
-      <c r="I819" s="80"/>
+      <c r="I819" s="82"/>
     </row>
     <row r="820">
       <c r="B820" s="81"/>
       <c r="G820" s="65"/>
-      <c r="I820" s="80"/>
+      <c r="I820" s="82"/>
     </row>
     <row r="821">
       <c r="B821" s="81"/>
       <c r="G821" s="65"/>
-      <c r="I821" s="80"/>
+      <c r="I821" s="82"/>
     </row>
     <row r="822">
       <c r="B822" s="81"/>
       <c r="G822" s="65"/>
-      <c r="I822" s="80"/>
+      <c r="I822" s="82"/>
     </row>
     <row r="823">
       <c r="B823" s="81"/>
       <c r="G823" s="65"/>
-      <c r="I823" s="80"/>
+      <c r="I823" s="82"/>
     </row>
     <row r="824">
       <c r="B824" s="81"/>
       <c r="G824" s="65"/>
-      <c r="I824" s="80"/>
+      <c r="I824" s="82"/>
     </row>
     <row r="825">
       <c r="B825" s="81"/>
       <c r="G825" s="65"/>
-      <c r="I825" s="80"/>
+      <c r="I825" s="82"/>
     </row>
     <row r="826">
       <c r="B826" s="81"/>
       <c r="G826" s="65"/>
-      <c r="I826" s="80"/>
+      <c r="I826" s="82"/>
     </row>
     <row r="827">
       <c r="B827" s="81"/>
       <c r="G827" s="65"/>
-      <c r="I827" s="80"/>
+      <c r="I827" s="82"/>
     </row>
     <row r="828">
       <c r="B828" s="81"/>
       <c r="G828" s="65"/>
-      <c r="I828" s="80"/>
+      <c r="I828" s="82"/>
     </row>
     <row r="829">
       <c r="B829" s="81"/>
       <c r="G829" s="65"/>
-      <c r="I829" s="80"/>
+      <c r="I829" s="82"/>
     </row>
     <row r="830">
       <c r="B830" s="81"/>
       <c r="G830" s="65"/>
-      <c r="I830" s="80"/>
+      <c r="I830" s="82"/>
     </row>
     <row r="831">
       <c r="B831" s="81"/>
       <c r="G831" s="65"/>
-      <c r="I831" s="80"/>
+      <c r="I831" s="82"/>
     </row>
     <row r="832">
       <c r="B832" s="81"/>
       <c r="G832" s="65"/>
-      <c r="I832" s="80"/>
+      <c r="I832" s="82"/>
     </row>
     <row r="833">
       <c r="B833" s="81"/>
       <c r="G833" s="65"/>
-      <c r="I833" s="80"/>
+      <c r="I833" s="82"/>
     </row>
     <row r="834">
       <c r="B834" s="81"/>
       <c r="G834" s="65"/>
-      <c r="I834" s="80"/>
+      <c r="I834" s="82"/>
     </row>
     <row r="835">
       <c r="B835" s="81"/>
       <c r="G835" s="65"/>
-      <c r="I835" s="80"/>
+      <c r="I835" s="82"/>
     </row>
     <row r="836">
       <c r="B836" s="81"/>
       <c r="G836" s="65"/>
-      <c r="I836" s="80"/>
+      <c r="I836" s="82"/>
     </row>
     <row r="837">
       <c r="B837" s="81"/>
       <c r="G837" s="65"/>
-      <c r="I837" s="80"/>
+      <c r="I837" s="82"/>
     </row>
     <row r="838">
       <c r="B838" s="81"/>
       <c r="G838" s="65"/>
-      <c r="I838" s="80"/>
+      <c r="I838" s="82"/>
     </row>
     <row r="839">
       <c r="B839" s="81"/>
       <c r="G839" s="65"/>
-      <c r="I839" s="80"/>
+      <c r="I839" s="82"/>
     </row>
     <row r="840">
       <c r="B840" s="81"/>
       <c r="G840" s="65"/>
-      <c r="I840" s="80"/>
+      <c r="I840" s="82"/>
     </row>
     <row r="841">
       <c r="B841" s="81"/>
       <c r="G841" s="65"/>
-      <c r="I841" s="80"/>
+      <c r="I841" s="82"/>
     </row>
     <row r="842">
       <c r="B842" s="81"/>
       <c r="G842" s="65"/>
-      <c r="I842" s="80"/>
+      <c r="I842" s="82"/>
     </row>
     <row r="843">
       <c r="B843" s="81"/>
       <c r="G843" s="65"/>
-      <c r="I843" s="80"/>
+      <c r="I843" s="82"/>
     </row>
     <row r="844">
       <c r="B844" s="81"/>
       <c r="G844" s="65"/>
-      <c r="I844" s="80"/>
+      <c r="I844" s="82"/>
     </row>
     <row r="845">
       <c r="B845" s="81"/>
       <c r="G845" s="65"/>
-      <c r="I845" s="80"/>
+      <c r="I845" s="82"/>
     </row>
     <row r="846">
       <c r="B846" s="81"/>
       <c r="G846" s="65"/>
-      <c r="I846" s="80"/>
+      <c r="I846" s="82"/>
     </row>
     <row r="847">
       <c r="B847" s="81"/>
       <c r="G847" s="65"/>
-      <c r="I847" s="80"/>
+      <c r="I847" s="82"/>
     </row>
     <row r="848">
       <c r="B848" s="81"/>
       <c r="G848" s="65"/>
-      <c r="I848" s="80"/>
+      <c r="I848" s="82"/>
     </row>
     <row r="849">
       <c r="B849" s="81"/>
       <c r="G849" s="65"/>
-      <c r="I849" s="80"/>
+      <c r="I849" s="82"/>
     </row>
     <row r="850">
       <c r="B850" s="81"/>
       <c r="G850" s="65"/>
-      <c r="I850" s="80"/>
+      <c r="I850" s="82"/>
     </row>
     <row r="851">
       <c r="B851" s="81"/>
       <c r="G851" s="65"/>
-      <c r="I851" s="80"/>
+      <c r="I851" s="82"/>
     </row>
     <row r="852">
       <c r="B852" s="81"/>
       <c r="G852" s="65"/>
-      <c r="I852" s="80"/>
+      <c r="I852" s="82"/>
     </row>
     <row r="853">
       <c r="B853" s="81"/>
       <c r="G853" s="65"/>
-      <c r="I853" s="80"/>
+      <c r="I853" s="82"/>
     </row>
     <row r="854">
       <c r="B854" s="81"/>
       <c r="G854" s="65"/>
-      <c r="I854" s="80"/>
+      <c r="I854" s="82"/>
     </row>
     <row r="855">
       <c r="B855" s="81"/>
       <c r="G855" s="65"/>
-      <c r="I855" s="80"/>
+      <c r="I855" s="82"/>
     </row>
     <row r="856">
       <c r="B856" s="81"/>
       <c r="G856" s="65"/>
-      <c r="I856" s="80"/>
+      <c r="I856" s="82"/>
     </row>
     <row r="857">
       <c r="B857" s="81"/>
       <c r="G857" s="65"/>
-      <c r="I857" s="80"/>
+      <c r="I857" s="82"/>
     </row>
     <row r="858">
       <c r="B858" s="81"/>
       <c r="G858" s="65"/>
-      <c r="I858" s="80"/>
+      <c r="I858" s="82"/>
     </row>
     <row r="859">
       <c r="B859" s="81"/>
       <c r="G859" s="65"/>
-      <c r="I859" s="80"/>
+      <c r="I859" s="82"/>
     </row>
     <row r="860">
       <c r="B860" s="81"/>
       <c r="G860" s="65"/>
-      <c r="I860" s="80"/>
+      <c r="I860" s="82"/>
     </row>
     <row r="861">
       <c r="B861" s="81"/>
       <c r="G861" s="65"/>
-      <c r="I861" s="80"/>
+      <c r="I861" s="82"/>
     </row>
     <row r="862">
       <c r="B862" s="81"/>
       <c r="G862" s="65"/>
-      <c r="I862" s="80"/>
+      <c r="I862" s="82"/>
     </row>
     <row r="863">
       <c r="B863" s="81"/>
       <c r="G863" s="65"/>
-      <c r="I863" s="80"/>
+      <c r="I863" s="82"/>
     </row>
     <row r="864">
       <c r="B864" s="81"/>
       <c r="G864" s="65"/>
-      <c r="I864" s="80"/>
+      <c r="I864" s="82"/>
     </row>
     <row r="865">
       <c r="B865" s="81"/>
       <c r="G865" s="65"/>
-      <c r="I865" s="80"/>
+      <c r="I865" s="82"/>
     </row>
     <row r="866">
       <c r="B866" s="81"/>
       <c r="G866" s="65"/>
-      <c r="I866" s="80"/>
+      <c r="I866" s="82"/>
     </row>
     <row r="867">
       <c r="B867" s="81"/>
       <c r="G867" s="65"/>
-      <c r="I867" s="80"/>
+      <c r="I867" s="82"/>
     </row>
     <row r="868">
       <c r="B868" s="81"/>
       <c r="G868" s="65"/>
-      <c r="I868" s="80"/>
+      <c r="I868" s="82"/>
     </row>
     <row r="869">
       <c r="B869" s="81"/>
       <c r="G869" s="65"/>
-      <c r="I869" s="80"/>
+      <c r="I869" s="82"/>
     </row>
     <row r="870">
       <c r="B870" s="81"/>
       <c r="G870" s="65"/>
-      <c r="I870" s="80"/>
+      <c r="I870" s="82"/>
     </row>
     <row r="871">
       <c r="B871" s="81"/>
       <c r="G871" s="65"/>
-      <c r="I871" s="80"/>
+      <c r="I871" s="82"/>
     </row>
     <row r="872">
       <c r="B872" s="81"/>
       <c r="G872" s="65"/>
-      <c r="I872" s="80"/>
+      <c r="I872" s="82"/>
     </row>
     <row r="873">
       <c r="B873" s="81"/>
       <c r="G873" s="65"/>
-      <c r="I873" s="80"/>
+      <c r="I873" s="82"/>
     </row>
     <row r="874">
       <c r="B874" s="81"/>
       <c r="G874" s="65"/>
-      <c r="I874" s="80"/>
+      <c r="I874" s="82"/>
     </row>
     <row r="875">
       <c r="B875" s="81"/>
       <c r="G875" s="65"/>
-      <c r="I875" s="80"/>
+      <c r="I875" s="82"/>
     </row>
     <row r="876">
       <c r="B876" s="81"/>
       <c r="G876" s="65"/>
-      <c r="I876" s="80"/>
+      <c r="I876" s="82"/>
     </row>
     <row r="877">
       <c r="B877" s="81"/>
       <c r="G877" s="65"/>
-      <c r="I877" s="80"/>
+      <c r="I877" s="82"/>
     </row>
     <row r="878">
       <c r="B878" s="81"/>
       <c r="G878" s="65"/>
-      <c r="I878" s="80"/>
+      <c r="I878" s="82"/>
     </row>
     <row r="879">
       <c r="B879" s="81"/>
       <c r="G879" s="65"/>
-      <c r="I879" s="80"/>
+      <c r="I879" s="82"/>
     </row>
     <row r="880">
       <c r="B880" s="81"/>
       <c r="G880" s="65"/>
-      <c r="I880" s="80"/>
+      <c r="I880" s="82"/>
     </row>
     <row r="881">
       <c r="B881" s="81"/>
       <c r="G881" s="65"/>
-      <c r="I881" s="80"/>
+      <c r="I881" s="82"/>
     </row>
     <row r="882">
       <c r="B882" s="81"/>
       <c r="G882" s="65"/>
-      <c r="I882" s="80"/>
+      <c r="I882" s="82"/>
     </row>
     <row r="883">
       <c r="B883" s="81"/>
       <c r="G883" s="65"/>
-      <c r="I883" s="80"/>
+      <c r="I883" s="82"/>
     </row>
     <row r="884">
       <c r="B884" s="81"/>
       <c r="G884" s="65"/>
-      <c r="I884" s="80"/>
+      <c r="I884" s="82"/>
     </row>
     <row r="885">
       <c r="B885" s="81"/>
       <c r="G885" s="65"/>
-      <c r="I885" s="80"/>
+      <c r="I885" s="82"/>
     </row>
     <row r="886">
       <c r="B886" s="81"/>
       <c r="G886" s="65"/>
-      <c r="I886" s="80"/>
+      <c r="I886" s="82"/>
     </row>
     <row r="887">
       <c r="B887" s="81"/>
       <c r="G887" s="65"/>
-      <c r="I887" s="80"/>
+      <c r="I887" s="82"/>
     </row>
     <row r="888">
       <c r="B888" s="81"/>
       <c r="G888" s="65"/>
-      <c r="I888" s="80"/>
+      <c r="I888" s="82"/>
     </row>
     <row r="889">
       <c r="B889" s="81"/>
       <c r="G889" s="65"/>
-      <c r="I889" s="80"/>
+      <c r="I889" s="82"/>
     </row>
     <row r="890">
       <c r="B890" s="81"/>
       <c r="G890" s="65"/>
-      <c r="I890" s="80"/>
+      <c r="I890" s="82"/>
     </row>
     <row r="891">
       <c r="B891" s="81"/>
       <c r="G891" s="65"/>
-      <c r="I891" s="80"/>
+      <c r="I891" s="82"/>
     </row>
     <row r="892">
       <c r="B892" s="81"/>
       <c r="G892" s="65"/>
-      <c r="I892" s="80"/>
+      <c r="I892" s="82"/>
     </row>
     <row r="893">
       <c r="B893" s="81"/>
       <c r="G893" s="65"/>
-      <c r="I893" s="80"/>
+      <c r="I893" s="82"/>
     </row>
     <row r="894">
       <c r="B894" s="81"/>
       <c r="G894" s="65"/>
-      <c r="I894" s="80"/>
+      <c r="I894" s="82"/>
     </row>
     <row r="895">
       <c r="B895" s="81"/>
       <c r="G895" s="65"/>
-      <c r="I895" s="80"/>
+      <c r="I895" s="82"/>
     </row>
     <row r="896">
       <c r="B896" s="81"/>
       <c r="G896" s="65"/>
-      <c r="I896" s="80"/>
+      <c r="I896" s="82"/>
     </row>
     <row r="897">
       <c r="B897" s="81"/>
       <c r="G897" s="65"/>
-      <c r="I897" s="80"/>
+      <c r="I897" s="82"/>
     </row>
     <row r="898">
       <c r="B898" s="81"/>
       <c r="G898" s="65"/>
-      <c r="I898" s="80"/>
+      <c r="I898" s="82"/>
     </row>
     <row r="899">
       <c r="B899" s="81"/>
       <c r="G899" s="65"/>
-      <c r="I899" s="80"/>
+      <c r="I899" s="82"/>
     </row>
     <row r="900">
       <c r="B900" s="81"/>
       <c r="G900" s="65"/>
-      <c r="I900" s="80"/>
+      <c r="I900" s="82"/>
     </row>
     <row r="901">
       <c r="B901" s="81"/>
       <c r="G901" s="65"/>
-      <c r="I901" s="80"/>
+      <c r="I901" s="82"/>
     </row>
     <row r="902">
       <c r="B902" s="81"/>
       <c r="G902" s="65"/>
-      <c r="I902" s="80"/>
+      <c r="I902" s="82"/>
     </row>
     <row r="903">
       <c r="B903" s="81"/>
       <c r="G903" s="65"/>
-      <c r="I903" s="80"/>
+      <c r="I903" s="82"/>
     </row>
     <row r="904">
       <c r="B904" s="81"/>
       <c r="G904" s="65"/>
-      <c r="I904" s="80"/>
+      <c r="I904" s="82"/>
     </row>
     <row r="905">
       <c r="B905" s="81"/>
       <c r="G905" s="65"/>
-      <c r="I905" s="80"/>
+      <c r="I905" s="82"/>
     </row>
     <row r="906">
       <c r="B906" s="81"/>
       <c r="G906" s="65"/>
-      <c r="I906" s="80"/>
+      <c r="I906" s="82"/>
     </row>
     <row r="907">
       <c r="B907" s="81"/>
       <c r="G907" s="65"/>
-      <c r="I907" s="80"/>
+      <c r="I907" s="82"/>
     </row>
     <row r="908">
       <c r="B908" s="81"/>
       <c r="G908" s="65"/>
-      <c r="I908" s="80"/>
+      <c r="I908" s="82"/>
     </row>
     <row r="909">
       <c r="B909" s="81"/>
       <c r="G909" s="65"/>
-      <c r="I909" s="80"/>
+      <c r="I909" s="82"/>
     </row>
     <row r="910">
       <c r="B910" s="81"/>
       <c r="G910" s="65"/>
-      <c r="I910" s="80"/>
+      <c r="I910" s="82"/>
     </row>
     <row r="911">
       <c r="B911" s="81"/>
       <c r="G911" s="65"/>
-      <c r="I911" s="80"/>
+      <c r="I911" s="82"/>
     </row>
     <row r="912">
       <c r="B912" s="81"/>
       <c r="G912" s="65"/>
-      <c r="I912" s="80"/>
+      <c r="I912" s="82"/>
     </row>
     <row r="913">
       <c r="B913" s="81"/>
       <c r="G913" s="65"/>
-      <c r="I913" s="80"/>
+      <c r="I913" s="82"/>
     </row>
     <row r="914">
       <c r="B914" s="81"/>
       <c r="G914" s="65"/>
-      <c r="I914" s="80"/>
+      <c r="I914" s="82"/>
     </row>
     <row r="915">
       <c r="B915" s="81"/>
       <c r="G915" s="65"/>
-      <c r="I915" s="80"/>
+      <c r="I915" s="82"/>
     </row>
     <row r="916">
       <c r="B916" s="81"/>
       <c r="G916" s="65"/>
-      <c r="I916" s="80"/>
+      <c r="I916" s="82"/>
     </row>
     <row r="917">
       <c r="B917" s="81"/>
       <c r="G917" s="65"/>
-      <c r="I917" s="80"/>
+      <c r="I917" s="82"/>
     </row>
     <row r="918">
       <c r="B918" s="81"/>
       <c r="G918" s="65"/>
-      <c r="I918" s="80"/>
+      <c r="I918" s="82"/>
     </row>
     <row r="919">
       <c r="B919" s="81"/>
       <c r="G919" s="65"/>
-      <c r="I919" s="80"/>
+      <c r="I919" s="82"/>
     </row>
     <row r="920">
       <c r="B920" s="81"/>
       <c r="G920" s="65"/>
-      <c r="I920" s="80"/>
+      <c r="I920" s="82"/>
     </row>
     <row r="921">
       <c r="B921" s="81"/>
       <c r="G921" s="65"/>
-      <c r="I921" s="80"/>
+      <c r="I921" s="82"/>
     </row>
     <row r="922">
       <c r="B922" s="81"/>
       <c r="G922" s="65"/>
-      <c r="I922" s="80"/>
+      <c r="I922" s="82"/>
     </row>
     <row r="923">
       <c r="B923" s="81"/>
       <c r="G923" s="65"/>
-      <c r="I923" s="80"/>
+      <c r="I923" s="82"/>
     </row>
     <row r="924">
       <c r="B924" s="81"/>
       <c r="G924" s="65"/>
-      <c r="I924" s="80"/>
+      <c r="I924" s="82"/>
     </row>
     <row r="925">
       <c r="B925" s="81"/>
       <c r="G925" s="65"/>
-      <c r="I925" s="80"/>
+      <c r="I925" s="82"/>
     </row>
     <row r="926">
       <c r="B926" s="81"/>
       <c r="G926" s="65"/>
-      <c r="I926" s="80"/>
+      <c r="I926" s="82"/>
     </row>
     <row r="927">
       <c r="B927" s="81"/>
       <c r="G927" s="65"/>
-      <c r="I927" s="80"/>
+      <c r="I927" s="82"/>
     </row>
     <row r="928">
       <c r="B928" s="81"/>
       <c r="G928" s="65"/>
-      <c r="I928" s="80"/>
+      <c r="I928" s="82"/>
     </row>
     <row r="929">
       <c r="B929" s="81"/>
       <c r="G929" s="65"/>
-      <c r="I929" s="80"/>
+      <c r="I929" s="82"/>
     </row>
     <row r="930">
       <c r="B930" s="81"/>
       <c r="G930" s="65"/>
-      <c r="I930" s="80"/>
+      <c r="I930" s="82"/>
     </row>
     <row r="931">
       <c r="B931" s="81"/>
       <c r="G931" s="65"/>
-      <c r="I931" s="80"/>
+      <c r="I931" s="82"/>
     </row>
     <row r="932">
       <c r="B932" s="81"/>
       <c r="G932" s="65"/>
-      <c r="I932" s="80"/>
+      <c r="I932" s="82"/>
     </row>
     <row r="933">
       <c r="B933" s="81"/>
       <c r="G933" s="65"/>
-      <c r="I933" s="80"/>
+      <c r="I933" s="82"/>
     </row>
     <row r="934">
       <c r="B934" s="81"/>
       <c r="G934" s="65"/>
-      <c r="I934" s="80"/>
+      <c r="I934" s="82"/>
     </row>
     <row r="935">
       <c r="B935" s="81"/>
       <c r="G935" s="65"/>
-      <c r="I935" s="80"/>
+      <c r="I935" s="82"/>
     </row>
     <row r="936">
       <c r="B936" s="81"/>
       <c r="G936" s="65"/>
-      <c r="I936" s="80"/>
+      <c r="I936" s="82"/>
     </row>
     <row r="937">
       <c r="B937" s="81"/>
       <c r="G937" s="65"/>
-      <c r="I937" s="80"/>
+      <c r="I937" s="82"/>
     </row>
     <row r="938">
       <c r="B938" s="81"/>
       <c r="G938" s="65"/>
-      <c r="I938" s="80"/>
+      <c r="I938" s="82"/>
     </row>
     <row r="939">
       <c r="B939" s="81"/>
       <c r="G939" s="65"/>
-      <c r="I939" s="80"/>
+      <c r="I939" s="82"/>
     </row>
     <row r="940">
       <c r="B940" s="81"/>
       <c r="G940" s="65"/>
-      <c r="I940" s="80"/>
+      <c r="I940" s="82"/>
     </row>
     <row r="941">
       <c r="B941" s="81"/>
       <c r="G941" s="65"/>
-      <c r="I941" s="80"/>
+      <c r="I941" s="82"/>
     </row>
     <row r="942">
       <c r="B942" s="81"/>
       <c r="G942" s="65"/>
-      <c r="I942" s="80"/>
+      <c r="I942" s="82"/>
     </row>
     <row r="943">
       <c r="B943" s="81"/>
       <c r="G943" s="65"/>
-      <c r="I943" s="80"/>
+      <c r="I943" s="82"/>
     </row>
     <row r="944">
       <c r="B944" s="81"/>
       <c r="G944" s="65"/>
-      <c r="I944" s="80"/>
+      <c r="I944" s="82"/>
     </row>
     <row r="945">
       <c r="B945" s="81"/>
       <c r="G945" s="65"/>
-      <c r="I945" s="80"/>
+      <c r="I945" s="82"/>
     </row>
     <row r="946">
       <c r="B946" s="81"/>
       <c r="G946" s="65"/>
-      <c r="I946" s="80"/>
+      <c r="I946" s="82"/>
     </row>
     <row r="947">
       <c r="B947" s="81"/>
       <c r="G947" s="65"/>
-      <c r="I947" s="80"/>
+      <c r="I947" s="82"/>
     </row>
     <row r="948">
       <c r="B948" s="81"/>
       <c r="G948" s="65"/>
-      <c r="I948" s="80"/>
+      <c r="I948" s="82"/>
     </row>
     <row r="949">
       <c r="B949" s="81"/>
       <c r="G949" s="65"/>
-      <c r="I949" s="80"/>
+      <c r="I949" s="82"/>
     </row>
     <row r="950">
       <c r="B950" s="81"/>
       <c r="G950" s="65"/>
-      <c r="I950" s="80"/>
+      <c r="I950" s="82"/>
     </row>
     <row r="951">
       <c r="B951" s="81"/>
       <c r="G951" s="65"/>
-      <c r="I951" s="80"/>
+      <c r="I951" s="82"/>
     </row>
     <row r="952">
       <c r="B952" s="81"/>
       <c r="G952" s="65"/>
-      <c r="I952" s="80"/>
+      <c r="I952" s="82"/>
     </row>
     <row r="953">
       <c r="B953" s="81"/>
       <c r="G953" s="65"/>
-      <c r="I953" s="80"/>
+      <c r="I953" s="82"/>
     </row>
     <row r="954">
       <c r="B954" s="81"/>
       <c r="G954" s="65"/>
-      <c r="I954" s="80"/>
+      <c r="I954" s="82"/>
     </row>
     <row r="955">
       <c r="B955" s="81"/>
       <c r="G955" s="65"/>
-      <c r="I955" s="80"/>
+      <c r="I955" s="82"/>
     </row>
     <row r="956">
       <c r="B956" s="81"/>
       <c r="G956" s="65"/>
-      <c r="I956" s="80"/>
+      <c r="I956" s="82"/>
     </row>
     <row r="957">
       <c r="B957" s="81"/>
       <c r="G957" s="65"/>
-      <c r="I957" s="80"/>
+      <c r="I957" s="82"/>
     </row>
     <row r="958">
       <c r="B958" s="81"/>
       <c r="G958" s="65"/>
-      <c r="I958" s="80"/>
+      <c r="I958" s="82"/>
     </row>
     <row r="959">
       <c r="B959" s="81"/>
       <c r="G959" s="65"/>
-      <c r="I959" s="80"/>
+      <c r="I959" s="82"/>
     </row>
     <row r="960">
       <c r="B960" s="81"/>
       <c r="G960" s="65"/>
-      <c r="I960" s="80"/>
+      <c r="I960" s="82"/>
     </row>
     <row r="961">
       <c r="B961" s="81"/>
       <c r="G961" s="65"/>
-      <c r="I961" s="80"/>
+      <c r="I961" s="82"/>
     </row>
     <row r="962">
       <c r="B962" s="81"/>
       <c r="G962" s="65"/>
-      <c r="I962" s="80"/>
+      <c r="I962" s="82"/>
     </row>
     <row r="963">
       <c r="B963" s="81"/>
       <c r="G963" s="65"/>
-      <c r="I963" s="80"/>
+      <c r="I963" s="82"/>
     </row>
     <row r="964">
       <c r="B964" s="81"/>
       <c r="G964" s="65"/>
-      <c r="I964" s="80"/>
+      <c r="I964" s="82"/>
     </row>
     <row r="965">
       <c r="B965" s="81"/>
       <c r="G965" s="65"/>
-      <c r="I965" s="80"/>
+      <c r="I965" s="82"/>
     </row>
     <row r="966">
       <c r="B966" s="81"/>
       <c r="G966" s="65"/>
-      <c r="I966" s="80"/>
+      <c r="I966" s="82"/>
     </row>
     <row r="967">
       <c r="B967" s="81"/>
       <c r="G967" s="65"/>
-      <c r="I967" s="80"/>
+      <c r="I967" s="82"/>
     </row>
     <row r="968">
       <c r="B968" s="81"/>
       <c r="G968" s="65"/>
-      <c r="I968" s="80"/>
+      <c r="I968" s="82"/>
     </row>
     <row r="969">
       <c r="B969" s="81"/>
       <c r="G969" s="65"/>
-      <c r="I969" s="80"/>
+      <c r="I969" s="82"/>
     </row>
     <row r="970">
       <c r="B970" s="81"/>
       <c r="G970" s="65"/>
-      <c r="I970" s="80"/>
+      <c r="I970" s="82"/>
     </row>
     <row r="971">
       <c r="B971" s="81"/>
       <c r="G971" s="65"/>
-      <c r="I971" s="80"/>
+      <c r="I971" s="82"/>
     </row>
     <row r="972">
       <c r="B972" s="81"/>
       <c r="G972" s="65"/>
-      <c r="I972" s="80"/>
+      <c r="I972" s="82"/>
     </row>
     <row r="973">
       <c r="B973" s="81"/>
       <c r="G973" s="65"/>
-      <c r="I973" s="80"/>
+      <c r="I973" s="82"/>
     </row>
     <row r="974">
       <c r="B974" s="81"/>
       <c r="G974" s="65"/>
-      <c r="I974" s="80"/>
+      <c r="I974" s="82"/>
     </row>
     <row r="975">
       <c r="B975" s="81"/>
       <c r="G975" s="65"/>
-      <c r="I975" s="80"/>
+      <c r="I975" s="82"/>
     </row>
     <row r="976">
       <c r="B976" s="81"/>
       <c r="G976" s="65"/>
-      <c r="I976" s="80"/>
+      <c r="I976" s="82"/>
     </row>
     <row r="977">
       <c r="B977" s="81"/>
       <c r="G977" s="65"/>
-      <c r="I977" s="80"/>
+      <c r="I977" s="82"/>
     </row>
     <row r="978">
       <c r="B978" s="81"/>
       <c r="G978" s="65"/>
-      <c r="I978" s="80"/>
+      <c r="I978" s="82"/>
     </row>
     <row r="979">
       <c r="B979" s="81"/>
       <c r="G979" s="65"/>
-      <c r="I979" s="80"/>
+      <c r="I979" s="82"/>
     </row>
     <row r="980">
       <c r="B980" s="81"/>
       <c r="G980" s="65"/>
-      <c r="I980" s="80"/>
+      <c r="I980" s="82"/>
     </row>
     <row r="981">
       <c r="B981" s="81"/>
       <c r="G981" s="65"/>
-      <c r="I981" s="80"/>
+      <c r="I981" s="82"/>
     </row>
     <row r="982">
       <c r="B982" s="81"/>
       <c r="G982" s="65"/>
-      <c r="I982" s="80"/>
+      <c r="I982" s="82"/>
     </row>
     <row r="983">
       <c r="B983" s="81"/>
       <c r="G983" s="65"/>
-      <c r="I983" s="80"/>
+      <c r="I983" s="82"/>
     </row>
     <row r="984">
       <c r="B984" s="81"/>
       <c r="G984" s="65"/>
-      <c r="I984" s="80"/>
+      <c r="I984" s="82"/>
     </row>
     <row r="985">
       <c r="B985" s="81"/>
       <c r="G985" s="65"/>
-      <c r="I985" s="80"/>
+      <c r="I985" s="82"/>
     </row>
     <row r="986">
       <c r="B986" s="81"/>
       <c r="G986" s="65"/>
-      <c r="I986" s="80"/>
+      <c r="I986" s="82"/>
     </row>
     <row r="987">
       <c r="B987" s="81"/>
       <c r="G987" s="65"/>
-      <c r="I987" s="80"/>
+      <c r="I987" s="82"/>
     </row>
     <row r="988">
       <c r="B988" s="81"/>
       <c r="G988" s="65"/>
-      <c r="I988" s="80"/>
+      <c r="I988" s="82"/>
     </row>
     <row r="989">
       <c r="B989" s="81"/>
       <c r="G989" s="65"/>
-      <c r="I989" s="80"/>
+      <c r="I989" s="82"/>
     </row>
     <row r="990">
       <c r="B990" s="81"/>
       <c r="G990" s="65"/>
-      <c r="I990" s="80"/>
+      <c r="I990" s="82"/>
     </row>
     <row r="991">
       <c r="B991" s="81"/>
       <c r="G991" s="65"/>
-      <c r="I991" s="80"/>
+      <c r="I991" s="82"/>
     </row>
     <row r="992">
       <c r="B992" s="81"/>
       <c r="G992" s="65"/>
-      <c r="I992" s="80"/>
+      <c r="I992" s="82"/>
     </row>
     <row r="993">
       <c r="B993" s="81"/>
       <c r="G993" s="65"/>
-      <c r="I993" s="80"/>
+      <c r="I993" s="82"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$AY$84"/>
+  <autoFilter ref="$A$1:$AY$85"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1909,11 +1909,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="654162920"/>
-        <c:axId val="1924792521"/>
+        <c:axId val="1865816637"/>
+        <c:axId val="325567113"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="654162920"/>
+        <c:axId val="1865816637"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1965,10 +1965,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1924792521"/>
+        <c:crossAx val="325567113"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1924792521"/>
+        <c:axId val="325567113"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2032,7 +2032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="654162920"/>
+        <c:crossAx val="1865816637"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1909,11 +1909,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1865816637"/>
-        <c:axId val="325567113"/>
+        <c:axId val="1254273233"/>
+        <c:axId val="2116146626"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1865816637"/>
+        <c:axId val="1254273233"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1965,10 +1965,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="325567113"/>
+        <c:crossAx val="2116146626"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="325567113"/>
+        <c:axId val="2116146626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2032,7 +2032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1865816637"/>
+        <c:crossAx val="1254273233"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -9,7 +9,7 @@
     <sheet state="visible" name="Carteira" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$225</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$226</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Inventário de Lotes'!$A$1:$E$45</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Resumo Mensal'!$A$3:$G$123</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$85</definedName>
@@ -20,14 +20,14 @@
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="pJRHvcXxvrt2iyftP589alz4iTYJ/TjvnqN2pkLwSTU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="YykOvY0Bmv9mpsg5RxHSAPHLZ3zOFxgZyJrEMKXXMP4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="444">
   <si>
     <t>Data</t>
   </si>
@@ -1909,11 +1909,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1169612973"/>
-        <c:axId val="1320945558"/>
+        <c:axId val="1232310031"/>
+        <c:axId val="1471548968"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1169612973"/>
+        <c:axId val="1232310031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1965,10 +1965,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1320945558"/>
+        <c:crossAx val="1471548968"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1320945558"/>
+        <c:axId val="1471548968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2032,7 +2032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1169612973"/>
+        <c:crossAx val="1232310031"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2171,7 +2171,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:E1014" sheet="Todos os Gastos"/>
+    <worksheetSource ref="C1:E1015" sheet="Todos os Gastos"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="Valor" numFmtId="2">
@@ -4340,8 +4340,8 @@
       <c r="H80" s="28"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="23">
-        <v>46150.0</v>
+      <c r="A81" s="25">
+        <v>46149.0</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>52</v>
@@ -4353,40 +4353,40 @@
       <c r="H81" s="28"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="23">
-        <v>46150.0</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C82" s="9">
-        <v>65.0</v>
+      <c r="A82" s="25">
+        <v>46149.0</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C82" s="19">
+        <v>120.0</v>
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="28"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="23">
-        <v>46153.0</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C83" s="19">
-        <v>98.88</v>
+        <v>46150.0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="9">
+        <v>65.0</v>
       </c>
       <c r="G83" s="9"/>
       <c r="H83" s="28"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="23">
-        <v>46154.0</v>
+        <v>46153.0</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C84" s="19">
-        <v>980.86</v>
+        <v>98.88</v>
       </c>
       <c r="G84" s="9"/>
       <c r="H84" s="28"/>
@@ -4396,10 +4396,10 @@
         <v>46154.0</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C85" s="3">
-        <v>2831.4</v>
+        <v>25</v>
+      </c>
+      <c r="C85" s="19">
+        <v>980.86</v>
       </c>
       <c r="G85" s="9"/>
       <c r="H85" s="28"/>
@@ -4409,36 +4409,36 @@
         <v>46154.0</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C86" s="9">
-        <v>50.0</v>
+        <v>33</v>
+      </c>
+      <c r="C86" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G86" s="9"/>
       <c r="H86" s="28"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="23">
-        <v>46157.0</v>
+        <v>46154.0</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C87" s="9">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="G87" s="9"/>
       <c r="H87" s="28"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="23">
-        <v>46162.0</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" s="19">
-        <v>5372.0</v>
+        <v>46157.0</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="9">
+        <v>132.4</v>
       </c>
       <c r="G88" s="9"/>
       <c r="H88" s="28"/>
@@ -4447,37 +4447,37 @@
       <c r="A89" s="23">
         <v>46162.0</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C89" s="9">
-        <v>113.31</v>
+      <c r="B89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" s="19">
+        <v>5372.0</v>
       </c>
       <c r="G89" s="9"/>
       <c r="H89" s="28"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
-      <c r="A90" s="1">
-        <v>46175.0</v>
+      <c r="A90" s="23">
+        <v>46162.0</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C90" s="9">
-        <v>580.0</v>
+        <v>113.31</v>
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="28"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
-      <c r="A91" s="23">
-        <v>46178.0</v>
+      <c r="A91" s="1">
+        <v>46175.0</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C91" s="9">
-        <v>195.0</v>
+        <v>580.0</v>
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="28"/>
@@ -4487,36 +4487,36 @@
         <v>46178.0</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C92" s="9">
-        <v>950.0</v>
+        <v>195.0</v>
       </c>
       <c r="G92" s="9"/>
       <c r="H92" s="28"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="1">
-        <v>46181.0</v>
+      <c r="A93" s="23">
+        <v>46178.0</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C93" s="9">
-        <v>120.0</v>
+        <v>950.0</v>
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="28"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1">
-        <v>46183.0</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>38</v>
+        <v>46181.0</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C94" s="9">
-        <v>65.0</v>
+        <v>120.0</v>
       </c>
       <c r="G94" s="9"/>
       <c r="H94" s="28"/>
@@ -4525,11 +4525,11 @@
       <c r="A95" s="1">
         <v>46183.0</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>44</v>
+      <c r="B95" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C95" s="9">
-        <v>50.0</v>
+        <v>65.0</v>
       </c>
       <c r="G95" s="9"/>
       <c r="H95" s="28"/>
@@ -4539,36 +4539,36 @@
         <v>46183.0</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C96" s="9">
-        <v>530.0</v>
+        <v>50.0</v>
       </c>
       <c r="G96" s="9"/>
       <c r="H96" s="28"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="1">
-        <v>46184.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C97" s="9">
-        <v>95.12</v>
+        <v>530.0</v>
       </c>
       <c r="G97" s="9"/>
       <c r="H97" s="28"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c r="A98" s="23">
-        <v>46185.0</v>
+      <c r="A98" s="1">
+        <v>46184.0</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C98" s="9">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="G98" s="9"/>
       <c r="H98" s="28"/>
@@ -4578,36 +4578,36 @@
         <v>46185.0</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C99" s="3">
-        <v>2831.4</v>
+        <v>25</v>
+      </c>
+      <c r="C99" s="9">
+        <v>981.95</v>
       </c>
       <c r="G99" s="9"/>
       <c r="H99" s="28"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="23">
-        <v>46188.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C100" s="9">
-        <v>132.4</v>
+        <v>33</v>
+      </c>
+      <c r="C100" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G100" s="9"/>
       <c r="H100" s="28"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="23">
-        <v>46192.0</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>23</v>
+        <v>46188.0</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C101" s="9">
-        <v>7200.0</v>
+        <v>132.4</v>
       </c>
       <c r="G101" s="9"/>
       <c r="H101" s="28"/>
@@ -4616,37 +4616,37 @@
       <c r="A102" s="23">
         <v>46192.0</v>
       </c>
-      <c r="B102" s="8" t="s">
-        <v>40</v>
+      <c r="B102" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C102" s="9">
-        <v>113.31</v>
+        <v>7200.0</v>
       </c>
       <c r="G102" s="9"/>
       <c r="H102" s="28"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
-      <c r="A103" s="1">
-        <v>46205.0</v>
+      <c r="A103" s="23">
+        <v>46192.0</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C103" s="9">
-        <v>930.0</v>
+        <v>113.31</v>
       </c>
       <c r="G103" s="9"/>
       <c r="H103" s="28"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
-      <c r="A104" s="23">
-        <v>46209.0</v>
+      <c r="A104" s="1">
+        <v>46205.0</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C104" s="9">
-        <v>195.0</v>
+        <v>930.0</v>
       </c>
       <c r="G104" s="9"/>
       <c r="H104" s="28"/>
@@ -4656,49 +4656,49 @@
         <v>46209.0</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C105" s="9">
-        <v>950.0</v>
+        <v>195.0</v>
       </c>
       <c r="G105" s="9"/>
       <c r="H105" s="28"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="23">
-        <v>46211.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C106" s="9">
-        <v>120.0</v>
+        <v>950.0</v>
       </c>
       <c r="G106" s="9"/>
       <c r="H106" s="28"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
-      <c r="A107" s="1">
-        <v>46213.0</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>38</v>
+      <c r="A107" s="23">
+        <v>46211.0</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C107" s="9">
-        <v>65.0</v>
+        <v>120.0</v>
       </c>
       <c r="G107" s="9"/>
       <c r="H107" s="28"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="23">
-        <v>46216.0</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>25</v>
+      <c r="A108" s="1">
+        <v>46213.0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C108" s="9">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="G108" s="9"/>
       <c r="H108" s="28"/>
@@ -4708,10 +4708,10 @@
         <v>46216.0</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C109" s="9">
-        <v>95.12</v>
+        <v>981.95</v>
       </c>
       <c r="G109" s="9"/>
       <c r="H109" s="28"/>
@@ -4721,23 +4721,23 @@
         <v>46216.0</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C110" s="3">
-        <v>2831.4</v>
+        <v>43</v>
+      </c>
+      <c r="C110" s="9">
+        <v>95.12</v>
       </c>
       <c r="G110" s="9"/>
       <c r="H110" s="28"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="23">
-        <v>46218.0</v>
+        <v>46216.0</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C111" s="9">
-        <v>132.4</v>
+        <v>33</v>
+      </c>
+      <c r="C111" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G111" s="9"/>
       <c r="H111" s="28"/>
@@ -4747,23 +4747,23 @@
         <v>46218.0</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C112" s="9">
-        <v>50.0</v>
+        <v>132.4</v>
       </c>
       <c r="G112" s="9"/>
       <c r="H112" s="28"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="23">
-        <v>46223.0</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>23</v>
+        <v>46218.0</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C113" s="9">
-        <v>6800.0</v>
+        <v>50.0</v>
       </c>
       <c r="G113" s="9"/>
       <c r="H113" s="28"/>
@@ -4772,53 +4772,50 @@
       <c r="A114" s="23">
         <v>46223.0</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>40</v>
+      <c r="B114" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C114" s="9">
-        <v>113.31</v>
+        <v>6800.0</v>
       </c>
       <c r="G114" s="9"/>
       <c r="H114" s="28"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
-      <c r="A115" s="1">
-        <v>46237.0</v>
+      <c r="A115" s="23">
+        <v>46223.0</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C115" s="9">
-        <v>1500.0</v>
+        <v>113.31</v>
       </c>
       <c r="G115" s="9"/>
       <c r="H115" s="28"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="23">
-        <v>46239.0</v>
+      <c r="A116" s="1">
+        <v>46237.0</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C116" s="9">
-        <v>950.0</v>
-      </c>
-      <c r="F116" s="26"/>
-      <c r="G116" s="12"/>
-      <c r="H116" s="21"/>
-      <c r="I116" s="14"/>
-      <c r="J116" s="14"/>
+        <v>1500.0</v>
+      </c>
+      <c r="G116" s="9"/>
+      <c r="H116" s="28"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="23">
-        <v>46240.0</v>
+        <v>46239.0</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C117" s="9">
-        <v>195.0</v>
+        <v>950.0</v>
       </c>
       <c r="F117" s="26"/>
       <c r="G117" s="12"/>
@@ -4831,49 +4828,52 @@
         <v>46240.0</v>
       </c>
       <c r="B118" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C118" s="9">
+        <v>195.0</v>
+      </c>
+      <c r="F118" s="26"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="21"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="14"/>
+    </row>
+    <row r="119" ht="14.25" customHeight="1">
+      <c r="A119" s="23">
+        <v>46240.0</v>
+      </c>
+      <c r="B119" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C119" s="9">
         <v>120.0</v>
-      </c>
-      <c r="G118" s="9"/>
-      <c r="H118" s="28"/>
-    </row>
-    <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="1">
-        <v>46244.0</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C119" s="9">
-        <v>65.0</v>
       </c>
       <c r="G119" s="9"/>
       <c r="H119" s="28"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
-      <c r="A120" s="23">
-        <v>46245.0</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>43</v>
+      <c r="A120" s="1">
+        <v>46244.0</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C120" s="9">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="G120" s="9"/>
       <c r="H120" s="28"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="1">
-        <v>46246.0</v>
+      <c r="A121" s="23">
+        <v>46245.0</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C121" s="9">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="G121" s="9"/>
       <c r="H121" s="28"/>
@@ -4883,10 +4883,10 @@
         <v>46246.0</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C122" s="3">
-        <v>2831.4</v>
+        <v>25</v>
+      </c>
+      <c r="C122" s="9">
+        <v>981.95</v>
       </c>
       <c r="G122" s="9"/>
       <c r="H122" s="28"/>
@@ -4896,10 +4896,10 @@
         <v>46246.0</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C123" s="9">
-        <v>460.0</v>
+        <v>33</v>
+      </c>
+      <c r="C123" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G123" s="9"/>
       <c r="H123" s="28"/>
@@ -4909,10 +4909,10 @@
         <v>46246.0</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C124" s="9">
-        <v>50.0</v>
+        <v>460.0</v>
       </c>
       <c r="G124" s="9"/>
       <c r="H124" s="28"/>
@@ -4922,36 +4922,36 @@
         <v>46246.0</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C125" s="9">
-        <v>530.0</v>
+        <v>50.0</v>
       </c>
       <c r="G125" s="9"/>
       <c r="H125" s="28"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="23">
-        <v>46249.0</v>
+      <c r="A126" s="1">
+        <v>46246.0</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C126" s="9">
-        <v>132.4</v>
+        <v>530.0</v>
       </c>
       <c r="G126" s="9"/>
       <c r="H126" s="28"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="23">
-        <v>46254.0</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>23</v>
+        <v>46249.0</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C127" s="9">
-        <v>5800.0</v>
+        <v>132.4</v>
       </c>
       <c r="G127" s="9"/>
       <c r="H127" s="28"/>
@@ -4960,63 +4960,63 @@
       <c r="A128" s="23">
         <v>46254.0</v>
       </c>
-      <c r="B128" s="8" t="s">
-        <v>40</v>
+      <c r="B128" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C128" s="9">
-        <v>113.31</v>
+        <v>5800.0</v>
       </c>
       <c r="G128" s="9"/>
       <c r="H128" s="28"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="1">
-        <v>46267.0</v>
+      <c r="A129" s="23">
+        <v>46254.0</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C129" s="9">
-        <v>2000.0</v>
+        <v>113.31</v>
       </c>
       <c r="G129" s="9"/>
       <c r="H129" s="28"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="23">
-        <v>46269.0</v>
+      <c r="A130" s="1">
+        <v>46267.0</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C130" s="9">
-        <v>950.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G130" s="9"/>
       <c r="H130" s="28"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="23">
-        <v>46271.0</v>
+        <v>46269.0</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C131" s="9">
-        <v>195.0</v>
+        <v>950.0</v>
       </c>
       <c r="G131" s="9"/>
       <c r="H131" s="28"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="23">
-        <v>46273.0</v>
+        <v>46271.0</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C132" s="9">
-        <v>120.0</v>
+        <v>195.0</v>
       </c>
       <c r="G132" s="9"/>
       <c r="H132" s="28"/>
@@ -5026,49 +5026,49 @@
         <v>46273.0</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C133" s="9">
-        <v>90.0</v>
+        <v>120.0</v>
       </c>
       <c r="G133" s="9"/>
       <c r="H133" s="28"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="23">
-        <v>46274.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C134" s="9">
-        <v>50.0</v>
+        <v>90.0</v>
       </c>
       <c r="G134" s="9"/>
       <c r="H134" s="28"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="1">
-        <v>46275.0</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>38</v>
+      <c r="A135" s="23">
+        <v>46274.0</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C135" s="9">
-        <v>65.0</v>
+        <v>50.0</v>
       </c>
       <c r="G135" s="9"/>
       <c r="H135" s="28"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="23">
-        <v>46276.0</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>25</v>
+      <c r="A136" s="1">
+        <v>46275.0</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C136" s="9">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="G136" s="9"/>
       <c r="H136" s="28"/>
@@ -5078,10 +5078,10 @@
         <v>46276.0</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C137" s="9">
-        <v>95.12</v>
+        <v>981.95</v>
       </c>
       <c r="G137" s="9"/>
       <c r="H137" s="28"/>
@@ -5091,114 +5091,114 @@
         <v>46276.0</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C138" s="3">
-        <v>2831.4</v>
+        <v>43</v>
+      </c>
+      <c r="C138" s="9">
+        <v>95.12</v>
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="28"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="23">
-        <v>46280.0</v>
+        <v>46276.0</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C139" s="9">
-        <v>132.4</v>
+        <v>33</v>
+      </c>
+      <c r="C139" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G139" s="9"/>
       <c r="H139" s="28"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="23">
-        <v>46285.0</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>23</v>
+        <v>46280.0</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C140" s="9">
-        <v>6850.0</v>
+        <v>132.4</v>
       </c>
       <c r="G140" s="9"/>
       <c r="H140" s="28"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="23">
-        <v>46286.0</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>40</v>
+        <v>46285.0</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C141" s="9">
-        <v>113.31</v>
+        <v>6850.0</v>
       </c>
       <c r="G141" s="9"/>
       <c r="H141" s="28"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
-      <c r="A142" s="1">
-        <v>46297.0</v>
+      <c r="A142" s="23">
+        <v>46286.0</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C142" s="9">
-        <v>1800.0</v>
+        <v>113.31</v>
       </c>
       <c r="G142" s="9"/>
       <c r="H142" s="28"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="23">
-        <v>46300.0</v>
+      <c r="A143" s="1">
+        <v>46297.0</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C143" s="9">
-        <v>950.0</v>
+        <v>1800.0</v>
       </c>
       <c r="G143" s="9"/>
       <c r="H143" s="28"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="23">
-        <v>46301.0</v>
+        <v>46300.0</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C144" s="9">
-        <v>195.0</v>
+        <v>950.0</v>
       </c>
       <c r="G144" s="9"/>
       <c r="H144" s="28"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="1">
-        <v>46302.0</v>
+      <c r="A145" s="23">
+        <v>46301.0</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C145" s="9">
-        <v>530.0</v>
+        <v>195.0</v>
       </c>
       <c r="G145" s="9"/>
       <c r="H145" s="28"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="1">
-        <v>46303.0</v>
+        <v>46302.0</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C146" s="9">
-        <v>120.0</v>
+        <v>530.0</v>
       </c>
       <c r="G146" s="9"/>
       <c r="H146" s="28"/>
@@ -5208,10 +5208,10 @@
         <v>46303.0</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C147" s="9">
-        <v>90.0</v>
+        <v>120.0</v>
       </c>
       <c r="G147" s="9"/>
       <c r="H147" s="28"/>
@@ -5221,36 +5221,36 @@
         <v>46303.0</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C148" s="9">
-        <v>119.8</v>
+        <v>90.0</v>
       </c>
       <c r="G148" s="9"/>
       <c r="H148" s="28"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="1">
-        <v>46305.0</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>38</v>
+        <v>46303.0</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C149" s="9">
-        <v>65.0</v>
+        <v>119.8</v>
       </c>
       <c r="G149" s="9"/>
       <c r="H149" s="28"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="23">
-        <v>46308.0</v>
-      </c>
-      <c r="B150" s="8" t="s">
-        <v>25</v>
+      <c r="A150" s="1">
+        <v>46305.0</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C150" s="9">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="G150" s="9"/>
       <c r="H150" s="28"/>
@@ -5260,10 +5260,10 @@
         <v>46308.0</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C151" s="9">
-        <v>95.12</v>
+        <v>981.95</v>
       </c>
       <c r="G151" s="9"/>
       <c r="H151" s="28"/>
@@ -5273,10 +5273,10 @@
         <v>46308.0</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C152" s="3">
-        <v>2831.4</v>
+        <v>43</v>
+      </c>
+      <c r="C152" s="9">
+        <v>95.12</v>
       </c>
       <c r="G152" s="9"/>
       <c r="H152" s="28"/>
@@ -5286,36 +5286,36 @@
         <v>46308.0</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C153" s="9">
-        <v>50.0</v>
+        <v>33</v>
+      </c>
+      <c r="C153" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G153" s="9"/>
       <c r="H153" s="28"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="23">
-        <v>46310.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C154" s="9">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="G154" s="9"/>
       <c r="H154" s="28"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="1">
-        <v>46315.0</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>23</v>
+      <c r="A155" s="23">
+        <v>46310.0</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C155" s="9">
-        <v>6000.0</v>
+        <v>132.4</v>
       </c>
       <c r="G155" s="9"/>
       <c r="H155" s="28"/>
@@ -5324,37 +5324,37 @@
       <c r="A156" s="1">
         <v>46315.0</v>
       </c>
-      <c r="B156" s="8" t="s">
-        <v>40</v>
+      <c r="B156" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C156" s="9">
-        <v>113.31</v>
+        <v>6000.0</v>
       </c>
       <c r="G156" s="9"/>
       <c r="H156" s="28"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="1">
-        <v>46329.0</v>
+        <v>46315.0</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C157" s="9">
-        <v>2200.0</v>
+        <v>113.31</v>
       </c>
       <c r="G157" s="9"/>
       <c r="H157" s="28"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="23">
-        <v>46332.0</v>
+      <c r="A158" s="1">
+        <v>46329.0</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C158" s="9">
-        <v>195.0</v>
+        <v>2200.0</v>
       </c>
       <c r="G158" s="9"/>
       <c r="H158" s="28"/>
@@ -5364,23 +5364,23 @@
         <v>46332.0</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C159" s="9">
-        <v>950.0</v>
+        <v>195.0</v>
       </c>
       <c r="G159" s="9"/>
       <c r="H159" s="28"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="23">
-        <v>46335.0</v>
+        <v>46332.0</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C160" s="9">
-        <v>120.0</v>
+        <v>950.0</v>
       </c>
       <c r="G160" s="9"/>
       <c r="H160" s="28"/>
@@ -5390,36 +5390,36 @@
         <v>46335.0</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C161" s="9">
-        <v>90.0</v>
+        <v>120.0</v>
       </c>
       <c r="G161" s="9"/>
       <c r="H161" s="28"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="1">
-        <v>46336.0</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>38</v>
+      <c r="A162" s="23">
+        <v>46335.0</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C162" s="9">
-        <v>65.0</v>
+        <v>90.0</v>
       </c>
       <c r="G162" s="9"/>
       <c r="H162" s="28"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="23">
-        <v>46337.0</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>43</v>
+      <c r="A163" s="1">
+        <v>46336.0</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C163" s="9">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="G163" s="9"/>
       <c r="H163" s="28"/>
@@ -5429,23 +5429,23 @@
         <v>46337.0</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C164" s="9">
-        <v>50.0</v>
+        <v>95.12</v>
       </c>
       <c r="G164" s="9"/>
       <c r="H164" s="28"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="A165" s="23">
-        <v>46338.0</v>
+        <v>46337.0</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C165" s="9">
-        <v>981.95</v>
+        <v>50.0</v>
       </c>
       <c r="G165" s="9"/>
       <c r="H165" s="28"/>
@@ -5455,36 +5455,36 @@
         <v>46338.0</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C166" s="3">
-        <v>2831.4</v>
+        <v>25</v>
+      </c>
+      <c r="C166" s="9">
+        <v>981.95</v>
       </c>
       <c r="G166" s="9"/>
       <c r="H166" s="28"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="23">
-        <v>46342.0</v>
+        <v>46338.0</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C167" s="9">
-        <v>132.4</v>
+        <v>33</v>
+      </c>
+      <c r="C167" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G167" s="9"/>
       <c r="H167" s="28"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c r="A168" s="23">
-        <v>46346.0</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>23</v>
+        <v>46342.0</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C168" s="9">
-        <v>5750.0</v>
+        <v>132.4</v>
       </c>
       <c r="G168" s="9"/>
       <c r="H168" s="28"/>
@@ -5493,115 +5493,115 @@
       <c r="A169" s="23">
         <v>46346.0</v>
       </c>
-      <c r="B169" s="8" t="s">
-        <v>40</v>
+      <c r="B169" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C169" s="9">
-        <v>113.31</v>
+        <v>5750.0</v>
       </c>
       <c r="G169" s="9"/>
       <c r="H169" s="28"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="1">
-        <v>46358.0</v>
+      <c r="A170" s="23">
+        <v>46346.0</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C170" s="9">
-        <v>1880.0</v>
+        <v>113.31</v>
       </c>
       <c r="G170" s="9"/>
       <c r="H170" s="28"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c r="A171" s="1">
-        <v>46360.0</v>
+        <v>46358.0</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C171" s="9">
-        <v>950.0</v>
+        <v>1880.0</v>
       </c>
       <c r="G171" s="9"/>
       <c r="H171" s="28"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="23">
-        <v>46363.0</v>
+      <c r="A172" s="1">
+        <v>46360.0</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C172" s="9">
-        <v>195.0</v>
+        <v>950.0</v>
       </c>
       <c r="G172" s="9"/>
       <c r="H172" s="28"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="1">
-        <v>46364.0</v>
+      <c r="A173" s="23">
+        <v>46363.0</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C173" s="9">
-        <v>120.0</v>
+        <v>195.0</v>
       </c>
       <c r="G173" s="9"/>
       <c r="H173" s="28"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="23">
-        <v>46365.0</v>
+      <c r="A174" s="1">
+        <v>46364.0</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C174" s="9">
-        <v>50.0</v>
+        <v>120.0</v>
       </c>
       <c r="G174" s="9"/>
       <c r="H174" s="28"/>
     </row>
     <row r="175" ht="14.25" customHeight="1">
-      <c r="A175" s="1">
+      <c r="A175" s="23">
         <v>46365.0</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C175" s="9">
-        <v>530.0</v>
+        <v>50.0</v>
       </c>
       <c r="G175" s="9"/>
       <c r="H175" s="28"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="1">
-        <v>46366.0</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>38</v>
+        <v>46365.0</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C176" s="9">
-        <v>65.0</v>
+        <v>530.0</v>
       </c>
       <c r="G176" s="9"/>
       <c r="H176" s="28"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="A177" s="23">
-        <v>46367.0</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>25</v>
+      <c r="A177" s="1">
+        <v>46366.0</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C177" s="9">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="G177" s="9"/>
       <c r="H177" s="28"/>
@@ -5611,10 +5611,10 @@
         <v>46367.0</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C178" s="9">
-        <v>95.12</v>
+        <v>981.95</v>
       </c>
       <c r="G178" s="9"/>
       <c r="H178" s="28"/>
@@ -5624,10 +5624,10 @@
         <v>46367.0</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C179" s="3">
-        <v>2831.4</v>
+        <v>43</v>
+      </c>
+      <c r="C179" s="9">
+        <v>95.12</v>
       </c>
       <c r="G179" s="9"/>
       <c r="H179" s="28"/>
@@ -5637,75 +5637,75 @@
         <v>46367.0</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C180" s="9">
-        <v>2900.0</v>
+        <v>33</v>
+      </c>
+      <c r="C180" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G180" s="9"/>
       <c r="H180" s="28"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="23">
-        <v>46368.0</v>
+        <v>46367.0</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="C181" s="9">
-        <v>132.4</v>
+        <v>2900.0</v>
       </c>
       <c r="G181" s="9"/>
       <c r="H181" s="28"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="23">
-        <v>46376.0</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>23</v>
+        <v>46368.0</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C182" s="9">
-        <v>6250.0</v>
+        <v>132.4</v>
       </c>
       <c r="G182" s="9"/>
       <c r="H182" s="28"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="23">
-        <v>46377.0</v>
-      </c>
-      <c r="B183" s="8" t="s">
-        <v>40</v>
+        <v>46376.0</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C183" s="9">
-        <v>113.31</v>
+        <v>6250.0</v>
       </c>
       <c r="G183" s="9"/>
       <c r="H183" s="28"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="23">
-        <v>46391.0</v>
+        <v>46377.0</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C184" s="9">
-        <v>2000.0</v>
+        <v>113.31</v>
       </c>
       <c r="G184" s="9"/>
       <c r="H184" s="28"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="23">
-        <v>46393.0</v>
+        <v>46391.0</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C185" s="9">
-        <v>281.1</v>
+        <v>2000.0</v>
       </c>
       <c r="G185" s="9"/>
       <c r="H185" s="28"/>
@@ -5715,101 +5715,101 @@
         <v>46393.0</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C186" s="9">
-        <v>950.0</v>
+        <v>281.1</v>
       </c>
       <c r="G186" s="9"/>
       <c r="H186" s="28"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="23">
-        <v>46395.0</v>
+        <v>46393.0</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C187" s="9">
-        <v>120.0</v>
+        <v>950.0</v>
       </c>
       <c r="G187" s="9"/>
       <c r="H187" s="28"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="A188" s="1">
-        <v>46397.0</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>38</v>
+      <c r="A188" s="23">
+        <v>46395.0</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C188" s="9">
-        <v>65.0</v>
+        <v>120.0</v>
       </c>
       <c r="G188" s="9"/>
       <c r="H188" s="28"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="23">
-        <v>46398.0</v>
-      </c>
-      <c r="B189" s="8" t="s">
-        <v>43</v>
+      <c r="A189" s="1">
+        <v>46397.0</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C189" s="9">
-        <v>105.37</v>
+        <v>65.0</v>
       </c>
       <c r="G189" s="9"/>
       <c r="H189" s="28"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="23">
-        <v>46399.0</v>
+        <v>46398.0</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C190" s="9">
-        <v>983.13</v>
+        <v>105.37</v>
       </c>
       <c r="G190" s="9"/>
       <c r="H190" s="28"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="23">
-        <v>46400.0</v>
+        <v>46399.0</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C191" s="9">
-        <v>50.0</v>
+        <v>983.13</v>
       </c>
       <c r="G191" s="9"/>
       <c r="H191" s="28"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="23">
-        <v>46403.0</v>
+        <v>46400.0</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C192" s="9">
-        <v>135.89</v>
+        <v>50.0</v>
       </c>
       <c r="G192" s="9"/>
       <c r="H192" s="28"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c r="A193" s="23">
-        <v>46407.0</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>23</v>
+        <v>46403.0</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C193" s="9">
-        <v>7796.0</v>
+        <v>135.89</v>
       </c>
       <c r="G193" s="9"/>
       <c r="H193" s="28"/>
@@ -5818,37 +5818,37 @@
       <c r="A194" s="23">
         <v>46407.0</v>
       </c>
-      <c r="B194" s="8" t="s">
-        <v>40</v>
+      <c r="B194" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C194" s="9">
-        <v>102.36</v>
+        <v>7796.0</v>
       </c>
       <c r="G194" s="9"/>
       <c r="H194" s="28"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="23">
-        <v>46420.0</v>
+        <v>46407.0</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C195" s="9">
-        <v>1800.0</v>
+        <v>102.36</v>
       </c>
       <c r="G195" s="9"/>
       <c r="H195" s="28"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="23">
-        <v>46422.0</v>
+        <v>46420.0</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C196" s="9">
-        <v>195.05</v>
+        <v>1800.0</v>
       </c>
       <c r="G196" s="9"/>
       <c r="H196" s="28"/>
@@ -5858,51 +5858,50 @@
         <v>46422.0</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C197" s="9">
-        <v>950.0</v>
+        <v>195.05</v>
       </c>
       <c r="G197" s="9"/>
       <c r="H197" s="28"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="23">
-        <v>46426.0</v>
+        <v>46422.0</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C198" s="9">
-        <v>120.0</v>
+        <v>950.0</v>
       </c>
       <c r="G198" s="9"/>
       <c r="H198" s="28"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="1">
-        <v>46428.0</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>38</v>
+      <c r="A199" s="23">
+        <v>46426.0</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C199" s="9">
-        <v>65.0</v>
+        <v>120.0</v>
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="28"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="23">
+      <c r="A200" s="1">
         <v>46428.0</v>
       </c>
-      <c r="B200" s="8" t="s">
-        <v>44</v>
+      <c r="B200" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C200" s="9">
-        <v>50.0</v>
-      </c>
-      <c r="E200" s="2"/>
+        <v>65.0</v>
+      </c>
       <c r="G200" s="9"/>
       <c r="H200" s="28"/>
     </row>
@@ -5911,36 +5910,37 @@
         <v>46428.0</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C201" s="9">
-        <v>530.0</v>
-      </c>
+        <v>50.0</v>
+      </c>
+      <c r="E201" s="2"/>
       <c r="G201" s="9"/>
       <c r="H201" s="28"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c r="A202" s="23">
-        <v>46429.0</v>
+        <v>46428.0</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C202" s="9">
-        <v>95.12</v>
+        <v>530.0</v>
       </c>
       <c r="G202" s="9"/>
       <c r="H202" s="28"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="23">
-        <v>46430.0</v>
+        <v>46429.0</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C203" s="9">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="G203" s="9"/>
       <c r="H203" s="28"/>
@@ -5949,37 +5949,37 @@
       <c r="A204" s="23">
         <v>46430.0</v>
       </c>
-      <c r="B204" s="23" t="s">
-        <v>27</v>
+      <c r="B204" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="C204" s="9">
-        <v>1407.65</v>
+        <v>981.95</v>
       </c>
       <c r="G204" s="9"/>
       <c r="H204" s="28"/>
     </row>
     <row r="205" ht="14.25" customHeight="1">
       <c r="A205" s="23">
-        <v>46433.0</v>
-      </c>
-      <c r="B205" s="8" t="s">
-        <v>29</v>
+        <v>46430.0</v>
+      </c>
+      <c r="B205" s="23" t="s">
+        <v>27</v>
       </c>
       <c r="C205" s="9">
-        <v>132.4</v>
+        <v>1407.65</v>
       </c>
       <c r="G205" s="9"/>
       <c r="H205" s="28"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c r="A206" s="23">
-        <v>46437.0</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>23</v>
+        <v>46433.0</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C206" s="9">
-        <v>6004.07</v>
+        <v>132.4</v>
       </c>
       <c r="G206" s="9"/>
       <c r="H206" s="28"/>
@@ -5988,11 +5988,11 @@
       <c r="A207" s="23">
         <v>46437.0</v>
       </c>
-      <c r="B207" s="8" t="s">
-        <v>40</v>
+      <c r="B207" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C207" s="9">
-        <v>113.31</v>
+        <v>6004.07</v>
       </c>
       <c r="G207" s="9"/>
       <c r="H207" s="28"/>
@@ -6002,10 +6002,10 @@
         <v>46437.0</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C208" s="9">
-        <v>2831.4</v>
+        <v>113.31</v>
       </c>
       <c r="G208" s="9"/>
       <c r="H208" s="28"/>
@@ -6015,36 +6015,36 @@
         <v>46437.0</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C209" s="9">
-        <v>460.0</v>
+        <v>2831.4</v>
       </c>
       <c r="G209" s="9"/>
       <c r="H209" s="28"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="1">
-        <v>46448.0</v>
+      <c r="A210" s="23">
+        <v>46437.0</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C210" s="9">
-        <v>1771.95</v>
+        <v>460.0</v>
       </c>
       <c r="G210" s="9"/>
       <c r="H210" s="28"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
       <c r="A211" s="1">
-        <v>46451.0</v>
+        <v>46448.0</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C211" s="9">
-        <v>64.89</v>
+        <v>1771.95</v>
       </c>
       <c r="G211" s="9"/>
       <c r="H211" s="28"/>
@@ -6054,23 +6054,23 @@
         <v>46451.0</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="C212" s="9">
-        <v>141.8</v>
+        <v>64.89</v>
       </c>
       <c r="G212" s="9"/>
       <c r="H212" s="28"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c r="A213" s="1">
-        <v>46452.0</v>
+        <v>46451.0</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C213" s="9">
-        <v>136.15</v>
+        <v>141.8</v>
       </c>
       <c r="G213" s="9"/>
       <c r="H213" s="28"/>
@@ -6080,36 +6080,36 @@
         <v>46452.0</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C214" s="9">
-        <v>800.0</v>
+        <v>136.15</v>
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="28"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
       <c r="A215" s="1">
-        <v>46455.0</v>
+        <v>46452.0</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C215" s="9">
-        <v>57.89</v>
+        <v>800.0</v>
       </c>
       <c r="G215" s="9"/>
       <c r="H215" s="28"/>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c r="A216" s="1">
-        <v>46456.0</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>39</v>
+        <v>46455.0</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="C216" s="9">
-        <v>1336.73</v>
+        <v>57.89</v>
       </c>
       <c r="G216" s="9"/>
       <c r="H216" s="28"/>
@@ -6119,23 +6119,23 @@
         <v>46456.0</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C217" s="9">
-        <v>65.0</v>
+        <v>1336.73</v>
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="28"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="1">
-        <v>46457.0</v>
-      </c>
-      <c r="B218" s="8" t="s">
-        <v>43</v>
+        <v>46456.0</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C218" s="9">
-        <v>86.15</v>
+        <v>65.0</v>
       </c>
       <c r="G218" s="9"/>
       <c r="H218" s="28"/>
@@ -6145,23 +6145,23 @@
         <v>46457.0</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C219" s="9">
-        <v>50.0</v>
+        <v>86.15</v>
       </c>
       <c r="G219" s="9"/>
       <c r="H219" s="28"/>
     </row>
     <row r="220" ht="14.25" customHeight="1">
-      <c r="A220" s="23">
-        <v>46458.0</v>
+      <c r="A220" s="1">
+        <v>46457.0</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C220" s="9">
-        <v>981.22</v>
+        <v>50.0</v>
       </c>
       <c r="G220" s="9"/>
       <c r="H220" s="28"/>
@@ -6171,36 +6171,36 @@
         <v>46458.0</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C221" s="3">
-        <v>2831.4</v>
+        <v>25</v>
+      </c>
+      <c r="C221" s="9">
+        <v>981.22</v>
       </c>
       <c r="G221" s="9"/>
       <c r="H221" s="28"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="1">
-        <v>46462.0</v>
+      <c r="A222" s="23">
+        <v>46458.0</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C222" s="9">
-        <v>132.4</v>
+        <v>33</v>
+      </c>
+      <c r="C222" s="3">
+        <v>2831.4</v>
       </c>
       <c r="G222" s="9"/>
       <c r="H222" s="28"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c r="A223" s="1">
-        <v>46466.0</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>23</v>
+        <v>46462.0</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C223" s="9">
-        <v>7494.55</v>
+        <v>132.4</v>
       </c>
       <c r="G223" s="9"/>
       <c r="H223" s="28"/>
@@ -6209,32 +6209,38 @@
       <c r="A224" s="1">
         <v>46466.0</v>
       </c>
-      <c r="B224" s="8" t="s">
-        <v>40</v>
+      <c r="B224" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C224" s="9">
-        <v>87.84</v>
+        <v>7494.55</v>
       </c>
       <c r="G224" s="9"/>
       <c r="H224" s="28"/>
     </row>
     <row r="225" ht="14.25" customHeight="1">
       <c r="A225" s="1">
-        <v>46477.0</v>
+        <v>46466.0</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C225" s="9">
-        <v>35.62</v>
+        <v>87.84</v>
       </c>
       <c r="G225" s="9"/>
       <c r="H225" s="28"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="23"/>
-      <c r="B226" s="23"/>
-      <c r="C226" s="9"/>
+      <c r="A226" s="1">
+        <v>46477.0</v>
+      </c>
+      <c r="B226" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C226" s="9">
+        <v>35.62</v>
+      </c>
       <c r="G226" s="9"/>
       <c r="H226" s="28"/>
     </row>
@@ -6932,9 +6938,9 @@
       <c r="H325" s="28"/>
     </row>
     <row r="326" ht="14.25" customHeight="1">
-      <c r="A326" s="29"/>
-      <c r="B326" s="29"/>
-      <c r="C326" s="30"/>
+      <c r="A326" s="23"/>
+      <c r="B326" s="23"/>
+      <c r="C326" s="9"/>
       <c r="G326" s="9"/>
       <c r="H326" s="28"/>
     </row>
@@ -7464,7 +7470,11 @@
       <c r="H401" s="28"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c r="A402" s="23"/>
+      <c r="A402" s="29"/>
+      <c r="B402" s="29"/>
+      <c r="C402" s="30"/>
+      <c r="G402" s="9"/>
+      <c r="H402" s="28"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
       <c r="A403" s="23"/>
@@ -7535,7 +7545,9 @@
     <row r="425" ht="14.25" customHeight="1">
       <c r="A425" s="23"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1">
+      <c r="A426" s="23"/>
+    </row>
     <row r="427" ht="15.75" customHeight="1"/>
     <row r="428" ht="15.75" customHeight="1"/>
     <row r="429" ht="15.75" customHeight="1"/>
@@ -8124,14 +8136,15 @@
     <row r="1012" ht="15.75" customHeight="1"/>
     <row r="1013" ht="15.75" customHeight="1"/>
     <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$E$225">
-    <sortState ref="A1:E225">
-      <sortCondition ref="E1:E225"/>
-      <sortCondition ref="A1:A225"/>
-      <sortCondition ref="B1:B225"/>
-      <sortCondition ref="C1:C225"/>
-      <sortCondition ref="D1:D225"/>
+  <autoFilter ref="$A$1:$E$226">
+    <sortState ref="A1:E226">
+      <sortCondition ref="E1:E226"/>
+      <sortCondition ref="A1:A226"/>
+      <sortCondition ref="B1:B226"/>
+      <sortCondition ref="C1:C226"/>
+      <sortCondition ref="D1:D226"/>
     </sortState>
   </autoFilter>
   <printOptions/>
@@ -11072,7 +11085,7 @@
       </c>
       <c r="K3" s="51">
         <f>SUM(B4:B123)</f>
-        <v>220901.1</v>
+        <v>221021.1</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>126</v>
@@ -11151,7 +11164,7 @@
       </c>
       <c r="K5" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A4:A123,"&lt;&gt;")</f>
-        <v>17116.42</v>
+        <v>16996.42</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -11188,7 +11201,7 @@
       </c>
       <c r="K6" s="51">
         <f>G17</f>
-        <v>1168.97</v>
+        <v>1048.97</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -11198,7 +11211,7 @@
       </c>
       <c r="B7" s="56">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>24317.36</v>
+        <v>24437.36</v>
       </c>
       <c r="C7" s="56">
         <f>IF($A7="","",SUMIFS('Inventário de Lotes'!$D:$D,'Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11206,11 +11219,11 @@
       </c>
       <c r="D7" s="56">
         <f t="shared" si="1"/>
-        <v>2233.3</v>
+        <v>2113.3</v>
       </c>
       <c r="E7" s="57">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="57">
         <f>IF($A7="","",COUNTIFS('Inventário de Lotes'!$B:$B,"&gt;="&amp;$A7,'Inventário de Lotes'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -11218,14 +11231,14 @@
       </c>
       <c r="G7" s="56">
         <f t="shared" si="2"/>
-        <v>17116.42</v>
+        <v>16996.42</v>
       </c>
       <c r="J7" s="50" t="s">
         <v>130</v>
       </c>
       <c r="K7" s="51">
         <f>SUMIFS(D4:D123,A4:A123,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A4:A123,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>2233.3</v>
+        <v>2113.3</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -11255,14 +11268,14 @@
       </c>
       <c r="G8" s="53">
         <f t="shared" si="2"/>
-        <v>17752.24</v>
+        <v>17632.24</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>131</v>
       </c>
       <c r="K8" s="51">
         <f>AVERAGEIF(D4:D123,"&lt;&gt;",D4:D123)</f>
-        <v>83.49785714</v>
+        <v>74.92642857</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -11292,14 +11305,14 @@
       </c>
       <c r="G9" s="56">
         <f t="shared" si="2"/>
-        <v>17168.06</v>
+        <v>17048.06</v>
       </c>
       <c r="J9" s="50" t="s">
         <v>132</v>
       </c>
       <c r="K9" s="51">
         <f>MAX(B4:B123)</f>
-        <v>24317.36</v>
+        <v>24437.36</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -11329,7 +11342,7 @@
       </c>
       <c r="G10" s="53">
         <f t="shared" si="2"/>
-        <v>16023.88</v>
+        <v>15903.88</v>
       </c>
       <c r="J10" s="50" t="s">
         <v>133</v>
@@ -11366,7 +11379,7 @@
       </c>
       <c r="G11" s="56">
         <f t="shared" si="2"/>
-        <v>14229.7</v>
+        <v>14109.7</v>
       </c>
       <c r="J11" s="50" t="s">
         <v>134</v>
@@ -11403,7 +11416,7 @@
       </c>
       <c r="G12" s="53">
         <f t="shared" si="2"/>
-        <v>12835.72</v>
+        <v>12715.72</v>
       </c>
       <c r="J12" s="50" t="s">
         <v>135</v>
@@ -11440,7 +11453,7 @@
       </c>
       <c r="G13" s="56">
         <f t="shared" si="2"/>
-        <v>11941.54</v>
+        <v>11821.54</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -11470,7 +11483,7 @@
       </c>
       <c r="G14" s="53">
         <f t="shared" si="2"/>
-        <v>7527.36</v>
+        <v>7407.36</v>
       </c>
       <c r="J14" s="59"/>
     </row>
@@ -11501,7 +11514,7 @@
       </c>
       <c r="G15" s="56">
         <f t="shared" si="2"/>
-        <v>7618.51</v>
+        <v>7498.51</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -11531,7 +11544,7 @@
       </c>
       <c r="G16" s="53">
         <f t="shared" si="2"/>
-        <v>4562.56</v>
+        <v>4442.56</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -11561,7 +11574,7 @@
       </c>
       <c r="G17" s="56">
         <f t="shared" si="2"/>
-        <v>1168.97</v>
+        <v>1048.97</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1909,11 +1909,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1232310031"/>
-        <c:axId val="1471548968"/>
+        <c:axId val="1192132915"/>
+        <c:axId val="649867445"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1232310031"/>
+        <c:axId val="1192132915"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1965,10 +1965,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1471548968"/>
+        <c:crossAx val="649867445"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1471548968"/>
+        <c:axId val="649867445"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2032,7 +2032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1232310031"/>
+        <c:crossAx val="1192132915"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1909,11 +1909,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1192132915"/>
-        <c:axId val="649867445"/>
+        <c:axId val="1398081001"/>
+        <c:axId val="353693013"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1192132915"/>
+        <c:axId val="1398081001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1965,10 +1965,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="649867445"/>
+        <c:crossAx val="353693013"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="649867445"/>
+        <c:axId val="353693013"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2032,7 +2032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1192132915"/>
+        <c:crossAx val="1398081001"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -4353,8 +4353,8 @@
       <c r="H81" s="28"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="25">
-        <v>46149.0</v>
+      <c r="A82" s="23">
+        <v>46150.0</v>
       </c>
       <c r="B82" s="27" t="s">
         <v>58</v>
@@ -8547,7 +8547,7 @@
         <v>93</v>
       </c>
       <c r="B23" s="25">
-        <v>46149.0</v>
+        <v>46150.0</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="19">
@@ -8560,7 +8560,7 @@
         <v>94</v>
       </c>
       <c r="B24" s="25">
-        <v>46149.0</v>
+        <v>46150.0</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9">

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1930,11 +1930,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1333615379"/>
-        <c:axId val="1332790156"/>
+        <c:axId val="1432652848"/>
+        <c:axId val="564721803"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1333615379"/>
+        <c:axId val="1432652848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1986,10 +1986,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1332790156"/>
+        <c:crossAx val="564721803"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1332790156"/>
+        <c:axId val="564721803"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2053,7 +2053,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1333615379"/>
+        <c:crossAx val="1432652848"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -231,10 +231,10 @@
     <t>IPVA</t>
   </si>
   <si>
-    <t>Escola</t>
+    <t>Material</t>
   </si>
   <si>
-    <t>Material</t>
+    <t>Escola</t>
   </si>
   <si>
     <t>Entrada Hotel</t>
@@ -1866,11 +1866,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1195912601"/>
-        <c:axId val="776587605"/>
+        <c:axId val="656741925"/>
+        <c:axId val="1817834988"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1195912601"/>
+        <c:axId val="656741925"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1922,10 +1922,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="776587605"/>
+        <c:crossAx val="1817834988"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="776587605"/>
+        <c:axId val="1817834988"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1989,7 +1989,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1195912601"/>
+        <c:crossAx val="656741925"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2168,8 +2168,8 @@
         <n v="981.95"/>
         <n v="1407.63"/>
         <n v="131.4"/>
+        <n v="460.0"/>
         <n v="2831.4"/>
-        <n v="460.0"/>
         <n v="74.18"/>
         <n v="1771.95"/>
         <n v="64.89"/>
@@ -2184,9 +2184,9 @@
         <n v="57.89"/>
         <n v="1336.73"/>
         <n v="86.15"/>
+        <n v="1368.12"/>
         <n v="473.73"/>
         <n v="508.07"/>
-        <n v="1368.12"/>
         <n v="660.99"/>
         <n v="807.2"/>
         <n v="132.4"/>
@@ -2203,21 +2203,21 @@
         <n v="52.0"/>
         <n v="120.0"/>
         <n v="182.8"/>
+        <n v="70.0"/>
         <n v="65.6"/>
-        <n v="70.0"/>
         <n v="434.75"/>
         <n v="981.22"/>
         <n v="45.0"/>
         <n v="151.71"/>
         <n v="206.8"/>
+        <n v="18.75"/>
         <n v="2472.89"/>
-        <n v="18.75"/>
         <n v="2837.48"/>
         <n v="2842.53"/>
-        <n v="670.0"/>
         <n v="98.98"/>
         <n v="120.75"/>
         <n v="113.8"/>
+        <n v="670.0"/>
         <n v="400.0"/>
         <n v="3452.5"/>
         <n v="59.8"/>
@@ -12456,13 +12456,13 @@
         <v>66</v>
       </c>
       <c r="C34" s="49">
-        <v>2831.4</v>
+        <v>460.0</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>37</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F34" s="39"/>
       <c r="G34" s="40"/>
@@ -12478,13 +12478,13 @@
         <v>67</v>
       </c>
       <c r="C35" s="49">
-        <v>460.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D35" s="36" t="s">
         <v>37</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F35" s="52"/>
       <c r="G35" s="40"/>
@@ -12892,17 +12892,17 @@
       <c r="A54" s="35">
         <v>46094.0</v>
       </c>
-      <c r="B54" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="49">
-        <v>473.73</v>
+      <c r="B54" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="55">
+        <v>1368.12</v>
       </c>
       <c r="D54" s="36" t="s">
         <v>37</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F54" s="54"/>
       <c r="G54" s="40"/>
@@ -12918,13 +12918,13 @@
         <v>61</v>
       </c>
       <c r="C55" s="49">
-        <v>508.07</v>
+        <v>473.73</v>
       </c>
       <c r="D55" s="36" t="s">
         <v>37</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F55" s="54"/>
       <c r="G55" s="40"/>
@@ -12936,17 +12936,17 @@
       <c r="A56" s="35">
         <v>46094.0</v>
       </c>
-      <c r="B56" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="55">
-        <v>1368.12</v>
+      <c r="B56" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="49">
+        <v>508.07</v>
       </c>
       <c r="D56" s="36" t="s">
         <v>37</v>
       </c>
       <c r="E56" s="36" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F56" s="54"/>
       <c r="G56" s="40"/>
@@ -12959,7 +12959,7 @@
         <v>46094.0</v>
       </c>
       <c r="B57" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C57" s="55">
         <v>660.99</v>
@@ -12981,7 +12981,7 @@
         <v>46094.0</v>
       </c>
       <c r="B58" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C58" s="49">
         <v>807.2</v>
@@ -13395,17 +13395,17 @@
       <c r="A77" s="35">
         <v>46120.0</v>
       </c>
-      <c r="B77" s="44" t="s">
-        <v>44</v>
+      <c r="B77" s="43" t="s">
+        <v>84</v>
       </c>
       <c r="C77" s="49">
-        <v>65.6</v>
+        <v>70.0</v>
       </c>
       <c r="D77" s="43" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G77" s="57"/>
       <c r="H77" s="58"/>
@@ -13414,17 +13414,17 @@
       <c r="A78" s="35">
         <v>46120.0</v>
       </c>
-      <c r="B78" s="43" t="s">
-        <v>84</v>
+      <c r="B78" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="C78" s="49">
-        <v>70.0</v>
+        <v>65.6</v>
       </c>
       <c r="D78" s="43" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G78" s="57"/>
       <c r="H78" s="58"/>
@@ -13529,7 +13529,7 @@
         <v>46126.0</v>
       </c>
       <c r="B84" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C84" s="47">
         <v>151.71</v>
@@ -13548,7 +13548,7 @@
         <v>46126.0</v>
       </c>
       <c r="B85" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C85" s="47">
         <v>206.8</v>
@@ -13567,16 +13567,16 @@
         <v>46126.0</v>
       </c>
       <c r="B86" s="43" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C86" s="47">
-        <v>2472.89</v>
+        <v>18.75</v>
       </c>
       <c r="D86" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E86" s="38" t="s">
-        <v>38</v>
+      <c r="E86" s="36" t="s">
+        <v>49</v>
       </c>
       <c r="G86" s="57"/>
       <c r="H86" s="58"/>
@@ -13586,16 +13586,16 @@
         <v>46126.0</v>
       </c>
       <c r="B87" s="43" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C87" s="47">
-        <v>18.75</v>
+        <v>2472.89</v>
       </c>
       <c r="D87" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E87" s="36" t="s">
-        <v>49</v>
+      <c r="E87" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="G87" s="57"/>
       <c r="H87" s="58"/>
@@ -13661,17 +13661,17 @@
       <c r="A91" s="35">
         <v>46132.0</v>
       </c>
-      <c r="B91" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C91" s="47">
-        <v>670.0</v>
+      <c r="B91" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="49">
+        <v>98.98</v>
       </c>
       <c r="D91" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="E91" s="38" t="s">
-        <v>38</v>
+      <c r="E91" s="36" t="s">
+        <v>55</v>
       </c>
       <c r="G91" s="57"/>
       <c r="H91" s="58"/>
@@ -13680,11 +13680,11 @@
       <c r="A92" s="35">
         <v>46132.0</v>
       </c>
-      <c r="B92" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C92" s="49">
-        <v>98.98</v>
+      <c r="B92" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92" s="47">
+        <v>120.75</v>
       </c>
       <c r="D92" s="36" t="s">
         <v>37</v>
@@ -13700,10 +13700,10 @@
         <v>46132.0</v>
       </c>
       <c r="B93" s="44" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C93" s="47">
-        <v>120.75</v>
+        <v>113.8</v>
       </c>
       <c r="D93" s="36" t="s">
         <v>37</v>
@@ -13718,17 +13718,17 @@
       <c r="A94" s="35">
         <v>46132.0</v>
       </c>
-      <c r="B94" s="44" t="s">
-        <v>54</v>
+      <c r="B94" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="C94" s="47">
-        <v>113.8</v>
+        <v>670.0</v>
       </c>
       <c r="D94" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="E94" s="36" t="s">
-        <v>55</v>
+      <c r="E94" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="G94" s="57"/>
       <c r="H94" s="58"/>
@@ -13977,7 +13977,7 @@
         <v>46154.0</v>
       </c>
       <c r="B108" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C108" s="49">
         <v>2831.4</v>
@@ -14187,7 +14187,7 @@
         <v>46185.0</v>
       </c>
       <c r="B122" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C122" s="49">
         <v>2831.4</v>
@@ -14388,7 +14388,7 @@
         <v>46215.0</v>
       </c>
       <c r="B135" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C135" s="49">
         <v>2831.4</v>
@@ -14583,7 +14583,7 @@
         <v>46246.0</v>
       </c>
       <c r="B148" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C148" s="49">
         <v>2831.4</v>
@@ -14598,7 +14598,7 @@
         <v>46246.0</v>
       </c>
       <c r="B149" s="43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C149" s="49">
         <v>460.0</v>
@@ -14808,7 +14808,7 @@
         <v>46277.0</v>
       </c>
       <c r="B163" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C163" s="49">
         <v>2831.4</v>
@@ -15033,7 +15033,7 @@
         <v>46307.0</v>
       </c>
       <c r="B178" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C178" s="49">
         <v>2831.4</v>
@@ -15228,7 +15228,7 @@
         <v>46338.0</v>
       </c>
       <c r="B191" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C191" s="49">
         <v>2831.4</v>
@@ -15438,7 +15438,7 @@
         <v>46368.0</v>
       </c>
       <c r="B205" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C205" s="49">
         <v>2831.4</v>
@@ -15768,7 +15768,7 @@
         <v>46430.0</v>
       </c>
       <c r="B227" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C227" s="49">
         <v>2831.4</v>
@@ -15828,7 +15828,7 @@
         <v>46437.0</v>
       </c>
       <c r="B231" s="43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C231" s="49">
         <v>460.0</v>
@@ -15993,7 +15993,7 @@
         <v>46458.0</v>
       </c>
       <c r="B242" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C242" s="49">
         <v>2831.4</v>
@@ -16173,7 +16173,7 @@
         <v>46489.0</v>
       </c>
       <c r="B254" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C254" s="49">
         <v>2831.4</v>
@@ -19764,8 +19764,8 @@
   <autoFilter ref="$A$1:$E$268">
     <sortState ref="A1:E268">
       <sortCondition ref="A1:A268"/>
+      <sortCondition ref="E1:E268"/>
       <sortCondition ref="B1:B268"/>
-      <sortCondition ref="E1:E268"/>
       <sortCondition ref="C1:C268"/>
       <sortCondition ref="D1:D268"/>
     </sortState>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -16,7 +16,7 @@
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$268</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Switching!$A$1:$F$5</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Inventário de Lotes'!$A$1:$E$15</definedName>
-    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$85</definedName>
+    <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$86</definedName>
   </definedNames>
   <calcPr/>
   <pivotCaches>
@@ -24,14 +24,14 @@
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="/dq+AaKCwVFERRViV1QYLC9uuSgvN+v6agxIOd28Ykc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="o7dUi0byVy7D4loE0MJkRhQIMmkBH9TRIvf0TGj5bjU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="425">
   <si>
     <t>Mês</t>
   </si>
@@ -996,6 +996,9 @@
     <t>Vencimento 11/06/2026; Rendimento desde o 1º dia útil; Após o vencimento rende 100% CDI com resgate 24h; Risco baixo</t>
   </si>
   <si>
+    <t>CDB Neon Planejado 160% CDI - 60 dias</t>
+  </si>
+  <si>
     <t>CDB PagBank 104%</t>
   </si>
   <si>
@@ -1863,11 +1866,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1126542554"/>
-        <c:axId val="2063252140"/>
+        <c:axId val="1816388622"/>
+        <c:axId val="842525366"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1126542554"/>
+        <c:axId val="1816388622"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1919,10 +1922,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2063252140"/>
+        <c:crossAx val="842525366"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2063252140"/>
+        <c:axId val="842525366"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1986,7 +1989,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1126542554"/>
+        <c:crossAx val="1816388622"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -35539,7 +35542,7 @@
         <v>321</v>
       </c>
       <c r="B50" s="82">
-        <v>104.0</v>
+        <v>160.0</v>
       </c>
       <c r="C50" s="82">
         <v>0.0</v>
@@ -35548,19 +35551,19 @@
         <v>0.0</v>
       </c>
       <c r="E50" s="82">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="F50" s="82">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="G50" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H50" s="82" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="I50" s="82">
-        <v>1.0E7</v>
+        <v>20000.0</v>
       </c>
       <c r="J50" s="81" t="s">
         <v>170</v>
@@ -35582,23 +35585,23 @@
         <v>170</v>
       </c>
       <c r="S50" s="81" t="s">
-        <v>322</v>
-      </c>
-      <c r="T50" s="87" t="s">
-        <v>323</v>
+        <v>320</v>
+      </c>
+      <c r="T50" s="81" t="s">
+        <v>311</v>
       </c>
       <c r="U50" s="83"/>
       <c r="V50" s="81" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="W50" s="83"/>
-      <c r="X50" s="85" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y50" s="86" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z50" s="85" t="s">
+      <c r="X50" s="94" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y50" s="97" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z50" s="94" t="s">
         <v>219</v>
       </c>
       <c r="AA50" s="87" t="s">
@@ -35608,7 +35611,7 @@
         <v>220</v>
       </c>
       <c r="AC50" s="82">
-        <v>45.0</v>
+        <v>65.0</v>
       </c>
       <c r="AD50" s="82">
         <v>100.0</v>
@@ -35617,16 +35620,16 @@
         <v>90.0</v>
       </c>
       <c r="AF50" s="82">
-        <v>100.0</v>
+        <v>95.0</v>
       </c>
       <c r="AG50" s="82">
-        <v>94.0</v>
+        <v>92.0</v>
       </c>
       <c r="AH50" s="82">
-        <v>14.56</v>
+        <v>21.0</v>
       </c>
       <c r="AI50" s="82">
-        <v>21.2</v>
+        <v>63.3</v>
       </c>
       <c r="AJ50" s="82">
         <v>75.0</v>
@@ -35635,16 +35638,16 @@
         <v>85.0</v>
       </c>
       <c r="AL50" s="88">
-        <v>64.5</v>
+        <v>78.3</v>
       </c>
       <c r="AM50" s="89">
+        <v>2.0</v>
+      </c>
+      <c r="AN50" s="89">
         <v>4.0</v>
       </c>
-      <c r="AN50" s="89">
-        <v>17.0</v>
-      </c>
       <c r="AO50" s="88">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="AP50" s="87" t="s">
         <v>200</v>
@@ -35656,19 +35659,19 @@
         <v>0.0</v>
       </c>
       <c r="AS50" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="AT50" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AU50" s="88">
+        <v>78.3</v>
+      </c>
+      <c r="AV50" s="89">
         <v>2.0</v>
       </c>
-      <c r="AT50" s="88">
-        <v>4.0</v>
-      </c>
-      <c r="AU50" s="88">
-        <v>60.5</v>
-      </c>
-      <c r="AV50" s="89">
-        <v>5.0</v>
-      </c>
       <c r="AW50" s="89">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="AX50" s="89" t="s">
         <v>259</v>
@@ -35679,10 +35682,10 @@
     </row>
     <row r="51">
       <c r="A51" s="81" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B51" s="82">
-        <v>105.0</v>
+        <v>104.0</v>
       </c>
       <c r="C51" s="82">
         <v>0.0</v>
@@ -35691,16 +35694,16 @@
         <v>0.0</v>
       </c>
       <c r="E51" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="F51" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="G51" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H51" s="82" t="s">
-        <v>325</v>
+        <v>244</v>
       </c>
       <c r="I51" s="82">
         <v>1.0E7</v>
@@ -35725,10 +35728,10 @@
         <v>170</v>
       </c>
       <c r="S51" s="81" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="T51" s="87" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U51" s="83"/>
       <c r="V51" s="81" t="s">
@@ -35754,7 +35757,7 @@
         <v>45.0</v>
       </c>
       <c r="AD51" s="82">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="AE51" s="82">
         <v>90.0</v>
@@ -35766,10 +35769,10 @@
         <v>94.0</v>
       </c>
       <c r="AH51" s="82">
-        <v>14.7</v>
+        <v>14.56</v>
       </c>
       <c r="AI51" s="82">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="AJ51" s="82">
         <v>75.0</v>
@@ -35778,16 +35781,16 @@
         <v>85.0</v>
       </c>
       <c r="AL51" s="88">
-        <v>62.9</v>
+        <v>64.5</v>
       </c>
       <c r="AM51" s="89">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="AN51" s="89">
-        <v>20.0</v>
+        <v>17.0</v>
       </c>
       <c r="AO51" s="88">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="AP51" s="87" t="s">
         <v>200</v>
@@ -35796,22 +35799,22 @@
         <v>201</v>
       </c>
       <c r="AR51" s="88">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS51" s="89">
         <v>2.0</v>
       </c>
       <c r="AT51" s="88">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="AU51" s="88">
-        <v>53.9</v>
+        <v>60.5</v>
       </c>
       <c r="AV51" s="89">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="AW51" s="89">
-        <v>29.0</v>
+        <v>15.0</v>
       </c>
       <c r="AX51" s="89" t="s">
         <v>259</v>
@@ -35822,10 +35825,10 @@
     </row>
     <row r="52">
       <c r="A52" s="81" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B52" s="82">
-        <v>14.9</v>
+        <v>105.0</v>
       </c>
       <c r="C52" s="82">
         <v>0.0</v>
@@ -35834,16 +35837,16 @@
         <v>0.0</v>
       </c>
       <c r="E52" s="82">
-        <v>365.0</v>
+        <v>180.0</v>
       </c>
       <c r="F52" s="82">
-        <v>365.0</v>
+        <v>180.0</v>
       </c>
       <c r="G52" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H52" s="82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I52" s="82">
         <v>1.0E7</v>
@@ -35862,37 +35865,39 @@
         <v>168</v>
       </c>
       <c r="Q52" s="81" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="R52" s="81" t="s">
         <v>170</v>
       </c>
       <c r="S52" s="81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="T52" s="87" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U52" s="83"/>
       <c r="V52" s="81" t="s">
         <v>198</v>
       </c>
       <c r="W52" s="83"/>
-      <c r="X52" s="92" t="s">
-        <v>228</v>
+      <c r="X52" s="85" t="s">
+        <v>176</v>
       </c>
       <c r="Y52" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z52" s="98"/>
+      <c r="Z52" s="85" t="s">
+        <v>219</v>
+      </c>
       <c r="AA52" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB52" s="87" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="AC52" s="82">
-        <v>25.0</v>
+        <v>45.0</v>
       </c>
       <c r="AD52" s="82">
         <v>90.0</v>
@@ -35907,10 +35912,10 @@
         <v>94.0</v>
       </c>
       <c r="AH52" s="82">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="AI52" s="82">
-        <v>23.4</v>
+        <v>22.1</v>
       </c>
       <c r="AJ52" s="82">
         <v>75.0</v>
@@ -35919,16 +35924,16 @@
         <v>85.0</v>
       </c>
       <c r="AL52" s="88">
-        <v>58.1</v>
+        <v>62.9</v>
       </c>
       <c r="AM52" s="89">
         <v>7.0</v>
       </c>
       <c r="AN52" s="89">
-        <v>32.0</v>
+        <v>20.0</v>
       </c>
       <c r="AO52" s="88">
-        <v>365.0</v>
+        <v>180.0</v>
       </c>
       <c r="AP52" s="87" t="s">
         <v>200</v>
@@ -35937,36 +35942,36 @@
         <v>201</v>
       </c>
       <c r="AR52" s="88">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS52" s="89">
         <v>2.0</v>
       </c>
       <c r="AT52" s="88">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="AU52" s="88">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="AV52" s="89">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AW52" s="89">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="AX52" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY52" s="81" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="81" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B53" s="82">
-        <v>15.0</v>
+        <v>14.9</v>
       </c>
       <c r="C53" s="82">
         <v>0.0</v>
@@ -35975,16 +35980,16 @@
         <v>0.0</v>
       </c>
       <c r="E53" s="82">
-        <v>180.0</v>
+        <v>365.0</v>
       </c>
       <c r="F53" s="82">
-        <v>180.0</v>
+        <v>365.0</v>
       </c>
       <c r="G53" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H53" s="82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I53" s="82">
         <v>1.0E7</v>
@@ -36009,33 +36014,31 @@
         <v>170</v>
       </c>
       <c r="S53" s="81" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T53" s="87" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="U53" s="83"/>
       <c r="V53" s="81" t="s">
         <v>198</v>
       </c>
       <c r="W53" s="83"/>
-      <c r="X53" s="85" t="s">
-        <v>176</v>
+      <c r="X53" s="92" t="s">
+        <v>228</v>
       </c>
       <c r="Y53" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z53" s="85" t="s">
-        <v>219</v>
-      </c>
+      <c r="Z53" s="98"/>
       <c r="AA53" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB53" s="87" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="AC53" s="82">
-        <v>45.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD53" s="82">
         <v>90.0</v>
@@ -36050,10 +36053,10 @@
         <v>94.0</v>
       </c>
       <c r="AH53" s="82">
-        <v>15.0</v>
+        <v>14.9</v>
       </c>
       <c r="AI53" s="82">
-        <v>24.0</v>
+        <v>23.4</v>
       </c>
       <c r="AJ53" s="82">
         <v>75.0</v>
@@ -36062,16 +36065,16 @@
         <v>85.0</v>
       </c>
       <c r="AL53" s="88">
-        <v>63.3</v>
+        <v>58.1</v>
       </c>
       <c r="AM53" s="89">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="AN53" s="89">
-        <v>18.0</v>
+        <v>32.0</v>
       </c>
       <c r="AO53" s="88">
-        <v>180.0</v>
+        <v>365.0</v>
       </c>
       <c r="AP53" s="87" t="s">
         <v>200</v>
@@ -36083,19 +36086,19 @@
         <v>0.0</v>
       </c>
       <c r="AS53" s="89">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AT53" s="88">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="AU53" s="88">
-        <v>61.3</v>
+        <v>54.1</v>
       </c>
       <c r="AV53" s="89">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="AW53" s="89">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
       <c r="AX53" s="89" t="s">
         <v>259</v>
@@ -36106,10 +36109,10 @@
     </row>
     <row r="54">
       <c r="A54" s="81" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B54" s="82">
-        <v>120.0</v>
+        <v>15.0</v>
       </c>
       <c r="C54" s="82">
         <v>0.0</v>
@@ -36118,59 +36121,61 @@
         <v>0.0</v>
       </c>
       <c r="E54" s="82">
-        <v>90.0</v>
+        <v>180.0</v>
       </c>
       <c r="F54" s="82">
-        <v>90.0</v>
+        <v>180.0</v>
       </c>
       <c r="G54" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H54" s="82" t="s">
-        <v>205</v>
-      </c>
-      <c r="I54" s="83"/>
+        <v>326</v>
+      </c>
+      <c r="I54" s="82">
+        <v>1.0E7</v>
+      </c>
       <c r="J54" s="81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K54" s="81" t="s">
         <v>255</v>
       </c>
-      <c r="L54" s="83"/>
-      <c r="M54" s="83"/>
-      <c r="N54" s="83"/>
-      <c r="O54" s="83"/>
+      <c r="L54" s="84"/>
+      <c r="M54" s="84"/>
+      <c r="N54" s="84"/>
+      <c r="O54" s="84"/>
       <c r="P54" s="81" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q54" s="81" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="R54" s="81" t="s">
         <v>170</v>
       </c>
       <c r="S54" s="81" t="s">
-        <v>332</v>
-      </c>
-      <c r="T54" s="81" t="s">
-        <v>257</v>
+        <v>331</v>
+      </c>
+      <c r="T54" s="87" t="s">
+        <v>324</v>
       </c>
       <c r="U54" s="83"/>
       <c r="V54" s="81" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="W54" s="83"/>
       <c r="X54" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="Y54" s="91" t="s">
-        <v>258</v>
+      <c r="Y54" s="86" t="s">
+        <v>177</v>
       </c>
       <c r="Z54" s="85" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="AA54" s="87" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AB54" s="87" t="s">
         <v>220</v>
@@ -36179,22 +36184,22 @@
         <v>45.0</v>
       </c>
       <c r="AD54" s="82">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="AE54" s="82">
         <v>90.0</v>
       </c>
       <c r="AF54" s="82">
-        <v>95.0</v>
+        <v>100.0</v>
       </c>
       <c r="AG54" s="82">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
       <c r="AH54" s="82">
-        <v>16.8</v>
+        <v>15.0</v>
       </c>
       <c r="AI54" s="82">
-        <v>35.8</v>
+        <v>24.0</v>
       </c>
       <c r="AJ54" s="82">
         <v>75.0</v>
@@ -36203,12 +36208,16 @@
         <v>85.0</v>
       </c>
       <c r="AL54" s="88">
-        <v>63.7</v>
-      </c>
-      <c r="AM54" s="95"/>
-      <c r="AN54" s="95"/>
+        <v>63.3</v>
+      </c>
+      <c r="AM54" s="89">
+        <v>5.0</v>
+      </c>
+      <c r="AN54" s="89">
+        <v>18.0</v>
+      </c>
       <c r="AO54" s="88">
-        <v>90.0</v>
+        <v>180.0</v>
       </c>
       <c r="AP54" s="87" t="s">
         <v>200</v>
@@ -36216,22 +36225,34 @@
       <c r="AQ54" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="AR54" s="96"/>
-      <c r="AS54" s="95"/>
-      <c r="AT54" s="96"/>
-      <c r="AU54" s="96"/>
-      <c r="AV54" s="95"/>
-      <c r="AW54" s="95"/>
+      <c r="AR54" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AS54" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="AT54" s="88">
+        <v>2.0</v>
+      </c>
+      <c r="AU54" s="88">
+        <v>61.3</v>
+      </c>
+      <c r="AV54" s="89">
+        <v>4.0</v>
+      </c>
+      <c r="AW54" s="89">
+        <v>13.0</v>
+      </c>
       <c r="AX54" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY54" s="81" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="81" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B55" s="82">
         <v>120.0</v>
@@ -36243,16 +36264,16 @@
         <v>0.0</v>
       </c>
       <c r="E55" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="F55" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="G55" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H55" s="82" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="I55" s="83"/>
       <c r="J55" s="81" t="s">
@@ -36275,7 +36296,7 @@
         <v>170</v>
       </c>
       <c r="S55" s="81" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T55" s="81" t="s">
         <v>257</v>
@@ -36304,7 +36325,7 @@
         <v>45.0</v>
       </c>
       <c r="AD55" s="82">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="AE55" s="82">
         <v>90.0</v>
@@ -36328,12 +36349,12 @@
         <v>85.0</v>
       </c>
       <c r="AL55" s="88">
-        <v>67.3</v>
+        <v>63.7</v>
       </c>
       <c r="AM55" s="95"/>
       <c r="AN55" s="95"/>
       <c r="AO55" s="88">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="AP55" s="87" t="s">
         <v>200</v>
@@ -36356,10 +36377,10 @@
     </row>
     <row r="56">
       <c r="A56" s="81" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B56" s="82">
-        <v>107.25</v>
+        <v>120.0</v>
       </c>
       <c r="C56" s="82">
         <v>0.0</v>
@@ -36368,10 +36389,10 @@
         <v>0.0</v>
       </c>
       <c r="E56" s="82">
-        <v>540.0</v>
+        <v>180.0</v>
       </c>
       <c r="F56" s="82">
-        <v>540.0</v>
+        <v>180.0</v>
       </c>
       <c r="G56" s="81" t="s">
         <v>168</v>
@@ -36381,17 +36402,17 @@
       </c>
       <c r="I56" s="83"/>
       <c r="J56" s="81" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K56" s="81" t="s">
         <v>255</v>
       </c>
-      <c r="L56" s="84"/>
-      <c r="M56" s="84"/>
-      <c r="N56" s="84"/>
-      <c r="O56" s="84"/>
+      <c r="L56" s="83"/>
+      <c r="M56" s="83"/>
+      <c r="N56" s="83"/>
+      <c r="O56" s="83"/>
       <c r="P56" s="81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q56" s="81" t="s">
         <v>195</v>
@@ -36400,7 +36421,7 @@
         <v>170</v>
       </c>
       <c r="S56" s="81" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T56" s="81" t="s">
         <v>257</v>
@@ -36413,20 +36434,20 @@
       <c r="X56" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="Y56" s="86" t="s">
-        <v>177</v>
+      <c r="Y56" s="91" t="s">
+        <v>258</v>
       </c>
       <c r="Z56" s="85" t="s">
         <v>178</v>
       </c>
       <c r="AA56" s="87" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AB56" s="87" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="AC56" s="82">
-        <v>10.0</v>
+        <v>45.0</v>
       </c>
       <c r="AD56" s="82">
         <v>100.0</v>
@@ -36441,10 +36462,10 @@
         <v>92.0</v>
       </c>
       <c r="AH56" s="82">
-        <v>15.02</v>
+        <v>16.8</v>
       </c>
       <c r="AI56" s="82">
-        <v>24.2</v>
+        <v>35.8</v>
       </c>
       <c r="AJ56" s="82">
         <v>75.0</v>
@@ -36453,16 +36474,12 @@
         <v>85.0</v>
       </c>
       <c r="AL56" s="88">
-        <v>56.0</v>
-      </c>
-      <c r="AM56" s="89">
-        <v>22.0</v>
-      </c>
-      <c r="AN56" s="89">
-        <v>48.0</v>
-      </c>
+        <v>67.3</v>
+      </c>
+      <c r="AM56" s="95"/>
+      <c r="AN56" s="95"/>
       <c r="AO56" s="88">
-        <v>540.0</v>
+        <v>180.0</v>
       </c>
       <c r="AP56" s="87" t="s">
         <v>200</v>
@@ -36470,24 +36487,12 @@
       <c r="AQ56" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="AR56" s="88">
-        <v>5.0</v>
-      </c>
-      <c r="AS56" s="89">
-        <v>3.0</v>
-      </c>
-      <c r="AT56" s="88">
-        <v>18.0</v>
-      </c>
-      <c r="AU56" s="88">
-        <v>38.0</v>
-      </c>
-      <c r="AV56" s="89">
-        <v>34.0</v>
-      </c>
-      <c r="AW56" s="89">
-        <v>61.0</v>
-      </c>
+      <c r="AR56" s="96"/>
+      <c r="AS56" s="95"/>
+      <c r="AT56" s="96"/>
+      <c r="AU56" s="96"/>
+      <c r="AV56" s="95"/>
+      <c r="AW56" s="95"/>
       <c r="AX56" s="89" t="s">
         <v>259</v>
       </c>
@@ -36497,10 +36502,10 @@
     </row>
     <row r="57">
       <c r="A57" s="81" t="s">
-        <v>114</v>
+        <v>336</v>
       </c>
       <c r="B57" s="82">
-        <v>105.0</v>
+        <v>107.25</v>
       </c>
       <c r="C57" s="82">
         <v>0.0</v>
@@ -36509,16 +36514,16 @@
         <v>0.0</v>
       </c>
       <c r="E57" s="82">
-        <v>1086.0</v>
+        <v>540.0</v>
       </c>
       <c r="F57" s="82">
-        <v>0.0</v>
+        <v>540.0</v>
       </c>
       <c r="G57" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H57" s="82" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="I57" s="83"/>
       <c r="J57" s="81" t="s">
@@ -36544,30 +36549,30 @@
         <v>337</v>
       </c>
       <c r="T57" s="81" t="s">
-        <v>338</v>
+        <v>257</v>
       </c>
       <c r="U57" s="83"/>
       <c r="V57" s="81" t="s">
         <v>209</v>
       </c>
       <c r="W57" s="83"/>
-      <c r="X57" s="94" t="s">
-        <v>239</v>
+      <c r="X57" s="85" t="s">
+        <v>176</v>
       </c>
       <c r="Y57" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z57" s="94" t="s">
-        <v>219</v>
+      <c r="Z57" s="85" t="s">
+        <v>178</v>
       </c>
       <c r="AA57" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB57" s="87" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="AC57" s="82">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
       <c r="AD57" s="82">
         <v>100.0</v>
@@ -36582,28 +36587,28 @@
         <v>92.0</v>
       </c>
       <c r="AH57" s="82">
-        <v>0.59</v>
+        <v>15.02</v>
       </c>
       <c r="AI57" s="82">
-        <v>0.0</v>
+        <v>24.2</v>
       </c>
       <c r="AJ57" s="82">
-        <v>51.0</v>
+        <v>75.0</v>
       </c>
       <c r="AK57" s="82">
         <v>85.0</v>
       </c>
       <c r="AL57" s="88">
-        <v>70.8</v>
+        <v>56.0</v>
       </c>
       <c r="AM57" s="89">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
       <c r="AN57" s="89">
-        <v>8.0</v>
+        <v>48.0</v>
       </c>
       <c r="AO57" s="88">
-        <v>0.0</v>
+        <v>540.0</v>
       </c>
       <c r="AP57" s="87" t="s">
         <v>200</v>
@@ -36612,22 +36617,22 @@
         <v>201</v>
       </c>
       <c r="AR57" s="88">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="AS57" s="89">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="AT57" s="88">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="AU57" s="88">
-        <v>70.8</v>
+        <v>38.0</v>
       </c>
       <c r="AV57" s="89">
-        <v>4.0</v>
+        <v>34.0</v>
       </c>
       <c r="AW57" s="89">
-        <v>7.0</v>
+        <v>61.0</v>
       </c>
       <c r="AX57" s="89" t="s">
         <v>259</v>
@@ -36638,19 +36643,19 @@
     </row>
     <row r="58">
       <c r="A58" s="81" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B58" s="82">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="C58" s="82">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
       <c r="D58" s="82">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="E58" s="82">
-        <v>30.0</v>
+        <v>1086.0</v>
       </c>
       <c r="F58" s="82">
         <v>0.0</v>
@@ -36663,7 +36668,7 @@
       </c>
       <c r="I58" s="83"/>
       <c r="J58" s="81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K58" s="81" t="s">
         <v>255</v>
@@ -36682,27 +36687,27 @@
         <v>170</v>
       </c>
       <c r="S58" s="81" t="s">
+        <v>338</v>
+      </c>
+      <c r="T58" s="81" t="s">
         <v>339</v>
-      </c>
-      <c r="T58" s="87" t="s">
-        <v>323</v>
       </c>
       <c r="U58" s="83"/>
       <c r="V58" s="81" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="W58" s="83"/>
-      <c r="X58" s="85" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y58" s="91" t="s">
+      <c r="X58" s="94" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y58" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z58" s="85" t="s">
-        <v>178</v>
+      <c r="Z58" s="94" t="s">
+        <v>219</v>
       </c>
       <c r="AA58" s="87" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AB58" s="87" t="s">
         <v>199</v>
@@ -36717,13 +36722,13 @@
         <v>90.0</v>
       </c>
       <c r="AF58" s="82">
-        <v>60.0</v>
+        <v>95.0</v>
       </c>
       <c r="AG58" s="82">
-        <v>78.0</v>
+        <v>92.0</v>
       </c>
       <c r="AH58" s="82">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="AI58" s="82">
         <v>0.0</v>
@@ -36735,10 +36740,14 @@
         <v>85.0</v>
       </c>
       <c r="AL58" s="88">
-        <v>68.0</v>
-      </c>
-      <c r="AM58" s="95"/>
-      <c r="AN58" s="95"/>
+        <v>70.8</v>
+      </c>
+      <c r="AM58" s="89">
+        <v>5.0</v>
+      </c>
+      <c r="AN58" s="89">
+        <v>8.0</v>
+      </c>
       <c r="AO58" s="88">
         <v>0.0</v>
       </c>
@@ -36748,12 +36757,24 @@
       <c r="AQ58" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="AR58" s="96"/>
-      <c r="AS58" s="95"/>
-      <c r="AT58" s="96"/>
-      <c r="AU58" s="96"/>
-      <c r="AV58" s="95"/>
-      <c r="AW58" s="95"/>
+      <c r="AR58" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AS58" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="AT58" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AU58" s="88">
+        <v>70.8</v>
+      </c>
+      <c r="AV58" s="89">
+        <v>4.0</v>
+      </c>
+      <c r="AW58" s="89">
+        <v>7.0</v>
+      </c>
       <c r="AX58" s="89" t="s">
         <v>259</v>
       </c>
@@ -36763,19 +36784,19 @@
     </row>
     <row r="59">
       <c r="A59" s="81" t="s">
-        <v>340</v>
+        <v>112</v>
       </c>
       <c r="B59" s="82">
-        <v>150.0</v>
+        <v>103.0</v>
       </c>
       <c r="C59" s="82">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
       <c r="D59" s="82">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="E59" s="82">
-        <v>60.0</v>
+        <v>30.0</v>
       </c>
       <c r="F59" s="82">
         <v>0.0</v>
@@ -36784,13 +36805,11 @@
         <v>168</v>
       </c>
       <c r="H59" s="82" t="s">
-        <v>341</v>
-      </c>
-      <c r="I59" s="82">
-        <v>60000.0</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="I59" s="83"/>
       <c r="J59" s="81" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K59" s="81" t="s">
         <v>255</v>
@@ -36809,27 +36828,27 @@
         <v>170</v>
       </c>
       <c r="S59" s="81" t="s">
-        <v>342</v>
-      </c>
-      <c r="T59" s="81" t="s">
-        <v>343</v>
+        <v>340</v>
+      </c>
+      <c r="T59" s="87" t="s">
+        <v>324</v>
       </c>
       <c r="U59" s="83"/>
       <c r="V59" s="81" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="W59" s="83"/>
       <c r="X59" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="Y59" s="97" t="s">
-        <v>248</v>
+      <c r="Y59" s="91" t="s">
+        <v>177</v>
       </c>
       <c r="Z59" s="85" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="AA59" s="87" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AB59" s="87" t="s">
         <v>199</v>
@@ -36838,19 +36857,19 @@
         <v>100.0</v>
       </c>
       <c r="AD59" s="82">
-        <v>15.0</v>
+        <v>100.0</v>
       </c>
       <c r="AE59" s="82">
         <v>90.0</v>
       </c>
       <c r="AF59" s="82">
-        <v>95.0</v>
+        <v>60.0</v>
       </c>
       <c r="AG59" s="82">
-        <v>92.0</v>
+        <v>78.0</v>
       </c>
       <c r="AH59" s="82">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="AI59" s="82">
         <v>0.0</v>
@@ -36862,14 +36881,10 @@
         <v>85.0</v>
       </c>
       <c r="AL59" s="88">
-        <v>55.5</v>
-      </c>
-      <c r="AM59" s="89">
-        <v>12.0</v>
-      </c>
-      <c r="AN59" s="89">
-        <v>52.0</v>
-      </c>
+        <v>68.0</v>
+      </c>
+      <c r="AM59" s="95"/>
+      <c r="AN59" s="95"/>
       <c r="AO59" s="88">
         <v>0.0</v>
       </c>
@@ -36879,24 +36894,12 @@
       <c r="AQ59" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="AR59" s="88">
-        <v>0.0</v>
-      </c>
-      <c r="AS59" s="89">
-        <v>0.0</v>
-      </c>
-      <c r="AT59" s="88">
-        <v>0.0</v>
-      </c>
-      <c r="AU59" s="88">
-        <v>55.5</v>
-      </c>
-      <c r="AV59" s="89">
-        <v>8.0</v>
-      </c>
-      <c r="AW59" s="89">
-        <v>23.0</v>
-      </c>
+      <c r="AR59" s="96"/>
+      <c r="AS59" s="95"/>
+      <c r="AT59" s="96"/>
+      <c r="AU59" s="96"/>
+      <c r="AV59" s="95"/>
+      <c r="AW59" s="95"/>
       <c r="AX59" s="89" t="s">
         <v>259</v>
       </c>
@@ -36906,10 +36909,10 @@
     </row>
     <row r="60">
       <c r="A60" s="81" t="s">
-        <v>113</v>
+        <v>341</v>
       </c>
       <c r="B60" s="82">
-        <v>230.0</v>
+        <v>150.0</v>
       </c>
       <c r="C60" s="82">
         <v>0.0</v>
@@ -36927,13 +36930,13 @@
         <v>168</v>
       </c>
       <c r="H60" s="82" t="s">
-        <v>169</v>
+        <v>342</v>
       </c>
       <c r="I60" s="82">
-        <v>3000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="J60" s="81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K60" s="81" t="s">
         <v>255</v>
@@ -36952,10 +36955,10 @@
         <v>170</v>
       </c>
       <c r="S60" s="81" t="s">
+        <v>343</v>
+      </c>
+      <c r="T60" s="81" t="s">
         <v>344</v>
-      </c>
-      <c r="T60" s="81" t="s">
-        <v>343</v>
       </c>
       <c r="U60" s="83"/>
       <c r="V60" s="81" t="s">
@@ -36965,14 +36968,14 @@
       <c r="X60" s="85" t="s">
         <v>176</v>
       </c>
-      <c r="Y60" s="91" t="s">
-        <v>258</v>
+      <c r="Y60" s="97" t="s">
+        <v>248</v>
       </c>
       <c r="Z60" s="85" t="s">
-        <v>345</v>
+        <v>219</v>
       </c>
       <c r="AA60" s="87" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AB60" s="87" t="s">
         <v>199</v>
@@ -36981,7 +36984,7 @@
         <v>100.0</v>
       </c>
       <c r="AD60" s="82">
-        <v>100.0</v>
+        <v>15.0</v>
       </c>
       <c r="AE60" s="82">
         <v>90.0</v>
@@ -36993,7 +36996,7 @@
         <v>92.0</v>
       </c>
       <c r="AH60" s="82">
-        <v>1.29</v>
+        <v>0.84</v>
       </c>
       <c r="AI60" s="82">
         <v>0.0</v>
@@ -37005,10 +37008,14 @@
         <v>85.0</v>
       </c>
       <c r="AL60" s="88">
-        <v>70.8</v>
-      </c>
-      <c r="AM60" s="95"/>
-      <c r="AN60" s="95"/>
+        <v>55.5</v>
+      </c>
+      <c r="AM60" s="89">
+        <v>12.0</v>
+      </c>
+      <c r="AN60" s="89">
+        <v>52.0</v>
+      </c>
       <c r="AO60" s="88">
         <v>0.0</v>
       </c>
@@ -37018,12 +37025,24 @@
       <c r="AQ60" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="AR60" s="96"/>
-      <c r="AS60" s="95"/>
-      <c r="AT60" s="96"/>
-      <c r="AU60" s="96"/>
-      <c r="AV60" s="95"/>
-      <c r="AW60" s="95"/>
+      <c r="AR60" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AS60" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="AT60" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AU60" s="88">
+        <v>55.5</v>
+      </c>
+      <c r="AV60" s="89">
+        <v>8.0</v>
+      </c>
+      <c r="AW60" s="89">
+        <v>23.0</v>
+      </c>
       <c r="AX60" s="89" t="s">
         <v>259</v>
       </c>
@@ -37033,19 +37052,19 @@
     </row>
     <row r="61">
       <c r="A61" s="81" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="B61" s="82">
-        <v>100.0</v>
+        <v>230.0</v>
       </c>
       <c r="C61" s="82">
-        <v>115.0</v>
+        <v>0.0</v>
       </c>
       <c r="D61" s="82">
         <v>0.0</v>
       </c>
       <c r="E61" s="82">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="F61" s="82">
         <v>0.0</v>
@@ -37054,27 +37073,21 @@
         <v>168</v>
       </c>
       <c r="H61" s="82" t="s">
-        <v>347</v>
-      </c>
-      <c r="I61" s="83"/>
+        <v>169</v>
+      </c>
+      <c r="I61" s="82">
+        <v>3000.0</v>
+      </c>
       <c r="J61" s="81" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K61" s="81" t="s">
-        <v>348</v>
-      </c>
-      <c r="L61" s="81" t="s">
-        <v>349</v>
-      </c>
-      <c r="M61" s="81" t="s">
-        <v>350</v>
-      </c>
-      <c r="N61" s="82">
-        <v>2.0</v>
-      </c>
-      <c r="O61" s="82">
-        <v>1.0</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="L61" s="84"/>
+      <c r="M61" s="84"/>
+      <c r="N61" s="84"/>
+      <c r="O61" s="84"/>
       <c r="P61" s="81" t="s">
         <v>168</v>
       </c>
@@ -37085,27 +37098,27 @@
         <v>170</v>
       </c>
       <c r="S61" s="81" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="T61" s="81" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="U61" s="83"/>
       <c r="V61" s="81" t="s">
         <v>209</v>
       </c>
       <c r="W61" s="83"/>
-      <c r="X61" s="90" t="s">
-        <v>187</v>
+      <c r="X61" s="85" t="s">
+        <v>176</v>
       </c>
       <c r="Y61" s="91" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z61" s="90" t="s">
-        <v>219</v>
+        <v>258</v>
+      </c>
+      <c r="Z61" s="85" t="s">
+        <v>346</v>
       </c>
       <c r="AA61" s="87" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AB61" s="87" t="s">
         <v>199</v>
@@ -37114,7 +37127,7 @@
         <v>100.0</v>
       </c>
       <c r="AD61" s="82">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="AE61" s="82">
         <v>90.0</v>
@@ -37126,26 +37139,22 @@
         <v>92.0</v>
       </c>
       <c r="AH61" s="82">
-        <v>0.64</v>
+        <v>1.29</v>
       </c>
       <c r="AI61" s="82">
         <v>0.0</v>
       </c>
       <c r="AJ61" s="82">
-        <v>16.0</v>
+        <v>51.0</v>
       </c>
       <c r="AK61" s="82">
         <v>85.0</v>
       </c>
       <c r="AL61" s="88">
-        <v>65.5</v>
-      </c>
-      <c r="AM61" s="89">
-        <v>7.0</v>
-      </c>
-      <c r="AN61" s="89">
-        <v>13.0</v>
-      </c>
+        <v>70.8</v>
+      </c>
+      <c r="AM61" s="95"/>
+      <c r="AN61" s="95"/>
       <c r="AO61" s="88">
         <v>0.0</v>
       </c>
@@ -37155,24 +37164,12 @@
       <c r="AQ61" s="87" t="s">
         <v>201</v>
       </c>
-      <c r="AR61" s="88">
-        <v>2.0</v>
-      </c>
-      <c r="AS61" s="89">
-        <v>0.0</v>
-      </c>
-      <c r="AT61" s="88">
-        <v>14.0</v>
-      </c>
-      <c r="AU61" s="88">
-        <v>51.5</v>
-      </c>
-      <c r="AV61" s="89">
-        <v>10.0</v>
-      </c>
-      <c r="AW61" s="89">
-        <v>32.0</v>
-      </c>
+      <c r="AR61" s="96"/>
+      <c r="AS61" s="95"/>
+      <c r="AT61" s="96"/>
+      <c r="AU61" s="96"/>
+      <c r="AV61" s="95"/>
+      <c r="AW61" s="95"/>
       <c r="AX61" s="89" t="s">
         <v>259</v>
       </c>
@@ -37182,13 +37179,13 @@
     </row>
     <row r="62">
       <c r="A62" s="81" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B62" s="82">
         <v>100.0</v>
       </c>
       <c r="C62" s="82">
-        <v>120.0</v>
+        <v>115.0</v>
       </c>
       <c r="D62" s="82">
         <v>0.0</v>
@@ -37202,26 +37199,26 @@
       <c r="G62" s="81" t="s">
         <v>168</v>
       </c>
-      <c r="H62" s="87" t="s">
-        <v>347</v>
+      <c r="H62" s="82" t="s">
+        <v>348</v>
       </c>
       <c r="I62" s="83"/>
       <c r="J62" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K62" s="81" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L62" s="81" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M62" s="81" t="s">
-        <v>354</v>
-      </c>
-      <c r="N62" s="87">
+        <v>351</v>
+      </c>
+      <c r="N62" s="82">
         <v>2.0</v>
       </c>
-      <c r="O62" s="87">
+      <c r="O62" s="82">
         <v>1.0</v>
       </c>
       <c r="P62" s="81" t="s">
@@ -37234,10 +37231,10 @@
         <v>170</v>
       </c>
       <c r="S62" s="81" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="T62" s="81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="U62" s="83"/>
       <c r="V62" s="81" t="s">
@@ -37275,7 +37272,7 @@
         <v>92.0</v>
       </c>
       <c r="AH62" s="82">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="AI62" s="82">
         <v>0.0</v>
@@ -37290,10 +37287,10 @@
         <v>65.5</v>
       </c>
       <c r="AM62" s="89">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="AN62" s="89">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AO62" s="88">
         <v>0.0</v>
@@ -37305,22 +37302,22 @@
         <v>201</v>
       </c>
       <c r="AR62" s="88">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AS62" s="89">
         <v>0.0</v>
       </c>
       <c r="AT62" s="88">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="AU62" s="88">
-        <v>65.5</v>
+        <v>51.5</v>
       </c>
       <c r="AV62" s="89">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="AW62" s="89">
-        <v>9.0</v>
+        <v>32.0</v>
       </c>
       <c r="AX62" s="89" t="s">
         <v>259</v>
@@ -37331,7 +37328,7 @@
     </row>
     <row r="63">
       <c r="A63" s="81" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B63" s="82">
         <v>100.0</v>
@@ -37343,7 +37340,7 @@
         <v>0.0</v>
       </c>
       <c r="E63" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="F63" s="82">
         <v>0.0</v>
@@ -37352,20 +37349,20 @@
         <v>168</v>
       </c>
       <c r="H63" s="87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I63" s="83"/>
       <c r="J63" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K63" s="81" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L63" s="81" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M63" s="81" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N63" s="87">
         <v>2.0</v>
@@ -37383,10 +37380,10 @@
         <v>170</v>
       </c>
       <c r="S63" s="81" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="T63" s="81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="U63" s="83"/>
       <c r="V63" s="81" t="s">
@@ -37439,10 +37436,10 @@
         <v>65.5</v>
       </c>
       <c r="AM63" s="89">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AN63" s="89">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="AO63" s="88">
         <v>0.0</v>
@@ -37466,10 +37463,10 @@
         <v>65.5</v>
       </c>
       <c r="AV63" s="89">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="AW63" s="89">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="AX63" s="89" t="s">
         <v>259</v>
@@ -37480,40 +37477,48 @@
     </row>
     <row r="64">
       <c r="A64" s="81" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B64" s="82">
-        <v>115.75</v>
+        <v>100.0</v>
       </c>
       <c r="C64" s="82">
-        <v>0.0</v>
+        <v>120.0</v>
       </c>
       <c r="D64" s="82">
         <v>0.0</v>
       </c>
       <c r="E64" s="82">
-        <v>365.0</v>
+        <v>180.0</v>
       </c>
       <c r="F64" s="82">
-        <v>365.0</v>
+        <v>0.0</v>
       </c>
       <c r="G64" s="81" t="s">
         <v>168</v>
       </c>
-      <c r="H64" s="82" t="s">
-        <v>169</v>
+      <c r="H64" s="87" t="s">
+        <v>348</v>
       </c>
       <c r="I64" s="83"/>
       <c r="J64" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K64" s="81" t="s">
-        <v>245</v>
-      </c>
-      <c r="L64" s="84"/>
-      <c r="M64" s="84"/>
-      <c r="N64" s="84"/>
-      <c r="O64" s="84"/>
+        <v>349</v>
+      </c>
+      <c r="L64" s="81" t="s">
+        <v>350</v>
+      </c>
+      <c r="M64" s="81" t="s">
+        <v>358</v>
+      </c>
+      <c r="N64" s="87">
+        <v>2.0</v>
+      </c>
+      <c r="O64" s="87">
+        <v>1.0</v>
+      </c>
       <c r="P64" s="81" t="s">
         <v>168</v>
       </c>
@@ -37521,72 +37526,72 @@
         <v>195</v>
       </c>
       <c r="R64" s="81" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="S64" s="81" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T64" s="81" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="U64" s="83"/>
       <c r="V64" s="81" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="W64" s="83"/>
-      <c r="X64" s="85" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y64" s="86" t="s">
+      <c r="X64" s="90" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y64" s="91" t="s">
         <v>177</v>
       </c>
-      <c r="Z64" s="85" t="s">
-        <v>178</v>
+      <c r="Z64" s="90" t="s">
+        <v>219</v>
       </c>
       <c r="AA64" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB64" s="87" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="AC64" s="82">
-        <v>25.0</v>
+        <v>100.0</v>
       </c>
       <c r="AD64" s="82">
-        <v>100.0</v>
+        <v>90.0</v>
       </c>
       <c r="AE64" s="82">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="AF64" s="82">
-        <v>60.0</v>
+        <v>95.0</v>
       </c>
       <c r="AG64" s="82">
-        <v>66.0</v>
+        <v>92.0</v>
       </c>
       <c r="AH64" s="82">
-        <v>16.2</v>
+        <v>0.67</v>
       </c>
       <c r="AI64" s="82">
-        <v>31.9</v>
+        <v>0.0</v>
       </c>
       <c r="AJ64" s="82">
-        <v>75.0</v>
+        <v>16.0</v>
       </c>
       <c r="AK64" s="82">
         <v>85.0</v>
       </c>
       <c r="AL64" s="88">
-        <v>56.2</v>
+        <v>65.5</v>
       </c>
       <c r="AM64" s="89">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
       <c r="AN64" s="89">
-        <v>47.0</v>
+        <v>15.0</v>
       </c>
       <c r="AO64" s="88">
-        <v>365.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP64" s="87" t="s">
         <v>200</v>
@@ -37595,22 +37600,22 @@
         <v>201</v>
       </c>
       <c r="AR64" s="88">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS64" s="89">
         <v>0.0</v>
       </c>
       <c r="AT64" s="88">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU64" s="88">
-        <v>49.2</v>
+        <v>65.5</v>
       </c>
       <c r="AV64" s="89">
-        <v>24.0</v>
+        <v>6.0</v>
       </c>
       <c r="AW64" s="89">
-        <v>46.0</v>
+        <v>10.0</v>
       </c>
       <c r="AX64" s="89" t="s">
         <v>259</v>
@@ -37621,10 +37626,10 @@
     </row>
     <row r="65">
       <c r="A65" s="81" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B65" s="82">
-        <v>119.16</v>
+        <v>115.75</v>
       </c>
       <c r="C65" s="82">
         <v>0.0</v>
@@ -37633,10 +37638,10 @@
         <v>0.0</v>
       </c>
       <c r="E65" s="82">
-        <v>730.0</v>
+        <v>365.0</v>
       </c>
       <c r="F65" s="82">
-        <v>730.0</v>
+        <v>365.0</v>
       </c>
       <c r="G65" s="81" t="s">
         <v>168</v>
@@ -37665,10 +37670,10 @@
         <v>168</v>
       </c>
       <c r="S65" s="81" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="T65" s="81" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U65" s="83"/>
       <c r="V65" s="81" t="s">
@@ -37681,7 +37686,9 @@
       <c r="Y65" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z65" s="93"/>
+      <c r="Z65" s="85" t="s">
+        <v>178</v>
+      </c>
       <c r="AA65" s="87" t="s">
         <v>170</v>
       </c>
@@ -37689,7 +37696,7 @@
         <v>179</v>
       </c>
       <c r="AC65" s="82">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD65" s="82">
         <v>100.0</v>
@@ -37704,10 +37711,10 @@
         <v>66.0</v>
       </c>
       <c r="AH65" s="82">
-        <v>16.68</v>
+        <v>16.2</v>
       </c>
       <c r="AI65" s="82">
-        <v>35.0</v>
+        <v>31.9</v>
       </c>
       <c r="AJ65" s="82">
         <v>75.0</v>
@@ -37716,16 +37723,16 @@
         <v>85.0</v>
       </c>
       <c r="AL65" s="88">
-        <v>53.2</v>
+        <v>56.2</v>
       </c>
       <c r="AM65" s="89">
-        <v>32.0</v>
+        <v>21.0</v>
       </c>
       <c r="AN65" s="89">
-        <v>60.0</v>
+        <v>47.0</v>
       </c>
       <c r="AO65" s="88">
-        <v>730.0</v>
+        <v>365.0</v>
       </c>
       <c r="AP65" s="87" t="s">
         <v>200</v>
@@ -37734,22 +37741,22 @@
         <v>201</v>
       </c>
       <c r="AR65" s="88">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS65" s="89">
         <v>0.0</v>
       </c>
       <c r="AT65" s="88">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="AU65" s="88">
-        <v>53.2</v>
+        <v>49.2</v>
       </c>
       <c r="AV65" s="89">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
       <c r="AW65" s="89">
-        <v>30.0</v>
+        <v>46.0</v>
       </c>
       <c r="AX65" s="89" t="s">
         <v>259</v>
@@ -37760,10 +37767,10 @@
     </row>
     <row r="66">
       <c r="A66" s="81" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B66" s="82">
-        <v>104.41</v>
+        <v>119.16</v>
       </c>
       <c r="C66" s="82">
         <v>0.0</v>
@@ -37772,10 +37779,10 @@
         <v>0.0</v>
       </c>
       <c r="E66" s="82">
-        <v>90.0</v>
+        <v>730.0</v>
       </c>
       <c r="F66" s="82">
-        <v>90.0</v>
+        <v>730.0</v>
       </c>
       <c r="G66" s="81" t="s">
         <v>168</v>
@@ -37804,10 +37811,10 @@
         <v>168</v>
       </c>
       <c r="S66" s="81" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T66" s="81" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U66" s="83"/>
       <c r="V66" s="81" t="s">
@@ -37820,17 +37827,15 @@
       <c r="Y66" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z66" s="85" t="s">
-        <v>178</v>
-      </c>
+      <c r="Z66" s="93"/>
       <c r="AA66" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB66" s="87" t="s">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="AC66" s="82">
-        <v>45.0</v>
+        <v>10.0</v>
       </c>
       <c r="AD66" s="82">
         <v>100.0</v>
@@ -37845,10 +37850,10 @@
         <v>66.0</v>
       </c>
       <c r="AH66" s="82">
-        <v>14.62</v>
+        <v>16.68</v>
       </c>
       <c r="AI66" s="82">
-        <v>21.5</v>
+        <v>35.0</v>
       </c>
       <c r="AJ66" s="82">
         <v>75.0</v>
@@ -37857,16 +37862,16 @@
         <v>85.0</v>
       </c>
       <c r="AL66" s="88">
-        <v>58.9</v>
+        <v>53.2</v>
       </c>
       <c r="AM66" s="89">
-        <v>11.0</v>
+        <v>32.0</v>
       </c>
       <c r="AN66" s="89">
-        <v>29.0</v>
+        <v>60.0</v>
       </c>
       <c r="AO66" s="88">
-        <v>90.0</v>
+        <v>730.0</v>
       </c>
       <c r="AP66" s="87" t="s">
         <v>200</v>
@@ -37875,22 +37880,22 @@
         <v>201</v>
       </c>
       <c r="AR66" s="88">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="AS66" s="89">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AT66" s="88">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="AU66" s="88">
-        <v>40.9</v>
+        <v>53.2</v>
       </c>
       <c r="AV66" s="89">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="AW66" s="89">
-        <v>56.0</v>
+        <v>30.0</v>
       </c>
       <c r="AX66" s="89" t="s">
         <v>259</v>
@@ -37901,10 +37906,10 @@
     </row>
     <row r="67">
       <c r="A67" s="81" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B67" s="82">
-        <v>108.76</v>
+        <v>104.41</v>
       </c>
       <c r="C67" s="82">
         <v>0.0</v>
@@ -37913,10 +37918,10 @@
         <v>0.0</v>
       </c>
       <c r="E67" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="F67" s="82">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="G67" s="81" t="s">
         <v>168</v>
@@ -37945,10 +37950,10 @@
         <v>168</v>
       </c>
       <c r="S67" s="81" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="T67" s="81" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U67" s="83"/>
       <c r="V67" s="81" t="s">
@@ -37986,10 +37991,10 @@
         <v>66.0</v>
       </c>
       <c r="AH67" s="82">
-        <v>15.23</v>
+        <v>14.62</v>
       </c>
       <c r="AI67" s="82">
-        <v>25.5</v>
+        <v>21.5</v>
       </c>
       <c r="AJ67" s="82">
         <v>75.0</v>
@@ -37998,16 +38003,16 @@
         <v>85.0</v>
       </c>
       <c r="AL67" s="88">
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
       <c r="AM67" s="89">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="AN67" s="89">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="AO67" s="88">
-        <v>180.0</v>
+        <v>90.0</v>
       </c>
       <c r="AP67" s="87" t="s">
         <v>200</v>
@@ -38016,22 +38021,22 @@
         <v>201</v>
       </c>
       <c r="AR67" s="88">
+        <v>3.0</v>
+      </c>
+      <c r="AS67" s="89">
         <v>2.0</v>
       </c>
-      <c r="AS67" s="89">
-        <v>1.0</v>
-      </c>
       <c r="AT67" s="88">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="AU67" s="88">
-        <v>45.8</v>
+        <v>40.9</v>
       </c>
       <c r="AV67" s="89">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="AW67" s="89">
-        <v>50.0</v>
+        <v>56.0</v>
       </c>
       <c r="AX67" s="89" t="s">
         <v>259</v>
@@ -38042,10 +38047,10 @@
     </row>
     <row r="68">
       <c r="A68" s="81" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B68" s="82">
-        <v>100.0</v>
+        <v>108.76</v>
       </c>
       <c r="C68" s="82">
         <v>0.0</v>
@@ -38054,23 +38059,23 @@
         <v>0.0</v>
       </c>
       <c r="E68" s="82">
-        <v>1.0</v>
+        <v>180.0</v>
       </c>
       <c r="F68" s="82">
-        <v>31.0</v>
+        <v>180.0</v>
       </c>
       <c r="G68" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H68" s="82" t="s">
-        <v>325</v>
+        <v>169</v>
       </c>
       <c r="I68" s="83"/>
       <c r="J68" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K68" s="81" t="s">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="L68" s="84"/>
       <c r="M68" s="84"/>
@@ -38086,10 +38091,10 @@
         <v>168</v>
       </c>
       <c r="S68" s="81" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="T68" s="81" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="U68" s="83"/>
       <c r="V68" s="81" t="s">
@@ -38103,19 +38108,19 @@
         <v>177</v>
       </c>
       <c r="Z68" s="85" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="AA68" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB68" s="87" t="s">
-        <v>308</v>
+        <v>220</v>
       </c>
       <c r="AC68" s="82">
-        <v>65.0</v>
+        <v>45.0</v>
       </c>
       <c r="AD68" s="82">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="AE68" s="82">
         <v>70.0</v>
@@ -38127,28 +38132,28 @@
         <v>66.0</v>
       </c>
       <c r="AH68" s="82">
-        <v>14.0</v>
+        <v>15.23</v>
       </c>
       <c r="AI68" s="82">
-        <v>17.5</v>
+        <v>25.5</v>
       </c>
       <c r="AJ68" s="82">
-        <v>40.0</v>
+        <v>75.0</v>
       </c>
       <c r="AK68" s="82">
         <v>85.0</v>
       </c>
       <c r="AL68" s="88">
-        <v>57.8</v>
+        <v>59.8</v>
       </c>
       <c r="AM68" s="89">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="AN68" s="89">
-        <v>33.0</v>
+        <v>28.0</v>
       </c>
       <c r="AO68" s="88">
-        <v>31.0</v>
+        <v>180.0</v>
       </c>
       <c r="AP68" s="87" t="s">
         <v>200</v>
@@ -38157,36 +38162,36 @@
         <v>201</v>
       </c>
       <c r="AR68" s="88">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AS68" s="89">
         <v>1.0</v>
       </c>
       <c r="AT68" s="88">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="AU68" s="88">
-        <v>50.8</v>
+        <v>45.8</v>
       </c>
       <c r="AV68" s="89">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="AW68" s="89">
-        <v>37.0</v>
+        <v>50.0</v>
       </c>
       <c r="AX68" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY68" s="81" t="s">
-        <v>371</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="81" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B69" s="82">
-        <v>104.21</v>
+        <v>100.0</v>
       </c>
       <c r="C69" s="82">
         <v>0.0</v>
@@ -38198,13 +38203,13 @@
         <v>1.0</v>
       </c>
       <c r="F69" s="82">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="G69" s="81" t="s">
         <v>168</v>
       </c>
       <c r="H69" s="82" t="s">
-        <v>205</v>
+        <v>326</v>
       </c>
       <c r="I69" s="83"/>
       <c r="J69" s="81" t="s">
@@ -38227,69 +38232,69 @@
         <v>168</v>
       </c>
       <c r="S69" s="81" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="T69" s="81" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="U69" s="83"/>
       <c r="V69" s="81" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="W69" s="83"/>
-      <c r="X69" s="92" t="s">
-        <v>228</v>
+      <c r="X69" s="85" t="s">
+        <v>176</v>
       </c>
       <c r="Y69" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z69" s="92" t="s">
+      <c r="Z69" s="85" t="s">
         <v>219</v>
       </c>
       <c r="AA69" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB69" s="87" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="AC69" s="82">
-        <v>100.0</v>
+        <v>65.0</v>
       </c>
       <c r="AD69" s="82">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="AE69" s="82">
         <v>70.0</v>
       </c>
       <c r="AF69" s="82">
-        <v>95.0</v>
+        <v>60.0</v>
       </c>
       <c r="AG69" s="82">
-        <v>80.0</v>
+        <v>66.0</v>
       </c>
       <c r="AH69" s="82">
-        <v>0.58</v>
+        <v>14.0</v>
       </c>
       <c r="AI69" s="82">
-        <v>0.0</v>
+        <v>17.5</v>
       </c>
       <c r="AJ69" s="82">
-        <v>16.0</v>
+        <v>40.0</v>
       </c>
       <c r="AK69" s="82">
         <v>85.0</v>
       </c>
       <c r="AL69" s="88">
-        <v>61.2</v>
+        <v>57.8</v>
       </c>
       <c r="AM69" s="89">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="AN69" s="89">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
       <c r="AO69" s="88">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="AP69" s="87" t="s">
         <v>200</v>
@@ -38298,36 +38303,36 @@
         <v>201</v>
       </c>
       <c r="AR69" s="88">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS69" s="89">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="AT69" s="88">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="AU69" s="88">
-        <v>43.2</v>
+        <v>50.8</v>
       </c>
       <c r="AV69" s="89">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="AW69" s="89">
-        <v>54.0</v>
+        <v>37.0</v>
       </c>
       <c r="AX69" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY69" s="81" t="s">
-        <v>183</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="81" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B70" s="82">
-        <v>7.67</v>
+        <v>104.21</v>
       </c>
       <c r="C70" s="82">
         <v>0.0</v>
@@ -38336,7 +38341,7 @@
         <v>0.0</v>
       </c>
       <c r="E70" s="82">
-        <v>2074.0</v>
+        <v>1.0</v>
       </c>
       <c r="F70" s="82">
         <v>0.0</v>
@@ -38345,14 +38350,14 @@
         <v>168</v>
       </c>
       <c r="H70" s="82" t="s">
-        <v>376</v>
+        <v>205</v>
       </c>
       <c r="I70" s="83"/>
       <c r="J70" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K70" s="81" t="s">
-        <v>377</v>
+        <v>171</v>
       </c>
       <c r="L70" s="84"/>
       <c r="M70" s="84"/>
@@ -38362,113 +38367,113 @@
         <v>168</v>
       </c>
       <c r="Q70" s="81" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="R70" s="81" t="s">
         <v>168</v>
       </c>
       <c r="S70" s="81" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="T70" s="81" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="U70" s="83"/>
       <c r="V70" s="81" t="s">
         <v>209</v>
       </c>
       <c r="W70" s="83"/>
-      <c r="X70" s="85" t="s">
-        <v>176</v>
+      <c r="X70" s="92" t="s">
+        <v>228</v>
       </c>
       <c r="Y70" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="Z70" s="85" t="s">
-        <v>178</v>
+      <c r="Z70" s="92" t="s">
+        <v>219</v>
       </c>
       <c r="AA70" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB70" s="87" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="AC70" s="82">
-        <v>25.0</v>
+        <v>100.0</v>
       </c>
       <c r="AD70" s="82">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="AE70" s="82">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
       <c r="AF70" s="82">
         <v>95.0</v>
       </c>
       <c r="AG70" s="82">
-        <v>98.0</v>
+        <v>80.0</v>
       </c>
       <c r="AH70" s="82">
-        <v>12.17</v>
+        <v>0.58</v>
       </c>
       <c r="AI70" s="82">
-        <v>5.5</v>
+        <v>0.0</v>
       </c>
       <c r="AJ70" s="82">
-        <v>75.0</v>
+        <v>16.0</v>
       </c>
       <c r="AK70" s="82">
         <v>85.0</v>
       </c>
       <c r="AL70" s="88">
-        <v>56.8</v>
+        <v>61.2</v>
       </c>
       <c r="AM70" s="89">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="AN70" s="89">
-        <v>35.0</v>
+        <v>23.0</v>
       </c>
       <c r="AO70" s="88">
-        <v>365.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP70" s="87" t="s">
-        <v>379</v>
+        <v>200</v>
       </c>
       <c r="AQ70" s="87" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="AR70" s="88">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="AS70" s="89">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="AT70" s="88">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="AU70" s="88">
-        <v>49.8</v>
+        <v>43.2</v>
       </c>
       <c r="AV70" s="89">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="AW70" s="89">
-        <v>38.0</v>
+        <v>54.0</v>
       </c>
       <c r="AX70" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY70" s="81" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="81" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B71" s="82">
-        <v>7.63</v>
+        <v>7.67</v>
       </c>
       <c r="C71" s="82">
         <v>0.0</v>
@@ -38477,7 +38482,7 @@
         <v>0.0</v>
       </c>
       <c r="E71" s="82">
-        <v>2440.0</v>
+        <v>2074.0</v>
       </c>
       <c r="F71" s="82">
         <v>0.0</v>
@@ -38486,14 +38491,14 @@
         <v>168</v>
       </c>
       <c r="H71" s="82" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I71" s="83"/>
       <c r="J71" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K71" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L71" s="84"/>
       <c r="M71" s="84"/>
@@ -38509,10 +38514,10 @@
         <v>168</v>
       </c>
       <c r="S71" s="81" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="T71" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U71" s="83"/>
       <c r="V71" s="81" t="s">
@@ -38550,10 +38555,10 @@
         <v>98.0</v>
       </c>
       <c r="AH71" s="82">
-        <v>12.13</v>
+        <v>12.17</v>
       </c>
       <c r="AI71" s="82">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AJ71" s="82">
         <v>75.0</v>
@@ -38562,19 +38567,19 @@
         <v>85.0</v>
       </c>
       <c r="AL71" s="88">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="AM71" s="89">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
       <c r="AN71" s="89">
-        <v>37.0</v>
+        <v>35.0</v>
       </c>
       <c r="AO71" s="88">
         <v>365.0</v>
       </c>
       <c r="AP71" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ71" s="87" t="s">
         <v>181</v>
@@ -38589,13 +38594,13 @@
         <v>7.0</v>
       </c>
       <c r="AU71" s="88">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="AV71" s="89">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="AW71" s="89">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="AX71" s="89" t="s">
         <v>259</v>
@@ -38606,10 +38611,10 @@
     </row>
     <row r="72">
       <c r="A72" s="81" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B72" s="82">
-        <v>7.6</v>
+        <v>7.63</v>
       </c>
       <c r="C72" s="82">
         <v>0.0</v>
@@ -38618,7 +38623,7 @@
         <v>0.0</v>
       </c>
       <c r="E72" s="82">
-        <v>2805.0</v>
+        <v>2440.0</v>
       </c>
       <c r="F72" s="82">
         <v>0.0</v>
@@ -38627,14 +38632,14 @@
         <v>168</v>
       </c>
       <c r="H72" s="82" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I72" s="83"/>
       <c r="J72" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K72" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L72" s="84"/>
       <c r="M72" s="84"/>
@@ -38650,10 +38655,10 @@
         <v>168</v>
       </c>
       <c r="S72" s="81" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="T72" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U72" s="83"/>
       <c r="V72" s="81" t="s">
@@ -38691,10 +38696,10 @@
         <v>98.0</v>
       </c>
       <c r="AH72" s="82">
-        <v>12.1</v>
+        <v>12.13</v>
       </c>
       <c r="AI72" s="82">
-        <v>5.0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ72" s="82">
         <v>75.0</v>
@@ -38706,16 +38711,16 @@
         <v>56.7</v>
       </c>
       <c r="AM72" s="89">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AN72" s="89">
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="AO72" s="88">
         <v>365.0</v>
       </c>
       <c r="AP72" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ72" s="87" t="s">
         <v>181</v>
@@ -38733,10 +38738,10 @@
         <v>49.7</v>
       </c>
       <c r="AV72" s="89">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="AW72" s="89">
-        <v>40.0</v>
+        <v>39.0</v>
       </c>
       <c r="AX72" s="89" t="s">
         <v>259</v>
@@ -38747,10 +38752,10 @@
     </row>
     <row r="73">
       <c r="A73" s="81" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B73" s="82">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="C73" s="82">
         <v>0.0</v>
@@ -38759,7 +38764,7 @@
         <v>0.0</v>
       </c>
       <c r="E73" s="82">
-        <v>3170.0</v>
+        <v>2805.0</v>
       </c>
       <c r="F73" s="82">
         <v>0.0</v>
@@ -38768,14 +38773,14 @@
         <v>168</v>
       </c>
       <c r="H73" s="82" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I73" s="83"/>
       <c r="J73" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K73" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L73" s="84"/>
       <c r="M73" s="84"/>
@@ -38791,10 +38796,10 @@
         <v>168</v>
       </c>
       <c r="S73" s="81" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="T73" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U73" s="83"/>
       <c r="V73" s="81" t="s">
@@ -38832,10 +38837,10 @@
         <v>98.0</v>
       </c>
       <c r="AH73" s="82">
-        <v>12.06</v>
+        <v>12.1</v>
       </c>
       <c r="AI73" s="82">
-        <v>4.8</v>
+        <v>5.0</v>
       </c>
       <c r="AJ73" s="82">
         <v>75.0</v>
@@ -38847,16 +38852,16 @@
         <v>56.7</v>
       </c>
       <c r="AM73" s="89">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="AN73" s="89">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="AO73" s="88">
         <v>365.0</v>
       </c>
       <c r="AP73" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ73" s="87" t="s">
         <v>181</v>
@@ -38874,10 +38879,10 @@
         <v>49.7</v>
       </c>
       <c r="AV73" s="89">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="AW73" s="89">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="AX73" s="89" t="s">
         <v>259</v>
@@ -38888,10 +38893,10 @@
     </row>
     <row r="74">
       <c r="A74" s="81" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B74" s="82">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="C74" s="82">
         <v>0.0</v>
@@ -38900,7 +38905,7 @@
         <v>0.0</v>
       </c>
       <c r="E74" s="82">
-        <v>3535.0</v>
+        <v>3170.0</v>
       </c>
       <c r="F74" s="82">
         <v>0.0</v>
@@ -38909,14 +38914,14 @@
         <v>168</v>
       </c>
       <c r="H74" s="82" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I74" s="83"/>
       <c r="J74" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K74" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L74" s="84"/>
       <c r="M74" s="84"/>
@@ -38932,10 +38937,10 @@
         <v>168</v>
       </c>
       <c r="S74" s="81" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="T74" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U74" s="83"/>
       <c r="V74" s="81" t="s">
@@ -38973,10 +38978,10 @@
         <v>98.0</v>
       </c>
       <c r="AH74" s="82">
-        <v>12.0</v>
+        <v>12.06</v>
       </c>
       <c r="AI74" s="82">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AJ74" s="82">
         <v>75.0</v>
@@ -38985,19 +38990,19 @@
         <v>85.0</v>
       </c>
       <c r="AL74" s="88">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="AM74" s="89">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="AN74" s="89">
-        <v>41.0</v>
+        <v>39.0</v>
       </c>
       <c r="AO74" s="88">
         <v>365.0</v>
       </c>
       <c r="AP74" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ74" s="87" t="s">
         <v>181</v>
@@ -39012,13 +39017,13 @@
         <v>7.0</v>
       </c>
       <c r="AU74" s="88">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="AV74" s="89">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="AW74" s="89">
-        <v>43.0</v>
+        <v>41.0</v>
       </c>
       <c r="AX74" s="89" t="s">
         <v>259</v>
@@ -39029,10 +39034,10 @@
     </row>
     <row r="75">
       <c r="A75" s="81" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B75" s="82">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="C75" s="82">
         <v>0.0</v>
@@ -39041,7 +39046,7 @@
         <v>0.0</v>
       </c>
       <c r="E75" s="82">
-        <v>3901.0</v>
+        <v>3535.0</v>
       </c>
       <c r="F75" s="82">
         <v>0.0</v>
@@ -39050,14 +39055,14 @@
         <v>168</v>
       </c>
       <c r="H75" s="82" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I75" s="83"/>
       <c r="J75" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K75" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L75" s="84"/>
       <c r="M75" s="84"/>
@@ -39073,10 +39078,10 @@
         <v>168</v>
       </c>
       <c r="S75" s="81" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="T75" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U75" s="83"/>
       <c r="V75" s="81" t="s">
@@ -39114,10 +39119,10 @@
         <v>98.0</v>
       </c>
       <c r="AH75" s="82">
-        <v>11.94</v>
+        <v>12.0</v>
       </c>
       <c r="AI75" s="82">
-        <v>4.0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ75" s="82">
         <v>75.0</v>
@@ -39126,19 +39131,19 @@
         <v>85.0</v>
       </c>
       <c r="AL75" s="88">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="AM75" s="89">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="AN75" s="89">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="AO75" s="88">
         <v>365.0</v>
       </c>
       <c r="AP75" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ75" s="87" t="s">
         <v>181</v>
@@ -39153,13 +39158,13 @@
         <v>7.0</v>
       </c>
       <c r="AU75" s="88">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="AV75" s="89">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="AW75" s="89">
-        <v>44.0</v>
+        <v>43.0</v>
       </c>
       <c r="AX75" s="89" t="s">
         <v>259</v>
@@ -39170,10 +39175,10 @@
     </row>
     <row r="76">
       <c r="A76" s="81" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B76" s="82">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="C76" s="82">
         <v>0.0</v>
@@ -39182,7 +39187,7 @@
         <v>0.0</v>
       </c>
       <c r="E76" s="82">
-        <v>4266.0</v>
+        <v>3901.0</v>
       </c>
       <c r="F76" s="82">
         <v>0.0</v>
@@ -39191,14 +39196,14 @@
         <v>168</v>
       </c>
       <c r="H76" s="82" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I76" s="83"/>
       <c r="J76" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K76" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L76" s="84"/>
       <c r="M76" s="84"/>
@@ -39214,10 +39219,10 @@
         <v>168</v>
       </c>
       <c r="S76" s="81" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="T76" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U76" s="83"/>
       <c r="V76" s="81" t="s">
@@ -39255,10 +39260,10 @@
         <v>98.0</v>
       </c>
       <c r="AH76" s="82">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="AI76" s="82">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="AJ76" s="82">
         <v>75.0</v>
@@ -39267,19 +39272,19 @@
         <v>85.0</v>
       </c>
       <c r="AL76" s="88">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="AM76" s="89">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="AN76" s="89">
-        <v>44.0</v>
+        <v>42.0</v>
       </c>
       <c r="AO76" s="88">
         <v>365.0</v>
       </c>
       <c r="AP76" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ76" s="87" t="s">
         <v>181</v>
@@ -39294,13 +39299,13 @@
         <v>7.0</v>
       </c>
       <c r="AU76" s="88">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="AV76" s="89">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AW76" s="89">
-        <v>45.0</v>
+        <v>44.0</v>
       </c>
       <c r="AX76" s="89" t="s">
         <v>259</v>
@@ -39311,10 +39316,10 @@
     </row>
     <row r="77">
       <c r="A77" s="81" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B77" s="82">
-        <v>7.31</v>
+        <v>7.38</v>
       </c>
       <c r="C77" s="82">
         <v>0.0</v>
@@ -39323,7 +39328,7 @@
         <v>0.0</v>
       </c>
       <c r="E77" s="82">
-        <v>4631.0</v>
+        <v>4266.0</v>
       </c>
       <c r="F77" s="82">
         <v>0.0</v>
@@ -39332,14 +39337,14 @@
         <v>168</v>
       </c>
       <c r="H77" s="82" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I77" s="83"/>
       <c r="J77" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K77" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L77" s="84"/>
       <c r="M77" s="84"/>
@@ -39355,10 +39360,10 @@
         <v>168</v>
       </c>
       <c r="S77" s="81" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="T77" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U77" s="83"/>
       <c r="V77" s="81" t="s">
@@ -39396,10 +39401,10 @@
         <v>98.0</v>
       </c>
       <c r="AH77" s="82">
-        <v>11.81</v>
+        <v>11.88</v>
       </c>
       <c r="AI77" s="82">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AJ77" s="82">
         <v>75.0</v>
@@ -39408,40 +39413,40 @@
         <v>85.0</v>
       </c>
       <c r="AL77" s="88">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
       <c r="AM77" s="89">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="AN77" s="89">
-        <v>45.0</v>
+        <v>44.0</v>
       </c>
       <c r="AO77" s="88">
         <v>365.0</v>
       </c>
       <c r="AP77" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ77" s="87" t="s">
         <v>181</v>
       </c>
       <c r="AR77" s="88">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS77" s="89">
         <v>1.0</v>
       </c>
       <c r="AT77" s="88">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="AU77" s="88">
-        <v>38.3</v>
+        <v>49.4</v>
       </c>
       <c r="AV77" s="89">
-        <v>33.0</v>
+        <v>23.0</v>
       </c>
       <c r="AW77" s="89">
-        <v>60.0</v>
+        <v>45.0</v>
       </c>
       <c r="AX77" s="89" t="s">
         <v>259</v>
@@ -39452,10 +39457,10 @@
     </row>
     <row r="78">
       <c r="A78" s="81" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B78" s="82">
-        <v>7.57</v>
+        <v>7.31</v>
       </c>
       <c r="C78" s="82">
         <v>0.0</v>
@@ -39464,7 +39469,7 @@
         <v>0.0</v>
       </c>
       <c r="E78" s="82">
-        <v>2318.0</v>
+        <v>4631.0</v>
       </c>
       <c r="F78" s="82">
         <v>0.0</v>
@@ -39473,14 +39478,14 @@
         <v>168</v>
       </c>
       <c r="H78" s="82" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I78" s="83"/>
       <c r="J78" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K78" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L78" s="84"/>
       <c r="M78" s="84"/>
@@ -39496,10 +39501,10 @@
         <v>168</v>
       </c>
       <c r="S78" s="81" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="T78" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U78" s="83"/>
       <c r="V78" s="81" t="s">
@@ -39537,10 +39542,10 @@
         <v>98.0</v>
       </c>
       <c r="AH78" s="82">
-        <v>12.07</v>
+        <v>11.81</v>
       </c>
       <c r="AI78" s="82">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AJ78" s="82">
         <v>75.0</v>
@@ -39549,40 +39554,40 @@
         <v>85.0</v>
       </c>
       <c r="AL78" s="88">
-        <v>56.7</v>
+        <v>56.3</v>
       </c>
       <c r="AM78" s="89">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="AN78" s="89">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="AO78" s="88">
         <v>365.0</v>
       </c>
       <c r="AP78" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ78" s="87" t="s">
         <v>181</v>
       </c>
       <c r="AR78" s="88">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="AS78" s="89">
         <v>1.0</v>
       </c>
       <c r="AT78" s="88">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="AU78" s="88">
-        <v>49.7</v>
+        <v>38.3</v>
       </c>
       <c r="AV78" s="89">
-        <v>20.0</v>
+        <v>33.0</v>
       </c>
       <c r="AW78" s="89">
-        <v>42.0</v>
+        <v>60.0</v>
       </c>
       <c r="AX78" s="89" t="s">
         <v>259</v>
@@ -39593,10 +39598,10 @@
     </row>
     <row r="79">
       <c r="A79" s="81" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B79" s="82">
-        <v>5.8</v>
+        <v>7.57</v>
       </c>
       <c r="C79" s="82">
         <v>0.0</v>
@@ -39605,7 +39610,7 @@
         <v>0.0</v>
       </c>
       <c r="E79" s="82">
-        <v>3285.0</v>
+        <v>2318.0</v>
       </c>
       <c r="F79" s="82">
         <v>0.0</v>
@@ -39614,14 +39619,14 @@
         <v>168</v>
       </c>
       <c r="H79" s="82" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I79" s="83"/>
       <c r="J79" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K79" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L79" s="84"/>
       <c r="M79" s="84"/>
@@ -39637,10 +39642,10 @@
         <v>168</v>
       </c>
       <c r="S79" s="81" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T79" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U79" s="83"/>
       <c r="V79" s="81" t="s">
@@ -39678,10 +39683,10 @@
         <v>98.0</v>
       </c>
       <c r="AH79" s="82">
-        <v>10.3</v>
+        <v>12.07</v>
       </c>
       <c r="AI79" s="82">
-        <v>0.0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ79" s="82">
         <v>75.0</v>
@@ -39690,40 +39695,40 @@
         <v>85.0</v>
       </c>
       <c r="AL79" s="88">
-        <v>55.6</v>
+        <v>56.7</v>
       </c>
       <c r="AM79" s="89">
-        <v>25.0</v>
+        <v>14.0</v>
       </c>
       <c r="AN79" s="89">
-        <v>51.0</v>
+        <v>40.0</v>
       </c>
       <c r="AO79" s="88">
         <v>365.0</v>
       </c>
       <c r="AP79" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ79" s="87" t="s">
         <v>181</v>
       </c>
       <c r="AR79" s="88">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS79" s="89">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="AT79" s="88">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="AU79" s="88">
-        <v>37.6</v>
+        <v>49.7</v>
       </c>
       <c r="AV79" s="89">
-        <v>37.0</v>
+        <v>20.0</v>
       </c>
       <c r="AW79" s="89">
-        <v>64.0</v>
+        <v>42.0</v>
       </c>
       <c r="AX79" s="89" t="s">
         <v>259</v>
@@ -39734,10 +39739,10 @@
     </row>
     <row r="80">
       <c r="A80" s="81" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B80" s="82">
-        <v>7.34</v>
+        <v>5.8</v>
       </c>
       <c r="C80" s="82">
         <v>0.0</v>
@@ -39746,7 +39751,7 @@
         <v>0.0</v>
       </c>
       <c r="E80" s="82">
-        <v>4052.0</v>
+        <v>3285.0</v>
       </c>
       <c r="F80" s="82">
         <v>0.0</v>
@@ -39755,14 +39760,14 @@
         <v>168</v>
       </c>
       <c r="H80" s="82" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I80" s="83"/>
       <c r="J80" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K80" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L80" s="84"/>
       <c r="M80" s="84"/>
@@ -39778,10 +39783,10 @@
         <v>168</v>
       </c>
       <c r="S80" s="81" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="T80" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U80" s="83"/>
       <c r="V80" s="81" t="s">
@@ -39819,10 +39824,10 @@
         <v>98.0</v>
       </c>
       <c r="AH80" s="82">
-        <v>11.84</v>
+        <v>10.3</v>
       </c>
       <c r="AI80" s="82">
-        <v>3.3</v>
+        <v>0.0</v>
       </c>
       <c r="AJ80" s="82">
         <v>75.0</v>
@@ -39831,40 +39836,40 @@
         <v>85.0</v>
       </c>
       <c r="AL80" s="88">
-        <v>56.3</v>
+        <v>55.6</v>
       </c>
       <c r="AM80" s="89">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="AN80" s="89">
-        <v>46.0</v>
+        <v>51.0</v>
       </c>
       <c r="AO80" s="88">
         <v>365.0</v>
       </c>
       <c r="AP80" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ80" s="87" t="s">
         <v>181</v>
       </c>
       <c r="AR80" s="88">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="AS80" s="89">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="AT80" s="88">
-        <v>14.0</v>
+        <v>18.0</v>
       </c>
       <c r="AU80" s="88">
-        <v>42.3</v>
+        <v>37.6</v>
       </c>
       <c r="AV80" s="89">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
       <c r="AW80" s="89">
-        <v>55.0</v>
+        <v>64.0</v>
       </c>
       <c r="AX80" s="89" t="s">
         <v>259</v>
@@ -39875,10 +39880,10 @@
     </row>
     <row r="81">
       <c r="A81" s="81" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B81" s="82">
-        <v>13.39</v>
+        <v>7.34</v>
       </c>
       <c r="C81" s="82">
         <v>0.0</v>
@@ -39887,7 +39892,7 @@
         <v>0.0</v>
       </c>
       <c r="E81" s="82">
-        <v>996.0</v>
+        <v>4052.0</v>
       </c>
       <c r="F81" s="82">
         <v>0.0</v>
@@ -39896,14 +39901,14 @@
         <v>168</v>
       </c>
       <c r="H81" s="82" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I81" s="83"/>
       <c r="J81" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K81" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L81" s="84"/>
       <c r="M81" s="84"/>
@@ -39913,16 +39918,16 @@
         <v>168</v>
       </c>
       <c r="Q81" s="81" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="R81" s="81" t="s">
         <v>168</v>
       </c>
       <c r="S81" s="81" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="T81" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U81" s="83"/>
       <c r="V81" s="81" t="s">
@@ -39936,7 +39941,7 @@
         <v>177</v>
       </c>
       <c r="Z81" s="85" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="AA81" s="87" t="s">
         <v>170</v>
@@ -39960,10 +39965,10 @@
         <v>98.0</v>
       </c>
       <c r="AH81" s="82">
-        <v>13.39</v>
+        <v>11.84</v>
       </c>
       <c r="AI81" s="82">
-        <v>13.5</v>
+        <v>3.3</v>
       </c>
       <c r="AJ81" s="82">
         <v>75.0</v>
@@ -39972,54 +39977,54 @@
         <v>85.0</v>
       </c>
       <c r="AL81" s="88">
-        <v>58.6</v>
+        <v>56.3</v>
       </c>
       <c r="AM81" s="89">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="AN81" s="89">
-        <v>30.0</v>
+        <v>46.0</v>
       </c>
       <c r="AO81" s="88">
-        <v>199.0</v>
+        <v>365.0</v>
       </c>
       <c r="AP81" s="87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ81" s="87" t="s">
         <v>181</v>
       </c>
       <c r="AR81" s="88">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="AS81" s="89">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AT81" s="88">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="AU81" s="88">
-        <v>58.6</v>
+        <v>42.3</v>
       </c>
       <c r="AV81" s="89">
-        <v>3.0</v>
+        <v>29.0</v>
       </c>
       <c r="AW81" s="89">
-        <v>19.0</v>
+        <v>55.0</v>
       </c>
       <c r="AX81" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY81" s="81" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="81" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B82" s="82">
-        <v>1.0</v>
+        <v>13.39</v>
       </c>
       <c r="C82" s="82">
         <v>0.0</v>
@@ -40028,7 +40033,7 @@
         <v>0.0</v>
       </c>
       <c r="E82" s="82">
-        <v>1095.0</v>
+        <v>996.0</v>
       </c>
       <c r="F82" s="82">
         <v>0.0</v>
@@ -40037,14 +40042,14 @@
         <v>168</v>
       </c>
       <c r="H82" s="82" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="I82" s="83"/>
       <c r="J82" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K82" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L82" s="84"/>
       <c r="M82" s="84"/>
@@ -40054,20 +40059,20 @@
         <v>168</v>
       </c>
       <c r="Q82" s="81" t="s">
-        <v>297</v>
+        <v>212</v>
       </c>
       <c r="R82" s="81" t="s">
         <v>168</v>
       </c>
       <c r="S82" s="81" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="T82" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U82" s="83"/>
       <c r="V82" s="81" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="W82" s="83"/>
       <c r="X82" s="85" t="s">
@@ -40083,10 +40088,10 @@
         <v>170</v>
       </c>
       <c r="AB82" s="87" t="s">
-        <v>308</v>
+        <v>179</v>
       </c>
       <c r="AC82" s="82">
-        <v>85.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD82" s="82">
         <v>100.0</v>
@@ -40095,37 +40100,37 @@
         <v>100.0</v>
       </c>
       <c r="AF82" s="82">
-        <v>100.0</v>
+        <v>95.0</v>
       </c>
       <c r="AG82" s="82">
-        <v>100.0</v>
+        <v>98.0</v>
       </c>
       <c r="AH82" s="82">
+        <v>13.39</v>
+      </c>
+      <c r="AI82" s="82">
         <v>13.5</v>
       </c>
-      <c r="AI82" s="82">
-        <v>14.2</v>
-      </c>
       <c r="AJ82" s="82">
-        <v>72.5</v>
+        <v>75.0</v>
       </c>
       <c r="AK82" s="82">
         <v>85.0</v>
       </c>
       <c r="AL82" s="88">
-        <v>73.9</v>
+        <v>58.6</v>
       </c>
       <c r="AM82" s="89">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="AN82" s="89">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="AO82" s="88">
-        <v>27.0</v>
+        <v>199.0</v>
       </c>
       <c r="AP82" s="87" t="s">
-        <v>415</v>
+        <v>380</v>
       </c>
       <c r="AQ82" s="87" t="s">
         <v>181</v>
@@ -40140,27 +40145,27 @@
         <v>0.0</v>
       </c>
       <c r="AU82" s="88">
-        <v>73.9</v>
+        <v>58.6</v>
       </c>
       <c r="AV82" s="89">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="AW82" s="89">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="AX82" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY82" s="81" t="s">
-        <v>299</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="81" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B83" s="82">
-        <v>0.09</v>
+        <v>1.0</v>
       </c>
       <c r="C83" s="82">
         <v>0.0</v>
@@ -40169,7 +40174,7 @@
         <v>0.0</v>
       </c>
       <c r="E83" s="82">
-        <v>1785.0</v>
+        <v>1095.0</v>
       </c>
       <c r="F83" s="82">
         <v>0.0</v>
@@ -40178,14 +40183,14 @@
         <v>168</v>
       </c>
       <c r="H83" s="82" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="I83" s="83"/>
       <c r="J83" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K83" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L83" s="84"/>
       <c r="M83" s="84"/>
@@ -40201,14 +40206,14 @@
         <v>168</v>
       </c>
       <c r="S83" s="81" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="T83" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U83" s="83"/>
       <c r="V83" s="81" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="W83" s="83"/>
       <c r="X83" s="85" t="s">
@@ -40227,81 +40232,81 @@
         <v>308</v>
       </c>
       <c r="AC83" s="82">
-        <v>65.0</v>
+        <v>85.0</v>
       </c>
       <c r="AD83" s="82">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
       <c r="AE83" s="82">
         <v>100.0</v>
       </c>
       <c r="AF83" s="82">
-        <v>95.0</v>
+        <v>100.0</v>
       </c>
       <c r="AG83" s="82">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
       <c r="AH83" s="82">
-        <v>14.09</v>
+        <v>13.5</v>
       </c>
       <c r="AI83" s="82">
-        <v>18.1</v>
+        <v>14.2</v>
       </c>
       <c r="AJ83" s="82">
-        <v>75.0</v>
+        <v>72.5</v>
       </c>
       <c r="AK83" s="82">
         <v>85.0</v>
       </c>
       <c r="AL83" s="88">
-        <v>67.8</v>
+        <v>73.9</v>
       </c>
       <c r="AM83" s="89">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AN83" s="89">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="AO83" s="88">
-        <v>35.0</v>
+        <v>27.0</v>
       </c>
       <c r="AP83" s="87" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ83" s="87" t="s">
         <v>181</v>
       </c>
       <c r="AR83" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AS83" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="AT83" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AU83" s="88">
+        <v>73.9</v>
+      </c>
+      <c r="AV83" s="89">
         <v>1.0</v>
       </c>
-      <c r="AS83" s="89">
-        <v>1.0</v>
-      </c>
-      <c r="AT83" s="88">
-        <v>7.0</v>
-      </c>
-      <c r="AU83" s="88">
-        <v>60.8</v>
-      </c>
-      <c r="AV83" s="89">
-        <v>3.0</v>
-      </c>
       <c r="AW83" s="89">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="AX83" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY83" s="81" t="s">
-        <v>419</v>
+        <v>299</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="81" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B84" s="82">
-        <v>100.47</v>
+        <v>0.09</v>
       </c>
       <c r="C84" s="82">
         <v>0.0</v>
@@ -40310,7 +40315,7 @@
         <v>0.0</v>
       </c>
       <c r="E84" s="82">
-        <v>1.0</v>
+        <v>1785.0</v>
       </c>
       <c r="F84" s="82">
         <v>0.0</v>
@@ -40319,14 +40324,14 @@
         <v>168</v>
       </c>
       <c r="H84" s="82" t="s">
-        <v>169</v>
+        <v>418</v>
       </c>
       <c r="I84" s="83"/>
       <c r="J84" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K84" s="81" t="s">
-        <v>171</v>
+        <v>378</v>
       </c>
       <c r="L84" s="84"/>
       <c r="M84" s="84"/>
@@ -40336,16 +40341,16 @@
         <v>168</v>
       </c>
       <c r="Q84" s="81" t="s">
-        <v>195</v>
+        <v>297</v>
       </c>
       <c r="R84" s="81" t="s">
         <v>168</v>
       </c>
       <c r="S84" s="81" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="T84" s="81" t="s">
-        <v>186</v>
+        <v>378</v>
       </c>
       <c r="U84" s="83"/>
       <c r="V84" s="81" t="s">
@@ -40365,84 +40370,84 @@
         <v>170</v>
       </c>
       <c r="AB84" s="87" t="s">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="AC84" s="82">
+        <v>65.0</v>
+      </c>
+      <c r="AD84" s="82">
+        <v>90.0</v>
+      </c>
+      <c r="AE84" s="82">
         <v>100.0</v>
-      </c>
-      <c r="AD84" s="82">
-        <v>100.0</v>
-      </c>
-      <c r="AE84" s="82">
-        <v>70.0</v>
       </c>
       <c r="AF84" s="82">
         <v>95.0</v>
       </c>
       <c r="AG84" s="82">
-        <v>80.0</v>
+        <v>98.0</v>
       </c>
       <c r="AH84" s="82">
-        <v>0.56</v>
+        <v>14.09</v>
       </c>
       <c r="AI84" s="82">
-        <v>0.0</v>
+        <v>18.1</v>
       </c>
       <c r="AJ84" s="82">
-        <v>16.0</v>
+        <v>75.0</v>
       </c>
       <c r="AK84" s="82">
         <v>85.0</v>
       </c>
       <c r="AL84" s="88">
-        <v>64.8</v>
+        <v>67.8</v>
       </c>
       <c r="AM84" s="89">
+        <v>2.0</v>
+      </c>
+      <c r="AN84" s="89">
         <v>10.0</v>
       </c>
-      <c r="AN84" s="89">
-        <v>16.0</v>
-      </c>
       <c r="AO84" s="88">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="AP84" s="87" t="s">
-        <v>200</v>
+        <v>416</v>
       </c>
       <c r="AQ84" s="87" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="AR84" s="88">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AS84" s="89">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="AT84" s="88">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="AU84" s="88">
-        <v>46.8</v>
+        <v>60.8</v>
       </c>
       <c r="AV84" s="89">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="AW84" s="89">
-        <v>48.0</v>
+        <v>14.0</v>
       </c>
       <c r="AX84" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY84" s="81" t="s">
-        <v>183</v>
+        <v>420</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="81" t="s">
-        <v>108</v>
+        <v>421</v>
       </c>
       <c r="B85" s="82">
-        <v>220.0</v>
+        <v>100.47</v>
       </c>
       <c r="C85" s="82">
         <v>0.0</v>
@@ -40451,10 +40456,10 @@
         <v>0.0</v>
       </c>
       <c r="E85" s="82">
-        <v>60.0</v>
+        <v>1.0</v>
       </c>
       <c r="F85" s="82">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="G85" s="81" t="s">
         <v>168</v>
@@ -40462,14 +40467,12 @@
       <c r="H85" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="I85" s="82">
-        <v>3000.0</v>
-      </c>
+      <c r="I85" s="83"/>
       <c r="J85" s="81" t="s">
         <v>170</v>
       </c>
       <c r="K85" s="81" t="s">
-        <v>255</v>
+        <v>171</v>
       </c>
       <c r="L85" s="84"/>
       <c r="M85" s="84"/>
@@ -40482,72 +40485,72 @@
         <v>195</v>
       </c>
       <c r="R85" s="81" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S85" s="81" t="s">
         <v>422</v>
       </c>
       <c r="T85" s="81" t="s">
-        <v>423</v>
+        <v>186</v>
       </c>
       <c r="U85" s="83"/>
       <c r="V85" s="81" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="W85" s="83"/>
-      <c r="X85" s="94" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y85" s="97" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z85" s="94" t="s">
+      <c r="X85" s="85" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y85" s="86" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z85" s="85" t="s">
         <v>219</v>
       </c>
       <c r="AA85" s="87" t="s">
         <v>170</v>
       </c>
       <c r="AB85" s="87" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="AC85" s="82">
-        <v>65.0</v>
+        <v>100.0</v>
       </c>
       <c r="AD85" s="82">
         <v>100.0</v>
       </c>
       <c r="AE85" s="82">
-        <v>90.0</v>
+        <v>70.0</v>
       </c>
       <c r="AF85" s="82">
-        <v>60.0</v>
+        <v>95.0</v>
       </c>
       <c r="AG85" s="82">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="AH85" s="82">
-        <v>30.8</v>
+        <v>0.56</v>
       </c>
       <c r="AI85" s="82">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="AJ85" s="82">
-        <v>75.0</v>
+        <v>16.0</v>
       </c>
       <c r="AK85" s="82">
         <v>85.0</v>
       </c>
       <c r="AL85" s="88">
-        <v>83.6</v>
+        <v>64.8</v>
       </c>
       <c r="AM85" s="89">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="AN85" s="89">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="AO85" s="88">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="AP85" s="87" t="s">
         <v>200</v>
@@ -40556,34 +40559,172 @@
         <v>201</v>
       </c>
       <c r="AR85" s="88">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="AS85" s="89">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="AT85" s="88">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="AU85" s="88">
-        <v>83.6</v>
+        <v>46.8</v>
       </c>
       <c r="AV85" s="89">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="AW85" s="89">
-        <v>1.0</v>
+        <v>48.0</v>
       </c>
       <c r="AX85" s="89" t="s">
         <v>259</v>
       </c>
       <c r="AY85" s="81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="B86" s="82">
+        <v>220.0</v>
+      </c>
+      <c r="C86" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="D86" s="82">
+        <v>0.0</v>
+      </c>
+      <c r="E86" s="82">
+        <v>60.0</v>
+      </c>
+      <c r="F86" s="82">
+        <v>60.0</v>
+      </c>
+      <c r="G86" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="H86" s="82" t="s">
+        <v>169</v>
+      </c>
+      <c r="I86" s="82">
+        <v>3000.0</v>
+      </c>
+      <c r="J86" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="K86" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="L86" s="84"/>
+      <c r="M86" s="84"/>
+      <c r="N86" s="84"/>
+      <c r="O86" s="84"/>
+      <c r="P86" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q86" s="81" t="s">
+        <v>195</v>
+      </c>
+      <c r="R86" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="S86" s="81" t="s">
+        <v>423</v>
+      </c>
+      <c r="T86" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="U86" s="83"/>
+      <c r="V86" s="81" t="s">
+        <v>175</v>
+      </c>
+      <c r="W86" s="83"/>
+      <c r="X86" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y86" s="97" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z86" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA86" s="87" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB86" s="87" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC86" s="82">
+        <v>65.0</v>
+      </c>
+      <c r="AD86" s="82">
+        <v>100.0</v>
+      </c>
+      <c r="AE86" s="82">
+        <v>90.0</v>
+      </c>
+      <c r="AF86" s="82">
+        <v>60.0</v>
+      </c>
+      <c r="AG86" s="82">
+        <v>78.0</v>
+      </c>
+      <c r="AH86" s="82">
+        <v>30.8</v>
+      </c>
+      <c r="AI86" s="82">
+        <v>100.0</v>
+      </c>
+      <c r="AJ86" s="82">
+        <v>75.0</v>
+      </c>
+      <c r="AK86" s="82">
+        <v>85.0</v>
+      </c>
+      <c r="AL86" s="88">
+        <v>83.6</v>
+      </c>
+      <c r="AM86" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="AN86" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="AO86" s="88">
+        <v>60.0</v>
+      </c>
+      <c r="AP86" s="87" t="s">
+        <v>200</v>
+      </c>
+      <c r="AQ86" s="87" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR86" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AS86" s="89">
+        <v>0.0</v>
+      </c>
+      <c r="AT86" s="88">
+        <v>0.0</v>
+      </c>
+      <c r="AU86" s="88">
+        <v>83.6</v>
+      </c>
+      <c r="AV86" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="AW86" s="89">
+        <v>1.0</v>
+      </c>
+      <c r="AX86" s="89" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY86" s="81" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="99"/>
-      <c r="G86" s="84"/>
-      <c r="I86" s="100"/>
     </row>
     <row r="87">
       <c r="B87" s="99"/>
@@ -45120,10 +45261,15 @@
       <c r="G993" s="84"/>
       <c r="I993" s="100"/>
     </row>
+    <row r="994">
+      <c r="B994" s="99"/>
+      <c r="G994" s="84"/>
+      <c r="I994" s="100"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$AY$85">
-    <sortState ref="A1:AY85">
-      <sortCondition ref="AX1:AX85"/>
+  <autoFilter ref="$A$1:$AY$86">
+    <sortState ref="A1:AY86">
+      <sortCondition ref="AX1:AX86"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -384,7 +384,7 @@
     <t xml:space="preserve">Lote 3000 mai. </t>
   </si>
   <si>
-    <t>Lote 2780 mai.</t>
+    <t>Lote 3400 mai.</t>
   </si>
   <si>
     <t>Taxa_Base_CDI</t>
@@ -1866,11 +1866,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="127065377"/>
-        <c:axId val="75342076"/>
+        <c:axId val="549310949"/>
+        <c:axId val="844051201"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="127065377"/>
+        <c:axId val="549310949"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1922,10 +1922,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75342076"/>
+        <c:crossAx val="844051201"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75342076"/>
+        <c:axId val="844051201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1989,7 +1989,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="127065377"/>
+        <c:crossAx val="549310949"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -24142,7 +24142,7 @@
         <v>46150.0</v>
       </c>
       <c r="D15" s="26">
-        <v>2777.0</v>
+        <v>3429.0</v>
       </c>
       <c r="E15" s="66" t="s">
         <v>106</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1878,11 +1878,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1040766129"/>
-        <c:axId val="192004381"/>
+        <c:axId val="1751389024"/>
+        <c:axId val="1735377195"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1040766129"/>
+        <c:axId val="1751389024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,10 +1934,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="192004381"/>
+        <c:crossAx val="1735377195"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="192004381"/>
+        <c:axId val="1735377195"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1040766129"/>
+        <c:crossAx val="1751389024"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1878,11 +1878,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1751389024"/>
-        <c:axId val="1735377195"/>
+        <c:axId val="351151564"/>
+        <c:axId val="965636631"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1751389024"/>
+        <c:axId val="351151564"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,10 +1934,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1735377195"/>
+        <c:crossAx val="965636631"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1735377195"/>
+        <c:axId val="965636631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1751389024"/>
+        <c:crossAx val="351151564"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="427">
   <si>
     <t>Mês</t>
   </si>
@@ -1878,11 +1878,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="351151564"/>
-        <c:axId val="965636631"/>
+        <c:axId val="169851099"/>
+        <c:axId val="974873360"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="351151564"/>
+        <c:axId val="169851099"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,10 +1934,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="965636631"/>
+        <c:crossAx val="974873360"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="965636631"/>
+        <c:axId val="974873360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="351151564"/>
+        <c:crossAx val="169851099"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -13985,8 +13985,12 @@
       <c r="C107" s="46">
         <v>98.88</v>
       </c>
-      <c r="D107" s="42"/>
-      <c r="E107" s="42"/>
+      <c r="D107" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E107" s="58" t="s">
+        <v>53</v>
+      </c>
       <c r="G107" s="56"/>
       <c r="H107" s="57"/>
     </row>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="427">
   <si>
     <t>Mês</t>
   </si>
@@ -1878,11 +1878,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="169851099"/>
-        <c:axId val="974873360"/>
+        <c:axId val="1589058995"/>
+        <c:axId val="1625498977"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="169851099"/>
+        <c:axId val="1589058995"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,10 +1934,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="974873360"/>
+        <c:crossAx val="1625498977"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="974873360"/>
+        <c:axId val="1625498977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="169851099"/>
+        <c:crossAx val="1589058995"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2238,7 +2238,7 @@
         <n v="110.0"/>
         <n v="44.0"/>
         <n v="98.88"/>
-        <n v="980.86"/>
+        <n v="980.0"/>
         <n v="5372.0"/>
         <n v="113.31"/>
         <n v="580.0"/>
@@ -2263,6 +2263,7 @@
         <n v="7494.55"/>
         <n v="35.62"/>
         <n v="6350.0"/>
+        <n v="980.86"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -2409,6 +2410,7 @@
         <item x="108"/>
         <item x="109"/>
         <item x="110"/>
+        <item x="111"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2756,7 +2758,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUM(B:B)</f>
-        <v>258373.74</v>
+        <v>258372.88</v>
       </c>
       <c r="L3" s="9">
         <f>EOMONTH(MAX(MAX('Todos os Gastos'!$A:$A),MAX('Salários'!$B:$B)),-1)+1</f>
@@ -2837,7 +2839,7 @@
       </c>
       <c r="J5" s="8">
         <f>SUMIFS(D:D,A:A,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A:A,"&lt;&gt;")</f>
-        <v>14031.01</v>
+        <v>14031.87</v>
       </c>
       <c r="L5" s="10">
         <v>46023.0</v>
@@ -2850,7 +2852,7 @@
       </c>
       <c r="B6" s="3">
         <f>IF($A6="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
-        <v>15447.25</v>
+        <v>15446.39</v>
       </c>
       <c r="C6" s="3">
         <f>IF($A6="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A6,'Salários'!$B:$B,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -2858,7 +2860,7 @@
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>1769.47</v>
+        <v>1770.33</v>
       </c>
       <c r="E6" s="4">
         <f>IF($A6="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -2870,14 +2872,14 @@
       </c>
       <c r="G6" s="3">
         <f t="shared" si="2"/>
-        <v>14031.01</v>
+        <v>14031.87</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2488.409999999987)</f>
-        <v>-2488.41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2487.5499999999865)</f>
+        <v>-2487.55</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -2907,14 +2909,14 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>14311.83</v>
+        <v>14312.69</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(D:D,A:A,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A:A,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>1769.47</v>
+        <v>1770.33</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -2944,14 +2946,14 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>13532.65</v>
+        <v>13533.51</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="8">
         <f>AVERAGEIF(D:D,"&lt;&gt;",D:D)</f>
-        <v>-146.3770588</v>
+        <v>-146.3264706</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -2981,7 +2983,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="2"/>
-        <v>12111.67</v>
+        <v>12112.53</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>16</v>
@@ -3018,7 +3020,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>10122.49</v>
+        <v>10123.35</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>17</v>
@@ -3055,7 +3057,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="2"/>
-        <v>8533.51</v>
+        <v>8534.37</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>18</v>
@@ -3092,7 +3094,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>7444.33</v>
+        <v>7445.19</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>19</v>
@@ -3129,7 +3131,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="2"/>
-        <v>3235.15</v>
+        <v>3236.01</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -3159,7 +3161,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>6074.89</v>
+        <v>6075.75</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -3189,7 +3191,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>3003.99</v>
+        <v>3004.85</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -3219,7 +3221,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>-177.13</v>
+        <v>-176.27</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -3249,7 +3251,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>-4530.18</v>
+        <v>-4529.32</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -3279,7 +3281,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>-2488.41</v>
+        <v>-2487.55</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -13995,23 +13997,27 @@
       <c r="H107" s="57"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
-      <c r="A108" s="34">
-        <v>46154.0</v>
+      <c r="A108" s="45">
+        <v>46155.0</v>
       </c>
       <c r="B108" s="43" t="s">
         <v>61</v>
       </c>
       <c r="C108" s="46">
-        <v>980.86</v>
-      </c>
-      <c r="D108" s="42"/>
-      <c r="E108" s="42"/>
+        <v>980.0</v>
+      </c>
+      <c r="D108" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E108" s="58" t="s">
+        <v>53</v>
+      </c>
       <c r="G108" s="56"/>
       <c r="H108" s="57"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
-      <c r="A109" s="34">
-        <v>46154.0</v>
+      <c r="A109" s="45">
+        <v>46155.0</v>
       </c>
       <c r="B109" s="42" t="s">
         <v>67</v>
@@ -14019,14 +14025,18 @@
       <c r="C109" s="48">
         <v>2831.4</v>
       </c>
-      <c r="D109" s="42"/>
-      <c r="E109" s="42"/>
+      <c r="D109" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E109" s="58" t="s">
+        <v>53</v>
+      </c>
       <c r="G109" s="56"/>
       <c r="H109" s="57"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
-      <c r="A110" s="34">
-        <v>46154.0</v>
+      <c r="A110" s="45">
+        <v>46155.0</v>
       </c>
       <c r="B110" s="43" t="s">
         <v>56</v>
@@ -14034,8 +14044,12 @@
       <c r="C110" s="48">
         <v>50.0</v>
       </c>
-      <c r="D110" s="42"/>
-      <c r="E110" s="42"/>
+      <c r="D110" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E110" s="58" t="s">
+        <v>53</v>
+      </c>
       <c r="G110" s="56"/>
       <c r="H110" s="57"/>
     </row>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1878,11 +1878,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1589058995"/>
-        <c:axId val="1625498977"/>
+        <c:axId val="2052730152"/>
+        <c:axId val="1414690732"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1589058995"/>
+        <c:axId val="2052730152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,10 +1934,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1625498977"/>
+        <c:crossAx val="1414690732"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1625498977"/>
+        <c:axId val="1414690732"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1589058995"/>
+        <c:crossAx val="2052730152"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Resumo Mensal'!$A$1:$G$121</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Salários'!$A$1:$D$43</definedName>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$269</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$271</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Switching!$A$1:$F$5</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Inventário de Lotes'!$A$1:$E$15</definedName>
     <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$86</definedName>
@@ -24,14 +24,14 @@
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="i7OzieYx0CMDkN7w4qX3AiDC2ysxRe76Byi+na2JT3c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="zrWWILu0ks1leT9OcrKOTqpS0SYnhSRbpltIQXfRWig="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="427">
   <si>
     <t>Mês</t>
   </si>
@@ -312,6 +312,9 @@
     <t>Churrasco são miguelense</t>
   </si>
   <si>
+    <t>Lote 2800 mai.</t>
+  </si>
+  <si>
     <t>Churrasco pelada</t>
   </si>
   <si>
@@ -379,9 +382,6 @@
   </si>
   <si>
     <t>CDB Sofisa 105%</t>
-  </si>
-  <si>
-    <t>Lote 2800 mai.</t>
   </si>
   <si>
     <t xml:space="preserve">Lote 3000 mai. </t>
@@ -1878,11 +1878,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="2052730152"/>
-        <c:axId val="1414690732"/>
+        <c:axId val="1195554634"/>
+        <c:axId val="48132615"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2052730152"/>
+        <c:axId val="1195554634"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1934,10 +1934,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1414690732"/>
+        <c:crossAx val="48132615"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1414690732"/>
+        <c:axId val="48132615"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2052730152"/>
+        <c:crossAx val="1195554634"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2148,7 +2148,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:E1013" sheet="Todos os Gastos"/>
+    <worksheetSource ref="C1:E1015" sheet="Todos os Gastos"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="Valor" numFmtId="166">
@@ -2238,7 +2238,10 @@
         <n v="110.0"/>
         <n v="44.0"/>
         <n v="98.88"/>
-        <n v="980.0"/>
+        <n v="192.89"/>
+        <n v="787.11"/>
+        <n v="26.0"/>
+        <n v="24.0"/>
         <n v="5372.0"/>
         <n v="113.31"/>
         <n v="580.0"/>
@@ -2286,6 +2289,7 @@
         <s v="Lote 8500 mar."/>
         <s v="Lote 7500 mai."/>
         <s v="Lote 3800 mai. "/>
+        <s v="Lote 2800 mai."/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -2411,6 +2415,9 @@
         <item x="109"/>
         <item x="110"/>
         <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2423,9 +2430,10 @@
     </pivotField>
     <pivotField name="Lote usado" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items>
-        <item h="1" x="11"/>
+        <item h="1" x="12"/>
         <item x="1"/>
         <item x="2"/>
+        <item h="1" x="11"/>
         <item x="10"/>
         <item x="3"/>
         <item x="4"/>
@@ -2864,7 +2872,7 @@
       </c>
       <c r="E6" s="4">
         <f>IF($A6="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4">
         <f>IF($A6="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A6,'Salários'!$B:$B,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -14004,13 +14012,13 @@
         <v>61</v>
       </c>
       <c r="C108" s="46">
-        <v>980.0</v>
+        <v>192.89</v>
       </c>
       <c r="D108" s="43" t="s">
         <v>37</v>
       </c>
       <c r="E108" s="58" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="G108" s="56"/>
       <c r="H108" s="57"/>
@@ -14019,11 +14027,11 @@
       <c r="A109" s="45">
         <v>46155.0</v>
       </c>
-      <c r="B109" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="C109" s="48">
-        <v>2831.4</v>
+      <c r="B109" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C109" s="46">
+        <v>787.11</v>
       </c>
       <c r="D109" s="43" t="s">
         <v>37</v>
@@ -14038,11 +14046,11 @@
       <c r="A110" s="45">
         <v>46155.0</v>
       </c>
-      <c r="B110" s="43" t="s">
-        <v>56</v>
+      <c r="B110" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C110" s="48">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D110" s="43" t="s">
         <v>37</v>
@@ -14054,44 +14062,52 @@
       <c r="H110" s="57"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
-      <c r="A111" s="34">
-        <v>46157.0</v>
+      <c r="A111" s="45">
+        <v>46155.0</v>
       </c>
       <c r="B111" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C111" s="48">
-        <v>132.4</v>
-      </c>
-      <c r="D111" s="42"/>
-      <c r="E111" s="42"/>
+        <v>56</v>
+      </c>
+      <c r="C111" s="46">
+        <v>26.0</v>
+      </c>
+      <c r="D111" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" s="58" t="s">
+        <v>53</v>
+      </c>
       <c r="G111" s="56"/>
       <c r="H111" s="57"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
-      <c r="A112" s="34">
-        <v>46162.0</v>
-      </c>
-      <c r="B112" s="35" t="s">
-        <v>36</v>
+      <c r="A112" s="45">
+        <v>46155.0</v>
+      </c>
+      <c r="B112" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C112" s="46">
-        <v>5372.0</v>
-      </c>
-      <c r="D112" s="42"/>
-      <c r="E112" s="42"/>
+        <v>24.0</v>
+      </c>
+      <c r="D112" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" s="58" t="s">
+        <v>93</v>
+      </c>
       <c r="G112" s="56"/>
       <c r="H112" s="57"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="34">
-        <v>46162.0</v>
+        <v>46157.0</v>
       </c>
       <c r="B113" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C113" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D113" s="42"/>
       <c r="E113" s="42"/>
@@ -14099,29 +14115,29 @@
       <c r="H113" s="57"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
-      <c r="A114" s="45">
-        <v>46172.0</v>
-      </c>
-      <c r="B114" s="43" t="s">
-        <v>89</v>
+      <c r="A114" s="34">
+        <v>46162.0</v>
+      </c>
+      <c r="B114" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C114" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D114" s="35"/>
-      <c r="E114" s="35"/>
+        <v>5372.0</v>
+      </c>
+      <c r="D114" s="42"/>
+      <c r="E114" s="42"/>
       <c r="G114" s="56"/>
       <c r="H114" s="57"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="34">
-        <v>46175.0</v>
-      </c>
-      <c r="B115" s="42" t="s">
-        <v>40</v>
+        <v>46162.0</v>
+      </c>
+      <c r="B115" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C115" s="48">
-        <v>580.0</v>
+        <v>113.31</v>
       </c>
       <c r="D115" s="42"/>
       <c r="E115" s="42"/>
@@ -14129,29 +14145,29 @@
       <c r="H115" s="57"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="34">
-        <v>46179.0</v>
+      <c r="A116" s="45">
+        <v>46172.0</v>
       </c>
       <c r="B116" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C116" s="48">
-        <v>950.0</v>
-      </c>
-      <c r="D116" s="42"/>
-      <c r="E116" s="42"/>
+        <v>89</v>
+      </c>
+      <c r="C116" s="46">
+        <v>400.0</v>
+      </c>
+      <c r="D116" s="35"/>
+      <c r="E116" s="35"/>
       <c r="G116" s="56"/>
       <c r="H116" s="57"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
-      <c r="A117" s="45">
-        <v>46180.0</v>
-      </c>
-      <c r="B117" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C117" s="46">
-        <v>110.0</v>
+      <c r="A117" s="34">
+        <v>46175.0</v>
+      </c>
+      <c r="B117" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" s="48">
+        <v>580.0</v>
       </c>
       <c r="D117" s="42"/>
       <c r="E117" s="42"/>
@@ -14160,13 +14176,13 @@
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="34">
-        <v>46183.0</v>
-      </c>
-      <c r="B118" s="35" t="s">
-        <v>73</v>
+        <v>46179.0</v>
+      </c>
+      <c r="B118" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C118" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D118" s="42"/>
       <c r="E118" s="42"/>
@@ -14174,14 +14190,14 @@
       <c r="H118" s="57"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="34">
-        <v>46183.0</v>
-      </c>
-      <c r="B119" s="42" t="s">
-        <v>82</v>
+      <c r="A119" s="45">
+        <v>46180.0</v>
+      </c>
+      <c r="B119" s="43" t="s">
+        <v>44</v>
       </c>
       <c r="C119" s="46">
-        <v>120.0</v>
+        <v>110.0</v>
       </c>
       <c r="D119" s="42"/>
       <c r="E119" s="42"/>
@@ -14192,11 +14208,11 @@
       <c r="A120" s="34">
         <v>46183.0</v>
       </c>
-      <c r="B120" s="42" t="s">
-        <v>62</v>
+      <c r="B120" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C120" s="48">
-        <v>530.0</v>
+        <v>65.0</v>
       </c>
       <c r="D120" s="42"/>
       <c r="E120" s="42"/>
@@ -14205,13 +14221,13 @@
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="34">
-        <v>46184.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C121" s="48">
-        <v>95.12</v>
+        <v>82</v>
+      </c>
+      <c r="C121" s="46">
+        <v>120.0</v>
       </c>
       <c r="D121" s="42"/>
       <c r="E121" s="42"/>
@@ -14220,13 +14236,13 @@
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="34">
-        <v>46185.0</v>
-      </c>
-      <c r="B122" s="43" t="s">
-        <v>61</v>
+        <v>46183.0</v>
+      </c>
+      <c r="B122" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="C122" s="48">
-        <v>981.95</v>
+        <v>530.0</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="42"/>
@@ -14235,13 +14251,13 @@
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="34">
-        <v>46185.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C123" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D123" s="42"/>
       <c r="E123" s="42"/>
@@ -14249,14 +14265,14 @@
       <c r="H123" s="57"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c r="A124" s="45">
+      <c r="A124" s="34">
         <v>46185.0</v>
       </c>
       <c r="B124" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C124" s="48">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D124" s="42"/>
       <c r="E124" s="42"/>
@@ -14265,13 +14281,13 @@
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="34">
-        <v>46188.0</v>
-      </c>
-      <c r="B125" s="43" t="s">
-        <v>60</v>
+        <v>46185.0</v>
+      </c>
+      <c r="B125" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C125" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D125" s="42"/>
       <c r="E125" s="42"/>
@@ -14280,13 +14296,13 @@
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="45">
-        <v>46192.0</v>
-      </c>
-      <c r="B126" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C126" s="46">
-        <v>40.0</v>
+        <v>46185.0</v>
+      </c>
+      <c r="B126" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C126" s="48">
+        <v>50.0</v>
       </c>
       <c r="D126" s="42"/>
       <c r="E126" s="42"/>
@@ -14295,13 +14311,13 @@
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="34">
-        <v>46193.0</v>
-      </c>
-      <c r="B127" s="35" t="s">
-        <v>36</v>
+        <v>46188.0</v>
+      </c>
+      <c r="B127" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C127" s="48">
-        <v>7200.0</v>
+        <v>132.4</v>
       </c>
       <c r="D127" s="42"/>
       <c r="E127" s="42"/>
@@ -14310,13 +14326,13 @@
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="45">
-        <v>46193.0</v>
-      </c>
-      <c r="B128" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C128" s="48">
-        <v>113.31</v>
+        <v>46192.0</v>
+      </c>
+      <c r="B128" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="C128" s="46">
+        <v>40.0</v>
       </c>
       <c r="D128" s="42"/>
       <c r="E128" s="42"/>
@@ -14324,80 +14340,80 @@
       <c r="H128" s="57"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c r="A129" s="45">
-        <v>46203.0</v>
-      </c>
-      <c r="B129" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C129" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D129" s="35"/>
-      <c r="E129" s="35"/>
-      <c r="F129" s="53"/>
-      <c r="G129" s="39"/>
-      <c r="H129" s="52"/>
-      <c r="I129" s="41"/>
-      <c r="J129" s="41"/>
+      <c r="A129" s="34">
+        <v>46193.0</v>
+      </c>
+      <c r="B129" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C129" s="48">
+        <v>7200.0</v>
+      </c>
+      <c r="D129" s="42"/>
+      <c r="E129" s="42"/>
+      <c r="G129" s="56"/>
+      <c r="H129" s="57"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
-      <c r="A130" s="34">
-        <v>46205.0</v>
-      </c>
-      <c r="B130" s="42" t="s">
-        <v>40</v>
+      <c r="A130" s="45">
+        <v>46193.0</v>
+      </c>
+      <c r="B130" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C130" s="48">
-        <v>930.0</v>
+        <v>113.31</v>
       </c>
       <c r="D130" s="42"/>
       <c r="E130" s="42"/>
-      <c r="F130" s="53"/>
-      <c r="G130" s="39"/>
-      <c r="H130" s="52"/>
-      <c r="I130" s="41"/>
-      <c r="J130" s="41"/>
+      <c r="G130" s="56"/>
+      <c r="H130" s="57"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="34">
-        <v>46209.0</v>
+      <c r="A131" s="45">
+        <v>46203.0</v>
       </c>
       <c r="B131" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C131" s="48">
-        <v>950.0</v>
-      </c>
-      <c r="D131" s="42"/>
-      <c r="E131" s="42"/>
-      <c r="G131" s="56"/>
-      <c r="H131" s="57"/>
+        <v>89</v>
+      </c>
+      <c r="C131" s="46">
+        <v>400.0</v>
+      </c>
+      <c r="D131" s="35"/>
+      <c r="E131" s="35"/>
+      <c r="F131" s="53"/>
+      <c r="G131" s="39"/>
+      <c r="H131" s="52"/>
+      <c r="I131" s="41"/>
+      <c r="J131" s="41"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="45">
-        <v>46210.0</v>
-      </c>
-      <c r="B132" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C132" s="46">
-        <v>110.0</v>
+      <c r="A132" s="34">
+        <v>46205.0</v>
+      </c>
+      <c r="B132" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C132" s="48">
+        <v>930.0</v>
       </c>
       <c r="D132" s="42"/>
       <c r="E132" s="42"/>
-      <c r="G132" s="56"/>
-      <c r="H132" s="57"/>
+      <c r="F132" s="53"/>
+      <c r="G132" s="39"/>
+      <c r="H132" s="52"/>
+      <c r="I132" s="41"/>
+      <c r="J132" s="41"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="34">
-        <v>46213.0</v>
-      </c>
-      <c r="B133" s="35" t="s">
-        <v>73</v>
+        <v>46209.0</v>
+      </c>
+      <c r="B133" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C133" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D133" s="42"/>
       <c r="E133" s="42"/>
@@ -14405,14 +14421,14 @@
       <c r="H133" s="57"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="34">
-        <v>46214.0</v>
-      </c>
-      <c r="B134" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C134" s="48">
-        <v>95.12</v>
+      <c r="A134" s="45">
+        <v>46210.0</v>
+      </c>
+      <c r="B134" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C134" s="46">
+        <v>110.0</v>
       </c>
       <c r="D134" s="42"/>
       <c r="E134" s="42"/>
@@ -14421,13 +14437,13 @@
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="34">
-        <v>46215.0</v>
-      </c>
-      <c r="B135" s="43" t="s">
-        <v>61</v>
+        <v>46213.0</v>
+      </c>
+      <c r="B135" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C135" s="48">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D135" s="42"/>
       <c r="E135" s="42"/>
@@ -14436,13 +14452,13 @@
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="34">
-        <v>46215.0</v>
+        <v>46214.0</v>
       </c>
       <c r="B136" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C136" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D136" s="42"/>
       <c r="E136" s="42"/>
@@ -14454,10 +14470,10 @@
         <v>46215.0</v>
       </c>
       <c r="B137" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C137" s="48">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D137" s="42"/>
       <c r="E137" s="42"/>
@@ -14466,13 +14482,13 @@
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="34">
-        <v>46218.0</v>
-      </c>
-      <c r="B138" s="43" t="s">
-        <v>60</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B138" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C138" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="42"/>
@@ -14481,13 +14497,13 @@
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="34">
-        <v>46223.0</v>
-      </c>
-      <c r="B139" s="35" t="s">
-        <v>36</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B139" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C139" s="48">
-        <v>6800.0</v>
+        <v>50.0</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="42"/>
@@ -14496,13 +14512,13 @@
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="34">
-        <v>46223.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B140" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C140" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="42"/>
@@ -14510,29 +14526,29 @@
       <c r="H140" s="57"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="45">
-        <v>46233.0</v>
-      </c>
-      <c r="B141" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C141" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D141" s="35"/>
-      <c r="E141" s="35"/>
+      <c r="A141" s="34">
+        <v>46223.0</v>
+      </c>
+      <c r="B141" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C141" s="48">
+        <v>6800.0</v>
+      </c>
+      <c r="D141" s="42"/>
+      <c r="E141" s="42"/>
       <c r="G141" s="56"/>
       <c r="H141" s="57"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c r="A142" s="34">
-        <v>46236.0</v>
-      </c>
-      <c r="B142" s="42" t="s">
-        <v>40</v>
+        <v>46223.0</v>
+      </c>
+      <c r="B142" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C142" s="48">
-        <v>1500.0</v>
+        <v>113.31</v>
       </c>
       <c r="D142" s="42"/>
       <c r="E142" s="42"/>
@@ -14541,13 +14557,13 @@
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="45">
-        <v>46239.0</v>
-      </c>
-      <c r="B143" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C143" s="48">
-        <v>81.8</v>
+        <v>46233.0</v>
+      </c>
+      <c r="B143" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C143" s="46">
+        <v>400.0</v>
       </c>
       <c r="D143" s="35"/>
       <c r="E143" s="35"/>
@@ -14556,13 +14572,13 @@
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="34">
-        <v>46240.0</v>
-      </c>
-      <c r="B144" s="43" t="s">
-        <v>59</v>
+        <v>46236.0</v>
+      </c>
+      <c r="B144" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C144" s="48">
-        <v>950.0</v>
+        <v>1500.0</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42"/>
@@ -14571,28 +14587,28 @@
     </row>
     <row r="145" ht="14.25" customHeight="1">
       <c r="A145" s="45">
-        <v>46241.0</v>
-      </c>
-      <c r="B145" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C145" s="46">
-        <v>110.0</v>
-      </c>
-      <c r="D145" s="42"/>
-      <c r="E145" s="42"/>
+        <v>46239.0</v>
+      </c>
+      <c r="B145" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C145" s="48">
+        <v>81.8</v>
+      </c>
+      <c r="D145" s="35"/>
+      <c r="E145" s="35"/>
       <c r="G145" s="56"/>
       <c r="H145" s="57"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="34">
-        <v>46244.0</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>73</v>
+        <v>46240.0</v>
+      </c>
+      <c r="B146" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C146" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D146" s="42"/>
       <c r="E146" s="42"/>
@@ -14600,14 +14616,14 @@
       <c r="H146" s="57"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
-      <c r="A147" s="34">
-        <v>46245.0</v>
-      </c>
-      <c r="B147" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C147" s="48">
-        <v>95.12</v>
+      <c r="A147" s="45">
+        <v>46241.0</v>
+      </c>
+      <c r="B147" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C147" s="46">
+        <v>110.0</v>
       </c>
       <c r="D147" s="42"/>
       <c r="E147" s="42"/>
@@ -14616,13 +14632,13 @@
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c r="A148" s="34">
-        <v>46246.0</v>
-      </c>
-      <c r="B148" s="43" t="s">
-        <v>61</v>
+        <v>46244.0</v>
+      </c>
+      <c r="B148" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C148" s="48">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D148" s="42"/>
       <c r="E148" s="42"/>
@@ -14631,13 +14647,13 @@
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="34">
-        <v>46246.0</v>
+        <v>46245.0</v>
       </c>
       <c r="B149" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C149" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D149" s="42"/>
       <c r="E149" s="42"/>
@@ -14648,11 +14664,11 @@
       <c r="A150" s="34">
         <v>46246.0</v>
       </c>
-      <c r="B150" s="42" t="s">
-        <v>66</v>
+      <c r="B150" s="43" t="s">
+        <v>61</v>
       </c>
       <c r="C150" s="48">
-        <v>460.0</v>
+        <v>981.95</v>
       </c>
       <c r="D150" s="42"/>
       <c r="E150" s="42"/>
@@ -14660,14 +14676,14 @@
       <c r="H150" s="57"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="45">
+      <c r="A151" s="34">
         <v>46246.0</v>
       </c>
-      <c r="B151" s="43" t="s">
-        <v>56</v>
+      <c r="B151" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C151" s="48">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D151" s="42"/>
       <c r="E151" s="42"/>
@@ -14679,10 +14695,10 @@
         <v>46246.0</v>
       </c>
       <c r="B152" s="42" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C152" s="48">
-        <v>530.0</v>
+        <v>460.0</v>
       </c>
       <c r="D152" s="42"/>
       <c r="E152" s="42"/>
@@ -14690,14 +14706,14 @@
       <c r="H152" s="57"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="34">
-        <v>46249.0</v>
+      <c r="A153" s="45">
+        <v>46246.0</v>
       </c>
       <c r="B153" s="43" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C153" s="48">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D153" s="42"/>
       <c r="E153" s="42"/>
@@ -14706,13 +14722,13 @@
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="34">
-        <v>46254.0</v>
-      </c>
-      <c r="B154" s="35" t="s">
-        <v>36</v>
+        <v>46246.0</v>
+      </c>
+      <c r="B154" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="C154" s="48">
-        <v>5800.0</v>
+        <v>530.0</v>
       </c>
       <c r="D154" s="42"/>
       <c r="E154" s="42"/>
@@ -14721,13 +14737,13 @@
     </row>
     <row r="155" ht="14.25" customHeight="1">
       <c r="A155" s="34">
-        <v>46254.0</v>
+        <v>46249.0</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C155" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D155" s="42"/>
       <c r="E155" s="42"/>
@@ -14735,29 +14751,29 @@
       <c r="H155" s="57"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="45">
-        <v>46264.0</v>
-      </c>
-      <c r="B156" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C156" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D156" s="35"/>
-      <c r="E156" s="35"/>
+      <c r="A156" s="34">
+        <v>46254.0</v>
+      </c>
+      <c r="B156" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C156" s="48">
+        <v>5800.0</v>
+      </c>
+      <c r="D156" s="42"/>
+      <c r="E156" s="42"/>
       <c r="G156" s="56"/>
       <c r="H156" s="57"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="34">
-        <v>46267.0</v>
-      </c>
-      <c r="B157" s="42" t="s">
-        <v>40</v>
+        <v>46254.0</v>
+      </c>
+      <c r="B157" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C157" s="48">
-        <v>2000.0</v>
+        <v>113.31</v>
       </c>
       <c r="D157" s="42"/>
       <c r="E157" s="42"/>
@@ -14765,29 +14781,29 @@
       <c r="H157" s="57"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="34">
-        <v>46271.0</v>
+      <c r="A158" s="45">
+        <v>46264.0</v>
       </c>
       <c r="B158" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C158" s="48">
-        <v>950.0</v>
-      </c>
-      <c r="D158" s="42"/>
-      <c r="E158" s="42"/>
+        <v>89</v>
+      </c>
+      <c r="C158" s="46">
+        <v>400.0</v>
+      </c>
+      <c r="D158" s="35"/>
+      <c r="E158" s="35"/>
       <c r="G158" s="56"/>
       <c r="H158" s="57"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="45">
-        <v>46272.0</v>
-      </c>
-      <c r="B159" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C159" s="46">
-        <v>110.0</v>
+      <c r="A159" s="34">
+        <v>46267.0</v>
+      </c>
+      <c r="B159" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C159" s="48">
+        <v>2000.0</v>
       </c>
       <c r="D159" s="42"/>
       <c r="E159" s="42"/>
@@ -14796,13 +14812,13 @@
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="34">
-        <v>46273.0</v>
-      </c>
-      <c r="B160" s="42" t="s">
-        <v>94</v>
+        <v>46271.0</v>
+      </c>
+      <c r="B160" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C160" s="48">
-        <v>90.0</v>
+        <v>950.0</v>
       </c>
       <c r="D160" s="42"/>
       <c r="E160" s="42"/>
@@ -14810,14 +14826,14 @@
       <c r="H160" s="57"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="34">
-        <v>46275.0</v>
-      </c>
-      <c r="B161" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C161" s="48">
-        <v>65.0</v>
+      <c r="A161" s="45">
+        <v>46272.0</v>
+      </c>
+      <c r="B161" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C161" s="46">
+        <v>110.0</v>
       </c>
       <c r="D161" s="42"/>
       <c r="E161" s="42"/>
@@ -14826,13 +14842,13 @@
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c r="A162" s="34">
-        <v>46276.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B162" s="42" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C162" s="48">
-        <v>95.12</v>
+        <v>90.0</v>
       </c>
       <c r="D162" s="42"/>
       <c r="E162" s="42"/>
@@ -14841,13 +14857,13 @@
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="34">
-        <v>46277.0</v>
-      </c>
-      <c r="B163" s="43" t="s">
-        <v>61</v>
+        <v>46275.0</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C163" s="48">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D163" s="42"/>
       <c r="E163" s="42"/>
@@ -14856,13 +14872,13 @@
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c r="A164" s="34">
-        <v>46277.0</v>
+        <v>46276.0</v>
       </c>
       <c r="B164" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C164" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42"/>
@@ -14874,10 +14890,10 @@
         <v>46277.0</v>
       </c>
       <c r="B165" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C165" s="48">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D165" s="42"/>
       <c r="E165" s="42"/>
@@ -14886,13 +14902,13 @@
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="34">
-        <v>46280.0</v>
-      </c>
-      <c r="B166" s="43" t="s">
-        <v>60</v>
+        <v>46277.0</v>
+      </c>
+      <c r="B166" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C166" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D166" s="42"/>
       <c r="E166" s="42"/>
@@ -14901,13 +14917,13 @@
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="34">
-        <v>46285.0</v>
-      </c>
-      <c r="B167" s="35" t="s">
-        <v>36</v>
+        <v>46277.0</v>
+      </c>
+      <c r="B167" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C167" s="48">
-        <v>6850.0</v>
+        <v>50.0</v>
       </c>
       <c r="D167" s="42"/>
       <c r="E167" s="42"/>
@@ -14915,14 +14931,14 @@
       <c r="H167" s="57"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c r="A168" s="45">
-        <v>46285.0</v>
+      <c r="A168" s="34">
+        <v>46280.0</v>
       </c>
       <c r="B168" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C168" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D168" s="42"/>
       <c r="E168" s="42"/>
@@ -14930,29 +14946,29 @@
       <c r="H168" s="57"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="45">
-        <v>46295.0</v>
-      </c>
-      <c r="B169" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C169" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D169" s="35"/>
-      <c r="E169" s="35"/>
+      <c r="A169" s="34">
+        <v>46285.0</v>
+      </c>
+      <c r="B169" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C169" s="48">
+        <v>6850.0</v>
+      </c>
+      <c r="D169" s="42"/>
+      <c r="E169" s="42"/>
       <c r="G169" s="56"/>
       <c r="H169" s="57"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="34">
-        <v>46297.0</v>
-      </c>
-      <c r="B170" s="42" t="s">
-        <v>40</v>
+      <c r="A170" s="45">
+        <v>46285.0</v>
+      </c>
+      <c r="B170" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C170" s="48">
-        <v>1800.0</v>
+        <v>113.31</v>
       </c>
       <c r="D170" s="42"/>
       <c r="E170" s="42"/>
@@ -14960,29 +14976,29 @@
       <c r="H170" s="57"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="34">
-        <v>46301.0</v>
+      <c r="A171" s="45">
+        <v>46295.0</v>
       </c>
       <c r="B171" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C171" s="48">
-        <v>950.0</v>
-      </c>
-      <c r="D171" s="42"/>
-      <c r="E171" s="42"/>
+        <v>89</v>
+      </c>
+      <c r="C171" s="46">
+        <v>400.0</v>
+      </c>
+      <c r="D171" s="35"/>
+      <c r="E171" s="35"/>
       <c r="G171" s="56"/>
       <c r="H171" s="57"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="45">
-        <v>46302.0</v>
-      </c>
-      <c r="B172" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C172" s="46">
-        <v>110.0</v>
+      <c r="A172" s="34">
+        <v>46297.0</v>
+      </c>
+      <c r="B172" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C172" s="48">
+        <v>1800.0</v>
       </c>
       <c r="D172" s="42"/>
       <c r="E172" s="42"/>
@@ -14991,13 +15007,13 @@
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c r="A173" s="34">
-        <v>46302.0</v>
-      </c>
-      <c r="B173" s="42" t="s">
-        <v>62</v>
+        <v>46301.0</v>
+      </c>
+      <c r="B173" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C173" s="48">
-        <v>530.0</v>
+        <v>950.0</v>
       </c>
       <c r="D173" s="42"/>
       <c r="E173" s="42"/>
@@ -15005,14 +15021,14 @@
       <c r="H173" s="57"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="34">
-        <v>46303.0</v>
-      </c>
-      <c r="B174" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C174" s="48">
-        <v>90.0</v>
+      <c r="A174" s="45">
+        <v>46302.0</v>
+      </c>
+      <c r="B174" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C174" s="46">
+        <v>110.0</v>
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42"/>
@@ -15021,13 +15037,13 @@
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="34">
-        <v>46303.0</v>
+        <v>46302.0</v>
       </c>
       <c r="B175" s="42" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C175" s="48">
-        <v>119.8</v>
+        <v>530.0</v>
       </c>
       <c r="D175" s="42"/>
       <c r="E175" s="42"/>
@@ -15036,13 +15052,13 @@
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="34">
-        <v>46305.0</v>
-      </c>
-      <c r="B176" s="35" t="s">
-        <v>73</v>
+        <v>46303.0</v>
+      </c>
+      <c r="B176" s="42" t="s">
+        <v>95</v>
       </c>
       <c r="C176" s="48">
-        <v>65.0</v>
+        <v>90.0</v>
       </c>
       <c r="D176" s="42"/>
       <c r="E176" s="42"/>
@@ -15051,13 +15067,13 @@
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="34">
-        <v>46306.0</v>
+        <v>46303.0</v>
       </c>
       <c r="B177" s="42" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="C177" s="48">
-        <v>95.12</v>
+        <v>119.8</v>
       </c>
       <c r="D177" s="42"/>
       <c r="E177" s="42"/>
@@ -15066,13 +15082,13 @@
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" s="34">
-        <v>46307.0</v>
-      </c>
-      <c r="B178" s="43" t="s">
-        <v>61</v>
+        <v>46305.0</v>
+      </c>
+      <c r="B178" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C178" s="48">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D178" s="42"/>
       <c r="E178" s="42"/>
@@ -15081,13 +15097,13 @@
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="34">
-        <v>46307.0</v>
+        <v>46306.0</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C179" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D179" s="42"/>
       <c r="E179" s="42"/>
@@ -15095,14 +15111,14 @@
       <c r="H179" s="57"/>
     </row>
     <row r="180" ht="14.25" customHeight="1">
-      <c r="A180" s="45">
+      <c r="A180" s="34">
         <v>46307.0</v>
       </c>
       <c r="B180" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C180" s="48">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D180" s="42"/>
       <c r="E180" s="42"/>
@@ -15111,13 +15127,13 @@
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="34">
-        <v>46310.0</v>
-      </c>
-      <c r="B181" s="43" t="s">
-        <v>60</v>
+        <v>46307.0</v>
+      </c>
+      <c r="B181" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C181" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D181" s="42"/>
       <c r="E181" s="42"/>
@@ -15125,14 +15141,14 @@
       <c r="H181" s="57"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" s="34">
-        <v>46315.0</v>
-      </c>
-      <c r="B182" s="35" t="s">
-        <v>36</v>
+      <c r="A182" s="45">
+        <v>46307.0</v>
+      </c>
+      <c r="B182" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C182" s="48">
-        <v>6000.0</v>
+        <v>50.0</v>
       </c>
       <c r="D182" s="42"/>
       <c r="E182" s="42"/>
@@ -15141,13 +15157,13 @@
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="34">
-        <v>46315.0</v>
+        <v>46310.0</v>
       </c>
       <c r="B183" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C183" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D183" s="42"/>
       <c r="E183" s="42"/>
@@ -15155,29 +15171,29 @@
       <c r="H183" s="57"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="45">
-        <v>46325.0</v>
-      </c>
-      <c r="B184" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C184" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D184" s="35"/>
-      <c r="E184" s="35"/>
+      <c r="A184" s="34">
+        <v>46315.0</v>
+      </c>
+      <c r="B184" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C184" s="48">
+        <v>6000.0</v>
+      </c>
+      <c r="D184" s="42"/>
+      <c r="E184" s="42"/>
       <c r="G184" s="56"/>
       <c r="H184" s="57"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="34">
-        <v>46328.0</v>
-      </c>
-      <c r="B185" s="42" t="s">
-        <v>40</v>
+        <v>46315.0</v>
+      </c>
+      <c r="B185" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C185" s="48">
-        <v>2200.0</v>
+        <v>113.31</v>
       </c>
       <c r="D185" s="42"/>
       <c r="E185" s="42"/>
@@ -15185,29 +15201,29 @@
       <c r="H185" s="57"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="34">
-        <v>46332.0</v>
+      <c r="A186" s="45">
+        <v>46325.0</v>
       </c>
       <c r="B186" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C186" s="48">
-        <v>950.0</v>
-      </c>
-      <c r="D186" s="42"/>
-      <c r="E186" s="42"/>
+        <v>89</v>
+      </c>
+      <c r="C186" s="46">
+        <v>400.0</v>
+      </c>
+      <c r="D186" s="35"/>
+      <c r="E186" s="35"/>
       <c r="G186" s="56"/>
       <c r="H186" s="57"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="45">
-        <v>46333.0</v>
-      </c>
-      <c r="B187" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C187" s="46">
-        <v>110.0</v>
+      <c r="A187" s="34">
+        <v>46328.0</v>
+      </c>
+      <c r="B187" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C187" s="48">
+        <v>2200.0</v>
       </c>
       <c r="D187" s="42"/>
       <c r="E187" s="42"/>
@@ -15216,13 +15232,13 @@
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c r="A188" s="34">
-        <v>46335.0</v>
-      </c>
-      <c r="B188" s="42" t="s">
-        <v>94</v>
+        <v>46332.0</v>
+      </c>
+      <c r="B188" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C188" s="48">
-        <v>90.0</v>
+        <v>950.0</v>
       </c>
       <c r="D188" s="42"/>
       <c r="E188" s="42"/>
@@ -15230,14 +15246,14 @@
       <c r="H188" s="57"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="34">
-        <v>46336.0</v>
-      </c>
-      <c r="B189" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C189" s="48">
-        <v>65.0</v>
+      <c r="A189" s="45">
+        <v>46333.0</v>
+      </c>
+      <c r="B189" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C189" s="46">
+        <v>110.0</v>
       </c>
       <c r="D189" s="42"/>
       <c r="E189" s="42"/>
@@ -15246,13 +15262,13 @@
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="34">
-        <v>46337.0</v>
+        <v>46335.0</v>
       </c>
       <c r="B190" s="42" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C190" s="48">
-        <v>95.12</v>
+        <v>90.0</v>
       </c>
       <c r="D190" s="42"/>
       <c r="E190" s="42"/>
@@ -15261,13 +15277,13 @@
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="34">
-        <v>46338.0</v>
-      </c>
-      <c r="B191" s="43" t="s">
-        <v>61</v>
+        <v>46336.0</v>
+      </c>
+      <c r="B191" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C191" s="48">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D191" s="42"/>
       <c r="E191" s="42"/>
@@ -15276,13 +15292,13 @@
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="34">
-        <v>46338.0</v>
+        <v>46337.0</v>
       </c>
       <c r="B192" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C192" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D192" s="42"/>
       <c r="E192" s="42"/>
@@ -15294,10 +15310,10 @@
         <v>46338.0</v>
       </c>
       <c r="B193" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C193" s="48">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D193" s="42"/>
       <c r="E193" s="42"/>
@@ -15306,13 +15322,13 @@
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c r="A194" s="34">
-        <v>46341.0</v>
-      </c>
-      <c r="B194" s="43" t="s">
-        <v>60</v>
+        <v>46338.0</v>
+      </c>
+      <c r="B194" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C194" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42"/>
@@ -15321,13 +15337,13 @@
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="34">
-        <v>46346.0</v>
-      </c>
-      <c r="B195" s="35" t="s">
-        <v>36</v>
+        <v>46338.0</v>
+      </c>
+      <c r="B195" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C195" s="48">
-        <v>5750.0</v>
+        <v>50.0</v>
       </c>
       <c r="D195" s="42"/>
       <c r="E195" s="42"/>
@@ -15336,13 +15352,13 @@
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="34">
-        <v>46346.0</v>
+        <v>46341.0</v>
       </c>
       <c r="B196" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C196" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D196" s="42"/>
       <c r="E196" s="42"/>
@@ -15350,29 +15366,29 @@
       <c r="H196" s="57"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="45">
-        <v>46356.0</v>
-      </c>
-      <c r="B197" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C197" s="46">
-        <v>400.0</v>
-      </c>
-      <c r="D197" s="35"/>
-      <c r="E197" s="35"/>
+      <c r="A197" s="34">
+        <v>46346.0</v>
+      </c>
+      <c r="B197" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C197" s="48">
+        <v>5750.0</v>
+      </c>
+      <c r="D197" s="42"/>
+      <c r="E197" s="42"/>
       <c r="G197" s="56"/>
       <c r="H197" s="57"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="34">
-        <v>46358.0</v>
-      </c>
-      <c r="B198" s="42" t="s">
-        <v>40</v>
+        <v>46346.0</v>
+      </c>
+      <c r="B198" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C198" s="48">
-        <v>1880.0</v>
+        <v>113.31</v>
       </c>
       <c r="D198" s="42"/>
       <c r="E198" s="42"/>
@@ -15380,29 +15396,29 @@
       <c r="H198" s="57"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="34">
-        <v>46362.0</v>
+      <c r="A199" s="45">
+        <v>46356.0</v>
       </c>
       <c r="B199" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C199" s="48">
-        <v>950.0</v>
-      </c>
-      <c r="D199" s="42"/>
-      <c r="E199" s="42"/>
+        <v>89</v>
+      </c>
+      <c r="C199" s="46">
+        <v>400.0</v>
+      </c>
+      <c r="D199" s="35"/>
+      <c r="E199" s="35"/>
       <c r="G199" s="56"/>
       <c r="H199" s="57"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="45">
-        <v>46363.0</v>
-      </c>
-      <c r="B200" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C200" s="46">
-        <v>110.0</v>
+      <c r="A200" s="34">
+        <v>46358.0</v>
+      </c>
+      <c r="B200" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C200" s="48">
+        <v>1880.0</v>
       </c>
       <c r="D200" s="42"/>
       <c r="E200" s="42"/>
@@ -15411,13 +15427,13 @@
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c r="A201" s="34">
-        <v>46365.0</v>
-      </c>
-      <c r="B201" s="42" t="s">
-        <v>62</v>
+        <v>46362.0</v>
+      </c>
+      <c r="B201" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C201" s="48">
-        <v>530.0</v>
+        <v>950.0</v>
       </c>
       <c r="D201" s="42"/>
       <c r="E201" s="42"/>
@@ -15425,14 +15441,14 @@
       <c r="H201" s="57"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="34">
-        <v>46366.0</v>
-      </c>
-      <c r="B202" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C202" s="48">
-        <v>65.0</v>
+      <c r="A202" s="45">
+        <v>46363.0</v>
+      </c>
+      <c r="B202" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" s="46">
+        <v>110.0</v>
       </c>
       <c r="D202" s="42"/>
       <c r="E202" s="42"/>
@@ -15441,13 +15457,13 @@
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="34">
-        <v>46367.0</v>
+        <v>46365.0</v>
       </c>
       <c r="B203" s="42" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C203" s="48">
-        <v>95.12</v>
+        <v>530.0</v>
       </c>
       <c r="D203" s="42"/>
       <c r="E203" s="42"/>
@@ -15456,13 +15472,13 @@
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c r="A204" s="34">
-        <v>46367.0</v>
-      </c>
-      <c r="B204" s="42" t="s">
-        <v>96</v>
+        <v>46366.0</v>
+      </c>
+      <c r="B204" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C204" s="48">
-        <v>2900.0</v>
+        <v>65.0</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42"/>
@@ -15471,13 +15487,13 @@
     </row>
     <row r="205" ht="14.25" customHeight="1">
       <c r="A205" s="34">
-        <v>46368.0</v>
-      </c>
-      <c r="B205" s="43" t="s">
-        <v>61</v>
+        <v>46367.0</v>
+      </c>
+      <c r="B205" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C205" s="48">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D205" s="42"/>
       <c r="E205" s="42"/>
@@ -15486,13 +15502,13 @@
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c r="A206" s="34">
-        <v>46368.0</v>
+        <v>46367.0</v>
       </c>
       <c r="B206" s="42" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C206" s="48">
-        <v>2831.4</v>
+        <v>2900.0</v>
       </c>
       <c r="D206" s="42"/>
       <c r="E206" s="42"/>
@@ -15500,14 +15516,14 @@
       <c r="H206" s="57"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
-      <c r="A207" s="45">
+      <c r="A207" s="34">
         <v>46368.0</v>
       </c>
       <c r="B207" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C207" s="48">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D207" s="42"/>
       <c r="E207" s="42"/>
@@ -15516,13 +15532,13 @@
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c r="A208" s="34">
-        <v>46371.0</v>
-      </c>
-      <c r="B208" s="43" t="s">
-        <v>60</v>
+        <v>46368.0</v>
+      </c>
+      <c r="B208" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C208" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D208" s="42"/>
       <c r="E208" s="42"/>
@@ -15530,14 +15546,14 @@
       <c r="H208" s="57"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="34">
-        <v>46376.0</v>
-      </c>
-      <c r="B209" s="35" t="s">
-        <v>36</v>
+      <c r="A209" s="45">
+        <v>46368.0</v>
+      </c>
+      <c r="B209" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C209" s="48">
-        <v>6250.0</v>
+        <v>50.0</v>
       </c>
       <c r="D209" s="42"/>
       <c r="E209" s="42"/>
@@ -15545,14 +15561,14 @@
       <c r="H209" s="57"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="45">
-        <v>46376.0</v>
+      <c r="A210" s="34">
+        <v>46371.0</v>
       </c>
       <c r="B210" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C210" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D210" s="42"/>
       <c r="E210" s="42"/>
@@ -15561,13 +15577,13 @@
     </row>
     <row r="211" ht="14.25" customHeight="1">
       <c r="A211" s="34">
-        <v>46389.0</v>
-      </c>
-      <c r="B211" s="42" t="s">
-        <v>40</v>
+        <v>46376.0</v>
+      </c>
+      <c r="B211" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C211" s="48">
-        <v>2000.0</v>
+        <v>6250.0</v>
       </c>
       <c r="D211" s="42"/>
       <c r="E211" s="42"/>
@@ -15575,14 +15591,14 @@
       <c r="H211" s="57"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="34">
-        <v>46393.0</v>
+      <c r="A212" s="45">
+        <v>46376.0</v>
       </c>
       <c r="B212" s="43" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C212" s="48">
-        <v>950.0</v>
+        <v>113.31</v>
       </c>
       <c r="D212" s="42"/>
       <c r="E212" s="42"/>
@@ -15590,14 +15606,14 @@
       <c r="H212" s="57"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="45">
-        <v>46394.0</v>
-      </c>
-      <c r="B213" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C213" s="46">
-        <v>110.0</v>
+      <c r="A213" s="34">
+        <v>46389.0</v>
+      </c>
+      <c r="B213" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C213" s="48">
+        <v>2000.0</v>
       </c>
       <c r="D213" s="42"/>
       <c r="E213" s="42"/>
@@ -15606,13 +15622,13 @@
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c r="A214" s="34">
-        <v>46397.0</v>
-      </c>
-      <c r="B214" s="35" t="s">
-        <v>73</v>
+        <v>46393.0</v>
+      </c>
+      <c r="B214" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C214" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D214" s="42"/>
       <c r="E214" s="42"/>
@@ -15620,14 +15636,14 @@
       <c r="H214" s="57"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
-      <c r="A215" s="34">
-        <v>46398.0</v>
-      </c>
-      <c r="B215" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C215" s="48">
-        <v>105.37</v>
+      <c r="A215" s="45">
+        <v>46394.0</v>
+      </c>
+      <c r="B215" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C215" s="46">
+        <v>110.0</v>
       </c>
       <c r="D215" s="42"/>
       <c r="E215" s="42"/>
@@ -15636,13 +15652,13 @@
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c r="A216" s="34">
-        <v>46399.0</v>
-      </c>
-      <c r="B216" s="43" t="s">
-        <v>61</v>
+        <v>46397.0</v>
+      </c>
+      <c r="B216" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C216" s="48">
-        <v>983.13</v>
+        <v>65.0</v>
       </c>
       <c r="D216" s="42"/>
       <c r="E216" s="42"/>
@@ -15651,13 +15667,13 @@
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c r="A217" s="34">
-        <v>46399.0</v>
-      </c>
-      <c r="B217" s="43" t="s">
-        <v>56</v>
+        <v>46398.0</v>
+      </c>
+      <c r="B217" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C217" s="48">
-        <v>50.0</v>
+        <v>105.37</v>
       </c>
       <c r="D217" s="42"/>
       <c r="E217" s="42"/>
@@ -15666,13 +15682,13 @@
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="34">
-        <v>46402.0</v>
+        <v>46399.0</v>
       </c>
       <c r="B218" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C218" s="48">
-        <v>132.4</v>
+        <v>983.13</v>
       </c>
       <c r="D218" s="42"/>
       <c r="E218" s="42"/>
@@ -15681,13 +15697,13 @@
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c r="A219" s="34">
-        <v>46407.0</v>
-      </c>
-      <c r="B219" s="35" t="s">
-        <v>36</v>
+        <v>46399.0</v>
+      </c>
+      <c r="B219" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C219" s="48">
-        <v>7796.0</v>
+        <v>50.0</v>
       </c>
       <c r="D219" s="42"/>
       <c r="E219" s="42"/>
@@ -15696,13 +15712,13 @@
     </row>
     <row r="220" ht="14.25" customHeight="1">
       <c r="A220" s="34">
-        <v>46407.0</v>
+        <v>46402.0</v>
       </c>
       <c r="B220" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C220" s="48">
-        <v>102.36</v>
+        <v>132.4</v>
       </c>
       <c r="D220" s="42"/>
       <c r="E220" s="42"/>
@@ -15711,13 +15727,13 @@
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c r="A221" s="34">
-        <v>46420.0</v>
-      </c>
-      <c r="B221" s="42" t="s">
-        <v>40</v>
+        <v>46407.0</v>
+      </c>
+      <c r="B221" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C221" s="48">
-        <v>1800.0</v>
+        <v>7796.0</v>
       </c>
       <c r="D221" s="42"/>
       <c r="E221" s="42"/>
@@ -15726,13 +15742,13 @@
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c r="A222" s="34">
-        <v>46424.0</v>
+        <v>46407.0</v>
       </c>
       <c r="B222" s="43" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C222" s="48">
-        <v>950.0</v>
+        <v>102.36</v>
       </c>
       <c r="D222" s="42"/>
       <c r="E222" s="42"/>
@@ -15740,14 +15756,14 @@
       <c r="H222" s="57"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="45">
-        <v>46425.0</v>
-      </c>
-      <c r="B223" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C223" s="46">
-        <v>110.0</v>
+      <c r="A223" s="34">
+        <v>46420.0</v>
+      </c>
+      <c r="B223" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C223" s="48">
+        <v>1800.0</v>
       </c>
       <c r="D223" s="42"/>
       <c r="E223" s="42"/>
@@ -15756,13 +15772,13 @@
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c r="A224" s="34">
-        <v>46428.0</v>
-      </c>
-      <c r="B224" s="35" t="s">
-        <v>73</v>
+        <v>46424.0</v>
+      </c>
+      <c r="B224" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C224" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D224" s="42"/>
       <c r="E224" s="42"/>
@@ -15770,14 +15786,14 @@
       <c r="H224" s="57"/>
     </row>
     <row r="225" ht="14.25" customHeight="1">
-      <c r="A225" s="34">
-        <v>46428.0</v>
-      </c>
-      <c r="B225" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C225" s="48">
-        <v>530.0</v>
+      <c r="A225" s="45">
+        <v>46425.0</v>
+      </c>
+      <c r="B225" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C225" s="46">
+        <v>110.0</v>
       </c>
       <c r="D225" s="42"/>
       <c r="E225" s="42"/>
@@ -15786,13 +15802,13 @@
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c r="A226" s="34">
-        <v>46429.0</v>
-      </c>
-      <c r="B226" s="42" t="s">
-        <v>42</v>
+        <v>46428.0</v>
+      </c>
+      <c r="B226" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C226" s="48">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D226" s="42"/>
       <c r="E226" s="42"/>
@@ -15801,13 +15817,13 @@
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c r="A227" s="34">
-        <v>46430.0</v>
-      </c>
-      <c r="B227" s="43" t="s">
-        <v>61</v>
+        <v>46428.0</v>
+      </c>
+      <c r="B227" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="C227" s="48">
-        <v>981.95</v>
+        <v>530.0</v>
       </c>
       <c r="D227" s="42"/>
       <c r="E227" s="42"/>
@@ -15816,13 +15832,13 @@
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c r="A228" s="34">
-        <v>46430.0</v>
+        <v>46429.0</v>
       </c>
       <c r="B228" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C228" s="48">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D228" s="42"/>
       <c r="E228" s="42"/>
@@ -15833,11 +15849,11 @@
       <c r="A229" s="34">
         <v>46430.0</v>
       </c>
-      <c r="B229" s="42" t="s">
-        <v>65</v>
+      <c r="B229" s="43" t="s">
+        <v>61</v>
       </c>
       <c r="C229" s="48">
-        <v>1407.65</v>
+        <v>981.95</v>
       </c>
       <c r="D229" s="42"/>
       <c r="E229" s="42"/>
@@ -15845,29 +15861,29 @@
       <c r="H229" s="57"/>
     </row>
     <row r="230" ht="14.25" customHeight="1">
-      <c r="A230" s="45">
+      <c r="A230" s="34">
         <v>46430.0</v>
       </c>
-      <c r="B230" s="43" t="s">
-        <v>56</v>
+      <c r="B230" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C230" s="48">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D230" s="42"/>
-      <c r="E230" s="35"/>
+      <c r="E230" s="42"/>
       <c r="G230" s="56"/>
       <c r="H230" s="57"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c r="A231" s="34">
-        <v>46433.0</v>
-      </c>
-      <c r="B231" s="43" t="s">
-        <v>60</v>
+        <v>46430.0</v>
+      </c>
+      <c r="B231" s="42" t="s">
+        <v>65</v>
       </c>
       <c r="C231" s="48">
-        <v>132.4</v>
+        <v>1407.65</v>
       </c>
       <c r="D231" s="42"/>
       <c r="E231" s="42"/>
@@ -15875,29 +15891,29 @@
       <c r="H231" s="57"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c r="A232" s="34">
-        <v>46437.0</v>
-      </c>
-      <c r="B232" s="42" t="s">
-        <v>66</v>
+      <c r="A232" s="45">
+        <v>46430.0</v>
+      </c>
+      <c r="B232" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C232" s="48">
-        <v>460.0</v>
+        <v>50.0</v>
       </c>
       <c r="D232" s="42"/>
-      <c r="E232" s="42"/>
+      <c r="E232" s="35"/>
       <c r="G232" s="56"/>
       <c r="H232" s="57"/>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c r="A233" s="34">
-        <v>46438.0</v>
-      </c>
-      <c r="B233" s="35" t="s">
-        <v>36</v>
+        <v>46433.0</v>
+      </c>
+      <c r="B233" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C233" s="48">
-        <v>6004.07</v>
+        <v>132.4</v>
       </c>
       <c r="D233" s="42"/>
       <c r="E233" s="42"/>
@@ -15905,14 +15921,14 @@
       <c r="H233" s="57"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="45">
-        <v>46438.0</v>
-      </c>
-      <c r="B234" s="43" t="s">
-        <v>54</v>
+      <c r="A234" s="34">
+        <v>46437.0</v>
+      </c>
+      <c r="B234" s="42" t="s">
+        <v>66</v>
       </c>
       <c r="C234" s="48">
-        <v>113.31</v>
+        <v>460.0</v>
       </c>
       <c r="D234" s="42"/>
       <c r="E234" s="42"/>
@@ -15921,13 +15937,13 @@
     </row>
     <row r="235" ht="14.25" customHeight="1">
       <c r="A235" s="34">
-        <v>46448.0</v>
-      </c>
-      <c r="B235" s="42" t="s">
-        <v>40</v>
+        <v>46438.0</v>
+      </c>
+      <c r="B235" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C235" s="48">
-        <v>1771.95</v>
+        <v>6004.07</v>
       </c>
       <c r="D235" s="42"/>
       <c r="E235" s="42"/>
@@ -15935,14 +15951,14 @@
       <c r="H235" s="57"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="34">
-        <v>46451.0</v>
-      </c>
-      <c r="B236" s="42" t="s">
-        <v>72</v>
+      <c r="A236" s="45">
+        <v>46438.0</v>
+      </c>
+      <c r="B236" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C236" s="48">
-        <v>81.8</v>
+        <v>113.31</v>
       </c>
       <c r="D236" s="42"/>
       <c r="E236" s="42"/>
@@ -15951,13 +15967,13 @@
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c r="A237" s="34">
-        <v>46452.0</v>
-      </c>
-      <c r="B237" s="43" t="s">
-        <v>59</v>
+        <v>46448.0</v>
+      </c>
+      <c r="B237" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C237" s="48">
-        <v>950.0</v>
+        <v>1771.95</v>
       </c>
       <c r="D237" s="42"/>
       <c r="E237" s="42"/>
@@ -15965,14 +15981,14 @@
       <c r="H237" s="57"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="45">
-        <v>46453.0</v>
-      </c>
-      <c r="B238" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C238" s="46">
-        <v>110.0</v>
+      <c r="A238" s="34">
+        <v>46451.0</v>
+      </c>
+      <c r="B238" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C238" s="48">
+        <v>81.8</v>
       </c>
       <c r="D238" s="42"/>
       <c r="E238" s="42"/>
@@ -15981,13 +15997,13 @@
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c r="A239" s="34">
-        <v>46456.0</v>
-      </c>
-      <c r="B239" s="35" t="s">
-        <v>50</v>
+        <v>46452.0</v>
+      </c>
+      <c r="B239" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C239" s="48">
-        <v>1336.73</v>
+        <v>950.0</v>
       </c>
       <c r="D239" s="42"/>
       <c r="E239" s="42"/>
@@ -15995,14 +16011,14 @@
       <c r="H239" s="57"/>
     </row>
     <row r="240" ht="14.25" customHeight="1">
-      <c r="A240" s="34">
-        <v>46456.0</v>
-      </c>
-      <c r="B240" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C240" s="48">
-        <v>65.0</v>
+      <c r="A240" s="45">
+        <v>46453.0</v>
+      </c>
+      <c r="B240" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C240" s="46">
+        <v>110.0</v>
       </c>
       <c r="D240" s="42"/>
       <c r="E240" s="42"/>
@@ -16011,13 +16027,13 @@
     </row>
     <row r="241" ht="14.25" customHeight="1">
       <c r="A241" s="34">
-        <v>46457.0</v>
-      </c>
-      <c r="B241" s="42" t="s">
-        <v>42</v>
+        <v>46456.0</v>
+      </c>
+      <c r="B241" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="C241" s="48">
-        <v>86.15</v>
+        <v>1336.73</v>
       </c>
       <c r="D241" s="42"/>
       <c r="E241" s="42"/>
@@ -16026,13 +16042,13 @@
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c r="A242" s="34">
-        <v>46458.0</v>
-      </c>
-      <c r="B242" s="43" t="s">
-        <v>61</v>
+        <v>46456.0</v>
+      </c>
+      <c r="B242" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C242" s="48">
-        <v>981.22</v>
+        <v>65.0</v>
       </c>
       <c r="D242" s="42"/>
       <c r="E242" s="42"/>
@@ -16041,13 +16057,13 @@
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c r="A243" s="34">
-        <v>46458.0</v>
+        <v>46457.0</v>
       </c>
       <c r="B243" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C243" s="48">
-        <v>2831.4</v>
+        <v>86.15</v>
       </c>
       <c r="D243" s="42"/>
       <c r="E243" s="42"/>
@@ -16059,10 +16075,10 @@
         <v>46458.0</v>
       </c>
       <c r="B244" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C244" s="48">
-        <v>50.0</v>
+        <v>981.22</v>
       </c>
       <c r="D244" s="42"/>
       <c r="E244" s="42"/>
@@ -16071,13 +16087,13 @@
     </row>
     <row r="245" ht="14.25" customHeight="1">
       <c r="A245" s="34">
-        <v>46461.0</v>
-      </c>
-      <c r="B245" s="43" t="s">
-        <v>60</v>
+        <v>46458.0</v>
+      </c>
+      <c r="B245" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C245" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D245" s="42"/>
       <c r="E245" s="42"/>
@@ -16086,13 +16102,13 @@
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c r="A246" s="34">
-        <v>46466.0</v>
-      </c>
-      <c r="B246" s="35" t="s">
-        <v>36</v>
+        <v>46458.0</v>
+      </c>
+      <c r="B246" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C246" s="48">
-        <v>7494.55</v>
+        <v>50.0</v>
       </c>
       <c r="D246" s="42"/>
       <c r="E246" s="42"/>
@@ -16101,13 +16117,13 @@
     </row>
     <row r="247" ht="14.25" customHeight="1">
       <c r="A247" s="34">
-        <v>46466.0</v>
+        <v>46461.0</v>
       </c>
       <c r="B247" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C247" s="48">
-        <v>87.84</v>
+        <v>132.4</v>
       </c>
       <c r="D247" s="42"/>
       <c r="E247" s="42"/>
@@ -16116,13 +16132,13 @@
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c r="A248" s="34">
-        <v>46477.0</v>
-      </c>
-      <c r="B248" s="42" t="s">
-        <v>76</v>
+        <v>46466.0</v>
+      </c>
+      <c r="B248" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C248" s="48">
-        <v>35.62</v>
+        <v>7494.55</v>
       </c>
       <c r="D248" s="42"/>
       <c r="E248" s="42"/>
@@ -16131,13 +16147,13 @@
     </row>
     <row r="249" ht="14.25" customHeight="1">
       <c r="A249" s="34">
-        <v>46479.0</v>
-      </c>
-      <c r="B249" s="42" t="s">
-        <v>40</v>
+        <v>46466.0</v>
+      </c>
+      <c r="B249" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C249" s="48">
-        <v>5310.25</v>
+        <v>87.84</v>
       </c>
       <c r="D249" s="42"/>
       <c r="E249" s="42"/>
@@ -16146,13 +16162,13 @@
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="34">
-        <v>46483.0</v>
-      </c>
-      <c r="B250" s="43" t="s">
-        <v>59</v>
+        <v>46477.0</v>
+      </c>
+      <c r="B250" s="42" t="s">
+        <v>76</v>
       </c>
       <c r="C250" s="48">
-        <v>950.0</v>
+        <v>35.62</v>
       </c>
       <c r="D250" s="42"/>
       <c r="E250" s="42"/>
@@ -16160,14 +16176,14 @@
       <c r="H250" s="57"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="45">
-        <v>46484.0</v>
-      </c>
-      <c r="B251" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C251" s="46">
-        <v>110.0</v>
+      <c r="A251" s="34">
+        <v>46479.0</v>
+      </c>
+      <c r="B251" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C251" s="48">
+        <v>5310.25</v>
       </c>
       <c r="D251" s="42"/>
       <c r="E251" s="42"/>
@@ -16176,13 +16192,13 @@
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="34">
-        <v>46487.0</v>
-      </c>
-      <c r="B252" s="35" t="s">
-        <v>73</v>
+        <v>46483.0</v>
+      </c>
+      <c r="B252" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C252" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D252" s="42"/>
       <c r="E252" s="42"/>
@@ -16190,14 +16206,14 @@
       <c r="H252" s="57"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="34">
-        <v>46488.0</v>
-      </c>
-      <c r="B253" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C253" s="48">
-        <v>98.98</v>
+      <c r="A253" s="45">
+        <v>46484.0</v>
+      </c>
+      <c r="B253" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C253" s="46">
+        <v>110.0</v>
       </c>
       <c r="D253" s="42"/>
       <c r="E253" s="42"/>
@@ -16206,13 +16222,13 @@
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c r="A254" s="34">
-        <v>46489.0</v>
-      </c>
-      <c r="B254" s="43" t="s">
-        <v>61</v>
+        <v>46487.0</v>
+      </c>
+      <c r="B254" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="C254" s="48">
-        <v>981.22</v>
+        <v>65.0</v>
       </c>
       <c r="D254" s="42"/>
       <c r="E254" s="42"/>
@@ -16221,13 +16237,13 @@
     </row>
     <row r="255" ht="14.25" customHeight="1">
       <c r="A255" s="34">
-        <v>46489.0</v>
+        <v>46488.0</v>
       </c>
       <c r="B255" s="42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C255" s="48">
-        <v>2831.4</v>
+        <v>98.98</v>
       </c>
       <c r="D255" s="42"/>
       <c r="E255" s="42"/>
@@ -16235,14 +16251,14 @@
       <c r="H255" s="57"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="45">
+      <c r="A256" s="34">
         <v>46489.0</v>
       </c>
       <c r="B256" s="43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C256" s="48">
-        <v>50.0</v>
+        <v>981.22</v>
       </c>
       <c r="D256" s="42"/>
       <c r="E256" s="42"/>
@@ -16251,13 +16267,13 @@
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c r="A257" s="34">
-        <v>46492.0</v>
-      </c>
-      <c r="B257" s="43" t="s">
-        <v>60</v>
+        <v>46489.0</v>
+      </c>
+      <c r="B257" s="42" t="s">
+        <v>67</v>
       </c>
       <c r="C257" s="48">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D257" s="42"/>
       <c r="E257" s="42"/>
@@ -16265,14 +16281,14 @@
       <c r="H257" s="57"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="34">
-        <v>46497.0</v>
-      </c>
-      <c r="B258" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C258" s="46">
-        <v>6350.0</v>
+      <c r="A258" s="45">
+        <v>46489.0</v>
+      </c>
+      <c r="B258" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C258" s="48">
+        <v>50.0</v>
       </c>
       <c r="D258" s="42"/>
       <c r="E258" s="42"/>
@@ -16280,14 +16296,14 @@
       <c r="H258" s="57"/>
     </row>
     <row r="259" ht="14.25" customHeight="1">
-      <c r="A259" s="45">
-        <v>46497.0</v>
+      <c r="A259" s="34">
+        <v>46492.0</v>
       </c>
       <c r="B259" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C259" s="46">
-        <v>113.8</v>
+        <v>60</v>
+      </c>
+      <c r="C259" s="48">
+        <v>132.4</v>
       </c>
       <c r="D259" s="42"/>
       <c r="E259" s="42"/>
@@ -16295,14 +16311,14 @@
       <c r="H259" s="57"/>
     </row>
     <row r="260" ht="14.25" customHeight="1">
-      <c r="A260" s="45">
-        <v>46507.0</v>
-      </c>
-      <c r="B260" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C260" s="48">
-        <v>530.0</v>
+      <c r="A260" s="34">
+        <v>46497.0</v>
+      </c>
+      <c r="B260" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C260" s="46">
+        <v>6350.0</v>
       </c>
       <c r="D260" s="42"/>
       <c r="E260" s="42"/>
@@ -16310,14 +16326,14 @@
       <c r="H260" s="57"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="34">
-        <v>46509.0</v>
-      </c>
-      <c r="B261" s="42" t="s">
-        <v>40</v>
+      <c r="A261" s="45">
+        <v>46497.0</v>
+      </c>
+      <c r="B261" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C261" s="46">
-        <v>3452.5</v>
+        <v>113.8</v>
       </c>
       <c r="D261" s="42"/>
       <c r="E261" s="42"/>
@@ -16325,14 +16341,14 @@
       <c r="H261" s="57"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="34">
-        <v>46513.0</v>
-      </c>
-      <c r="B262" s="43" t="s">
-        <v>59</v>
+      <c r="A262" s="45">
+        <v>46507.0</v>
+      </c>
+      <c r="B262" s="42" t="s">
+        <v>62</v>
       </c>
       <c r="C262" s="48">
-        <v>950.0</v>
+        <v>530.0</v>
       </c>
       <c r="D262" s="42"/>
       <c r="E262" s="42"/>
@@ -16340,14 +16356,14 @@
       <c r="H262" s="57"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c r="A263" s="45">
-        <v>46514.0</v>
-      </c>
-      <c r="B263" s="43" t="s">
-        <v>44</v>
+      <c r="A263" s="34">
+        <v>46509.0</v>
+      </c>
+      <c r="B263" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C263" s="46">
-        <v>110.0</v>
+        <v>3452.5</v>
       </c>
       <c r="D263" s="42"/>
       <c r="E263" s="42"/>
@@ -16356,13 +16372,13 @@
     </row>
     <row r="264" ht="14.25" customHeight="1">
       <c r="A264" s="34">
-        <v>46517.0</v>
-      </c>
-      <c r="B264" s="35" t="s">
-        <v>73</v>
+        <v>46513.0</v>
+      </c>
+      <c r="B264" s="43" t="s">
+        <v>59</v>
       </c>
       <c r="C264" s="48">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D264" s="42"/>
       <c r="E264" s="42"/>
@@ -16370,14 +16386,14 @@
       <c r="H264" s="57"/>
     </row>
     <row r="265" ht="14.25" customHeight="1">
-      <c r="A265" s="34">
-        <v>46518.0</v>
-      </c>
-      <c r="B265" s="42" t="s">
-        <v>42</v>
+      <c r="A265" s="45">
+        <v>46514.0</v>
+      </c>
+      <c r="B265" s="43" t="s">
+        <v>44</v>
       </c>
       <c r="C265" s="46">
-        <v>98.88</v>
+        <v>110.0</v>
       </c>
       <c r="D265" s="42"/>
       <c r="E265" s="42"/>
@@ -16386,13 +16402,13 @@
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c r="A266" s="34">
-        <v>46519.0</v>
-      </c>
-      <c r="B266" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C266" s="46">
-        <v>980.86</v>
+        <v>46517.0</v>
+      </c>
+      <c r="B266" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C266" s="48">
+        <v>65.0</v>
       </c>
       <c r="D266" s="42"/>
       <c r="E266" s="42"/>
@@ -16401,13 +16417,13 @@
     </row>
     <row r="267" ht="14.25" customHeight="1">
       <c r="A267" s="34">
-        <v>46522.0</v>
-      </c>
-      <c r="B267" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C267" s="48">
-        <v>132.4</v>
+        <v>46518.0</v>
+      </c>
+      <c r="B267" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C267" s="46">
+        <v>98.88</v>
       </c>
       <c r="D267" s="42"/>
       <c r="E267" s="42"/>
@@ -16416,13 +16432,13 @@
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c r="A268" s="34">
-        <v>46527.0</v>
-      </c>
-      <c r="B268" s="35" t="s">
-        <v>36</v>
+        <v>46519.0</v>
+      </c>
+      <c r="B268" s="43" t="s">
+        <v>61</v>
       </c>
       <c r="C268" s="46">
-        <v>5372.0</v>
+        <v>980.86</v>
       </c>
       <c r="D268" s="42"/>
       <c r="E268" s="42"/>
@@ -16430,14 +16446,14 @@
       <c r="H268" s="57"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="45">
-        <v>46527.0</v>
+      <c r="A269" s="34">
+        <v>46522.0</v>
       </c>
       <c r="B269" s="43" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C269" s="48">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D269" s="42"/>
       <c r="E269" s="42"/>
@@ -16445,16 +16461,32 @@
       <c r="H269" s="57"/>
     </row>
     <row r="270" ht="14.25" customHeight="1">
-      <c r="A270" s="59"/>
-      <c r="B270" s="60"/>
-      <c r="C270" s="61"/>
+      <c r="A270" s="34">
+        <v>46527.0</v>
+      </c>
+      <c r="B270" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C270" s="46">
+        <v>5372.0</v>
+      </c>
+      <c r="D270" s="42"/>
+      <c r="E270" s="42"/>
       <c r="G270" s="56"/>
       <c r="H270" s="57"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="59"/>
-      <c r="B271" s="60"/>
-      <c r="C271" s="61"/>
+      <c r="A271" s="45">
+        <v>46527.0</v>
+      </c>
+      <c r="B271" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C271" s="48">
+        <v>113.31</v>
+      </c>
+      <c r="D271" s="42"/>
+      <c r="E271" s="42"/>
       <c r="G271" s="56"/>
       <c r="H271" s="57"/>
     </row>
@@ -16823,16 +16855,16 @@
       <c r="H323" s="57"/>
     </row>
     <row r="324" ht="14.25" customHeight="1">
-      <c r="A324" s="62"/>
-      <c r="B324" s="63"/>
-      <c r="C324" s="64"/>
+      <c r="A324" s="59"/>
+      <c r="B324" s="60"/>
+      <c r="C324" s="61"/>
       <c r="G324" s="56"/>
       <c r="H324" s="57"/>
     </row>
     <row r="325" ht="14.25" customHeight="1">
-      <c r="A325" s="62"/>
-      <c r="B325" s="63"/>
-      <c r="C325" s="64"/>
+      <c r="A325" s="59"/>
+      <c r="B325" s="60"/>
+      <c r="C325" s="61"/>
       <c r="G325" s="56"/>
       <c r="H325" s="57"/>
     </row>
@@ -17355,18 +17387,24 @@
       <c r="H399" s="57"/>
     </row>
     <row r="400" ht="14.25" customHeight="1">
-      <c r="A400" s="59"/>
-      <c r="C400" s="32"/>
+      <c r="A400" s="62"/>
+      <c r="B400" s="63"/>
+      <c r="C400" s="64"/>
       <c r="G400" s="56"/>
       <c r="H400" s="57"/>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c r="A401" s="59"/>
-      <c r="C401" s="32"/>
+      <c r="A401" s="62"/>
+      <c r="B401" s="63"/>
+      <c r="C401" s="64"/>
+      <c r="G401" s="56"/>
+      <c r="H401" s="57"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
       <c r="A402" s="59"/>
       <c r="C402" s="32"/>
+      <c r="G402" s="56"/>
+      <c r="H402" s="57"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
       <c r="A403" s="59"/>
@@ -17453,14 +17491,14 @@
       <c r="C423" s="32"/>
     </row>
     <row r="424" ht="14.25" customHeight="1">
-      <c r="A424" s="31"/>
+      <c r="A424" s="59"/>
       <c r="C424" s="32"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="31"/>
+    <row r="425" ht="14.25" customHeight="1">
+      <c r="A425" s="59"/>
       <c r="C425" s="32"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" ht="14.25" customHeight="1">
       <c r="A426" s="31"/>
       <c r="C426" s="32"/>
     </row>
@@ -19810,15 +19848,23 @@
     </row>
     <row r="1013" ht="15.75" customHeight="1">
       <c r="A1013" s="31"/>
+      <c r="C1013" s="32"/>
+    </row>
+    <row r="1014" ht="15.75" customHeight="1">
+      <c r="A1014" s="31"/>
+      <c r="C1014" s="32"/>
+    </row>
+    <row r="1015" ht="15.75" customHeight="1">
+      <c r="A1015" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$269">
-    <sortState ref="A1:E269">
-      <sortCondition ref="A1:A269"/>
-      <sortCondition ref="E1:E269"/>
-      <sortCondition ref="B1:B269"/>
-      <sortCondition ref="C1:C269"/>
-      <sortCondition ref="D1:D269"/>
+  <autoFilter ref="$A$1:$E$271">
+    <sortState ref="A1:E271">
+      <sortCondition ref="A1:A271"/>
+      <sortCondition ref="E1:E271"/>
+      <sortCondition ref="B1:B271"/>
+      <sortCondition ref="C1:C271"/>
+      <sortCondition ref="D1:D271"/>
     </sortState>
   </autoFilter>
   <printOptions/>
@@ -19845,30 +19891,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="65" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C2" s="30">
         <v>46146.0</v>
@@ -19880,15 +19926,15 @@
         <v>3122.53</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" s="30">
         <v>46146.0</v>
@@ -19900,7 +19946,7 @@
         <v>3119.0</v>
       </c>
       <c r="F3" s="66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -19908,7 +19954,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C4" s="30">
         <v>46148.0</v>
@@ -19920,7 +19966,7 @@
         <v>3000.0</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -19928,7 +19974,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" s="30">
         <v>46148.0</v>
@@ -19940,7 +19986,7 @@
         <v>192.41</v>
       </c>
       <c r="F5" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -23946,19 +23992,19 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
@@ -23975,7 +24021,7 @@
         <v>4000.0</v>
       </c>
       <c r="E2" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -23992,7 +24038,7 @@
         <v>6630.64</v>
       </c>
       <c r="E3" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -24009,7 +24055,7 @@
         <v>10342.0</v>
       </c>
       <c r="E4" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -24026,7 +24072,7 @@
         <v>4124.75</v>
       </c>
       <c r="E5" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -24043,7 +24089,7 @@
         <v>5400.0</v>
       </c>
       <c r="E6" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -24060,12 +24106,12 @@
         <v>2063.11</v>
       </c>
       <c r="E7" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="65" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="70">
         <v>46084.0</v>
@@ -24077,12 +24123,12 @@
         <v>3000.0</v>
       </c>
       <c r="E8" s="72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="70">
         <v>46085.0</v>
@@ -24094,7 +24140,7 @@
         <v>3000.0</v>
       </c>
       <c r="E9" s="72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -24111,7 +24157,7 @@
         <v>8587.0</v>
       </c>
       <c r="E10" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -24128,7 +24174,7 @@
         <v>5680.0</v>
       </c>
       <c r="E11" s="66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -24145,12 +24191,12 @@
         <v>7536.72</v>
       </c>
       <c r="E12" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="58" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B13" s="30">
         <v>46150.0</v>
@@ -24162,7 +24208,7 @@
         <v>2800.0</v>
       </c>
       <c r="E13" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -24179,7 +24225,7 @@
         <v>3000.0</v>
       </c>
       <c r="E14" s="66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -24196,7 +24242,7 @@
         <v>3429.0</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -31096,7 +31142,7 @@
     </row>
     <row r="18">
       <c r="A18" s="81" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" s="82">
         <v>120.0</v>
@@ -35447,7 +35493,7 @@
     </row>
     <row r="49">
       <c r="A49" s="81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B49" s="82">
         <v>150.0</v>
@@ -36694,7 +36740,7 @@
     </row>
     <row r="58">
       <c r="A58" s="81" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B58" s="82">
         <v>105.0</v>
@@ -36835,7 +36881,7 @@
     </row>
     <row r="59">
       <c r="A59" s="81" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B59" s="82">
         <v>103.0</v>
@@ -37103,7 +37149,7 @@
     </row>
     <row r="61">
       <c r="A61" s="81" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B61" s="82">
         <v>230.0</v>
@@ -40636,7 +40682,7 @@
     </row>
     <row r="86">
       <c r="A86" s="81" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B86" s="82">
         <v>220.0</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1656588178"/>
-        <c:axId val="263384051"/>
+        <c:axId val="867850629"/>
+        <c:axId val="873704375"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1656588178"/>
+        <c:axId val="867850629"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="263384051"/>
+        <c:crossAx val="873704375"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="263384051"/>
+        <c:axId val="873704375"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1656588178"/>
+        <c:crossAx val="867850629"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2425" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="427">
   <si>
     <t>Mês</t>
   </si>
@@ -156,16 +156,25 @@
     <t>Cartão NU</t>
   </si>
   <si>
-    <t>Lote 2063,11 fev.</t>
+    <t>Lote 190 mai</t>
   </si>
   <si>
     <t>Cemig</t>
   </si>
   <si>
+    <t>Lote 2063,11 fev.</t>
+  </si>
+  <si>
+    <t>Claro</t>
+  </si>
+  <si>
+    <t>Lote 3120 mai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lote 3800 mai. </t>
   </si>
   <si>
-    <t>Claro</t>
+    <t>Resto praia</t>
   </si>
   <si>
     <t>Lote 4000 fev.</t>
@@ -174,46 +183,43 @@
     <t>Lote 4124,75 fev.</t>
   </si>
   <si>
-    <t>Resto praia</t>
+    <t>Cartão PS</t>
   </si>
   <si>
     <t>Lote 5400 fev.</t>
   </si>
   <si>
+    <t>Concurso ze</t>
+  </si>
+  <si>
     <t>Lote 5680 abr.</t>
   </si>
   <si>
-    <t>Cartão PS</t>
+    <t>Condomínio</t>
   </si>
   <si>
     <t>Lote 6630,64 fev.</t>
   </si>
   <si>
-    <t>Concurso ze</t>
+    <t>Pelada</t>
   </si>
   <si>
     <t>Lote 7500 mai.</t>
   </si>
   <si>
-    <t>Condomínio</t>
+    <t>Cemig SIM</t>
   </si>
   <si>
     <t>Lote 8500 mar.</t>
-  </si>
-  <si>
-    <t>Pelada</t>
-  </si>
-  <si>
-    <t>Cemig SIM</t>
-  </si>
-  <si>
-    <t>Total geral</t>
   </si>
   <si>
     <t>Faxina Rosa</t>
   </si>
   <si>
     <t>Internet</t>
+  </si>
+  <si>
+    <t>Total geral</t>
   </si>
   <si>
     <t>Aluguel</t>
@@ -312,9 +318,6 @@
     <t>Churrasco são miguelense</t>
   </si>
   <si>
-    <t>Lote 2800 mai.</t>
-  </si>
-  <si>
     <t>Churrasco pelada</t>
   </si>
   <si>
@@ -345,9 +348,6 @@
     <t>Lote 3000 mar. V</t>
   </si>
   <si>
-    <t>Lote 3120 mai</t>
-  </si>
-  <si>
     <t>Mercado Pago Cofrinho 120% CDI (Meli+)</t>
   </si>
   <si>
@@ -366,9 +366,6 @@
     <t>CDB Genial 220% CDI - 60 dias</t>
   </si>
   <si>
-    <t>Lote 190 mai</t>
-  </si>
-  <si>
     <t>Lote (ID)</t>
   </si>
   <si>
@@ -382,6 +379,9 @@
   </si>
   <si>
     <t>CDB Sofisa 105%</t>
+  </si>
+  <si>
+    <t>Lote 2800 mai.</t>
   </si>
   <si>
     <t xml:space="preserve">Lote 3000 mai. </t>
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="867850629"/>
-        <c:axId val="873704375"/>
+        <c:axId val="461849869"/>
+        <c:axId val="1206437602"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="867850629"/>
+        <c:axId val="461849869"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="873704375"/>
+        <c:crossAx val="1206437602"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="873704375"/>
+        <c:axId val="1206437602"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="867850629"/>
+        <c:crossAx val="461849869"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2292,7 +2292,8 @@
         <s v="Lote 8500 mar."/>
         <s v="Lote 7500 mai."/>
         <s v="Lote 3800 mai. "/>
-        <s v="Lote 2800 mai."/>
+        <s v="Lote 190 mai"/>
+        <s v="Lote 3120 mai"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -2302,7 +2303,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Todos os Gastos" cacheId="0" dataCaption="" compact="0" compactData="0">
-  <location ref="G1:H13" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <location ref="G1:H15" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields>
     <pivotField name="Valor" dataField="1" compact="0" numFmtId="166" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items>
@@ -2433,10 +2434,11 @@
     </pivotField>
     <pivotField name="Lote usado" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items>
-        <item h="1" x="12"/>
+        <item h="1" x="13"/>
         <item x="1"/>
+        <item x="11"/>
         <item x="2"/>
-        <item h="1" x="11"/>
+        <item x="12"/>
         <item x="10"/>
         <item x="3"/>
         <item x="4"/>
@@ -12012,7 +12014,7 @@
         <v>46034.0</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="36">
         <v>281.1</v>
@@ -12032,7 +12034,7 @@
         <v>46034.0</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="36">
         <v>950.0</v>
@@ -12044,8 +12046,6 @@
         <v>38</v>
       </c>
       <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="40"/>
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
     </row>
@@ -12054,7 +12054,7 @@
         <v>46038.0</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="36">
         <v>135.89</v>
@@ -12066,8 +12066,6 @@
         <v>38</v>
       </c>
       <c r="F15" s="38"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
       <c r="I15" s="41"/>
       <c r="J15" s="41"/>
     </row>
@@ -12076,7 +12074,7 @@
         <v>46042.0</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" s="36">
         <v>983.13</v>
@@ -12120,7 +12118,7 @@
         <v>46056.0</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" s="47">
         <v>530.0</v>
@@ -12142,7 +12140,7 @@
         <v>46057.0</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C19" s="45">
         <v>78.0</v>
@@ -12186,7 +12184,7 @@
         <v>46057.0</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="47">
         <v>195.05</v>
@@ -12208,7 +12206,7 @@
         <v>46057.0</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C22" s="47">
         <v>950.0</v>
@@ -12230,7 +12228,7 @@
         <v>46057.0</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" s="45">
         <v>75.0</v>
@@ -12305,7 +12303,7 @@
         <v>37</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F26" s="38"/>
       <c r="G26" s="39"/>
@@ -12353,7 +12351,7 @@
         <v>37</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F28" s="38"/>
       <c r="G28" s="39"/>
@@ -12379,7 +12377,7 @@
         <v>37</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F29" s="38"/>
       <c r="G29" s="39"/>
@@ -12401,7 +12399,7 @@
         <v>37</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F30" s="38"/>
       <c r="G30" s="39"/>
@@ -12414,7 +12412,7 @@
         <v>46065.0</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C31" s="49">
         <v>981.95</v>
@@ -12436,7 +12434,7 @@
         <v>46065.0</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C32" s="47">
         <v>1407.63</v>
@@ -12458,7 +12456,7 @@
         <v>46069.0</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C33" s="47">
         <v>131.4</v>
@@ -12480,7 +12478,7 @@
         <v>46072.0</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C34" s="49">
         <v>460.0</v>
@@ -12502,7 +12500,7 @@
         <v>46072.0</v>
       </c>
       <c r="B35" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C35" s="49">
         <v>2831.4</v>
@@ -12511,7 +12509,7 @@
         <v>37</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F35" s="52"/>
       <c r="G35" s="39"/>
@@ -12533,7 +12531,7 @@
         <v>37</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F36" s="52"/>
       <c r="G36" s="39"/>
@@ -12555,7 +12553,7 @@
         <v>37</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F37" s="52"/>
       <c r="G37" s="39"/>
@@ -12590,7 +12588,7 @@
         <v>46086.0</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C39" s="49">
         <v>520.0</v>
@@ -12612,7 +12610,7 @@
         <v>46086.0</v>
       </c>
       <c r="B40" s="42" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C40" s="49">
         <v>60.0</v>
@@ -12634,7 +12632,7 @@
         <v>46086.0</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C41" s="47">
         <v>60.0</v>
@@ -12656,7 +12654,7 @@
         <v>46086.0</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C42" s="49">
         <v>58.0</v>
@@ -12678,7 +12676,7 @@
         <v>46086.0</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C43" s="49">
         <v>138.69</v>
@@ -12700,7 +12698,7 @@
         <v>46086.0</v>
       </c>
       <c r="B44" s="42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C44" s="49">
         <v>40.0</v>
@@ -12722,7 +12720,7 @@
         <v>46086.0</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C45" s="49">
         <v>40.0</v>
@@ -12744,7 +12742,7 @@
         <v>46086.0</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C46" s="49">
         <v>81.8</v>
@@ -12766,7 +12764,7 @@
         <v>46087.0</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C47" s="49">
         <v>136.15</v>
@@ -12788,7 +12786,7 @@
         <v>46087.0</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C48" s="49">
         <v>800.0</v>
@@ -12819,7 +12817,7 @@
         <v>37</v>
       </c>
       <c r="E49" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F49" s="54"/>
       <c r="G49" s="39"/>
@@ -12841,7 +12839,7 @@
         <v>37</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F50" s="54"/>
       <c r="G50" s="39"/>
@@ -12854,7 +12852,7 @@
         <v>46091.0</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C51" s="49">
         <v>65.0</v>
@@ -12863,7 +12861,7 @@
         <v>37</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F51" s="54"/>
       <c r="G51" s="39"/>
@@ -12885,7 +12883,7 @@
         <v>37</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="39"/>
@@ -12907,7 +12905,7 @@
         <v>37</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F53" s="54"/>
       <c r="G53" s="39"/>
@@ -12920,7 +12918,7 @@
         <v>46094.0</v>
       </c>
       <c r="B54" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C54" s="55">
         <v>1368.12</v>
@@ -12942,7 +12940,7 @@
         <v>46094.0</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C55" s="49">
         <v>473.73</v>
@@ -12951,7 +12949,7 @@
         <v>37</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F55" s="54"/>
       <c r="G55" s="39"/>
@@ -12964,7 +12962,7 @@
         <v>46094.0</v>
       </c>
       <c r="B56" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C56" s="49">
         <v>508.07</v>
@@ -12973,7 +12971,7 @@
         <v>37</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F56" s="54"/>
       <c r="G56" s="39"/>
@@ -12986,7 +12984,7 @@
         <v>46094.0</v>
       </c>
       <c r="B57" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C57" s="55">
         <v>660.99</v>
@@ -12995,7 +12993,7 @@
         <v>37</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F57" s="54"/>
       <c r="G57" s="39"/>
@@ -13008,7 +13006,7 @@
         <v>46094.0</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C58" s="49">
         <v>807.2</v>
@@ -13017,7 +13015,7 @@
         <v>37</v>
       </c>
       <c r="E58" s="35" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F58" s="54"/>
       <c r="G58" s="39"/>
@@ -13030,7 +13028,7 @@
         <v>46097.0</v>
       </c>
       <c r="B59" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C59" s="49">
         <v>132.4</v>
@@ -13039,7 +13037,7 @@
         <v>37</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F59" s="54"/>
       <c r="G59" s="39"/>
@@ -13061,7 +13059,7 @@
         <v>37</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F60" s="54"/>
       <c r="G60" s="39"/>
@@ -13083,7 +13081,7 @@
         <v>37</v>
       </c>
       <c r="E61" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F61" s="54"/>
       <c r="G61" s="39"/>
@@ -13096,7 +13094,7 @@
         <v>46101.0</v>
       </c>
       <c r="B62" s="42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C62" s="49">
         <v>35.0</v>
@@ -13105,7 +13103,7 @@
         <v>37</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F62" s="54"/>
       <c r="G62" s="39"/>
@@ -13127,7 +13125,7 @@
         <v>37</v>
       </c>
       <c r="E63" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F63" s="54"/>
       <c r="G63" s="39"/>
@@ -13140,7 +13138,7 @@
         <v>46101.0</v>
       </c>
       <c r="B64" s="42" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C64" s="49">
         <v>450.0</v>
@@ -13149,7 +13147,7 @@
         <v>37</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F64" s="54"/>
       <c r="G64" s="39"/>
@@ -13171,7 +13169,7 @@
         <v>37</v>
       </c>
       <c r="E65" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F65" s="54"/>
       <c r="G65" s="39"/>
@@ -13184,7 +13182,7 @@
         <v>46113.0</v>
       </c>
       <c r="B66" s="42" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C66" s="56">
         <v>36.02</v>
@@ -13206,7 +13204,7 @@
         <v>46114.0</v>
       </c>
       <c r="B67" s="42" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C67" s="49">
         <v>150.0</v>
@@ -13250,7 +13248,7 @@
         <v>46114.0</v>
       </c>
       <c r="B69" s="42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C69" s="49">
         <v>170.0</v>
@@ -13272,7 +13270,7 @@
         <v>46114.0</v>
       </c>
       <c r="B70" s="42" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C70" s="49">
         <v>900.0</v>
@@ -13294,7 +13292,7 @@
         <v>46114.0</v>
       </c>
       <c r="B71" s="42" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C71" s="49">
         <v>170.0</v>
@@ -13316,7 +13314,7 @@
         <v>46114.0</v>
       </c>
       <c r="B72" s="42" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C72" s="49">
         <v>52.0</v>
@@ -13338,7 +13336,7 @@
         <v>46114.0</v>
       </c>
       <c r="B73" s="42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C73" s="49">
         <v>120.0</v>
@@ -13360,7 +13358,7 @@
         <v>46114.0</v>
       </c>
       <c r="B74" s="42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C74" s="49">
         <v>35.0</v>
@@ -13382,7 +13380,7 @@
         <v>46118.0</v>
       </c>
       <c r="B75" s="43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C75" s="49">
         <v>182.8</v>
@@ -13391,7 +13389,7 @@
         <v>37</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F75" s="54"/>
       <c r="G75" s="39"/>
@@ -13404,7 +13402,7 @@
         <v>46118.0</v>
       </c>
       <c r="B76" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C76" s="49">
         <v>950.0</v>
@@ -13423,7 +13421,7 @@
         <v>46120.0</v>
       </c>
       <c r="B77" s="42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C77" s="49">
         <v>70.0</v>
@@ -13432,7 +13430,7 @@
         <v>37</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G77" s="57"/>
       <c r="H77" s="58"/>
@@ -13451,7 +13449,7 @@
         <v>37</v>
       </c>
       <c r="E78" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G78" s="57"/>
       <c r="H78" s="58"/>
@@ -13461,7 +13459,7 @@
         <v>46122.0</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C79" s="49">
         <v>434.75</v>
@@ -13470,7 +13468,7 @@
         <v>37</v>
       </c>
       <c r="E79" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G79" s="57"/>
       <c r="H79" s="58"/>
@@ -13480,7 +13478,7 @@
         <v>46122.0</v>
       </c>
       <c r="B80" s="42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C80" s="49">
         <v>70.0</v>
@@ -13499,7 +13497,7 @@
         <v>46122.0</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C81" s="49">
         <v>65.0</v>
@@ -13518,7 +13516,7 @@
         <v>46125.0</v>
       </c>
       <c r="B82" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C82" s="49">
         <v>981.22</v>
@@ -13537,7 +13535,7 @@
         <v>46126.0</v>
       </c>
       <c r="B83" s="43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C83" s="47">
         <v>45.0</v>
@@ -13546,7 +13544,7 @@
         <v>37</v>
       </c>
       <c r="E83" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G83" s="57"/>
       <c r="H83" s="58"/>
@@ -13556,7 +13554,7 @@
         <v>46126.0</v>
       </c>
       <c r="B84" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C84" s="47">
         <v>151.71</v>
@@ -13565,7 +13563,7 @@
         <v>37</v>
       </c>
       <c r="E84" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G84" s="57"/>
       <c r="H84" s="58"/>
@@ -13575,7 +13573,7 @@
         <v>46126.0</v>
       </c>
       <c r="B85" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C85" s="47">
         <v>206.8</v>
@@ -13584,7 +13582,7 @@
         <v>37</v>
       </c>
       <c r="E85" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G85" s="57"/>
       <c r="H85" s="58"/>
@@ -13603,7 +13601,7 @@
         <v>37</v>
       </c>
       <c r="E86" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G86" s="57"/>
       <c r="H86" s="58"/>
@@ -13613,7 +13611,7 @@
         <v>46126.0</v>
       </c>
       <c r="B87" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C87" s="47">
         <v>2472.89</v>
@@ -13632,7 +13630,7 @@
         <v>46127.0</v>
       </c>
       <c r="B88" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C88" s="49">
         <v>132.4</v>
@@ -13641,7 +13639,7 @@
         <v>37</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G88" s="57"/>
       <c r="H88" s="58"/>
@@ -13660,7 +13658,7 @@
         <v>37</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G89" s="57"/>
       <c r="H89" s="58"/>
@@ -13679,7 +13677,7 @@
         <v>37</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G90" s="57"/>
       <c r="H90" s="58"/>
@@ -13698,7 +13696,7 @@
         <v>37</v>
       </c>
       <c r="E91" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G91" s="57"/>
       <c r="H91" s="58"/>
@@ -13708,7 +13706,7 @@
         <v>46132.0</v>
       </c>
       <c r="B92" s="43" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C92" s="47">
         <v>120.75</v>
@@ -13717,7 +13715,7 @@
         <v>37</v>
       </c>
       <c r="E92" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G92" s="57"/>
       <c r="H92" s="58"/>
@@ -13736,7 +13734,7 @@
         <v>37</v>
       </c>
       <c r="E93" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G93" s="57"/>
       <c r="H93" s="58"/>
@@ -13774,7 +13772,7 @@
         <v>37</v>
       </c>
       <c r="E95" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G95" s="57"/>
       <c r="H95" s="58"/>
@@ -13784,7 +13782,7 @@
         <v>46142.0</v>
       </c>
       <c r="B96" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C96" s="47">
         <v>400.0</v>
@@ -13793,7 +13791,7 @@
         <v>37</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G96" s="57"/>
       <c r="H96" s="58"/>
@@ -13803,7 +13801,7 @@
         <v>46142.0</v>
       </c>
       <c r="B97" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C97" s="49">
         <v>530.0</v>
@@ -13812,7 +13810,7 @@
         <v>37</v>
       </c>
       <c r="E97" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G97" s="57"/>
       <c r="H97" s="58"/>
@@ -13831,7 +13829,7 @@
         <v>37</v>
       </c>
       <c r="E98" s="37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G98" s="57"/>
       <c r="H98" s="58"/>
@@ -13841,7 +13839,7 @@
         <v>46146.0</v>
       </c>
       <c r="B99" s="43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C99" s="47">
         <v>59.8</v>
@@ -13850,7 +13848,7 @@
         <v>37</v>
       </c>
       <c r="E99" s="37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G99" s="57"/>
       <c r="H99" s="58"/>
@@ -13860,7 +13858,7 @@
         <v>46146.0</v>
       </c>
       <c r="B100" s="43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C100" s="47">
         <v>250.0</v>
@@ -13869,7 +13867,7 @@
         <v>37</v>
       </c>
       <c r="E100" s="37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G100" s="57"/>
       <c r="H100" s="58"/>
@@ -13879,7 +13877,7 @@
         <v>46148.0</v>
       </c>
       <c r="B101" s="43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C101" s="47">
         <v>417.1</v>
@@ -13888,7 +13886,7 @@
         <v>37</v>
       </c>
       <c r="E101" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G101" s="57"/>
       <c r="H101" s="58"/>
@@ -13898,7 +13896,7 @@
         <v>46148.0</v>
       </c>
       <c r="B102" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C102" s="49">
         <v>950.0</v>
@@ -13907,7 +13905,7 @@
         <v>37</v>
       </c>
       <c r="E102" s="35" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G102" s="57"/>
       <c r="H102" s="58"/>
@@ -13936,7 +13934,7 @@
         <v>46150.0</v>
       </c>
       <c r="B104" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C104" s="49">
         <v>65.0</v>
@@ -13945,7 +13943,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="37" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G104" s="57"/>
       <c r="H104" s="58"/>
@@ -13955,7 +13953,7 @@
         <v>46150.0</v>
       </c>
       <c r="B105" s="42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C105" s="47">
         <v>120.0</v>
@@ -13964,7 +13962,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G105" s="57"/>
       <c r="H105" s="58"/>
@@ -13974,7 +13972,7 @@
         <v>46151.0</v>
       </c>
       <c r="B106" s="43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C106" s="47">
         <v>44.0</v>
@@ -13983,7 +13981,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G106" s="57"/>
       <c r="H106" s="58"/>
@@ -14002,7 +14000,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G107" s="57"/>
       <c r="H107" s="58"/>
@@ -14012,7 +14010,7 @@
         <v>46155.0</v>
       </c>
       <c r="B108" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C108" s="47">
         <v>192.89</v>
@@ -14021,7 +14019,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="59" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G108" s="57"/>
       <c r="H108" s="58"/>
@@ -14031,7 +14029,7 @@
         <v>46155.0</v>
       </c>
       <c r="B109" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C109" s="47">
         <v>787.11</v>
@@ -14040,7 +14038,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G109" s="57"/>
       <c r="H109" s="58"/>
@@ -14050,7 +14048,7 @@
         <v>46155.0</v>
       </c>
       <c r="B110" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C110" s="49">
         <v>2831.4</v>
@@ -14059,7 +14057,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G110" s="57"/>
       <c r="H110" s="58"/>
@@ -14078,7 +14076,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G111" s="57"/>
       <c r="H111" s="58"/>
@@ -14097,7 +14095,7 @@
         <v>37</v>
       </c>
       <c r="E112" s="59" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="G112" s="57"/>
       <c r="H112" s="58"/>
@@ -14107,7 +14105,7 @@
         <v>46157.0</v>
       </c>
       <c r="B113" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C113" s="49">
         <v>132.4</v>
@@ -14152,7 +14150,7 @@
         <v>46172.0</v>
       </c>
       <c r="B116" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C116" s="47">
         <v>400.0</v>
@@ -14182,7 +14180,7 @@
         <v>46179.0</v>
       </c>
       <c r="B118" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C118" s="49">
         <v>950.0</v>
@@ -14212,7 +14210,7 @@
         <v>46183.0</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C120" s="49">
         <v>65.0</v>
@@ -14227,7 +14225,7 @@
         <v>46183.0</v>
       </c>
       <c r="B121" s="42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C121" s="47">
         <v>120.0</v>
@@ -14242,7 +14240,7 @@
         <v>46183.0</v>
       </c>
       <c r="B122" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C122" s="49">
         <v>530.0</v>
@@ -14272,7 +14270,7 @@
         <v>46185.0</v>
       </c>
       <c r="B124" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C124" s="49">
         <v>981.95</v>
@@ -14287,7 +14285,7 @@
         <v>46185.0</v>
       </c>
       <c r="B125" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C125" s="49">
         <v>2831.4</v>
@@ -14317,7 +14315,7 @@
         <v>46188.0</v>
       </c>
       <c r="B127" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C127" s="49">
         <v>132.4</v>
@@ -14332,7 +14330,7 @@
         <v>46192.0</v>
       </c>
       <c r="B128" s="37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C128" s="47">
         <v>40.0</v>
@@ -14377,7 +14375,7 @@
         <v>46203.0</v>
       </c>
       <c r="B131" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C131" s="47">
         <v>400.0</v>
@@ -14413,7 +14411,7 @@
         <v>46209.0</v>
       </c>
       <c r="B133" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C133" s="49">
         <v>950.0</v>
@@ -14443,7 +14441,7 @@
         <v>46213.0</v>
       </c>
       <c r="B135" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C135" s="49">
         <v>65.0</v>
@@ -14473,7 +14471,7 @@
         <v>46215.0</v>
       </c>
       <c r="B137" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C137" s="49">
         <v>981.95</v>
@@ -14488,7 +14486,7 @@
         <v>46215.0</v>
       </c>
       <c r="B138" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C138" s="49">
         <v>2831.4</v>
@@ -14518,7 +14516,7 @@
         <v>46218.0</v>
       </c>
       <c r="B140" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C140" s="49">
         <v>132.4</v>
@@ -14563,7 +14561,7 @@
         <v>46233.0</v>
       </c>
       <c r="B143" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C143" s="47">
         <v>400.0</v>
@@ -14593,7 +14591,7 @@
         <v>46239.0</v>
       </c>
       <c r="B145" s="42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C145" s="49">
         <v>81.8</v>
@@ -14608,7 +14606,7 @@
         <v>46240.0</v>
       </c>
       <c r="B146" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C146" s="49">
         <v>950.0</v>
@@ -14638,7 +14636,7 @@
         <v>46244.0</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C148" s="49">
         <v>65.0</v>
@@ -14668,7 +14666,7 @@
         <v>46246.0</v>
       </c>
       <c r="B150" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C150" s="49">
         <v>981.95</v>
@@ -14683,7 +14681,7 @@
         <v>46246.0</v>
       </c>
       <c r="B151" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C151" s="49">
         <v>2831.4</v>
@@ -14698,7 +14696,7 @@
         <v>46246.0</v>
       </c>
       <c r="B152" s="42" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C152" s="49">
         <v>460.0</v>
@@ -14728,7 +14726,7 @@
         <v>46246.0</v>
       </c>
       <c r="B154" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C154" s="49">
         <v>530.0</v>
@@ -14743,7 +14741,7 @@
         <v>46249.0</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C155" s="49">
         <v>132.4</v>
@@ -14788,7 +14786,7 @@
         <v>46264.0</v>
       </c>
       <c r="B158" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C158" s="47">
         <v>400.0</v>
@@ -14818,7 +14816,7 @@
         <v>46271.0</v>
       </c>
       <c r="B160" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C160" s="49">
         <v>950.0</v>
@@ -14848,7 +14846,7 @@
         <v>46273.0</v>
       </c>
       <c r="B162" s="42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C162" s="49">
         <v>90.0</v>
@@ -14863,7 +14861,7 @@
         <v>46275.0</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C163" s="49">
         <v>65.0</v>
@@ -14893,7 +14891,7 @@
         <v>46277.0</v>
       </c>
       <c r="B165" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C165" s="49">
         <v>981.95</v>
@@ -14908,7 +14906,7 @@
         <v>46277.0</v>
       </c>
       <c r="B166" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C166" s="49">
         <v>2831.4</v>
@@ -14938,7 +14936,7 @@
         <v>46280.0</v>
       </c>
       <c r="B168" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C168" s="49">
         <v>132.4</v>
@@ -14983,7 +14981,7 @@
         <v>46295.0</v>
       </c>
       <c r="B171" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C171" s="47">
         <v>400.0</v>
@@ -15013,7 +15011,7 @@
         <v>46301.0</v>
       </c>
       <c r="B173" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C173" s="49">
         <v>950.0</v>
@@ -15043,7 +15041,7 @@
         <v>46302.0</v>
       </c>
       <c r="B175" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C175" s="49">
         <v>530.0</v>
@@ -15058,7 +15056,7 @@
         <v>46303.0</v>
       </c>
       <c r="B176" s="42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C176" s="49">
         <v>90.0</v>
@@ -15073,7 +15071,7 @@
         <v>46303.0</v>
       </c>
       <c r="B177" s="42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C177" s="49">
         <v>119.8</v>
@@ -15088,7 +15086,7 @@
         <v>46305.0</v>
       </c>
       <c r="B178" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C178" s="49">
         <v>65.0</v>
@@ -15118,7 +15116,7 @@
         <v>46307.0</v>
       </c>
       <c r="B180" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C180" s="49">
         <v>981.95</v>
@@ -15133,7 +15131,7 @@
         <v>46307.0</v>
       </c>
       <c r="B181" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C181" s="49">
         <v>2831.4</v>
@@ -15163,7 +15161,7 @@
         <v>46310.0</v>
       </c>
       <c r="B183" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C183" s="49">
         <v>132.4</v>
@@ -15208,7 +15206,7 @@
         <v>46325.0</v>
       </c>
       <c r="B186" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C186" s="47">
         <v>400.0</v>
@@ -15238,7 +15236,7 @@
         <v>46332.0</v>
       </c>
       <c r="B188" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C188" s="49">
         <v>950.0</v>
@@ -15268,7 +15266,7 @@
         <v>46335.0</v>
       </c>
       <c r="B190" s="42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C190" s="49">
         <v>90.0</v>
@@ -15283,7 +15281,7 @@
         <v>46336.0</v>
       </c>
       <c r="B191" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C191" s="49">
         <v>65.0</v>
@@ -15313,7 +15311,7 @@
         <v>46338.0</v>
       </c>
       <c r="B193" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C193" s="49">
         <v>981.95</v>
@@ -15328,7 +15326,7 @@
         <v>46338.0</v>
       </c>
       <c r="B194" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C194" s="49">
         <v>2831.4</v>
@@ -15358,7 +15356,7 @@
         <v>46341.0</v>
       </c>
       <c r="B196" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C196" s="49">
         <v>132.4</v>
@@ -15403,7 +15401,7 @@
         <v>46356.0</v>
       </c>
       <c r="B199" s="43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C199" s="47">
         <v>400.0</v>
@@ -15433,7 +15431,7 @@
         <v>46362.0</v>
       </c>
       <c r="B201" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C201" s="49">
         <v>950.0</v>
@@ -15463,7 +15461,7 @@
         <v>46365.0</v>
       </c>
       <c r="B203" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C203" s="49">
         <v>530.0</v>
@@ -15478,7 +15476,7 @@
         <v>46366.0</v>
       </c>
       <c r="B204" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C204" s="49">
         <v>65.0</v>
@@ -15508,7 +15506,7 @@
         <v>46367.0</v>
       </c>
       <c r="B206" s="42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C206" s="49">
         <v>2900.0</v>
@@ -15523,7 +15521,7 @@
         <v>46368.0</v>
       </c>
       <c r="B207" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C207" s="49">
         <v>981.95</v>
@@ -15538,7 +15536,7 @@
         <v>46368.0</v>
       </c>
       <c r="B208" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C208" s="49">
         <v>2831.4</v>
@@ -15568,7 +15566,7 @@
         <v>46371.0</v>
       </c>
       <c r="B210" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C210" s="49">
         <v>132.4</v>
@@ -15628,7 +15626,7 @@
         <v>46393.0</v>
       </c>
       <c r="B214" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C214" s="49">
         <v>950.0</v>
@@ -15658,7 +15656,7 @@
         <v>46397.0</v>
       </c>
       <c r="B216" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C216" s="49">
         <v>65.0</v>
@@ -15688,7 +15686,7 @@
         <v>46399.0</v>
       </c>
       <c r="B218" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C218" s="49">
         <v>983.13</v>
@@ -15718,7 +15716,7 @@
         <v>46402.0</v>
       </c>
       <c r="B220" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C220" s="49">
         <v>132.4</v>
@@ -15778,7 +15776,7 @@
         <v>46424.0</v>
       </c>
       <c r="B224" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C224" s="49">
         <v>950.0</v>
@@ -15808,7 +15806,7 @@
         <v>46428.0</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C226" s="49">
         <v>65.0</v>
@@ -15823,7 +15821,7 @@
         <v>46428.0</v>
       </c>
       <c r="B227" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C227" s="49">
         <v>530.0</v>
@@ -15853,7 +15851,7 @@
         <v>46430.0</v>
       </c>
       <c r="B229" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C229" s="49">
         <v>981.95</v>
@@ -15868,7 +15866,7 @@
         <v>46430.0</v>
       </c>
       <c r="B230" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C230" s="49">
         <v>2831.4</v>
@@ -15883,7 +15881,7 @@
         <v>46430.0</v>
       </c>
       <c r="B231" s="42" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C231" s="49">
         <v>1407.65</v>
@@ -15913,7 +15911,7 @@
         <v>46433.0</v>
       </c>
       <c r="B233" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C233" s="49">
         <v>132.4</v>
@@ -15928,7 +15926,7 @@
         <v>46437.0</v>
       </c>
       <c r="B234" s="42" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C234" s="49">
         <v>460.0</v>
@@ -15988,7 +15986,7 @@
         <v>46451.0</v>
       </c>
       <c r="B238" s="42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C238" s="49">
         <v>81.8</v>
@@ -16003,7 +16001,7 @@
         <v>46452.0</v>
       </c>
       <c r="B239" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C239" s="49">
         <v>950.0</v>
@@ -16048,7 +16046,7 @@
         <v>46456.0</v>
       </c>
       <c r="B242" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C242" s="49">
         <v>65.0</v>
@@ -16078,7 +16076,7 @@
         <v>46458.0</v>
       </c>
       <c r="B244" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C244" s="49">
         <v>981.22</v>
@@ -16093,7 +16091,7 @@
         <v>46458.0</v>
       </c>
       <c r="B245" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C245" s="49">
         <v>2831.4</v>
@@ -16123,7 +16121,7 @@
         <v>46461.0</v>
       </c>
       <c r="B247" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C247" s="49">
         <v>132.4</v>
@@ -16168,7 +16166,7 @@
         <v>46477.0</v>
       </c>
       <c r="B250" s="42" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C250" s="49">
         <v>35.62</v>
@@ -16198,7 +16196,7 @@
         <v>46483.0</v>
       </c>
       <c r="B252" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C252" s="49">
         <v>950.0</v>
@@ -16228,7 +16226,7 @@
         <v>46487.0</v>
       </c>
       <c r="B254" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C254" s="49">
         <v>65.0</v>
@@ -16258,7 +16256,7 @@
         <v>46489.0</v>
       </c>
       <c r="B256" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C256" s="49">
         <v>981.22</v>
@@ -16273,7 +16271,7 @@
         <v>46489.0</v>
       </c>
       <c r="B257" s="42" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C257" s="49">
         <v>2831.4</v>
@@ -16303,7 +16301,7 @@
         <v>46492.0</v>
       </c>
       <c r="B259" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C259" s="49">
         <v>132.4</v>
@@ -16348,7 +16346,7 @@
         <v>46507.0</v>
       </c>
       <c r="B262" s="42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C262" s="49">
         <v>530.0</v>
@@ -16378,7 +16376,7 @@
         <v>46513.0</v>
       </c>
       <c r="B264" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C264" s="49">
         <v>950.0</v>
@@ -16408,7 +16406,7 @@
         <v>46517.0</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C266" s="49">
         <v>65.0</v>
@@ -16438,7 +16436,7 @@
         <v>46519.0</v>
       </c>
       <c r="B268" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C268" s="47">
         <v>980.86</v>
@@ -16453,7 +16451,7 @@
         <v>46522.0</v>
       </c>
       <c r="B269" s="43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C269" s="49">
         <v>132.4</v>
@@ -19894,30 +19892,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="C2" s="30">
         <v>46146.0</v>
@@ -19954,7 +19952,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B4" s="59" t="s">
         <v>109</v>
@@ -19974,10 +19972,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>111</v>
+        <v>41</v>
       </c>
       <c r="C5" s="30">
         <v>46148.0</v>
@@ -23995,24 +23993,24 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="66" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B2" s="25">
         <v>46057.0</v>
@@ -24024,12 +24022,12 @@
         <v>4000.0</v>
       </c>
       <c r="E2" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="66" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B3" s="25">
         <v>46057.0</v>
@@ -24041,7 +24039,7 @@
         <v>6630.64</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -24058,12 +24056,12 @@
         <v>10342.0</v>
       </c>
       <c r="E4" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="66" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B5" s="27">
         <v>46058.0</v>
@@ -24075,12 +24073,12 @@
         <v>4124.75</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="66" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B6" s="27">
         <v>46058.0</v>
@@ -24092,12 +24090,12 @@
         <v>5400.0</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="27">
         <v>46059.0</v>
@@ -24109,12 +24107,12 @@
         <v>2063.11</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="71">
         <v>46084.0</v>
@@ -24126,7 +24124,7 @@
         <v>3000.0</v>
       </c>
       <c r="E8" s="73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -24143,12 +24141,12 @@
         <v>3000.0</v>
       </c>
       <c r="E9" s="73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="66" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" s="71">
         <v>46087.0</v>
@@ -24160,12 +24158,12 @@
         <v>8587.0</v>
       </c>
       <c r="E10" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="66" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="71">
         <v>46118.0</v>
@@ -24182,7 +24180,7 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="59" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B12" s="30">
         <v>46146.0</v>
@@ -24199,7 +24197,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="59" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B13" s="30">
         <v>46150.0</v>
@@ -36743,7 +36741,7 @@
     </row>
     <row r="58">
       <c r="A58" s="82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B58" s="83">
         <v>105.0</v>
@@ -36884,7 +36882,7 @@
     </row>
     <row r="59">
       <c r="A59" s="82" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B59" s="83">
         <v>103.0</v>
@@ -37152,7 +37150,7 @@
     </row>
     <row r="61">
       <c r="A61" s="82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B61" s="83">
         <v>230.0</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="461849869"/>
-        <c:axId val="1206437602"/>
+        <c:axId val="1812406660"/>
+        <c:axId val="130072092"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="461849869"/>
+        <c:axId val="1812406660"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1206437602"/>
+        <c:crossAx val="130072092"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1206437602"/>
+        <c:axId val="130072092"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="461849869"/>
+        <c:crossAx val="1812406660"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="427">
   <si>
     <t>Mês</t>
   </si>
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1812406660"/>
-        <c:axId val="130072092"/>
+        <c:axId val="884757071"/>
+        <c:axId val="1327428171"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1812406660"/>
+        <c:axId val="884757071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="130072092"/>
+        <c:crossAx val="1327428171"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="130072092"/>
+        <c:axId val="1327428171"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1812406660"/>
+        <c:crossAx val="884757071"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -14110,8 +14110,12 @@
       <c r="C113" s="49">
         <v>132.4</v>
       </c>
-      <c r="D113" s="42"/>
-      <c r="E113" s="42"/>
+      <c r="D113" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E113" s="59" t="s">
+        <v>45</v>
+      </c>
       <c r="G113" s="57"/>
       <c r="H113" s="58"/>
     </row>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Resumo Mensal'!$A$1:$G$121</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Salários'!$A$1:$D$43</definedName>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$271</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$273</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Switching!$A$1:$F$5</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Inventário de Lotes'!$A$1:$E$15</definedName>
     <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$86</definedName>
@@ -24,14 +24,14 @@
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="zrWWILu0ks1leT9OcrKOTqpS0SYnhSRbpltIQXfRWig="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="OfLD/fPL1u84Fvh55VsFZ5OehLJPi2Z4ILPY6bnln4g="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="427">
   <si>
     <t>Mês</t>
   </si>
@@ -168,61 +168,64 @@
     <t>Claro</t>
   </si>
   <si>
+    <t>Lote 2800 mai.</t>
+  </si>
+  <si>
     <t>Lote 3120 mai</t>
+  </si>
+  <si>
+    <t>Resto praia</t>
   </si>
   <si>
     <t xml:space="preserve">Lote 3800 mai. </t>
   </si>
   <si>
-    <t>Resto praia</t>
+    <t>Lote 4000 fev.</t>
   </si>
   <si>
-    <t>Lote 4000 fev.</t>
+    <t>Cartão PS</t>
   </si>
   <si>
     <t>Lote 4124,75 fev.</t>
   </si>
   <si>
-    <t>Cartão PS</t>
+    <t>Concurso ze</t>
   </si>
   <si>
     <t>Lote 5400 fev.</t>
   </si>
   <si>
-    <t>Concurso ze</t>
+    <t>Condomínio</t>
   </si>
   <si>
     <t>Lote 5680 abr.</t>
   </si>
   <si>
-    <t>Condomínio</t>
+    <t>Pelada</t>
   </si>
   <si>
     <t>Lote 6630,64 fev.</t>
   </si>
   <si>
-    <t>Pelada</t>
+    <t>Cemig SIM</t>
   </si>
   <si>
     <t>Lote 7500 mai.</t>
   </si>
   <si>
-    <t>Cemig SIM</t>
+    <t>Faxina Rosa</t>
   </si>
   <si>
     <t>Lote 8500 mar.</t>
   </si>
   <si>
-    <t>Faxina Rosa</t>
-  </si>
-  <si>
     <t>Internet</t>
   </si>
   <si>
-    <t>Total geral</t>
+    <t>Aluguel</t>
   </si>
   <si>
-    <t>Aluguel</t>
+    <t>Total geral</t>
   </si>
   <si>
     <t>Tratamento Lara</t>
@@ -379,9 +382,6 @@
   </si>
   <si>
     <t>CDB Sofisa 105%</t>
-  </si>
-  <si>
-    <t>Lote 2800 mai.</t>
   </si>
   <si>
     <t xml:space="preserve">Lote 3000 mai. </t>
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="884757071"/>
-        <c:axId val="1327428171"/>
+        <c:axId val="427096795"/>
+        <c:axId val="1732889436"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="884757071"/>
+        <c:axId val="427096795"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1327428171"/>
+        <c:crossAx val="1732889436"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1327428171"/>
+        <c:axId val="1732889436"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="884757071"/>
+        <c:crossAx val="427096795"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2151,7 +2151,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:E1015" sheet="Todos os Gastos"/>
+    <worksheetSource ref="C1:E1017" sheet="Todos os Gastos"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="Valor" numFmtId="166">
@@ -2245,10 +2245,13 @@
         <n v="787.11"/>
         <n v="26.0"/>
         <n v="24.0"/>
-        <n v="5372.0"/>
-        <n v="113.31"/>
+        <n v="2913.53"/>
+        <n v="2811.15"/>
+        <n v="73.19"/>
+        <n v="19.02"/>
         <n v="580.0"/>
         <n v="7200.0"/>
+        <n v="113.31"/>
         <n v="930.0"/>
         <n v="6800.0"/>
         <n v="1500.0"/>
@@ -2270,6 +2273,7 @@
         <n v="35.62"/>
         <n v="6350.0"/>
         <n v="980.86"/>
+        <n v="5372.0"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -2294,6 +2298,7 @@
         <s v="Lote 3800 mai. "/>
         <s v="Lote 190 mai"/>
         <s v="Lote 3120 mai"/>
+        <s v="Lote 2800 mai."/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -2303,7 +2308,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Todos os Gastos" cacheId="0" dataCaption="" compact="0" compactData="0">
-  <location ref="G1:H15" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <location ref="G1:H16" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields>
     <pivotField name="Valor" dataField="1" compact="0" numFmtId="166" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items>
@@ -2422,6 +2427,10 @@
         <item x="112"/>
         <item x="113"/>
         <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2434,10 +2443,11 @@
     </pivotField>
     <pivotField name="Lote usado" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items>
-        <item h="1" x="13"/>
+        <item h="1" x="14"/>
         <item x="1"/>
         <item x="11"/>
         <item x="2"/>
+        <item x="13"/>
         <item x="12"/>
         <item x="10"/>
         <item x="3"/>
@@ -2771,7 +2781,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUM(B:B)</f>
-        <v>258372.88</v>
+        <v>258704.46</v>
       </c>
       <c r="L3" s="9">
         <f>EOMONTH(MAX(MAX('Todos os Gastos'!$A:$A),MAX('Salários'!$B:$B)),-1)+1</f>
@@ -2852,7 +2862,7 @@
       </c>
       <c r="J5" s="8">
         <f>SUMIFS(D:D,A:A,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A:A,"&lt;&gt;")</f>
-        <v>14031.87</v>
+        <v>14100.29</v>
       </c>
       <c r="L5" s="10">
         <v>46023.0</v>
@@ -2865,7 +2875,7 @@
       </c>
       <c r="B6" s="3">
         <f>IF($A6="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
-        <v>15446.39</v>
+        <v>15377.97</v>
       </c>
       <c r="C6" s="3">
         <f>IF($A6="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A6,'Salários'!$B:$B,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -2873,11 +2883,11 @@
       </c>
       <c r="D6" s="3">
         <f t="shared" si="1"/>
-        <v>1770.33</v>
+        <v>1838.75</v>
       </c>
       <c r="E6" s="4">
         <f>IF($A6="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A6,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A6,1)))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4">
         <f>IF($A6="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A6,'Salários'!$B:$B,"&lt;"&amp;EDATE($A6,1)))</f>
@@ -2885,14 +2895,14 @@
       </c>
       <c r="G6" s="3">
         <f t="shared" si="2"/>
-        <v>14031.87</v>
+        <v>14100.29</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2487.5499999999865)</f>
-        <v>-2487.55</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2819.1299999999883)</f>
+        <v>-2819.13</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -2902,7 +2912,7 @@
       </c>
       <c r="B7" s="6">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>14199.18</v>
+        <v>14599.18</v>
       </c>
       <c r="C7" s="6">
         <f>IF($A7="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2910,11 +2920,11 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>280.82</v>
+        <v>-119.18</v>
       </c>
       <c r="E7" s="4">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="4">
         <f>IF($A7="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2922,14 +2932,14 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>14312.69</v>
+        <v>13981.11</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(D:D,A:A,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A:A,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>1770.33</v>
+        <v>1838.75</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -2959,14 +2969,14 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>13533.51</v>
+        <v>13201.93</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="8">
         <f>AVERAGEIF(D:D,"&lt;&gt;",D:D)</f>
-        <v>-146.3264706</v>
+        <v>-165.8311765</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -2996,7 +3006,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="2"/>
-        <v>12112.53</v>
+        <v>11780.95</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>16</v>
@@ -3033,7 +3043,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>10123.35</v>
+        <v>9791.77</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>17</v>
@@ -3070,7 +3080,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="2"/>
-        <v>8534.37</v>
+        <v>8202.79</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>18</v>
@@ -3107,7 +3117,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>7445.19</v>
+        <v>7113.61</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>19</v>
@@ -3144,7 +3154,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="2"/>
-        <v>3236.01</v>
+        <v>2904.43</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -3174,7 +3184,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>6075.75</v>
+        <v>5744.17</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -3204,7 +3214,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>3004.85</v>
+        <v>2673.27</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -3234,7 +3244,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>-176.27</v>
+        <v>-507.85</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -3264,7 +3274,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>-4529.32</v>
+        <v>-4860.9</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -3294,7 +3304,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>-2487.55</v>
+        <v>-2819.13</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -12054,7 +12064,7 @@
         <v>46038.0</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="36">
         <v>135.89</v>
@@ -12086,8 +12096,6 @@
         <v>38</v>
       </c>
       <c r="F16" s="38"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
       <c r="I16" s="41"/>
       <c r="J16" s="41"/>
     </row>
@@ -12118,7 +12126,7 @@
         <v>46056.0</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="47">
         <v>530.0</v>
@@ -12140,7 +12148,7 @@
         <v>46057.0</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="45">
         <v>78.0</v>
@@ -12228,7 +12236,7 @@
         <v>46057.0</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="45">
         <v>75.0</v>
@@ -12351,7 +12359,7 @@
         <v>37</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" s="38"/>
       <c r="G28" s="39"/>
@@ -12377,7 +12385,7 @@
         <v>37</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F29" s="38"/>
       <c r="G29" s="39"/>
@@ -12399,7 +12407,7 @@
         <v>37</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F30" s="38"/>
       <c r="G30" s="39"/>
@@ -12434,7 +12442,7 @@
         <v>46065.0</v>
       </c>
       <c r="B32" s="42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" s="47">
         <v>1407.63</v>
@@ -12456,7 +12464,7 @@
         <v>46069.0</v>
       </c>
       <c r="B33" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="47">
         <v>131.4</v>
@@ -12478,7 +12486,7 @@
         <v>46072.0</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C34" s="49">
         <v>460.0</v>
@@ -12500,7 +12508,7 @@
         <v>46072.0</v>
       </c>
       <c r="B35" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="49">
         <v>2831.4</v>
@@ -12509,7 +12517,7 @@
         <v>37</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F35" s="52"/>
       <c r="G35" s="39"/>
@@ -12531,7 +12539,7 @@
         <v>37</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F36" s="52"/>
       <c r="G36" s="39"/>
@@ -12553,7 +12561,7 @@
         <v>37</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F37" s="52"/>
       <c r="G37" s="39"/>
@@ -12588,7 +12596,7 @@
         <v>46086.0</v>
       </c>
       <c r="B39" s="42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="49">
         <v>520.0</v>
@@ -12610,7 +12618,7 @@
         <v>46086.0</v>
       </c>
       <c r="B40" s="42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="49">
         <v>60.0</v>
@@ -12632,7 +12640,7 @@
         <v>46086.0</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="47">
         <v>60.0</v>
@@ -12654,7 +12662,7 @@
         <v>46086.0</v>
       </c>
       <c r="B42" s="42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C42" s="49">
         <v>58.0</v>
@@ -12676,7 +12684,7 @@
         <v>46086.0</v>
       </c>
       <c r="B43" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C43" s="49">
         <v>138.69</v>
@@ -12698,7 +12706,7 @@
         <v>46086.0</v>
       </c>
       <c r="B44" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C44" s="49">
         <v>40.0</v>
@@ -12720,7 +12728,7 @@
         <v>46086.0</v>
       </c>
       <c r="B45" s="42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C45" s="49">
         <v>40.0</v>
@@ -12742,7 +12750,7 @@
         <v>46086.0</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C46" s="49">
         <v>81.8</v>
@@ -12817,7 +12825,7 @@
         <v>37</v>
       </c>
       <c r="E49" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F49" s="54"/>
       <c r="G49" s="39"/>
@@ -12839,7 +12847,7 @@
         <v>37</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F50" s="54"/>
       <c r="G50" s="39"/>
@@ -12852,7 +12860,7 @@
         <v>46091.0</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C51" s="49">
         <v>65.0</v>
@@ -12861,7 +12869,7 @@
         <v>37</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F51" s="54"/>
       <c r="G51" s="39"/>
@@ -12883,7 +12891,7 @@
         <v>37</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F52" s="54"/>
       <c r="G52" s="39"/>
@@ -12905,7 +12913,7 @@
         <v>37</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F53" s="54"/>
       <c r="G53" s="39"/>
@@ -12918,7 +12926,7 @@
         <v>46094.0</v>
       </c>
       <c r="B54" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C54" s="55">
         <v>1368.12</v>
@@ -12949,7 +12957,7 @@
         <v>37</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F55" s="54"/>
       <c r="G55" s="39"/>
@@ -12971,7 +12979,7 @@
         <v>37</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F56" s="54"/>
       <c r="G56" s="39"/>
@@ -12984,7 +12992,7 @@
         <v>46094.0</v>
       </c>
       <c r="B57" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C57" s="55">
         <v>660.99</v>
@@ -12993,7 +13001,7 @@
         <v>37</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F57" s="54"/>
       <c r="G57" s="39"/>
@@ -13006,7 +13014,7 @@
         <v>46094.0</v>
       </c>
       <c r="B58" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C58" s="49">
         <v>807.2</v>
@@ -13015,7 +13023,7 @@
         <v>37</v>
       </c>
       <c r="E58" s="35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F58" s="54"/>
       <c r="G58" s="39"/>
@@ -13028,7 +13036,7 @@
         <v>46097.0</v>
       </c>
       <c r="B59" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C59" s="49">
         <v>132.4</v>
@@ -13037,7 +13045,7 @@
         <v>37</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F59" s="54"/>
       <c r="G59" s="39"/>
@@ -13059,7 +13067,7 @@
         <v>37</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F60" s="54"/>
       <c r="G60" s="39"/>
@@ -13081,7 +13089,7 @@
         <v>37</v>
       </c>
       <c r="E61" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F61" s="54"/>
       <c r="G61" s="39"/>
@@ -13094,7 +13102,7 @@
         <v>46101.0</v>
       </c>
       <c r="B62" s="42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C62" s="49">
         <v>35.0</v>
@@ -13103,7 +13111,7 @@
         <v>37</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F62" s="54"/>
       <c r="G62" s="39"/>
@@ -13125,7 +13133,7 @@
         <v>37</v>
       </c>
       <c r="E63" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F63" s="54"/>
       <c r="G63" s="39"/>
@@ -13138,7 +13146,7 @@
         <v>46101.0</v>
       </c>
       <c r="B64" s="42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C64" s="49">
         <v>450.0</v>
@@ -13147,7 +13155,7 @@
         <v>37</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F64" s="54"/>
       <c r="G64" s="39"/>
@@ -13169,7 +13177,7 @@
         <v>37</v>
       </c>
       <c r="E65" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F65" s="54"/>
       <c r="G65" s="39"/>
@@ -13182,7 +13190,7 @@
         <v>46113.0</v>
       </c>
       <c r="B66" s="42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C66" s="56">
         <v>36.02</v>
@@ -13204,7 +13212,7 @@
         <v>46114.0</v>
       </c>
       <c r="B67" s="42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" s="49">
         <v>150.0</v>
@@ -13248,7 +13256,7 @@
         <v>46114.0</v>
       </c>
       <c r="B69" s="42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C69" s="49">
         <v>170.0</v>
@@ -13270,7 +13278,7 @@
         <v>46114.0</v>
       </c>
       <c r="B70" s="42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C70" s="49">
         <v>900.0</v>
@@ -13292,7 +13300,7 @@
         <v>46114.0</v>
       </c>
       <c r="B71" s="42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C71" s="49">
         <v>170.0</v>
@@ -13314,7 +13322,7 @@
         <v>46114.0</v>
       </c>
       <c r="B72" s="42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C72" s="49">
         <v>52.0</v>
@@ -13336,7 +13344,7 @@
         <v>46114.0</v>
       </c>
       <c r="B73" s="42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C73" s="49">
         <v>120.0</v>
@@ -13358,7 +13366,7 @@
         <v>46114.0</v>
       </c>
       <c r="B74" s="42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C74" s="49">
         <v>35.0</v>
@@ -13389,7 +13397,7 @@
         <v>37</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F75" s="54"/>
       <c r="G75" s="39"/>
@@ -13421,7 +13429,7 @@
         <v>46120.0</v>
       </c>
       <c r="B77" s="42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C77" s="49">
         <v>70.0</v>
@@ -13430,7 +13438,7 @@
         <v>37</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G77" s="57"/>
       <c r="H77" s="58"/>
@@ -13449,7 +13457,7 @@
         <v>37</v>
       </c>
       <c r="E78" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G78" s="57"/>
       <c r="H78" s="58"/>
@@ -13459,7 +13467,7 @@
         <v>46122.0</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C79" s="49">
         <v>434.75</v>
@@ -13468,7 +13476,7 @@
         <v>37</v>
       </c>
       <c r="E79" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G79" s="57"/>
       <c r="H79" s="58"/>
@@ -13478,7 +13486,7 @@
         <v>46122.0</v>
       </c>
       <c r="B80" s="42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C80" s="49">
         <v>70.0</v>
@@ -13497,7 +13505,7 @@
         <v>46122.0</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C81" s="49">
         <v>65.0</v>
@@ -13535,7 +13543,7 @@
         <v>46126.0</v>
       </c>
       <c r="B83" s="43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C83" s="47">
         <v>45.0</v>
@@ -13544,7 +13552,7 @@
         <v>37</v>
       </c>
       <c r="E83" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G83" s="57"/>
       <c r="H83" s="58"/>
@@ -13554,7 +13562,7 @@
         <v>46126.0</v>
       </c>
       <c r="B84" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C84" s="47">
         <v>151.71</v>
@@ -13563,7 +13571,7 @@
         <v>37</v>
       </c>
       <c r="E84" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G84" s="57"/>
       <c r="H84" s="58"/>
@@ -13573,7 +13581,7 @@
         <v>46126.0</v>
       </c>
       <c r="B85" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C85" s="47">
         <v>206.8</v>
@@ -13582,7 +13590,7 @@
         <v>37</v>
       </c>
       <c r="E85" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G85" s="57"/>
       <c r="H85" s="58"/>
@@ -13601,7 +13609,7 @@
         <v>37</v>
       </c>
       <c r="E86" s="35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G86" s="57"/>
       <c r="H86" s="58"/>
@@ -13611,7 +13619,7 @@
         <v>46126.0</v>
       </c>
       <c r="B87" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C87" s="47">
         <v>2472.89</v>
@@ -13630,7 +13638,7 @@
         <v>46127.0</v>
       </c>
       <c r="B88" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C88" s="49">
         <v>132.4</v>
@@ -13639,7 +13647,7 @@
         <v>37</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G88" s="57"/>
       <c r="H88" s="58"/>
@@ -13658,7 +13666,7 @@
         <v>37</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G89" s="57"/>
       <c r="H89" s="58"/>
@@ -13677,7 +13685,7 @@
         <v>37</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G90" s="57"/>
       <c r="H90" s="58"/>
@@ -13696,7 +13704,7 @@
         <v>37</v>
       </c>
       <c r="E91" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G91" s="57"/>
       <c r="H91" s="58"/>
@@ -13706,7 +13714,7 @@
         <v>46132.0</v>
       </c>
       <c r="B92" s="43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C92" s="47">
         <v>120.75</v>
@@ -13715,7 +13723,7 @@
         <v>37</v>
       </c>
       <c r="E92" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G92" s="57"/>
       <c r="H92" s="58"/>
@@ -13734,7 +13742,7 @@
         <v>37</v>
       </c>
       <c r="E93" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G93" s="57"/>
       <c r="H93" s="58"/>
@@ -13772,7 +13780,7 @@
         <v>37</v>
       </c>
       <c r="E95" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G95" s="57"/>
       <c r="H95" s="58"/>
@@ -13782,7 +13790,7 @@
         <v>46142.0</v>
       </c>
       <c r="B96" s="43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C96" s="47">
         <v>400.0</v>
@@ -13791,7 +13799,7 @@
         <v>37</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G96" s="57"/>
       <c r="H96" s="58"/>
@@ -13801,7 +13809,7 @@
         <v>46142.0</v>
       </c>
       <c r="B97" s="42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C97" s="49">
         <v>530.0</v>
@@ -13810,7 +13818,7 @@
         <v>37</v>
       </c>
       <c r="E97" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G97" s="57"/>
       <c r="H97" s="58"/>
@@ -13829,7 +13837,7 @@
         <v>37</v>
       </c>
       <c r="E98" s="37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G98" s="57"/>
       <c r="H98" s="58"/>
@@ -13839,7 +13847,7 @@
         <v>46146.0</v>
       </c>
       <c r="B99" s="43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C99" s="47">
         <v>59.8</v>
@@ -13848,7 +13856,7 @@
         <v>37</v>
       </c>
       <c r="E99" s="37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G99" s="57"/>
       <c r="H99" s="58"/>
@@ -13858,7 +13866,7 @@
         <v>46146.0</v>
       </c>
       <c r="B100" s="43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C100" s="47">
         <v>250.0</v>
@@ -13867,7 +13875,7 @@
         <v>37</v>
       </c>
       <c r="E100" s="37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G100" s="57"/>
       <c r="H100" s="58"/>
@@ -13886,7 +13894,7 @@
         <v>37</v>
       </c>
       <c r="E101" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G101" s="57"/>
       <c r="H101" s="58"/>
@@ -13905,7 +13913,7 @@
         <v>37</v>
       </c>
       <c r="E102" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G102" s="57"/>
       <c r="H102" s="58"/>
@@ -13934,7 +13942,7 @@
         <v>46150.0</v>
       </c>
       <c r="B104" s="35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C104" s="49">
         <v>65.0</v>
@@ -13943,7 +13951,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G104" s="57"/>
       <c r="H104" s="58"/>
@@ -13953,7 +13961,7 @@
         <v>46150.0</v>
       </c>
       <c r="B105" s="42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C105" s="47">
         <v>120.0</v>
@@ -13962,7 +13970,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G105" s="57"/>
       <c r="H105" s="58"/>
@@ -13972,7 +13980,7 @@
         <v>46151.0</v>
       </c>
       <c r="B106" s="43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C106" s="47">
         <v>44.0</v>
@@ -13981,7 +13989,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="59" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G106" s="57"/>
       <c r="H106" s="58"/>
@@ -14000,7 +14008,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="59" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G107" s="57"/>
       <c r="H107" s="58"/>
@@ -14038,7 +14046,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="59" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G109" s="57"/>
       <c r="H109" s="58"/>
@@ -14048,7 +14056,7 @@
         <v>46155.0</v>
       </c>
       <c r="B110" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C110" s="49">
         <v>2831.4</v>
@@ -14057,7 +14065,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="59" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G110" s="57"/>
       <c r="H110" s="58"/>
@@ -14076,7 +14084,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="59" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G111" s="57"/>
       <c r="H111" s="58"/>
@@ -14095,7 +14103,7 @@
         <v>37</v>
       </c>
       <c r="E112" s="59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G112" s="57"/>
       <c r="H112" s="58"/>
@@ -14105,7 +14113,7 @@
         <v>46157.0</v>
       </c>
       <c r="B113" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C113" s="49">
         <v>132.4</v>
@@ -14114,7 +14122,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G113" s="57"/>
       <c r="H113" s="58"/>
@@ -14127,10 +14135,14 @@
         <v>36</v>
       </c>
       <c r="C114" s="47">
-        <v>5372.0</v>
-      </c>
-      <c r="D114" s="42"/>
-      <c r="E114" s="42"/>
+        <v>2913.53</v>
+      </c>
+      <c r="D114" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E114" s="59" t="s">
+        <v>46</v>
+      </c>
       <c r="G114" s="57"/>
       <c r="H114" s="58"/>
     </row>
@@ -14138,71 +14150,83 @@
       <c r="A115" s="34">
         <v>46162.0</v>
       </c>
-      <c r="B115" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C115" s="49">
-        <v>113.31</v>
-      </c>
-      <c r="D115" s="42"/>
-      <c r="E115" s="42"/>
+      <c r="B115" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C115" s="47">
+        <v>2811.15</v>
+      </c>
+      <c r="D115" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E115" s="59" t="s">
+        <v>45</v>
+      </c>
       <c r="G115" s="57"/>
       <c r="H115" s="58"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
-      <c r="A116" s="46">
-        <v>46172.0</v>
+      <c r="A116" s="34">
+        <v>46162.0</v>
       </c>
       <c r="B116" s="43" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="C116" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D116" s="35"/>
-      <c r="E116" s="35"/>
+        <v>73.19</v>
+      </c>
+      <c r="D116" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E116" s="43" t="s">
+        <v>38</v>
+      </c>
       <c r="G116" s="57"/>
       <c r="H116" s="58"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="34">
-        <v>46175.0</v>
-      </c>
-      <c r="B117" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C117" s="49">
-        <v>580.0</v>
-      </c>
-      <c r="D117" s="42"/>
-      <c r="E117" s="42"/>
+        <v>46162.0</v>
+      </c>
+      <c r="B117" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C117" s="47">
+        <v>19.02</v>
+      </c>
+      <c r="D117" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E117" s="59" t="s">
+        <v>46</v>
+      </c>
       <c r="G117" s="57"/>
       <c r="H117" s="58"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="34">
-        <v>46179.0</v>
+        <v>46175.0</v>
       </c>
       <c r="B118" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C118" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D118" s="42"/>
-      <c r="E118" s="42"/>
+        <v>92</v>
+      </c>
+      <c r="C118" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D118" s="35"/>
+      <c r="E118" s="35"/>
       <c r="G118" s="57"/>
       <c r="H118" s="58"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
-      <c r="A119" s="46">
-        <v>46180.0</v>
-      </c>
-      <c r="B119" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C119" s="47">
-        <v>110.0</v>
+      <c r="A119" s="34">
+        <v>46175.0</v>
+      </c>
+      <c r="B119" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" s="49">
+        <v>580.0</v>
       </c>
       <c r="D119" s="42"/>
       <c r="E119" s="42"/>
@@ -14211,13 +14235,13 @@
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="34">
-        <v>46183.0</v>
-      </c>
-      <c r="B120" s="35" t="s">
-        <v>75</v>
+        <v>46179.0</v>
+      </c>
+      <c r="B120" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C120" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D120" s="42"/>
       <c r="E120" s="42"/>
@@ -14225,14 +14249,14 @@
       <c r="H120" s="58"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
-      <c r="A121" s="34">
-        <v>46183.0</v>
-      </c>
-      <c r="B121" s="42" t="s">
-        <v>84</v>
+      <c r="A121" s="46">
+        <v>46180.0</v>
+      </c>
+      <c r="B121" s="43" t="s">
+        <v>44</v>
       </c>
       <c r="C121" s="47">
-        <v>120.0</v>
+        <v>110.0</v>
       </c>
       <c r="D121" s="42"/>
       <c r="E121" s="42"/>
@@ -14243,11 +14267,11 @@
       <c r="A122" s="34">
         <v>46183.0</v>
       </c>
-      <c r="B122" s="42" t="s">
-        <v>64</v>
+      <c r="B122" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C122" s="49">
-        <v>530.0</v>
+        <v>65.0</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="42"/>
@@ -14256,13 +14280,13 @@
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="34">
-        <v>46184.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B123" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C123" s="49">
-        <v>95.12</v>
+        <v>85</v>
+      </c>
+      <c r="C123" s="47">
+        <v>120.0</v>
       </c>
       <c r="D123" s="42"/>
       <c r="E123" s="42"/>
@@ -14271,13 +14295,13 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="34">
-        <v>46185.0</v>
-      </c>
-      <c r="B124" s="43" t="s">
-        <v>63</v>
+        <v>46183.0</v>
+      </c>
+      <c r="B124" s="42" t="s">
+        <v>65</v>
       </c>
       <c r="C124" s="49">
-        <v>981.95</v>
+        <v>530.0</v>
       </c>
       <c r="D124" s="42"/>
       <c r="E124" s="42"/>
@@ -14286,13 +14310,13 @@
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="34">
-        <v>46185.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B125" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C125" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D125" s="42"/>
       <c r="E125" s="42"/>
@@ -14300,14 +14324,14 @@
       <c r="H125" s="58"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" s="46">
+      <c r="A126" s="34">
         <v>46185.0</v>
       </c>
       <c r="B126" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C126" s="49">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D126" s="42"/>
       <c r="E126" s="42"/>
@@ -14316,13 +14340,13 @@
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="34">
-        <v>46188.0</v>
-      </c>
-      <c r="B127" s="43" t="s">
-        <v>61</v>
+        <v>46185.0</v>
+      </c>
+      <c r="B127" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C127" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D127" s="42"/>
       <c r="E127" s="42"/>
@@ -14331,13 +14355,13 @@
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="46">
-        <v>46192.0</v>
-      </c>
-      <c r="B128" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="C128" s="47">
-        <v>40.0</v>
+        <v>46185.0</v>
+      </c>
+      <c r="B128" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C128" s="49">
+        <v>50.0</v>
       </c>
       <c r="D128" s="42"/>
       <c r="E128" s="42"/>
@@ -14346,13 +14370,13 @@
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="34">
-        <v>46193.0</v>
-      </c>
-      <c r="B129" s="35" t="s">
-        <v>36</v>
+        <v>46188.0</v>
+      </c>
+      <c r="B129" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C129" s="49">
-        <v>7200.0</v>
+        <v>132.4</v>
       </c>
       <c r="D129" s="42"/>
       <c r="E129" s="42"/>
@@ -14361,13 +14385,13 @@
     </row>
     <row r="130" ht="14.25" customHeight="1">
       <c r="A130" s="46">
-        <v>46193.0</v>
-      </c>
-      <c r="B130" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C130" s="49">
-        <v>113.31</v>
+        <v>46192.0</v>
+      </c>
+      <c r="B130" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C130" s="47">
+        <v>40.0</v>
       </c>
       <c r="D130" s="42"/>
       <c r="E130" s="42"/>
@@ -14375,80 +14399,80 @@
       <c r="H130" s="58"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
-      <c r="A131" s="46">
-        <v>46203.0</v>
-      </c>
-      <c r="B131" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C131" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D131" s="35"/>
-      <c r="E131" s="35"/>
-      <c r="F131" s="54"/>
-      <c r="G131" s="39"/>
-      <c r="H131" s="53"/>
-      <c r="I131" s="41"/>
-      <c r="J131" s="41"/>
+      <c r="A131" s="34">
+        <v>46193.0</v>
+      </c>
+      <c r="B131" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131" s="49">
+        <v>7200.0</v>
+      </c>
+      <c r="D131" s="42"/>
+      <c r="E131" s="42"/>
+      <c r="G131" s="57"/>
+      <c r="H131" s="58"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="34">
-        <v>46205.0</v>
-      </c>
-      <c r="B132" s="42" t="s">
-        <v>40</v>
+      <c r="A132" s="46">
+        <v>46193.0</v>
+      </c>
+      <c r="B132" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C132" s="49">
-        <v>930.0</v>
+        <v>113.31</v>
       </c>
       <c r="D132" s="42"/>
       <c r="E132" s="42"/>
-      <c r="F132" s="54"/>
-      <c r="G132" s="39"/>
-      <c r="H132" s="53"/>
-      <c r="I132" s="41"/>
-      <c r="J132" s="41"/>
+      <c r="G132" s="57"/>
+      <c r="H132" s="58"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="34">
-        <v>46209.0</v>
+      <c r="A133" s="46">
+        <v>46203.0</v>
       </c>
       <c r="B133" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C133" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D133" s="42"/>
-      <c r="E133" s="42"/>
-      <c r="G133" s="57"/>
-      <c r="H133" s="58"/>
+        <v>92</v>
+      </c>
+      <c r="C133" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D133" s="35"/>
+      <c r="E133" s="35"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="39"/>
+      <c r="H133" s="53"/>
+      <c r="I133" s="41"/>
+      <c r="J133" s="41"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c r="A134" s="46">
-        <v>46210.0</v>
-      </c>
-      <c r="B134" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C134" s="47">
-        <v>110.0</v>
+      <c r="A134" s="34">
+        <v>46205.0</v>
+      </c>
+      <c r="B134" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C134" s="49">
+        <v>930.0</v>
       </c>
       <c r="D134" s="42"/>
       <c r="E134" s="42"/>
-      <c r="G134" s="57"/>
-      <c r="H134" s="58"/>
+      <c r="F134" s="54"/>
+      <c r="G134" s="39"/>
+      <c r="H134" s="53"/>
+      <c r="I134" s="41"/>
+      <c r="J134" s="41"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="34">
-        <v>46213.0</v>
-      </c>
-      <c r="B135" s="35" t="s">
-        <v>75</v>
+        <v>46209.0</v>
+      </c>
+      <c r="B135" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C135" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D135" s="42"/>
       <c r="E135" s="42"/>
@@ -14456,14 +14480,14 @@
       <c r="H135" s="58"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="34">
-        <v>46214.0</v>
-      </c>
-      <c r="B136" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C136" s="49">
-        <v>95.12</v>
+      <c r="A136" s="46">
+        <v>46210.0</v>
+      </c>
+      <c r="B136" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C136" s="47">
+        <v>110.0</v>
       </c>
       <c r="D136" s="42"/>
       <c r="E136" s="42"/>
@@ -14472,13 +14496,13 @@
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="34">
-        <v>46215.0</v>
-      </c>
-      <c r="B137" s="43" t="s">
-        <v>63</v>
+        <v>46213.0</v>
+      </c>
+      <c r="B137" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C137" s="49">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D137" s="42"/>
       <c r="E137" s="42"/>
@@ -14487,13 +14511,13 @@
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="34">
-        <v>46215.0</v>
+        <v>46214.0</v>
       </c>
       <c r="B138" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C138" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="42"/>
@@ -14505,10 +14529,10 @@
         <v>46215.0</v>
       </c>
       <c r="B139" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C139" s="49">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="42"/>
@@ -14517,13 +14541,13 @@
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="34">
-        <v>46218.0</v>
-      </c>
-      <c r="B140" s="43" t="s">
-        <v>61</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C140" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="42"/>
@@ -14532,13 +14556,13 @@
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="34">
-        <v>46223.0</v>
-      </c>
-      <c r="B141" s="35" t="s">
-        <v>36</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B141" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C141" s="49">
-        <v>6800.0</v>
+        <v>50.0</v>
       </c>
       <c r="D141" s="42"/>
       <c r="E141" s="42"/>
@@ -14547,13 +14571,13 @@
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c r="A142" s="34">
-        <v>46223.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B142" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C142" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D142" s="42"/>
       <c r="E142" s="42"/>
@@ -14561,29 +14585,29 @@
       <c r="H142" s="58"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="46">
-        <v>46233.0</v>
-      </c>
-      <c r="B143" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C143" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D143" s="35"/>
-      <c r="E143" s="35"/>
+      <c r="A143" s="34">
+        <v>46223.0</v>
+      </c>
+      <c r="B143" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C143" s="49">
+        <v>6800.0</v>
+      </c>
+      <c r="D143" s="42"/>
+      <c r="E143" s="42"/>
       <c r="G143" s="57"/>
       <c r="H143" s="58"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="34">
-        <v>46236.0</v>
-      </c>
-      <c r="B144" s="42" t="s">
-        <v>40</v>
+        <v>46223.0</v>
+      </c>
+      <c r="B144" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C144" s="49">
-        <v>1500.0</v>
+        <v>113.31</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42"/>
@@ -14592,13 +14616,13 @@
     </row>
     <row r="145" ht="14.25" customHeight="1">
       <c r="A145" s="46">
-        <v>46239.0</v>
-      </c>
-      <c r="B145" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C145" s="49">
-        <v>81.8</v>
+        <v>46233.0</v>
+      </c>
+      <c r="B145" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C145" s="47">
+        <v>400.0</v>
       </c>
       <c r="D145" s="35"/>
       <c r="E145" s="35"/>
@@ -14607,13 +14631,13 @@
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="34">
-        <v>46240.0</v>
-      </c>
-      <c r="B146" s="43" t="s">
-        <v>60</v>
+        <v>46236.0</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C146" s="49">
-        <v>950.0</v>
+        <v>1500.0</v>
       </c>
       <c r="D146" s="42"/>
       <c r="E146" s="42"/>
@@ -14622,28 +14646,28 @@
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="46">
-        <v>46241.0</v>
-      </c>
-      <c r="B147" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C147" s="47">
-        <v>110.0</v>
-      </c>
-      <c r="D147" s="42"/>
-      <c r="E147" s="42"/>
+        <v>46239.0</v>
+      </c>
+      <c r="B147" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C147" s="49">
+        <v>81.8</v>
+      </c>
+      <c r="D147" s="35"/>
+      <c r="E147" s="35"/>
       <c r="G147" s="57"/>
       <c r="H147" s="58"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c r="A148" s="34">
-        <v>46244.0</v>
-      </c>
-      <c r="B148" s="35" t="s">
-        <v>75</v>
+        <v>46240.0</v>
+      </c>
+      <c r="B148" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C148" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D148" s="42"/>
       <c r="E148" s="42"/>
@@ -14651,14 +14675,14 @@
       <c r="H148" s="58"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
-      <c r="A149" s="34">
-        <v>46245.0</v>
-      </c>
-      <c r="B149" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C149" s="49">
-        <v>95.12</v>
+      <c r="A149" s="46">
+        <v>46241.0</v>
+      </c>
+      <c r="B149" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C149" s="47">
+        <v>110.0</v>
       </c>
       <c r="D149" s="42"/>
       <c r="E149" s="42"/>
@@ -14667,13 +14691,13 @@
     </row>
     <row r="150" ht="14.25" customHeight="1">
       <c r="A150" s="34">
-        <v>46246.0</v>
-      </c>
-      <c r="B150" s="43" t="s">
-        <v>63</v>
+        <v>46244.0</v>
+      </c>
+      <c r="B150" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C150" s="49">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D150" s="42"/>
       <c r="E150" s="42"/>
@@ -14682,13 +14706,13 @@
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c r="A151" s="34">
-        <v>46246.0</v>
+        <v>46245.0</v>
       </c>
       <c r="B151" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C151" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D151" s="42"/>
       <c r="E151" s="42"/>
@@ -14699,11 +14723,11 @@
       <c r="A152" s="34">
         <v>46246.0</v>
       </c>
-      <c r="B152" s="42" t="s">
-        <v>68</v>
+      <c r="B152" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="C152" s="49">
-        <v>460.0</v>
+        <v>981.95</v>
       </c>
       <c r="D152" s="42"/>
       <c r="E152" s="42"/>
@@ -14711,14 +14735,14 @@
       <c r="H152" s="58"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c r="A153" s="46">
+      <c r="A153" s="34">
         <v>46246.0</v>
       </c>
-      <c r="B153" s="43" t="s">
-        <v>56</v>
+      <c r="B153" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C153" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D153" s="42"/>
       <c r="E153" s="42"/>
@@ -14730,10 +14754,10 @@
         <v>46246.0</v>
       </c>
       <c r="B154" s="42" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C154" s="49">
-        <v>530.0</v>
+        <v>460.0</v>
       </c>
       <c r="D154" s="42"/>
       <c r="E154" s="42"/>
@@ -14741,14 +14765,14 @@
       <c r="H154" s="58"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="34">
-        <v>46249.0</v>
+      <c r="A155" s="46">
+        <v>46246.0</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C155" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D155" s="42"/>
       <c r="E155" s="42"/>
@@ -14757,13 +14781,13 @@
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="34">
-        <v>46254.0</v>
-      </c>
-      <c r="B156" s="35" t="s">
-        <v>36</v>
+        <v>46246.0</v>
+      </c>
+      <c r="B156" s="42" t="s">
+        <v>65</v>
       </c>
       <c r="C156" s="49">
-        <v>5800.0</v>
+        <v>530.0</v>
       </c>
       <c r="D156" s="42"/>
       <c r="E156" s="42"/>
@@ -14772,13 +14796,13 @@
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="34">
-        <v>46254.0</v>
+        <v>46249.0</v>
       </c>
       <c r="B157" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C157" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D157" s="42"/>
       <c r="E157" s="42"/>
@@ -14786,29 +14810,29 @@
       <c r="H157" s="58"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="46">
-        <v>46264.0</v>
-      </c>
-      <c r="B158" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C158" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D158" s="35"/>
-      <c r="E158" s="35"/>
+      <c r="A158" s="34">
+        <v>46254.0</v>
+      </c>
+      <c r="B158" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C158" s="49">
+        <v>5800.0</v>
+      </c>
+      <c r="D158" s="42"/>
+      <c r="E158" s="42"/>
       <c r="G158" s="57"/>
       <c r="H158" s="58"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c r="A159" s="34">
-        <v>46267.0</v>
-      </c>
-      <c r="B159" s="42" t="s">
-        <v>40</v>
+        <v>46254.0</v>
+      </c>
+      <c r="B159" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C159" s="49">
-        <v>2000.0</v>
+        <v>113.31</v>
       </c>
       <c r="D159" s="42"/>
       <c r="E159" s="42"/>
@@ -14816,29 +14840,29 @@
       <c r="H159" s="58"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
-      <c r="A160" s="34">
-        <v>46271.0</v>
+      <c r="A160" s="46">
+        <v>46264.0</v>
       </c>
       <c r="B160" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C160" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D160" s="42"/>
-      <c r="E160" s="42"/>
+        <v>92</v>
+      </c>
+      <c r="C160" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D160" s="35"/>
+      <c r="E160" s="35"/>
       <c r="G160" s="57"/>
       <c r="H160" s="58"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="46">
-        <v>46272.0</v>
-      </c>
-      <c r="B161" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C161" s="47">
-        <v>110.0</v>
+      <c r="A161" s="34">
+        <v>46267.0</v>
+      </c>
+      <c r="B161" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C161" s="49">
+        <v>2000.0</v>
       </c>
       <c r="D161" s="42"/>
       <c r="E161" s="42"/>
@@ -14847,13 +14871,13 @@
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c r="A162" s="34">
-        <v>46273.0</v>
-      </c>
-      <c r="B162" s="42" t="s">
-        <v>96</v>
+        <v>46271.0</v>
+      </c>
+      <c r="B162" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C162" s="49">
-        <v>90.0</v>
+        <v>950.0</v>
       </c>
       <c r="D162" s="42"/>
       <c r="E162" s="42"/>
@@ -14861,14 +14885,14 @@
       <c r="H162" s="58"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="34">
-        <v>46275.0</v>
-      </c>
-      <c r="B163" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C163" s="49">
-        <v>65.0</v>
+      <c r="A163" s="46">
+        <v>46272.0</v>
+      </c>
+      <c r="B163" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C163" s="47">
+        <v>110.0</v>
       </c>
       <c r="D163" s="42"/>
       <c r="E163" s="42"/>
@@ -14877,13 +14901,13 @@
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c r="A164" s="34">
-        <v>46276.0</v>
+        <v>46273.0</v>
       </c>
       <c r="B164" s="42" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="C164" s="49">
-        <v>95.12</v>
+        <v>90.0</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42"/>
@@ -14892,13 +14916,13 @@
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="A165" s="34">
-        <v>46277.0</v>
-      </c>
-      <c r="B165" s="43" t="s">
-        <v>63</v>
+        <v>46275.0</v>
+      </c>
+      <c r="B165" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C165" s="49">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D165" s="42"/>
       <c r="E165" s="42"/>
@@ -14907,13 +14931,13 @@
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="34">
-        <v>46277.0</v>
+        <v>46276.0</v>
       </c>
       <c r="B166" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C166" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D166" s="42"/>
       <c r="E166" s="42"/>
@@ -14925,10 +14949,10 @@
         <v>46277.0</v>
       </c>
       <c r="B167" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C167" s="49">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D167" s="42"/>
       <c r="E167" s="42"/>
@@ -14937,13 +14961,13 @@
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c r="A168" s="34">
-        <v>46280.0</v>
-      </c>
-      <c r="B168" s="43" t="s">
-        <v>61</v>
+        <v>46277.0</v>
+      </c>
+      <c r="B168" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C168" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D168" s="42"/>
       <c r="E168" s="42"/>
@@ -14952,13 +14976,13 @@
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c r="A169" s="34">
-        <v>46285.0</v>
-      </c>
-      <c r="B169" s="35" t="s">
-        <v>36</v>
+        <v>46277.0</v>
+      </c>
+      <c r="B169" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C169" s="49">
-        <v>6850.0</v>
+        <v>50.0</v>
       </c>
       <c r="D169" s="42"/>
       <c r="E169" s="42"/>
@@ -14966,14 +14990,14 @@
       <c r="H169" s="58"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="46">
-        <v>46285.0</v>
+      <c r="A170" s="34">
+        <v>46280.0</v>
       </c>
       <c r="B170" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C170" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D170" s="42"/>
       <c r="E170" s="42"/>
@@ -14981,29 +15005,29 @@
       <c r="H170" s="58"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c r="A171" s="46">
-        <v>46295.0</v>
-      </c>
-      <c r="B171" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C171" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D171" s="35"/>
-      <c r="E171" s="35"/>
+      <c r="A171" s="34">
+        <v>46285.0</v>
+      </c>
+      <c r="B171" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C171" s="49">
+        <v>6850.0</v>
+      </c>
+      <c r="D171" s="42"/>
+      <c r="E171" s="42"/>
       <c r="G171" s="57"/>
       <c r="H171" s="58"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="34">
-        <v>46297.0</v>
-      </c>
-      <c r="B172" s="42" t="s">
-        <v>40</v>
+      <c r="A172" s="46">
+        <v>46285.0</v>
+      </c>
+      <c r="B172" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C172" s="49">
-        <v>1800.0</v>
+        <v>113.31</v>
       </c>
       <c r="D172" s="42"/>
       <c r="E172" s="42"/>
@@ -15011,29 +15035,29 @@
       <c r="H172" s="58"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="34">
-        <v>46301.0</v>
+      <c r="A173" s="46">
+        <v>46295.0</v>
       </c>
       <c r="B173" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C173" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D173" s="42"/>
-      <c r="E173" s="42"/>
+        <v>92</v>
+      </c>
+      <c r="C173" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D173" s="35"/>
+      <c r="E173" s="35"/>
       <c r="G173" s="57"/>
       <c r="H173" s="58"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
-      <c r="A174" s="46">
-        <v>46302.0</v>
-      </c>
-      <c r="B174" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C174" s="47">
-        <v>110.0</v>
+      <c r="A174" s="34">
+        <v>46297.0</v>
+      </c>
+      <c r="B174" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C174" s="49">
+        <v>1800.0</v>
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42"/>
@@ -15042,13 +15066,13 @@
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="34">
-        <v>46302.0</v>
-      </c>
-      <c r="B175" s="42" t="s">
-        <v>64</v>
+        <v>46301.0</v>
+      </c>
+      <c r="B175" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C175" s="49">
-        <v>530.0</v>
+        <v>950.0</v>
       </c>
       <c r="D175" s="42"/>
       <c r="E175" s="42"/>
@@ -15056,14 +15080,14 @@
       <c r="H175" s="58"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
-      <c r="A176" s="34">
-        <v>46303.0</v>
-      </c>
-      <c r="B176" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C176" s="49">
-        <v>90.0</v>
+      <c r="A176" s="46">
+        <v>46302.0</v>
+      </c>
+      <c r="B176" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C176" s="47">
+        <v>110.0</v>
       </c>
       <c r="D176" s="42"/>
       <c r="E176" s="42"/>
@@ -15072,13 +15096,13 @@
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="34">
-        <v>46303.0</v>
+        <v>46302.0</v>
       </c>
       <c r="B177" s="42" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="C177" s="49">
-        <v>119.8</v>
+        <v>530.0</v>
       </c>
       <c r="D177" s="42"/>
       <c r="E177" s="42"/>
@@ -15087,13 +15111,13 @@
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" s="34">
-        <v>46305.0</v>
-      </c>
-      <c r="B178" s="35" t="s">
-        <v>75</v>
+        <v>46303.0</v>
+      </c>
+      <c r="B178" s="42" t="s">
+        <v>97</v>
       </c>
       <c r="C178" s="49">
-        <v>65.0</v>
+        <v>90.0</v>
       </c>
       <c r="D178" s="42"/>
       <c r="E178" s="42"/>
@@ -15102,13 +15126,13 @@
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="34">
-        <v>46306.0</v>
+        <v>46303.0</v>
       </c>
       <c r="B179" s="42" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C179" s="49">
-        <v>95.12</v>
+        <v>119.8</v>
       </c>
       <c r="D179" s="42"/>
       <c r="E179" s="42"/>
@@ -15117,13 +15141,13 @@
     </row>
     <row r="180" ht="14.25" customHeight="1">
       <c r="A180" s="34">
-        <v>46307.0</v>
-      </c>
-      <c r="B180" s="43" t="s">
-        <v>63</v>
+        <v>46305.0</v>
+      </c>
+      <c r="B180" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C180" s="49">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D180" s="42"/>
       <c r="E180" s="42"/>
@@ -15132,13 +15156,13 @@
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="34">
-        <v>46307.0</v>
+        <v>46306.0</v>
       </c>
       <c r="B181" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C181" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D181" s="42"/>
       <c r="E181" s="42"/>
@@ -15146,14 +15170,14 @@
       <c r="H181" s="58"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" s="46">
+      <c r="A182" s="34">
         <v>46307.0</v>
       </c>
       <c r="B182" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C182" s="49">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D182" s="42"/>
       <c r="E182" s="42"/>
@@ -15162,13 +15186,13 @@
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="34">
-        <v>46310.0</v>
-      </c>
-      <c r="B183" s="43" t="s">
-        <v>61</v>
+        <v>46307.0</v>
+      </c>
+      <c r="B183" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C183" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D183" s="42"/>
       <c r="E183" s="42"/>
@@ -15176,14 +15200,14 @@
       <c r="H183" s="58"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="34">
-        <v>46315.0</v>
-      </c>
-      <c r="B184" s="35" t="s">
-        <v>36</v>
+      <c r="A184" s="46">
+        <v>46307.0</v>
+      </c>
+      <c r="B184" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C184" s="49">
-        <v>6000.0</v>
+        <v>50.0</v>
       </c>
       <c r="D184" s="42"/>
       <c r="E184" s="42"/>
@@ -15192,13 +15216,13 @@
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="34">
-        <v>46315.0</v>
+        <v>46310.0</v>
       </c>
       <c r="B185" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C185" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D185" s="42"/>
       <c r="E185" s="42"/>
@@ -15206,29 +15230,29 @@
       <c r="H185" s="58"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="46">
-        <v>46325.0</v>
-      </c>
-      <c r="B186" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C186" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D186" s="35"/>
-      <c r="E186" s="35"/>
+      <c r="A186" s="34">
+        <v>46315.0</v>
+      </c>
+      <c r="B186" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C186" s="49">
+        <v>6000.0</v>
+      </c>
+      <c r="D186" s="42"/>
+      <c r="E186" s="42"/>
       <c r="G186" s="57"/>
       <c r="H186" s="58"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="34">
-        <v>46328.0</v>
-      </c>
-      <c r="B187" s="42" t="s">
-        <v>40</v>
+        <v>46315.0</v>
+      </c>
+      <c r="B187" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C187" s="49">
-        <v>2200.0</v>
+        <v>113.31</v>
       </c>
       <c r="D187" s="42"/>
       <c r="E187" s="42"/>
@@ -15236,29 +15260,29 @@
       <c r="H187" s="58"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c r="A188" s="34">
-        <v>46332.0</v>
+      <c r="A188" s="46">
+        <v>46325.0</v>
       </c>
       <c r="B188" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C188" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D188" s="42"/>
-      <c r="E188" s="42"/>
+        <v>92</v>
+      </c>
+      <c r="C188" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D188" s="35"/>
+      <c r="E188" s="35"/>
       <c r="G188" s="57"/>
       <c r="H188" s="58"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="46">
-        <v>46333.0</v>
-      </c>
-      <c r="B189" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C189" s="47">
-        <v>110.0</v>
+      <c r="A189" s="34">
+        <v>46328.0</v>
+      </c>
+      <c r="B189" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C189" s="49">
+        <v>2200.0</v>
       </c>
       <c r="D189" s="42"/>
       <c r="E189" s="42"/>
@@ -15267,13 +15291,13 @@
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="34">
-        <v>46335.0</v>
-      </c>
-      <c r="B190" s="42" t="s">
-        <v>96</v>
+        <v>46332.0</v>
+      </c>
+      <c r="B190" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C190" s="49">
-        <v>90.0</v>
+        <v>950.0</v>
       </c>
       <c r="D190" s="42"/>
       <c r="E190" s="42"/>
@@ -15281,14 +15305,14 @@
       <c r="H190" s="58"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c r="A191" s="34">
-        <v>46336.0</v>
-      </c>
-      <c r="B191" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C191" s="49">
-        <v>65.0</v>
+      <c r="A191" s="46">
+        <v>46333.0</v>
+      </c>
+      <c r="B191" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C191" s="47">
+        <v>110.0</v>
       </c>
       <c r="D191" s="42"/>
       <c r="E191" s="42"/>
@@ -15297,13 +15321,13 @@
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="34">
-        <v>46337.0</v>
+        <v>46335.0</v>
       </c>
       <c r="B192" s="42" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="C192" s="49">
-        <v>95.12</v>
+        <v>90.0</v>
       </c>
       <c r="D192" s="42"/>
       <c r="E192" s="42"/>
@@ -15312,13 +15336,13 @@
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c r="A193" s="34">
-        <v>46338.0</v>
-      </c>
-      <c r="B193" s="43" t="s">
-        <v>63</v>
+        <v>46336.0</v>
+      </c>
+      <c r="B193" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C193" s="49">
-        <v>981.95</v>
+        <v>65.0</v>
       </c>
       <c r="D193" s="42"/>
       <c r="E193" s="42"/>
@@ -15327,13 +15351,13 @@
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c r="A194" s="34">
-        <v>46338.0</v>
+        <v>46337.0</v>
       </c>
       <c r="B194" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C194" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42"/>
@@ -15345,10 +15369,10 @@
         <v>46338.0</v>
       </c>
       <c r="B195" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C195" s="49">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D195" s="42"/>
       <c r="E195" s="42"/>
@@ -15357,13 +15381,13 @@
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="34">
-        <v>46341.0</v>
-      </c>
-      <c r="B196" s="43" t="s">
-        <v>61</v>
+        <v>46338.0</v>
+      </c>
+      <c r="B196" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C196" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D196" s="42"/>
       <c r="E196" s="42"/>
@@ -15372,13 +15396,13 @@
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c r="A197" s="34">
-        <v>46346.0</v>
-      </c>
-      <c r="B197" s="35" t="s">
-        <v>36</v>
+        <v>46338.0</v>
+      </c>
+      <c r="B197" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C197" s="49">
-        <v>5750.0</v>
+        <v>50.0</v>
       </c>
       <c r="D197" s="42"/>
       <c r="E197" s="42"/>
@@ -15387,13 +15411,13 @@
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="34">
-        <v>46346.0</v>
+        <v>46341.0</v>
       </c>
       <c r="B198" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C198" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D198" s="42"/>
       <c r="E198" s="42"/>
@@ -15401,29 +15425,29 @@
       <c r="H198" s="58"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c r="A199" s="46">
-        <v>46356.0</v>
-      </c>
-      <c r="B199" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C199" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D199" s="35"/>
-      <c r="E199" s="35"/>
+      <c r="A199" s="34">
+        <v>46346.0</v>
+      </c>
+      <c r="B199" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C199" s="49">
+        <v>5750.0</v>
+      </c>
+      <c r="D199" s="42"/>
+      <c r="E199" s="42"/>
       <c r="G199" s="57"/>
       <c r="H199" s="58"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
       <c r="A200" s="34">
-        <v>46358.0</v>
-      </c>
-      <c r="B200" s="42" t="s">
-        <v>40</v>
+        <v>46346.0</v>
+      </c>
+      <c r="B200" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C200" s="49">
-        <v>1880.0</v>
+        <v>113.31</v>
       </c>
       <c r="D200" s="42"/>
       <c r="E200" s="42"/>
@@ -15431,29 +15455,29 @@
       <c r="H200" s="58"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="34">
-        <v>46362.0</v>
+      <c r="A201" s="46">
+        <v>46356.0</v>
       </c>
       <c r="B201" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C201" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D201" s="42"/>
-      <c r="E201" s="42"/>
+        <v>92</v>
+      </c>
+      <c r="C201" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D201" s="35"/>
+      <c r="E201" s="35"/>
       <c r="G201" s="57"/>
       <c r="H201" s="58"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="46">
-        <v>46363.0</v>
-      </c>
-      <c r="B202" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C202" s="47">
-        <v>110.0</v>
+      <c r="A202" s="34">
+        <v>46358.0</v>
+      </c>
+      <c r="B202" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C202" s="49">
+        <v>1880.0</v>
       </c>
       <c r="D202" s="42"/>
       <c r="E202" s="42"/>
@@ -15462,13 +15486,13 @@
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="34">
-        <v>46365.0</v>
-      </c>
-      <c r="B203" s="42" t="s">
-        <v>64</v>
+        <v>46362.0</v>
+      </c>
+      <c r="B203" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C203" s="49">
-        <v>530.0</v>
+        <v>950.0</v>
       </c>
       <c r="D203" s="42"/>
       <c r="E203" s="42"/>
@@ -15476,14 +15500,14 @@
       <c r="H203" s="58"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="34">
-        <v>46366.0</v>
-      </c>
-      <c r="B204" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C204" s="49">
-        <v>65.0</v>
+      <c r="A204" s="46">
+        <v>46363.0</v>
+      </c>
+      <c r="B204" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C204" s="47">
+        <v>110.0</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42"/>
@@ -15492,13 +15516,13 @@
     </row>
     <row r="205" ht="14.25" customHeight="1">
       <c r="A205" s="34">
-        <v>46367.0</v>
+        <v>46365.0</v>
       </c>
       <c r="B205" s="42" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C205" s="49">
-        <v>95.12</v>
+        <v>530.0</v>
       </c>
       <c r="D205" s="42"/>
       <c r="E205" s="42"/>
@@ -15507,13 +15531,13 @@
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c r="A206" s="34">
-        <v>46367.0</v>
-      </c>
-      <c r="B206" s="42" t="s">
-        <v>98</v>
+        <v>46366.0</v>
+      </c>
+      <c r="B206" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C206" s="49">
-        <v>2900.0</v>
+        <v>65.0</v>
       </c>
       <c r="D206" s="42"/>
       <c r="E206" s="42"/>
@@ -15522,13 +15546,13 @@
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="34">
-        <v>46368.0</v>
-      </c>
-      <c r="B207" s="43" t="s">
-        <v>63</v>
+        <v>46367.0</v>
+      </c>
+      <c r="B207" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C207" s="49">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D207" s="42"/>
       <c r="E207" s="42"/>
@@ -15537,13 +15561,13 @@
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c r="A208" s="34">
-        <v>46368.0</v>
+        <v>46367.0</v>
       </c>
       <c r="B208" s="42" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="C208" s="49">
-        <v>2831.4</v>
+        <v>2900.0</v>
       </c>
       <c r="D208" s="42"/>
       <c r="E208" s="42"/>
@@ -15551,14 +15575,14 @@
       <c r="H208" s="58"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="A209" s="46">
+      <c r="A209" s="34">
         <v>46368.0</v>
       </c>
       <c r="B209" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C209" s="49">
-        <v>50.0</v>
+        <v>981.95</v>
       </c>
       <c r="D209" s="42"/>
       <c r="E209" s="42"/>
@@ -15567,13 +15591,13 @@
     </row>
     <row r="210" ht="14.25" customHeight="1">
       <c r="A210" s="34">
-        <v>46371.0</v>
-      </c>
-      <c r="B210" s="43" t="s">
-        <v>61</v>
+        <v>46368.0</v>
+      </c>
+      <c r="B210" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C210" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D210" s="42"/>
       <c r="E210" s="42"/>
@@ -15581,14 +15605,14 @@
       <c r="H210" s="58"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="34">
-        <v>46376.0</v>
-      </c>
-      <c r="B211" s="35" t="s">
-        <v>36</v>
+      <c r="A211" s="46">
+        <v>46368.0</v>
+      </c>
+      <c r="B211" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C211" s="49">
-        <v>6250.0</v>
+        <v>50.0</v>
       </c>
       <c r="D211" s="42"/>
       <c r="E211" s="42"/>
@@ -15596,14 +15620,14 @@
       <c r="H211" s="58"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
-      <c r="A212" s="46">
-        <v>46376.0</v>
+      <c r="A212" s="34">
+        <v>46371.0</v>
       </c>
       <c r="B212" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C212" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D212" s="42"/>
       <c r="E212" s="42"/>
@@ -15612,13 +15636,13 @@
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c r="A213" s="34">
-        <v>46389.0</v>
-      </c>
-      <c r="B213" s="42" t="s">
-        <v>40</v>
+        <v>46376.0</v>
+      </c>
+      <c r="B213" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C213" s="49">
-        <v>2000.0</v>
+        <v>6250.0</v>
       </c>
       <c r="D213" s="42"/>
       <c r="E213" s="42"/>
@@ -15626,14 +15650,14 @@
       <c r="H213" s="58"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="34">
-        <v>46393.0</v>
+      <c r="A214" s="46">
+        <v>46376.0</v>
       </c>
       <c r="B214" s="43" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C214" s="49">
-        <v>950.0</v>
+        <v>113.31</v>
       </c>
       <c r="D214" s="42"/>
       <c r="E214" s="42"/>
@@ -15641,14 +15665,14 @@
       <c r="H214" s="58"/>
     </row>
     <row r="215" ht="14.25" customHeight="1">
-      <c r="A215" s="46">
-        <v>46394.0</v>
-      </c>
-      <c r="B215" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C215" s="47">
-        <v>110.0</v>
+      <c r="A215" s="34">
+        <v>46389.0</v>
+      </c>
+      <c r="B215" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C215" s="49">
+        <v>2000.0</v>
       </c>
       <c r="D215" s="42"/>
       <c r="E215" s="42"/>
@@ -15657,13 +15681,13 @@
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c r="A216" s="34">
-        <v>46397.0</v>
-      </c>
-      <c r="B216" s="35" t="s">
-        <v>75</v>
+        <v>46393.0</v>
+      </c>
+      <c r="B216" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C216" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D216" s="42"/>
       <c r="E216" s="42"/>
@@ -15671,14 +15695,14 @@
       <c r="H216" s="58"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
-      <c r="A217" s="34">
-        <v>46398.0</v>
-      </c>
-      <c r="B217" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C217" s="49">
-        <v>105.37</v>
+      <c r="A217" s="46">
+        <v>46394.0</v>
+      </c>
+      <c r="B217" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C217" s="47">
+        <v>110.0</v>
       </c>
       <c r="D217" s="42"/>
       <c r="E217" s="42"/>
@@ -15687,13 +15711,13 @@
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="34">
-        <v>46399.0</v>
-      </c>
-      <c r="B218" s="43" t="s">
-        <v>63</v>
+        <v>46397.0</v>
+      </c>
+      <c r="B218" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C218" s="49">
-        <v>983.13</v>
+        <v>65.0</v>
       </c>
       <c r="D218" s="42"/>
       <c r="E218" s="42"/>
@@ -15702,13 +15726,13 @@
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c r="A219" s="34">
-        <v>46399.0</v>
-      </c>
-      <c r="B219" s="43" t="s">
-        <v>56</v>
+        <v>46398.0</v>
+      </c>
+      <c r="B219" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C219" s="49">
-        <v>50.0</v>
+        <v>105.37</v>
       </c>
       <c r="D219" s="42"/>
       <c r="E219" s="42"/>
@@ -15717,13 +15741,13 @@
     </row>
     <row r="220" ht="14.25" customHeight="1">
       <c r="A220" s="34">
-        <v>46402.0</v>
+        <v>46399.0</v>
       </c>
       <c r="B220" s="43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C220" s="49">
-        <v>132.4</v>
+        <v>983.13</v>
       </c>
       <c r="D220" s="42"/>
       <c r="E220" s="42"/>
@@ -15732,13 +15756,13 @@
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c r="A221" s="34">
-        <v>46407.0</v>
-      </c>
-      <c r="B221" s="35" t="s">
-        <v>36</v>
+        <v>46399.0</v>
+      </c>
+      <c r="B221" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C221" s="49">
-        <v>7796.0</v>
+        <v>50.0</v>
       </c>
       <c r="D221" s="42"/>
       <c r="E221" s="42"/>
@@ -15747,13 +15771,13 @@
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c r="A222" s="34">
-        <v>46407.0</v>
+        <v>46402.0</v>
       </c>
       <c r="B222" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C222" s="49">
-        <v>102.36</v>
+        <v>132.4</v>
       </c>
       <c r="D222" s="42"/>
       <c r="E222" s="42"/>
@@ -15762,13 +15786,13 @@
     </row>
     <row r="223" ht="14.25" customHeight="1">
       <c r="A223" s="34">
-        <v>46420.0</v>
-      </c>
-      <c r="B223" s="42" t="s">
-        <v>40</v>
+        <v>46407.0</v>
+      </c>
+      <c r="B223" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C223" s="49">
-        <v>1800.0</v>
+        <v>7796.0</v>
       </c>
       <c r="D223" s="42"/>
       <c r="E223" s="42"/>
@@ -15777,13 +15801,13 @@
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c r="A224" s="34">
-        <v>46424.0</v>
+        <v>46407.0</v>
       </c>
       <c r="B224" s="43" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C224" s="49">
-        <v>950.0</v>
+        <v>102.36</v>
       </c>
       <c r="D224" s="42"/>
       <c r="E224" s="42"/>
@@ -15791,14 +15815,14 @@
       <c r="H224" s="58"/>
     </row>
     <row r="225" ht="14.25" customHeight="1">
-      <c r="A225" s="46">
-        <v>46425.0</v>
-      </c>
-      <c r="B225" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C225" s="47">
-        <v>110.0</v>
+      <c r="A225" s="34">
+        <v>46420.0</v>
+      </c>
+      <c r="B225" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C225" s="49">
+        <v>1800.0</v>
       </c>
       <c r="D225" s="42"/>
       <c r="E225" s="42"/>
@@ -15807,13 +15831,13 @@
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c r="A226" s="34">
-        <v>46428.0</v>
-      </c>
-      <c r="B226" s="35" t="s">
-        <v>75</v>
+        <v>46424.0</v>
+      </c>
+      <c r="B226" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C226" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D226" s="42"/>
       <c r="E226" s="42"/>
@@ -15821,14 +15845,14 @@
       <c r="H226" s="58"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
-      <c r="A227" s="34">
-        <v>46428.0</v>
-      </c>
-      <c r="B227" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C227" s="49">
-        <v>530.0</v>
+      <c r="A227" s="46">
+        <v>46425.0</v>
+      </c>
+      <c r="B227" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C227" s="47">
+        <v>110.0</v>
       </c>
       <c r="D227" s="42"/>
       <c r="E227" s="42"/>
@@ -15837,13 +15861,13 @@
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c r="A228" s="34">
-        <v>46429.0</v>
-      </c>
-      <c r="B228" s="42" t="s">
-        <v>42</v>
+        <v>46428.0</v>
+      </c>
+      <c r="B228" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C228" s="49">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D228" s="42"/>
       <c r="E228" s="42"/>
@@ -15852,13 +15876,13 @@
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c r="A229" s="34">
-        <v>46430.0</v>
-      </c>
-      <c r="B229" s="43" t="s">
-        <v>63</v>
+        <v>46428.0</v>
+      </c>
+      <c r="B229" s="42" t="s">
+        <v>65</v>
       </c>
       <c r="C229" s="49">
-        <v>981.95</v>
+        <v>530.0</v>
       </c>
       <c r="D229" s="42"/>
       <c r="E229" s="42"/>
@@ -15867,13 +15891,13 @@
     </row>
     <row r="230" ht="14.25" customHeight="1">
       <c r="A230" s="34">
-        <v>46430.0</v>
+        <v>46429.0</v>
       </c>
       <c r="B230" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C230" s="49">
-        <v>2831.4</v>
+        <v>95.12</v>
       </c>
       <c r="D230" s="42"/>
       <c r="E230" s="42"/>
@@ -15884,11 +15908,11 @@
       <c r="A231" s="34">
         <v>46430.0</v>
       </c>
-      <c r="B231" s="42" t="s">
-        <v>67</v>
+      <c r="B231" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="C231" s="49">
-        <v>1407.65</v>
+        <v>981.95</v>
       </c>
       <c r="D231" s="42"/>
       <c r="E231" s="42"/>
@@ -15896,29 +15920,29 @@
       <c r="H231" s="58"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c r="A232" s="46">
+      <c r="A232" s="34">
         <v>46430.0</v>
       </c>
-      <c r="B232" s="43" t="s">
-        <v>56</v>
+      <c r="B232" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C232" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D232" s="42"/>
-      <c r="E232" s="35"/>
+      <c r="E232" s="42"/>
       <c r="G232" s="57"/>
       <c r="H232" s="58"/>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c r="A233" s="34">
-        <v>46433.0</v>
-      </c>
-      <c r="B233" s="43" t="s">
-        <v>61</v>
+        <v>46430.0</v>
+      </c>
+      <c r="B233" s="42" t="s">
+        <v>68</v>
       </c>
       <c r="C233" s="49">
-        <v>132.4</v>
+        <v>1407.65</v>
       </c>
       <c r="D233" s="42"/>
       <c r="E233" s="42"/>
@@ -15926,29 +15950,29 @@
       <c r="H233" s="58"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="34">
-        <v>46437.0</v>
-      </c>
-      <c r="B234" s="42" t="s">
-        <v>68</v>
+      <c r="A234" s="46">
+        <v>46430.0</v>
+      </c>
+      <c r="B234" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C234" s="49">
-        <v>460.0</v>
+        <v>50.0</v>
       </c>
       <c r="D234" s="42"/>
-      <c r="E234" s="42"/>
+      <c r="E234" s="35"/>
       <c r="G234" s="57"/>
       <c r="H234" s="58"/>
     </row>
     <row r="235" ht="14.25" customHeight="1">
       <c r="A235" s="34">
-        <v>46438.0</v>
-      </c>
-      <c r="B235" s="35" t="s">
-        <v>36</v>
+        <v>46433.0</v>
+      </c>
+      <c r="B235" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C235" s="49">
-        <v>6004.07</v>
+        <v>132.4</v>
       </c>
       <c r="D235" s="42"/>
       <c r="E235" s="42"/>
@@ -15956,14 +15980,14 @@
       <c r="H235" s="58"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="46">
-        <v>46438.0</v>
-      </c>
-      <c r="B236" s="43" t="s">
-        <v>54</v>
+      <c r="A236" s="34">
+        <v>46437.0</v>
+      </c>
+      <c r="B236" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="C236" s="49">
-        <v>113.31</v>
+        <v>460.0</v>
       </c>
       <c r="D236" s="42"/>
       <c r="E236" s="42"/>
@@ -15972,13 +15996,13 @@
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c r="A237" s="34">
-        <v>46448.0</v>
-      </c>
-      <c r="B237" s="42" t="s">
-        <v>40</v>
+        <v>46438.0</v>
+      </c>
+      <c r="B237" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C237" s="49">
-        <v>1771.95</v>
+        <v>6004.07</v>
       </c>
       <c r="D237" s="42"/>
       <c r="E237" s="42"/>
@@ -15986,14 +16010,14 @@
       <c r="H237" s="58"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="34">
-        <v>46451.0</v>
-      </c>
-      <c r="B238" s="42" t="s">
-        <v>74</v>
+      <c r="A238" s="46">
+        <v>46438.0</v>
+      </c>
+      <c r="B238" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C238" s="49">
-        <v>81.8</v>
+        <v>113.31</v>
       </c>
       <c r="D238" s="42"/>
       <c r="E238" s="42"/>
@@ -16002,13 +16026,13 @@
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c r="A239" s="34">
-        <v>46452.0</v>
-      </c>
-      <c r="B239" s="43" t="s">
-        <v>60</v>
+        <v>46448.0</v>
+      </c>
+      <c r="B239" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C239" s="49">
-        <v>950.0</v>
+        <v>1771.95</v>
       </c>
       <c r="D239" s="42"/>
       <c r="E239" s="42"/>
@@ -16016,14 +16040,14 @@
       <c r="H239" s="58"/>
     </row>
     <row r="240" ht="14.25" customHeight="1">
-      <c r="A240" s="46">
-        <v>46453.0</v>
-      </c>
-      <c r="B240" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C240" s="47">
-        <v>110.0</v>
+      <c r="A240" s="34">
+        <v>46451.0</v>
+      </c>
+      <c r="B240" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C240" s="49">
+        <v>81.8</v>
       </c>
       <c r="D240" s="42"/>
       <c r="E240" s="42"/>
@@ -16032,13 +16056,13 @@
     </row>
     <row r="241" ht="14.25" customHeight="1">
       <c r="A241" s="34">
-        <v>46456.0</v>
-      </c>
-      <c r="B241" s="35" t="s">
-        <v>50</v>
+        <v>46452.0</v>
+      </c>
+      <c r="B241" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C241" s="49">
-        <v>1336.73</v>
+        <v>950.0</v>
       </c>
       <c r="D241" s="42"/>
       <c r="E241" s="42"/>
@@ -16046,14 +16070,14 @@
       <c r="H241" s="58"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
-      <c r="A242" s="34">
-        <v>46456.0</v>
-      </c>
-      <c r="B242" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C242" s="49">
-        <v>65.0</v>
+      <c r="A242" s="46">
+        <v>46453.0</v>
+      </c>
+      <c r="B242" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C242" s="47">
+        <v>110.0</v>
       </c>
       <c r="D242" s="42"/>
       <c r="E242" s="42"/>
@@ -16062,13 +16086,13 @@
     </row>
     <row r="243" ht="14.25" customHeight="1">
       <c r="A243" s="34">
-        <v>46457.0</v>
-      </c>
-      <c r="B243" s="42" t="s">
-        <v>42</v>
+        <v>46456.0</v>
+      </c>
+      <c r="B243" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="C243" s="49">
-        <v>86.15</v>
+        <v>1336.73</v>
       </c>
       <c r="D243" s="42"/>
       <c r="E243" s="42"/>
@@ -16077,13 +16101,13 @@
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c r="A244" s="34">
-        <v>46458.0</v>
-      </c>
-      <c r="B244" s="43" t="s">
-        <v>63</v>
+        <v>46456.0</v>
+      </c>
+      <c r="B244" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C244" s="49">
-        <v>981.22</v>
+        <v>65.0</v>
       </c>
       <c r="D244" s="42"/>
       <c r="E244" s="42"/>
@@ -16092,13 +16116,13 @@
     </row>
     <row r="245" ht="14.25" customHeight="1">
       <c r="A245" s="34">
-        <v>46458.0</v>
+        <v>46457.0</v>
       </c>
       <c r="B245" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C245" s="49">
-        <v>2831.4</v>
+        <v>86.15</v>
       </c>
       <c r="D245" s="42"/>
       <c r="E245" s="42"/>
@@ -16110,10 +16134,10 @@
         <v>46458.0</v>
       </c>
       <c r="B246" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C246" s="49">
-        <v>50.0</v>
+        <v>981.22</v>
       </c>
       <c r="D246" s="42"/>
       <c r="E246" s="42"/>
@@ -16122,13 +16146,13 @@
     </row>
     <row r="247" ht="14.25" customHeight="1">
       <c r="A247" s="34">
-        <v>46461.0</v>
-      </c>
-      <c r="B247" s="43" t="s">
-        <v>61</v>
+        <v>46458.0</v>
+      </c>
+      <c r="B247" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C247" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D247" s="42"/>
       <c r="E247" s="42"/>
@@ -16137,13 +16161,13 @@
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c r="A248" s="34">
-        <v>46466.0</v>
-      </c>
-      <c r="B248" s="35" t="s">
-        <v>36</v>
+        <v>46458.0</v>
+      </c>
+      <c r="B248" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C248" s="49">
-        <v>7494.55</v>
+        <v>50.0</v>
       </c>
       <c r="D248" s="42"/>
       <c r="E248" s="42"/>
@@ -16152,13 +16176,13 @@
     </row>
     <row r="249" ht="14.25" customHeight="1">
       <c r="A249" s="34">
-        <v>46466.0</v>
+        <v>46461.0</v>
       </c>
       <c r="B249" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C249" s="49">
-        <v>87.84</v>
+        <v>132.4</v>
       </c>
       <c r="D249" s="42"/>
       <c r="E249" s="42"/>
@@ -16167,13 +16191,13 @@
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="34">
-        <v>46477.0</v>
-      </c>
-      <c r="B250" s="42" t="s">
-        <v>78</v>
+        <v>46466.0</v>
+      </c>
+      <c r="B250" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C250" s="49">
-        <v>35.62</v>
+        <v>7494.55</v>
       </c>
       <c r="D250" s="42"/>
       <c r="E250" s="42"/>
@@ -16182,13 +16206,13 @@
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c r="A251" s="34">
-        <v>46479.0</v>
-      </c>
-      <c r="B251" s="42" t="s">
-        <v>40</v>
+        <v>46466.0</v>
+      </c>
+      <c r="B251" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C251" s="49">
-        <v>5310.25</v>
+        <v>87.84</v>
       </c>
       <c r="D251" s="42"/>
       <c r="E251" s="42"/>
@@ -16197,13 +16221,13 @@
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="34">
-        <v>46483.0</v>
-      </c>
-      <c r="B252" s="43" t="s">
-        <v>60</v>
+        <v>46477.0</v>
+      </c>
+      <c r="B252" s="42" t="s">
+        <v>79</v>
       </c>
       <c r="C252" s="49">
-        <v>950.0</v>
+        <v>35.62</v>
       </c>
       <c r="D252" s="42"/>
       <c r="E252" s="42"/>
@@ -16211,14 +16235,14 @@
       <c r="H252" s="58"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="46">
-        <v>46484.0</v>
-      </c>
-      <c r="B253" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C253" s="47">
-        <v>110.0</v>
+      <c r="A253" s="34">
+        <v>46479.0</v>
+      </c>
+      <c r="B253" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C253" s="49">
+        <v>5310.25</v>
       </c>
       <c r="D253" s="42"/>
       <c r="E253" s="42"/>
@@ -16227,13 +16251,13 @@
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c r="A254" s="34">
-        <v>46487.0</v>
-      </c>
-      <c r="B254" s="35" t="s">
-        <v>75</v>
+        <v>46483.0</v>
+      </c>
+      <c r="B254" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C254" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D254" s="42"/>
       <c r="E254" s="42"/>
@@ -16241,14 +16265,14 @@
       <c r="H254" s="58"/>
     </row>
     <row r="255" ht="14.25" customHeight="1">
-      <c r="A255" s="34">
-        <v>46488.0</v>
-      </c>
-      <c r="B255" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C255" s="49">
-        <v>98.98</v>
+      <c r="A255" s="46">
+        <v>46484.0</v>
+      </c>
+      <c r="B255" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C255" s="47">
+        <v>110.0</v>
       </c>
       <c r="D255" s="42"/>
       <c r="E255" s="42"/>
@@ -16257,13 +16281,13 @@
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c r="A256" s="34">
-        <v>46489.0</v>
-      </c>
-      <c r="B256" s="43" t="s">
-        <v>63</v>
+        <v>46487.0</v>
+      </c>
+      <c r="B256" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="C256" s="49">
-        <v>981.22</v>
+        <v>65.0</v>
       </c>
       <c r="D256" s="42"/>
       <c r="E256" s="42"/>
@@ -16272,13 +16296,13 @@
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c r="A257" s="34">
-        <v>46489.0</v>
+        <v>46488.0</v>
       </c>
       <c r="B257" s="42" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C257" s="49">
-        <v>2831.4</v>
+        <v>98.98</v>
       </c>
       <c r="D257" s="42"/>
       <c r="E257" s="42"/>
@@ -16286,14 +16310,14 @@
       <c r="H257" s="58"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="46">
+      <c r="A258" s="34">
         <v>46489.0</v>
       </c>
       <c r="B258" s="43" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C258" s="49">
-        <v>50.0</v>
+        <v>981.22</v>
       </c>
       <c r="D258" s="42"/>
       <c r="E258" s="42"/>
@@ -16302,13 +16326,13 @@
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c r="A259" s="34">
-        <v>46492.0</v>
-      </c>
-      <c r="B259" s="43" t="s">
-        <v>61</v>
+        <v>46489.0</v>
+      </c>
+      <c r="B259" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C259" s="49">
-        <v>132.4</v>
+        <v>2831.4</v>
       </c>
       <c r="D259" s="42"/>
       <c r="E259" s="42"/>
@@ -16316,14 +16340,14 @@
       <c r="H259" s="58"/>
     </row>
     <row r="260" ht="14.25" customHeight="1">
-      <c r="A260" s="34">
-        <v>46497.0</v>
-      </c>
-      <c r="B260" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C260" s="47">
-        <v>6350.0</v>
+      <c r="A260" s="46">
+        <v>46489.0</v>
+      </c>
+      <c r="B260" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C260" s="49">
+        <v>50.0</v>
       </c>
       <c r="D260" s="42"/>
       <c r="E260" s="42"/>
@@ -16331,14 +16355,14 @@
       <c r="H260" s="58"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="46">
-        <v>46497.0</v>
+      <c r="A261" s="34">
+        <v>46492.0</v>
       </c>
       <c r="B261" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C261" s="47">
-        <v>113.8</v>
+        <v>62</v>
+      </c>
+      <c r="C261" s="49">
+        <v>132.4</v>
       </c>
       <c r="D261" s="42"/>
       <c r="E261" s="42"/>
@@ -16346,14 +16370,14 @@
       <c r="H261" s="58"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="46">
-        <v>46507.0</v>
-      </c>
-      <c r="B262" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C262" s="49">
-        <v>530.0</v>
+      <c r="A262" s="34">
+        <v>46497.0</v>
+      </c>
+      <c r="B262" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C262" s="47">
+        <v>6350.0</v>
       </c>
       <c r="D262" s="42"/>
       <c r="E262" s="42"/>
@@ -16361,14 +16385,14 @@
       <c r="H262" s="58"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c r="A263" s="34">
-        <v>46509.0</v>
-      </c>
-      <c r="B263" s="42" t="s">
-        <v>40</v>
+      <c r="A263" s="46">
+        <v>46497.0</v>
+      </c>
+      <c r="B263" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C263" s="47">
-        <v>3452.5</v>
+        <v>113.8</v>
       </c>
       <c r="D263" s="42"/>
       <c r="E263" s="42"/>
@@ -16376,14 +16400,14 @@
       <c r="H263" s="58"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="34">
-        <v>46513.0</v>
-      </c>
-      <c r="B264" s="43" t="s">
-        <v>60</v>
+      <c r="A264" s="46">
+        <v>46507.0</v>
+      </c>
+      <c r="B264" s="42" t="s">
+        <v>65</v>
       </c>
       <c r="C264" s="49">
-        <v>950.0</v>
+        <v>530.0</v>
       </c>
       <c r="D264" s="42"/>
       <c r="E264" s="42"/>
@@ -16391,14 +16415,14 @@
       <c r="H264" s="58"/>
     </row>
     <row r="265" ht="14.25" customHeight="1">
-      <c r="A265" s="46">
-        <v>46514.0</v>
-      </c>
-      <c r="B265" s="43" t="s">
-        <v>44</v>
+      <c r="A265" s="34">
+        <v>46509.0</v>
+      </c>
+      <c r="B265" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C265" s="47">
-        <v>110.0</v>
+        <v>3452.5</v>
       </c>
       <c r="D265" s="42"/>
       <c r="E265" s="42"/>
@@ -16407,13 +16431,13 @@
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c r="A266" s="34">
-        <v>46517.0</v>
-      </c>
-      <c r="B266" s="35" t="s">
-        <v>75</v>
+        <v>46513.0</v>
+      </c>
+      <c r="B266" s="43" t="s">
+        <v>60</v>
       </c>
       <c r="C266" s="49">
-        <v>65.0</v>
+        <v>950.0</v>
       </c>
       <c r="D266" s="42"/>
       <c r="E266" s="42"/>
@@ -16421,14 +16445,14 @@
       <c r="H266" s="58"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="34">
-        <v>46518.0</v>
-      </c>
-      <c r="B267" s="42" t="s">
-        <v>42</v>
+      <c r="A267" s="46">
+        <v>46514.0</v>
+      </c>
+      <c r="B267" s="43" t="s">
+        <v>44</v>
       </c>
       <c r="C267" s="47">
-        <v>98.88</v>
+        <v>110.0</v>
       </c>
       <c r="D267" s="42"/>
       <c r="E267" s="42"/>
@@ -16437,13 +16461,13 @@
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c r="A268" s="34">
-        <v>46519.0</v>
-      </c>
-      <c r="B268" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C268" s="47">
-        <v>980.86</v>
+        <v>46517.0</v>
+      </c>
+      <c r="B268" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C268" s="49">
+        <v>65.0</v>
       </c>
       <c r="D268" s="42"/>
       <c r="E268" s="42"/>
@@ -16452,13 +16476,13 @@
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c r="A269" s="34">
-        <v>46522.0</v>
-      </c>
-      <c r="B269" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C269" s="49">
-        <v>132.4</v>
+        <v>46518.0</v>
+      </c>
+      <c r="B269" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C269" s="47">
+        <v>98.88</v>
       </c>
       <c r="D269" s="42"/>
       <c r="E269" s="42"/>
@@ -16467,13 +16491,13 @@
     </row>
     <row r="270" ht="14.25" customHeight="1">
       <c r="A270" s="34">
-        <v>46527.0</v>
-      </c>
-      <c r="B270" s="35" t="s">
-        <v>36</v>
+        <v>46519.0</v>
+      </c>
+      <c r="B270" s="43" t="s">
+        <v>63</v>
       </c>
       <c r="C270" s="47">
-        <v>5372.0</v>
+        <v>980.86</v>
       </c>
       <c r="D270" s="42"/>
       <c r="E270" s="42"/>
@@ -16481,14 +16505,14 @@
       <c r="H270" s="58"/>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="46">
-        <v>46527.0</v>
+      <c r="A271" s="34">
+        <v>46522.0</v>
       </c>
       <c r="B271" s="43" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C271" s="49">
-        <v>113.31</v>
+        <v>132.4</v>
       </c>
       <c r="D271" s="42"/>
       <c r="E271" s="42"/>
@@ -16496,16 +16520,32 @@
       <c r="H271" s="58"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c r="A272" s="60"/>
-      <c r="B272" s="61"/>
-      <c r="C272" s="62"/>
+      <c r="A272" s="34">
+        <v>46527.0</v>
+      </c>
+      <c r="B272" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C272" s="47">
+        <v>5372.0</v>
+      </c>
+      <c r="D272" s="42"/>
+      <c r="E272" s="42"/>
       <c r="G272" s="57"/>
       <c r="H272" s="58"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="60"/>
-      <c r="B273" s="61"/>
-      <c r="C273" s="62"/>
+      <c r="A273" s="46">
+        <v>46527.0</v>
+      </c>
+      <c r="B273" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C273" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D273" s="42"/>
+      <c r="E273" s="42"/>
       <c r="G273" s="57"/>
       <c r="H273" s="58"/>
     </row>
@@ -16874,16 +16914,16 @@
       <c r="H325" s="58"/>
     </row>
     <row r="326" ht="14.25" customHeight="1">
-      <c r="A326" s="63"/>
-      <c r="B326" s="64"/>
-      <c r="C326" s="65"/>
+      <c r="A326" s="60"/>
+      <c r="B326" s="61"/>
+      <c r="C326" s="62"/>
       <c r="G326" s="57"/>
       <c r="H326" s="58"/>
     </row>
     <row r="327" ht="14.25" customHeight="1">
-      <c r="A327" s="63"/>
-      <c r="B327" s="64"/>
-      <c r="C327" s="65"/>
+      <c r="A327" s="60"/>
+      <c r="B327" s="61"/>
+      <c r="C327" s="62"/>
       <c r="G327" s="57"/>
       <c r="H327" s="58"/>
     </row>
@@ -17406,18 +17446,24 @@
       <c r="H401" s="58"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c r="A402" s="60"/>
-      <c r="C402" s="32"/>
+      <c r="A402" s="63"/>
+      <c r="B402" s="64"/>
+      <c r="C402" s="65"/>
       <c r="G402" s="57"/>
       <c r="H402" s="58"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c r="A403" s="60"/>
-      <c r="C403" s="32"/>
+      <c r="A403" s="63"/>
+      <c r="B403" s="64"/>
+      <c r="C403" s="65"/>
+      <c r="G403" s="57"/>
+      <c r="H403" s="58"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
       <c r="A404" s="60"/>
       <c r="C404" s="32"/>
+      <c r="G404" s="57"/>
+      <c r="H404" s="58"/>
     </row>
     <row r="405" ht="14.25" customHeight="1">
       <c r="A405" s="60"/>
@@ -17504,14 +17550,14 @@
       <c r="C425" s="32"/>
     </row>
     <row r="426" ht="14.25" customHeight="1">
-      <c r="A426" s="31"/>
+      <c r="A426" s="60"/>
       <c r="C426" s="32"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="31"/>
+    <row r="427" ht="14.25" customHeight="1">
+      <c r="A427" s="60"/>
       <c r="C427" s="32"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" ht="14.25" customHeight="1">
       <c r="A428" s="31"/>
       <c r="C428" s="32"/>
     </row>
@@ -19861,15 +19907,23 @@
     </row>
     <row r="1015" ht="15.75" customHeight="1">
       <c r="A1015" s="31"/>
+      <c r="C1015" s="32"/>
+    </row>
+    <row r="1016" ht="15.75" customHeight="1">
+      <c r="A1016" s="31"/>
+      <c r="C1016" s="32"/>
+    </row>
+    <row r="1017" ht="15.75" customHeight="1">
+      <c r="A1017" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$271">
-    <sortState ref="A1:E271">
-      <sortCondition ref="A1:A271"/>
-      <sortCondition ref="E1:E271"/>
-      <sortCondition ref="B1:B271"/>
-      <sortCondition ref="C1:C271"/>
-      <sortCondition ref="D1:D271"/>
+  <autoFilter ref="$A$1:$E$273">
+    <sortState ref="A1:E273">
+      <sortCondition ref="A1:A273"/>
+      <sortCondition ref="E1:E273"/>
+      <sortCondition ref="B1:B273"/>
+      <sortCondition ref="C1:C273"/>
+      <sortCondition ref="D1:D273"/>
     </sortState>
   </autoFilter>
   <printOptions/>
@@ -19896,30 +19950,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="30">
         <v>46146.0</v>
@@ -19931,15 +19985,15 @@
         <v>3122.53</v>
       </c>
       <c r="F2" s="67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" s="30">
         <v>46146.0</v>
@@ -19951,15 +20005,15 @@
         <v>3119.0</v>
       </c>
       <c r="F3" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="66" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C4" s="30">
         <v>46148.0</v>
@@ -19971,12 +20025,12 @@
         <v>3000.0</v>
       </c>
       <c r="F4" s="67" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="66" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" s="59" t="s">
         <v>41</v>
@@ -19991,7 +20045,7 @@
         <v>192.41</v>
       </c>
       <c r="F5" s="67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
@@ -23997,24 +24051,24 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="25">
         <v>46057.0</v>
@@ -24026,12 +24080,12 @@
         <v>4000.0</v>
       </c>
       <c r="E2" s="70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="66" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B3" s="25">
         <v>46057.0</v>
@@ -24043,7 +24097,7 @@
         <v>6630.64</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -24060,12 +24114,12 @@
         <v>10342.0</v>
       </c>
       <c r="E4" s="70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="66" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" s="27">
         <v>46058.0</v>
@@ -24077,12 +24131,12 @@
         <v>4124.75</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="66" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" s="27">
         <v>46058.0</v>
@@ -24094,7 +24148,7 @@
         <v>5400.0</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -24111,12 +24165,12 @@
         <v>2063.11</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" s="71">
         <v>46084.0</v>
@@ -24128,12 +24182,12 @@
         <v>3000.0</v>
       </c>
       <c r="E8" s="73" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" s="71">
         <v>46085.0</v>
@@ -24145,12 +24199,12 @@
         <v>3000.0</v>
       </c>
       <c r="E9" s="73" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="66" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" s="71">
         <v>46087.0</v>
@@ -24162,12 +24216,12 @@
         <v>8587.0</v>
       </c>
       <c r="E10" s="74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="66" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="71">
         <v>46118.0</v>
@@ -24179,12 +24233,12 @@
         <v>5680.0</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="59" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B12" s="30">
         <v>46146.0</v>
@@ -24196,12 +24250,12 @@
         <v>7536.72</v>
       </c>
       <c r="E12" s="67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="59" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="B13" s="30">
         <v>46150.0</v>
@@ -24213,7 +24267,7 @@
         <v>2800.0</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -24230,7 +24284,7 @@
         <v>3000.0</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -24247,7 +24301,7 @@
         <v>3429.0</v>
       </c>
       <c r="E15" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
@@ -31147,7 +31201,7 @@
     </row>
     <row r="18">
       <c r="A18" s="82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="83">
         <v>120.0</v>
@@ -35498,7 +35552,7 @@
     </row>
     <row r="49">
       <c r="A49" s="82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B49" s="83">
         <v>150.0</v>
@@ -36745,7 +36799,7 @@
     </row>
     <row r="58">
       <c r="A58" s="82" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B58" s="83">
         <v>105.0</v>
@@ -36886,7 +36940,7 @@
     </row>
     <row r="59">
       <c r="A59" s="82" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B59" s="83">
         <v>103.0</v>
@@ -37154,7 +37208,7 @@
     </row>
     <row r="61">
       <c r="A61" s="82" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B61" s="83">
         <v>230.0</v>
@@ -40687,7 +40741,7 @@
     </row>
     <row r="86">
       <c r="A86" s="82" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B86" s="83">
         <v>220.0</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="427096795"/>
-        <c:axId val="1732889436"/>
+        <c:axId val="1048450435"/>
+        <c:axId val="1683088026"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="427096795"/>
+        <c:axId val="1048450435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1732889436"/>
+        <c:crossAx val="1683088026"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1732889436"/>
+        <c:axId val="1683088026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427096795"/>
+        <c:crossAx val="1048450435"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2250,6 +2250,8 @@
         <n v="73.19"/>
         <n v="19.02"/>
         <n v="580.0"/>
+        <n v="101.47"/>
+        <n v="983.8"/>
         <n v="7200.0"/>
         <n v="113.31"/>
         <n v="930.0"/>
@@ -2431,6 +2433,8 @@
         <item x="116"/>
         <item x="117"/>
         <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2781,7 +2785,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUM(B:B)</f>
-        <v>258704.46</v>
+        <v>258712.66</v>
       </c>
       <c r="L3" s="9">
         <f>EOMONTH(MAX(MAX('Todos os Gastos'!$A:$A),MAX('Salários'!$B:$B)),-1)+1</f>
@@ -2822,7 +2826,7 @@
       </c>
       <c r="J4" s="8">
         <f>SUM(C:C)</f>
-        <v>255885.33</v>
+        <v>258648.33</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>11</v>
@@ -2901,8 +2905,8 @@
         <v>13</v>
       </c>
       <c r="J6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2819.1299999999883)</f>
-        <v>-2819.13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-64.3299999999872)</f>
+        <v>-64.33</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -2912,15 +2916,15 @@
       </c>
       <c r="B7" s="6">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>14599.18</v>
+        <v>14607.38</v>
       </c>
       <c r="C7" s="6">
         <f>IF($A7="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>14480</v>
+        <v>17243</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>-119.18</v>
+        <v>2635.62</v>
       </c>
       <c r="E7" s="4">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2932,7 +2936,7 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>13981.11</v>
+        <v>16735.91</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
@@ -2969,14 +2973,14 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>13201.93</v>
+        <v>15956.73</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="8">
         <f>AVERAGEIF(D:D,"&lt;&gt;",D:D)</f>
-        <v>-165.8311765</v>
+        <v>-3.784117647</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -3006,7 +3010,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="2"/>
-        <v>11780.95</v>
+        <v>14535.75</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>16</v>
@@ -3043,7 +3047,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>9791.77</v>
+        <v>12546.57</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>17</v>
@@ -3080,7 +3084,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="2"/>
-        <v>8202.79</v>
+        <v>10957.59</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>18</v>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>7113.61</v>
+        <v>9868.41</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>19</v>
@@ -3154,7 +3158,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="2"/>
-        <v>2904.43</v>
+        <v>5659.23</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -3184,7 +3188,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>5744.17</v>
+        <v>8498.97</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>2673.27</v>
+        <v>5428.07</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -3244,7 +3248,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>-507.85</v>
+        <v>2246.95</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -3274,7 +3278,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>-4860.9</v>
+        <v>-2106.1</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -3304,7 +3308,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>-2819.13</v>
+        <v>-64.33</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -7556,8 +7560,8 @@
       <c r="C19" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="28">
-        <v>7000.0</v>
+      <c r="D19" s="26">
+        <v>7663.0</v>
       </c>
     </row>
     <row r="20">
@@ -7571,7 +7575,7 @@
         <v>26</v>
       </c>
       <c r="D20" s="26">
-        <v>1800.0</v>
+        <v>3900.0</v>
       </c>
     </row>
     <row r="21">
@@ -14315,8 +14319,8 @@
       <c r="B125" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C125" s="49">
-        <v>95.12</v>
+      <c r="C125" s="47">
+        <v>101.47</v>
       </c>
       <c r="D125" s="42"/>
       <c r="E125" s="42"/>
@@ -14330,8 +14334,8 @@
       <c r="B126" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C126" s="49">
-        <v>981.95</v>
+      <c r="C126" s="47">
+        <v>983.8</v>
       </c>
       <c r="D126" s="42"/>
       <c r="E126" s="42"/>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1881,11 +1881,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1048450435"/>
-        <c:axId val="1683088026"/>
+        <c:axId val="1395213691"/>
+        <c:axId val="430812404"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1048450435"/>
+        <c:axId val="1395213691"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1937,10 +1937,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1683088026"/>
+        <c:crossAx val="430812404"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1683088026"/>
+        <c:axId val="430812404"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2004,7 +2004,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1048450435"/>
+        <c:crossAx val="1395213691"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2249,10 +2249,10 @@
         <n v="2811.15"/>
         <n v="73.19"/>
         <n v="19.02"/>
-        <n v="580.0"/>
+        <n v="5301.28"/>
         <n v="101.47"/>
         <n v="983.8"/>
-        <n v="7200.0"/>
+        <n v="4875.26"/>
         <n v="113.31"/>
         <n v="930.0"/>
         <n v="6800.0"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUM(B:B)</f>
-        <v>258712.66</v>
+        <v>261109.2</v>
       </c>
       <c r="L3" s="9">
         <f>EOMONTH(MAX(MAX('Todos os Gastos'!$A:$A),MAX('Salários'!$B:$B)),-1)+1</f>
@@ -2905,8 +2905,8 @@
         <v>13</v>
       </c>
       <c r="J6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-64.3299999999872)</f>
-        <v>-64.33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2460.8699999999917)</f>
+        <v>-2460.87</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B7" s="6">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>14607.38</v>
+        <v>16603.92</v>
       </c>
       <c r="C7" s="6">
         <f>IF($A7="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2924,11 +2924,11 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>2635.62</v>
+        <v>639.08</v>
       </c>
       <c r="E7" s="4">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4">
         <f>IF($A7="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>16735.91</v>
+        <v>14739.37</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B8" s="3">
         <f>IF($A8="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>13459.18</v>
+        <v>13859.18</v>
       </c>
       <c r="C8" s="3">
         <f>IF($A8="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -2961,11 +2961,11 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="1"/>
-        <v>-779.18</v>
+        <v>-1179.18</v>
       </c>
       <c r="E8" s="4">
         <f>IF($A8="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="4">
         <f>IF($A8="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -2973,14 +2973,14 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>15956.73</v>
+        <v>13560.19</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="8">
         <f>AVERAGEIF(D:D,"&lt;&gt;",D:D)</f>
-        <v>-3.784117647</v>
+        <v>-144.7570588</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="2"/>
-        <v>14535.75</v>
+        <v>12139.21</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>16</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>12546.57</v>
+        <v>10150.03</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>17</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="2"/>
-        <v>10957.59</v>
+        <v>8561.05</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>18</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>9868.41</v>
+        <v>7471.87</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>19</v>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="2"/>
-        <v>5659.23</v>
+        <v>3262.69</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>8498.97</v>
+        <v>6102.43</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>5428.07</v>
+        <v>3031.53</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>2246.95</v>
+        <v>-149.59</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>-2106.1</v>
+        <v>-4502.64</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>-64.33</v>
+        <v>-2460.87</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -14229,8 +14229,8 @@
       <c r="B119" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="C119" s="49">
-        <v>580.0</v>
+      <c r="C119" s="47">
+        <v>5301.28</v>
       </c>
       <c r="D119" s="42"/>
       <c r="E119" s="42"/>
@@ -14409,8 +14409,8 @@
       <c r="B131" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C131" s="49">
-        <v>7200.0</v>
+      <c r="C131" s="47">
+        <v>4875.26</v>
       </c>
       <c r="D131" s="42"/>
       <c r="E131" s="42"/>
@@ -14433,8 +14433,8 @@
       <c r="H132" s="58"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
-      <c r="A133" s="46">
-        <v>46203.0</v>
+      <c r="A133" s="34">
+        <v>46205.0</v>
       </c>
       <c r="B133" s="43" t="s">
         <v>92</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="430">
   <si>
     <t>Mês</t>
   </si>
@@ -324,6 +324,9 @@
     <t>Futebol</t>
   </si>
   <si>
+    <t>Lote 7600 jun.</t>
+  </si>
+  <si>
     <t>Mari</t>
   </si>
   <si>
@@ -394,9 +397,6 @@
   </si>
   <si>
     <t>Lote 3400 mai.</t>
-  </si>
-  <si>
-    <t>Lote 7600 jun.</t>
   </si>
   <si>
     <t>Taxa_Base_CDI</t>
@@ -1890,11 +1890,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1221299180"/>
-        <c:axId val="50444089"/>
+        <c:axId val="1505083291"/>
+        <c:axId val="2090637336"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1221299180"/>
+        <c:axId val="1505083291"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1946,10 +1946,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50444089"/>
+        <c:crossAx val="2090637336"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50444089"/>
+        <c:axId val="2090637336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2013,7 +2013,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1221299180"/>
+        <c:crossAx val="1505083291"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2311,6 +2311,7 @@
         <s v="Lote 190 mai"/>
         <s v="Lote 3120 mai"/>
         <s v="Lote 2800 mai."/>
+        <s v="Lote 7600 jun."/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -2458,7 +2459,7 @@
     </pivotField>
     <pivotField name="Lote usado" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
       <items>
-        <item h="1" x="14"/>
+        <item h="1" x="15"/>
         <item x="1"/>
         <item x="11"/>
         <item x="2"/>
@@ -2471,6 +2472,7 @@
         <item x="7"/>
         <item x="6"/>
         <item x="9"/>
+        <item h="1" x="14"/>
         <item x="8"/>
         <item x="0"/>
         <item t="default"/>
@@ -14247,8 +14249,12 @@
       <c r="C119" s="47">
         <v>5301.28</v>
       </c>
-      <c r="D119" s="42"/>
-      <c r="E119" s="42"/>
+      <c r="D119" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E119" s="59" t="s">
+        <v>97</v>
+      </c>
       <c r="G119" s="57"/>
       <c r="H119" s="58"/>
     </row>
@@ -14262,8 +14268,12 @@
       <c r="C120" s="47">
         <v>400.0</v>
       </c>
-      <c r="D120" s="35"/>
-      <c r="E120" s="35"/>
+      <c r="D120" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E120" s="59" t="s">
+        <v>97</v>
+      </c>
       <c r="G120" s="57"/>
       <c r="H120" s="58"/>
     </row>
@@ -14332,7 +14342,7 @@
         <v>46183.0</v>
       </c>
       <c r="B125" s="43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C125" s="47">
         <v>50.0</v>
@@ -14452,7 +14462,7 @@
         <v>46192.0</v>
       </c>
       <c r="B133" s="37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C133" s="47">
         <v>40.0</v>
@@ -14968,7 +14978,7 @@
         <v>46273.0</v>
       </c>
       <c r="B167" s="42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C167" s="49">
         <v>90.0</v>
@@ -15178,7 +15188,7 @@
         <v>46303.0</v>
       </c>
       <c r="B181" s="42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C181" s="49">
         <v>90.0</v>
@@ -15193,7 +15203,7 @@
         <v>46303.0</v>
       </c>
       <c r="B182" s="42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C182" s="49">
         <v>119.8</v>
@@ -15388,7 +15398,7 @@
         <v>46335.0</v>
       </c>
       <c r="B195" s="42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C195" s="49">
         <v>90.0</v>
@@ -15628,7 +15638,7 @@
         <v>46367.0</v>
       </c>
       <c r="B211" s="42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C211" s="49">
         <v>2900.0</v>
@@ -20014,27 +20024,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B2" s="59" t="s">
         <v>46</v>
@@ -20049,15 +20059,15 @@
         <v>3122.53</v>
       </c>
       <c r="F2" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="27">
         <v>46146.0</v>
@@ -20069,7 +20079,7 @@
         <v>3119.0</v>
       </c>
       <c r="F3" s="67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -20077,7 +20087,7 @@
         <v>61</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" s="27">
         <v>46148.0</v>
@@ -20089,7 +20099,7 @@
         <v>3000.0</v>
       </c>
       <c r="F4" s="67" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -20109,7 +20119,7 @@
         <v>192.41</v>
       </c>
       <c r="F5" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
@@ -24115,19 +24125,19 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
@@ -24144,7 +24154,7 @@
         <v>4000.0</v>
       </c>
       <c r="E2" s="70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -24161,7 +24171,7 @@
         <v>6630.64</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -24178,7 +24188,7 @@
         <v>10342.0</v>
       </c>
       <c r="E4" s="70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -24195,7 +24205,7 @@
         <v>4124.75</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -24212,7 +24222,7 @@
         <v>5400.0</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -24229,12 +24239,12 @@
         <v>2063.11</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="66" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" s="71">
         <v>46084.0</v>
@@ -24246,12 +24256,12 @@
         <v>3000.0</v>
       </c>
       <c r="E8" s="73" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="66" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="71">
         <v>46085.0</v>
@@ -24263,7 +24273,7 @@
         <v>3000.0</v>
       </c>
       <c r="E9" s="73" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -24280,7 +24290,7 @@
         <v>8587.0</v>
       </c>
       <c r="E10" s="74" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
@@ -24297,7 +24307,7 @@
         <v>5680.0</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -24314,7 +24324,7 @@
         <v>7536.72</v>
       </c>
       <c r="E12" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -24331,12 +24341,12 @@
         <v>2800.0</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="59" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" s="27">
         <v>46150.0</v>
@@ -24348,12 +24358,12 @@
         <v>3000.0</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B15" s="27">
         <v>46150.0</v>
@@ -24365,12 +24375,12 @@
         <v>3429.0</v>
       </c>
       <c r="E15" s="67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="59" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B16" s="27">
         <v>46174.0</v>
@@ -24382,7 +24392,7 @@
         <v>7561.0</v>
       </c>
       <c r="E16" s="67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -31275,7 +31285,7 @@
     </row>
     <row r="18">
       <c r="A18" s="82" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B18" s="83">
         <v>120.0</v>
@@ -35626,7 +35636,7 @@
     </row>
     <row r="49">
       <c r="A49" s="82" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="83">
         <v>150.0</v>
@@ -36873,7 +36883,7 @@
     </row>
     <row r="58">
       <c r="A58" s="82" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B58" s="83">
         <v>105.0</v>
@@ -37014,7 +37024,7 @@
     </row>
     <row r="59">
       <c r="A59" s="82" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B59" s="83">
         <v>103.0</v>
@@ -37282,7 +37292,7 @@
     </row>
     <row r="61">
       <c r="A61" s="82" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B61" s="83">
         <v>230.0</v>
@@ -40815,7 +40825,7 @@
     </row>
     <row r="86">
       <c r="A86" s="82" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B86" s="83">
         <v>220.0</v>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="431">
   <si>
     <t>Mês</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Salário UFV</t>
   </si>
   <si>
-    <t>Salário UEMG</t>
-  </si>
-  <si>
     <t>Velt</t>
   </si>
   <si>
@@ -121,6 +118,9 @@
   </si>
   <si>
     <t>Bolsa Doutorado</t>
+  </si>
+  <si>
+    <t>Salário UEMG</t>
   </si>
   <si>
     <t/>
@@ -1899,11 +1899,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="796605436"/>
-        <c:axId val="1688745908"/>
+        <c:axId val="1997471734"/>
+        <c:axId val="1112197495"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="796605436"/>
+        <c:axId val="1997471734"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1955,10 +1955,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1688745908"/>
+        <c:crossAx val="1112197495"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1688745908"/>
+        <c:axId val="1112197495"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2022,7 +2022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="796605436"/>
+        <c:crossAx val="1997471734"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -7350,21 +7350,21 @@
     </row>
     <row r="3">
       <c r="A3" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="23">
         <v>46027.0</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="24">
-        <v>3634.7</v>
+        <v>5680.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="23">
         <v>46027.0</v>
@@ -7373,12 +7373,12 @@
         <v>28</v>
       </c>
       <c r="D4" s="24">
-        <v>5680.0</v>
+        <v>4500.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B5" s="23">
         <v>46027.0</v>
@@ -7387,7 +7387,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="24">
-        <v>4500.0</v>
+        <v>3634.7</v>
       </c>
     </row>
     <row r="6">
@@ -7406,21 +7406,21 @@
     </row>
     <row r="7">
       <c r="A7" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="25">
         <v>46058.0</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="24">
-        <v>2063.11</v>
+        <v>11360.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="25">
         <v>46058.0</v>
@@ -7429,12 +7429,12 @@
         <v>28</v>
       </c>
       <c r="D8" s="24">
-        <v>11360.0</v>
+        <v>4500.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9" s="25">
         <v>46058.0</v>
@@ -7443,7 +7443,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="24">
-        <v>4500.0</v>
+        <v>2063.11</v>
       </c>
     </row>
     <row r="10">
@@ -7462,30 +7462,30 @@
     </row>
     <row r="11">
       <c r="A11" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B11" s="25">
         <v>46087.0</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="24">
-        <v>3523.0</v>
+        <v>5680.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" s="25">
         <v>46087.0</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="24">
-        <v>5680.0</v>
+        <v>3523.0</v>
       </c>
     </row>
     <row r="13">
@@ -7504,30 +7504,30 @@
     </row>
     <row r="14">
       <c r="A14" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B14" s="25">
         <v>46120.0</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="24">
-        <v>3696.0</v>
+        <v>5680.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B15" s="25">
         <v>46120.0</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="24">
-        <v>5680.0</v>
+        <v>3696.0</v>
       </c>
     </row>
     <row r="16">
@@ -7546,30 +7546,30 @@
     </row>
     <row r="17">
       <c r="A17" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="25">
         <v>46150.0</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="24">
-        <v>3900.0</v>
+        <v>5680.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B18" s="25">
         <v>46150.0</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="24">
-        <v>5680.0</v>
+        <v>3900.0</v>
       </c>
     </row>
     <row r="19">
@@ -7588,30 +7588,30 @@
     </row>
     <row r="20">
       <c r="A20" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="28">
         <v>46178.0</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="26">
-        <v>3900.0</v>
+        <v>27</v>
+      </c>
+      <c r="D20" s="29">
+        <v>5680.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="28">
-        <v>46178.0</v>
+        <v>24</v>
+      </c>
+      <c r="B21" s="27">
+        <v>46181.0</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="29">
-        <v>5680.0</v>
+        <v>29</v>
+      </c>
+      <c r="D21" s="26">
+        <v>3900.0</v>
       </c>
     </row>
     <row r="22">
@@ -7630,13 +7630,13 @@
     </row>
     <row r="23">
       <c r="A23" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="28">
         <v>46208.0</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="29">
         <v>5680.0</v>
@@ -7661,13 +7661,13 @@
     </row>
     <row r="25">
       <c r="A25" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="28">
         <v>46238.0</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="29">
         <v>5680.0</v>
@@ -7689,13 +7689,13 @@
     </row>
     <row r="27">
       <c r="A27" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="28">
         <v>46269.0</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="29">
         <v>5680.0</v>
@@ -7717,13 +7717,13 @@
     </row>
     <row r="29">
       <c r="A29" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="28">
         <v>46300.0</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="29">
         <v>5680.0</v>
@@ -7745,13 +7745,13 @@
     </row>
     <row r="31">
       <c r="A31" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" s="28">
         <v>46331.0</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" s="29">
         <v>5680.0</v>
@@ -7773,13 +7773,13 @@
     </row>
     <row r="33">
       <c r="A33" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" s="28">
         <v>46362.0</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="29">
         <v>5680.0</v>
@@ -7801,13 +7801,13 @@
     </row>
     <row r="35">
       <c r="A35" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" s="23">
         <v>46392.0</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="24">
         <v>5680.0</v>
@@ -7829,13 +7829,13 @@
     </row>
     <row r="37">
       <c r="A37" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" s="28">
         <v>46424.0</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37" s="29">
         <v>5680.0</v>
@@ -7857,13 +7857,13 @@
     </row>
     <row r="39">
       <c r="A39" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" s="28">
         <v>46452.0</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" s="29">
         <v>5680.0</v>
@@ -7885,13 +7885,13 @@
     </row>
     <row r="41">
       <c r="A41" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" s="27">
         <v>46483.0</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41" s="29">
         <v>5680.0</v>
@@ -7913,13 +7913,13 @@
     </row>
     <row r="43">
       <c r="A43" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B43" s="27">
         <v>46513.0</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" s="29">
         <v>5680.0</v>
@@ -11773,6 +11773,7 @@
   <autoFilter ref="$A$1:$D$43">
     <sortState ref="A1:D43">
       <sortCondition ref="B1:B43"/>
+      <sortCondition ref="C1:C43"/>
       <sortCondition ref="A1:A43"/>
     </sortState>
   </autoFilter>
@@ -13194,7 +13195,7 @@
         <v>46101.0</v>
       </c>
       <c r="B65" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C65" s="49">
         <v>75.0</v>
@@ -13645,7 +13646,7 @@
         <v>46126.0</v>
       </c>
       <c r="B87" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C87" s="47">
         <v>18.75</v>
@@ -14296,8 +14297,12 @@
       <c r="C121" s="49">
         <v>950.0</v>
       </c>
-      <c r="D121" s="42"/>
-      <c r="E121" s="42"/>
+      <c r="D121" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E121" s="59" t="s">
+        <v>97</v>
+      </c>
       <c r="G121" s="57"/>
       <c r="H121" s="58"/>
     </row>
@@ -14311,8 +14316,12 @@
       <c r="C122" s="47">
         <v>110.0</v>
       </c>
-      <c r="D122" s="42"/>
-      <c r="E122" s="42"/>
+      <c r="D122" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E122" s="59" t="s">
+        <v>97</v>
+      </c>
       <c r="G122" s="57"/>
       <c r="H122" s="58"/>
     </row>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="435">
   <si>
     <t>Mês</t>
   </si>
@@ -1905,11 +1905,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1696433328"/>
-        <c:axId val="424910265"/>
+        <c:axId val="1757612991"/>
+        <c:axId val="1962999325"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1696433328"/>
+        <c:axId val="1757612991"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1961,10 +1961,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="424910265"/>
+        <c:crossAx val="1962999325"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="424910265"/>
+        <c:axId val="1962999325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2028,7 +2028,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1696433328"/>
+        <c:crossAx val="1757612991"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2286,6 +2286,7 @@
         <n v="4875.26"/>
         <n v="113.31"/>
         <n v="930.0"/>
+        <n v="981.88"/>
         <n v="6800.0"/>
         <n v="1500.0"/>
         <n v="5800.0"/>
@@ -2474,6 +2475,7 @@
         <item x="125"/>
         <item x="126"/>
         <item x="127"/>
+        <item x="128"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2825,7 +2827,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUM(B:B)</f>
-        <v>261386.65</v>
+        <v>261386.58</v>
       </c>
       <c r="L3" s="9">
         <f>EOMONTH(MAX(MAX('Todos os Gastos'!$A:$A),MAX('Salários'!$B:$B)),-1)+1</f>
@@ -2945,8 +2947,8 @@
         <v>13</v>
       </c>
       <c r="J6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2838.3199999999924)</f>
-        <v>-2838.32</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-2838.2499999999927)</f>
+        <v>-2838.25</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -2993,7 +2995,7 @@
       </c>
       <c r="B8" s="3">
         <f>IF($A8="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>13859.18</v>
+        <v>13859.11</v>
       </c>
       <c r="C8" s="3">
         <f>IF($A8="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -3001,7 +3003,7 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="1"/>
-        <v>-1179.18</v>
+        <v>-1179.11</v>
       </c>
       <c r="E8" s="4">
         <f>IF($A8="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -3013,14 +3015,14 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>13182.74</v>
+        <v>13182.81</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="8">
         <f>AVERAGEIF(D:D,"&lt;&gt;",D:D)</f>
-        <v>-166.96</v>
+        <v>-166.9558824</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -3050,7 +3052,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="2"/>
-        <v>11761.76</v>
+        <v>11761.83</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>16</v>
@@ -3087,7 +3089,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>9772.58</v>
+        <v>9772.65</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>17</v>
@@ -3124,7 +3126,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="2"/>
-        <v>8183.6</v>
+        <v>8183.67</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>18</v>
@@ -3161,7 +3163,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>7094.42</v>
+        <v>7094.49</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>19</v>
@@ -3198,7 +3200,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="2"/>
-        <v>2885.24</v>
+        <v>2885.31</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -3228,7 +3230,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>5724.98</v>
+        <v>5725.05</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -3258,7 +3260,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>2654.08</v>
+        <v>2654.15</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -3288,7 +3290,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>-527.04</v>
+        <v>-526.97</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -3318,7 +3320,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>-4880.09</v>
+        <v>-4880.02</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -3348,7 +3350,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>-2838.32</v>
+        <v>-2838.25</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -14465,8 +14467,12 @@
       <c r="C129" s="47">
         <v>101.47</v>
       </c>
-      <c r="D129" s="42"/>
-      <c r="E129" s="42"/>
+      <c r="D129" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E129" s="59" t="s">
+        <v>61</v>
+      </c>
       <c r="G129" s="57"/>
       <c r="H129" s="58"/>
     </row>
@@ -14753,8 +14759,8 @@
       <c r="B148" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C148" s="49">
-        <v>981.95</v>
+      <c r="C148" s="47">
+        <v>981.88</v>
       </c>
       <c r="D148" s="42"/>
       <c r="E148" s="42"/>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Resumo Mensal'!$A$1:$G$121</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Salários'!$A$1:$D$43</definedName>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$282</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Todos os Gastos'!$A$1:$E$283</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Switching!$A$1:$F$5</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Inventário de Lotes'!$A$1:$E$18</definedName>
     <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Carteira!$A$1:$AY$86</definedName>
@@ -24,14 +24,14 @@
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="pgb9ME1uZzuFb3vOhE+YBsaXzBa2Jy5tJT7pGf/ic+I="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="DQBKD5XoRJI9lKVG2XC65VDSJEYPPdBiStsAN31p2q4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="435">
   <si>
     <t>Mês</t>
   </si>
@@ -336,10 +336,10 @@
     <t>Cartão Mercado Pago</t>
   </si>
   <si>
-    <t>Mari</t>
+    <t>Churrasco pelada</t>
   </si>
   <si>
-    <t>Churrasco pelada</t>
+    <t>Mari</t>
   </si>
   <si>
     <t>IPTU</t>
@@ -1668,13 +1668,13 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1905,11 +1905,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1757612991"/>
-        <c:axId val="1962999325"/>
+        <c:axId val="1315791852"/>
+        <c:axId val="1200097796"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1757612991"/>
+        <c:axId val="1315791852"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1961,10 +1961,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1962999325"/>
+        <c:crossAx val="1200097796"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1962999325"/>
+        <c:axId val="1200097796"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2028,7 +2028,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1757612991"/>
+        <c:crossAx val="1315791852"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2175,7 +2175,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
   <cacheSource type="worksheet">
-    <worksheetSource ref="C1:E1026" sheet="Todos os Gastos"/>
+    <worksheetSource ref="C1:E1027" sheet="Todos os Gastos"/>
   </cacheSource>
   <cacheFields>
     <cacheField name="Valor" numFmtId="166">
@@ -2282,7 +2282,7 @@
         <n v="204.85"/>
         <n v="82.09"/>
         <n v="101.47"/>
-        <n v="983.8"/>
+        <n v="183.8"/>
         <n v="4875.26"/>
         <n v="113.31"/>
         <n v="930.0"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J5" s="8">
         <f>SUMIFS(D:D,A:A,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A:A,"&lt;&gt;")</f>
-        <v>14361.92</v>
+        <v>14471.92</v>
       </c>
       <c r="L5" s="10">
         <v>46023.0</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B7" s="6">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>16876.37</v>
+        <v>16766.37</v>
       </c>
       <c r="C7" s="6">
         <f>IF($A7="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2966,11 +2966,11 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>266.63</v>
+        <v>376.63</v>
       </c>
       <c r="E7" s="4">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4">
         <f>IF($A7="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>14361.92</v>
+        <v>14471.92</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(D:D,A:A,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A:A,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>266.63</v>
+        <v>376.63</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B8" s="3">
         <f>IF($A8="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>13859.11</v>
+        <v>13969.11</v>
       </c>
       <c r="C8" s="3">
         <f>IF($A8="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -3003,11 +3003,11 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="1"/>
-        <v>-1179.11</v>
+        <v>-1289.11</v>
       </c>
       <c r="E8" s="4">
         <f>IF($A8="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" s="4">
         <f>IF($A8="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -14484,25 +14484,33 @@
         <v>64</v>
       </c>
       <c r="C130" s="47">
-        <v>983.8</v>
-      </c>
-      <c r="D130" s="42"/>
-      <c r="E130" s="42"/>
+        <v>800.0</v>
+      </c>
+      <c r="D130" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E130" s="59" t="s">
+        <v>61</v>
+      </c>
       <c r="G130" s="57"/>
       <c r="H130" s="58"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="34">
-        <v>46188.0</v>
-      </c>
-      <c r="B131" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="C131" s="49">
-        <v>2831.4</v>
-      </c>
-      <c r="D131" s="42"/>
-      <c r="E131" s="42"/>
+        <v>46185.0</v>
+      </c>
+      <c r="B131" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C131" s="47">
+        <v>183.8</v>
+      </c>
+      <c r="D131" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E131" s="43" t="s">
+        <v>38</v>
+      </c>
       <c r="G131" s="57"/>
       <c r="H131" s="58"/>
     </row>
@@ -14510,14 +14518,18 @@
       <c r="A132" s="34">
         <v>46188.0</v>
       </c>
-      <c r="B132" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C132" s="47">
-        <v>60.0</v>
-      </c>
-      <c r="D132" s="42"/>
-      <c r="E132" s="42"/>
+      <c r="B132" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C132" s="49">
+        <v>2831.4</v>
+      </c>
+      <c r="D132" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E132" s="60" t="s">
+        <v>55</v>
+      </c>
       <c r="G132" s="57"/>
       <c r="H132" s="58"/>
     </row>
@@ -14531,8 +14543,12 @@
       <c r="C133" s="49">
         <v>65.0</v>
       </c>
-      <c r="D133" s="42"/>
-      <c r="E133" s="42"/>
+      <c r="D133" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E133" s="60" t="s">
+        <v>55</v>
+      </c>
       <c r="G133" s="57"/>
       <c r="H133" s="58"/>
     </row>
@@ -14546,20 +14562,24 @@
       <c r="C134" s="49">
         <v>132.4</v>
       </c>
-      <c r="D134" s="42"/>
-      <c r="E134" s="42"/>
+      <c r="D134" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E134" s="60" t="s">
+        <v>55</v>
+      </c>
       <c r="G134" s="57"/>
       <c r="H134" s="58"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
-      <c r="A135" s="34">
-        <v>46188.0</v>
-      </c>
-      <c r="B135" s="43" t="s">
+      <c r="A135" s="46">
+        <v>46192.0</v>
+      </c>
+      <c r="B135" s="37" t="s">
         <v>101</v>
       </c>
       <c r="C135" s="47">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="D135" s="42"/>
       <c r="E135" s="42"/>
@@ -14567,14 +14587,14 @@
       <c r="H135" s="58"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
-      <c r="A136" s="34">
-        <v>46188.0</v>
-      </c>
-      <c r="B136" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="C136" s="47">
-        <v>120.0</v>
+      <c r="A136" s="46">
+        <v>46192.0</v>
+      </c>
+      <c r="B136" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C136" s="49">
+        <v>50.0</v>
       </c>
       <c r="D136" s="42"/>
       <c r="E136" s="42"/>
@@ -14585,11 +14605,11 @@
       <c r="A137" s="46">
         <v>46192.0</v>
       </c>
-      <c r="B137" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C137" s="47">
-        <v>40.0</v>
+      <c r="B137" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C137" s="49">
+        <v>530.0</v>
       </c>
       <c r="D137" s="42"/>
       <c r="E137" s="42"/>
@@ -14597,14 +14617,14 @@
       <c r="H137" s="58"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="46">
-        <v>46192.0</v>
-      </c>
-      <c r="B138" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C138" s="49">
-        <v>50.0</v>
+      <c r="A138" s="34">
+        <v>46193.0</v>
+      </c>
+      <c r="B138" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C138" s="47">
+        <v>4875.26</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="42"/>
@@ -14613,13 +14633,13 @@
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="46">
-        <v>46192.0</v>
-      </c>
-      <c r="B139" s="42" t="s">
-        <v>66</v>
+        <v>46193.0</v>
+      </c>
+      <c r="B139" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C139" s="49">
-        <v>530.0</v>
+        <v>113.31</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="42"/>
@@ -14630,11 +14650,11 @@
       <c r="A140" s="34">
         <v>46193.0</v>
       </c>
-      <c r="B140" s="35" t="s">
-        <v>36</v>
+      <c r="B140" s="42" t="s">
+        <v>86</v>
       </c>
       <c r="C140" s="47">
-        <v>4875.26</v>
+        <v>120.0</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="42"/>
@@ -14642,14 +14662,14 @@
       <c r="H140" s="58"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="46">
-        <v>46193.0</v>
-      </c>
-      <c r="B141" s="43" t="s">
-        <v>54</v>
+      <c r="A141" s="34">
+        <v>46205.0</v>
+      </c>
+      <c r="B141" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C141" s="49">
-        <v>113.31</v>
+        <v>930.0</v>
       </c>
       <c r="D141" s="42"/>
       <c r="E141" s="42"/>
@@ -14660,32 +14680,29 @@
       <c r="A142" s="34">
         <v>46205.0</v>
       </c>
-      <c r="B142" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C142" s="49">
-        <v>930.0</v>
-      </c>
-      <c r="D142" s="42"/>
-      <c r="E142" s="42"/>
-      <c r="F142" s="54"/>
-      <c r="G142" s="39"/>
-      <c r="H142" s="53"/>
-      <c r="I142" s="41"/>
-      <c r="J142" s="41"/>
+      <c r="B142" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C142" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D142" s="35"/>
+      <c r="E142" s="35"/>
+      <c r="G142" s="57"/>
+      <c r="H142" s="58"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="34">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B143" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C143" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D143" s="35"/>
-      <c r="E143" s="35"/>
+        <v>60</v>
+      </c>
+      <c r="C143" s="49">
+        <v>950.0</v>
+      </c>
+      <c r="D143" s="42"/>
+      <c r="E143" s="42"/>
       <c r="F143" s="54"/>
       <c r="G143" s="39"/>
       <c r="H143" s="53"/>
@@ -14693,29 +14710,32 @@
       <c r="J143" s="41"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="34">
-        <v>46209.0</v>
+      <c r="A144" s="46">
+        <v>46210.0</v>
       </c>
       <c r="B144" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C144" s="49">
-        <v>950.0</v>
+        <v>44</v>
+      </c>
+      <c r="C144" s="47">
+        <v>110.0</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42"/>
-      <c r="G144" s="57"/>
-      <c r="H144" s="58"/>
+      <c r="F144" s="54"/>
+      <c r="G144" s="39"/>
+      <c r="H144" s="53"/>
+      <c r="I144" s="41"/>
+      <c r="J144" s="41"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="46">
-        <v>46210.0</v>
-      </c>
-      <c r="B145" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C145" s="47">
-        <v>110.0</v>
+      <c r="A145" s="34">
+        <v>46213.0</v>
+      </c>
+      <c r="B145" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C145" s="49">
+        <v>65.0</v>
       </c>
       <c r="D145" s="42"/>
       <c r="E145" s="42"/>
@@ -14724,13 +14744,13 @@
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="34">
-        <v>46213.0</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>77</v>
+        <v>46214.0</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C146" s="49">
-        <v>65.0</v>
+        <v>95.12</v>
       </c>
       <c r="D146" s="42"/>
       <c r="E146" s="42"/>
@@ -14739,13 +14759,13 @@
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="34">
-        <v>46214.0</v>
-      </c>
-      <c r="B147" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C147" s="49">
-        <v>95.12</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B147" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C147" s="47">
+        <v>981.88</v>
       </c>
       <c r="D147" s="42"/>
       <c r="E147" s="42"/>
@@ -14756,11 +14776,11 @@
       <c r="A148" s="34">
         <v>46215.0</v>
       </c>
-      <c r="B148" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C148" s="47">
-        <v>981.88</v>
+      <c r="B148" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C148" s="49">
+        <v>2831.4</v>
       </c>
       <c r="D148" s="42"/>
       <c r="E148" s="42"/>
@@ -14771,11 +14791,11 @@
       <c r="A149" s="34">
         <v>46215.0</v>
       </c>
-      <c r="B149" s="42" t="s">
-        <v>70</v>
+      <c r="B149" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C149" s="49">
-        <v>2831.4</v>
+        <v>50.0</v>
       </c>
       <c r="D149" s="42"/>
       <c r="E149" s="42"/>
@@ -14783,14 +14803,14 @@
       <c r="H149" s="58"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="34">
-        <v>46215.0</v>
+      <c r="A150" s="46">
+        <v>46218.0</v>
       </c>
       <c r="B150" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C150" s="49">
-        <v>50.0</v>
+        <v>90</v>
+      </c>
+      <c r="C150" s="47">
+        <v>60.0</v>
       </c>
       <c r="D150" s="42"/>
       <c r="E150" s="42"/>
@@ -14813,14 +14833,14 @@
       <c r="H151" s="58"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="34">
-        <v>46223.0</v>
-      </c>
-      <c r="B152" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C152" s="49">
-        <v>6800.0</v>
+      <c r="A152" s="46">
+        <v>46218.0</v>
+      </c>
+      <c r="B152" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C152" s="47">
+        <v>50.0</v>
       </c>
       <c r="D152" s="42"/>
       <c r="E152" s="42"/>
@@ -14831,11 +14851,11 @@
       <c r="A153" s="34">
         <v>46223.0</v>
       </c>
-      <c r="B153" s="43" t="s">
-        <v>54</v>
+      <c r="B153" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C153" s="49">
-        <v>113.31</v>
+        <v>6800.0</v>
       </c>
       <c r="D153" s="42"/>
       <c r="E153" s="42"/>
@@ -14843,74 +14863,74 @@
       <c r="H153" s="58"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="46">
-        <v>46233.0</v>
+      <c r="A154" s="34">
+        <v>46223.0</v>
       </c>
       <c r="B154" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C154" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D154" s="35"/>
-      <c r="E154" s="35"/>
+        <v>54</v>
+      </c>
+      <c r="C154" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D154" s="42"/>
+      <c r="E154" s="42"/>
       <c r="G154" s="57"/>
       <c r="H154" s="58"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
-      <c r="A155" s="34">
-        <v>46236.0</v>
-      </c>
-      <c r="B155" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C155" s="49">
-        <v>1500.0</v>
-      </c>
-      <c r="D155" s="42"/>
-      <c r="E155" s="42"/>
+      <c r="A155" s="46">
+        <v>46233.0</v>
+      </c>
+      <c r="B155" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C155" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D155" s="35"/>
+      <c r="E155" s="35"/>
       <c r="G155" s="57"/>
       <c r="H155" s="58"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="46">
-        <v>46239.0</v>
+      <c r="A156" s="34">
+        <v>46236.0</v>
       </c>
       <c r="B156" s="42" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C156" s="49">
-        <v>81.8</v>
-      </c>
-      <c r="D156" s="35"/>
-      <c r="E156" s="35"/>
+        <v>1500.0</v>
+      </c>
+      <c r="D156" s="42"/>
+      <c r="E156" s="42"/>
       <c r="G156" s="57"/>
       <c r="H156" s="58"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
-      <c r="A157" s="34">
-        <v>46240.0</v>
-      </c>
-      <c r="B157" s="43" t="s">
-        <v>60</v>
+      <c r="A157" s="46">
+        <v>46239.0</v>
+      </c>
+      <c r="B157" s="42" t="s">
+        <v>76</v>
       </c>
       <c r="C157" s="49">
-        <v>950.0</v>
-      </c>
-      <c r="D157" s="42"/>
-      <c r="E157" s="42"/>
+        <v>81.8</v>
+      </c>
+      <c r="D157" s="35"/>
+      <c r="E157" s="35"/>
       <c r="G157" s="57"/>
       <c r="H157" s="58"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c r="A158" s="46">
-        <v>46241.0</v>
+      <c r="A158" s="34">
+        <v>46240.0</v>
       </c>
       <c r="B158" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C158" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C158" s="49">
+        <v>950.0</v>
       </c>
       <c r="D158" s="42"/>
       <c r="E158" s="42"/>
@@ -14918,14 +14938,14 @@
       <c r="H158" s="58"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="34">
-        <v>46244.0</v>
-      </c>
-      <c r="B159" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C159" s="49">
-        <v>65.0</v>
+      <c r="A159" s="46">
+        <v>46241.0</v>
+      </c>
+      <c r="B159" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C159" s="47">
+        <v>110.0</v>
       </c>
       <c r="D159" s="42"/>
       <c r="E159" s="42"/>
@@ -14934,13 +14954,13 @@
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="34">
-        <v>46245.0</v>
-      </c>
-      <c r="B160" s="42" t="s">
-        <v>42</v>
+        <v>46244.0</v>
+      </c>
+      <c r="B160" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C160" s="49">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D160" s="42"/>
       <c r="E160" s="42"/>
@@ -14949,13 +14969,13 @@
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c r="A161" s="34">
-        <v>46246.0</v>
-      </c>
-      <c r="B161" s="43" t="s">
-        <v>64</v>
+        <v>46245.0</v>
+      </c>
+      <c r="B161" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C161" s="49">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D161" s="42"/>
       <c r="E161" s="42"/>
@@ -14966,11 +14986,11 @@
       <c r="A162" s="34">
         <v>46246.0</v>
       </c>
-      <c r="B162" s="42" t="s">
-        <v>70</v>
+      <c r="B162" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C162" s="49">
-        <v>2831.4</v>
+        <v>981.95</v>
       </c>
       <c r="D162" s="42"/>
       <c r="E162" s="42"/>
@@ -14982,10 +15002,10 @@
         <v>46246.0</v>
       </c>
       <c r="B163" s="42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C163" s="49">
-        <v>460.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D163" s="42"/>
       <c r="E163" s="42"/>
@@ -14993,14 +15013,14 @@
       <c r="H163" s="58"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="46">
+      <c r="A164" s="34">
         <v>46246.0</v>
       </c>
-      <c r="B164" s="43" t="s">
-        <v>56</v>
+      <c r="B164" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="C164" s="49">
-        <v>50.0</v>
+        <v>460.0</v>
       </c>
       <c r="D164" s="42"/>
       <c r="E164" s="42"/>
@@ -15008,14 +15028,14 @@
       <c r="H164" s="58"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
-      <c r="A165" s="34">
+      <c r="A165" s="46">
         <v>46246.0</v>
       </c>
-      <c r="B165" s="42" t="s">
-        <v>66</v>
+      <c r="B165" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C165" s="49">
-        <v>530.0</v>
+        <v>50.0</v>
       </c>
       <c r="D165" s="42"/>
       <c r="E165" s="42"/>
@@ -15024,13 +15044,13 @@
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="34">
-        <v>46249.0</v>
-      </c>
-      <c r="B166" s="43" t="s">
-        <v>62</v>
+        <v>46246.0</v>
+      </c>
+      <c r="B166" s="42" t="s">
+        <v>66</v>
       </c>
       <c r="C166" s="49">
-        <v>132.4</v>
+        <v>530.0</v>
       </c>
       <c r="D166" s="42"/>
       <c r="E166" s="42"/>
@@ -15039,13 +15059,13 @@
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="34">
-        <v>46254.0</v>
-      </c>
-      <c r="B167" s="35" t="s">
-        <v>36</v>
+        <v>46249.0</v>
+      </c>
+      <c r="B167" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C167" s="49">
-        <v>5800.0</v>
+        <v>132.4</v>
       </c>
       <c r="D167" s="42"/>
       <c r="E167" s="42"/>
@@ -15056,11 +15076,11 @@
       <c r="A168" s="34">
         <v>46254.0</v>
       </c>
-      <c r="B168" s="43" t="s">
-        <v>54</v>
+      <c r="B168" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C168" s="49">
-        <v>113.31</v>
+        <v>5800.0</v>
       </c>
       <c r="D168" s="42"/>
       <c r="E168" s="42"/>
@@ -15068,44 +15088,44 @@
       <c r="H168" s="58"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="46">
-        <v>46264.0</v>
+      <c r="A169" s="34">
+        <v>46254.0</v>
       </c>
       <c r="B169" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C169" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D169" s="35"/>
-      <c r="E169" s="35"/>
+        <v>54</v>
+      </c>
+      <c r="C169" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D169" s="42"/>
+      <c r="E169" s="42"/>
       <c r="G169" s="57"/>
       <c r="H169" s="58"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
-      <c r="A170" s="34">
-        <v>46267.0</v>
-      </c>
-      <c r="B170" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C170" s="49">
-        <v>2000.0</v>
-      </c>
-      <c r="D170" s="42"/>
-      <c r="E170" s="42"/>
+      <c r="A170" s="46">
+        <v>46264.0</v>
+      </c>
+      <c r="B170" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C170" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D170" s="35"/>
+      <c r="E170" s="35"/>
       <c r="G170" s="57"/>
       <c r="H170" s="58"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c r="A171" s="34">
-        <v>46271.0</v>
-      </c>
-      <c r="B171" s="43" t="s">
-        <v>60</v>
+        <v>46267.0</v>
+      </c>
+      <c r="B171" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C171" s="49">
-        <v>950.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D171" s="42"/>
       <c r="E171" s="42"/>
@@ -15113,14 +15133,14 @@
       <c r="H171" s="58"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="46">
-        <v>46272.0</v>
+      <c r="A172" s="34">
+        <v>46271.0</v>
       </c>
       <c r="B172" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C172" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C172" s="49">
+        <v>950.0</v>
       </c>
       <c r="D172" s="42"/>
       <c r="E172" s="42"/>
@@ -15128,14 +15148,14 @@
       <c r="H172" s="58"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="34">
-        <v>46273.0</v>
-      </c>
-      <c r="B173" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C173" s="49">
-        <v>90.0</v>
+      <c r="A173" s="46">
+        <v>46272.0</v>
+      </c>
+      <c r="B173" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C173" s="47">
+        <v>110.0</v>
       </c>
       <c r="D173" s="42"/>
       <c r="E173" s="42"/>
@@ -15144,13 +15164,13 @@
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c r="A174" s="34">
-        <v>46275.0</v>
-      </c>
-      <c r="B174" s="35" t="s">
-        <v>77</v>
+        <v>46273.0</v>
+      </c>
+      <c r="B174" s="42" t="s">
+        <v>103</v>
       </c>
       <c r="C174" s="49">
-        <v>65.0</v>
+        <v>90.0</v>
       </c>
       <c r="D174" s="42"/>
       <c r="E174" s="42"/>
@@ -15159,13 +15179,13 @@
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="34">
-        <v>46276.0</v>
-      </c>
-      <c r="B175" s="42" t="s">
-        <v>42</v>
+        <v>46275.0</v>
+      </c>
+      <c r="B175" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C175" s="49">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D175" s="42"/>
       <c r="E175" s="42"/>
@@ -15174,13 +15194,13 @@
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="34">
-        <v>46277.0</v>
-      </c>
-      <c r="B176" s="43" t="s">
-        <v>64</v>
+        <v>46276.0</v>
+      </c>
+      <c r="B176" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C176" s="49">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D176" s="42"/>
       <c r="E176" s="42"/>
@@ -15191,11 +15211,11 @@
       <c r="A177" s="34">
         <v>46277.0</v>
       </c>
-      <c r="B177" s="42" t="s">
-        <v>70</v>
+      <c r="B177" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C177" s="49">
-        <v>2831.4</v>
+        <v>981.95</v>
       </c>
       <c r="D177" s="42"/>
       <c r="E177" s="42"/>
@@ -15206,11 +15226,11 @@
       <c r="A178" s="34">
         <v>46277.0</v>
       </c>
-      <c r="B178" s="43" t="s">
-        <v>56</v>
+      <c r="B178" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C178" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D178" s="42"/>
       <c r="E178" s="42"/>
@@ -15219,13 +15239,13 @@
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="34">
-        <v>46280.0</v>
+        <v>46277.0</v>
       </c>
       <c r="B179" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C179" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D179" s="42"/>
       <c r="E179" s="42"/>
@@ -15234,13 +15254,13 @@
     </row>
     <row r="180" ht="14.25" customHeight="1">
       <c r="A180" s="34">
-        <v>46285.0</v>
-      </c>
-      <c r="B180" s="35" t="s">
-        <v>36</v>
+        <v>46280.0</v>
+      </c>
+      <c r="B180" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C180" s="49">
-        <v>6850.0</v>
+        <v>132.4</v>
       </c>
       <c r="D180" s="42"/>
       <c r="E180" s="42"/>
@@ -15248,14 +15268,14 @@
       <c r="H180" s="58"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c r="A181" s="46">
+      <c r="A181" s="34">
         <v>46285.0</v>
       </c>
-      <c r="B181" s="43" t="s">
-        <v>54</v>
+      <c r="B181" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C181" s="49">
-        <v>113.31</v>
+        <v>6850.0</v>
       </c>
       <c r="D181" s="42"/>
       <c r="E181" s="42"/>
@@ -15264,43 +15284,43 @@
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="46">
-        <v>46295.0</v>
+        <v>46285.0</v>
       </c>
       <c r="B182" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C182" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D182" s="35"/>
-      <c r="E182" s="35"/>
+        <v>54</v>
+      </c>
+      <c r="C182" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D182" s="42"/>
+      <c r="E182" s="42"/>
       <c r="G182" s="57"/>
       <c r="H182" s="58"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
-      <c r="A183" s="34">
-        <v>46297.0</v>
-      </c>
-      <c r="B183" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C183" s="49">
-        <v>1800.0</v>
-      </c>
-      <c r="D183" s="42"/>
-      <c r="E183" s="42"/>
+      <c r="A183" s="46">
+        <v>46295.0</v>
+      </c>
+      <c r="B183" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C183" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D183" s="35"/>
+      <c r="E183" s="35"/>
       <c r="G183" s="57"/>
       <c r="H183" s="58"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="34">
-        <v>46301.0</v>
-      </c>
-      <c r="B184" s="43" t="s">
-        <v>60</v>
+        <v>46297.0</v>
+      </c>
+      <c r="B184" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C184" s="49">
-        <v>950.0</v>
+        <v>1800.0</v>
       </c>
       <c r="D184" s="42"/>
       <c r="E184" s="42"/>
@@ -15308,14 +15328,14 @@
       <c r="H184" s="58"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
-      <c r="A185" s="46">
-        <v>46302.0</v>
+      <c r="A185" s="34">
+        <v>46301.0</v>
       </c>
       <c r="B185" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C185" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C185" s="49">
+        <v>950.0</v>
       </c>
       <c r="D185" s="42"/>
       <c r="E185" s="42"/>
@@ -15323,14 +15343,14 @@
       <c r="H185" s="58"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c r="A186" s="34">
+      <c r="A186" s="46">
         <v>46302.0</v>
       </c>
-      <c r="B186" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C186" s="49">
-        <v>530.0</v>
+      <c r="B186" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C186" s="47">
+        <v>110.0</v>
       </c>
       <c r="D186" s="42"/>
       <c r="E186" s="42"/>
@@ -15339,13 +15359,13 @@
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="34">
-        <v>46303.0</v>
+        <v>46302.0</v>
       </c>
       <c r="B187" s="42" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="C187" s="49">
-        <v>90.0</v>
+        <v>530.0</v>
       </c>
       <c r="D187" s="42"/>
       <c r="E187" s="42"/>
@@ -15357,10 +15377,10 @@
         <v>46303.0</v>
       </c>
       <c r="B188" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C188" s="49">
-        <v>119.8</v>
+        <v>90.0</v>
       </c>
       <c r="D188" s="42"/>
       <c r="E188" s="42"/>
@@ -15369,13 +15389,13 @@
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c r="A189" s="34">
-        <v>46305.0</v>
-      </c>
-      <c r="B189" s="35" t="s">
-        <v>77</v>
+        <v>46303.0</v>
+      </c>
+      <c r="B189" s="42" t="s">
+        <v>104</v>
       </c>
       <c r="C189" s="49">
-        <v>65.0</v>
+        <v>119.8</v>
       </c>
       <c r="D189" s="42"/>
       <c r="E189" s="42"/>
@@ -15384,13 +15404,13 @@
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="34">
-        <v>46306.0</v>
-      </c>
-      <c r="B190" s="42" t="s">
-        <v>42</v>
+        <v>46305.0</v>
+      </c>
+      <c r="B190" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C190" s="49">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D190" s="42"/>
       <c r="E190" s="42"/>
@@ -15399,13 +15419,13 @@
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="34">
-        <v>46307.0</v>
-      </c>
-      <c r="B191" s="43" t="s">
-        <v>64</v>
+        <v>46306.0</v>
+      </c>
+      <c r="B191" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C191" s="49">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D191" s="42"/>
       <c r="E191" s="42"/>
@@ -15416,11 +15436,11 @@
       <c r="A192" s="34">
         <v>46307.0</v>
       </c>
-      <c r="B192" s="42" t="s">
-        <v>70</v>
+      <c r="B192" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C192" s="49">
-        <v>2831.4</v>
+        <v>981.95</v>
       </c>
       <c r="D192" s="42"/>
       <c r="E192" s="42"/>
@@ -15428,14 +15448,14 @@
       <c r="H192" s="58"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
-      <c r="A193" s="46">
+      <c r="A193" s="34">
         <v>46307.0</v>
       </c>
-      <c r="B193" s="43" t="s">
-        <v>56</v>
+      <c r="B193" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C193" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D193" s="42"/>
       <c r="E193" s="42"/>
@@ -15443,14 +15463,14 @@
       <c r="H193" s="58"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="34">
-        <v>46310.0</v>
+      <c r="A194" s="46">
+        <v>46307.0</v>
       </c>
       <c r="B194" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C194" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D194" s="42"/>
       <c r="E194" s="42"/>
@@ -15459,13 +15479,13 @@
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="34">
-        <v>46315.0</v>
-      </c>
-      <c r="B195" s="35" t="s">
-        <v>36</v>
+        <v>46310.0</v>
+      </c>
+      <c r="B195" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C195" s="49">
-        <v>6000.0</v>
+        <v>132.4</v>
       </c>
       <c r="D195" s="42"/>
       <c r="E195" s="42"/>
@@ -15476,11 +15496,11 @@
       <c r="A196" s="34">
         <v>46315.0</v>
       </c>
-      <c r="B196" s="43" t="s">
-        <v>54</v>
+      <c r="B196" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C196" s="49">
-        <v>113.31</v>
+        <v>6000.0</v>
       </c>
       <c r="D196" s="42"/>
       <c r="E196" s="42"/>
@@ -15488,44 +15508,44 @@
       <c r="H196" s="58"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="46">
-        <v>46325.0</v>
+      <c r="A197" s="34">
+        <v>46315.0</v>
       </c>
       <c r="B197" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C197" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D197" s="35"/>
-      <c r="E197" s="35"/>
+        <v>54</v>
+      </c>
+      <c r="C197" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D197" s="42"/>
+      <c r="E197" s="42"/>
       <c r="G197" s="57"/>
       <c r="H197" s="58"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
-      <c r="A198" s="34">
-        <v>46328.0</v>
-      </c>
-      <c r="B198" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C198" s="49">
-        <v>2200.0</v>
-      </c>
-      <c r="D198" s="42"/>
-      <c r="E198" s="42"/>
+      <c r="A198" s="46">
+        <v>46325.0</v>
+      </c>
+      <c r="B198" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C198" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D198" s="35"/>
+      <c r="E198" s="35"/>
       <c r="G198" s="57"/>
       <c r="H198" s="58"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="34">
-        <v>46332.0</v>
-      </c>
-      <c r="B199" s="43" t="s">
-        <v>60</v>
+        <v>46328.0</v>
+      </c>
+      <c r="B199" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C199" s="49">
-        <v>950.0</v>
+        <v>2200.0</v>
       </c>
       <c r="D199" s="42"/>
       <c r="E199" s="42"/>
@@ -15533,14 +15553,14 @@
       <c r="H199" s="58"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
-      <c r="A200" s="46">
-        <v>46333.0</v>
+      <c r="A200" s="34">
+        <v>46332.0</v>
       </c>
       <c r="B200" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C200" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C200" s="49">
+        <v>950.0</v>
       </c>
       <c r="D200" s="42"/>
       <c r="E200" s="42"/>
@@ -15548,14 +15568,14 @@
       <c r="H200" s="58"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
-      <c r="A201" s="34">
-        <v>46335.0</v>
-      </c>
-      <c r="B201" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="C201" s="49">
-        <v>90.0</v>
+      <c r="A201" s="46">
+        <v>46333.0</v>
+      </c>
+      <c r="B201" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C201" s="47">
+        <v>110.0</v>
       </c>
       <c r="D201" s="42"/>
       <c r="E201" s="42"/>
@@ -15564,13 +15584,13 @@
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c r="A202" s="34">
-        <v>46336.0</v>
-      </c>
-      <c r="B202" s="35" t="s">
-        <v>77</v>
+        <v>46335.0</v>
+      </c>
+      <c r="B202" s="42" t="s">
+        <v>103</v>
       </c>
       <c r="C202" s="49">
-        <v>65.0</v>
+        <v>90.0</v>
       </c>
       <c r="D202" s="42"/>
       <c r="E202" s="42"/>
@@ -15579,13 +15599,13 @@
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="34">
-        <v>46337.0</v>
-      </c>
-      <c r="B203" s="42" t="s">
-        <v>42</v>
+        <v>46336.0</v>
+      </c>
+      <c r="B203" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C203" s="49">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D203" s="42"/>
       <c r="E203" s="42"/>
@@ -15594,13 +15614,13 @@
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c r="A204" s="34">
-        <v>46338.0</v>
-      </c>
-      <c r="B204" s="43" t="s">
-        <v>64</v>
+        <v>46337.0</v>
+      </c>
+      <c r="B204" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C204" s="49">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D204" s="42"/>
       <c r="E204" s="42"/>
@@ -15611,11 +15631,11 @@
       <c r="A205" s="34">
         <v>46338.0</v>
       </c>
-      <c r="B205" s="42" t="s">
-        <v>70</v>
+      <c r="B205" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C205" s="49">
-        <v>2831.4</v>
+        <v>981.95</v>
       </c>
       <c r="D205" s="42"/>
       <c r="E205" s="42"/>
@@ -15626,11 +15646,11 @@
       <c r="A206" s="34">
         <v>46338.0</v>
       </c>
-      <c r="B206" s="43" t="s">
-        <v>56</v>
+      <c r="B206" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C206" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D206" s="42"/>
       <c r="E206" s="42"/>
@@ -15639,13 +15659,13 @@
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="34">
-        <v>46341.0</v>
+        <v>46338.0</v>
       </c>
       <c r="B207" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C207" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D207" s="42"/>
       <c r="E207" s="42"/>
@@ -15654,13 +15674,13 @@
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c r="A208" s="34">
-        <v>46346.0</v>
-      </c>
-      <c r="B208" s="35" t="s">
-        <v>36</v>
+        <v>46341.0</v>
+      </c>
+      <c r="B208" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C208" s="49">
-        <v>5750.0</v>
+        <v>132.4</v>
       </c>
       <c r="D208" s="42"/>
       <c r="E208" s="42"/>
@@ -15671,11 +15691,11 @@
       <c r="A209" s="34">
         <v>46346.0</v>
       </c>
-      <c r="B209" s="43" t="s">
-        <v>54</v>
+      <c r="B209" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C209" s="49">
-        <v>113.31</v>
+        <v>5750.0</v>
       </c>
       <c r="D209" s="42"/>
       <c r="E209" s="42"/>
@@ -15683,44 +15703,44 @@
       <c r="H209" s="58"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="A210" s="46">
-        <v>46356.0</v>
+      <c r="A210" s="34">
+        <v>46346.0</v>
       </c>
       <c r="B210" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C210" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D210" s="35"/>
-      <c r="E210" s="35"/>
+        <v>54</v>
+      </c>
+      <c r="C210" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D210" s="42"/>
+      <c r="E210" s="42"/>
       <c r="G210" s="57"/>
       <c r="H210" s="58"/>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="34">
-        <v>46358.0</v>
-      </c>
-      <c r="B211" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C211" s="49">
-        <v>1880.0</v>
-      </c>
-      <c r="D211" s="42"/>
-      <c r="E211" s="42"/>
+      <c r="A211" s="46">
+        <v>46356.0</v>
+      </c>
+      <c r="B211" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C211" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D211" s="35"/>
+      <c r="E211" s="35"/>
       <c r="G211" s="57"/>
       <c r="H211" s="58"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
       <c r="A212" s="34">
-        <v>46362.0</v>
-      </c>
-      <c r="B212" s="43" t="s">
-        <v>60</v>
+        <v>46358.0</v>
+      </c>
+      <c r="B212" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C212" s="49">
-        <v>950.0</v>
+        <v>1880.0</v>
       </c>
       <c r="D212" s="42"/>
       <c r="E212" s="42"/>
@@ -15728,14 +15748,14 @@
       <c r="H212" s="58"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c r="A213" s="46">
-        <v>46363.0</v>
+      <c r="A213" s="34">
+        <v>46362.0</v>
       </c>
       <c r="B213" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C213" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C213" s="49">
+        <v>950.0</v>
       </c>
       <c r="D213" s="42"/>
       <c r="E213" s="42"/>
@@ -15743,14 +15763,14 @@
       <c r="H213" s="58"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
-      <c r="A214" s="34">
-        <v>46365.0</v>
-      </c>
-      <c r="B214" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C214" s="49">
-        <v>530.0</v>
+      <c r="A214" s="46">
+        <v>46363.0</v>
+      </c>
+      <c r="B214" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C214" s="47">
+        <v>110.0</v>
       </c>
       <c r="D214" s="42"/>
       <c r="E214" s="42"/>
@@ -15759,13 +15779,13 @@
     </row>
     <row r="215" ht="14.25" customHeight="1">
       <c r="A215" s="34">
-        <v>46366.0</v>
-      </c>
-      <c r="B215" s="35" t="s">
-        <v>77</v>
+        <v>46365.0</v>
+      </c>
+      <c r="B215" s="42" t="s">
+        <v>66</v>
       </c>
       <c r="C215" s="49">
-        <v>65.0</v>
+        <v>530.0</v>
       </c>
       <c r="D215" s="42"/>
       <c r="E215" s="42"/>
@@ -15774,13 +15794,13 @@
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c r="A216" s="34">
-        <v>46367.0</v>
-      </c>
-      <c r="B216" s="42" t="s">
-        <v>42</v>
+        <v>46366.0</v>
+      </c>
+      <c r="B216" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C216" s="49">
-        <v>95.12</v>
+        <v>65.0</v>
       </c>
       <c r="D216" s="42"/>
       <c r="E216" s="42"/>
@@ -15792,10 +15812,10 @@
         <v>46367.0</v>
       </c>
       <c r="B217" s="42" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="C217" s="49">
-        <v>2900.0</v>
+        <v>95.12</v>
       </c>
       <c r="D217" s="42"/>
       <c r="E217" s="42"/>
@@ -15804,13 +15824,13 @@
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="34">
-        <v>46368.0</v>
-      </c>
-      <c r="B218" s="43" t="s">
-        <v>64</v>
+        <v>46367.0</v>
+      </c>
+      <c r="B218" s="42" t="s">
+        <v>105</v>
       </c>
       <c r="C218" s="49">
-        <v>981.95</v>
+        <v>2900.0</v>
       </c>
       <c r="D218" s="42"/>
       <c r="E218" s="42"/>
@@ -15821,11 +15841,11 @@
       <c r="A219" s="34">
         <v>46368.0</v>
       </c>
-      <c r="B219" s="42" t="s">
-        <v>70</v>
+      <c r="B219" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C219" s="49">
-        <v>2831.4</v>
+        <v>981.95</v>
       </c>
       <c r="D219" s="42"/>
       <c r="E219" s="42"/>
@@ -15833,14 +15853,14 @@
       <c r="H219" s="58"/>
     </row>
     <row r="220" ht="14.25" customHeight="1">
-      <c r="A220" s="46">
+      <c r="A220" s="34">
         <v>46368.0</v>
       </c>
-      <c r="B220" s="43" t="s">
-        <v>56</v>
+      <c r="B220" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C220" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D220" s="42"/>
       <c r="E220" s="42"/>
@@ -15848,14 +15868,14 @@
       <c r="H220" s="58"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
-      <c r="A221" s="34">
-        <v>46371.0</v>
+      <c r="A221" s="46">
+        <v>46368.0</v>
       </c>
       <c r="B221" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C221" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D221" s="42"/>
       <c r="E221" s="42"/>
@@ -15864,13 +15884,13 @@
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c r="A222" s="34">
-        <v>46376.0</v>
-      </c>
-      <c r="B222" s="35" t="s">
-        <v>36</v>
+        <v>46371.0</v>
+      </c>
+      <c r="B222" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C222" s="49">
-        <v>6250.0</v>
+        <v>132.4</v>
       </c>
       <c r="D222" s="42"/>
       <c r="E222" s="42"/>
@@ -15878,14 +15898,14 @@
       <c r="H222" s="58"/>
     </row>
     <row r="223" ht="14.25" customHeight="1">
-      <c r="A223" s="46">
+      <c r="A223" s="34">
         <v>46376.0</v>
       </c>
-      <c r="B223" s="43" t="s">
-        <v>54</v>
+      <c r="B223" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C223" s="49">
-        <v>113.31</v>
+        <v>6250.0</v>
       </c>
       <c r="D223" s="42"/>
       <c r="E223" s="42"/>
@@ -15893,14 +15913,14 @@
       <c r="H223" s="58"/>
     </row>
     <row r="224" ht="14.25" customHeight="1">
-      <c r="A224" s="34">
-        <v>46389.0</v>
-      </c>
-      <c r="B224" s="42" t="s">
-        <v>40</v>
+      <c r="A224" s="46">
+        <v>46376.0</v>
+      </c>
+      <c r="B224" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C224" s="49">
-        <v>2000.0</v>
+        <v>113.31</v>
       </c>
       <c r="D224" s="42"/>
       <c r="E224" s="42"/>
@@ -15909,13 +15929,13 @@
     </row>
     <row r="225" ht="14.25" customHeight="1">
       <c r="A225" s="34">
-        <v>46393.0</v>
-      </c>
-      <c r="B225" s="43" t="s">
-        <v>60</v>
+        <v>46389.0</v>
+      </c>
+      <c r="B225" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C225" s="49">
-        <v>950.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D225" s="42"/>
       <c r="E225" s="42"/>
@@ -15923,14 +15943,14 @@
       <c r="H225" s="58"/>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="46">
-        <v>46394.0</v>
+      <c r="A226" s="34">
+        <v>46393.0</v>
       </c>
       <c r="B226" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C226" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C226" s="49">
+        <v>950.0</v>
       </c>
       <c r="D226" s="42"/>
       <c r="E226" s="42"/>
@@ -15938,14 +15958,14 @@
       <c r="H226" s="58"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
-      <c r="A227" s="34">
-        <v>46397.0</v>
-      </c>
-      <c r="B227" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C227" s="49">
-        <v>65.0</v>
+      <c r="A227" s="46">
+        <v>46394.0</v>
+      </c>
+      <c r="B227" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C227" s="47">
+        <v>110.0</v>
       </c>
       <c r="D227" s="42"/>
       <c r="E227" s="42"/>
@@ -15954,13 +15974,13 @@
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c r="A228" s="34">
-        <v>46398.0</v>
-      </c>
-      <c r="B228" s="42" t="s">
-        <v>42</v>
+        <v>46397.0</v>
+      </c>
+      <c r="B228" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C228" s="49">
-        <v>105.37</v>
+        <v>65.0</v>
       </c>
       <c r="D228" s="42"/>
       <c r="E228" s="42"/>
@@ -15969,13 +15989,13 @@
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c r="A229" s="34">
-        <v>46399.0</v>
-      </c>
-      <c r="B229" s="43" t="s">
-        <v>64</v>
+        <v>46398.0</v>
+      </c>
+      <c r="B229" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C229" s="49">
-        <v>983.13</v>
+        <v>105.37</v>
       </c>
       <c r="D229" s="42"/>
       <c r="E229" s="42"/>
@@ -15987,10 +16007,10 @@
         <v>46399.0</v>
       </c>
       <c r="B230" s="43" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C230" s="49">
-        <v>50.0</v>
+        <v>983.13</v>
       </c>
       <c r="D230" s="42"/>
       <c r="E230" s="42"/>
@@ -15999,13 +16019,13 @@
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c r="A231" s="34">
-        <v>46402.0</v>
+        <v>46399.0</v>
       </c>
       <c r="B231" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C231" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D231" s="42"/>
       <c r="E231" s="42"/>
@@ -16014,13 +16034,13 @@
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c r="A232" s="34">
-        <v>46407.0</v>
-      </c>
-      <c r="B232" s="35" t="s">
-        <v>36</v>
+        <v>46402.0</v>
+      </c>
+      <c r="B232" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C232" s="49">
-        <v>7796.0</v>
+        <v>132.4</v>
       </c>
       <c r="D232" s="42"/>
       <c r="E232" s="42"/>
@@ -16031,11 +16051,11 @@
       <c r="A233" s="34">
         <v>46407.0</v>
       </c>
-      <c r="B233" s="43" t="s">
-        <v>54</v>
+      <c r="B233" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C233" s="49">
-        <v>102.36</v>
+        <v>7796.0</v>
       </c>
       <c r="D233" s="42"/>
       <c r="E233" s="42"/>
@@ -16044,13 +16064,13 @@
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c r="A234" s="34">
-        <v>46420.0</v>
-      </c>
-      <c r="B234" s="42" t="s">
-        <v>40</v>
+        <v>46407.0</v>
+      </c>
+      <c r="B234" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C234" s="49">
-        <v>1800.0</v>
+        <v>102.36</v>
       </c>
       <c r="D234" s="42"/>
       <c r="E234" s="42"/>
@@ -16059,13 +16079,13 @@
     </row>
     <row r="235" ht="14.25" customHeight="1">
       <c r="A235" s="34">
-        <v>46424.0</v>
-      </c>
-      <c r="B235" s="43" t="s">
-        <v>60</v>
+        <v>46420.0</v>
+      </c>
+      <c r="B235" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C235" s="49">
-        <v>950.0</v>
+        <v>1800.0</v>
       </c>
       <c r="D235" s="42"/>
       <c r="E235" s="42"/>
@@ -16073,14 +16093,14 @@
       <c r="H235" s="58"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="46">
-        <v>46425.0</v>
+      <c r="A236" s="34">
+        <v>46424.0</v>
       </c>
       <c r="B236" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C236" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C236" s="49">
+        <v>950.0</v>
       </c>
       <c r="D236" s="42"/>
       <c r="E236" s="42"/>
@@ -16088,14 +16108,14 @@
       <c r="H236" s="58"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
-      <c r="A237" s="34">
-        <v>46428.0</v>
-      </c>
-      <c r="B237" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C237" s="49">
-        <v>65.0</v>
+      <c r="A237" s="46">
+        <v>46425.0</v>
+      </c>
+      <c r="B237" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C237" s="47">
+        <v>110.0</v>
       </c>
       <c r="D237" s="42"/>
       <c r="E237" s="42"/>
@@ -16106,11 +16126,11 @@
       <c r="A238" s="34">
         <v>46428.0</v>
       </c>
-      <c r="B238" s="42" t="s">
-        <v>66</v>
+      <c r="B238" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C238" s="49">
-        <v>530.0</v>
+        <v>65.0</v>
       </c>
       <c r="D238" s="42"/>
       <c r="E238" s="42"/>
@@ -16119,13 +16139,13 @@
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c r="A239" s="34">
-        <v>46429.0</v>
+        <v>46428.0</v>
       </c>
       <c r="B239" s="42" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C239" s="49">
-        <v>95.12</v>
+        <v>530.0</v>
       </c>
       <c r="D239" s="42"/>
       <c r="E239" s="42"/>
@@ -16134,13 +16154,13 @@
     </row>
     <row r="240" ht="14.25" customHeight="1">
       <c r="A240" s="34">
-        <v>46430.0</v>
-      </c>
-      <c r="B240" s="43" t="s">
-        <v>64</v>
+        <v>46429.0</v>
+      </c>
+      <c r="B240" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C240" s="49">
-        <v>981.95</v>
+        <v>95.12</v>
       </c>
       <c r="D240" s="42"/>
       <c r="E240" s="42"/>
@@ -16151,11 +16171,11 @@
       <c r="A241" s="34">
         <v>46430.0</v>
       </c>
-      <c r="B241" s="42" t="s">
-        <v>70</v>
+      <c r="B241" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C241" s="49">
-        <v>2831.4</v>
+        <v>981.95</v>
       </c>
       <c r="D241" s="42"/>
       <c r="E241" s="42"/>
@@ -16167,10 +16187,10 @@
         <v>46430.0</v>
       </c>
       <c r="B242" s="42" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C242" s="49">
-        <v>1407.65</v>
+        <v>2831.4</v>
       </c>
       <c r="D242" s="42"/>
       <c r="E242" s="42"/>
@@ -16178,44 +16198,44 @@
       <c r="H242" s="58"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="46">
+      <c r="A243" s="34">
         <v>46430.0</v>
       </c>
-      <c r="B243" s="43" t="s">
-        <v>56</v>
+      <c r="B243" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="C243" s="49">
-        <v>50.0</v>
+        <v>1407.65</v>
       </c>
       <c r="D243" s="42"/>
-      <c r="E243" s="35"/>
+      <c r="E243" s="42"/>
       <c r="G243" s="57"/>
       <c r="H243" s="58"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="34">
-        <v>46433.0</v>
+      <c r="A244" s="46">
+        <v>46430.0</v>
       </c>
       <c r="B244" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C244" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D244" s="42"/>
-      <c r="E244" s="42"/>
+      <c r="E244" s="35"/>
       <c r="G244" s="57"/>
       <c r="H244" s="58"/>
     </row>
     <row r="245" ht="14.25" customHeight="1">
       <c r="A245" s="34">
-        <v>46437.0</v>
-      </c>
-      <c r="B245" s="42" t="s">
-        <v>71</v>
+        <v>46433.0</v>
+      </c>
+      <c r="B245" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C245" s="49">
-        <v>460.0</v>
+        <v>132.4</v>
       </c>
       <c r="D245" s="42"/>
       <c r="E245" s="42"/>
@@ -16224,13 +16244,13 @@
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c r="A246" s="34">
-        <v>46438.0</v>
-      </c>
-      <c r="B246" s="35" t="s">
-        <v>36</v>
+        <v>46437.0</v>
+      </c>
+      <c r="B246" s="42" t="s">
+        <v>71</v>
       </c>
       <c r="C246" s="49">
-        <v>6004.07</v>
+        <v>460.0</v>
       </c>
       <c r="D246" s="42"/>
       <c r="E246" s="42"/>
@@ -16238,14 +16258,14 @@
       <c r="H246" s="58"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="46">
+      <c r="A247" s="34">
         <v>46438.0</v>
       </c>
-      <c r="B247" s="43" t="s">
-        <v>54</v>
+      <c r="B247" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C247" s="49">
-        <v>113.31</v>
+        <v>6004.07</v>
       </c>
       <c r="D247" s="42"/>
       <c r="E247" s="42"/>
@@ -16253,14 +16273,14 @@
       <c r="H247" s="58"/>
     </row>
     <row r="248" ht="14.25" customHeight="1">
-      <c r="A248" s="34">
-        <v>46448.0</v>
-      </c>
-      <c r="B248" s="42" t="s">
-        <v>40</v>
+      <c r="A248" s="46">
+        <v>46438.0</v>
+      </c>
+      <c r="B248" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C248" s="49">
-        <v>1771.95</v>
+        <v>113.31</v>
       </c>
       <c r="D248" s="42"/>
       <c r="E248" s="42"/>
@@ -16269,13 +16289,13 @@
     </row>
     <row r="249" ht="14.25" customHeight="1">
       <c r="A249" s="34">
-        <v>46451.0</v>
+        <v>46448.0</v>
       </c>
       <c r="B249" s="42" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C249" s="49">
-        <v>81.8</v>
+        <v>1771.95</v>
       </c>
       <c r="D249" s="42"/>
       <c r="E249" s="42"/>
@@ -16284,13 +16304,13 @@
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="34">
-        <v>46452.0</v>
-      </c>
-      <c r="B250" s="43" t="s">
-        <v>60</v>
+        <v>46451.0</v>
+      </c>
+      <c r="B250" s="42" t="s">
+        <v>76</v>
       </c>
       <c r="C250" s="49">
-        <v>950.0</v>
+        <v>81.8</v>
       </c>
       <c r="D250" s="42"/>
       <c r="E250" s="42"/>
@@ -16298,14 +16318,14 @@
       <c r="H250" s="58"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="46">
-        <v>46453.0</v>
+      <c r="A251" s="34">
+        <v>46452.0</v>
       </c>
       <c r="B251" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C251" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C251" s="49">
+        <v>950.0</v>
       </c>
       <c r="D251" s="42"/>
       <c r="E251" s="42"/>
@@ -16313,14 +16333,14 @@
       <c r="H251" s="58"/>
     </row>
     <row r="252" ht="14.25" customHeight="1">
-      <c r="A252" s="34">
-        <v>46456.0</v>
-      </c>
-      <c r="B252" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C252" s="49">
-        <v>1336.73</v>
+      <c r="A252" s="46">
+        <v>46453.0</v>
+      </c>
+      <c r="B252" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C252" s="47">
+        <v>110.0</v>
       </c>
       <c r="D252" s="42"/>
       <c r="E252" s="42"/>
@@ -16332,10 +16352,10 @@
         <v>46456.0</v>
       </c>
       <c r="B253" s="35" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C253" s="49">
-        <v>65.0</v>
+        <v>1336.73</v>
       </c>
       <c r="D253" s="42"/>
       <c r="E253" s="42"/>
@@ -16344,13 +16364,13 @@
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c r="A254" s="34">
-        <v>46457.0</v>
-      </c>
-      <c r="B254" s="42" t="s">
-        <v>42</v>
+        <v>46456.0</v>
+      </c>
+      <c r="B254" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C254" s="49">
-        <v>86.15</v>
+        <v>65.0</v>
       </c>
       <c r="D254" s="42"/>
       <c r="E254" s="42"/>
@@ -16359,13 +16379,13 @@
     </row>
     <row r="255" ht="14.25" customHeight="1">
       <c r="A255" s="34">
-        <v>46458.0</v>
-      </c>
-      <c r="B255" s="43" t="s">
-        <v>64</v>
+        <v>46457.0</v>
+      </c>
+      <c r="B255" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C255" s="49">
-        <v>981.22</v>
+        <v>86.15</v>
       </c>
       <c r="D255" s="42"/>
       <c r="E255" s="42"/>
@@ -16376,11 +16396,11 @@
       <c r="A256" s="34">
         <v>46458.0</v>
       </c>
-      <c r="B256" s="42" t="s">
-        <v>70</v>
+      <c r="B256" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C256" s="49">
-        <v>2831.4</v>
+        <v>981.22</v>
       </c>
       <c r="D256" s="42"/>
       <c r="E256" s="42"/>
@@ -16391,11 +16411,11 @@
       <c r="A257" s="34">
         <v>46458.0</v>
       </c>
-      <c r="B257" s="43" t="s">
-        <v>56</v>
+      <c r="B257" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C257" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D257" s="42"/>
       <c r="E257" s="42"/>
@@ -16404,13 +16424,13 @@
     </row>
     <row r="258" ht="14.25" customHeight="1">
       <c r="A258" s="34">
-        <v>46461.0</v>
+        <v>46458.0</v>
       </c>
       <c r="B258" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C258" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D258" s="42"/>
       <c r="E258" s="42"/>
@@ -16419,13 +16439,13 @@
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c r="A259" s="34">
-        <v>46466.0</v>
-      </c>
-      <c r="B259" s="35" t="s">
-        <v>36</v>
+        <v>46461.0</v>
+      </c>
+      <c r="B259" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="C259" s="49">
-        <v>7494.55</v>
+        <v>132.4</v>
       </c>
       <c r="D259" s="42"/>
       <c r="E259" s="42"/>
@@ -16436,11 +16456,11 @@
       <c r="A260" s="34">
         <v>46466.0</v>
       </c>
-      <c r="B260" s="43" t="s">
-        <v>54</v>
+      <c r="B260" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C260" s="49">
-        <v>87.84</v>
+        <v>7494.55</v>
       </c>
       <c r="D260" s="42"/>
       <c r="E260" s="42"/>
@@ -16449,13 +16469,13 @@
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c r="A261" s="34">
-        <v>46477.0</v>
-      </c>
-      <c r="B261" s="42" t="s">
-        <v>80</v>
+        <v>46466.0</v>
+      </c>
+      <c r="B261" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C261" s="49">
-        <v>35.62</v>
+        <v>87.84</v>
       </c>
       <c r="D261" s="42"/>
       <c r="E261" s="42"/>
@@ -16464,13 +16484,13 @@
     </row>
     <row r="262" ht="14.25" customHeight="1">
       <c r="A262" s="34">
-        <v>46479.0</v>
+        <v>46477.0</v>
       </c>
       <c r="B262" s="42" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C262" s="49">
-        <v>5310.25</v>
+        <v>35.62</v>
       </c>
       <c r="D262" s="42"/>
       <c r="E262" s="42"/>
@@ -16479,13 +16499,13 @@
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c r="A263" s="34">
-        <v>46483.0</v>
-      </c>
-      <c r="B263" s="43" t="s">
-        <v>60</v>
+        <v>46479.0</v>
+      </c>
+      <c r="B263" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="C263" s="49">
-        <v>950.0</v>
+        <v>5310.25</v>
       </c>
       <c r="D263" s="42"/>
       <c r="E263" s="42"/>
@@ -16493,14 +16513,14 @@
       <c r="H263" s="58"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="46">
-        <v>46484.0</v>
+      <c r="A264" s="34">
+        <v>46483.0</v>
       </c>
       <c r="B264" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C264" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C264" s="49">
+        <v>950.0</v>
       </c>
       <c r="D264" s="42"/>
       <c r="E264" s="42"/>
@@ -16508,14 +16528,14 @@
       <c r="H264" s="58"/>
     </row>
     <row r="265" ht="14.25" customHeight="1">
-      <c r="A265" s="34">
-        <v>46487.0</v>
-      </c>
-      <c r="B265" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C265" s="49">
-        <v>65.0</v>
+      <c r="A265" s="46">
+        <v>46484.0</v>
+      </c>
+      <c r="B265" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C265" s="47">
+        <v>110.0</v>
       </c>
       <c r="D265" s="42"/>
       <c r="E265" s="42"/>
@@ -16524,13 +16544,13 @@
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c r="A266" s="34">
-        <v>46488.0</v>
-      </c>
-      <c r="B266" s="42" t="s">
-        <v>42</v>
+        <v>46487.0</v>
+      </c>
+      <c r="B266" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="C266" s="49">
-        <v>98.98</v>
+        <v>65.0</v>
       </c>
       <c r="D266" s="42"/>
       <c r="E266" s="42"/>
@@ -16539,13 +16559,13 @@
     </row>
     <row r="267" ht="14.25" customHeight="1">
       <c r="A267" s="34">
-        <v>46489.0</v>
-      </c>
-      <c r="B267" s="43" t="s">
-        <v>64</v>
+        <v>46488.0</v>
+      </c>
+      <c r="B267" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C267" s="49">
-        <v>981.22</v>
+        <v>98.98</v>
       </c>
       <c r="D267" s="42"/>
       <c r="E267" s="42"/>
@@ -16556,11 +16576,11 @@
       <c r="A268" s="34">
         <v>46489.0</v>
       </c>
-      <c r="B268" s="42" t="s">
-        <v>70</v>
+      <c r="B268" s="43" t="s">
+        <v>64</v>
       </c>
       <c r="C268" s="49">
-        <v>2831.4</v>
+        <v>981.22</v>
       </c>
       <c r="D268" s="42"/>
       <c r="E268" s="42"/>
@@ -16568,14 +16588,14 @@
       <c r="H268" s="58"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="46">
+      <c r="A269" s="34">
         <v>46489.0</v>
       </c>
-      <c r="B269" s="43" t="s">
-        <v>56</v>
+      <c r="B269" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="C269" s="49">
-        <v>50.0</v>
+        <v>2831.4</v>
       </c>
       <c r="D269" s="42"/>
       <c r="E269" s="42"/>
@@ -16583,14 +16603,14 @@
       <c r="H269" s="58"/>
     </row>
     <row r="270" ht="14.25" customHeight="1">
-      <c r="A270" s="34">
-        <v>46492.0</v>
+      <c r="A270" s="46">
+        <v>46489.0</v>
       </c>
       <c r="B270" s="43" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C270" s="49">
-        <v>132.4</v>
+        <v>50.0</v>
       </c>
       <c r="D270" s="42"/>
       <c r="E270" s="42"/>
@@ -16599,13 +16619,13 @@
     </row>
     <row r="271" ht="14.25" customHeight="1">
       <c r="A271" s="34">
-        <v>46497.0</v>
-      </c>
-      <c r="B271" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C271" s="47">
-        <v>6350.0</v>
+        <v>46492.0</v>
+      </c>
+      <c r="B271" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C271" s="49">
+        <v>132.4</v>
       </c>
       <c r="D271" s="42"/>
       <c r="E271" s="42"/>
@@ -16613,14 +16633,14 @@
       <c r="H271" s="58"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
-      <c r="A272" s="46">
+      <c r="A272" s="34">
         <v>46497.0</v>
       </c>
-      <c r="B272" s="43" t="s">
-        <v>54</v>
+      <c r="B272" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C272" s="47">
-        <v>113.8</v>
+        <v>6350.0</v>
       </c>
       <c r="D272" s="42"/>
       <c r="E272" s="42"/>
@@ -16629,13 +16649,13 @@
     </row>
     <row r="273" ht="14.25" customHeight="1">
       <c r="A273" s="46">
-        <v>46507.0</v>
-      </c>
-      <c r="B273" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C273" s="49">
-        <v>530.0</v>
+        <v>46497.0</v>
+      </c>
+      <c r="B273" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C273" s="47">
+        <v>113.8</v>
       </c>
       <c r="D273" s="42"/>
       <c r="E273" s="42"/>
@@ -16643,14 +16663,14 @@
       <c r="H273" s="58"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
-      <c r="A274" s="34">
-        <v>46509.0</v>
+      <c r="A274" s="46">
+        <v>46507.0</v>
       </c>
       <c r="B274" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C274" s="47">
-        <v>3452.5</v>
+        <v>66</v>
+      </c>
+      <c r="C274" s="49">
+        <v>530.0</v>
       </c>
       <c r="D274" s="42"/>
       <c r="E274" s="42"/>
@@ -16659,13 +16679,13 @@
     </row>
     <row r="275" ht="14.25" customHeight="1">
       <c r="A275" s="34">
-        <v>46513.0</v>
-      </c>
-      <c r="B275" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C275" s="49">
-        <v>950.0</v>
+        <v>46509.0</v>
+      </c>
+      <c r="B275" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C275" s="47">
+        <v>3452.5</v>
       </c>
       <c r="D275" s="42"/>
       <c r="E275" s="42"/>
@@ -16673,14 +16693,14 @@
       <c r="H275" s="58"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
-      <c r="A276" s="46">
-        <v>46514.0</v>
+      <c r="A276" s="34">
+        <v>46513.0</v>
       </c>
       <c r="B276" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C276" s="47">
-        <v>110.0</v>
+        <v>60</v>
+      </c>
+      <c r="C276" s="49">
+        <v>950.0</v>
       </c>
       <c r="D276" s="42"/>
       <c r="E276" s="42"/>
@@ -16688,14 +16708,14 @@
       <c r="H276" s="58"/>
     </row>
     <row r="277" ht="14.25" customHeight="1">
-      <c r="A277" s="34">
-        <v>46517.0</v>
-      </c>
-      <c r="B277" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C277" s="49">
-        <v>65.0</v>
+      <c r="A277" s="46">
+        <v>46514.0</v>
+      </c>
+      <c r="B277" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C277" s="47">
+        <v>110.0</v>
       </c>
       <c r="D277" s="42"/>
       <c r="E277" s="42"/>
@@ -16704,13 +16724,13 @@
     </row>
     <row r="278" ht="14.25" customHeight="1">
       <c r="A278" s="34">
-        <v>46518.0</v>
-      </c>
-      <c r="B278" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C278" s="47">
-        <v>98.88</v>
+        <v>46517.0</v>
+      </c>
+      <c r="B278" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C278" s="49">
+        <v>65.0</v>
       </c>
       <c r="D278" s="42"/>
       <c r="E278" s="42"/>
@@ -16719,13 +16739,13 @@
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c r="A279" s="34">
-        <v>46519.0</v>
-      </c>
-      <c r="B279" s="43" t="s">
-        <v>64</v>
+        <v>46518.0</v>
+      </c>
+      <c r="B279" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C279" s="47">
-        <v>980.86</v>
+        <v>98.88</v>
       </c>
       <c r="D279" s="42"/>
       <c r="E279" s="42"/>
@@ -16734,13 +16754,13 @@
     </row>
     <row r="280" ht="14.25" customHeight="1">
       <c r="A280" s="34">
-        <v>46522.0</v>
+        <v>46519.0</v>
       </c>
       <c r="B280" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C280" s="49">
-        <v>132.4</v>
+        <v>64</v>
+      </c>
+      <c r="C280" s="47">
+        <v>980.86</v>
       </c>
       <c r="D280" s="42"/>
       <c r="E280" s="42"/>
@@ -16749,13 +16769,13 @@
     </row>
     <row r="281" ht="14.25" customHeight="1">
       <c r="A281" s="34">
-        <v>46527.0</v>
-      </c>
-      <c r="B281" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C281" s="47">
-        <v>5372.0</v>
+        <v>46522.0</v>
+      </c>
+      <c r="B281" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C281" s="49">
+        <v>132.4</v>
       </c>
       <c r="D281" s="42"/>
       <c r="E281" s="42"/>
@@ -16763,14 +16783,14 @@
       <c r="H281" s="58"/>
     </row>
     <row r="282" ht="14.25" customHeight="1">
-      <c r="A282" s="46">
+      <c r="A282" s="34">
         <v>46527.0</v>
       </c>
-      <c r="B282" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C282" s="49">
-        <v>113.31</v>
+      <c r="B282" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C282" s="47">
+        <v>5372.0</v>
       </c>
       <c r="D282" s="42"/>
       <c r="E282" s="42"/>
@@ -16778,1018 +16798,1029 @@
       <c r="H282" s="58"/>
     </row>
     <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="60"/>
-      <c r="B283" s="61"/>
-      <c r="C283" s="62"/>
+      <c r="A283" s="46">
+        <v>46527.0</v>
+      </c>
+      <c r="B283" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C283" s="49">
+        <v>113.31</v>
+      </c>
+      <c r="D283" s="42"/>
+      <c r="E283" s="42"/>
       <c r="G283" s="57"/>
       <c r="H283" s="58"/>
     </row>
     <row r="284" ht="14.25" customHeight="1">
-      <c r="A284" s="60"/>
-      <c r="B284" s="61"/>
-      <c r="C284" s="62"/>
+      <c r="A284" s="61"/>
+      <c r="B284" s="62"/>
+      <c r="C284" s="63"/>
       <c r="G284" s="57"/>
       <c r="H284" s="58"/>
     </row>
     <row r="285" ht="14.25" customHeight="1">
-      <c r="A285" s="60"/>
-      <c r="B285" s="61"/>
-      <c r="C285" s="62"/>
+      <c r="A285" s="61"/>
+      <c r="B285" s="62"/>
+      <c r="C285" s="63"/>
       <c r="G285" s="57"/>
       <c r="H285" s="58"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="60"/>
-      <c r="B286" s="61"/>
-      <c r="C286" s="62"/>
+      <c r="A286" s="61"/>
+      <c r="B286" s="62"/>
+      <c r="C286" s="63"/>
       <c r="G286" s="57"/>
       <c r="H286" s="58"/>
     </row>
     <row r="287" ht="14.25" customHeight="1">
-      <c r="A287" s="60"/>
-      <c r="B287" s="61"/>
-      <c r="C287" s="62"/>
+      <c r="A287" s="61"/>
+      <c r="B287" s="62"/>
+      <c r="C287" s="63"/>
       <c r="G287" s="57"/>
       <c r="H287" s="58"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c r="A288" s="60"/>
-      <c r="B288" s="61"/>
-      <c r="C288" s="62"/>
+      <c r="A288" s="61"/>
+      <c r="B288" s="62"/>
+      <c r="C288" s="63"/>
       <c r="G288" s="57"/>
       <c r="H288" s="58"/>
     </row>
     <row r="289" ht="14.25" customHeight="1">
-      <c r="A289" s="60"/>
-      <c r="B289" s="61"/>
-      <c r="C289" s="62"/>
+      <c r="A289" s="61"/>
+      <c r="B289" s="62"/>
+      <c r="C289" s="63"/>
       <c r="G289" s="57"/>
       <c r="H289" s="58"/>
     </row>
     <row r="290" ht="14.25" customHeight="1">
-      <c r="A290" s="60"/>
-      <c r="B290" s="61"/>
-      <c r="C290" s="62"/>
+      <c r="A290" s="61"/>
+      <c r="B290" s="62"/>
+      <c r="C290" s="63"/>
       <c r="G290" s="57"/>
       <c r="H290" s="58"/>
     </row>
     <row r="291" ht="14.25" customHeight="1">
-      <c r="A291" s="60"/>
-      <c r="B291" s="61"/>
-      <c r="C291" s="62"/>
+      <c r="A291" s="61"/>
+      <c r="B291" s="62"/>
+      <c r="C291" s="63"/>
       <c r="G291" s="57"/>
       <c r="H291" s="58"/>
     </row>
     <row r="292" ht="14.25" customHeight="1">
-      <c r="A292" s="60"/>
-      <c r="B292" s="61"/>
-      <c r="C292" s="62"/>
+      <c r="A292" s="61"/>
+      <c r="B292" s="62"/>
+      <c r="C292" s="63"/>
       <c r="G292" s="57"/>
       <c r="H292" s="58"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="60"/>
-      <c r="B293" s="61"/>
-      <c r="C293" s="62"/>
+      <c r="A293" s="61"/>
+      <c r="B293" s="62"/>
+      <c r="C293" s="63"/>
       <c r="G293" s="57"/>
       <c r="H293" s="58"/>
     </row>
     <row r="294" ht="14.25" customHeight="1">
-      <c r="A294" s="60"/>
-      <c r="B294" s="61"/>
-      <c r="C294" s="62"/>
+      <c r="A294" s="61"/>
+      <c r="B294" s="62"/>
+      <c r="C294" s="63"/>
       <c r="G294" s="57"/>
       <c r="H294" s="58"/>
     </row>
     <row r="295" ht="14.25" customHeight="1">
-      <c r="A295" s="60"/>
-      <c r="B295" s="61"/>
-      <c r="C295" s="62"/>
+      <c r="A295" s="61"/>
+      <c r="B295" s="62"/>
+      <c r="C295" s="63"/>
       <c r="G295" s="57"/>
       <c r="H295" s="58"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="60"/>
-      <c r="B296" s="61"/>
-      <c r="C296" s="62"/>
+      <c r="A296" s="61"/>
+      <c r="B296" s="62"/>
+      <c r="C296" s="63"/>
       <c r="G296" s="57"/>
       <c r="H296" s="58"/>
     </row>
     <row r="297" ht="14.25" customHeight="1">
-      <c r="A297" s="60"/>
-      <c r="B297" s="61"/>
-      <c r="C297" s="62"/>
+      <c r="A297" s="61"/>
+      <c r="B297" s="62"/>
+      <c r="C297" s="63"/>
       <c r="G297" s="57"/>
       <c r="H297" s="58"/>
     </row>
     <row r="298" ht="14.25" customHeight="1">
-      <c r="A298" s="60"/>
-      <c r="B298" s="61"/>
-      <c r="C298" s="62"/>
+      <c r="A298" s="61"/>
+      <c r="B298" s="62"/>
+      <c r="C298" s="63"/>
       <c r="G298" s="57"/>
       <c r="H298" s="58"/>
     </row>
     <row r="299" ht="14.25" customHeight="1">
-      <c r="A299" s="60"/>
-      <c r="B299" s="61"/>
-      <c r="C299" s="62"/>
+      <c r="A299" s="61"/>
+      <c r="B299" s="62"/>
+      <c r="C299" s="63"/>
       <c r="G299" s="57"/>
       <c r="H299" s="58"/>
     </row>
     <row r="300" ht="14.25" customHeight="1">
-      <c r="A300" s="60"/>
-      <c r="B300" s="61"/>
-      <c r="C300" s="62"/>
+      <c r="A300" s="61"/>
+      <c r="B300" s="62"/>
+      <c r="C300" s="63"/>
       <c r="G300" s="57"/>
       <c r="H300" s="58"/>
     </row>
     <row r="301" ht="14.25" customHeight="1">
-      <c r="A301" s="60"/>
-      <c r="B301" s="61"/>
-      <c r="C301" s="62"/>
+      <c r="A301" s="61"/>
+      <c r="B301" s="62"/>
+      <c r="C301" s="63"/>
       <c r="G301" s="57"/>
       <c r="H301" s="58"/>
     </row>
     <row r="302" ht="14.25" customHeight="1">
-      <c r="A302" s="60"/>
-      <c r="B302" s="61"/>
-      <c r="C302" s="62"/>
+      <c r="A302" s="61"/>
+      <c r="B302" s="62"/>
+      <c r="C302" s="63"/>
       <c r="G302" s="57"/>
       <c r="H302" s="58"/>
     </row>
     <row r="303" ht="14.25" customHeight="1">
-      <c r="A303" s="60"/>
-      <c r="B303" s="61"/>
-      <c r="C303" s="62"/>
+      <c r="A303" s="61"/>
+      <c r="B303" s="62"/>
+      <c r="C303" s="63"/>
       <c r="G303" s="57"/>
       <c r="H303" s="58"/>
     </row>
     <row r="304" ht="14.25" customHeight="1">
-      <c r="A304" s="60"/>
-      <c r="B304" s="61"/>
-      <c r="C304" s="62"/>
+      <c r="A304" s="61"/>
+      <c r="B304" s="62"/>
+      <c r="C304" s="63"/>
       <c r="G304" s="57"/>
       <c r="H304" s="58"/>
     </row>
     <row r="305" ht="14.25" customHeight="1">
-      <c r="A305" s="60"/>
-      <c r="B305" s="61"/>
-      <c r="C305" s="62"/>
+      <c r="A305" s="61"/>
+      <c r="B305" s="62"/>
+      <c r="C305" s="63"/>
       <c r="G305" s="57"/>
       <c r="H305" s="58"/>
     </row>
     <row r="306" ht="14.25" customHeight="1">
-      <c r="A306" s="60"/>
-      <c r="B306" s="61"/>
-      <c r="C306" s="62"/>
+      <c r="A306" s="61"/>
+      <c r="B306" s="62"/>
+      <c r="C306" s="63"/>
       <c r="G306" s="57"/>
       <c r="H306" s="58"/>
     </row>
     <row r="307" ht="14.25" customHeight="1">
-      <c r="A307" s="60"/>
-      <c r="B307" s="61"/>
-      <c r="C307" s="62"/>
+      <c r="A307" s="61"/>
+      <c r="B307" s="62"/>
+      <c r="C307" s="63"/>
       <c r="G307" s="57"/>
       <c r="H307" s="58"/>
     </row>
     <row r="308" ht="14.25" customHeight="1">
-      <c r="A308" s="60"/>
-      <c r="B308" s="61"/>
-      <c r="C308" s="62"/>
+      <c r="A308" s="61"/>
+      <c r="B308" s="62"/>
+      <c r="C308" s="63"/>
       <c r="G308" s="57"/>
       <c r="H308" s="58"/>
     </row>
     <row r="309" ht="14.25" customHeight="1">
-      <c r="A309" s="60"/>
-      <c r="B309" s="61"/>
-      <c r="C309" s="62"/>
+      <c r="A309" s="61"/>
+      <c r="B309" s="62"/>
+      <c r="C309" s="63"/>
       <c r="G309" s="57"/>
       <c r="H309" s="58"/>
     </row>
     <row r="310" ht="14.25" customHeight="1">
-      <c r="A310" s="60"/>
-      <c r="B310" s="61"/>
-      <c r="C310" s="62"/>
+      <c r="A310" s="61"/>
+      <c r="B310" s="62"/>
+      <c r="C310" s="63"/>
       <c r="G310" s="57"/>
       <c r="H310" s="58"/>
     </row>
     <row r="311" ht="14.25" customHeight="1">
-      <c r="A311" s="60"/>
-      <c r="B311" s="61"/>
-      <c r="C311" s="62"/>
+      <c r="A311" s="61"/>
+      <c r="B311" s="62"/>
+      <c r="C311" s="63"/>
       <c r="G311" s="57"/>
       <c r="H311" s="58"/>
     </row>
     <row r="312" ht="14.25" customHeight="1">
-      <c r="A312" s="60"/>
-      <c r="B312" s="61"/>
-      <c r="C312" s="62"/>
+      <c r="A312" s="61"/>
+      <c r="B312" s="62"/>
+      <c r="C312" s="63"/>
       <c r="G312" s="57"/>
       <c r="H312" s="58"/>
     </row>
     <row r="313" ht="14.25" customHeight="1">
-      <c r="A313" s="60"/>
-      <c r="B313" s="61"/>
-      <c r="C313" s="62"/>
+      <c r="A313" s="61"/>
+      <c r="B313" s="62"/>
+      <c r="C313" s="63"/>
       <c r="G313" s="57"/>
       <c r="H313" s="58"/>
     </row>
     <row r="314" ht="14.25" customHeight="1">
-      <c r="A314" s="60"/>
-      <c r="B314" s="61"/>
-      <c r="C314" s="62"/>
+      <c r="A314" s="61"/>
+      <c r="B314" s="62"/>
+      <c r="C314" s="63"/>
       <c r="G314" s="57"/>
       <c r="H314" s="58"/>
     </row>
     <row r="315" ht="14.25" customHeight="1">
-      <c r="A315" s="60"/>
-      <c r="B315" s="61"/>
-      <c r="C315" s="62"/>
+      <c r="A315" s="61"/>
+      <c r="B315" s="62"/>
+      <c r="C315" s="63"/>
       <c r="G315" s="57"/>
       <c r="H315" s="58"/>
     </row>
     <row r="316" ht="14.25" customHeight="1">
-      <c r="A316" s="60"/>
-      <c r="B316" s="61"/>
-      <c r="C316" s="62"/>
+      <c r="A316" s="61"/>
+      <c r="B316" s="62"/>
+      <c r="C316" s="63"/>
       <c r="G316" s="57"/>
       <c r="H316" s="58"/>
     </row>
     <row r="317" ht="14.25" customHeight="1">
-      <c r="A317" s="60"/>
-      <c r="B317" s="61"/>
-      <c r="C317" s="62"/>
+      <c r="A317" s="61"/>
+      <c r="B317" s="62"/>
+      <c r="C317" s="63"/>
       <c r="G317" s="57"/>
       <c r="H317" s="58"/>
     </row>
     <row r="318" ht="14.25" customHeight="1">
-      <c r="A318" s="60"/>
-      <c r="B318" s="61"/>
-      <c r="C318" s="62"/>
+      <c r="A318" s="61"/>
+      <c r="B318" s="62"/>
+      <c r="C318" s="63"/>
       <c r="G318" s="57"/>
       <c r="H318" s="58"/>
     </row>
     <row r="319" ht="14.25" customHeight="1">
-      <c r="A319" s="60"/>
-      <c r="B319" s="61"/>
-      <c r="C319" s="62"/>
+      <c r="A319" s="61"/>
+      <c r="B319" s="62"/>
+      <c r="C319" s="63"/>
       <c r="G319" s="57"/>
       <c r="H319" s="58"/>
     </row>
     <row r="320" ht="14.25" customHeight="1">
-      <c r="A320" s="60"/>
-      <c r="B320" s="61"/>
-      <c r="C320" s="62"/>
+      <c r="A320" s="61"/>
+      <c r="B320" s="62"/>
+      <c r="C320" s="63"/>
       <c r="G320" s="57"/>
       <c r="H320" s="58"/>
     </row>
     <row r="321" ht="14.25" customHeight="1">
-      <c r="A321" s="60"/>
-      <c r="B321" s="61"/>
-      <c r="C321" s="62"/>
+      <c r="A321" s="61"/>
+      <c r="B321" s="62"/>
+      <c r="C321" s="63"/>
       <c r="G321" s="57"/>
       <c r="H321" s="58"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c r="A322" s="60"/>
-      <c r="B322" s="61"/>
-      <c r="C322" s="62"/>
+      <c r="A322" s="61"/>
+      <c r="B322" s="62"/>
+      <c r="C322" s="63"/>
       <c r="G322" s="57"/>
       <c r="H322" s="58"/>
     </row>
     <row r="323" ht="14.25" customHeight="1">
-      <c r="A323" s="60"/>
-      <c r="B323" s="61"/>
-      <c r="C323" s="62"/>
+      <c r="A323" s="61"/>
+      <c r="B323" s="62"/>
+      <c r="C323" s="63"/>
       <c r="G323" s="57"/>
       <c r="H323" s="58"/>
     </row>
     <row r="324" ht="14.25" customHeight="1">
-      <c r="A324" s="60"/>
-      <c r="B324" s="61"/>
-      <c r="C324" s="62"/>
+      <c r="A324" s="61"/>
+      <c r="B324" s="62"/>
+      <c r="C324" s="63"/>
       <c r="G324" s="57"/>
       <c r="H324" s="58"/>
     </row>
     <row r="325" ht="14.25" customHeight="1">
-      <c r="A325" s="60"/>
-      <c r="B325" s="61"/>
-      <c r="C325" s="62"/>
+      <c r="A325" s="61"/>
+      <c r="B325" s="62"/>
+      <c r="C325" s="63"/>
       <c r="G325" s="57"/>
       <c r="H325" s="58"/>
     </row>
     <row r="326" ht="14.25" customHeight="1">
-      <c r="A326" s="60"/>
-      <c r="B326" s="61"/>
-      <c r="C326" s="62"/>
+      <c r="A326" s="61"/>
+      <c r="B326" s="62"/>
+      <c r="C326" s="63"/>
       <c r="G326" s="57"/>
       <c r="H326" s="58"/>
     </row>
     <row r="327" ht="14.25" customHeight="1">
-      <c r="A327" s="60"/>
-      <c r="B327" s="61"/>
-      <c r="C327" s="62"/>
+      <c r="A327" s="61"/>
+      <c r="B327" s="62"/>
+      <c r="C327" s="63"/>
       <c r="G327" s="57"/>
       <c r="H327" s="58"/>
     </row>
     <row r="328" ht="14.25" customHeight="1">
-      <c r="A328" s="60"/>
-      <c r="B328" s="61"/>
-      <c r="C328" s="62"/>
+      <c r="A328" s="61"/>
+      <c r="B328" s="62"/>
+      <c r="C328" s="63"/>
       <c r="G328" s="57"/>
       <c r="H328" s="58"/>
     </row>
     <row r="329" ht="14.25" customHeight="1">
-      <c r="A329" s="60"/>
-      <c r="B329" s="61"/>
-      <c r="C329" s="62"/>
+      <c r="A329" s="61"/>
+      <c r="B329" s="62"/>
+      <c r="C329" s="63"/>
       <c r="G329" s="57"/>
       <c r="H329" s="58"/>
     </row>
     <row r="330" ht="14.25" customHeight="1">
-      <c r="A330" s="60"/>
-      <c r="B330" s="61"/>
-      <c r="C330" s="62"/>
+      <c r="A330" s="61"/>
+      <c r="B330" s="62"/>
+      <c r="C330" s="63"/>
       <c r="G330" s="57"/>
       <c r="H330" s="58"/>
     </row>
     <row r="331" ht="14.25" customHeight="1">
-      <c r="A331" s="60"/>
-      <c r="B331" s="61"/>
-      <c r="C331" s="62"/>
+      <c r="A331" s="61"/>
+      <c r="B331" s="62"/>
+      <c r="C331" s="63"/>
       <c r="G331" s="57"/>
       <c r="H331" s="58"/>
     </row>
     <row r="332" ht="14.25" customHeight="1">
-      <c r="A332" s="60"/>
-      <c r="B332" s="61"/>
-      <c r="C332" s="62"/>
+      <c r="A332" s="61"/>
+      <c r="B332" s="62"/>
+      <c r="C332" s="63"/>
       <c r="G332" s="57"/>
       <c r="H332" s="58"/>
     </row>
     <row r="333" ht="14.25" customHeight="1">
-      <c r="A333" s="60"/>
-      <c r="B333" s="61"/>
-      <c r="C333" s="62"/>
+      <c r="A333" s="61"/>
+      <c r="B333" s="62"/>
+      <c r="C333" s="63"/>
       <c r="G333" s="57"/>
       <c r="H333" s="58"/>
     </row>
     <row r="334" ht="14.25" customHeight="1">
-      <c r="A334" s="60"/>
-      <c r="B334" s="61"/>
-      <c r="C334" s="62"/>
+      <c r="A334" s="61"/>
+      <c r="B334" s="62"/>
+      <c r="C334" s="63"/>
       <c r="G334" s="57"/>
       <c r="H334" s="58"/>
     </row>
     <row r="335" ht="14.25" customHeight="1">
-      <c r="A335" s="60"/>
-      <c r="B335" s="61"/>
-      <c r="C335" s="62"/>
+      <c r="A335" s="61"/>
+      <c r="B335" s="62"/>
+      <c r="C335" s="63"/>
       <c r="G335" s="57"/>
       <c r="H335" s="58"/>
     </row>
     <row r="336" ht="14.25" customHeight="1">
-      <c r="A336" s="60"/>
-      <c r="B336" s="61"/>
-      <c r="C336" s="62"/>
+      <c r="A336" s="61"/>
+      <c r="B336" s="62"/>
+      <c r="C336" s="63"/>
       <c r="G336" s="57"/>
       <c r="H336" s="58"/>
     </row>
     <row r="337" ht="14.25" customHeight="1">
-      <c r="A337" s="63"/>
-      <c r="B337" s="64"/>
-      <c r="C337" s="65"/>
+      <c r="A337" s="61"/>
+      <c r="B337" s="62"/>
+      <c r="C337" s="63"/>
       <c r="G337" s="57"/>
       <c r="H337" s="58"/>
     </row>
     <row r="338" ht="14.25" customHeight="1">
-      <c r="A338" s="63"/>
-      <c r="B338" s="64"/>
-      <c r="C338" s="65"/>
+      <c r="A338" s="64"/>
+      <c r="B338" s="65"/>
+      <c r="C338" s="66"/>
       <c r="G338" s="57"/>
       <c r="H338" s="58"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c r="A339" s="63"/>
-      <c r="B339" s="64"/>
-      <c r="C339" s="65"/>
+      <c r="A339" s="64"/>
+      <c r="B339" s="65"/>
+      <c r="C339" s="66"/>
       <c r="G339" s="57"/>
       <c r="H339" s="58"/>
     </row>
     <row r="340" ht="14.25" customHeight="1">
-      <c r="A340" s="63"/>
-      <c r="B340" s="64"/>
-      <c r="C340" s="65"/>
+      <c r="A340" s="64"/>
+      <c r="B340" s="65"/>
+      <c r="C340" s="66"/>
       <c r="G340" s="57"/>
       <c r="H340" s="58"/>
     </row>
     <row r="341" ht="14.25" customHeight="1">
-      <c r="A341" s="63"/>
-      <c r="B341" s="64"/>
-      <c r="C341" s="65"/>
+      <c r="A341" s="64"/>
+      <c r="B341" s="65"/>
+      <c r="C341" s="66"/>
       <c r="G341" s="57"/>
       <c r="H341" s="58"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c r="A342" s="63"/>
-      <c r="B342" s="64"/>
-      <c r="C342" s="65"/>
+      <c r="A342" s="64"/>
+      <c r="B342" s="65"/>
+      <c r="C342" s="66"/>
       <c r="G342" s="57"/>
       <c r="H342" s="58"/>
     </row>
     <row r="343" ht="14.25" customHeight="1">
-      <c r="A343" s="63"/>
-      <c r="B343" s="64"/>
-      <c r="C343" s="65"/>
+      <c r="A343" s="64"/>
+      <c r="B343" s="65"/>
+      <c r="C343" s="66"/>
       <c r="G343" s="57"/>
       <c r="H343" s="58"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c r="A344" s="63"/>
-      <c r="B344" s="64"/>
-      <c r="C344" s="65"/>
+      <c r="A344" s="64"/>
+      <c r="B344" s="65"/>
+      <c r="C344" s="66"/>
       <c r="G344" s="57"/>
       <c r="H344" s="58"/>
     </row>
     <row r="345" ht="14.25" customHeight="1">
-      <c r="A345" s="63"/>
-      <c r="B345" s="64"/>
-      <c r="C345" s="65"/>
+      <c r="A345" s="64"/>
+      <c r="B345" s="65"/>
+      <c r="C345" s="66"/>
       <c r="G345" s="57"/>
       <c r="H345" s="58"/>
     </row>
     <row r="346" ht="14.25" customHeight="1">
-      <c r="A346" s="63"/>
-      <c r="B346" s="64"/>
-      <c r="C346" s="65"/>
+      <c r="A346" s="64"/>
+      <c r="B346" s="65"/>
+      <c r="C346" s="66"/>
       <c r="G346" s="57"/>
       <c r="H346" s="58"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
-      <c r="A347" s="63"/>
-      <c r="B347" s="64"/>
-      <c r="C347" s="65"/>
+      <c r="A347" s="64"/>
+      <c r="B347" s="65"/>
+      <c r="C347" s="66"/>
       <c r="G347" s="57"/>
       <c r="H347" s="58"/>
     </row>
     <row r="348" ht="14.25" customHeight="1">
-      <c r="A348" s="63"/>
-      <c r="B348" s="64"/>
-      <c r="C348" s="65"/>
+      <c r="A348" s="64"/>
+      <c r="B348" s="65"/>
+      <c r="C348" s="66"/>
       <c r="G348" s="57"/>
       <c r="H348" s="58"/>
     </row>
     <row r="349" ht="14.25" customHeight="1">
-      <c r="A349" s="63"/>
-      <c r="B349" s="64"/>
-      <c r="C349" s="65"/>
+      <c r="A349" s="64"/>
+      <c r="B349" s="65"/>
+      <c r="C349" s="66"/>
       <c r="G349" s="57"/>
       <c r="H349" s="58"/>
     </row>
     <row r="350" ht="14.25" customHeight="1">
-      <c r="A350" s="63"/>
-      <c r="B350" s="64"/>
-      <c r="C350" s="65"/>
+      <c r="A350" s="64"/>
+      <c r="B350" s="65"/>
+      <c r="C350" s="66"/>
       <c r="G350" s="57"/>
       <c r="H350" s="58"/>
     </row>
     <row r="351" ht="14.25" customHeight="1">
-      <c r="A351" s="63"/>
-      <c r="B351" s="64"/>
-      <c r="C351" s="65"/>
+      <c r="A351" s="64"/>
+      <c r="B351" s="65"/>
+      <c r="C351" s="66"/>
       <c r="G351" s="57"/>
       <c r="H351" s="58"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
-      <c r="A352" s="63"/>
-      <c r="B352" s="64"/>
-      <c r="C352" s="65"/>
+      <c r="A352" s="64"/>
+      <c r="B352" s="65"/>
+      <c r="C352" s="66"/>
       <c r="G352" s="57"/>
       <c r="H352" s="58"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c r="A353" s="63"/>
-      <c r="B353" s="64"/>
-      <c r="C353" s="65"/>
+      <c r="A353" s="64"/>
+      <c r="B353" s="65"/>
+      <c r="C353" s="66"/>
       <c r="G353" s="57"/>
       <c r="H353" s="58"/>
     </row>
     <row r="354" ht="14.25" customHeight="1">
-      <c r="A354" s="63"/>
-      <c r="B354" s="64"/>
-      <c r="C354" s="65"/>
+      <c r="A354" s="64"/>
+      <c r="B354" s="65"/>
+      <c r="C354" s="66"/>
       <c r="G354" s="57"/>
       <c r="H354" s="58"/>
     </row>
     <row r="355" ht="14.25" customHeight="1">
-      <c r="A355" s="63"/>
-      <c r="B355" s="64"/>
-      <c r="C355" s="65"/>
+      <c r="A355" s="64"/>
+      <c r="B355" s="65"/>
+      <c r="C355" s="66"/>
       <c r="G355" s="57"/>
       <c r="H355" s="58"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c r="A356" s="63"/>
-      <c r="B356" s="64"/>
-      <c r="C356" s="65"/>
+      <c r="A356" s="64"/>
+      <c r="B356" s="65"/>
+      <c r="C356" s="66"/>
       <c r="G356" s="57"/>
       <c r="H356" s="58"/>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c r="A357" s="63"/>
-      <c r="B357" s="64"/>
-      <c r="C357" s="65"/>
+      <c r="A357" s="64"/>
+      <c r="B357" s="65"/>
+      <c r="C357" s="66"/>
       <c r="G357" s="57"/>
       <c r="H357" s="58"/>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c r="A358" s="63"/>
-      <c r="B358" s="64"/>
-      <c r="C358" s="65"/>
+      <c r="A358" s="64"/>
+      <c r="B358" s="65"/>
+      <c r="C358" s="66"/>
       <c r="G358" s="57"/>
       <c r="H358" s="58"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
-      <c r="A359" s="63"/>
-      <c r="B359" s="64"/>
-      <c r="C359" s="65"/>
+      <c r="A359" s="64"/>
+      <c r="B359" s="65"/>
+      <c r="C359" s="66"/>
       <c r="G359" s="57"/>
       <c r="H359" s="58"/>
     </row>
     <row r="360" ht="14.25" customHeight="1">
-      <c r="A360" s="63"/>
-      <c r="B360" s="64"/>
-      <c r="C360" s="65"/>
+      <c r="A360" s="64"/>
+      <c r="B360" s="65"/>
+      <c r="C360" s="66"/>
       <c r="G360" s="57"/>
       <c r="H360" s="58"/>
     </row>
     <row r="361" ht="14.25" customHeight="1">
-      <c r="A361" s="63"/>
-      <c r="B361" s="64"/>
-      <c r="C361" s="65"/>
+      <c r="A361" s="64"/>
+      <c r="B361" s="65"/>
+      <c r="C361" s="66"/>
       <c r="G361" s="57"/>
       <c r="H361" s="58"/>
     </row>
     <row r="362" ht="14.25" customHeight="1">
-      <c r="A362" s="63"/>
-      <c r="B362" s="64"/>
-      <c r="C362" s="65"/>
+      <c r="A362" s="64"/>
+      <c r="B362" s="65"/>
+      <c r="C362" s="66"/>
       <c r="G362" s="57"/>
       <c r="H362" s="58"/>
     </row>
     <row r="363" ht="14.25" customHeight="1">
-      <c r="A363" s="63"/>
-      <c r="B363" s="64"/>
-      <c r="C363" s="65"/>
+      <c r="A363" s="64"/>
+      <c r="B363" s="65"/>
+      <c r="C363" s="66"/>
       <c r="G363" s="57"/>
       <c r="H363" s="58"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c r="A364" s="63"/>
-      <c r="B364" s="64"/>
-      <c r="C364" s="65"/>
+      <c r="A364" s="64"/>
+      <c r="B364" s="65"/>
+      <c r="C364" s="66"/>
       <c r="G364" s="57"/>
       <c r="H364" s="58"/>
     </row>
     <row r="365" ht="14.25" customHeight="1">
-      <c r="A365" s="63"/>
-      <c r="B365" s="64"/>
-      <c r="C365" s="65"/>
+      <c r="A365" s="64"/>
+      <c r="B365" s="65"/>
+      <c r="C365" s="66"/>
       <c r="G365" s="57"/>
       <c r="H365" s="58"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c r="A366" s="63"/>
-      <c r="B366" s="64"/>
-      <c r="C366" s="65"/>
+      <c r="A366" s="64"/>
+      <c r="B366" s="65"/>
+      <c r="C366" s="66"/>
       <c r="G366" s="57"/>
       <c r="H366" s="58"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
-      <c r="A367" s="63"/>
-      <c r="B367" s="64"/>
-      <c r="C367" s="65"/>
+      <c r="A367" s="64"/>
+      <c r="B367" s="65"/>
+      <c r="C367" s="66"/>
       <c r="G367" s="57"/>
       <c r="H367" s="58"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c r="A368" s="63"/>
-      <c r="B368" s="64"/>
-      <c r="C368" s="65"/>
+      <c r="A368" s="64"/>
+      <c r="B368" s="65"/>
+      <c r="C368" s="66"/>
       <c r="G368" s="57"/>
       <c r="H368" s="58"/>
     </row>
     <row r="369" ht="14.25" customHeight="1">
-      <c r="A369" s="63"/>
-      <c r="B369" s="64"/>
-      <c r="C369" s="65"/>
+      <c r="A369" s="64"/>
+      <c r="B369" s="65"/>
+      <c r="C369" s="66"/>
       <c r="G369" s="57"/>
       <c r="H369" s="58"/>
     </row>
     <row r="370" ht="14.25" customHeight="1">
-      <c r="A370" s="63"/>
-      <c r="B370" s="64"/>
-      <c r="C370" s="65"/>
+      <c r="A370" s="64"/>
+      <c r="B370" s="65"/>
+      <c r="C370" s="66"/>
       <c r="G370" s="57"/>
       <c r="H370" s="58"/>
     </row>
     <row r="371" ht="14.25" customHeight="1">
-      <c r="A371" s="63"/>
-      <c r="B371" s="64"/>
-      <c r="C371" s="65"/>
+      <c r="A371" s="64"/>
+      <c r="B371" s="65"/>
+      <c r="C371" s="66"/>
       <c r="G371" s="57"/>
       <c r="H371" s="58"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
-      <c r="A372" s="63"/>
-      <c r="B372" s="64"/>
-      <c r="C372" s="65"/>
+      <c r="A372" s="64"/>
+      <c r="B372" s="65"/>
+      <c r="C372" s="66"/>
       <c r="G372" s="57"/>
       <c r="H372" s="58"/>
     </row>
     <row r="373" ht="14.25" customHeight="1">
-      <c r="A373" s="63"/>
-      <c r="B373" s="64"/>
-      <c r="C373" s="65"/>
+      <c r="A373" s="64"/>
+      <c r="B373" s="65"/>
+      <c r="C373" s="66"/>
       <c r="G373" s="57"/>
       <c r="H373" s="58"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c r="A374" s="63"/>
-      <c r="B374" s="64"/>
-      <c r="C374" s="65"/>
+      <c r="A374" s="64"/>
+      <c r="B374" s="65"/>
+      <c r="C374" s="66"/>
       <c r="G374" s="57"/>
       <c r="H374" s="58"/>
     </row>
     <row r="375" ht="14.25" customHeight="1">
-      <c r="A375" s="63"/>
-      <c r="B375" s="64"/>
-      <c r="C375" s="65"/>
+      <c r="A375" s="64"/>
+      <c r="B375" s="65"/>
+      <c r="C375" s="66"/>
       <c r="G375" s="57"/>
       <c r="H375" s="58"/>
     </row>
     <row r="376" ht="14.25" customHeight="1">
-      <c r="A376" s="63"/>
-      <c r="B376" s="64"/>
-      <c r="C376" s="65"/>
+      <c r="A376" s="64"/>
+      <c r="B376" s="65"/>
+      <c r="C376" s="66"/>
       <c r="G376" s="57"/>
       <c r="H376" s="58"/>
     </row>
     <row r="377" ht="14.25" customHeight="1">
-      <c r="A377" s="63"/>
-      <c r="B377" s="64"/>
-      <c r="C377" s="65"/>
+      <c r="A377" s="64"/>
+      <c r="B377" s="65"/>
+      <c r="C377" s="66"/>
       <c r="G377" s="57"/>
       <c r="H377" s="58"/>
     </row>
     <row r="378" ht="14.25" customHeight="1">
-      <c r="A378" s="63"/>
-      <c r="B378" s="64"/>
-      <c r="C378" s="65"/>
+      <c r="A378" s="64"/>
+      <c r="B378" s="65"/>
+      <c r="C378" s="66"/>
       <c r="G378" s="57"/>
       <c r="H378" s="58"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
-      <c r="A379" s="63"/>
-      <c r="B379" s="64"/>
-      <c r="C379" s="65"/>
+      <c r="A379" s="64"/>
+      <c r="B379" s="65"/>
+      <c r="C379" s="66"/>
       <c r="G379" s="57"/>
       <c r="H379" s="58"/>
     </row>
     <row r="380" ht="14.25" customHeight="1">
-      <c r="A380" s="63"/>
-      <c r="B380" s="64"/>
-      <c r="C380" s="65"/>
+      <c r="A380" s="64"/>
+      <c r="B380" s="65"/>
+      <c r="C380" s="66"/>
       <c r="G380" s="57"/>
       <c r="H380" s="58"/>
     </row>
     <row r="381" ht="14.25" customHeight="1">
-      <c r="A381" s="63"/>
-      <c r="B381" s="64"/>
-      <c r="C381" s="65"/>
+      <c r="A381" s="64"/>
+      <c r="B381" s="65"/>
+      <c r="C381" s="66"/>
       <c r="G381" s="57"/>
       <c r="H381" s="58"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c r="A382" s="63"/>
-      <c r="B382" s="64"/>
-      <c r="C382" s="65"/>
+      <c r="A382" s="64"/>
+      <c r="B382" s="65"/>
+      <c r="C382" s="66"/>
       <c r="G382" s="57"/>
       <c r="H382" s="58"/>
     </row>
     <row r="383" ht="14.25" customHeight="1">
-      <c r="A383" s="63"/>
-      <c r="B383" s="64"/>
-      <c r="C383" s="65"/>
+      <c r="A383" s="64"/>
+      <c r="B383" s="65"/>
+      <c r="C383" s="66"/>
       <c r="G383" s="57"/>
       <c r="H383" s="58"/>
     </row>
     <row r="384" ht="14.25" customHeight="1">
-      <c r="A384" s="63"/>
-      <c r="B384" s="64"/>
-      <c r="C384" s="65"/>
+      <c r="A384" s="64"/>
+      <c r="B384" s="65"/>
+      <c r="C384" s="66"/>
       <c r="G384" s="57"/>
       <c r="H384" s="58"/>
     </row>
     <row r="385" ht="14.25" customHeight="1">
-      <c r="A385" s="63"/>
-      <c r="B385" s="64"/>
-      <c r="C385" s="65"/>
+      <c r="A385" s="64"/>
+      <c r="B385" s="65"/>
+      <c r="C385" s="66"/>
       <c r="G385" s="57"/>
       <c r="H385" s="58"/>
     </row>
     <row r="386" ht="14.25" customHeight="1">
-      <c r="A386" s="63"/>
-      <c r="B386" s="64"/>
-      <c r="C386" s="65"/>
+      <c r="A386" s="64"/>
+      <c r="B386" s="65"/>
+      <c r="C386" s="66"/>
       <c r="G386" s="57"/>
       <c r="H386" s="58"/>
     </row>
     <row r="387" ht="14.25" customHeight="1">
-      <c r="A387" s="63"/>
-      <c r="B387" s="64"/>
-      <c r="C387" s="65"/>
+      <c r="A387" s="64"/>
+      <c r="B387" s="65"/>
+      <c r="C387" s="66"/>
       <c r="G387" s="57"/>
       <c r="H387" s="58"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c r="A388" s="63"/>
-      <c r="B388" s="64"/>
-      <c r="C388" s="65"/>
+      <c r="A388" s="64"/>
+      <c r="B388" s="65"/>
+      <c r="C388" s="66"/>
       <c r="G388" s="57"/>
       <c r="H388" s="58"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c r="A389" s="63"/>
-      <c r="B389" s="64"/>
-      <c r="C389" s="65"/>
+      <c r="A389" s="64"/>
+      <c r="B389" s="65"/>
+      <c r="C389" s="66"/>
       <c r="G389" s="57"/>
       <c r="H389" s="58"/>
     </row>
     <row r="390" ht="14.25" customHeight="1">
-      <c r="A390" s="63"/>
-      <c r="B390" s="64"/>
-      <c r="C390" s="65"/>
+      <c r="A390" s="64"/>
+      <c r="B390" s="65"/>
+      <c r="C390" s="66"/>
       <c r="G390" s="57"/>
       <c r="H390" s="58"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c r="A391" s="63"/>
-      <c r="B391" s="64"/>
-      <c r="C391" s="65"/>
+      <c r="A391" s="64"/>
+      <c r="B391" s="65"/>
+      <c r="C391" s="66"/>
       <c r="G391" s="57"/>
       <c r="H391" s="58"/>
     </row>
     <row r="392" ht="14.25" customHeight="1">
-      <c r="A392" s="63"/>
-      <c r="B392" s="64"/>
-      <c r="C392" s="65"/>
+      <c r="A392" s="64"/>
+      <c r="B392" s="65"/>
+      <c r="C392" s="66"/>
       <c r="G392" s="57"/>
       <c r="H392" s="58"/>
     </row>
     <row r="393" ht="14.25" customHeight="1">
-      <c r="A393" s="63"/>
-      <c r="B393" s="64"/>
-      <c r="C393" s="65"/>
+      <c r="A393" s="64"/>
+      <c r="B393" s="65"/>
+      <c r="C393" s="66"/>
       <c r="G393" s="57"/>
       <c r="H393" s="58"/>
     </row>
     <row r="394" ht="14.25" customHeight="1">
-      <c r="A394" s="63"/>
-      <c r="B394" s="64"/>
-      <c r="C394" s="65"/>
+      <c r="A394" s="64"/>
+      <c r="B394" s="65"/>
+      <c r="C394" s="66"/>
       <c r="G394" s="57"/>
       <c r="H394" s="58"/>
     </row>
     <row r="395" ht="14.25" customHeight="1">
-      <c r="A395" s="63"/>
-      <c r="B395" s="64"/>
-      <c r="C395" s="65"/>
+      <c r="A395" s="64"/>
+      <c r="B395" s="65"/>
+      <c r="C395" s="66"/>
       <c r="G395" s="57"/>
       <c r="H395" s="58"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c r="A396" s="63"/>
-      <c r="B396" s="64"/>
-      <c r="C396" s="65"/>
+      <c r="A396" s="64"/>
+      <c r="B396" s="65"/>
+      <c r="C396" s="66"/>
       <c r="G396" s="57"/>
       <c r="H396" s="58"/>
     </row>
     <row r="397" ht="14.25" customHeight="1">
-      <c r="A397" s="63"/>
-      <c r="B397" s="64"/>
-      <c r="C397" s="65"/>
+      <c r="A397" s="64"/>
+      <c r="B397" s="65"/>
+      <c r="C397" s="66"/>
       <c r="G397" s="57"/>
       <c r="H397" s="58"/>
     </row>
     <row r="398" ht="14.25" customHeight="1">
-      <c r="A398" s="63"/>
-      <c r="B398" s="64"/>
-      <c r="C398" s="65"/>
+      <c r="A398" s="64"/>
+      <c r="B398" s="65"/>
+      <c r="C398" s="66"/>
       <c r="G398" s="57"/>
       <c r="H398" s="58"/>
     </row>
     <row r="399" ht="14.25" customHeight="1">
-      <c r="A399" s="63"/>
-      <c r="B399" s="64"/>
-      <c r="C399" s="65"/>
+      <c r="A399" s="64"/>
+      <c r="B399" s="65"/>
+      <c r="C399" s="66"/>
       <c r="G399" s="57"/>
       <c r="H399" s="58"/>
     </row>
     <row r="400" ht="14.25" customHeight="1">
-      <c r="A400" s="63"/>
-      <c r="B400" s="64"/>
-      <c r="C400" s="65"/>
+      <c r="A400" s="64"/>
+      <c r="B400" s="65"/>
+      <c r="C400" s="66"/>
       <c r="G400" s="57"/>
       <c r="H400" s="58"/>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c r="A401" s="63"/>
-      <c r="B401" s="64"/>
-      <c r="C401" s="65"/>
+      <c r="A401" s="64"/>
+      <c r="B401" s="65"/>
+      <c r="C401" s="66"/>
       <c r="G401" s="57"/>
       <c r="H401" s="58"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c r="A402" s="63"/>
-      <c r="B402" s="64"/>
-      <c r="C402" s="65"/>
+      <c r="A402" s="64"/>
+      <c r="B402" s="65"/>
+      <c r="C402" s="66"/>
       <c r="G402" s="57"/>
       <c r="H402" s="58"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c r="A403" s="63"/>
-      <c r="B403" s="64"/>
-      <c r="C403" s="65"/>
+      <c r="A403" s="64"/>
+      <c r="B403" s="65"/>
+      <c r="C403" s="66"/>
       <c r="G403" s="57"/>
       <c r="H403" s="58"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
-      <c r="A404" s="63"/>
-      <c r="B404" s="64"/>
-      <c r="C404" s="65"/>
+      <c r="A404" s="64"/>
+      <c r="B404" s="65"/>
+      <c r="C404" s="66"/>
       <c r="G404" s="57"/>
       <c r="H404" s="58"/>
     </row>
     <row r="405" ht="14.25" customHeight="1">
-      <c r="A405" s="63"/>
-      <c r="B405" s="64"/>
-      <c r="C405" s="65"/>
+      <c r="A405" s="64"/>
+      <c r="B405" s="65"/>
+      <c r="C405" s="66"/>
       <c r="G405" s="57"/>
       <c r="H405" s="58"/>
     </row>
     <row r="406" ht="14.25" customHeight="1">
-      <c r="A406" s="63"/>
-      <c r="B406" s="64"/>
-      <c r="C406" s="65"/>
+      <c r="A406" s="64"/>
+      <c r="B406" s="65"/>
+      <c r="C406" s="66"/>
       <c r="G406" s="57"/>
       <c r="H406" s="58"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c r="A407" s="63"/>
-      <c r="B407" s="64"/>
-      <c r="C407" s="65"/>
+      <c r="A407" s="64"/>
+      <c r="B407" s="65"/>
+      <c r="C407" s="66"/>
       <c r="G407" s="57"/>
       <c r="H407" s="58"/>
     </row>
     <row r="408" ht="14.25" customHeight="1">
-      <c r="A408" s="63"/>
-      <c r="B408" s="64"/>
-      <c r="C408" s="65"/>
+      <c r="A408" s="64"/>
+      <c r="B408" s="65"/>
+      <c r="C408" s="66"/>
       <c r="G408" s="57"/>
       <c r="H408" s="58"/>
     </row>
     <row r="409" ht="14.25" customHeight="1">
-      <c r="A409" s="63"/>
-      <c r="B409" s="64"/>
-      <c r="C409" s="65"/>
+      <c r="A409" s="64"/>
+      <c r="B409" s="65"/>
+      <c r="C409" s="66"/>
       <c r="G409" s="57"/>
       <c r="H409" s="58"/>
     </row>
     <row r="410" ht="14.25" customHeight="1">
-      <c r="A410" s="63"/>
-      <c r="B410" s="64"/>
-      <c r="C410" s="65"/>
+      <c r="A410" s="64"/>
+      <c r="B410" s="65"/>
+      <c r="C410" s="66"/>
       <c r="G410" s="57"/>
       <c r="H410" s="58"/>
     </row>
     <row r="411" ht="14.25" customHeight="1">
-      <c r="A411" s="63"/>
-      <c r="B411" s="64"/>
-      <c r="C411" s="65"/>
+      <c r="A411" s="64"/>
+      <c r="B411" s="65"/>
+      <c r="C411" s="66"/>
       <c r="G411" s="57"/>
       <c r="H411" s="58"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
-      <c r="A412" s="63"/>
-      <c r="B412" s="64"/>
-      <c r="C412" s="65"/>
+      <c r="A412" s="64"/>
+      <c r="B412" s="65"/>
+      <c r="C412" s="66"/>
       <c r="G412" s="57"/>
       <c r="H412" s="58"/>
     </row>
     <row r="413" ht="14.25" customHeight="1">
-      <c r="A413" s="60"/>
-      <c r="C413" s="32"/>
+      <c r="A413" s="64"/>
+      <c r="B413" s="65"/>
+      <c r="C413" s="66"/>
       <c r="G413" s="57"/>
       <c r="H413" s="58"/>
     </row>
     <row r="414" ht="14.25" customHeight="1">
-      <c r="A414" s="60"/>
+      <c r="A414" s="61"/>
       <c r="C414" s="32"/>
+      <c r="G414" s="57"/>
+      <c r="H414" s="58"/>
     </row>
     <row r="415" ht="14.25" customHeight="1">
-      <c r="A415" s="60"/>
+      <c r="A415" s="61"/>
       <c r="C415" s="32"/>
     </row>
     <row r="416" ht="14.25" customHeight="1">
-      <c r="A416" s="60"/>
+      <c r="A416" s="61"/>
       <c r="C416" s="32"/>
     </row>
     <row r="417" ht="14.25" customHeight="1">
-      <c r="A417" s="60"/>
+      <c r="A417" s="61"/>
       <c r="C417" s="32"/>
     </row>
     <row r="418" ht="14.25" customHeight="1">
-      <c r="A418" s="60"/>
+      <c r="A418" s="61"/>
       <c r="C418" s="32"/>
     </row>
     <row r="419" ht="14.25" customHeight="1">
-      <c r="A419" s="60"/>
+      <c r="A419" s="61"/>
       <c r="C419" s="32"/>
     </row>
     <row r="420" ht="14.25" customHeight="1">
-      <c r="A420" s="60"/>
+      <c r="A420" s="61"/>
       <c r="C420" s="32"/>
     </row>
     <row r="421" ht="14.25" customHeight="1">
-      <c r="A421" s="60"/>
+      <c r="A421" s="61"/>
       <c r="C421" s="32"/>
     </row>
     <row r="422" ht="14.25" customHeight="1">
-      <c r="A422" s="60"/>
+      <c r="A422" s="61"/>
       <c r="C422" s="32"/>
     </row>
     <row r="423" ht="14.25" customHeight="1">
-      <c r="A423" s="60"/>
+      <c r="A423" s="61"/>
       <c r="C423" s="32"/>
     </row>
     <row r="424" ht="14.25" customHeight="1">
-      <c r="A424" s="60"/>
+      <c r="A424" s="61"/>
       <c r="C424" s="32"/>
     </row>
     <row r="425" ht="14.25" customHeight="1">
-      <c r="A425" s="60"/>
+      <c r="A425" s="61"/>
       <c r="C425" s="32"/>
     </row>
     <row r="426" ht="14.25" customHeight="1">
-      <c r="A426" s="60"/>
+      <c r="A426" s="61"/>
       <c r="C426" s="32"/>
     </row>
     <row r="427" ht="14.25" customHeight="1">
-      <c r="A427" s="60"/>
+      <c r="A427" s="61"/>
       <c r="C427" s="32"/>
     </row>
     <row r="428" ht="14.25" customHeight="1">
-      <c r="A428" s="60"/>
+      <c r="A428" s="61"/>
       <c r="C428" s="32"/>
     </row>
     <row r="429" ht="14.25" customHeight="1">
-      <c r="A429" s="60"/>
+      <c r="A429" s="61"/>
       <c r="C429" s="32"/>
     </row>
     <row r="430" ht="14.25" customHeight="1">
-      <c r="A430" s="60"/>
+      <c r="A430" s="61"/>
       <c r="C430" s="32"/>
     </row>
     <row r="431" ht="14.25" customHeight="1">
-      <c r="A431" s="60"/>
+      <c r="A431" s="61"/>
       <c r="C431" s="32"/>
     </row>
     <row r="432" ht="14.25" customHeight="1">
-      <c r="A432" s="60"/>
+      <c r="A432" s="61"/>
       <c r="C432" s="32"/>
     </row>
     <row r="433" ht="14.25" customHeight="1">
-      <c r="A433" s="60"/>
+      <c r="A433" s="61"/>
       <c r="C433" s="32"/>
     </row>
     <row r="434" ht="14.25" customHeight="1">
-      <c r="A434" s="60"/>
+      <c r="A434" s="61"/>
       <c r="C434" s="32"/>
     </row>
     <row r="435" ht="14.25" customHeight="1">
-      <c r="A435" s="60"/>
+      <c r="A435" s="61"/>
       <c r="C435" s="32"/>
     </row>
     <row r="436" ht="14.25" customHeight="1">
-      <c r="A436" s="60"/>
+      <c r="A436" s="61"/>
       <c r="C436" s="32"/>
     </row>
     <row r="437" ht="14.25" customHeight="1">
-      <c r="A437" s="31"/>
+      <c r="A437" s="61"/>
       <c r="C437" s="32"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" ht="14.25" customHeight="1">
       <c r="A438" s="31"/>
       <c r="C438" s="32"/>
     </row>
@@ -20143,15 +20174,19 @@
     </row>
     <row r="1026" ht="15.75" customHeight="1">
       <c r="A1026" s="31"/>
+      <c r="C1026" s="32"/>
+    </row>
+    <row r="1027" ht="15.75" customHeight="1">
+      <c r="A1027" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$282">
-    <sortState ref="A1:E282">
-      <sortCondition ref="A1:A282"/>
-      <sortCondition ref="B1:B282"/>
-      <sortCondition ref="E1:E282"/>
-      <sortCondition ref="C1:C282"/>
-      <sortCondition ref="D1:D282"/>
+  <autoFilter ref="$A$1:$E$283">
+    <sortState ref="A1:E283">
+      <sortCondition ref="A1:A283"/>
+      <sortCondition ref="B1:B283"/>
+      <sortCondition ref="E1:E283"/>
+      <sortCondition ref="C1:C283"/>
+      <sortCondition ref="D1:D283"/>
     </sortState>
   </autoFilter>
   <printOptions/>
@@ -20197,7 +20232,7 @@
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="60" t="s">
         <v>111</v>
       </c>
       <c r="B2" s="59" t="s">
@@ -20217,7 +20252,7 @@
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="60" t="s">
         <v>113</v>
       </c>
       <c r="B3" s="59" t="s">
@@ -20237,7 +20272,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="60" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="59" t="s">
@@ -20257,7 +20292,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="60" t="s">
         <v>63</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -24295,7 +24330,7 @@
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="60" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="25">
@@ -24312,7 +24347,7 @@
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="60" t="s">
         <v>57</v>
       </c>
       <c r="B3" s="25">
@@ -24329,7 +24364,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="60" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="28">
@@ -24346,7 +24381,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="60" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="28">
@@ -24363,7 +24398,7 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="60" t="s">
         <v>53</v>
       </c>
       <c r="B6" s="28">
@@ -24380,7 +24415,7 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="60" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="28">
@@ -24397,7 +24432,7 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="60" t="s">
         <v>111</v>
       </c>
       <c r="B8" s="71">
@@ -24414,7 +24449,7 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="60" t="s">
         <v>113</v>
       </c>
       <c r="B9" s="71">
@@ -24431,7 +24466,7 @@
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="60" t="s">
         <v>63</v>
       </c>
       <c r="B10" s="71">
@@ -24448,7 +24483,7 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="60" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="71">
@@ -24585,1341 +24620,1341 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="77"/>
-      <c r="B19" s="61"/>
+      <c r="B19" s="62"/>
       <c r="C19" s="57"/>
-      <c r="D19" s="62"/>
+      <c r="D19" s="63"/>
       <c r="E19" s="78"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="77"/>
-      <c r="B20" s="61"/>
+      <c r="B20" s="62"/>
       <c r="C20" s="57"/>
-      <c r="D20" s="62"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="78"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="77"/>
-      <c r="B21" s="61"/>
+      <c r="B21" s="62"/>
       <c r="C21" s="57"/>
-      <c r="D21" s="62"/>
+      <c r="D21" s="63"/>
       <c r="E21" s="78"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="77"/>
-      <c r="B22" s="61"/>
+      <c r="B22" s="62"/>
       <c r="C22" s="57"/>
-      <c r="D22" s="62"/>
+      <c r="D22" s="63"/>
       <c r="E22" s="78"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="77"/>
-      <c r="B23" s="61"/>
+      <c r="B23" s="62"/>
       <c r="C23" s="57"/>
-      <c r="D23" s="62"/>
+      <c r="D23" s="63"/>
       <c r="E23" s="78"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="77"/>
-      <c r="B24" s="61"/>
+      <c r="B24" s="62"/>
       <c r="C24" s="57"/>
-      <c r="D24" s="62"/>
+      <c r="D24" s="63"/>
       <c r="E24" s="78"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="77"/>
-      <c r="B25" s="61"/>
+      <c r="B25" s="62"/>
       <c r="C25" s="57"/>
-      <c r="D25" s="62"/>
+      <c r="D25" s="63"/>
       <c r="E25" s="78"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="77"/>
-      <c r="B26" s="61"/>
+      <c r="B26" s="62"/>
       <c r="C26" s="57"/>
-      <c r="D26" s="62"/>
+      <c r="D26" s="63"/>
       <c r="E26" s="78"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="77"/>
-      <c r="B27" s="61"/>
+      <c r="B27" s="62"/>
       <c r="C27" s="57"/>
-      <c r="D27" s="62"/>
+      <c r="D27" s="63"/>
       <c r="E27" s="78"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="77"/>
-      <c r="B28" s="61"/>
+      <c r="B28" s="62"/>
       <c r="C28" s="57"/>
-      <c r="D28" s="62"/>
+      <c r="D28" s="63"/>
       <c r="E28" s="78"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="77"/>
-      <c r="B29" s="61"/>
+      <c r="B29" s="62"/>
       <c r="C29" s="57"/>
-      <c r="D29" s="62"/>
+      <c r="D29" s="63"/>
       <c r="E29" s="78"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="77"/>
-      <c r="B30" s="61"/>
+      <c r="B30" s="62"/>
       <c r="C30" s="57"/>
-      <c r="D30" s="62"/>
+      <c r="D30" s="63"/>
       <c r="E30" s="78"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="77"/>
-      <c r="B31" s="61"/>
+      <c r="B31" s="62"/>
       <c r="C31" s="57"/>
-      <c r="D31" s="62"/>
+      <c r="D31" s="63"/>
       <c r="E31" s="78"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="77"/>
-      <c r="B32" s="61"/>
+      <c r="B32" s="62"/>
       <c r="C32" s="57"/>
-      <c r="D32" s="62"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="78"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="77"/>
-      <c r="B33" s="61"/>
+      <c r="B33" s="62"/>
       <c r="C33" s="57"/>
-      <c r="D33" s="62"/>
+      <c r="D33" s="63"/>
       <c r="E33" s="78"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="77"/>
-      <c r="B34" s="61"/>
+      <c r="B34" s="62"/>
       <c r="C34" s="57"/>
-      <c r="D34" s="62"/>
+      <c r="D34" s="63"/>
       <c r="E34" s="78"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="77"/>
-      <c r="B35" s="61"/>
+      <c r="B35" s="62"/>
       <c r="C35" s="57"/>
-      <c r="D35" s="62"/>
+      <c r="D35" s="63"/>
       <c r="E35" s="78"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="77"/>
-      <c r="B36" s="61"/>
+      <c r="B36" s="62"/>
       <c r="C36" s="57"/>
-      <c r="D36" s="62"/>
+      <c r="D36" s="63"/>
       <c r="E36" s="78"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="77"/>
-      <c r="B37" s="61"/>
+      <c r="B37" s="62"/>
       <c r="C37" s="57"/>
-      <c r="D37" s="62"/>
+      <c r="D37" s="63"/>
       <c r="E37" s="78"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="77"/>
-      <c r="B38" s="61"/>
+      <c r="B38" s="62"/>
       <c r="C38" s="57"/>
-      <c r="D38" s="62"/>
+      <c r="D38" s="63"/>
       <c r="E38" s="78"/>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="77"/>
-      <c r="B39" s="61"/>
+      <c r="B39" s="62"/>
       <c r="C39" s="57"/>
-      <c r="D39" s="62"/>
+      <c r="D39" s="63"/>
       <c r="E39" s="78"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="77"/>
-      <c r="B40" s="61"/>
+      <c r="B40" s="62"/>
       <c r="C40" s="57"/>
-      <c r="D40" s="62"/>
+      <c r="D40" s="63"/>
       <c r="E40" s="78"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="77"/>
-      <c r="B41" s="61"/>
+      <c r="B41" s="62"/>
       <c r="C41" s="57"/>
-      <c r="D41" s="62"/>
+      <c r="D41" s="63"/>
       <c r="E41" s="78"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="77"/>
-      <c r="B42" s="61"/>
+      <c r="B42" s="62"/>
       <c r="C42" s="57"/>
-      <c r="D42" s="62"/>
+      <c r="D42" s="63"/>
       <c r="E42" s="78"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="77"/>
-      <c r="B43" s="61"/>
+      <c r="B43" s="62"/>
       <c r="C43" s="57"/>
-      <c r="D43" s="62"/>
+      <c r="D43" s="63"/>
       <c r="E43" s="78"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="77"/>
-      <c r="B44" s="61"/>
+      <c r="B44" s="62"/>
       <c r="C44" s="57"/>
-      <c r="D44" s="62"/>
+      <c r="D44" s="63"/>
       <c r="E44" s="78"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="77"/>
-      <c r="B45" s="61"/>
+      <c r="B45" s="62"/>
       <c r="C45" s="57"/>
-      <c r="D45" s="62"/>
+      <c r="D45" s="63"/>
       <c r="E45" s="78"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="77"/>
-      <c r="B46" s="61"/>
+      <c r="B46" s="62"/>
       <c r="C46" s="57"/>
-      <c r="D46" s="62"/>
+      <c r="D46" s="63"/>
       <c r="E46" s="78"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="77"/>
-      <c r="B47" s="61"/>
+      <c r="B47" s="62"/>
       <c r="C47" s="57"/>
-      <c r="D47" s="62"/>
+      <c r="D47" s="63"/>
       <c r="E47" s="78"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="77"/>
-      <c r="B48" s="61"/>
+      <c r="B48" s="62"/>
       <c r="C48" s="57"/>
-      <c r="D48" s="62"/>
+      <c r="D48" s="63"/>
       <c r="E48" s="78"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="77"/>
-      <c r="B49" s="61"/>
+      <c r="B49" s="62"/>
       <c r="C49" s="57"/>
-      <c r="D49" s="62"/>
+      <c r="D49" s="63"/>
       <c r="E49" s="78"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="77"/>
-      <c r="B50" s="61"/>
+      <c r="B50" s="62"/>
       <c r="C50" s="57"/>
-      <c r="D50" s="62"/>
+      <c r="D50" s="63"/>
       <c r="E50" s="78"/>
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="77"/>
-      <c r="B51" s="61"/>
+      <c r="B51" s="62"/>
       <c r="C51" s="57"/>
-      <c r="D51" s="62"/>
+      <c r="D51" s="63"/>
       <c r="E51" s="78"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="77"/>
-      <c r="B52" s="61"/>
+      <c r="B52" s="62"/>
       <c r="C52" s="57"/>
-      <c r="D52" s="62"/>
+      <c r="D52" s="63"/>
       <c r="E52" s="78"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="77"/>
-      <c r="B53" s="61"/>
+      <c r="B53" s="62"/>
       <c r="C53" s="57"/>
-      <c r="D53" s="62"/>
+      <c r="D53" s="63"/>
       <c r="E53" s="78"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="77"/>
-      <c r="B54" s="61"/>
+      <c r="B54" s="62"/>
       <c r="C54" s="57"/>
-      <c r="D54" s="62"/>
+      <c r="D54" s="63"/>
       <c r="E54" s="78"/>
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="77"/>
-      <c r="B55" s="61"/>
+      <c r="B55" s="62"/>
       <c r="C55" s="57"/>
-      <c r="D55" s="62"/>
+      <c r="D55" s="63"/>
       <c r="E55" s="78"/>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="77"/>
-      <c r="B56" s="61"/>
+      <c r="B56" s="62"/>
       <c r="C56" s="57"/>
-      <c r="D56" s="62"/>
+      <c r="D56" s="63"/>
       <c r="E56" s="78"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="77"/>
-      <c r="B57" s="61"/>
+      <c r="B57" s="62"/>
       <c r="C57" s="57"/>
-      <c r="D57" s="62"/>
+      <c r="D57" s="63"/>
       <c r="E57" s="78"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="77"/>
-      <c r="B58" s="61"/>
+      <c r="B58" s="62"/>
       <c r="C58" s="57"/>
-      <c r="D58" s="62"/>
+      <c r="D58" s="63"/>
       <c r="E58" s="78"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="77"/>
-      <c r="B59" s="61"/>
+      <c r="B59" s="62"/>
       <c r="C59" s="57"/>
-      <c r="D59" s="62"/>
+      <c r="D59" s="63"/>
       <c r="E59" s="78"/>
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="77"/>
-      <c r="B60" s="61"/>
+      <c r="B60" s="62"/>
       <c r="C60" s="57"/>
-      <c r="D60" s="62"/>
+      <c r="D60" s="63"/>
       <c r="E60" s="78"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="77"/>
-      <c r="B61" s="61"/>
+      <c r="B61" s="62"/>
       <c r="C61" s="57"/>
-      <c r="D61" s="62"/>
+      <c r="D61" s="63"/>
       <c r="E61" s="78"/>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="77"/>
-      <c r="B62" s="61"/>
+      <c r="B62" s="62"/>
       <c r="C62" s="57"/>
-      <c r="D62" s="62"/>
+      <c r="D62" s="63"/>
       <c r="E62" s="78"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="77"/>
-      <c r="B63" s="61"/>
+      <c r="B63" s="62"/>
       <c r="C63" s="57"/>
-      <c r="D63" s="62"/>
+      <c r="D63" s="63"/>
       <c r="E63" s="78"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="77"/>
-      <c r="B64" s="61"/>
+      <c r="B64" s="62"/>
       <c r="C64" s="57"/>
-      <c r="D64" s="62"/>
+      <c r="D64" s="63"/>
       <c r="E64" s="78"/>
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="77"/>
-      <c r="B65" s="61"/>
+      <c r="B65" s="62"/>
       <c r="C65" s="57"/>
-      <c r="D65" s="62"/>
+      <c r="D65" s="63"/>
       <c r="E65" s="78"/>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="77"/>
-      <c r="B66" s="61"/>
+      <c r="B66" s="62"/>
       <c r="C66" s="57"/>
-      <c r="D66" s="62"/>
+      <c r="D66" s="63"/>
       <c r="E66" s="78"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="77"/>
-      <c r="B67" s="61"/>
+      <c r="B67" s="62"/>
       <c r="C67" s="57"/>
-      <c r="D67" s="62"/>
+      <c r="D67" s="63"/>
       <c r="E67" s="78"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
       <c r="A68" s="77"/>
-      <c r="B68" s="61"/>
+      <c r="B68" s="62"/>
       <c r="C68" s="57"/>
-      <c r="D68" s="62"/>
+      <c r="D68" s="63"/>
       <c r="E68" s="78"/>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="77"/>
-      <c r="B69" s="61"/>
+      <c r="B69" s="62"/>
       <c r="C69" s="57"/>
-      <c r="D69" s="62"/>
+      <c r="D69" s="63"/>
       <c r="E69" s="78"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
       <c r="A70" s="77"/>
-      <c r="B70" s="61"/>
+      <c r="B70" s="62"/>
       <c r="C70" s="57"/>
-      <c r="D70" s="62"/>
+      <c r="D70" s="63"/>
       <c r="E70" s="78"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c r="A71" s="77"/>
-      <c r="B71" s="61"/>
+      <c r="B71" s="62"/>
       <c r="C71" s="57"/>
-      <c r="D71" s="62"/>
+      <c r="D71" s="63"/>
       <c r="E71" s="78"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c r="A72" s="77"/>
-      <c r="B72" s="61"/>
+      <c r="B72" s="62"/>
       <c r="C72" s="57"/>
-      <c r="D72" s="62"/>
+      <c r="D72" s="63"/>
       <c r="E72" s="78"/>
     </row>
     <row r="73" ht="14.25" customHeight="1">
       <c r="A73" s="77"/>
-      <c r="B73" s="61"/>
+      <c r="B73" s="62"/>
       <c r="C73" s="57"/>
-      <c r="D73" s="62"/>
+      <c r="D73" s="63"/>
       <c r="E73" s="78"/>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c r="A74" s="77"/>
-      <c r="B74" s="61"/>
+      <c r="B74" s="62"/>
       <c r="C74" s="57"/>
-      <c r="D74" s="62"/>
+      <c r="D74" s="63"/>
       <c r="E74" s="78"/>
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="77"/>
-      <c r="B75" s="61"/>
+      <c r="B75" s="62"/>
       <c r="C75" s="57"/>
-      <c r="D75" s="62"/>
+      <c r="D75" s="63"/>
       <c r="E75" s="78"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="77"/>
-      <c r="B76" s="61"/>
+      <c r="B76" s="62"/>
       <c r="C76" s="57"/>
-      <c r="D76" s="62"/>
+      <c r="D76" s="63"/>
       <c r="E76" s="78"/>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="77"/>
-      <c r="B77" s="61"/>
+      <c r="B77" s="62"/>
       <c r="C77" s="57"/>
-      <c r="D77" s="62"/>
+      <c r="D77" s="63"/>
       <c r="E77" s="78"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="77"/>
-      <c r="B78" s="61"/>
+      <c r="B78" s="62"/>
       <c r="C78" s="57"/>
-      <c r="D78" s="62"/>
+      <c r="D78" s="63"/>
       <c r="E78" s="78"/>
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="77"/>
-      <c r="B79" s="61"/>
+      <c r="B79" s="62"/>
       <c r="C79" s="57"/>
-      <c r="D79" s="62"/>
+      <c r="D79" s="63"/>
       <c r="E79" s="78"/>
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="77"/>
-      <c r="B80" s="61"/>
+      <c r="B80" s="62"/>
       <c r="C80" s="57"/>
-      <c r="D80" s="62"/>
+      <c r="D80" s="63"/>
       <c r="E80" s="78"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="77"/>
-      <c r="B81" s="61"/>
+      <c r="B81" s="62"/>
       <c r="C81" s="57"/>
-      <c r="D81" s="62"/>
+      <c r="D81" s="63"/>
       <c r="E81" s="78"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="77"/>
-      <c r="B82" s="61"/>
+      <c r="B82" s="62"/>
       <c r="C82" s="57"/>
-      <c r="D82" s="62"/>
+      <c r="D82" s="63"/>
       <c r="E82" s="78"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="77"/>
-      <c r="B83" s="61"/>
+      <c r="B83" s="62"/>
       <c r="C83" s="57"/>
-      <c r="D83" s="62"/>
+      <c r="D83" s="63"/>
       <c r="E83" s="78"/>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="77"/>
-      <c r="B84" s="61"/>
+      <c r="B84" s="62"/>
       <c r="C84" s="57"/>
-      <c r="D84" s="62"/>
+      <c r="D84" s="63"/>
       <c r="E84" s="78"/>
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="77"/>
-      <c r="B85" s="61"/>
+      <c r="B85" s="62"/>
       <c r="C85" s="57"/>
-      <c r="D85" s="62"/>
+      <c r="D85" s="63"/>
       <c r="E85" s="78"/>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="77"/>
-      <c r="B86" s="61"/>
+      <c r="B86" s="62"/>
       <c r="C86" s="57"/>
-      <c r="D86" s="62"/>
+      <c r="D86" s="63"/>
       <c r="E86" s="78"/>
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="77"/>
-      <c r="B87" s="61"/>
+      <c r="B87" s="62"/>
       <c r="C87" s="57"/>
-      <c r="D87" s="62"/>
+      <c r="D87" s="63"/>
       <c r="E87" s="78"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="77"/>
-      <c r="B88" s="61"/>
+      <c r="B88" s="62"/>
       <c r="C88" s="57"/>
-      <c r="D88" s="62"/>
+      <c r="D88" s="63"/>
       <c r="E88" s="78"/>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="77"/>
-      <c r="B89" s="61"/>
+      <c r="B89" s="62"/>
       <c r="C89" s="57"/>
-      <c r="D89" s="62"/>
+      <c r="D89" s="63"/>
       <c r="E89" s="78"/>
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="77"/>
-      <c r="B90" s="61"/>
+      <c r="B90" s="62"/>
       <c r="C90" s="57"/>
-      <c r="D90" s="62"/>
+      <c r="D90" s="63"/>
       <c r="E90" s="78"/>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="77"/>
-      <c r="B91" s="61"/>
+      <c r="B91" s="62"/>
       <c r="C91" s="57"/>
-      <c r="D91" s="62"/>
+      <c r="D91" s="63"/>
       <c r="E91" s="78"/>
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="77"/>
-      <c r="B92" s="61"/>
+      <c r="B92" s="62"/>
       <c r="C92" s="57"/>
-      <c r="D92" s="62"/>
+      <c r="D92" s="63"/>
       <c r="E92" s="78"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="77"/>
-      <c r="B93" s="61"/>
+      <c r="B93" s="62"/>
       <c r="C93" s="57"/>
-      <c r="D93" s="62"/>
+      <c r="D93" s="63"/>
       <c r="E93" s="78"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="77"/>
-      <c r="B94" s="61"/>
+      <c r="B94" s="62"/>
       <c r="C94" s="57"/>
-      <c r="D94" s="62"/>
+      <c r="D94" s="63"/>
       <c r="E94" s="78"/>
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="77"/>
-      <c r="B95" s="61"/>
+      <c r="B95" s="62"/>
       <c r="C95" s="57"/>
-      <c r="D95" s="62"/>
+      <c r="D95" s="63"/>
       <c r="E95" s="78"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="77"/>
-      <c r="B96" s="61"/>
+      <c r="B96" s="62"/>
       <c r="C96" s="57"/>
-      <c r="D96" s="62"/>
+      <c r="D96" s="63"/>
       <c r="E96" s="78"/>
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="77"/>
-      <c r="B97" s="61"/>
+      <c r="B97" s="62"/>
       <c r="C97" s="57"/>
-      <c r="D97" s="62"/>
+      <c r="D97" s="63"/>
       <c r="E97" s="78"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="77"/>
-      <c r="B98" s="61"/>
+      <c r="B98" s="62"/>
       <c r="C98" s="57"/>
-      <c r="D98" s="62"/>
+      <c r="D98" s="63"/>
       <c r="E98" s="78"/>
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="77"/>
-      <c r="B99" s="61"/>
+      <c r="B99" s="62"/>
       <c r="C99" s="57"/>
-      <c r="D99" s="62"/>
+      <c r="D99" s="63"/>
       <c r="E99" s="78"/>
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="77"/>
-      <c r="B100" s="61"/>
+      <c r="B100" s="62"/>
       <c r="C100" s="57"/>
-      <c r="D100" s="62"/>
+      <c r="D100" s="63"/>
       <c r="E100" s="78"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="77"/>
-      <c r="B101" s="61"/>
+      <c r="B101" s="62"/>
       <c r="C101" s="57"/>
-      <c r="D101" s="62"/>
+      <c r="D101" s="63"/>
       <c r="E101" s="78"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="77"/>
-      <c r="B102" s="61"/>
+      <c r="B102" s="62"/>
       <c r="C102" s="57"/>
-      <c r="D102" s="62"/>
+      <c r="D102" s="63"/>
       <c r="E102" s="78"/>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="77"/>
-      <c r="B103" s="61"/>
+      <c r="B103" s="62"/>
       <c r="C103" s="57"/>
-      <c r="D103" s="62"/>
+      <c r="D103" s="63"/>
       <c r="E103" s="78"/>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="77"/>
-      <c r="B104" s="61"/>
+      <c r="B104" s="62"/>
       <c r="C104" s="57"/>
-      <c r="D104" s="62"/>
+      <c r="D104" s="63"/>
       <c r="E104" s="78"/>
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="77"/>
-      <c r="B105" s="61"/>
+      <c r="B105" s="62"/>
       <c r="C105" s="57"/>
-      <c r="D105" s="62"/>
+      <c r="D105" s="63"/>
       <c r="E105" s="78"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="77"/>
-      <c r="B106" s="61"/>
+      <c r="B106" s="62"/>
       <c r="C106" s="57"/>
-      <c r="D106" s="62"/>
+      <c r="D106" s="63"/>
       <c r="E106" s="78"/>
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="77"/>
-      <c r="B107" s="61"/>
+      <c r="B107" s="62"/>
       <c r="C107" s="57"/>
-      <c r="D107" s="62"/>
+      <c r="D107" s="63"/>
       <c r="E107" s="78"/>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c r="A108" s="77"/>
-      <c r="B108" s="61"/>
+      <c r="B108" s="62"/>
       <c r="C108" s="57"/>
-      <c r="D108" s="62"/>
+      <c r="D108" s="63"/>
       <c r="E108" s="78"/>
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="77"/>
-      <c r="B109" s="61"/>
+      <c r="B109" s="62"/>
       <c r="C109" s="57"/>
-      <c r="D109" s="62"/>
+      <c r="D109" s="63"/>
       <c r="E109" s="78"/>
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="77"/>
-      <c r="B110" s="61"/>
+      <c r="B110" s="62"/>
       <c r="C110" s="57"/>
-      <c r="D110" s="62"/>
+      <c r="D110" s="63"/>
       <c r="E110" s="78"/>
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="77"/>
-      <c r="B111" s="61"/>
+      <c r="B111" s="62"/>
       <c r="C111" s="57"/>
-      <c r="D111" s="62"/>
+      <c r="D111" s="63"/>
       <c r="E111" s="78"/>
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="77"/>
-      <c r="B112" s="61"/>
+      <c r="B112" s="62"/>
       <c r="C112" s="57"/>
-      <c r="D112" s="62"/>
+      <c r="D112" s="63"/>
       <c r="E112" s="78"/>
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="77"/>
-      <c r="B113" s="61"/>
+      <c r="B113" s="62"/>
       <c r="C113" s="57"/>
-      <c r="D113" s="62"/>
+      <c r="D113" s="63"/>
       <c r="E113" s="78"/>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="77"/>
-      <c r="B114" s="61"/>
+      <c r="B114" s="62"/>
       <c r="C114" s="57"/>
-      <c r="D114" s="62"/>
+      <c r="D114" s="63"/>
       <c r="E114" s="78"/>
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="77"/>
-      <c r="B115" s="61"/>
+      <c r="B115" s="62"/>
       <c r="C115" s="57"/>
-      <c r="D115" s="62"/>
+      <c r="D115" s="63"/>
       <c r="E115" s="78"/>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="77"/>
-      <c r="B116" s="61"/>
+      <c r="B116" s="62"/>
       <c r="C116" s="57"/>
-      <c r="D116" s="62"/>
+      <c r="D116" s="63"/>
       <c r="E116" s="78"/>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="77"/>
-      <c r="B117" s="61"/>
+      <c r="B117" s="62"/>
       <c r="C117" s="57"/>
-      <c r="D117" s="62"/>
+      <c r="D117" s="63"/>
       <c r="E117" s="78"/>
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="77"/>
-      <c r="B118" s="61"/>
+      <c r="B118" s="62"/>
       <c r="C118" s="57"/>
-      <c r="D118" s="62"/>
+      <c r="D118" s="63"/>
       <c r="E118" s="78"/>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="77"/>
-      <c r="B119" s="61"/>
+      <c r="B119" s="62"/>
       <c r="C119" s="57"/>
-      <c r="D119" s="62"/>
+      <c r="D119" s="63"/>
       <c r="E119" s="78"/>
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="77"/>
-      <c r="B120" s="61"/>
+      <c r="B120" s="62"/>
       <c r="C120" s="57"/>
-      <c r="D120" s="62"/>
+      <c r="D120" s="63"/>
       <c r="E120" s="78"/>
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="77"/>
-      <c r="B121" s="61"/>
+      <c r="B121" s="62"/>
       <c r="C121" s="57"/>
-      <c r="D121" s="62"/>
+      <c r="D121" s="63"/>
       <c r="E121" s="78"/>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="77"/>
-      <c r="B122" s="61"/>
+      <c r="B122" s="62"/>
       <c r="C122" s="57"/>
-      <c r="D122" s="62"/>
+      <c r="D122" s="63"/>
       <c r="E122" s="78"/>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="77"/>
-      <c r="B123" s="61"/>
+      <c r="B123" s="62"/>
       <c r="C123" s="57"/>
-      <c r="D123" s="62"/>
+      <c r="D123" s="63"/>
       <c r="E123" s="78"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="77"/>
-      <c r="B124" s="61"/>
+      <c r="B124" s="62"/>
       <c r="C124" s="57"/>
-      <c r="D124" s="62"/>
+      <c r="D124" s="63"/>
       <c r="E124" s="78"/>
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="77"/>
-      <c r="B125" s="61"/>
+      <c r="B125" s="62"/>
       <c r="C125" s="57"/>
-      <c r="D125" s="62"/>
+      <c r="D125" s="63"/>
       <c r="E125" s="78"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="77"/>
-      <c r="B126" s="61"/>
+      <c r="B126" s="62"/>
       <c r="C126" s="57"/>
-      <c r="D126" s="62"/>
+      <c r="D126" s="63"/>
       <c r="E126" s="78"/>
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="77"/>
-      <c r="B127" s="61"/>
+      <c r="B127" s="62"/>
       <c r="C127" s="57"/>
-      <c r="D127" s="62"/>
+      <c r="D127" s="63"/>
       <c r="E127" s="78"/>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="77"/>
-      <c r="B128" s="61"/>
+      <c r="B128" s="62"/>
       <c r="C128" s="57"/>
-      <c r="D128" s="62"/>
+      <c r="D128" s="63"/>
       <c r="E128" s="78"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="77"/>
-      <c r="B129" s="61"/>
+      <c r="B129" s="62"/>
       <c r="C129" s="57"/>
-      <c r="D129" s="62"/>
+      <c r="D129" s="63"/>
       <c r="E129" s="78"/>
     </row>
     <row r="130" ht="14.25" customHeight="1">
       <c r="A130" s="77"/>
-      <c r="B130" s="61"/>
+      <c r="B130" s="62"/>
       <c r="C130" s="57"/>
-      <c r="D130" s="62"/>
+      <c r="D130" s="63"/>
       <c r="E130" s="78"/>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c r="A131" s="77"/>
-      <c r="B131" s="61"/>
+      <c r="B131" s="62"/>
       <c r="C131" s="57"/>
-      <c r="D131" s="62"/>
+      <c r="D131" s="63"/>
       <c r="E131" s="78"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
       <c r="A132" s="77"/>
-      <c r="B132" s="61"/>
+      <c r="B132" s="62"/>
       <c r="C132" s="57"/>
-      <c r="D132" s="62"/>
+      <c r="D132" s="63"/>
       <c r="E132" s="78"/>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c r="A133" s="77"/>
-      <c r="B133" s="61"/>
+      <c r="B133" s="62"/>
       <c r="C133" s="57"/>
-      <c r="D133" s="62"/>
+      <c r="D133" s="63"/>
       <c r="E133" s="78"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c r="A134" s="77"/>
-      <c r="B134" s="61"/>
+      <c r="B134" s="62"/>
       <c r="C134" s="57"/>
-      <c r="D134" s="62"/>
+      <c r="D134" s="63"/>
       <c r="E134" s="78"/>
     </row>
     <row r="135" ht="14.25" customHeight="1">
       <c r="A135" s="77"/>
-      <c r="B135" s="61"/>
+      <c r="B135" s="62"/>
       <c r="C135" s="57"/>
-      <c r="D135" s="62"/>
+      <c r="D135" s="63"/>
       <c r="E135" s="78"/>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="77"/>
-      <c r="B136" s="61"/>
+      <c r="B136" s="62"/>
       <c r="C136" s="57"/>
-      <c r="D136" s="62"/>
+      <c r="D136" s="63"/>
       <c r="E136" s="78"/>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="77"/>
-      <c r="B137" s="61"/>
+      <c r="B137" s="62"/>
       <c r="C137" s="57"/>
-      <c r="D137" s="62"/>
+      <c r="D137" s="63"/>
       <c r="E137" s="78"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c r="A138" s="77"/>
-      <c r="B138" s="61"/>
+      <c r="B138" s="62"/>
       <c r="C138" s="57"/>
-      <c r="D138" s="62"/>
+      <c r="D138" s="63"/>
       <c r="E138" s="78"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
       <c r="A139" s="77"/>
-      <c r="B139" s="61"/>
+      <c r="B139" s="62"/>
       <c r="C139" s="57"/>
-      <c r="D139" s="62"/>
+      <c r="D139" s="63"/>
       <c r="E139" s="78"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
       <c r="A140" s="77"/>
-      <c r="B140" s="61"/>
+      <c r="B140" s="62"/>
       <c r="C140" s="57"/>
-      <c r="D140" s="62"/>
+      <c r="D140" s="63"/>
       <c r="E140" s="78"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="77"/>
-      <c r="B141" s="61"/>
+      <c r="B141" s="62"/>
       <c r="C141" s="57"/>
-      <c r="D141" s="62"/>
+      <c r="D141" s="63"/>
       <c r="E141" s="78"/>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c r="A142" s="77"/>
-      <c r="B142" s="61"/>
+      <c r="B142" s="62"/>
       <c r="C142" s="57"/>
-      <c r="D142" s="62"/>
+      <c r="D142" s="63"/>
       <c r="E142" s="78"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="77"/>
-      <c r="B143" s="61"/>
+      <c r="B143" s="62"/>
       <c r="C143" s="57"/>
-      <c r="D143" s="62"/>
+      <c r="D143" s="63"/>
       <c r="E143" s="78"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
       <c r="A144" s="77"/>
-      <c r="B144" s="61"/>
+      <c r="B144" s="62"/>
       <c r="C144" s="57"/>
-      <c r="D144" s="62"/>
+      <c r="D144" s="63"/>
       <c r="E144" s="78"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
       <c r="A145" s="77"/>
-      <c r="B145" s="61"/>
+      <c r="B145" s="62"/>
       <c r="C145" s="57"/>
-      <c r="D145" s="62"/>
+      <c r="D145" s="63"/>
       <c r="E145" s="78"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="77"/>
-      <c r="B146" s="61"/>
+      <c r="B146" s="62"/>
       <c r="C146" s="57"/>
-      <c r="D146" s="62"/>
+      <c r="D146" s="63"/>
       <c r="E146" s="78"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="77"/>
-      <c r="B147" s="61"/>
+      <c r="B147" s="62"/>
       <c r="C147" s="57"/>
-      <c r="D147" s="62"/>
+      <c r="D147" s="63"/>
       <c r="E147" s="78"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c r="A148" s="77"/>
-      <c r="B148" s="61"/>
+      <c r="B148" s="62"/>
       <c r="C148" s="57"/>
-      <c r="D148" s="62"/>
+      <c r="D148" s="63"/>
       <c r="E148" s="78"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c r="A149" s="77"/>
-      <c r="B149" s="61"/>
+      <c r="B149" s="62"/>
       <c r="C149" s="57"/>
-      <c r="D149" s="62"/>
+      <c r="D149" s="63"/>
       <c r="E149" s="78"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
       <c r="A150" s="77"/>
-      <c r="B150" s="61"/>
+      <c r="B150" s="62"/>
       <c r="C150" s="57"/>
-      <c r="D150" s="62"/>
+      <c r="D150" s="63"/>
       <c r="E150" s="78"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c r="A151" s="77"/>
-      <c r="B151" s="61"/>
+      <c r="B151" s="62"/>
       <c r="C151" s="57"/>
-      <c r="D151" s="62"/>
+      <c r="D151" s="63"/>
       <c r="E151" s="78"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c r="A152" s="77"/>
-      <c r="B152" s="61"/>
+      <c r="B152" s="62"/>
       <c r="C152" s="57"/>
-      <c r="D152" s="62"/>
+      <c r="D152" s="63"/>
       <c r="E152" s="78"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="77"/>
-      <c r="B153" s="61"/>
+      <c r="B153" s="62"/>
       <c r="C153" s="57"/>
-      <c r="D153" s="62"/>
+      <c r="D153" s="63"/>
       <c r="E153" s="78"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c r="A154" s="77"/>
-      <c r="B154" s="61"/>
+      <c r="B154" s="62"/>
       <c r="C154" s="57"/>
-      <c r="D154" s="62"/>
+      <c r="D154" s="63"/>
       <c r="E154" s="78"/>
     </row>
     <row r="155" ht="14.25" customHeight="1">
       <c r="A155" s="77"/>
-      <c r="B155" s="61"/>
+      <c r="B155" s="62"/>
       <c r="C155" s="57"/>
-      <c r="D155" s="62"/>
+      <c r="D155" s="63"/>
       <c r="E155" s="78"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="77"/>
-      <c r="B156" s="61"/>
+      <c r="B156" s="62"/>
       <c r="C156" s="57"/>
-      <c r="D156" s="62"/>
+      <c r="D156" s="63"/>
       <c r="E156" s="78"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c r="A157" s="77"/>
-      <c r="B157" s="61"/>
+      <c r="B157" s="62"/>
       <c r="C157" s="57"/>
-      <c r="D157" s="62"/>
+      <c r="D157" s="63"/>
       <c r="E157" s="78"/>
     </row>
     <row r="158" ht="14.25" customHeight="1">
       <c r="A158" s="77"/>
-      <c r="B158" s="61"/>
+      <c r="B158" s="62"/>
       <c r="C158" s="57"/>
-      <c r="D158" s="62"/>
+      <c r="D158" s="63"/>
       <c r="E158" s="78"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
       <c r="A159" s="77"/>
-      <c r="B159" s="61"/>
+      <c r="B159" s="62"/>
       <c r="C159" s="57"/>
-      <c r="D159" s="62"/>
+      <c r="D159" s="63"/>
       <c r="E159" s="78"/>
     </row>
     <row r="160" ht="14.25" customHeight="1">
       <c r="A160" s="77"/>
-      <c r="B160" s="61"/>
+      <c r="B160" s="62"/>
       <c r="C160" s="57"/>
-      <c r="D160" s="62"/>
+      <c r="D160" s="63"/>
       <c r="E160" s="78"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c r="A161" s="77"/>
-      <c r="B161" s="61"/>
+      <c r="B161" s="62"/>
       <c r="C161" s="57"/>
-      <c r="D161" s="62"/>
+      <c r="D161" s="63"/>
       <c r="E161" s="78"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c r="A162" s="77"/>
-      <c r="B162" s="61"/>
+      <c r="B162" s="62"/>
       <c r="C162" s="57"/>
-      <c r="D162" s="62"/>
+      <c r="D162" s="63"/>
       <c r="E162" s="78"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c r="A163" s="77"/>
-      <c r="B163" s="61"/>
+      <c r="B163" s="62"/>
       <c r="C163" s="57"/>
-      <c r="D163" s="62"/>
+      <c r="D163" s="63"/>
       <c r="E163" s="78"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c r="A164" s="77"/>
-      <c r="B164" s="61"/>
+      <c r="B164" s="62"/>
       <c r="C164" s="57"/>
-      <c r="D164" s="62"/>
+      <c r="D164" s="63"/>
       <c r="E164" s="78"/>
     </row>
     <row r="165" ht="14.25" customHeight="1">
       <c r="A165" s="77"/>
-      <c r="B165" s="61"/>
+      <c r="B165" s="62"/>
       <c r="C165" s="57"/>
-      <c r="D165" s="62"/>
+      <c r="D165" s="63"/>
       <c r="E165" s="78"/>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c r="A166" s="77"/>
-      <c r="B166" s="61"/>
+      <c r="B166" s="62"/>
       <c r="C166" s="57"/>
-      <c r="D166" s="62"/>
+      <c r="D166" s="63"/>
       <c r="E166" s="78"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c r="A167" s="77"/>
-      <c r="B167" s="61"/>
+      <c r="B167" s="62"/>
       <c r="C167" s="57"/>
-      <c r="D167" s="62"/>
+      <c r="D167" s="63"/>
       <c r="E167" s="78"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c r="A168" s="77"/>
-      <c r="B168" s="61"/>
+      <c r="B168" s="62"/>
       <c r="C168" s="57"/>
-      <c r="D168" s="62"/>
+      <c r="D168" s="63"/>
       <c r="E168" s="78"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c r="A169" s="77"/>
-      <c r="B169" s="61"/>
+      <c r="B169" s="62"/>
       <c r="C169" s="57"/>
-      <c r="D169" s="62"/>
+      <c r="D169" s="63"/>
       <c r="E169" s="78"/>
     </row>
     <row r="170" ht="14.25" customHeight="1">
       <c r="A170" s="77"/>
-      <c r="B170" s="61"/>
+      <c r="B170" s="62"/>
       <c r="C170" s="57"/>
-      <c r="D170" s="62"/>
+      <c r="D170" s="63"/>
       <c r="E170" s="78"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c r="A171" s="77"/>
-      <c r="B171" s="61"/>
+      <c r="B171" s="62"/>
       <c r="C171" s="57"/>
-      <c r="D171" s="62"/>
+      <c r="D171" s="63"/>
       <c r="E171" s="78"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
       <c r="A172" s="77"/>
-      <c r="B172" s="61"/>
+      <c r="B172" s="62"/>
       <c r="C172" s="57"/>
-      <c r="D172" s="62"/>
+      <c r="D172" s="63"/>
       <c r="E172" s="78"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c r="A173" s="77"/>
-      <c r="B173" s="61"/>
+      <c r="B173" s="62"/>
       <c r="C173" s="57"/>
-      <c r="D173" s="62"/>
+      <c r="D173" s="63"/>
       <c r="E173" s="78"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c r="A174" s="77"/>
-      <c r="B174" s="61"/>
+      <c r="B174" s="62"/>
       <c r="C174" s="57"/>
-      <c r="D174" s="62"/>
+      <c r="D174" s="63"/>
       <c r="E174" s="78"/>
     </row>
     <row r="175" ht="14.25" customHeight="1">
       <c r="A175" s="77"/>
-      <c r="B175" s="61"/>
+      <c r="B175" s="62"/>
       <c r="C175" s="57"/>
-      <c r="D175" s="62"/>
+      <c r="D175" s="63"/>
       <c r="E175" s="78"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c r="A176" s="77"/>
-      <c r="B176" s="61"/>
+      <c r="B176" s="62"/>
       <c r="C176" s="57"/>
-      <c r="D176" s="62"/>
+      <c r="D176" s="63"/>
       <c r="E176" s="78"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="77"/>
-      <c r="B177" s="61"/>
+      <c r="B177" s="62"/>
       <c r="C177" s="57"/>
-      <c r="D177" s="62"/>
+      <c r="D177" s="63"/>
       <c r="E177" s="78"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" s="77"/>
-      <c r="B178" s="61"/>
+      <c r="B178" s="62"/>
       <c r="C178" s="57"/>
-      <c r="D178" s="62"/>
+      <c r="D178" s="63"/>
       <c r="E178" s="78"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c r="A179" s="77"/>
-      <c r="B179" s="61"/>
+      <c r="B179" s="62"/>
       <c r="C179" s="57"/>
-      <c r="D179" s="62"/>
+      <c r="D179" s="63"/>
       <c r="E179" s="78"/>
     </row>
     <row r="180" ht="14.25" customHeight="1">
       <c r="A180" s="77"/>
-      <c r="B180" s="61"/>
+      <c r="B180" s="62"/>
       <c r="C180" s="57"/>
-      <c r="D180" s="62"/>
+      <c r="D180" s="63"/>
       <c r="E180" s="78"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c r="A181" s="77"/>
-      <c r="B181" s="61"/>
+      <c r="B181" s="62"/>
       <c r="C181" s="57"/>
-      <c r="D181" s="62"/>
+      <c r="D181" s="63"/>
       <c r="E181" s="78"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
       <c r="A182" s="77"/>
-      <c r="B182" s="61"/>
+      <c r="B182" s="62"/>
       <c r="C182" s="57"/>
-      <c r="D182" s="62"/>
+      <c r="D182" s="63"/>
       <c r="E182" s="78"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="A183" s="77"/>
-      <c r="B183" s="61"/>
+      <c r="B183" s="62"/>
       <c r="C183" s="57"/>
-      <c r="D183" s="62"/>
+      <c r="D183" s="63"/>
       <c r="E183" s="78"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="77"/>
-      <c r="B184" s="61"/>
+      <c r="B184" s="62"/>
       <c r="C184" s="57"/>
-      <c r="D184" s="62"/>
+      <c r="D184" s="63"/>
       <c r="E184" s="78"/>
     </row>
     <row r="185" ht="14.25" customHeight="1">
       <c r="A185" s="77"/>
-      <c r="B185" s="61"/>
+      <c r="B185" s="62"/>
       <c r="C185" s="57"/>
-      <c r="D185" s="62"/>
+      <c r="D185" s="63"/>
       <c r="E185" s="78"/>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c r="A186" s="77"/>
-      <c r="B186" s="61"/>
+      <c r="B186" s="62"/>
       <c r="C186" s="57"/>
-      <c r="D186" s="62"/>
+      <c r="D186" s="63"/>
       <c r="E186" s="78"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c r="A187" s="77"/>
-      <c r="B187" s="61"/>
+      <c r="B187" s="62"/>
       <c r="C187" s="57"/>
-      <c r="D187" s="62"/>
+      <c r="D187" s="63"/>
       <c r="E187" s="78"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c r="A188" s="77"/>
-      <c r="B188" s="61"/>
+      <c r="B188" s="62"/>
       <c r="C188" s="57"/>
-      <c r="D188" s="62"/>
+      <c r="D188" s="63"/>
       <c r="E188" s="78"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c r="A189" s="77"/>
-      <c r="B189" s="61"/>
+      <c r="B189" s="62"/>
       <c r="C189" s="57"/>
-      <c r="D189" s="62"/>
+      <c r="D189" s="63"/>
       <c r="E189" s="78"/>
     </row>
     <row r="190" ht="14.25" customHeight="1">
       <c r="A190" s="77"/>
-      <c r="B190" s="61"/>
+      <c r="B190" s="62"/>
       <c r="C190" s="57"/>
-      <c r="D190" s="62"/>
+      <c r="D190" s="63"/>
       <c r="E190" s="78"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c r="A191" s="77"/>
-      <c r="B191" s="61"/>
+      <c r="B191" s="62"/>
       <c r="C191" s="57"/>
-      <c r="D191" s="62"/>
+      <c r="D191" s="63"/>
       <c r="E191" s="78"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="77"/>
-      <c r="B192" s="61"/>
+      <c r="B192" s="62"/>
       <c r="C192" s="57"/>
-      <c r="D192" s="62"/>
+      <c r="D192" s="63"/>
       <c r="E192" s="78"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c r="A193" s="77"/>
-      <c r="B193" s="61"/>
+      <c r="B193" s="62"/>
       <c r="C193" s="57"/>
-      <c r="D193" s="62"/>
+      <c r="D193" s="63"/>
       <c r="E193" s="78"/>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c r="A194" s="77"/>
-      <c r="B194" s="61"/>
+      <c r="B194" s="62"/>
       <c r="C194" s="57"/>
-      <c r="D194" s="62"/>
+      <c r="D194" s="63"/>
       <c r="E194" s="78"/>
     </row>
     <row r="195" ht="14.25" customHeight="1">
       <c r="A195" s="77"/>
-      <c r="B195" s="61"/>
+      <c r="B195" s="62"/>
       <c r="C195" s="57"/>
-      <c r="D195" s="62"/>
+      <c r="D195" s="63"/>
       <c r="E195" s="78"/>
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c r="A196" s="77"/>
-      <c r="B196" s="61"/>
+      <c r="B196" s="62"/>
       <c r="C196" s="57"/>
-      <c r="D196" s="62"/>
+      <c r="D196" s="63"/>
       <c r="E196" s="78"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c r="A197" s="77"/>
-      <c r="B197" s="61"/>
+      <c r="B197" s="62"/>
       <c r="C197" s="57"/>
-      <c r="D197" s="62"/>
+      <c r="D197" s="63"/>
       <c r="E197" s="78"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c r="A198" s="77"/>
-      <c r="B198" s="61"/>
+      <c r="B198" s="62"/>
       <c r="C198" s="57"/>
-      <c r="D198" s="62"/>
+      <c r="D198" s="63"/>
       <c r="E198" s="78"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="77"/>
-      <c r="B199" s="61"/>
+      <c r="B199" s="62"/>
       <c r="C199" s="57"/>
-      <c r="D199" s="62"/>
+      <c r="D199" s="63"/>
       <c r="E199" s="78"/>
     </row>
     <row r="200" ht="14.25" customHeight="1">
       <c r="A200" s="77"/>
-      <c r="B200" s="61"/>
+      <c r="B200" s="62"/>
       <c r="C200" s="57"/>
-      <c r="D200" s="62"/>
+      <c r="D200" s="63"/>
       <c r="E200" s="78"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c r="A201" s="77"/>
-      <c r="B201" s="61"/>
+      <c r="B201" s="62"/>
       <c r="C201" s="57"/>
-      <c r="D201" s="62"/>
+      <c r="D201" s="63"/>
       <c r="E201" s="78"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c r="A202" s="77"/>
-      <c r="B202" s="61"/>
+      <c r="B202" s="62"/>
       <c r="C202" s="57"/>
-      <c r="D202" s="62"/>
+      <c r="D202" s="63"/>
       <c r="E202" s="78"/>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c r="A203" s="77"/>
-      <c r="B203" s="61"/>
+      <c r="B203" s="62"/>
       <c r="C203" s="57"/>
-      <c r="D203" s="62"/>
+      <c r="D203" s="63"/>
       <c r="E203" s="78"/>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c r="A204" s="77"/>
-      <c r="B204" s="61"/>
+      <c r="B204" s="62"/>
       <c r="C204" s="57"/>
-      <c r="D204" s="62"/>
+      <c r="D204" s="63"/>
       <c r="E204" s="78"/>
     </row>
     <row r="205" ht="14.25" customHeight="1">
       <c r="A205" s="77"/>
-      <c r="B205" s="61"/>
+      <c r="B205" s="62"/>
       <c r="C205" s="57"/>
-      <c r="D205" s="62"/>
+      <c r="D205" s="63"/>
       <c r="E205" s="78"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c r="A206" s="77"/>
-      <c r="B206" s="61"/>
+      <c r="B206" s="62"/>
       <c r="C206" s="57"/>
-      <c r="D206" s="62"/>
+      <c r="D206" s="63"/>
       <c r="E206" s="78"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="77"/>
-      <c r="B207" s="61"/>
+      <c r="B207" s="62"/>
       <c r="C207" s="57"/>
-      <c r="D207" s="62"/>
+      <c r="D207" s="63"/>
       <c r="E207" s="78"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
       <c r="A208" s="77"/>
-      <c r="B208" s="61"/>
+      <c r="B208" s="62"/>
       <c r="C208" s="57"/>
-      <c r="D208" s="62"/>
+      <c r="D208" s="63"/>
       <c r="E208" s="78"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
-      <c r="B209" s="61"/>
+      <c r="B209" s="62"/>
       <c r="D209" s="32"/>
       <c r="E209" s="79"/>
     </row>
     <row r="210" ht="14.25" customHeight="1">
-      <c r="B210" s="61"/>
+      <c r="B210" s="62"/>
       <c r="D210" s="32"/>
       <c r="E210" s="79"/>
     </row>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1917,11 +1917,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1066563110"/>
-        <c:axId val="600694185"/>
+        <c:axId val="1465629420"/>
+        <c:axId val="1652203528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1066563110"/>
+        <c:axId val="1465629420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1973,10 +1973,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="600694185"/>
+        <c:crossAx val="1652203528"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="600694185"/>
+        <c:axId val="1652203528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2040,7 +2040,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1066563110"/>
+        <c:crossAx val="1465629420"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="J5" s="8">
         <f>SUMIFS(D:D,A:A,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A:A,"&lt;&gt;")</f>
-        <v>13415.75</v>
+        <v>13945.75</v>
       </c>
       <c r="L5" s="10">
         <v>46023.0</v>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B7" s="6">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>17822.54</v>
+        <v>17292.54</v>
       </c>
       <c r="C7" s="6">
         <f>IF($A7="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2984,11 +2984,11 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>-679.54</v>
+        <v>-149.54</v>
       </c>
       <c r="E7" s="4">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4">
         <f>IF($A7="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2996,14 +2996,14 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>13415.75</v>
+        <v>13945.75</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(D:D,A:A,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A:A,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>-679.54</v>
+        <v>-149.54</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="B8" s="3">
         <f>IF($A8="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>13969.11</v>
+        <v>14499.11</v>
       </c>
       <c r="C8" s="3">
         <f>IF($A8="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -3021,11 +3021,11 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" si="1"/>
-        <v>-1289.11</v>
+        <v>-1819.11</v>
       </c>
       <c r="E8" s="4">
         <f>IF($A8="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A8,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A8,1)))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="4">
         <f>IF($A8="","",COUNTIFS('Salários'!$B:$B,"&gt;="&amp;$A8,'Salários'!$B:$B,"&lt;"&amp;EDATE($A8,1)))</f>
@@ -14637,14 +14637,14 @@
       <c r="H137" s="58"/>
     </row>
     <row r="138" ht="14.25" customHeight="1">
-      <c r="A138" s="46">
-        <v>46192.0</v>
-      </c>
-      <c r="B138" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C138" s="49">
-        <v>530.0</v>
+      <c r="A138" s="34">
+        <v>46193.0</v>
+      </c>
+      <c r="B138" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C138" s="47">
+        <v>5931.43</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="42"/>
@@ -14652,14 +14652,14 @@
       <c r="H138" s="58"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="34">
+      <c r="A139" s="46">
         <v>46193.0</v>
       </c>
-      <c r="B139" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C139" s="47">
-        <v>5931.43</v>
+      <c r="B139" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C139" s="49">
+        <v>113.31</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="42"/>
@@ -14667,14 +14667,14 @@
       <c r="H139" s="58"/>
     </row>
     <row r="140" ht="14.25" customHeight="1">
-      <c r="A140" s="46">
+      <c r="A140" s="34">
         <v>46193.0</v>
       </c>
-      <c r="B140" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C140" s="49">
-        <v>113.31</v>
+      <c r="B140" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="C140" s="47">
+        <v>120.0</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="42"/>
@@ -14683,13 +14683,13 @@
     </row>
     <row r="141" ht="14.25" customHeight="1">
       <c r="A141" s="34">
-        <v>46193.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B141" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C141" s="47">
-        <v>120.0</v>
+        <v>40</v>
+      </c>
+      <c r="C141" s="49">
+        <v>930.0</v>
       </c>
       <c r="D141" s="42"/>
       <c r="E141" s="42"/>
@@ -14700,41 +14700,41 @@
       <c r="A142" s="34">
         <v>46205.0</v>
       </c>
-      <c r="B142" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C142" s="49">
-        <v>930.0</v>
-      </c>
-      <c r="D142" s="42"/>
-      <c r="E142" s="42"/>
+      <c r="B142" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C142" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D142" s="35"/>
+      <c r="E142" s="35"/>
       <c r="G142" s="57"/>
       <c r="H142" s="58"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="34">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B143" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C143" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D143" s="35"/>
-      <c r="E143" s="35"/>
+        <v>60</v>
+      </c>
+      <c r="C143" s="49">
+        <v>950.0</v>
+      </c>
+      <c r="D143" s="42"/>
+      <c r="E143" s="42"/>
       <c r="G143" s="57"/>
       <c r="H143" s="58"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="34">
-        <v>46209.0</v>
+      <c r="A144" s="46">
+        <v>46210.0</v>
       </c>
       <c r="B144" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C144" s="49">
-        <v>950.0</v>
+        <v>44</v>
+      </c>
+      <c r="C144" s="47">
+        <v>110.0</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42"/>
@@ -14745,14 +14745,14 @@
       <c r="J144" s="41"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="46">
-        <v>46210.0</v>
-      </c>
-      <c r="B145" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C145" s="47">
-        <v>110.0</v>
+      <c r="A145" s="34">
+        <v>46213.0</v>
+      </c>
+      <c r="B145" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145" s="49">
+        <v>65.0</v>
       </c>
       <c r="D145" s="42"/>
       <c r="E145" s="42"/>
@@ -14764,13 +14764,13 @@
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="34">
-        <v>46213.0</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>78</v>
+        <v>46214.0</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C146" s="49">
-        <v>65.0</v>
+        <v>95.12</v>
       </c>
       <c r="D146" s="42"/>
       <c r="E146" s="42"/>
@@ -14779,13 +14779,13 @@
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="34">
-        <v>46214.0</v>
-      </c>
-      <c r="B147" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C147" s="49">
-        <v>95.12</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B147" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C147" s="47">
+        <v>981.88</v>
       </c>
       <c r="D147" s="42"/>
       <c r="E147" s="42"/>
@@ -14796,11 +14796,11 @@
       <c r="A148" s="34">
         <v>46215.0</v>
       </c>
-      <c r="B148" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C148" s="47">
-        <v>981.88</v>
+      <c r="B148" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="C148" s="49">
+        <v>2831.4</v>
       </c>
       <c r="D148" s="42"/>
       <c r="E148" s="42"/>
@@ -14811,11 +14811,11 @@
       <c r="A149" s="34">
         <v>46215.0</v>
       </c>
-      <c r="B149" s="42" t="s">
-        <v>71</v>
+      <c r="B149" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C149" s="49">
-        <v>2831.4</v>
+        <v>50.0</v>
       </c>
       <c r="D149" s="42"/>
       <c r="E149" s="42"/>
@@ -14823,14 +14823,14 @@
       <c r="H149" s="58"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="34">
-        <v>46215.0</v>
+      <c r="A150" s="46">
+        <v>46218.0</v>
       </c>
       <c r="B150" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C150" s="49">
-        <v>50.0</v>
+        <v>91</v>
+      </c>
+      <c r="C150" s="47">
+        <v>60.0</v>
       </c>
       <c r="D150" s="42"/>
       <c r="E150" s="42"/>
@@ -14838,14 +14838,14 @@
       <c r="H150" s="58"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="46">
+      <c r="A151" s="34">
         <v>46218.0</v>
       </c>
       <c r="B151" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C151" s="47">
-        <v>60.0</v>
+        <v>62</v>
+      </c>
+      <c r="C151" s="49">
+        <v>132.4</v>
       </c>
       <c r="D151" s="42"/>
       <c r="E151" s="42"/>
@@ -14853,14 +14853,14 @@
       <c r="H151" s="58"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="34">
+      <c r="A152" s="46">
         <v>46218.0</v>
       </c>
       <c r="B152" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C152" s="49">
-        <v>132.4</v>
+        <v>103</v>
+      </c>
+      <c r="C152" s="47">
+        <v>50.0</v>
       </c>
       <c r="D152" s="42"/>
       <c r="E152" s="42"/>
@@ -14869,13 +14869,13 @@
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="46">
-        <v>46218.0</v>
-      </c>
-      <c r="B153" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C153" s="47">
-        <v>50.0</v>
+        <v>46222.0</v>
+      </c>
+      <c r="B153" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C153" s="49">
+        <v>530.0</v>
       </c>
       <c r="D153" s="42"/>
       <c r="E153" s="42"/>

--- a/dados/dados_financeiros.xlsx
+++ b/dados/dados_financeiros.xlsx
@@ -1920,11 +1920,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="755235438"/>
-        <c:axId val="1642839468"/>
+        <c:axId val="817208267"/>
+        <c:axId val="26482938"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="755235438"/>
+        <c:axId val="817208267"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1976,10 +1976,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1642839468"/>
+        <c:crossAx val="26482938"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1642839468"/>
+        <c:axId val="26482938"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2043,7 +2043,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="755235438"/>
+        <c:crossAx val="817208267"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2301,11 +2301,12 @@
         <n v="16.15"/>
         <n v="48.85"/>
         <n v="5931.43"/>
-        <n v="113.31"/>
+        <n v="80.92"/>
         <n v="280.0"/>
         <n v="930.0"/>
         <n v="981.88"/>
         <n v="6800.0"/>
+        <n v="113.31"/>
         <n v="1500.0"/>
         <n v="5800.0"/>
         <n v="2000.0"/>
@@ -2498,6 +2499,7 @@
         <item x="129"/>
         <item x="130"/>
         <item x="131"/>
+        <item x="132"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2850,7 +2852,7 @@
       </c>
       <c r="J3" s="8">
         <f>SUM(B:B)</f>
-        <v>262722.75</v>
+        <v>262690.36</v>
       </c>
       <c r="L3" s="9">
         <f>EOMONTH(MAX(MAX('Todos os Gastos'!$A:$A),MAX('Salários'!$B:$B)),-1)+1</f>
@@ -2931,7 +2933,7 @@
       </c>
       <c r="J5" s="8">
         <f>SUMIFS(D:D,A:A,"&lt;="&amp;EOMONTH(TODAY(),0)+1-1,A:A,"&lt;&gt;")</f>
-        <v>13785.75</v>
+        <v>13818.14</v>
       </c>
       <c r="L5" s="10">
         <v>46023.0</v>
@@ -2970,8 +2972,8 @@
         <v>13</v>
       </c>
       <c r="J6" s="8">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-4174.419999999995)</f>
-        <v>-4174.42</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("INDEX(G:G, MAX(FILTER(ROW(G:G), G:G&lt;&gt;"""")))"),-4142.029999999992)</f>
+        <v>-4142.03</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -2981,7 +2983,7 @@
       </c>
       <c r="B7" s="6">
         <f>IF($A7="","",SUMIFS('Todos os Gastos'!$C:$C,'Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
-        <v>17452.54</v>
+        <v>17420.15</v>
       </c>
       <c r="C7" s="6">
         <f>IF($A7="","",SUMIFS('Salários'!$D:$D,'Salários'!$B:$B,"&gt;="&amp;$A7,'Salários'!$B:$B,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -2989,7 +2991,7 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="1"/>
-        <v>-309.54</v>
+        <v>-277.15</v>
       </c>
       <c r="E7" s="4">
         <f>IF($A7="","",COUNTIFS('Todos os Gastos'!$A:$A,"&gt;="&amp;$A7,'Todos os Gastos'!$A:$A,"&lt;"&amp;EDATE($A7,1)))</f>
@@ -3001,14 +3003,14 @@
       </c>
       <c r="G7" s="6">
         <f t="shared" si="2"/>
-        <v>13785.75</v>
+        <v>13818.14</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(D:D,A:A,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,A:A,"&lt;"&amp;EDATE(EOMONTH(TODAY(),-1)+1,1))</f>
-        <v>-309.54</v>
+        <v>-277.15</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -3038,14 +3040,14 @@
       </c>
       <c r="G8" s="3">
         <f t="shared" si="2"/>
-        <v>11846.64</v>
+        <v>11879.03</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="8">
         <f>AVERAGEIF(D:D,"&lt;&gt;",D:D)</f>
-        <v>-245.5541176</v>
+        <v>-243.6488235</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -3075,7 +3077,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="2"/>
-        <v>10425.66</v>
+        <v>10458.05</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>16</v>
@@ -3112,7 +3114,7 @@
       </c>
       <c r="G10" s="3">
         <f t="shared" si="2"/>
-        <v>8436.48</v>
+        <v>8468.87</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>17</v>
@@ -3149,7 +3151,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="2"/>
-        <v>6847.5</v>
+        <v>6879.89</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>18</v>
@@ -3186,7 +3188,7 @@
       </c>
       <c r="G12" s="3">
         <f t="shared" si="2"/>
-        <v>5758.32</v>
+        <v>5790.71</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>19</v>
@@ -3223,7 +3225,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="2"/>
-        <v>1549.14</v>
+        <v>1581.53</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -3253,7 +3255,7 @@
       </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>4388.88</v>
+        <v>4421.27</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -3283,7 +3285,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="2"/>
-        <v>1317.98</v>
+        <v>1350.37</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -3313,7 +3315,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>-1863.14</v>
+        <v>-1830.75</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -3343,7 +3345,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="2"/>
-        <v>-6216.19</v>
+        <v>-6183.8</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
@@ -3373,7 +3375,7 @@
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>-4174.42</v>
+        <v>-4142.03</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
@@ -14663,8 +14665,8 @@
       <c r="B139" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="C139" s="49">
-        <v>113.31</v>
+      <c r="C139" s="47">
+        <v>80.92</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="42"/>
@@ -14687,14 +14689,14 @@
       <c r="H140" s="58"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c r="A141" s="46">
-        <v>46223.0</v>
+      <c r="A141" s="34">
+        <v>46205.0</v>
       </c>
       <c r="B141" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C141" s="47">
-        <v>120.0</v>
+        <v>40</v>
+      </c>
+      <c r="C141" s="49">
+        <v>930.0</v>
       </c>
       <c r="D141" s="42"/>
       <c r="E141" s="42"/>
@@ -14705,41 +14707,41 @@
       <c r="A142" s="34">
         <v>46205.0</v>
       </c>
-      <c r="B142" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="C142" s="49">
-        <v>930.0</v>
-      </c>
-      <c r="D142" s="42"/>
-      <c r="E142" s="42"/>
+      <c r="B142" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C142" s="47">
+        <v>400.0</v>
+      </c>
+      <c r="D142" s="35"/>
+      <c r="E142" s="35"/>
       <c r="G142" s="57"/>
       <c r="H142" s="58"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
       <c r="A143" s="34">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B143" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C143" s="47">
-        <v>400.0</v>
-      </c>
-      <c r="D143" s="35"/>
-      <c r="E143" s="35"/>
+        <v>60</v>
+      </c>
+      <c r="C143" s="49">
+        <v>950.0</v>
+      </c>
+      <c r="D143" s="42"/>
+      <c r="E143" s="42"/>
       <c r="G143" s="57"/>
       <c r="H143" s="58"/>
     </row>
     <row r="144" ht="14.25" customHeight="1">
-      <c r="A144" s="34">
-        <v>46209.0</v>
+      <c r="A144" s="46">
+        <v>46210.0</v>
       </c>
       <c r="B144" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C144" s="49">
-        <v>950.0</v>
+        <v>44</v>
+      </c>
+      <c r="C144" s="47">
+        <v>110.0</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="42"/>
@@ -14747,14 +14749,14 @@
       <c r="H144" s="58"/>
     </row>
     <row r="145" ht="14.25" customHeight="1">
-      <c r="A145" s="46">
-        <v>46210.0</v>
-      </c>
-      <c r="B145" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C145" s="47">
-        <v>110.0</v>
+      <c r="A145" s="34">
+        <v>46213.0</v>
+      </c>
+      <c r="B145" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145" s="49">
+        <v>65.0</v>
       </c>
       <c r="D145" s="42"/>
       <c r="E145" s="42"/>
@@ -14766,13 +14768,13 @@
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c r="A146" s="34">
-        <v>46213.0</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>78</v>
+        <v>46214.0</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="C146" s="49">
-        <v>65.0</v>
+        <v>95.12</v>
       </c>
       <c r="D146" s="42"/>
       <c r="E146" s="42"/>
@@ -14784,13 +14786,13 @@
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c r="A147" s="34">
-        <v>46214.0</v>
-      </c>
-      <c r="B147" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C147" s="49">
-        <v>95.12</v>
+        <v>46215.0</v>
+      </c>
+      <c r="B147" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C147" s="47">
+        <v>981.88</v>
       </c>
       <c r="D147" s="42"/>
       <c r="E147" s="42"/>
@@ -14801,11 +14803,11 @@
       <c r="A148" s="34">
         <v>46215.0</v>
       </c>
-      <c r="B148" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C148" s="47">
-        <v>981.88</v>
+      <c r="B148" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="C148" s="49">
+        <v>2831.4</v>
       </c>
       <c r="D148" s="42"/>
       <c r="E148" s="42"/>
@@ -14816,11 +14818,11 @@
       <c r="A149" s="34">
         <v>46215.0</v>
       </c>
-      <c r="B149" s="42" t="s">
-        <v>71</v>
+      <c r="B149" s="43" t="s">
+        <v>56</v>
       </c>
       <c r="C149" s="49">
-        <v>2831.4</v>
+        <v>50.0</v>
       </c>
       <c r="D149" s="42"/>
       <c r="E149" s="42"/>
@@ -14828,14 +14830,14 @@
       <c r="H149" s="58"/>
     </row>
     <row r="150" ht="14.25" customHeight="1">
-      <c r="A150" s="34">
-        <v>46215.0</v>
+      <c r="A150" s="46">
+        <v>46218.0</v>
       </c>
       <c r="B150" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C150" s="49">
-        <v>50.0</v>
+        <v>91</v>
+      </c>
+      <c r="C150" s="47">
+        <v>60.0</v>
       </c>
       <c r="D150" s="42"/>
       <c r="E150" s="42"/>
@@ -14843,14 +14845,14 @@
       <c r="H150" s="58"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="46">
+      <c r="A151" s="34">
         <v>46218.0</v>
       </c>
       <c r="B151" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C151" s="47">
-        <v>60.0</v>
+        <v>62</v>
+      </c>
+      <c r="C151" s="49">
+        <v>132.4</v>
       </c>
       <c r="D151" s="42"/>
       <c r="E151" s="42"/>
@@ -14858,14 +14860,14 @@
       <c r="H151" s="58"/>
     </row>
     <row r="152" ht="14.25" customHeight="1">
-      <c r="A152" s="34">
+      <c r="A152" s="46">
         <v>46218.0</v>
       </c>
       <c r="B152" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C152" s="49">
-        <v>132.4</v>
+        <v>104</v>
+      </c>
+      <c r="C152" s="47">
+        <v>50.0</v>
       </c>
       <c r="D152" s="42"/>
       <c r="E152" s="42"/>
@@ -14874,13 +14876,13 @@
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="46">
-        <v>46218.0</v>
-      </c>
-      <c r="B153" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="C153" s="47">
-        <v>50.0</v>
+        <v>46222.0</v>
+      </c>
+      <c r="B153" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C153" s="49">
+        <v>530.0</v>
       </c>
       <c r="D153" s="42"/>
       <c r="E153" s="42"/>
@@ -14888,14 +14890,14 @@
       <c r="H153" s="58"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="46">
-        <v>46222.0</v>
-      </c>
-      <c r="B154" s="42" t="s">
-        <v>66</v>
+      <c r="A154" s="34">
+        <v>46223.0</v>
+      </c>
+      <c r="B154" s="35" t="s">
+        <v>36</v>
       </c>
       <c r="C154" s="49">
-        <v>530.0</v>
+        <v>6800.0</v>
       </c>
       <c r="D154" s="42"/>
       <c r="E154" s="42"/>
@@ -14906,11 +14908,11 @@
       <c r="A155" s="34">
         <v>46223.0</v>
       </c>
-      <c r="B155" s="35" t="s">
-        <v>36</v>
+      <c r="B155" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C155" s="49">
-        <v>6800.0</v>
+        <v>113.31</v>
       </c>
       <c r="D155" s="42"/>
       <c r="E155" s="42"/>
@@ -14918,14 +14920,14 @@
       <c r="H155" s="58"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c r="A156" s="34">
+      <c r="A156" s="46">
         <v>46223.0</v>
       </c>
-      <c r="B156" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C156" s="49">
-        <v>113.31</v>
+      <c r="B156" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="C156" s="47">
+        <v>120.0</v>
       </c>
       <c r="D156" s="42"/>
       <c r="E156" s="42"/>
